--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.39" customWidth="1" style="19" min="1" max="2"/>
@@ -6727,7 +6727,29 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="21"/>
+    <row r="101" ht="15" customHeight="1" s="21">
+      <c r="A101" t="n">
+        <v>-350</v>
+      </c>
+      <c r="B101" t="n">
+        <v>-280</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>- 350 A JC  - 280 A JC</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>TESTUS Philosophus</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Fiche de test pour valider le bat.&lt;/p&gt;</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.39" customWidth="1" style="19" min="1" max="2"/>
@@ -6727,29 +6727,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="21">
-      <c r="A101" t="n">
-        <v>-350</v>
-      </c>
-      <c r="B101" t="n">
-        <v>-280</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>- 350 A JC  - 280 A JC</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>TESTUS Philosophus</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Fiche de test pour valider le bat.&lt;/p&gt;</t>
-        </is>
-      </c>
-    </row>
+    <row r="101" ht="15" customHeight="1" s="21"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.39" customWidth="1" style="19" min="1" max="2"/>
@@ -6727,7 +6727,34 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="21"/>
+    <row r="101" ht="15" customHeight="1" s="21">
+      <c r="A101" t="n">
+        <v>-350</v>
+      </c>
+      <c r="B101" t="n">
+        <v>-280</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>- 350 A JC  - 280 A JC</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DEMO Test Philosophe</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Fiche de demonstration complete (xlsx + portrait).&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>/pho/demo-test-philosophe-mini.webp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.39" customWidth="1" style="19" min="1" max="2"/>
@@ -6727,34 +6727,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="21">
-      <c r="A101" t="n">
-        <v>-350</v>
-      </c>
-      <c r="B101" t="n">
-        <v>-280</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>- 350 A JC  - 280 A JC</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>DEMO Test Philosophe</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Fiche de demonstration complete (xlsx + portrait).&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>/pho/demo-test-philosophe-mini.webp</t>
-        </is>
-      </c>
-    </row>
+    <row r="101" ht="15" customHeight="1" s="21"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="824">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES GRÉCO-ROMAINS</t>
   </si>
@@ -372,6 +372,9 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/empedocle-mini.webp</t>
   </si>
   <si>
+    <t xml:space="preserve"> poète, orateur et philosophe, figure quasi mythique de son vivant, que la légende dit mort en se jetant dans l'Etna pour prouver sa divinité.</t>
+  </si>
+  <si>
     <t xml:space="preserve">-420</t>
   </si>
   <si>
@@ -1536,6 +1539,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/telecles-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> philosophe grec représentant de la moyenne académie platonicienne.</t>
   </si>
   <si>
     <t xml:space="preserve">-109</t>
@@ -1942,6 +1948,7 @@
         <sz val="9"/>
         <rFont val="Microsoft YaHei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">｜</t>
     </r>
@@ -2678,7 +2685,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2752,6 +2759,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -2779,15 +2793,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2880,80 +2894,84 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3719,44 +3737,47 @@
       <c r="L14" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="M14" s="11" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
         <v>-490</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="11" t="s">
         <v>113</v>
       </c>
+      <c r="E15" s="12" t="s">
+        <v>114</v>
+      </c>
       <c r="F15" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3764,38 +3785,38 @@
         <v>-490</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3803,38 +3824,38 @@
         <v>-480</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E17" s="11" t="s">
         <v>132</v>
       </c>
+      <c r="E17" s="12" t="s">
+        <v>133</v>
+      </c>
       <c r="F17" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3842,38 +3863,38 @@
         <v>-470</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3881,25 +3902,25 @@
         <v>-470</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="2" t="s">
@@ -3912,7 +3933,7 @@
         <v>24</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3920,25 +3941,25 @@
         <v>-465</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="2" t="s">
@@ -3948,10 +3969,10 @@
         <v>58</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="193.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3959,38 +3980,38 @@
         <v>-460</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="E21" s="12" t="s">
         <v>168</v>
       </c>
+      <c r="E21" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="F21" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3998,38 +4019,38 @@
         <v>-459</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E22" s="13" t="s">
         <v>176</v>
       </c>
+      <c r="E22" s="14" t="s">
+        <v>177</v>
+      </c>
       <c r="F22" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4037,38 +4058,38 @@
         <v>-450</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4076,38 +4097,38 @@
         <v>-445</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4115,38 +4136,38 @@
         <v>-436</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="154.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4154,38 +4175,38 @@
         <v>-435</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4193,25 +4214,25 @@
         <v>-430</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="2" t="s">
@@ -4221,10 +4242,10 @@
         <v>23</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="232.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4232,38 +4253,38 @@
         <v>-428</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4271,38 +4292,38 @@
         <v>-412</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4310,38 +4331,38 @@
         <v>-408</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="E30" s="11" t="s">
         <v>246</v>
       </c>
+      <c r="E30" s="12" t="s">
+        <v>247</v>
+      </c>
       <c r="F30" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4349,25 +4370,25 @@
         <v>-407</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="2" t="s">
@@ -4377,10 +4398,10 @@
         <v>33</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="152.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4388,38 +4409,38 @@
         <v>-405</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G32" s="14" t="s">
         <v>265</v>
       </c>
+      <c r="G32" s="15" t="s">
+        <v>266</v>
+      </c>
       <c r="H32" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4427,38 +4448,38 @@
         <v>-400</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4466,38 +4487,38 @@
         <v>-396</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4505,25 +4526,25 @@
         <v>-385</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="2" t="s">
@@ -4533,10 +4554,10 @@
         <v>33</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4544,38 +4565,38 @@
         <v>-384</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4583,38 +4604,38 @@
         <v>-380</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="H37" s="11" t="s">
         <v>308</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>309</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4622,38 +4643,38 @@
         <v>-370</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4661,38 +4682,38 @@
         <v>-365</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4700,38 +4721,38 @@
         <v>-365</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="221.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4739,38 +4760,38 @@
         <v>-362</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4778,38 +4799,38 @@
         <v>-360</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4817,38 +4838,38 @@
         <v>-360</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4856,38 +4877,38 @@
         <v>-341</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="E44" s="13" t="s">
         <v>362</v>
       </c>
+      <c r="E44" s="14" t="s">
+        <v>363</v>
+      </c>
       <c r="F44" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4895,38 +4916,38 @@
         <v>-340</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4934,38 +4955,38 @@
         <v>-334</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4973,38 +4994,38 @@
         <v>-330</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5012,38 +5033,38 @@
         <v>-325</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5051,38 +5072,38 @@
         <v>-315</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5090,25 +5111,25 @@
         <v>-306</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="2" t="s">
@@ -5118,10 +5139,10 @@
         <v>23</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="209.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5129,38 +5150,38 @@
         <v>-281</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5168,38 +5189,38 @@
         <v>-280</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5207,40 +5228,40 @@
         <v>-240</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="I53" s="11" t="s">
         <v>443</v>
       </c>
+      <c r="I53" s="12" t="s">
+        <v>444</v>
+      </c>
       <c r="J53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5248,38 +5269,38 @@
         <v>-230</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="E54" s="11" t="s">
         <v>448</v>
       </c>
+      <c r="E54" s="12" t="s">
+        <v>449</v>
+      </c>
       <c r="F54" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="G54" s="14" t="s">
         <v>450</v>
       </c>
+      <c r="G54" s="15" t="s">
+        <v>451</v>
+      </c>
       <c r="H54" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5287,38 +5308,38 @@
         <v>-213</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="E55" s="11" t="s">
         <v>456</v>
       </c>
+      <c r="E55" s="12" t="s">
+        <v>457</v>
+      </c>
       <c r="F55" s="7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5326,38 +5347,38 @@
         <v>-210</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5365,35 +5386,38 @@
         <v>-204</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="E57" s="11" t="s">
         <v>472</v>
       </c>
+      <c r="E57" s="12" t="s">
+        <v>473</v>
+      </c>
       <c r="F57" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5401,25 +5425,25 @@
         <v>-185</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>481</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="2" t="s">
@@ -5429,10 +5453,10 @@
         <v>23</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5440,25 +5464,25 @@
         <v>-135</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>489</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="2" t="s">
@@ -5468,10 +5492,10 @@
         <v>33</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5479,38 +5503,38 @@
         <v>-110</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5518,38 +5542,38 @@
         <v>-106</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5557,38 +5581,38 @@
         <v>-94</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5596,38 +5620,38 @@
         <v>-80</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5635,38 +5659,38 @@
         <v>-20</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>75</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5674,38 +5698,38 @@
         <v>-4</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>542</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5713,25 +5737,25 @@
         <v>10</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>550</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="2" t="s">
@@ -5741,10 +5765,10 @@
         <v>58</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5752,38 +5776,38 @@
         <v>15</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5791,38 +5815,38 @@
         <v>46</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5830,38 +5854,38 @@
         <v>50</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>64</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5869,25 +5893,25 @@
         <v>60</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="2" t="s">
@@ -5897,10 +5921,10 @@
         <v>33</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5908,38 +5932,38 @@
         <v>121</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5947,38 +5971,38 @@
         <v>175</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>75</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5986,38 +6010,38 @@
         <v>205</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>75</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="186.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6025,38 +6049,38 @@
         <v>213</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="G74" s="14" t="s">
-        <v>614</v>
+        <v>615</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>616</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6064,25 +6088,25 @@
         <v>234</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="2" t="s">
@@ -6092,10 +6116,10 @@
         <v>75</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6106,35 +6130,35 @@
         <v>325</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="H76" s="11" t="s">
-        <v>630</v>
+        <v>631</v>
+      </c>
+      <c r="H76" s="12" t="s">
+        <v>632</v>
       </c>
       <c r="I76" s="9"/>
       <c r="J76" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>75</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6142,38 +6166,38 @@
         <v>290</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>75</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6181,38 +6205,38 @@
         <v>317</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6220,38 +6244,38 @@
         <v>335</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="239.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6259,38 +6283,38 @@
         <v>354</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6298,38 +6322,38 @@
         <v>354</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>75</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6337,38 +6361,38 @@
         <v>355</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6379,22 +6403,22 @@
         <v>437</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="E83" s="15" t="s">
-        <v>689</v>
+        <v>690</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>691</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="H83" s="16" t="s">
-        <v>692</v>
+        <v>693</v>
+      </c>
+      <c r="H83" s="17" t="s">
+        <v>694</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>22</v>
@@ -6403,10 +6427,10 @@
         <v>58</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6417,22 +6441,22 @@
         <v>413</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="E84" s="17" t="s">
-        <v>696</v>
+        <v>697</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>698</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>22</v>
@@ -6441,10 +6465,10 @@
         <v>75</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="204" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6452,25 +6476,25 @@
         <v>412</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>703</v>
-      </c>
-      <c r="E85" s="11" t="s">
-        <v>704</v>
+        <v>705</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>706</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="2" t="s">
@@ -6480,10 +6504,10 @@
         <v>75</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6491,25 +6515,25 @@
         <v>415</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>712</v>
+        <v>713</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>714</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="I86" s="9"/>
       <c r="J86" s="2" t="s">
@@ -6519,10 +6543,10 @@
         <v>58</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6530,25 +6554,25 @@
         <v>420</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="2" t="s">
@@ -6558,10 +6582,10 @@
         <v>75</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6569,25 +6593,25 @@
         <v>435</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="H88" s="11" t="s">
-        <v>731</v>
+        <v>732</v>
+      </c>
+      <c r="H88" s="12" t="s">
+        <v>733</v>
       </c>
       <c r="I88" s="9"/>
       <c r="J88" s="2" t="s">
@@ -6597,10 +6621,10 @@
         <v>58</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="119.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6608,25 +6632,25 @@
         <v>440</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="E89" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>738</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>737</v>
-      </c>
-      <c r="G89" s="14" t="s">
-        <v>738</v>
+        <v>739</v>
+      </c>
+      <c r="G89" s="15" t="s">
+        <v>740</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="2" t="s">
@@ -6636,10 +6660,10 @@
         <v>33</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6647,25 +6671,25 @@
         <v>453</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>744</v>
-      </c>
-      <c r="F90" s="18" t="s">
         <v>745</v>
       </c>
-      <c r="G90" s="14" t="s">
+      <c r="E90" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="H90" s="11" t="s">
-        <v>692</v>
+      <c r="F90" s="19" t="s">
+        <v>747</v>
+      </c>
+      <c r="G90" s="15" t="s">
+        <v>748</v>
+      </c>
+      <c r="H90" s="12" t="s">
+        <v>694</v>
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="2" t="s">
@@ -6675,10 +6699,10 @@
         <v>58</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6686,38 +6710,38 @@
         <v>458</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>75</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6725,38 +6749,38 @@
         <v>472</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="I92" s="9"/>
       <c r="J92" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6764,25 +6788,25 @@
         <v>475</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>766</v>
-      </c>
-      <c r="E93" s="14" t="s">
-        <v>767</v>
+        <v>768</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>769</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>769</v>
-      </c>
-      <c r="H93" s="11" t="s">
-        <v>692</v>
+        <v>771</v>
+      </c>
+      <c r="H93" s="12" t="s">
+        <v>694</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="2" t="s">
@@ -6792,10 +6816,10 @@
         <v>58</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6803,25 +6827,25 @@
         <v>480</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="E94" s="11" t="s">
-        <v>774</v>
+        <v>775</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>776</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="I94" s="9"/>
       <c r="J94" s="2" t="s">
@@ -6831,10 +6855,10 @@
         <v>33</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6842,38 +6866,38 @@
         <v>490</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6881,25 +6905,25 @@
         <v>490</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="I96" s="9"/>
       <c r="J96" s="2" t="s">
@@ -6909,10 +6933,10 @@
         <v>33</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6920,25 +6944,25 @@
         <v>493</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>796</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
+      </c>
+      <c r="E97" s="14" t="s">
+        <v>799</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="I97" s="9"/>
       <c r="J97" s="2" t="s">
@@ -6948,10 +6972,10 @@
         <v>58</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6959,25 +6983,25 @@
         <v>495</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="I98" s="9"/>
       <c r="J98" s="2" t="s">
@@ -6987,10 +7011,10 @@
         <v>58</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6998,25 +7022,25 @@
         <v>495</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="E99" s="11" t="s">
-        <v>812</v>
+        <v>813</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>814</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>813</v>
-      </c>
-      <c r="G99" s="14" t="s">
-        <v>814</v>
-      </c>
-      <c r="H99" s="11" t="s">
-        <v>692</v>
+        <v>815</v>
+      </c>
+      <c r="G99" s="15" t="s">
+        <v>816</v>
+      </c>
+      <c r="H99" s="12" t="s">
+        <v>694</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="2" t="s">
@@ -7026,10 +7050,10 @@
         <v>58</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7037,23 +7061,23 @@
         <v>505</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>818</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>819</v>
+        <v>820</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>821</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G100" s="9"/>
       <c r="H100" s="9" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="I100" s="9"/>
       <c r="J100" s="2" t="s">
@@ -7063,10 +7087,10 @@
         <v>58</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3878,7 +3878,7 @@
       </c>
       <c r="M54" s="21" t="inlineStr">
         <is>
-          <t>philosophe grec représentant de la Moyenne Académie platonicienne.</t>
+          <t>philosophe grec de la Moyenne Académie, scolarque après Évandre et maître de Carnéade.</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="M57" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> philosophe grec représentant de la moyenne académie platonicienne.</t>
+          <t>philosophe grec, disciple de Lacydès, qui dirigea l'Académie avec Évandre.</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="M72" s="21" t="inlineStr">
         <is>
-          <t>philosophe grec et neveu de Platon qui reprit la tête de l'Académie.</t>
+          <t>philosophe d'Alexandrie, maître de Plotin et précurseur du néoplatonisme.</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="M92" s="21" t="inlineStr">
         <is>
-          <t>philosophe romain qui a oeuvré pour la conservation des textes anciens.</t>
+          <t>philosophe romain, auteur de « La Consolation de la Philosophie », écrite en prison.</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="M95" s="21" t="inlineStr">
         <is>
-          <t>philosophe romain qui a oeuvré pour la conservation des textes anciens.</t>
+          <t>homme d'État romain, fondateur du monastère de Vivarium, voué à la copie des textes anciens.</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.39" customWidth="1" style="20" min="1" max="2"/>
@@ -681,6 +681,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="116.25" customHeight="1" s="22">
       <c r="A4" s="27" t="n">
@@ -4511,6 +4516,11 @@
       <c r="M64" s="21" t="inlineStr">
         <is>
           <t>philosophe juif qui tenta d'harmoniser la philosophie grecque avec la Bible hébraïque.</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - 576 A JC  - 480 A JC  </t>
+          <t xml:space="preserve"> - 535 A JC  - 480 A JC  </t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>-480 AJC   - 356 AJC</t>
+          <t xml:space="preserve">-480 AJC   - 375 AJC</t>
         </is>
       </c>
       <c r="D17" s="28" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="L51" s="21" t="inlineStr">
         <is>
-          <t>Stoïcisme ; Déterminisme ; Comptabilisme</t>
+          <t xml:space="preserve">Stoïcisme ; Déterminisme ; Compatibilisme</t>
         </is>
       </c>
       <c r="M51" s="21" t="inlineStr">
@@ -6207,8 +6207,8 @@
       </c>
     </row>
     <row r="92" ht="136.5" customHeight="1" s="22">
-      <c r="A92" s="27" t="n">
-        <v>472</v>
+      <c r="A92" s="27">
+        <v>480</v>
       </c>
       <c r="B92" s="27" t="inlineStr">
         <is>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -4314,9 +4314,7 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P25">
-        <v>3</v>
-      </c>
+      <c r="P25"/>
     </row>
     <row r="26" customFormat="false" ht="154.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3227,7 +3227,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="6.39"/>
@@ -4668,6 +4668,11 @@
       <c r="M33" s="2" t="s">
         <v>279</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -6862,6 +6867,11 @@
       <c r="M82" s="2" t="s">
         <v>691</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -7086,6 +7096,11 @@
       <c r="M87" s="2" t="s">
         <v>729</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O87" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -7671,7 +7686,168 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="7">
+        <v>-550</v>
+      </c>
+      <c r="B101" s="7">
+        <v>-480</v>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIe siècle A JC</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THÉANO</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Théano_(pythagoricienne)"  title=" Wikipedia"&gt;THÉANO&lt;/a&gt; est une philosophe grecque du VIe siècle avant J.-C., membre de la communauté fondée par Pythagore à Crotone, en Grande-Grèce (le sud de l'Italie). Les sources anciennes la présentent tantôt comme l'épouse de Pythagore et la mère de ses enfants, tantôt comme l'épouse de Brontinos et simple disciple du maître. Il est même possible que plusieurs philosophes pythagoriciennes aient porté ce nom.&lt;/p&gt; &lt;p&gt;L'école pythagoricienne avait ceci de remarquable qu'elle accueillait des femmes, ce qui était rare dans le monde grec. On attribue à Théano des traités &lt;em&gt;De la piété&lt;/em&gt; et &lt;em&gt;De la vertu&lt;/em&gt;, des conseils aux femmes, des apophtegmes et plusieurs lettres. Dans l'une d'elles, elle affirme que le nombre n'est pas la substance des choses mais le principe de leur ordre, ce qui nuance la doctrine attribuée à Pythagore.&lt;/p&gt; &lt;p&gt;La tradition rapporte de nombreuses sentences de Théano sur la vie des femmes et la vertu. À une femme qui lui demandait combien de temps après avoir été avec un homme elle pouvait se rendre au temple, elle aurait répondu : « avec son mari, aussitôt ; avec un autre, jamais ». On lui prête aussi la direction de l'école pythagoricienne après la mort de Pythagore, avec leurs enfants, ce qui ferait d'elle l'une des premières femmes à la tête d'une école de philosophie.&lt;/p&gt; &lt;p&gt;La plupart de ces écrits sont sans doute apocryphes, rédigés plusieurs siècles plus tard par des pythagoriciens qui se plaçaient sous son autorité. Leur existence même montre pourtant que Théano était restée, dans la mémoire antique, le modèle de la femme philosophe, alliant sagesse morale, réflexion sur l'harmonie du monde et vie communautaire.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pythagorisme</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe pythagoricienne, présentée comme l'épouse ou la disciple de Pythagore.</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="7">
+        <v>-450</v>
+      </c>
+      <c r="B102" s="7">
+        <v>-400</v>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ve siècle A JC</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIOTIME de Mantinée</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diotime_de_Mantinée"  title=" Wikipedia"&gt;DIOTIME de Mantinée&lt;/a&gt; est une prêtresse et une sage du Ve siècle avant J.-C., connue uniquement par le &lt;em&gt;Banquet&lt;/em&gt; de Platon. Socrate y raconte que, dans sa jeunesse, c'est elle qui lui a enseigné tout ce qu'il sait sur l'amour. Aucune autre source antique ne la mentionne, et son nom, « honorée par Zeus », ainsi que son origine, Mantinée, qui évoque le mot grec pour « devin », laissent penser qu'elle pourrait être une invention de Platon.&lt;/p&gt; &lt;p&gt;Son discours est pourtant le sommet du dialogue. Diotime explique qu'Éros n'est pas un dieu mais un « grand démon », un intermédiaire entre les mortels et les immortels, fils de Pauvreté et d'Expédient : il manque de ce qu'il désire et cherche sans cesse à l'obtenir. Aimer, c'est désirer posséder le bien pour toujours, et donc vouloir engendrer dans la beauté, par les enfants ou par les œuvres de l'esprit.&lt;/p&gt; &lt;p&gt;Le choix de Platon de faire parler une femme n'est pas anodin : dans un banquet où ne siègent que des hommes, c'est une étrangère, prêtresse et savante, qui détient la vérité la plus haute. Socrate, qui d'ordinaire interroge les autres, se présente ici comme un élève qu'elle corrige et fait progresser. La méthode de Diotime ressemble d'ailleurs à celle de Socrate lui-même : elle pose des questions, relève les contradictions et conduit pas à pas son interlocuteur vers la vérité.&lt;/p&gt; &lt;p&gt;Elle décrit ensuite la célèbre « échelle de l'amour » : de l'amour d'un beau corps, on s'élève à celui de tous les beaux corps, puis des belles âmes, des belles lois, des belles connaissances, jusqu'à la contemplation de la Beauté en soi, éternelle et parfaite. Réelle ou imaginée, Diotime reste la femme qui, chez Platon, enseigne au plus grand des philosophes l'une des idées les plus influentes de l'histoire de la pensée.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; esthetique</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platonisme</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prêtresse et sage qui, dans le Banquet de Platon, enseigne à Socrate la nature de l'amour.</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="7">
+        <v>-350</v>
+      </c>
+      <c r="B103" s="7">
+        <v>-280</v>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">350 A JC - 280 A JC</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIPPARCHIA de Maronée</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hipparchia"  title=" Wikipedia"&gt;HIPPARCHIA de Maronée&lt;/a&gt; (vers 350-280 avant J.-C.) est une philosophe cynique grecque, originaire de Maronée en Thrace. Issue d'une famille aisée, elle tomba amoureuse du philosophe Cratès de Thèbes, disciple de Diogène, qui avait renoncé à toute sa fortune. Ses parents s'opposèrent au mariage ; elle menaça de se tuer. Cratès lui-même tenta de la dissuader en lui montrant sa pauvreté, mais elle choisit de partager sa vie et ses idées.&lt;/p&gt; &lt;p&gt;Le cynisme prônait une vie simple, conforme à la nature, libérée des richesses, des honneurs et des conventions sociales jugées artificielles. Hipparchia vécut ainsi avec Cratès, en public et sans honte, portant le même manteau grossier que lui, et participa comme un homme aux banquets et aux discussions philosophiques, ce qui fit scandale à Athènes.&lt;/p&gt; &lt;p&gt;Selon Diogène Laërce, elle aurait écrit des traités philosophiques, des lettres et des réponses à des questions posées au philosophe Théodore, aujourd'hui perdus. Elle eut avec Cratès au moins deux enfants et continua de mener une vie de philosophe. Pour les anciens, elle était la preuve qu'une femme pouvait choisir librement la vie philosophique la plus exigeante, et plusieurs auteurs, jusqu'à l'époque chrétienne, citèrent son exemple.&lt;/p&gt; &lt;p&gt;Diogène Laërce rapporte une anecdote célèbre : lors d'un banquet, le philosophe Théodore l'Athée voulut l'humilier en lui demandant qui avait donc laissé sa navette sur le métier à tisser. Elle répondit qu'elle avait consacré à l'étude le temps qu'on aurait voulu lui faire perdre au rouet. Hipparchia est ainsi devenue le symbole de la femme qui revendique le droit de penser et de vivre en philosophe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cynisme</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe cynique grecque, épouse de Cratès, qui vécut selon ses idées contre les conventions de son temps.</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P103">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3640,77 +3640,101 @@
         </is>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7">
+        <v>-550</v>
+      </c>
+      <c r="B11" s="7">
+        <v>-480</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIe siècle A JC</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THÉANO</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Théano_(pythagoricienne)" title=" Wikipedia"&gt;THÉANO&lt;/a&gt; est une philosophe grecque du VIe siècle avant J.-C., membre de la communauté fondée par Pythagore à Crotone, en Grande-Grèce (le sud de l'Italie). Les sources anciennes la présentent tantôt comme l'épouse de Pythagore et la mère de ses enfants, tantôt comme l'épouse de Brontinos et simple disciple du maître. Il est même possible que plusieurs philosophes pythagoriciennes aient porté ce nom.&lt;/p&gt; &lt;p&gt;L'école pythagoricienne avait ceci de remarquable qu'elle accueillait des femmes, ce qui était rare dans le monde grec. On attribue à Théano des traités &lt;em&gt;De la piété&lt;/em&gt; et &lt;em&gt;De la vertu&lt;/em&gt;, des conseils aux femmes, des apophtegmes et plusieurs lettres. Dans l'une d'elles, elle affirme que le nombre n'est pas la substance des choses mais le principe de leur ordre, ce qui nuance la doctrine attribuée à Pythagore.&lt;/p&gt; &lt;p&gt;La tradition rapporte de nombreuses sentences de Théano sur la vie des femmes et la vertu. À une femme qui lui demandait combien de temps après avoir été avec un homme elle pouvait se rendre au temple, elle aurait répondu : « avec son mari, aussitôt ; avec un autre, jamais ». On lui prête aussi la direction de l'école pythagoricienne après la mort de Pythagore, avec leurs enfants, ce qui ferait d'elle l'une des premières femmes à la tête d'une école de philosophie.&lt;/p&gt; &lt;p&gt;La plupart de ces écrits sont sans doute &lt;a href="https://fr.wikipedia.org/wiki/Apocryphe_biblique" title=" Wikipedia"&gt;apocryphes&lt;/a&gt;, rédigés plusieurs siècles plus tard par des pythagoriciens qui se plaçaient sous son autorité. Leur existence même montre pourtant que Théano était restée, dans la mémoire antique, le modèle de la femme philosophe, alliant sagesse morale, réflexion sur l'harmonie du monde et vie communautaire.&lt;/p&gt;  &lt;audio controls title="la vie et l'oeuvre de Pythagore et de sa femme THEANO"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10212-08.01.2008-ITEMA_20104885-2008F10732S0008-27.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UktaE9uuYao</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Theano (fl. 6th century BCE) | AI Podcast" par AI History of Western Philosophy</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/theano-mini.webp</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; ethique</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pythagorisme</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe pythagoricienne, présentée comme l'épouse ou la disciple de Pythagore.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
         <v>-535</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>-515</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>94</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="2" t="s">
@@ -3720,10 +3744,10 @@
         <v>34</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -3734,30 +3758,30 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
-        <v>-500</v>
+        <v>-515</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="2" t="s">
@@ -3770,51 +3794,54 @@
         <v>25</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="191.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
-        <v>-495</v>
+        <v>-500</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>107</v>
+        <v>98</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M14" s="11" t="s">
-        <v>111</v>
+      <c r="M14" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -3822,43 +3849,43 @@
         </is>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="191.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
-        <v>-490</v>
+        <v>-495</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>115</v>
+        <v>106</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>107</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>121</v>
+        <v>25</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3866,212 +3893,212 @@
         </is>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
         <v>-490</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>125</v>
+        <v>114</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="17" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
-        <v>-480</v>
+        <v>-490</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>134</v>
+        <v>124</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
-        <v>-470</v>
+        <v>-480</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>144</v>
+        <v>133</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="19" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
         <v>-470</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>25</v>
+        <v>149</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
-        <v>-465</v>
+        <v>-470</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>161</v>
+        <v>153</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="2" t="s">
@@ -4081,10 +4108,10 @@
         <v>59</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -4092,43 +4119,43 @@
         </is>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="193.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
-        <v>-460</v>
+        <v>-465</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>170</v>
+        <v>160</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>161</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>165</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -4136,43 +4163,43 @@
         </is>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="193.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
-        <v>-459</v>
+        <v>-460</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>178</v>
+        <v>169</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4180,223 +4207,223 @@
         </is>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
-        <v>-450</v>
+        <v>-459</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>187</v>
+        <v>177</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>178</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="24" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
-        <v>-445</v>
+        <v>-450</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
-        <v>-436</v>
+        <v>-445</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P25"/>
-    </row>
-    <row r="26" customFormat="false" ht="154.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="26" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
-        <v>-435</v>
+        <v>-436</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>218</v>
+        <v>139</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P26"/>
+    </row>
+    <row r="27" customFormat="false" ht="154.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
-        <v>-430</v>
+        <v>-435</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4404,90 +4431,87 @@
         </is>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="232.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="n">
-        <v>-428</v>
+        <v>-430</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>231</v>
+        <v>222</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>223</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>235</v>
+        <v>24</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>236</v>
+        <v>149</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="29" customFormat="false" ht="232.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
-        <v>-412</v>
+        <v>-428</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>241</v>
+        <v>230</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4495,90 +4519,93 @@
         </is>
       </c>
       <c r="P29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
-        <v>-408</v>
+        <v>-412</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>248</v>
+        <v>240</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>241</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
-        <v>-407</v>
+        <v>-408</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>257</v>
+        <v>247</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>248</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>236</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4586,43 +4613,43 @@
         </is>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="152.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
-        <v>-405</v>
+        <v>-407</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>267</v>
+        <v>258</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>259</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>269</v>
+        <v>34</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>149</v>
+        <v>236</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4630,48 +4657,43 @@
         </is>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="152.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
-        <v>-400</v>
+        <v>-405</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>276</v>
+        <v>266</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>267</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>200</v>
+        <v>269</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>278</v>
+        <v>149</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
+        <v>270</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4679,43 +4701,48 @@
         </is>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
-        <v>-396</v>
+        <v>-400</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4725,88 +4752,85 @@
     </row>
     <row r="35" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
-        <v>-385</v>
+        <v>-396</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>34</v>
+        <v>174</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>236</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="36" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
-        <v>-384</v>
+        <v>-385</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>288</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>302</v>
+        <v>236</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4814,90 +4838,93 @@
         </is>
       </c>
       <c r="P36">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
-        <v>-380</v>
+        <v>-384</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>310</v>
+        <v>300</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
-        <v>-370</v>
+        <v>-380</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>318</v>
+        <v>309</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>310</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>319</v>
+        <v>200</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -4905,43 +4932,43 @@
         </is>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
-        <v>-365</v>
+        <v>-370</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>200</v>
+        <v>319</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4949,7 +4976,7 @@
         </is>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
         <v>-365</v>
       </c>
@@ -4960,32 +4987,32 @@
         <v>322</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>149</v>
+        <v>201</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -4993,43 +5020,43 @@
         </is>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="221.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
-        <v>-362</v>
+        <v>-365</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>342</v>
+        <v>149</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5037,43 +5064,43 @@
         </is>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="221.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
-        <v>-360</v>
+        <v>-362</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>351</v>
+        <v>252</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>149</v>
+        <v>342</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5081,43 +5108,43 @@
         </is>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
         <v>-360</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>304</v>
+        <v>344</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>302</v>
+        <v>149</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5125,77 +5152,74 @@
         </is>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
-        <v>-341</v>
+        <v>-360</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>361</v>
+        <v>304</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>355</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>369</v>
+        <v>302</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="45" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
-        <v>-340</v>
+        <v>-341</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>374</v>
+        <v>363</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>364</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="2" t="s">
@@ -5205,41 +5229,44 @@
         <v>368</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>278</v>
+        <v>369</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
-        <v>-334</v>
+        <v>-340</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="2" t="s">
@@ -5249,44 +5276,41 @@
         <v>368</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>386</v>
+        <v>278</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="47" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
-        <v>-330</v>
+        <v>-334</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="2" t="s">
@@ -5299,51 +5323,54 @@
         <v>386</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
-        <v>-325</v>
+        <v>-330</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>200</v>
+        <v>368</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>201</v>
+        <v>386</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -5351,43 +5378,43 @@
         </is>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
-        <v>-315</v>
+        <v>-325</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>342</v>
+        <v>201</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -5395,43 +5422,43 @@
         </is>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
-        <v>-306</v>
+        <v>-315</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>252</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -5439,43 +5466,43 @@
         </is>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="209.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
-        <v>-281</v>
+        <v>-306</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>427</v>
+        <v>24</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>428</v>
+        <v>386</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -5483,43 +5510,43 @@
         </is>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="209.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
-        <v>-280</v>
+        <v>-281</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>252</v>
+        <v>427</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>342</v>
+        <v>428</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -5527,34 +5554,32 @@
         </is>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
-        <v>-240</v>
+        <v>-280</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="I53" s="12" t="s">
-        <v>445</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="I53" s="9"/>
       <c r="J53" s="2" t="s">
         <v>23</v>
       </c>
@@ -5565,7 +5590,7 @@
         <v>342</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -5573,32 +5598,34 @@
         </is>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
-        <v>-230</v>
+        <v>-240</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>450</v>
+        <v>440</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>441</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="G54" s="15" t="s">
-        <v>452</v>
+        <v>442</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>443</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="I54" s="9"/>
+        <v>444</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>445</v>
+      </c>
       <c r="J54" s="2" t="s">
         <v>23</v>
       </c>
@@ -5609,7 +5636,7 @@
         <v>342</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5617,30 +5644,30 @@
         </is>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
-        <v>-213</v>
+        <v>-230</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>460</v>
+        <v>451</v>
+      </c>
+      <c r="G55" s="15" t="s">
+        <v>452</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="2" t="s">
@@ -5653,7 +5680,7 @@
         <v>342</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5661,30 +5688,30 @@
         </is>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
-        <v>-210</v>
+        <v>-213</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>466</v>
+        <v>457</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>458</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="2" t="s">
@@ -5697,7 +5724,7 @@
         <v>342</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5705,30 +5732,30 @@
         </is>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
-        <v>-204</v>
+        <v>-210</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>474</v>
+        <v>465</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>466</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="2" t="s">
@@ -5740,8 +5767,8 @@
       <c r="L57" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="M57" s="11" t="s">
-        <v>478</v>
+      <c r="M57" s="2" t="s">
+        <v>470</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5749,43 +5776,43 @@
         </is>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
-        <v>-185</v>
+        <v>-204</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>252</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>486</v>
+        <v>342</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>478</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5793,43 +5820,43 @@
         </is>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
-        <v>-135</v>
+        <v>-185</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>386</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5837,43 +5864,43 @@
         </is>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
-        <v>-110</v>
+        <v>-135</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>498</v>
+        <v>489</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>490</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>502</v>
+        <v>34</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>503</v>
+        <v>386</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5881,134 +5908,134 @@
         </is>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
-        <v>-106</v>
+        <v>-110</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="2" t="s">
-        <v>512</v>
+        <v>23</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>182</v>
+        <v>502</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>386</v>
+        <v>503</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="62" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
-        <v>-94</v>
+        <v>-106</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="2" t="s">
         <v>512</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>503</v>
+        <v>386</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
-        <v>-80</v>
+        <v>-94</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>252</v>
+        <v>174</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>342</v>
+        <v>503</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6016,181 +6043,181 @@
         </is>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
-        <v>-20</v>
+        <v>-80</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="2" t="s">
-        <v>537</v>
+        <v>23</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>538</v>
+        <v>342</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="N64" s="0" t="s">
-        <v>540</v>
-      </c>
-      <c r="O64" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>529</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>544</v>
+        <v>532</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>533</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="2" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>386</v>
+        <v>538</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P65">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>539</v>
+      </c>
+      <c r="N65" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="O65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>552</v>
+        <v>543</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>544</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>236</v>
+        <v>386</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>560</v>
+        <v>551</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>552</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>564</v>
+        <v>59</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>565</v>
+        <v>236</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6198,43 +6225,43 @@
         </is>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>368</v>
+        <v>564</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>236</v>
+        <v>565</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6242,212 +6269,212 @@
         </is>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>567</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>65</v>
+        <v>571</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>200</v>
+        <v>368</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>386</v>
+        <v>236</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P69">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="70" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>585</v>
+        <v>65</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>538</v>
+        <v>386</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>592</v>
+        <v>583</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>584</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="2" t="s">
-        <v>512</v>
+        <v>23</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>386</v>
+        <v>538</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P71">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="72" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="2" t="s">
-        <v>604</v>
+        <v>512</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>538</v>
+        <v>386</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>609</v>
+        <v>599</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>600</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="2" t="s">
@@ -6460,98 +6487,98 @@
         <v>538</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P73">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="186.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="74" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="G74" s="15" t="s">
-        <v>619</v>
+        <v>610</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>611</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="2" t="s">
-        <v>23</v>
+        <v>604</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>359</v>
+        <v>76</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="186.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>626</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>627</v>
+        <v>618</v>
+      </c>
+      <c r="G75" s="15" t="s">
+        <v>619</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>76</v>
+        <v>359</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6559,34 +6586,34 @@
         </is>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
-        <v>245</v>
-      </c>
-      <c r="B76" s="7" t="n">
-        <v>325</v>
+        <v>234</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>622</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="H76" s="12" t="s">
-        <v>635</v>
+        <v>627</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>628</v>
       </c>
       <c r="I76" s="9"/>
       <c r="J76" s="2" t="s">
-        <v>636</v>
+        <v>23</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>76</v>
@@ -6595,7 +6622,7 @@
         <v>538</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6603,34 +6630,34 @@
         </is>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="n">
-        <v>290</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>638</v>
+        <v>245</v>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>325</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>644</v>
+        <v>634</v>
+      </c>
+      <c r="H77" s="12" t="s">
+        <v>635</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="2" t="s">
-        <v>512</v>
+        <v>636</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>76</v>
@@ -6639,7 +6666,7 @@
         <v>538</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -6647,43 +6674,43 @@
         </is>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="n">
-        <v>317</v>
+        <v>290</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>653</v>
+        <v>76</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>302</v>
+        <v>538</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -6691,305 +6718,305 @@
         </is>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="n">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>564</v>
+        <v>653</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>662</v>
+        <v>302</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P79">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="239.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="80" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="2" t="s">
-        <v>671</v>
+        <v>23</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>672</v>
+        <v>564</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>662</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="239.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
         <v>354</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="2" t="s">
-        <v>512</v>
+        <v>671</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>76</v>
+        <v>672</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>681</v>
+        <v>662</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P81">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="82" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K82" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="7" t="n">
+        <v>355</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="I83" s="9"/>
+      <c r="J83" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K83" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="L82" s="2" t="s">
+      <c r="L83" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="M82" s="2" t="s">
+      <c r="M83" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="n">
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="n">
         <v>365</v>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B84" s="1" t="n">
         <v>437</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E84" s="11" t="s">
         <v>694</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F84" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G84" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="H83" s="16" t="s">
+      <c r="H84" s="16" t="s">
         <v>697</v>
       </c>
-      <c r="J83" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K83" s="2" t="s">
+      <c r="J84" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K84" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L83" s="2" t="s">
+      <c r="L84" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="M83" s="2" t="s">
+      <c r="M84" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B85" s="1" t="n">
         <v>413</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="E84" s="17" t="s">
+      <c r="E85" s="17" t="s">
         <v>701</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F85" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G85" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H85" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="J84" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="204" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="n">
-        <v>412</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>707</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>709</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>710</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>711</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>712</v>
-      </c>
-      <c r="I85" s="9"/>
       <c r="J85" s="2" t="s">
         <v>23</v>
       </c>
@@ -7000,54 +7027,51 @@
         <v>538</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P85">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="86" customFormat="false" ht="204" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="n">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="I86" s="9"/>
       <c r="J86" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7058,92 +7082,95 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="E87" s="9" t="s">
-        <v>725</v>
+        <v>716</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>717</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
+        <v>721</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="H88" s="12" t="s">
-        <v>736</v>
+        <v>727</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>728</v>
       </c>
       <c r="I88" s="9"/>
       <c r="J88" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>737</v>
+        <v>729</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7151,43 +7178,43 @@
         </is>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="119.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>741</v>
+        <v>732</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>733</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>742</v>
-      </c>
-      <c r="G89" s="15" t="s">
-        <v>743</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>744</v>
+        <v>734</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="H89" s="12" t="s">
+        <v>736</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -7195,43 +7222,43 @@
         </is>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="119.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="n">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>749</v>
-      </c>
-      <c r="F90" s="18" t="s">
-        <v>750</v>
+        <v>740</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>741</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>742</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>751</v>
-      </c>
-      <c r="H90" s="12" t="s">
-        <v>697</v>
+        <v>743</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>744</v>
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -7239,225 +7266,225 @@
         </is>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="n">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>755</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>756</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>736</v>
+        <v>748</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="F91" s="18" t="s">
+        <v>750</v>
+      </c>
+      <c r="G91" s="15" t="s">
+        <v>751</v>
+      </c>
+      <c r="H91" s="12" t="s">
+        <v>697</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="2" t="s">
-        <v>636</v>
+        <v>23</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P91">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="92" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="E92" s="9" t="s">
-        <v>763</v>
+        <v>755</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>756</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>766</v>
+        <v>736</v>
       </c>
       <c r="I92" s="9"/>
       <c r="J92" s="2" t="s">
-        <v>512</v>
+        <v>636</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>767</v>
+        <v>538</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="E93" s="15" t="s">
-        <v>772</v>
+        <v>762</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>763</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>774</v>
-      </c>
-      <c r="H93" s="12" t="s">
-        <v>697</v>
+        <v>765</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>766</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>538</v>
+        <v>767</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="94" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>778</v>
-      </c>
-      <c r="E94" s="12" t="s">
-        <v>779</v>
+        <v>771</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>772</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>781</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>782</v>
+        <v>774</v>
+      </c>
+      <c r="H94" s="12" t="s">
+        <v>697</v>
       </c>
       <c r="I94" s="9"/>
       <c r="J94" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>786</v>
-      </c>
-      <c r="E95" s="9" t="s">
-        <v>787</v>
+        <v>778</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>779</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="2" t="s">
-        <v>512</v>
+        <v>23</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>252</v>
+        <v>34</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>662</v>
+        <v>538</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -7465,43 +7492,43 @@
         </is>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
         <v>490</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>794</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>795</v>
+        <v>786</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>787</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="I96" s="9"/>
       <c r="J96" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>538</v>
+        <v>662</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -7509,43 +7536,43 @@
         </is>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>802</v>
-      </c>
-      <c r="E97" s="14" t="s">
-        <v>803</v>
+        <v>794</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>795</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>697</v>
+        <v>798</v>
       </c>
       <c r="I97" s="9"/>
       <c r="J97" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -7553,30 +7580,30 @@
         </is>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="E98" s="9" t="s">
-        <v>810</v>
+        <v>802</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>803</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>813</v>
+        <v>697</v>
       </c>
       <c r="I98" s="9"/>
       <c r="J98" s="2" t="s">
@@ -7589,7 +7616,7 @@
         <v>538</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -7597,30 +7624,30 @@
         </is>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
         <v>495</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>817</v>
-      </c>
-      <c r="E99" s="12" t="s">
-        <v>818</v>
+        <v>809</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>810</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>819</v>
-      </c>
-      <c r="G99" s="15" t="s">
-        <v>820</v>
-      </c>
-      <c r="H99" s="12" t="s">
-        <v>697</v>
+        <v>811</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>812</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>813</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="2" t="s">
@@ -7633,7 +7660,7 @@
         <v>538</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -7641,28 +7668,30 @@
         </is>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="E100" s="14" t="s">
-        <v>825</v>
+        <v>816</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>818</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9" t="s">
-        <v>826</v>
+        <v>819</v>
+      </c>
+      <c r="G100" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="H100" s="12" t="s">
+        <v>697</v>
       </c>
       <c r="I100" s="9"/>
       <c r="J100" s="2" t="s">
@@ -7675,68 +7704,57 @@
         <v>538</v>
       </c>
       <c r="M100" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="E101" s="14" t="s">
+        <v>825</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="G101" s="9"/>
+      <c r="H101" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="I101" s="9"/>
+      <c r="J101" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="M101" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P100">
+      <c r="O101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P101">
         <v>2</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="7">
-        <v>-550</v>
-      </c>
-      <c r="B101" s="7">
-        <v>-480</v>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIe siècle A JC</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THÉANO</t>
-        </is>
-      </c>
-      <c r="E101" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Théano_(pythagoricienne)"  title=" Wikipedia"&gt;THÉANO&lt;/a&gt; est une philosophe grecque du VIe siècle avant J.-C., membre de la communauté fondée par Pythagore à Crotone, en Grande-Grèce (le sud de l'Italie). Les sources anciennes la présentent tantôt comme l'épouse de Pythagore et la mère de ses enfants, tantôt comme l'épouse de Brontinos et simple disciple du maître. Il est même possible que plusieurs philosophes pythagoriciennes aient porté ce nom.&lt;/p&gt; &lt;p&gt;L'école pythagoricienne avait ceci de remarquable qu'elle accueillait des femmes, ce qui était rare dans le monde grec. On attribue à Théano des traités &lt;em&gt;De la piété&lt;/em&gt; et &lt;em&gt;De la vertu&lt;/em&gt;, des conseils aux femmes, des apophtegmes et plusieurs lettres. Dans l'une d'elles, elle affirme que le nombre n'est pas la substance des choses mais le principe de leur ordre, ce qui nuance la doctrine attribuée à Pythagore.&lt;/p&gt; &lt;p&gt;La tradition rapporte de nombreuses sentences de Théano sur la vie des femmes et la vertu. À une femme qui lui demandait combien de temps après avoir été avec un homme elle pouvait se rendre au temple, elle aurait répondu : « avec son mari, aussitôt ; avec un autre, jamais ». On lui prête aussi la direction de l'école pythagoricienne après la mort de Pythagore, avec leurs enfants, ce qui ferait d'elle l'une des premières femmes à la tête d'une école de philosophie.&lt;/p&gt; &lt;p&gt;La plupart de ces écrits sont sans doute apocryphes, rédigés plusieurs siècles plus tard par des pythagoriciens qui se plaçaient sous son autorité. Leur existence même montre pourtant que Théano était restée, dans la mémoire antique, le modèle de la femme philosophe, alliant sagesse morale, réflexion sur l'harmonie du monde et vie communautaire.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grecque</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique ; metaphysique</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pythagorisme</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe pythagoricienne, présentée comme l'épouse ou la disciple de Pythagore.</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7854,35 +7872,35 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E15" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Protagoras&quot;  title=&quot;Protagoras par Wikipédia&quot;&gt; PROTAGORAS&lt;/a&gt;  était un philosophe considéré comme l'un &lt;a href=&quot;https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;ab_channel=Bibiclo&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Les Sophistes par Bobiclo&quot;&gt; des sophistes&lt;/a&gt; les plus célèbres de cette période.&lt;/p&gt;&#10;&#10;&lt;p&gt;Les sophistes étaient des enseignants itinérants qui offraient &lt;a href=&quot;https://www.youtube.com/watch?v=X5bZKSCfc_g&amp;ab_channel=AlainBajom%C3%A9e&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Rhétorique et relativisme par Alain Bajomée&quot;&gt; des cours de rhétorique&lt;/a&gt;, d'éloquence et de persuader efficacement. Cependant, il a également suscité des débats et des controverses en raison de ses opinions et de ses idées.&lt;/p&gt;&#10;&lt;p&gt;L'une de ses déclarations les plus célèbres est : &quot;L'homme est la mesure de toutes choses : de celles qui sont, tant quand elles sont en tant qu'elles sont, que de celles qui ne sont pas, tant quand elles ne sont pas en tant qu'elles ne sont pas.&quot; Cela suggère que la perception et l'expérience individuelles sont centrales pour la compréhension de la réalité, et que la vérité peut être relative à chaque individu. Cette déclaration forme le fondement de ce que l'on appelle &lt;a href=&quot;https://www.youtube.com/watch?v=LxSCq1F7pSk&amp;ab_channel=LePr%C3%A9cepteur&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Le relativisme par le Précepteur&quot;&gt; le relativisme.&lt;/a&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Il a également abordé des sujets tels que la nature de la justice, l'éducation et le rôle des dieux dans la vie humaine. Ses enseignements ont été critiqués par d'autres philosophes, notamment Socrate et Platon, qui les voyaient vides de fondement rationnel.&lt;/p&gt;&#10;&#10;&lt;p&gt;Bien qu'il ait laissé peu d'œuvres écrites, sa vision de la relativité de la vérité et de l'importance de la rhétorique a contribué à façonner les débats sur la nature de la connaissance et de la réalité dans la philosophie grecque antique.&lt;/p&gt;  &lt;audio controls title=&quot;Platon vs. Protagoras: l'homme est il la mesure de toutes choses? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/09/s40/NET_FC_f081bba4-88ba-4b62-930d-2c30e49863d9.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E17" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gorgias&quot; title=&quot; Wikipedia&quot;&gt;GORGIAS&lt;/a&gt; était un philosophe présocratique et l'une des figures les plus importantes de la &lt;a href=&quot;https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;t=184s&quot; title=&quot; Les sophistes par Bibiclo&quot;&gt;sophistique&lt;/a&gt;.  Contrairement aux philosophes comme Platon ou Aristote, qui cherchaient à découvrir des vérités universelles en mettant l'accent sur l'importance de l'opinion et de la persuasion dans les affaires humaines.  Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;  - &quot;Sur le Non-Être ou sur la Nature&quot; : Il développe une argumentation radicale qui remet en question la possibilité même de la connaissance et de la communication.&lt;/p&gt; &lt;p&gt; -  Il soutient trois thèses principales : - Rien n'existe.  - Si quelque chose existait, nous ne pourrions pas le connaître. - Si nous pouvions le connaître, nous ne pourrions pas le communiquer aux autres. &lt;/p&gt; &lt;p&gt; Ces thèses sont souvent interprétées comme une critique de l'ontologie éléatique, notamment des idées de Parménide, qui affirmait que l'être est un et immuable. &lt;/p&gt;  &lt;p&gt; - &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89loge_d%27H%C3%A9l%C3%A8ne &quot;  title=&quot; Gorgias Eloge d’Helene  parWikipedia&quot;&gt;&quot;Éloge d'Hélène&quot;&lt;/a&gt;  : Dans ce discours, Il défend Hélène de Troie, souvent considérée comme responsable de la guerre de Troie. Il utilise des arguments rhétoriques pour montrer qu'elle ne peut être tenue pour responsable, car elle a été soit victime de la volonté des dieux, soit de la séduction de Pâris, soit de la force.  &lt;/p&gt; &lt;p&gt; -  &quot;Défense de Palamède&quot; : Dans ce discours, il défend Palamède, un héros grec accusé de trahison par Ulysse. Il utilise des arguments logiques et rhétoriques pour démontrer son l'innocence, montrant ainsi la puissance de la parole pour influencer les jugements. &lt;p&gt; Il  est souvent considéré comme un relativiste et un sceptique. Il met en doute la possibilité de connaître la vérité absolue et souligne l'importance de la persuasion dans les affaires humaines. Sa philosophie a eu une influence significative sur la pensée grecque, notamment sur Platon, qui le critique sévèrement dans son dialogue &quot;Gorgias&quot;. Platon y oppose la recherche de la vérité à l'art de la persuasion, qu'il associe à la sophistique. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E21" r:id="rId3" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/D%C3%A9mocrite&quot; title=&quot; Wikipedia&quot;&gt; DÉMOCRITE&lt;/a&gt; était un philosophe Grec connu pour être l'un des fondateurs avec LEUCIPPE de la philosophie  &lt;a href=&quot;https://www.youtube.com/watch?v=AGvcey2B3Vc&amp;t=3s&amp;ab_channel=Coursitout&quot;   title=&quot;l'Atomisme des philosophes Grecs par Coursitout&quot;&gt; atomiste&lt;/a&gt;, une théorie selon laquelle tout dans l'univers est composé de particules indivisibles appelées atomes. Selon lui, ils sont en mouvement perpétuel et se combinent pour former toutes les substances et objets que nous voyons autour de nous.  Il était réputé pour sa grande curiosité intellectuelle et aurait beaucoup voyagé, notamment en Égypte et en Orient, afin d’enrichir ses connaissances. Surnommé parfois « le philosophe rieur », il adoptait une attitude détachée face aux préoccupations humaines, considérant que la sérénité naît de la compréhension du monde et de la maîtrise de soi.  &lt;/p&gt; &lt;p&gt;Il avait une approche &lt;a href=&quot;https://www.youtube.com/watch?v=_uXOu9ZRD4I&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;le matérialisme par Alain Bajomée&quot;&gt; matérialiste&lt;/a&gt; de la réalité et croyait que tout ce qui existe était composé de matière et de vide, et que la perception humaine était basée sur l'interaction entre les atomes et les sens. Il était également connu pour ses idées sur l'éthique et la morale et croyait que le bonheur et la vertu pouvaient être atteints grâce à une vie simple et équilibrée, et que les désirs excessifs et les passions pouvaient entraîner la souffrance. &lt;/p&gt; &lt;p&gt; Sa pensée ne se limite pas à la physique : il développe aussi une réflexion approfondie sur la connaissance en distinguant les qualités « réelles » (comme la forme et le mouvement des atomes) des qualités « sensibles » (comme les couleurs ou les saveurs), qui dépendent de nos perceptions. Cette distinction annonce des débats majeurs de la philosophie moderne. Son influence se retrouvera plus tard chez des penseurs comme Épicure, qui reprendra l’atomisme en y intégrant une dimension éthique centrée sur la recherche du plaisir mesuré et de l’absence de trouble.   &lt;/p&gt; &lt;p&gt; Peu de ses écrits ont survécu jusqu'à nos jours, et la plupart de ce que nous connaissons provient de commentaires ultérieurs et de citations dans les œuvres d'autres philosophes grecs. Cependant, ses contributions à la théorie atomique ont été fondamentales pour la compréhension moderne de la physique et de la chimie. &lt;/p&gt; &lt;audio controls title=&quot;Démocrite contre Platon par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2015/06/s27/net-fi-be35a965-485b-4f98-9b10-0e2051e903ec.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E22" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thrasymaque&quot;title=&quot; Wikipedia&quot;&gt;THRASYMAQUE&lt;/a&gt; était un philosophe sophiste grec connue pour son rôle dans &lt;a href=&quot;https://www.youtube.com/watch?v=qSrvZvjPG_w&quot; style=&quot;color:#88A1E9&quot; title=&quot; PLATON-Cest quoi la république par Kosmos &quot;&gt;&quot;La République&quot;&lt;/a&gt; de Platon. Il est l'un des interlocuteurs de Socrate dans ce dialogue, où il défend une vision provocante et cynique de la justice. &lt;/p&gt;&lt;p&gt; Il  affirme que &quot;&lt;a href=&quot;https://www.youtube.com/watch?v=VlLLr8kVya0&quot;  title=&quot;  Qu'est-ce que la Justice en Philosophie ?   par Coursitout &quot;&gt;la justice&lt;/a&gt; n'est rien d'autre que l'intérêt du plus fort&quot;. Selon lui, les lois et les normes sociales sont établies par ceux qui détiennent le pouvoir (les gouvernants, les tyrans, les aristocrates) pour servir leurs propres intérêts. Ainsi, la justice n'est pas une valeur universelle ou objective, mais un outil de domination. Il  va plus loin en affirmant que l'injustice est une vertu. Selon lui, les individus injustes sont plus heureux et plus prospères que les justes, car ils savent exploiter les autres à leur avantage. La justice, au contraire, est une faiblesse qui empêche les individus de réaliser leur plein potentiel. &lt;/p&gt;&lt;p&gt; Il  est souvent vu comme un précurseur du relativisme moral, qui nie l'existence de valeurs universelles. Sa pensée peut être rapprochée du réalisme politique, qui considère que la politique est avant tout une lutte pour le pouvoir et que les notions de justice et de moralité sont secondaires. &lt;/p&gt; &lt;p&gt; Il  incarne une vision cynique et réaliste de la justice, qui &lt;a href=&quot;https://www.persee.fr/doc/antiq_0770-2817_2018_num_87_1_3962&quot; style=&quot;color:#88A1E9&quot; title=&quot;Les difficultés du débat sur la justice entre Socrate et Thrasymaque dans la République par Persée &quot;&gt;contraste fortement&lt;/a&gt; avec l'idéalisme de Socrate. Bien que ses arguments soient finalement réfutés dans le dialogue, ils restent une contribution importante à la philosophie politique, car ils soulèvent des questions fondamentales sur la nature du pouvoir, de la moralité et de la justice. &lt;/p&gt;"/>
-    <hyperlink ref="E30" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eudoxe_de_Cnide&quot;  title=&quot; Wikipedia&quot;&gt;EUDOXE de Cnide&lt;/a&gt; était un mathématicien, astronome et philosophe grec de l'Antiquité, originaire de la ville de Cnide, en Asie Mineure (actuelle Turquie). Il est surtout connu pour   &lt;a href=&quot;https://www.youtube.com/watch?v=YiWuTuTPOEw&quot;  style=&quot;color:#88A1E9&quot; title=&quot; The Fascinating History of Mathematics : Eudoxus of Cnidus par Cambia Math Tutors&quot;&gt;ses travaux &lt;/a&gt;  en géométrie et en théorie des proportions. Ses contributions ont jeté les bases de nombreuses décounidevertes ultérieures, notamment celles d'Euclide. Il a développé une théorie générale des proportions qui permettait de comparer des grandeurs incommensurables. Cette théorie a permis de surmonter les limitations des mathématiques pythagoriciennes, qui étaient basées sur les nombres entiers. Il a étudié les sections coniques et les solides géométriques, contribuant à la compréhension des formes tridimensionnelles. &lt;/p&gt; &lt;p&gt; Il a proposé un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%A9ocentrisme&quot;  title=&quot; geocentrisme par wikipedia&quot;&gt;modèle géocentrique &lt;/a&gt; complexe pour expliquer les mouvements apparents des planètes, du Soleil et de la Lune. Selon ce modèle, chaque corps céleste est attaché à une série de sphères imbriquées, tournant à des vitesses et des angles différents. Ce système permettait de reproduire les mouvements rétrogrades des planètes (lorsqu'elles semblent reculer dans le ciel). Bien que ce modèle ait été remplacé plus tard par celui de Ptolémée, il a marqué une étape importante dans l'histoire de l'astronomie. &lt;/p&gt; &lt;p&gt; Il a soutenu que le plaisir est le bien suprême, une idée qui contraste avec les vues de Platon et d'Aristote. Pour Eudoxe, le plaisir est une fin en soi et non simplement un moyen et a critiqué la théorie des Idées de Platon, arguant que les Idées ne peuvent pas exister séparément des objets concrets. &lt;/p&gt; "/>
-    <hyperlink ref="H37" r:id="rId6" display="https://www.laphilo.fr/pho/aristippel-mini.webp"/>
-    <hyperlink ref="E44" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89picure&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9donisme&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'hédonisme par Wikipédia&quot;&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href=&quot;https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href=&quot;https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href=&quot;https://www.youtube.com/watch?v=cb1YHXSuxlM&quot;   title=&quot;La philosophie du bonheur par Parole de philosophe&quot;&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt;  &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées &quot;atomes&quot;.&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt;  &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title=&quot;Est il bien raisonnable d'avoir peur de la mort par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E54" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame&quot; title=&quot;Wikipedia&quot;&gt;Hégésinous de PERGAME&lt;/a&gt; était un philosophe grec, représentant de la &lt;em&gt;Moyenne Académie&lt;/em&gt; platonicienne. Il succéda à Évandre et Télécès à la direction de l'Académie d'Athènes et fut le maître direct de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt;, qui allait révolutionner la pensée académicienne avec sa Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Comme ses prédécesseurs, Hégésinous s'inscrivait dans la tradition sceptique d'Arcésilas, défendant la suspension du jugement face à l'incertitude radicale de la connaissance humaine. Son enseignement, dont nous ne conservons aucun écrit, fut néanmoins suffisamment stimulant pour former l'un des plus grands dialecticiens de l'Antiquité en la personne de Carnéade.&lt;/p&gt; &lt;p&gt;Hégésinous appartient à cette lignée de scholarques discrets qui assurèrent la survie institutionnelle de l'Académie durant les IIIe et IIe siècles av. J.-C. Son rôle de maillon entre la Moyenne et la Nouvelle Académie est fondamental, même si son nom reste peu connu en dehors des spécialistes de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie hellénistique sur Wikipedia&quot;&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;"/>
-    <hyperlink ref="E55" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Wikipedia&quot;&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Dialectique&quot; title=&quot;Dialectique par Wikipedia&quot;&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272&quot; title=&quot;Opinion et certitude par Persee&quot;&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href=&quot;https://fr.wikipedia.org/wiki/Cic%C3%A9ron&quot; style=&quot;color:#6A142A&quot; title=&quot;Cicéron sur Wikipedia&quot;&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il.&lt;/p&gt;"/>
-    <hyperlink ref="E57" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s&quot; title=&quot;Wikipedia&quot;&gt;TÉLÉCLÈS&lt;/a&gt; était un philosophe grec représentant de la Moyenne Académie platonicienne. Disciple de Lacydès de Cyrène, il dirigea conjointement l'Académie d'Athènes avec Évandre, après que Lacydès leur eut confié la responsabilité de l'École de son vivant.&lt;/p&gt; &lt;p&gt;Très peu de détails biographiques nous sont parvenus sur sa vie et sa pensée. Il s'inscrivait dans la tradition sceptique inaugurée par Arcésilas, défendant l'idée que la raison humaine ne peut accéder à une certitude absolue, et que la sagesse réside dans la suspension du jugement et l'adhésion au vraisemblable. Ses étudiants comprenaient de futurs représentants de la Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Téléclès appartient à ces figures de transition dont le rôle, discret mais essentiel, fut d'assurer la pérennité de l'Académie entre deux grandes figures : Lacydès avant lui et &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; style=&quot;color:#6A142A&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt; après lui. Son passage à la direction de l'École illustre la collégialité qui caractérisait l'organisation de la pensée académicienne.&lt;/p&gt;"/>
-    <hyperlink ref="E58" r:id="rId11" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes&quot;  title=&quot; Wikipedia&quot;&gt;PANÉTIUS DE RHODES&lt;/a&gt;  était un philosophe grec considéré comme le fondateur de l'école Stoïcienne de Rhodes. Il a étudié avec Diogène de Babylone et est devenu plus tard l'un des penseurs de Cicéron, le célèbre orateur et homme politique romain. &lt;/p&gt; &lt;p&gt;  Il a contribué à façonner la  &lt;a href=&quot;https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie&quot;  title=&quot;Le Stoïcisme par apprendre la philo&quot;&gt;pensée stoïcienne&lt;/a&gt; en l'adaptant aux besoins de son temps en la conciliant  avec d'autres courants philosophiques comme l'épicurisme et le scepticisme. Il rompt avec les dogmes stoïciens. « Il nie la conflagration universelle et croit à l'éternité d'un monde que la Providence rend parfait ». &lt;/p&gt; &lt;p&gt; Il se défie de la mantique (la divination) et nie l'immortalité de l'âme. Il reconnaît en nous, à côté des impulsions de l'instinct premier, des tendances fondamentales où s'associent nature et raison. &lt;/p&gt; &lt;p&gt; Il aboutit à un humanisme, il tend à une sérénité morale faite de calme, de mesure, d'harmonie. Il a également développé la notion de justice naturelle, qui est une forme de justice qui découle de la nature même de l'homme et de la société, et qui est différente de la justice conventionnelle établie par les lois et les coutumes.&lt;/p&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E59" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Posidonios&quot;  title=&quot; Wikipedia&quot;&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href=&quot;https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770&quot;  title=&quot;Posidonius d'Apamée théoricien de la géométrie par Persée&quot;&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href=&quot;https://www.youtube.com/watch?v=EqU-kD8dW4Y&quot; title=&quot;Grèce antique - 33 La civilisation hellénistique par Yannick Rub&quot;&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289&quot;  title=&quot;La philosophiede Posidonius par Persee&quot;&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; "/>
-    <hyperlink ref="E65" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que&quot; title=&quot; Wikipedia&quot;&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href=&quot;https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Le Stoïcisme par le Précepteur&quot;&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=J3wZoqElCgs&quot; title=&quot;Who is Seneca par Daily Stoic &quot;&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href=&quot;https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin&quot; title=&quot;La vie Heureuse par Karl Baudoin&quot;&gt; &quot;une vie heureuse&quot;.&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : - De la brièveté de la vie (consideration sur l’usage du temps). - De la colère (sur la maîtrise de cette passion destructive). - De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt;  est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href=&quot;https://www.youtube.com/watch?v=d_cge9OwVAs&quot; title=&quot;La vie philosophique de Sénèque par Kosmos&quot;&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title=&quot;Les lettres à Lucilius – Senèque  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="E66" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;AMMONIOS d'Athènes&lt;/a&gt; était un philosophe platonicien originaire d'Égypte, qui enseigna à Athènes et fut l'un des maîtres de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Plutarque&quot; style=&quot;color:#6A142A&quot; title=&quot;Plutarque sur Wikipedia&quot;&gt;Plutarque&lt;/a&gt;. Représentant du médio-platonisme, il cherchait à concilier la philosophie de Platon avec d'autres courants de pensée de l'Antiquité tardive.&lt;/p&gt; &lt;p&gt;Son enseignement oral laissa une empreinte durable sur ses disciples, bien qu'il n'ait laissé aucun écrit. Il défendait une lecture spirituelle et morale du platonisme, insistant sur la contemplation du Bien et la purification de l'âme. Plutarque, son élève le plus illustre, rapporte ses enseignements dans ses &lt;em&gt;Moralia&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Ammonios d'Athènes appartient à ce courant de platoniciens qui, entre Platon et Plotin, ont préparé le terrain au &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;, en développant une exégèse du &lt;em&gt;Timée&lt;/em&gt; et de la &lt;em&gt;République&lt;/em&gt;. Sa discrétion littéraire contraste avec l'influence considérable qu'il exerça sur le cercle intellectuel d'Athènes de son époque.&lt;/p&gt;"/>
-    <hyperlink ref="H76" r:id="rId15" display="https://www.laphilo.fr/pho/jamblique-mini.webp"/>
-    <hyperlink ref="H83" r:id="rId16" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="H84" r:id="rId17" display="https://www.laphilo.fr/pho/scyrene-mini.webp"/>
-    <hyperlink ref="E85" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot;   title=&quot;Proclus par Wikipédia&quot;&gt; PROCLUS&lt;/a&gt; était un philosophe &lt;a href=&quot;https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D&quot;   title=&quot;Le Néoplatonisme par Anne Baudart&quot;&gt; Néoplatonicien grec&lt;/a&gt; et il est considéré comme l'un des derniers grands philosophes de l'Antiquité classique.&lt;/p&gt;&#10;&lt;p&gt; Sa philosophie est basée sur les enseignements de Platon et d'Aristote. Il a développé une théorie complexe de l'univers qui est basée sur l'idée d'une hiérarchie de réalités. Au sommet de cette hiérarchie se trouve l'Un, qui est la réalité ultime et incompréhensible. Voici les principaux concepts de la philosophie de Proclus :&lt;/p&gt;&#10;&lt;dd&gt;L'Un : Réalité ultime et incompréhensible, qui est la source de toutes choses.&lt;/dd&gt;&#10;&lt;dd&gt;Le Démiurge : Force créatrice qui a donné forme à l'univers.&lt;/dd&gt;&#10;&lt;dd&gt;Les dieux : Intermédiaires entre l'Un et le monde sensible.&lt;/dd&gt;&#10;&lt;dd&gt;Les âmes : Principes vitaux qui animent les êtres vivants.&lt;/dd&gt;&#10;&lt;dd&gt;La matière : Réalité la plus basse de la hiérarchie, source du changement et de la corruption.&lt;/dd&gt;&#10;&lt;p&gt; Il a écrit un grand nombre &lt;a href=&quot;https://remacle.org/bloodwolf/philosophes/proclus/table.htm&quot;   title=&quot;Proclus par Philippe Remacle&quot;&gt; d'ouvrages sur la philosophie&lt;/a&gt;, dont les plus importants sont &lt;a href=&quot;https://www.youtube.com/watch?v=SJK1kbyXXno&quot;   title=&quot;Les éléments de Théologie de Proclus par LabEx HaStec&quot;&gt; les Commentaires sur le Timée de Platon&lt;/a&gt;, les Éléments de théologie et les Hypotyposes platonicae. Ces ouvrages ont été d'une grande influence sur la philosophie occidentale, et ils continuent à être étudiés aujourd'hui. &lt;/p&gt;   &lt;audio controls title=&quot; Proclus, un philosophe étoilé par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;"/>
-    <hyperlink ref="E86" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;HERMIAS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien, élève du grand &lt;a href=&quot;https://fr.wikipedia.org/wiki/Syrianos&quot; title=&quot;Syrianus sur Wikipedia&quot;&gt;Syrianus&lt;/a&gt; à Athènes. De retour à Alexandrie, il y fonda une école philosophique et épousa Aidésia, dont il eut pour fils le célèbre Ammonios d'Alexandrie.&lt;/p&gt; &lt;p&gt;Son œuvre principale est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes prises lors des cours de Syrianus. Cet ouvrage, qui nous est parvenu, offre une interprétation allégorique et métaphysique du dialogue platonicien sur l'amour, l'âme et la beauté, dans la tradition néoplatonicienne.&lt;/p&gt; &lt;p&gt;Hermias s'inscrit dans la lignée des maîtres qui firent d'Alexandrie un foyer majeur de la pensée antique tardive. Son rôle de transmetteur entre l'école d'Athènes et celle d'Alexandrie fut déterminant pour la pérennité du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;. Sa mort prématurée laissa Aidésia seule pour assurer l'avenir philosophique de leurs fils.&lt;/p&gt;"/>
-    <hyperlink ref="H88" r:id="rId20" display="https://www.laphilo.fr/pho/damascios-mini.webp"/>
-    <hyperlink ref="E89" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;AMMONIOS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien de la fin de l'Antiquité, fils d'Hermias et d'Aidésia, tous deux philosophes. Il succéda à Proclos comme tête de l'école néoplatonicienne d'Athènes et dirigea l'école alexandrine, formant une génération de commentateurs d'Aristote comme Olympiodore, Jean Philopon ou Simplicius, dans un contexte de tensions entre païens et chrétiens. Il enseigna l'Aristote aux païens et le Platon aux chrétiens pour favoriser une harmonie entre doctrines. &lt;/p&gt; &lt;p&gt; Spécialiste des commentaires d'Aristote, il défendit une interprétation néoplatonicienne unifiant Aristote et Platon : Aristote prépare à Platon, l'âme s'élève de la matière à l'Intellect divin. Ses écrits, perdus sauf fragments, insistent sur la théurgie et l'exégèse allégorique.&lt;/p&gt; &lt;p&gt; Son école alexandrine préserva le corpus aristotélicien pour l'Islam et l'Occident médiéval. &lt;/p&gt; Aucun texte complet ne survit directement, mais ses leçons sont préservées via les commentaires de ses élèves, comme ceux de Philopon sur l'Isagogè. Il chercha à harmoniser les deux grands penseurs antiques pour préserver la tradition païenne face au christianisme dominant.https://www.ljallamion.fr/spip.php?article6169 &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E90" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isidore_de_Gaza&quot; title=&quot;Wikipedia&quot;&gt;ISIDORE de Gaza&lt;/a&gt; était un philosophe néoplatonicien, né à Gaza en Palestine. Maître de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Damascios&quot; title=&quot;Damascios sur Wikipedia&quot;&gt;Damascios&lt;/a&gt;, le dernier scholarque de l'Académie d'Athènes, il fut l'un des derniers grands représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot;  title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique.&lt;/p&gt; &lt;p&gt;Damascios lui consacra une biographie dans sa &lt;em&gt;Vie d'Isidore&lt;/em&gt; (aussi connue sous le nom de &lt;em&gt;Vie des philosophes&lt;/em&gt;), où il le dépeint comme un personnage d'une grande intégrité morale, attaché aux traditions philosophiques grecques et à la piété envers les dieux, dans un contexte où le christianisme triomphait. Isidore représentait une philosophie vécue comme exercice spirituel, alliant rigueur intellectuelle et pratique ascétique.&lt;/p&gt; &lt;p&gt;Sa pensée s'inscrit dans la grande tradition de l'école néoplatonicienne d'Athènes, héritière de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot; title=&quot;Proclus sur Wikipedia&quot;&gt;Proclus&lt;/a&gt;. Il incarne ces penseurs de la fin du paganisme grec qui, face à la montée de la chrétienté, s'accrochaient à la philosophie comme à une forme de spiritualité rationnelle et contemplative, gardienne de l'héritage intellectuel de la Grèce.&lt;/p&gt;"/>
-    <hyperlink ref="H90" r:id="rId23" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="H93" r:id="rId24" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="E94" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Simplicius_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698&quot; style=&quot;color:#88A1E9&quot; title=&quot;A propos de la biographie de Simplicius par Persée&quot;&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le &quot;Manuel d’Épictète&quot; et, selon la tradition, sur &quot;De l’âme&quot;. Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href=&quot;https://www.youtube.com/watch?v=C17VYcyLkiY&quot; style=&quot;color:#88A1E9&quot; title=&quot;SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions&quot;&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.  &lt;a href=&quot;https://www.youtube.com/watch?v=6a4uQpmGsUg&quot; style=&quot;color:#88A1E9&quot; title=&quot;Simplicius – The Last Guardian of Ancient Philosophy par A time in history&quot;&gt; Transmis et traduits&lt;/a&gt; dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; "/>
-    <hyperlink ref="E97" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Priscien_de_Lydie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316&quot; title=&quot;la géographie et les originesnéoplatonisme sur Persee&quot;&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité :  - « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. - « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;"/>
-    <hyperlink ref="E99" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;EULAMIOS de Phrygie&lt;/a&gt; était un philosophe néoplatonicien du VIe siècle, originaire de Phrygie en Asie Mineure (actuelle Turquie). Il appartient au cercle des derniers représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique, dont il perpétua la tradition après la fermeture de l'Académie d'Athènes par Justinien en 529.&lt;/p&gt; &lt;p&gt;Figure peu documentée de cette période de transition, il s'inscrit dans le mouvement de philosophes néoplatoniciens qui, après l'exil perse et la dispersion de l'école athénienne, continuèrent à enseigner et transmettre la philosophie grecque en dehors des institutions officielles. Ses liens avec les cercles de Damascios et Simplicius laissent penser qu'il participa à la préservation du corpus philosophique antique.&lt;/p&gt; &lt;p&gt;Eulamios représente la philosophie de survie du néoplatonisme face à la christianisation de l'Empire. Comme ses contemporains, il incarne la volonté de maintenir vivante une tradition intellectuelle millénaire, préservant ainsi les conditions de la redécouverte médiévale et renaissante de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_antique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie antique sur Wikipedia&quot;&gt;philosophie antique&lt;/a&gt;.&lt;/p&gt;"/>
-    <hyperlink ref="H99" r:id="rId28" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="E100" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie&quot; title=&quot;Wikipedia&quot;&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.https://fr.wikipedia.org/wiki/Diogène_de_Phénicie    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;"/>
+    <hyperlink ref="E16" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Protagoras&quot;  title=&quot;Protagoras par Wikipédia&quot;&gt; PROTAGORAS&lt;/a&gt;  était un philosophe considéré comme l'un &lt;a href=&quot;https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;ab_channel=Bibiclo&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Les Sophistes par Bobiclo&quot;&gt; des sophistes&lt;/a&gt; les plus célèbres de cette période.&lt;/p&gt;&#10;&#10;&lt;p&gt;Les sophistes étaient des enseignants itinérants qui offraient &lt;a href=&quot;https://www.youtube.com/watch?v=X5bZKSCfc_g&amp;ab_channel=AlainBajom%C3%A9e&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Rhétorique et relativisme par Alain Bajomée&quot;&gt; des cours de rhétorique&lt;/a&gt;, d'éloquence et de persuader efficacement. Cependant, il a également suscité des débats et des controverses en raison de ses opinions et de ses idées.&lt;/p&gt;&#10;&lt;p&gt;L'une de ses déclarations les plus célèbres est : &quot;L'homme est la mesure de toutes choses : de celles qui sont, tant quand elles sont en tant qu'elles sont, que de celles qui ne sont pas, tant quand elles ne sont pas en tant qu'elles ne sont pas.&quot; Cela suggère que la perception et l'expérience individuelles sont centrales pour la compréhension de la réalité, et que la vérité peut être relative à chaque individu. Cette déclaration forme le fondement de ce que l'on appelle &lt;a href=&quot;https://www.youtube.com/watch?v=LxSCq1F7pSk&amp;ab_channel=LePr%C3%A9cepteur&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Le relativisme par le Précepteur&quot;&gt; le relativisme.&lt;/a&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Il a également abordé des sujets tels que la nature de la justice, l'éducation et le rôle des dieux dans la vie humaine. Ses enseignements ont été critiqués par d'autres philosophes, notamment Socrate et Platon, qui les voyaient vides de fondement rationnel.&lt;/p&gt;&#10;&#10;&lt;p&gt;Bien qu'il ait laissé peu d'œuvres écrites, sa vision de la relativité de la vérité et de l'importance de la rhétorique a contribué à façonner les débats sur la nature de la connaissance et de la réalité dans la philosophie grecque antique.&lt;/p&gt;  &lt;audio controls title=&quot;Platon vs. Protagoras: l'homme est il la mesure de toutes choses? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/09/s40/NET_FC_f081bba4-88ba-4b62-930d-2c30e49863d9.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E18" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gorgias&quot; title=&quot; Wikipedia&quot;&gt;GORGIAS&lt;/a&gt; était un philosophe présocratique et l'une des figures les plus importantes de la &lt;a href=&quot;https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;t=184s&quot; title=&quot; Les sophistes par Bibiclo&quot;&gt;sophistique&lt;/a&gt;.  Contrairement aux philosophes comme Platon ou Aristote, qui cherchaient à découvrir des vérités universelles en mettant l'accent sur l'importance de l'opinion et de la persuasion dans les affaires humaines.  Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;  - &quot;Sur le Non-Être ou sur la Nature&quot; : Il développe une argumentation radicale qui remet en question la possibilité même de la connaissance et de la communication.&lt;/p&gt; &lt;p&gt; -  Il soutient trois thèses principales : - Rien n'existe.  - Si quelque chose existait, nous ne pourrions pas le connaître. - Si nous pouvions le connaître, nous ne pourrions pas le communiquer aux autres. &lt;/p&gt; &lt;p&gt; Ces thèses sont souvent interprétées comme une critique de l'ontologie éléatique, notamment des idées de Parménide, qui affirmait que l'être est un et immuable. &lt;/p&gt;  &lt;p&gt; - &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89loge_d%27H%C3%A9l%C3%A8ne &quot;  title=&quot; Gorgias Eloge d’Helene  parWikipedia&quot;&gt;&quot;Éloge d'Hélène&quot;&lt;/a&gt;  : Dans ce discours, Il défend Hélène de Troie, souvent considérée comme responsable de la guerre de Troie. Il utilise des arguments rhétoriques pour montrer qu'elle ne peut être tenue pour responsable, car elle a été soit victime de la volonté des dieux, soit de la séduction de Pâris, soit de la force.  &lt;/p&gt; &lt;p&gt; -  &quot;Défense de Palamède&quot; : Dans ce discours, il défend Palamède, un héros grec accusé de trahison par Ulysse. Il utilise des arguments logiques et rhétoriques pour démontrer son l'innocence, montrant ainsi la puissance de la parole pour influencer les jugements. &lt;p&gt; Il  est souvent considéré comme un relativiste et un sceptique. Il met en doute la possibilité de connaître la vérité absolue et souligne l'importance de la persuasion dans les affaires humaines. Sa philosophie a eu une influence significative sur la pensée grecque, notamment sur Platon, qui le critique sévèrement dans son dialogue &quot;Gorgias&quot;. Platon y oppose la recherche de la vérité à l'art de la persuasion, qu'il associe à la sophistique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E22" r:id="rId3" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/D%C3%A9mocrite&quot; title=&quot; Wikipedia&quot;&gt; DÉMOCRITE&lt;/a&gt; était un philosophe Grec connu pour être l'un des fondateurs avec LEUCIPPE de la philosophie  &lt;a href=&quot;https://www.youtube.com/watch?v=AGvcey2B3Vc&amp;t=3s&amp;ab_channel=Coursitout&quot;   title=&quot;l'Atomisme des philosophes Grecs par Coursitout&quot;&gt; atomiste&lt;/a&gt;, une théorie selon laquelle tout dans l'univers est composé de particules indivisibles appelées atomes. Selon lui, ils sont en mouvement perpétuel et se combinent pour former toutes les substances et objets que nous voyons autour de nous.  Il était réputé pour sa grande curiosité intellectuelle et aurait beaucoup voyagé, notamment en Égypte et en Orient, afin d’enrichir ses connaissances. Surnommé parfois « le philosophe rieur », il adoptait une attitude détachée face aux préoccupations humaines, considérant que la sérénité naît de la compréhension du monde et de la maîtrise de soi.  &lt;/p&gt; &lt;p&gt;Il avait une approche &lt;a href=&quot;https://www.youtube.com/watch?v=_uXOu9ZRD4I&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;le matérialisme par Alain Bajomée&quot;&gt; matérialiste&lt;/a&gt; de la réalité et croyait que tout ce qui existe était composé de matière et de vide, et que la perception humaine était basée sur l'interaction entre les atomes et les sens. Il était également connu pour ses idées sur l'éthique et la morale et croyait que le bonheur et la vertu pouvaient être atteints grâce à une vie simple et équilibrée, et que les désirs excessifs et les passions pouvaient entraîner la souffrance. &lt;/p&gt; &lt;p&gt; Sa pensée ne se limite pas à la physique : il développe aussi une réflexion approfondie sur la connaissance en distinguant les qualités « réelles » (comme la forme et le mouvement des atomes) des qualités « sensibles » (comme les couleurs ou les saveurs), qui dépendent de nos perceptions. Cette distinction annonce des débats majeurs de la philosophie moderne. Son influence se retrouvera plus tard chez des penseurs comme Épicure, qui reprendra l’atomisme en y intégrant une dimension éthique centrée sur la recherche du plaisir mesuré et de l’absence de trouble.   &lt;/p&gt; &lt;p&gt; Peu de ses écrits ont survécu jusqu'à nos jours, et la plupart de ce que nous connaissons provient de commentaires ultérieurs et de citations dans les œuvres d'autres philosophes grecs. Cependant, ses contributions à la théorie atomique ont été fondamentales pour la compréhension moderne de la physique et de la chimie. &lt;/p&gt; &lt;audio controls title=&quot;Démocrite contre Platon par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2015/06/s27/net-fi-be35a965-485b-4f98-9b10-0e2051e903ec.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="E23" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thrasymaque&quot;title=&quot; Wikipedia&quot;&gt;THRASYMAQUE&lt;/a&gt; était un philosophe sophiste grec connue pour son rôle dans &lt;a href=&quot;https://www.youtube.com/watch?v=qSrvZvjPG_w&quot; style=&quot;color:#88A1E9&quot; title=&quot; PLATON-Cest quoi la république par Kosmos &quot;&gt;&quot;La République&quot;&lt;/a&gt; de Platon. Il est l'un des interlocuteurs de Socrate dans ce dialogue, où il défend une vision provocante et cynique de la justice. &lt;/p&gt;&lt;p&gt; Il  affirme que &quot;&lt;a href=&quot;https://www.youtube.com/watch?v=VlLLr8kVya0&quot;  title=&quot;  Qu'est-ce que la Justice en Philosophie ?   par Coursitout &quot;&gt;la justice&lt;/a&gt; n'est rien d'autre que l'intérêt du plus fort&quot;. Selon lui, les lois et les normes sociales sont établies par ceux qui détiennent le pouvoir (les gouvernants, les tyrans, les aristocrates) pour servir leurs propres intérêts. Ainsi, la justice n'est pas une valeur universelle ou objective, mais un outil de domination. Il  va plus loin en affirmant que l'injustice est une vertu. Selon lui, les individus injustes sont plus heureux et plus prospères que les justes, car ils savent exploiter les autres à leur avantage. La justice, au contraire, est une faiblesse qui empêche les individus de réaliser leur plein potentiel. &lt;/p&gt;&lt;p&gt; Il  est souvent vu comme un précurseur du relativisme moral, qui nie l'existence de valeurs universelles. Sa pensée peut être rapprochée du réalisme politique, qui considère que la politique est avant tout une lutte pour le pouvoir et que les notions de justice et de moralité sont secondaires. &lt;/p&gt; &lt;p&gt; Il  incarne une vision cynique et réaliste de la justice, qui &lt;a href=&quot;https://www.persee.fr/doc/antiq_0770-2817_2018_num_87_1_3962&quot; style=&quot;color:#88A1E9&quot; title=&quot;Les difficultés du débat sur la justice entre Socrate et Thrasymaque dans la République par Persée &quot;&gt;contraste fortement&lt;/a&gt; avec l'idéalisme de Socrate. Bien que ses arguments soient finalement réfutés dans le dialogue, ils restent une contribution importante à la philosophie politique, car ils soulèvent des questions fondamentales sur la nature du pouvoir, de la moralité et de la justice. &lt;/p&gt;"/>
+    <hyperlink ref="E31" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eudoxe_de_Cnide&quot;  title=&quot; Wikipedia&quot;&gt;EUDOXE de Cnide&lt;/a&gt; était un mathématicien, astronome et philosophe grec de l'Antiquité, originaire de la ville de Cnide, en Asie Mineure (actuelle Turquie). Il est surtout connu pour   &lt;a href=&quot;https://www.youtube.com/watch?v=YiWuTuTPOEw&quot;  style=&quot;color:#88A1E9&quot; title=&quot; The Fascinating History of Mathematics : Eudoxus of Cnidus par Cambia Math Tutors&quot;&gt;ses travaux &lt;/a&gt;  en géométrie et en théorie des proportions. Ses contributions ont jeté les bases de nombreuses décounidevertes ultérieures, notamment celles d'Euclide. Il a développé une théorie générale des proportions qui permettait de comparer des grandeurs incommensurables. Cette théorie a permis de surmonter les limitations des mathématiques pythagoriciennes, qui étaient basées sur les nombres entiers. Il a étudié les sections coniques et les solides géométriques, contribuant à la compréhension des formes tridimensionnelles. &lt;/p&gt; &lt;p&gt; Il a proposé un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%A9ocentrisme&quot;  title=&quot; geocentrisme par wikipedia&quot;&gt;modèle géocentrique &lt;/a&gt; complexe pour expliquer les mouvements apparents des planètes, du Soleil et de la Lune. Selon ce modèle, chaque corps céleste est attaché à une série de sphères imbriquées, tournant à des vitesses et des angles différents. Ce système permettait de reproduire les mouvements rétrogrades des planètes (lorsqu'elles semblent reculer dans le ciel). Bien que ce modèle ait été remplacé plus tard par celui de Ptolémée, il a marqué une étape importante dans l'histoire de l'astronomie. &lt;/p&gt; &lt;p&gt; Il a soutenu que le plaisir est le bien suprême, une idée qui contraste avec les vues de Platon et d'Aristote. Pour Eudoxe, le plaisir est une fin en soi et non simplement un moyen et a critiqué la théorie des Idées de Platon, arguant que les Idées ne peuvent pas exister séparément des objets concrets. &lt;/p&gt; "/>
+    <hyperlink ref="H38" r:id="rId6" display="https://www.laphilo.fr/pho/aristippel-mini.webp"/>
+    <hyperlink ref="E45" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89picure&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9donisme&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'hédonisme par Wikipédia&quot;&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href=&quot;https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href=&quot;https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href=&quot;https://www.youtube.com/watch?v=cb1YHXSuxlM&quot;   title=&quot;La philosophie du bonheur par Parole de philosophe&quot;&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt;  &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées &quot;atomes&quot;.&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt;  &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title=&quot;Est il bien raisonnable d'avoir peur de la mort par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E55" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame&quot; title=&quot;Wikipedia&quot;&gt;Hégésinous de PERGAME&lt;/a&gt; était un philosophe grec, représentant de la &lt;em&gt;Moyenne Académie&lt;/em&gt; platonicienne. Il succéda à Évandre et Télécès à la direction de l'Académie d'Athènes et fut le maître direct de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt;, qui allait révolutionner la pensée académicienne avec sa Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Comme ses prédécesseurs, Hégésinous s'inscrivait dans la tradition sceptique d'Arcésilas, défendant la suspension du jugement face à l'incertitude radicale de la connaissance humaine. Son enseignement, dont nous ne conservons aucun écrit, fut néanmoins suffisamment stimulant pour former l'un des plus grands dialecticiens de l'Antiquité en la personne de Carnéade.&lt;/p&gt; &lt;p&gt;Hégésinous appartient à cette lignée de scholarques discrets qui assurèrent la survie institutionnelle de l'Académie durant les IIIe et IIe siècles av. J.-C. Son rôle de maillon entre la Moyenne et la Nouvelle Académie est fondamental, même si son nom reste peu connu en dehors des spécialistes de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie hellénistique sur Wikipedia&quot;&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;"/>
+    <hyperlink ref="E56" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Wikipedia&quot;&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Dialectique&quot; title=&quot;Dialectique par Wikipedia&quot;&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272&quot; title=&quot;Opinion et certitude par Persee&quot;&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href=&quot;https://fr.wikipedia.org/wiki/Cic%C3%A9ron&quot; style=&quot;color:#6A142A&quot; title=&quot;Cicéron sur Wikipedia&quot;&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il.&lt;/p&gt;"/>
+    <hyperlink ref="E58" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s&quot; title=&quot;Wikipedia&quot;&gt;TÉLÉCLÈS&lt;/a&gt; était un philosophe grec représentant de la Moyenne Académie platonicienne. Disciple de Lacydès de Cyrène, il dirigea conjointement l'Académie d'Athènes avec Évandre, après que Lacydès leur eut confié la responsabilité de l'École de son vivant.&lt;/p&gt; &lt;p&gt;Très peu de détails biographiques nous sont parvenus sur sa vie et sa pensée. Il s'inscrivait dans la tradition sceptique inaugurée par Arcésilas, défendant l'idée que la raison humaine ne peut accéder à une certitude absolue, et que la sagesse réside dans la suspension du jugement et l'adhésion au vraisemblable. Ses étudiants comprenaient de futurs représentants de la Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Téléclès appartient à ces figures de transition dont le rôle, discret mais essentiel, fut d'assurer la pérennité de l'Académie entre deux grandes figures : Lacydès avant lui et &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; style=&quot;color:#6A142A&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt; après lui. Son passage à la direction de l'École illustre la collégialité qui caractérisait l'organisation de la pensée académicienne.&lt;/p&gt;"/>
+    <hyperlink ref="E59" r:id="rId11" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes&quot;  title=&quot; Wikipedia&quot;&gt;PANÉTIUS DE RHODES&lt;/a&gt;  était un philosophe grec considéré comme le fondateur de l'école Stoïcienne de Rhodes. Il a étudié avec Diogène de Babylone et est devenu plus tard l'un des penseurs de Cicéron, le célèbre orateur et homme politique romain. &lt;/p&gt; &lt;p&gt;  Il a contribué à façonner la  &lt;a href=&quot;https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie&quot;  title=&quot;Le Stoïcisme par apprendre la philo&quot;&gt;pensée stoïcienne&lt;/a&gt; en l'adaptant aux besoins de son temps en la conciliant  avec d'autres courants philosophiques comme l'épicurisme et le scepticisme. Il rompt avec les dogmes stoïciens. « Il nie la conflagration universelle et croit à l'éternité d'un monde que la Providence rend parfait ». &lt;/p&gt; &lt;p&gt; Il se défie de la mantique (la divination) et nie l'immortalité de l'âme. Il reconnaît en nous, à côté des impulsions de l'instinct premier, des tendances fondamentales où s'associent nature et raison. &lt;/p&gt; &lt;p&gt; Il aboutit à un humanisme, il tend à une sérénité morale faite de calme, de mesure, d'harmonie. Il a également développé la notion de justice naturelle, qui est une forme de justice qui découle de la nature même de l'homme et de la société, et qui est différente de la justice conventionnelle établie par les lois et les coutumes.&lt;/p&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E60" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Posidonios&quot;  title=&quot; Wikipedia&quot;&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href=&quot;https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770&quot;  title=&quot;Posidonius d'Apamée théoricien de la géométrie par Persée&quot;&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href=&quot;https://www.youtube.com/watch?v=EqU-kD8dW4Y&quot; title=&quot;Grèce antique - 33 La civilisation hellénistique par Yannick Rub&quot;&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289&quot;  title=&quot;La philosophiede Posidonius par Persee&quot;&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; "/>
+    <hyperlink ref="E66" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que&quot; title=&quot; Wikipedia&quot;&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href=&quot;https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Le Stoïcisme par le Précepteur&quot;&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=J3wZoqElCgs&quot; title=&quot;Who is Seneca par Daily Stoic &quot;&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href=&quot;https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin&quot; title=&quot;La vie Heureuse par Karl Baudoin&quot;&gt; &quot;une vie heureuse&quot;.&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : - De la brièveté de la vie (consideration sur l’usage du temps). - De la colère (sur la maîtrise de cette passion destructive). - De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt;  est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href=&quot;https://www.youtube.com/watch?v=d_cge9OwVAs&quot; title=&quot;La vie philosophique de Sénèque par Kosmos&quot;&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title=&quot;Les lettres à Lucilius – Senèque  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="E67" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;AMMONIOS d'Athènes&lt;/a&gt; était un philosophe platonicien originaire d'Égypte, qui enseigna à Athènes et fut l'un des maîtres de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Plutarque&quot; style=&quot;color:#6A142A&quot; title=&quot;Plutarque sur Wikipedia&quot;&gt;Plutarque&lt;/a&gt;. Représentant du médio-platonisme, il cherchait à concilier la philosophie de Platon avec d'autres courants de pensée de l'Antiquité tardive.&lt;/p&gt; &lt;p&gt;Son enseignement oral laissa une empreinte durable sur ses disciples, bien qu'il n'ait laissé aucun écrit. Il défendait une lecture spirituelle et morale du platonisme, insistant sur la contemplation du Bien et la purification de l'âme. Plutarque, son élève le plus illustre, rapporte ses enseignements dans ses &lt;em&gt;Moralia&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Ammonios d'Athènes appartient à ce courant de platoniciens qui, entre Platon et Plotin, ont préparé le terrain au &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;, en développant une exégèse du &lt;em&gt;Timée&lt;/em&gt; et de la &lt;em&gt;République&lt;/em&gt;. Sa discrétion littéraire contraste avec l'influence considérable qu'il exerça sur le cercle intellectuel d'Athènes de son époque.&lt;/p&gt;"/>
+    <hyperlink ref="H77" r:id="rId15" display="https://www.laphilo.fr/pho/jamblique-mini.webp"/>
+    <hyperlink ref="H84" r:id="rId16" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="H85" r:id="rId17" display="https://www.laphilo.fr/pho/scyrene-mini.webp"/>
+    <hyperlink ref="E86" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot;   title=&quot;Proclus par Wikipédia&quot;&gt; PROCLUS&lt;/a&gt; était un philosophe &lt;a href=&quot;https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D&quot;   title=&quot;Le Néoplatonisme par Anne Baudart&quot;&gt; Néoplatonicien grec&lt;/a&gt; et il est considéré comme l'un des derniers grands philosophes de l'Antiquité classique.&lt;/p&gt;&#10;&lt;p&gt; Sa philosophie est basée sur les enseignements de Platon et d'Aristote. Il a développé une théorie complexe de l'univers qui est basée sur l'idée d'une hiérarchie de réalités. Au sommet de cette hiérarchie se trouve l'Un, qui est la réalité ultime et incompréhensible. Voici les principaux concepts de la philosophie de Proclus :&lt;/p&gt;&#10;&lt;dd&gt;L'Un : Réalité ultime et incompréhensible, qui est la source de toutes choses.&lt;/dd&gt;&#10;&lt;dd&gt;Le Démiurge : Force créatrice qui a donné forme à l'univers.&lt;/dd&gt;&#10;&lt;dd&gt;Les dieux : Intermédiaires entre l'Un et le monde sensible.&lt;/dd&gt;&#10;&lt;dd&gt;Les âmes : Principes vitaux qui animent les êtres vivants.&lt;/dd&gt;&#10;&lt;dd&gt;La matière : Réalité la plus basse de la hiérarchie, source du changement et de la corruption.&lt;/dd&gt;&#10;&lt;p&gt; Il a écrit un grand nombre &lt;a href=&quot;https://remacle.org/bloodwolf/philosophes/proclus/table.htm&quot;   title=&quot;Proclus par Philippe Remacle&quot;&gt; d'ouvrages sur la philosophie&lt;/a&gt;, dont les plus importants sont &lt;a href=&quot;https://www.youtube.com/watch?v=SJK1kbyXXno&quot;   title=&quot;Les éléments de Théologie de Proclus par LabEx HaStec&quot;&gt; les Commentaires sur le Timée de Platon&lt;/a&gt;, les Éléments de théologie et les Hypotyposes platonicae. Ces ouvrages ont été d'une grande influence sur la philosophie occidentale, et ils continuent à être étudiés aujourd'hui. &lt;/p&gt;   &lt;audio controls title=&quot; Proclus, un philosophe étoilé par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;"/>
+    <hyperlink ref="E87" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;HERMIAS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien, élève du grand &lt;a href=&quot;https://fr.wikipedia.org/wiki/Syrianos&quot; title=&quot;Syrianus sur Wikipedia&quot;&gt;Syrianus&lt;/a&gt; à Athènes. De retour à Alexandrie, il y fonda une école philosophique et épousa Aidésia, dont il eut pour fils le célèbre Ammonios d'Alexandrie.&lt;/p&gt; &lt;p&gt;Son œuvre principale est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes prises lors des cours de Syrianus. Cet ouvrage, qui nous est parvenu, offre une interprétation allégorique et métaphysique du dialogue platonicien sur l'amour, l'âme et la beauté, dans la tradition néoplatonicienne.&lt;/p&gt; &lt;p&gt;Hermias s'inscrit dans la lignée des maîtres qui firent d'Alexandrie un foyer majeur de la pensée antique tardive. Son rôle de transmetteur entre l'école d'Athènes et celle d'Alexandrie fut déterminant pour la pérennité du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;. Sa mort prématurée laissa Aidésia seule pour assurer l'avenir philosophique de leurs fils.&lt;/p&gt;"/>
+    <hyperlink ref="H89" r:id="rId20" display="https://www.laphilo.fr/pho/damascios-mini.webp"/>
+    <hyperlink ref="E90" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;AMMONIOS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien de la fin de l'Antiquité, fils d'Hermias et d'Aidésia, tous deux philosophes. Il succéda à Proclos comme tête de l'école néoplatonicienne d'Athènes et dirigea l'école alexandrine, formant une génération de commentateurs d'Aristote comme Olympiodore, Jean Philopon ou Simplicius, dans un contexte de tensions entre païens et chrétiens. Il enseigna l'Aristote aux païens et le Platon aux chrétiens pour favoriser une harmonie entre doctrines. &lt;/p&gt; &lt;p&gt; Spécialiste des commentaires d'Aristote, il défendit une interprétation néoplatonicienne unifiant Aristote et Platon : Aristote prépare à Platon, l'âme s'élève de la matière à l'Intellect divin. Ses écrits, perdus sauf fragments, insistent sur la théurgie et l'exégèse allégorique.&lt;/p&gt; &lt;p&gt; Son école alexandrine préserva le corpus aristotélicien pour l'Islam et l'Occident médiéval. &lt;/p&gt; Aucun texte complet ne survit directement, mais ses leçons sont préservées via les commentaires de ses élèves, comme ceux de Philopon sur l'Isagogè. Il chercha à harmoniser les deux grands penseurs antiques pour préserver la tradition païenne face au christianisme dominant.https://www.ljallamion.fr/spip.php?article6169 &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E91" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isidore_de_Gaza&quot; title=&quot;Wikipedia&quot;&gt;ISIDORE de Gaza&lt;/a&gt; était un philosophe néoplatonicien, né à Gaza en Palestine. Maître de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Damascios&quot; title=&quot;Damascios sur Wikipedia&quot;&gt;Damascios&lt;/a&gt;, le dernier scholarque de l'Académie d'Athènes, il fut l'un des derniers grands représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot;  title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique.&lt;/p&gt; &lt;p&gt;Damascios lui consacra une biographie dans sa &lt;em&gt;Vie d'Isidore&lt;/em&gt; (aussi connue sous le nom de &lt;em&gt;Vie des philosophes&lt;/em&gt;), où il le dépeint comme un personnage d'une grande intégrité morale, attaché aux traditions philosophiques grecques et à la piété envers les dieux, dans un contexte où le christianisme triomphait. Isidore représentait une philosophie vécue comme exercice spirituel, alliant rigueur intellectuelle et pratique ascétique.&lt;/p&gt; &lt;p&gt;Sa pensée s'inscrit dans la grande tradition de l'école néoplatonicienne d'Athènes, héritière de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot; title=&quot;Proclus sur Wikipedia&quot;&gt;Proclus&lt;/a&gt;. Il incarne ces penseurs de la fin du paganisme grec qui, face à la montée de la chrétienté, s'accrochaient à la philosophie comme à une forme de spiritualité rationnelle et contemplative, gardienne de l'héritage intellectuel de la Grèce.&lt;/p&gt;"/>
+    <hyperlink ref="H91" r:id="rId23" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="H94" r:id="rId24" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="E95" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Simplicius_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698&quot; style=&quot;color:#88A1E9&quot; title=&quot;A propos de la biographie de Simplicius par Persée&quot;&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le &quot;Manuel d’Épictète&quot; et, selon la tradition, sur &quot;De l’âme&quot;. Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href=&quot;https://www.youtube.com/watch?v=C17VYcyLkiY&quot; style=&quot;color:#88A1E9&quot; title=&quot;SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions&quot;&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.  &lt;a href=&quot;https://www.youtube.com/watch?v=6a4uQpmGsUg&quot; style=&quot;color:#88A1E9&quot; title=&quot;Simplicius – The Last Guardian of Ancient Philosophy par A time in history&quot;&gt; Transmis et traduits&lt;/a&gt; dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; "/>
+    <hyperlink ref="E98" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Priscien_de_Lydie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316&quot; title=&quot;la géographie et les originesnéoplatonisme sur Persee&quot;&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité :  - « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. - « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;"/>
+    <hyperlink ref="E100" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;EULAMIOS de Phrygie&lt;/a&gt; était un philosophe néoplatonicien du VIe siècle, originaire de Phrygie en Asie Mineure (actuelle Turquie). Il appartient au cercle des derniers représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique, dont il perpétua la tradition après la fermeture de l'Académie d'Athènes par Justinien en 529.&lt;/p&gt; &lt;p&gt;Figure peu documentée de cette période de transition, il s'inscrit dans le mouvement de philosophes néoplatoniciens qui, après l'exil perse et la dispersion de l'école athénienne, continuèrent à enseigner et transmettre la philosophie grecque en dehors des institutions officielles. Ses liens avec les cercles de Damascios et Simplicius laissent penser qu'il participa à la préservation du corpus philosophique antique.&lt;/p&gt; &lt;p&gt;Eulamios représente la philosophie de survie du néoplatonisme face à la christianisation de l'Empire. Comme ses contemporains, il incarne la volonté de maintenir vivante une tradition intellectuelle millénaire, préservant ainsi les conditions de la redécouverte médiévale et renaissante de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_antique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie antique sur Wikipedia&quot;&gt;philosophie antique&lt;/a&gt;.&lt;/p&gt;"/>
+    <hyperlink ref="H100" r:id="rId28" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="E101" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie&quot; title=&quot;Wikipedia&quot;&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.https://fr.wikipedia.org/wiki/Diogène_de_Phénicie    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3628,8 +3628,10 @@
       <c r="K10" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>77</v>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Présocratique ; Monothéisme ; Éléatisme</t>
+        </is>
       </c>
       <c r="M10" s="2" t="s">
         <v>78</v>
@@ -3790,8 +3792,10 @@
       <c r="K13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>25</v>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Présocratique ; Éléatisme</t>
+        </is>
       </c>
       <c r="M13" s="2" t="s">
         <v>95</v>
@@ -3969,8 +3973,10 @@
       <c r="K17" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>25</v>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Présocratique ; Éléatisme</t>
+        </is>
       </c>
       <c r="M17" s="2" t="s">
         <v>130</v>
@@ -4107,8 +4113,10 @@
       <c r="K20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>25</v>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Présocratique ; Éléatisme</t>
+        </is>
       </c>
       <c r="M20" s="2" t="s">
         <v>158</v>
@@ -4283,8 +4291,10 @@
       <c r="K24" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="L24" s="2" t="s">
-        <v>149</v>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; École mégarique</t>
+        </is>
       </c>
       <c r="M24" s="2" t="s">
         <v>192</v>
@@ -4689,8 +4699,10 @@
       <c r="K33" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>149</v>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; École mégarique</t>
+        </is>
       </c>
       <c r="M33" s="2" t="s">
         <v>270</v>
@@ -5052,8 +5064,10 @@
       <c r="K41" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="L41" s="2" t="s">
-        <v>149</v>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; École mégarique</t>
+        </is>
       </c>
       <c r="M41" s="2" t="s">
         <v>334</v>
@@ -5140,8 +5154,10 @@
       <c r="K43" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="L43" s="2" t="s">
-        <v>149</v>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; École mégarique</t>
+        </is>
       </c>
       <c r="M43" s="2" t="s">
         <v>352</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -4872,8 +4872,10 @@
       <c r="F37" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G37" s="9" t="s">
-        <v>300</v>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La philosophie d'Aristote" par Voyages Endormis</t>
+        </is>
       </c>
       <c r="H37" s="9" t="s">
         <v>301</v>
@@ -6169,8 +6171,10 @@
       <c r="F66" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="G66" s="9" t="s">
-        <v>546</v>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Sénèque – Pourquoi vous gaspillez votre vie par Voyages Endormis</t>
+        </is>
       </c>
       <c r="H66" s="9" t="s">
         <v>547</v>
@@ -6530,8 +6534,10 @@
       <c r="F74" s="7" t="s">
         <v>610</v>
       </c>
-      <c r="G74" s="9" t="s">
-        <v>611</v>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L’ascension de Plotin" par Vox Temporis</t>
+        </is>
       </c>
       <c r="H74" s="9" t="s">
         <v>612</v>
@@ -7070,8 +7076,10 @@
       <c r="F86" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="G86" s="9" t="s">
-        <v>711</v>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Une vie, une œuvre" par Rien ne veut rien dire</t>
+        </is>
       </c>
       <c r="H86" s="9" t="s">
         <v>712</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3430,8 +3430,16 @@
       <c r="D6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>39</v>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anaximandre" style="color:#88A1E9"   title="Anaximandre par Wikipédia"&gt; ANAXIMANDRE DE MILET&lt;/a&gt; était un philosophe présocratique de l'école Ionienne et  un contemporain de Thalès, et il est souvent considéré comme l'un des premiers penseurs à développer des idées philosophiques systématiques sur la nature du monde.&lt;/p&gt;&lt;p&gt;
+L'une de ses contributions les plus importantes était sa tentative de fournir une explication naturelle et non mythologique de &lt;a href="https://www.youtube.com/watch?v=5x7J2u5LSh4&amp;t=2s&amp;ab_channel=Coursitout" style="color:#88A1E9"   title="L'origine de l'Univers selon Anaximandre par Coursitout"&gt; l'origine et de la structure de l'univers.&lt;/a&gt;. Il est souvent crédité d'avoir élaboré la première carte géographique du monde connu à l'époque. 
+&lt;/p&gt;&lt;p&gt;
+Il est aussi connu pour sa théorie de  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1957_num_70_329_3473" style="color:#88A1E9"   title="Sur la signification de l'apeiron d'Anaximandre par Persée"&gt; "l'apeiron"&lt;/a&gt;, également traduit par le terme "infini" ou "illimité". Selon lui, l'apeiron est l'élément primordial à partir duquel tout provient et dans lequel tout finit. C'est une substance indéfinie et indéterminée, ni de l'eau ni de l'air, qui est à l'origine du cosmos. Il pensait que tous les éléments et les objets de l'univers étaient issus de l'apeiron par des processus de séparation et de condensation.
+&lt;/p&gt;&lt;p&gt;
+Il pensait que la Terre était suspendue dans l'espace, sans soutien visible, et que les étoiles étaient des trous à travers lesquels la lumière du feu intérieur du cosmos brillait. Ces idées ont été radicales pour l'époque et ont contribué à poser les bases de la pensée philosophique et scientifique future.
+&lt;/p&gt; &lt;audio controls title="Anaximandre, Héraclite et les autres : au commencement était le feu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-13.09.2021-ITEMA_22772439-2021C12410S0256-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F6" s="7" t="s">
         <v>40</v>
@@ -3474,8 +3482,11 @@
       <c r="D7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>47</v>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chilon"  style="color:#6A142A"  title=" Wikipedia"&gt;CHILON de Sparte&lt;/a&gt; était un philosophe grec et l'un des &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2003_num_105_1_5661_t1_0315_0000_3" style="color:#88A1E9" title="Les Sept Sages de la Grèce antique par Persée"&gt;Sept Sages &lt;/a&gt; de la Grèce, un groupe de penseurs et législateurs renommés pour leur  &lt;a href="https://www.youtube.com/watch?v=gW0-ikAVNnE" style="color:#88A1E9" title="Les Sept Sages: Chilon par Karl Baudoin"&gt;sagesse pratique&lt;/a&gt;. Il incarne la sagesse pratique spartiate, centrée sur la modération et la maîtrise de soi. Ses préceptes sont souvent formulés sous forme de maximes : &lt;/p&gt; &lt;p&gt; 
+- "Connais-toi toi-même" : Bien que parfois attribué à Socrate, cette inscription du temple de Delphes aurait été popularisée par Chilon. Elle résume l'idéal de réflexion personnelle et d'humilité. &lt;/p&gt; &lt;p&gt; - "La modération est la meilleure des choses" : Un appel à éviter les excès, en accord avec l'éthique spartiate de discipline. &lt;/p&gt; &lt;p&gt; - "Ne ris pas de ton ennemi" : Mise en garde contre l'arrogance, soulignant que les circonstances peuvent changer. &lt;/p&gt; &lt;p&gt; En tant qu'éphore, Chilon aurait contribué à renforcer les institutions spartiates, comme la Grande Rhêtra (loi fondamentale attribuée à Lycurgue).  Il aurait conseillé la prudence dans les relations extérieures, évitant les guerres inutiles tout en consolidant la puissance de Sparte. &lt;/p&gt; &lt;p&gt;  Il représente l'idéal spartiate de sagesse appliquée, où la philosophie ne se dissocie pas de l'action politique et de la discipline personnelle. Son héritage, bien que fragmentaire, reste un pont entre la pensée archaïque grecque et la philosophie classique. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F7" s="7" t="s">
         <v>48</v>
@@ -3518,8 +3529,11 @@
       <c r="D8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>55</v>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anaxim%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;Anaximène&lt;/a&gt;  était un philosophe présocratique grec, généralement considéré comme le troisième grand représentant de l’école de Milet, après Thalès et Anaximandre. Comme les autres milésiens, il cherche l’archè, le principe premier dont tout dérive et où tout retourne.​ Là où Thalès choisit l’eau et Anaximandre l’apeiron indéfini, il désigne &lt;a href="https://www.youtube.com/watch?v=Hla3IPk2kM8" style="color:#88A1E9" title=" Et si l’air expliquait tout ? La théorie fascinante d’Anaximène par philo Scrolls en Fr"&gt; l’air&lt;/a&gt; comme substance fondamentale, à la fois illimitée, en mouvement et divine.​  Pour les Grecs, l’air est proche de l’âme (psychè, pneuma) : de même que le souffle anime le corps, l’air universel anime et structure le cosmos. &lt;/p&gt; &lt;p&gt; Sa &lt;a href="https://www.erudit.org/fr/revues/ltp/1962-v18-n1-ltp0960/1020018ar.pdf" style="color:#88A1E9" title="Anaximène par erudit"&gt;grande innovation&lt;/a&gt; est d’expliquer la diversité des choses par des variations de l’air en termes de densité : raréfaction et condensation.​ L’air raréfié devient feu, tandis que l’air condensé produit successivement vent, nuages, eau, puis terre et pierres.​ Cette réduction des différences qualitatives (feu, eau, terre, etc.) à des différences quantitatives (plus ou moins dense) est souvent vue comme un pas important vers une pensée physico-scientifique. &lt;/p&gt; &lt;p&gt; Il conçoit la Terre comme un disque plat flottant dans l’air, suspendu sans support matériel, entouré par un dôme céleste.​ Les astres sont des disques ou masses enflammées, portées par l’air, qui tournent autour de la Terre; il pense que le Soleil ne passe pas sous la Terre mais se dissimule derrière l’horizon pendant la nuit pour revenir à son point de départ.​ Il décrit également les phénomènes météorologiques (nuages, pluie, tonnerre, tremblements de terre) à partir de l’action de l’air et de ses mouvements, cherchant des causes naturelles plutôt que mythologiques.​ &lt;/p&gt; &lt;p&gt; Il  appartient aux « physiologues » présocratiques, qui remplacent le récit mythique par un discours rationnel sur la nature et l’origine du monde.​ &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F8" s="7" t="s">
         <v>56</v>
@@ -3562,8 +3576,12 @@
       <c r="D9" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>64</v>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Pythagore"  style="color:#6A142A"  title=" Wikipedia"&gt; PYTHAGORE&lt;/a&gt; était un philosophe, mathématicien et musicien grec célèbre pour ses contributions à la théorie des nombres, en particulier le fameux "théorème de Pythagore". Il a fondé une école de pensée dans le sud de l'Italie, où ses membres, appelés les  &lt;a href="https://www.normalesup.org/~adanchin/causeries/Pythagoriciens.html"  style="color:#88A1E9"  title="Pythagoriciens par Pierre Duhem"&gt; pythagoriciens&lt;/a&gt;, croyaient que les nombres étaient la clé de l'univers et que toute chose était régie par des lois mathématiques.  &lt;/p&gt; &lt;p&gt; Il croyait également en la &lt;a href="https://www.youtube.com/watch?v=_K28O2yEweI&amp;ab_channel=LaM%C3%A9moth%C3%A8que"  style="color:#88A1E9"  title="Transmigration des âmes par La Mémothèque"&gt; transmigration des âmes&lt;/a&gt;, l'idée que les âmes peuvent passer d'un corps à un autre, et que la purification de l'âme à travers l'éducation et la pratique de la vertu peut conduire à l'harmonie avec l'univers. &lt;/p&gt; &lt;p&gt; Pour lui, la musique était un moyen important d'atteindre cette harmonie, les sons et les vibrations pouvaient affecter l'âme de manière profonde. &lt;/p&gt; &lt;p&gt;  La philosophie pythagoricienne comprenait également des idées sur l'importance de l'équilibre et de l'harmonie dans tous les aspects de la vie, y compris la santé, la politique et la société. &lt;/p&gt; &lt;p&gt;
+Il lui a été crédité de nombreux autres développements mathématiques, notamment la découverte des propriétés des proportions musicales et la mise en évidence de la relation entre la longueur d'une corde et la hauteur de la note qu'elle produit. &lt;/p&gt; &lt;audio controls title="Pythagore est l'ancêtre des végétariens par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2016/05/s20/net-fi-e5fc1669-4513-4bb0-915b-d87efce86894.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+&lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F9" s="7" t="s">
         <v>65</v>
@@ -3726,8 +3744,14 @@
       <c r="D12" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>82</v>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclite"  style="color:#6A142A"  title=" Wikipedia"&gt;HÉRACLITE&lt;/a&gt; était un philosophe présocratique Grec de &lt;a href="https://archive.org/details/histoiredelaphil00mall/page/116/mode/2up" style="color:#88A1E9"   title="L'école Ionienne par internet archive"&gt; l'école Ionienne&lt;/a&gt; et dont le courant de pensée est le &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclit%C3%A9isme"  style="color:#88A1E9"  title="Le Mobilisme par Wikipedia"&gt;Mobilisme&lt;/a&gt;. Il connu pour ses écrits fragmentaires, dont le plus connue est celle de la "doctrine du flux perpétuel" ou &lt;a href="http://www.etienne-barilier.name/Conferences/2011/Panta_rhei%20.pdf"  style="color:#88A1E9"  title="Conférence 'panta rhei' par Etienne Barilier"&gt;"panta rhei"&lt;/a&gt;, qui signifie "tout coule". Selon cette idée, &lt;a href="https://www.youtube.com/watch?v=rbgWLqDwEjs&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Rien n'est figé par Le Précepteur"&gt;rien n'est figé&lt;/a&gt;, tout est en mouvement constant et tout change dans le monde, en disant que "rien ne se crée, rien ne se perd, tout se transforme". &lt;/p&gt; &lt;p&gt; 
+Il a également affirmé que le monde était gouverné par une loi universelle, appelée &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1986_num_99_470_1455"  style="color:#88A1E9"  title="Le Logos selon Héraclite par Persée"&gt;"Logos"&lt;/a&gt;, qui est souvent traduit comme "parole" ou "raison" et qui régissait tout dans l'univers, y compris les êtres humains. Le Logos était à la fois ordre et chaos, car il était à la fois créateur et destructeur.   &lt;/p&gt; &lt;p&gt;                                       
+Pour lui, le monde est gouverné par des lois naturelles, plutôt que par des dieux capricieux et irrationnels et il avait une vision pessimiste de la nature humaine, affirmant que les êtres humains sont souvent gouvernés par leurs passions et leurs désirs, plutôt que par &lt;a href="https://www.youtube.com/watch?v=-fzeW9YP8TI&amp;ab_channel=Lepayssanschemin"  style="color:#88A1E9"  title="L'éveil de la raison par Le pays sans chemin"&gt;la raison&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; 
+Bien que peu de ses écrits aient survécu jusqu'à nos jours, sa pensée a eu une influence durable sur la philosophie et elle a inspiré notamment Platon et Aristote, ainsi que des philosophes modernes tels que Friedrich Nietzsche et Martin Heidegger.  &lt;/p&gt; &lt;audio controls title="Thèmes et controverses- l'héritage d'Héraclite par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/10/s41/RF_CD1E6508-A3E8-4B48-BFCF-A6BC3A6CA34B_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+&lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F12" s="7" t="s">
         <v>83</v>
@@ -4321,8 +4345,13 @@
       <c r="D25" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>196</v>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antisth%C3%A8ne" style="color:#6A142A"   title="Antisthène par Wikipédia"&gt; ANTISTHÈNE &lt;/a&gt; était un philosophe disciple de Socrate et il a eu une influence significative sur le développement de la philosophie morale et éthique en cherchant à préserver et à développer les idées de son maître, en mettant l'accent sur la vertu personnelle et l'authenticité. &lt;/p&gt;
+&lt;p&gt; Il est considéré comme le fondateur de &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=133s&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Comprendre les Cyniques par Alain Bajomée"&gt; l'école de pensée cynique.&lt;/a&gt; Après la mort de Socrate, il a développé ses propres idées en reprenant certains des thèmes centraux de l'enseignement de Socrate et a donné à l'école le nom de "cynique", qui dérive du mot grec "kynikos", signifiant "chien". Ce nom faisait référence à l'accent mis sur la vie simple et naturelle détachée des désirs matériels et des plaisirs superficiels, ainsi qu'à la critique des conventions sociales. Il croyait que le bonheur réside dans la maîtrise de soi et dans le rejet des biens matériels. Il vivait lui-même une vie ascétique et rejetait les besoins et les désirs superflus. &lt;/p&gt;
+&lt;p&gt; Il pensait que la sagesse et la vertu étaient atteintes par la pratique de la philosophie et l'engagement dans une vie vertueuse et critiquait ouvertement les normes sociales et les valeurs conventionnelles de la société grecque de l'époque. Il remettait en question la poursuite des richesses matérielles, du prestige social et du pouvoir, préférant se concentrer sur la recherche de la véritable vertu et du bonheur. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;
+</t>
+        </is>
       </c>
       <c r="F25" s="7" t="s">
         <v>197</v>
@@ -4498,8 +4527,10 @@
       <c r="D29" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>231</v>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Platon"  style="color:#6A142A"  title=" Wikipedia"&gt;PLATON&lt;/a&gt; fut  un des plus grands penseurs de l'Antiquité.  Il était l'élève de Socrate, dont la méthode dialectique et la quête de la vérité le marquent profondément. La condamnation à mort de Socrate en 399 av. J.-C. influence sa méfiance envers la démocratie athénienne. &lt;/p&gt; &lt;p&gt; Il fonda  &lt;a href="https://www.youtube.com/watch?v=q0M8zV-XHbQ"  style="color:#88A1E9" title="L'académie de Platon Platon par Luc Ferry"&gt;l'Académie&lt;/a&gt; à Athènes, qui est considérée comme la première institution d'enseignement supérieur de l'histoire où  il y enseigne la philosophie, les mathématiques et les sciences. L'Académie fonctionnera pendant près de 900 ans.&lt;/p&gt; Il développe une philosophie complexe et systématique, centrée sur des concepts clés comme les Idées, &lt;a href="https://www.persee.fr/doc/phlou_0776-5541_1905_num_12_46_1881"  style="color:#88A1E9" title="Dieu, d'après Platon par Persée"&gt;l'âme&lt;/a&gt;, la justice et la connaissance. Ses idées sont principalement exposées sous forme de dialogues, où Socrate est souvent le personnage principal. Il distingue &lt;a href="https://www.youtube.com/watch?v=o5TbXYe64A8&amp;t=18s&amp;ab_channel=AlainBajom%C3%A9e"  style="color:#88A1E9" title="La théorie des idées par Alain Bajomée"&gt;deux mondes&lt;/a&gt; : le monde sensible (celui que nous percevons par les sens) et le monde intelligible (celui des Idées, éternel et immuable). Pour lui, les Idées sont des réalités parfaites et immuables qui existent indépendamment du monde matériel. Par exemple, il existe une Idée de la Beauté, de la Justice ou du Bien, dont les objets sensibles ne sont que des copies imparfaites. &lt;/p&gt; &lt;p&gt;Il a écrit une trentaine de dialogues, dont les plus célèbres sont :  - La République (justice, politique, éducation). - Phédon (immortalité de l'âme). -  &lt;a href="https://www.youtube.com/watch?v=Mbtxr1hsP7A"  title="  Ce que Le Banquet de Platon révèle sur l'amour  par Resumon ça"&gt;Le Banquet &lt;/a&gt;(amour et beauté). - Phèdre (rhétorique et amour). - Ménon (vertu et réminiscence). - Timée (cosmologie et physique). - Critias (mythe de l'Atlantide). - Apologie de Socrate (défense de Socrate lors de son procès). - Phédon (immortalité de l'âme). &lt;/p&gt; &lt;p&gt;  Dans son ouvrage  le plus célèbre  &lt;a href="https://www.youtube.com/watch?v=qSrvZvjPG_w&amp;t=811s&amp;ab_channel=Kosmos"  style="color:#88A1E9" title="La République, c'est quoi par Kosmos"&gt;La République&lt;/a&gt;, il décrit sa vision d'une société idéale où les dirigeants sont des philosophes-rois et où la justice et la vertu sont les principes fondamentaux. Il y présente une métaphore de la condition humaine, l'allégorie de la &lt;a href="https://www.youtube.com/watch?v=N519gbEXbbw&amp;t=13s&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9" title="L'allégorie de la Caverne par le Précepteur "&gt;La Caverne&lt;/a&gt;, lieu où des gens vivent et où ils ne voient que des ombres projetées sur les murs en croyant que c'est la réalité.&lt;/p&gt;    &lt;p&gt; Il reste une figure centrale de la philosophie, dont les idées continuent d'inspirer et de provoquer la réflexion. Sa quête de la vérité, sa vision idéaliste et sa méthode dialectique en font un penseur intemporel. &lt;/p&gt;   &lt;audio controls title="Platon et la politique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.11.2025-ITEMA_24317262-2025C48904S0324-NET_MFC_E07CEF22-5D42-4358-8035-01B7B6D438EF-21-f49f7fca67cbafd4d44c5b4c00fead78.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F29" s="7" t="s">
         <v>232</v>
@@ -4545,8 +4576,13 @@
       <c r="D30" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>241</v>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Sinope"   title="Diogène de Sinope par Wikipédia"&gt; DIOGÈNE DE SINOPE &lt;/a&gt; était un philosophe grec antique connu pour son mode de vie ascétique et ses provocations intellectuelles. Il est souvent surnommé "Diogène le Cynique" en raison de son affiliation à l'école de pensée cynique, qui prônait le rejet des conventions sociales, le détachement des désirs matériels et une vie en accord avec la nature. Il vivait une vie extrêmement simple et minimaliste et rejetait les besoins conventionnels et matérialistes, préférant se contenter de peu. Il est célèbre pour avoir vécu dans un tonneau (ou grand récipient) à Athènes. &lt;/p&gt;
+&lt;p&gt;Diogène était connu pour &lt;a href="https://www.philo5.com/Les%20philosophes%20Textes/Diogene_OntDitSur.htm#_ftn4"  title="Diogène de Sinope d'après Diogène Laërce par philo5"&gt; défier les normes&lt;/a&gt; sociales et philosophiques de son époque en utilisant souvent des actions et des paroles provocantes pour critiquer la société, remettre en question les valeurs établies et provoquer des réflexions profondes. Par exemple, il se promenait en plein jour avec une lanterne allumée à la recherche d'un "homme honnête", soulignant ainsi l'absence de personnes vertueuses.  &lt;a href="https://www.youtube.com/watch?v=aNUDOhr9yLs"  title=" La philosophie Diogène de Sinope par parole de philosophes "&gt; Il croyait &lt;/a&gt; que la société et ses institutions étaient corrompues et prônait la simplicité et la nature, rejetant les normes artificielles et les désirs superficiels qui causaient souvent des souffrances et des conflits.&lt;/p&gt;
+&lt;p&gt;  Diogène aurait eu une rencontre célèbre avec Alexandre le Grand, qui, impressionné par la renommée de Diogène, l'aurait trouvé dans son tonneau et aurait demandé s'il pouvait faire quelque chose pour lui. Diogène aurait répondu simplement : "Ôte-toi de mon soleil." Cette anecdote illustre l'attitude nonchalante et provocatrice de Diogène. &lt;/p&gt;
+&lt;p&gt;Ses enseignements exacts  ne sont pas bien documentés, car peu de ses écrits ont survécu. Cependant, &lt;a href="https://www.youtube.com/watch?v=epW-8gZwQEk&amp;ab_channel=R%C3%A9sonance%5Bs%5D"  title="Diogène de Sinope, le chien royal par Résonance"&gt;son mode de vie&lt;/a&gt; et ses actions ont eu un impact durable sur la philosophie occidentale en remettant en question les valeurs conventionnelles et en mettant l'accent sur la simplicité et l'authenticité. &lt;/p&gt;   &lt;audio controls title="Osons le cynisme ! retour à Diogène par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/02/s09/LES_NOUVEAUX_CHEMINS_DE_LA_CONNAISSANCE.NET_FC_4EBE3123-A5B5-49FF-96B5-DB4346498425.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F30" s="7" t="s">
         <v>242</v>
@@ -5763,8 +5799,13 @@
       <c r="D57" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="E57" s="9" t="s">
-        <v>466</v>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sextus_Empiricus"  title=" Wikipedia"&gt;Sextus EMPIRICUS&lt;/a&gt;  était un philosophe et médecin grec et  une figure importante du scepticisme, souvent appelé "pyrrhonisme" en référence à Pyrrhon d'Élis. Contrairement à d'autres formes de scepticisme, qui peuvent aboutir à une négation de la possibilité de connaître la vérité, le &lt;a href="https://www.youtube.com/watch?v=Xvgfo_ADlPM"  title=" Sextus Empiricus, Esquisses pyrrhoniennes, Ne rien affirmer et l'enseignement inexistant par Koalemos"&gt;pyrrhonisme&lt;/a&gt; propose de suspendre tout jugement sur la nature ultime des choses, car il considère que les arguments pour et contre toute proposition sont également convaincants. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2002_num_100_4_7456_t1_0797_0000_2" title="Sextus Empiricus, Esquisses pyrrhoniennes. Introduction, traduction et commentaires par Pierre Pellegrin par Persée"&gt;"Les Esquisses pyrrhoniennes"&lt;/a&gt;, il présente une introduction systématique au scepticisme pyrrhonien. L'ouvrage est divisé en trois livres : &lt;/p&gt; 
+&lt;p&gt; - Livre I : Il expose les principes fondamentaux du scepticisme, y compris la distinction entre le scepticisme pyrrhonien et d'autres formes de scepticisme, comme celui de l'Académie. Il explique également les concepts clés tels que l'épochè (suspension du jugement), les tropes (modes d'argumentation sceptique), et l'ataraxie. &lt;/p&gt; 
+&lt;p&gt; - Livre II : Il traite de la critique sceptique des dogmatismes philosophiques, en particulier dans les domaines de la logique, de la physique et de l'éthique. Il montre comment les arguments des dogmatiques peuvent être contredits, ce qui justifie la suspension du jugement. &lt;/p&gt; 
+&lt;p&gt; - Livre III : Il approfondit la critique des dogmatismes, en se concentrant sur des questions spécifiques comme la causalité, la divinité, et la nature du bien et du mal. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/spira_0994-3722_2007_num_39_1_1264_t14_0182_0000_2" style="color:#88A1E9" title=" Sur le Contre les professeurs de Sextus Empiricus par Persée"&gt;"Contre les professeurs"&lt;/a&gt;, il s'attaque à diverses disciplines intellectuelles de son époque, notamment la grammaire, la rhétorique, la géométrie, l'arithmétique, l'astronomie et la musique. Il soutient qu'elles ne peuvent pas prétendre à une connaissance certaine ou absolue. Son but est de montrer que les prétentions à la vérité dans ces domaines sont infondées. &lt;/p&gt; &lt;p&gt; Il  est également connu pour avoir systématisé &lt;a href="https://hal.science/hal-03091658v1/document" style="color:#88A1E9" title=" Sextus Empiricus et les tropes par Hall science"&gt;les "tropes"&lt;/a&gt;, des arguments ou modes de raisonnement qui justifient la suspension du jugement. Ce sont des outils dialectiques qui montrent comment les perceptions et les jugements varient selon les circonstances, les individus, les cultures, etc. &lt;/p&gt; &lt;p&gt;Ses écrits ont été redécouverts à la Renaissance et ont joué un rôle clé dans le développement de la pensée sceptique moderne, influençant des philosophes comme Montaigne, Descartes et Hume. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F57" s="7" t="s">
         <v>467</v>
@@ -6074,8 +6115,20 @@
       <c r="D64" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="E64" s="9" t="s">
-        <v>525</v>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89n%C3%A9sid%C3%A8me"  style="color:#6A142A"  title=" Wikipedia"&gt;ÉNÉSIDÈME&lt;/a&gt; était un philosophe grec de la tradition sceptique.  Il vécu à une époque où le &lt;a href="https://www.youtube.com/watch?v=_En3Pz6sWL8" style="color:#88A1E9" title="Scepticisme et interpedendance par PHILOSOPHIA"&gt;scepticisme&lt;/a&gt; philosophique était en plein essor, en réaction aux dogmatismes des écoles philosophiques comme le stoïcisme et l'épicurisme.  &lt;/p&gt; &lt;p&gt; Il a systématisé les  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1918_num_20_2_2006" style="color:#88A1E9" title="Pour l'histoire du scepticisme antique : les tropes d'Énésidème contre la logique inductive par Persée"&gt;arguments sceptiques&lt;/a&gt; dans ce qu'on appelle les &lt;a href="https://guykarl.canalblog.com/archives/2012/08/31/25001663.html" style="color:#88A1E9" title="PYRRHONISME : les dix tropes d' ENESIDEME par Le jardin Philosophe"&gt;"Dix Modes"&lt;/a&gt;, qui visent à montrer que nos perceptions et nos jugements sont influencés par divers facteurs, rendant impossible l'accès à une connaissance certaine : &lt;/p&gt;
+&lt;p&gt; - La diversité des animaux : Les espèces perçoivent le monde de manière différente, ce qui suggère que nos perceptions ne reflètent pas nécessairement la réalité objective. &lt;/p&gt;
+&lt;p&gt; - La diversité des humains : Parmi les humains, les perceptions et les jugements varient considérablement, ce qui rend difficile de déterminer quelle perception est "correcte". &lt;/p&gt; 
+&lt;p&gt; - La diversité des sens : Les différents sens peuvent donner des informations contradictoires sur un même objet. &lt;/p&gt;
+&lt;p&gt; - Les circonstances : Les conditions dans lesquelles nous percevons quelque chose peuvent influencer notre perception. &lt;/p&gt;
+&lt;p&gt; - Les positions et distances : La position et la distance par rapport à un objet peuvent altérer notre perception de celui-ci. &lt;/p&gt; 
+&lt;p&gt; - Les mélanges : Les objets ne sont jamais perçus isolément, mais toujours dans un contexte qui peut influencer notre perception. &lt;/p&gt;
+&lt;p&gt; - Les quantités et constitutions : La quantité et la composition d'un objet peuvent affecter la manière dont nous le percevons. &lt;/p&gt; 
+&lt;p&gt; - La relation : Tout est perçu en relation avec autre chose, ce qui rend difficile de connaître la nature intrinsèque d'un objet.&lt;/p&gt; 
+&lt;p&gt; -  La fréquence ou la rareté : La fréquence avec laquelle nous rencontrons quelque chose peut influencer notre perception de sa valeur ou de sa nature. &lt;/p&gt; 
+&lt;p&gt; - Les coutumes et les croyances : Les habitudes culturelles et les croyances peuvent profondément influencer nos perceptions et nos jugements. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Ses arguments mettent en lumière les limites de notre capacité à connaître le monde de manière certaine et nous invitent à adopter une attitude plus humble et critique face à nos propres perceptions et jugements. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F64" s="7" t="s">
         <v>526</v>
@@ -6165,8 +6218,11 @@
       <c r="D66" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="E66" s="13" t="s">
-        <v>544</v>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que" title=" Wikipedia"&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href="https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Stoïcisme par le Précepteur"&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=J3wZoqElCgs" title="Who is Seneca par Daily Stoic "&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href="https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin" title="La vie Heureuse par Karl Baudoin"&gt; "une vie heureuse".&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : - De la brièveté de la vie (consideration sur l’usage du temps). - De la colère (sur la maîtrise de cette passion destructive). - De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt; Sénèque est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href="https://www.youtube.com/watch?v=d_cge9OwVAs" title="La vie philosophique de Sénèque par Kosmos"&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title="Les lettres à Lucilius – Senèque  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F66" s="7" t="s">
         <v>545</v>
@@ -6258,8 +6314,11 @@
       <c r="D68" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="E68" s="9" t="s">
-        <v>560</v>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apollonios_de_Tyane"  style="color:#6A142A"  title=" Wikipedia"&gt; Apollonios de Tyane&lt;/a&gt;, né à Tyane en Cappadoce (Turquie),   est une figure emblématique de l’Antiquité, à la croisée de la philosophie, de la spiritualité et du mysticisme, souvent décrit comme un philosophe, thaumaturge et ascète.  Il est principalement associé au &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_pythagoricienne" title="Phytagorisme par wikipedia "&gt; pythagorisme&lt;/a&gt;, un courant philosophique inspiré des enseignements de Pythagore, pratique et ascétique, visant à transformer la vie par des principes éthiques rigoureux et une quête de sagesse. Il prônait une vie fondée sur la pureté, la discipline et l’harmonie universelle,  adoptant un mode de vie ascétique caractérisé par le végétarisme, l’abstinence de vin et un dévouement à la recherche de la sagesse. &lt;/p&gt;  &lt;p&gt;   Comme de nombreux philosophes de son temps, il a entrepris de longs voyages pour acquérir des connaissances. Il se rendit notamment en Égypte, en Inde, en Mésopotamie et en Grèce. En Inde, il aurait rencontré des sages et des brahmanes qui auraient influencé sa pensée, assimilant et intégrant à sa pensée des éléments de traditions diverses.  &lt;/p&gt; &lt;p&gt; Au cours des siècles, il a souvent été comparé à Jésus-Christ, en raison des similitudes perçues entre leurs vies (miracles, ascétisme, message spirituel). Certains penseurs païens de l'Antiquité ont même présenté &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1999_num_1_3_1959" style="color:#88A1E9" title="Mythe avorté d'une sagesse totale par Persée "&gt; Apollonios&lt;/a&gt; comme une alternative païenne à Jésus, bien que les deux figures soient très différentes dans leur contexte et leur message. &lt;/p&gt; &lt;p&gt;Il incarte une forme de tolérance religieuse cosidérant que l'on peut reconnaitre sa religion dans la religion de l'autre.&lt;/p&gt; &lt;p&gt;  Sa vie, relatée par &lt;a href="https://fr.wikipedia.org/wiki/Philostrate_d%27Ath%C3%A8nes" style="color:#88A1E9" title="Philostrate par Wikipedia "&gt; Philostrate&lt;/a&gt; dans  &lt;a href="https://fr.wikipedia.org/wiki/Vie_d%27Apollonios_de_Tyane" style="color:#88A1E9" title="Vie d'Apollonios de Tyare par Wikipedia "&gt; Vie d’Apollonios de Tyane&lt;/a&gt;, mêle éléments historiques et légendaires. Profondément spirituel, il prônait une piété réfléchie et critiquait les pratiques religieuses vides de sens, notamment les sacrifices sanglants, préférant une relation intérieure avec le divin et des rituels plus éthiques. Convaincu de l’immortalité de l’âme et de la réincarnation, il voyait la philosophie comme une voie vers la purification spirituelle et morale. &lt;/p&gt; &lt;p&gt;Son engagement ne se limitait pas à la sphère personnelle : il joua un rôle actif dans la société en critiquant les tyrans, en défendant la justice et en conseillant les gouvernants. Considéré par ses contemporains comme un thaumaturge, il aurait accompli des miracles tels que des guérisons, des prédictions et des résurrections, bien que ces récits soient teintés de légende. Sa pensée et sa vie incarnaient une quête universelle de vérité et d'harmonie, cherchant à unifier les enseignements philosophiques et spirituels dans une vision globale.&lt;/p&gt; &lt;p&gt; Apollonios demeure une figure complexe, à mi-chemin entre le philosophe et le sage mystique, dont l'héritage, bien que controversé, continue d'inspirer les amateurs de sagesse antique. &lt;/p&gt;   
+</t>
+        </is>
       </c>
       <c r="F68" s="7" t="s">
         <v>561</v>
@@ -6393,8 +6452,10 @@
       <c r="D71" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="E71" s="9" t="s">
-        <v>584</v>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicomaque_de_G%C3%A9rase"  style="color:#6A142A"  title=" Wikipedia"&gt;NICOMAQUE de Gérase&lt;/a&gt; était un mathématicien et philosophe néo-pythagoricien grec mettant l'accent sur l'importance des nombres et de leurs propriétés dans la compréhension de l'univers. Pour lui, ils n'étaient pas de simples outils de calcul, mais des  &lt;a href="https://www.youtube.com/watch?v=Jbuap2Pahbg" style="color:#88A1E9" title=" Pourquoi rééditer l'Introduction arithmétique de Nicomaque de Gerasa en France ?  par LabEx HaStec"&gt;principes fondamentaux &lt;/a&gt; qui sous-tendent la réalité. Il cherchait à réduire les Formes platoniciennes et les catégories aristotéliciennes aux propriétés formelles des nombres. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus célèbre et le plus influent "Introduction à l'arithmétique" est un manuel fondamental qui a servi de base à l'arithmétique pendant une grande partie du Moyen Âge, notamment grâce à sa traduction et adaptation par Boèce (vers 505) dans son "De institutione arithmetica". Ce traité aborde des concepts comme les nombres figurés, les nombres parfaits, abondants et déficients, et la théorie des nombres en général. &lt;/p&gt; &lt;p&gt;  Dans son deuxième ovrage " Théologie de l'arithmétique", il  explore les significations mystiques et philosophiques des nombres, rattachant les propriétés numériques à des concepts divins et cosmologiques.   Il était également théoricien de la musique et musicologue où dans  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1956_num_69_324_3426" style="color:#88A1E9" title=" L'hexatonique grec d'après Nicomaque  par Persée"&gt; 'L'hexatonique"&lt;/a&gt;, il témoigne de son intérêt pour les relations mathématiques sous-jacentes à l'harmonie musicale. &lt;/p&gt; &lt;p&gt; Il  est une figure essentielle pour comprendre la philosophie et les mathématiques de l'Antiquité tardive, en particulier le courant néo-pythagoricien qui cherchait à concilier les doctrines platoniciennes et aristotéliciennes avec la mystique des nombres. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F71" s="7" t="s">
         <v>585</v>
@@ -6437,8 +6498,10 @@
       <c r="D72" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="E72" s="10" t="s">
-        <v>592</v>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le"  style="color:#6A142A"  title=" Wikipedia"&gt;Marc AURÈLE&lt;/a&gt; était un empereur romain considéré comme l'un des plus justes et des plus sages.&lt;/p&gt; &lt;p&gt; Il était connu pour son livre &lt;a href="https://fr.wikipedia.org/wiki/Pens%C3%A9es_pour_moi-m%C3%AAme"  title="Les pensées pour moi même de Marc AURELE "&gt;"Méditations" &lt;/a&gt; ou « &lt;em&gt;Les pensées pour moi même&lt;/em&gt;, qui reflète ses pensées sur la philosophie stoïcienne et qui est considéré comme un classique de la littérature spirituelle ont été rédigées en grec, probablement comme  &lt;a href="https://www.youtube.com/watch?v=KKSRqzRdBx0"  title="Les pensées pour moi même Marc AURELE par Kosmos"&gt;un journal intime &lt;/a&gt; ou un exercice personnel, et non comme un livre destiné à la publication. Il  appartient au stoïcisme, une philosophie qui insiste sur la maîtrise de soi, le devoir et l’acceptation de ce qu’on ne contrôle pas. &lt;p&gt; Dans ses écrits, il a souligné l'importance de la sagesse, de la vertu et de la modération, et a exhorté les gens à rester calmes et à rester imperméables aux émotions négatives telles que la peur, la colère et la tristesse.&lt;/p&gt; &lt;p&gt; Il a également abordé des sujets tels que la mort, la justice, la responsabilité et le devoir. &lt;a href="https://www.youtube.com/watch?v=1OeNwG_bxWg&amp;ab_channel=FranceCulture"   title="Les pensées de Marc AURELE au quotidien par France Culture"&gt;"De nos jours"&lt;/a&gt;, ses idées sont encore étudiées et appréciées pour leur pertinence et leur sagesse, et sont considérées comme un élément fondamental de la philosophie stoïcienne moderne. &lt;/p&gt; &lt;p&gt;   Il est important à la fois pour l’histoire romaine et pour la philosophie, car il incarne un rare mélange de pouvoir politique et de réflexion morale. Son influence perdure surtout grâce à ses écrits, souvent lus aujourd’hui comme un guide de vie stoïcienne,&lt;/p&gt;  &lt;audio controls title="Pensée pour moi même par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.01.2016-ITEMA_20899513-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F72" s="7" t="s">
         <v>593</v>
@@ -6484,8 +6547,10 @@
       <c r="D73" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="E73" s="10" t="s">
-        <v>600</v>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas"  title="Wikipedia"&gt;Ammonios SACCAS&lt;/a&gt; était un philosophe grec dont on connaît mal sa vie car il n’a laissé aucun écrit direct. Son surnom “Saccas” est souvent expliqué comme un surnom lié à une origine modeste ou à un métier manuel, même si l’étymologie exacte reste discutée, &lt;/p&gt;&lt;p&gt; On le considère souvent comme le fondateur de l’école néoplatonicienne de Rome, surtout parce qu’il a formé Plotin, qui a ensuite systématisé cette philosophie. Les sources anciennes lui attribuent aussi l’idée que Platon et Aristote convergent sur l’essentiel, ce qui en fait une figure de réconciliation philosophique. &lt;/p&gt; &lt;p&gt; Comme il n’a rien écrit, sa doctrine est reconstruite à partir de témoignages, surtout ceux de Plotin et d’auteurs tardifs. On lui associe une philosophie centrée sur l’unité du réel, la purification de l’âme, et une vie tournée vers la contemplation intellectuelle.&lt;/p&gt; &lt;p&gt;  Il  est souvent qualifié de  &lt;a href="https://www.youtube.com/watch?v=hSIeYrZa-X4"title=" Ammonios SACCAS maitre de Plotin  par Vox Temporis"&gt;“maître silencieux”&lt;/a&gt;parce que sa pensée est très influente, mais presque entièrement indirecte. Il se situe à la charnière entre le platonisme tardif et le néoplatonisme de Plotin.&lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F73" s="7" t="s">
         <v>601</v>
@@ -6709,8 +6774,13 @@
       <c r="D78" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="E78" s="9" t="s">
-        <v>641</v>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marius_Victorinus"  style="color:#6A142A"  title=" Wikipedia"&gt;Marius VICTORINUS&lt;/a&gt; était un philosophe, africain de naissance puis romain enseignant la rhétorique et la philosophie.  Il s'est converti au Christianisme après avoir étudié les Écritures. Sa conversion a été perçue comme un symbole de la capacité du christianisme à attirer même les intellectuels les plus érudits. Il  a laissé une œuvre variée, à la fois philosophique et  &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1957_num_70_66_20268" style="color:#88A1E9" title=" Oeuvres théologiques de Marius Victorinus par Persée"&gt;théologique. &lt;/a&gt;&lt;p&gt; - Avant sa conversion :  Il a écrit des commentaires sur des textes philosophiques grecs, notamment ceux d'Aristote et de Platon. Ces travaux montrent sa maîtrise de la philosophie néoplatonicienne, qui a profondément influencé sa pensée.  Il a traduit et adapté des œuvres néoplatoniciennes, comme celles de Plotin et de Porphyre, contribuant à diffuser ces idées dans le monde latin. &lt;/p&gt; &lt;p&gt; -  Après sa conversion :  Il s'est concentré sur des questions théologiques, en particulier sur la Trinité et la nature du Christ et de &lt;a href="https://www.youtube.com/watch?v=DCbfSqUZFs0" style="color:#88A1E9" title=" La notion de pré-étant selon Marius Victorinus  par Hervé Pasqua"&gt;l'être&lt;/a&gt;. Ses œuvres les plus importantes incluent : &lt;/p&gt; 
+&lt;dd&gt; - Adversus Arium : Une défense de l'orthodoxie nicéenne contre  &lt;a href="https://fr.wikipedia.org/wiki/Arianisme" style="color:#88A1E9" title=" Arianisme par Wikipédia"&gt;l'arianisme&lt;/a&gt;, qui niait la divinité du Christ. &lt;/dd&gt; 
+&lt;dd&gt; - De generatione divini Verbi  : Un traité sur la relation entre le Père et le Fils dans la Trinité. &lt;/dd&gt; 
+&lt;dd&gt; - De Trinitate : Une exploration approfondie de la doctrine trinitaire, influencée par la philosophie néoplatonicienne. &lt;/dd&gt;  &lt;p&gt; Son utilisation des concepts néoplatoniciens pour expliquer des doctrines chrétiennes complexes, comme la Trinité, a influencé des théologiens ultérieurs, notamment saint Augustin. Il  a également contribué à la formation d'un langage théologique latin, en adaptant des concepts philosophiques grecs à la pensée chrétienne. &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F78" s="7" t="s">
         <v>642</v>
@@ -6753,8 +6823,10 @@
       <c r="D79" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="E79" s="9" t="s">
-        <v>649</v>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9mistios"  style="color:#6A142A"  title=" Wikipedia"&gt;THÉMISTIOS&lt;/a&gt; était un philosophe, homme politique  romain connu pour ses talents d'orateur et ses contributions à la philosophie néoplatonicienne, ainsi que pour &lt;a href="https://www.youtube.com/watch?v=JdIUtCSF-JA" style="color:#88A1E9" title="«L’œuvre de Thémistios et son importance pour l’histoire de la philosophie» par Histoire de la mémoire et des idées"&gt;son rôle &lt;/a&gt; dans la vie politique et culturelle de son époque. Il  a vécu pendant une période de transition importante dans l'Empire romain, marquée par la montée du christianisme et le déclin progressif du paganisme. &lt;/p&gt; &lt;p&gt; Ses &lt;a href="https://www.persee.fr/doc/topoi_1764-0733_2006_mel_7_1_2980" style="color:#88A1E9" title="Thémistios et ses adversaires : le témoignage du discours  par Persée"&gt;écrits &lt;/a&gt; reflètent une profonde connaissance de la philosophie grecque, en particulier ses "&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_12_5759" style="color:#88A1E9" title=" d'Aristote par Themistius par Persée"&gt;paraphrases des traités d'Aristote &lt;/a&gt;", qui visaient à rendre la pensée du philosophe plus accessible à ses contemporains. Il croyait en l'harmonie entre la raison et la révélation, et soutenait que la philosophie pouvait coexister avec la religion. Cette position lui a permis de maintenir un dialogue avec les chrétiens tout en restant fidèle à ses racines païennes.&lt;/p&gt; &lt;p&gt;  Son travail et son influence reflète les tensions et les transformations de son époque, tout en témoignant d'une quête constante de sagesse et de conciliation entre les différentes traditions philosophiques et religieuses. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F79" s="7" t="s">
         <v>650</v>
@@ -6844,8 +6916,14 @@
       <c r="D81" s="8" t="s">
         <v>666</v>
       </c>
-      <c r="E81" s="9" t="s">
-        <v>667</v>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9lage_(h%C3%A9r%C3%A9siarque)"  style="color:#6A142A"  title=" Wikipedia"&gt;PÉLAGE&lt;/a&gt;  également connu sous le nom Pelagius en latin, était un moine et théologien britannique surtout connu pour avoir été au cœur d'une controverse théologique majeure dans l'histoire de l'Église chrétienne, connue sous le nom de &lt;a href="https://www.la-croix.com/Religion/Religion-et-spiritualite/Comprendre-pelagianisme-2018-11-17-1200983747" title="comprendre le Pélage par la Croix"&gt; pélagianisme&lt;/a&gt;. 
+Originaire des îles britanniques, actif principalement à Rome et en Afrique du Nord au début du Ve siècle, il était profondément engagé dans la vie monastique et était reconnu pour son ascétisme rigoureux. &lt;/p&gt;
+&lt;p&gt;La principale controverse associée à Pelage concernait la question de la nature du péché, de la grâce et du libre arbitre. Pelage soutenait que les êtres humains avaient la capacité intrinsèque de choisir le bien et d'éviter le péché sans l'aide de la grâce divine. Il rejetait l'idée du péché originel, enseignant que chaque personne naissait dans un état d'innocence et avait la possibilité de vivre une vie sans péché.&lt;/p&gt;
+&lt;p&gt;Ces enseignements ont été fermement contestés par des figures théologiques importantes de l'époque, notamment Augustin d'Hippone. Augustin affirmait que la nature humaine était corrompue par le péché originel et que la grâce divine était nécessaire pour la rédemption et la sanctification des individus. Il considérait les enseignements de Pelage comme hérétiques et dangereux pour la foi chrétienne. &lt;/p&gt;
+&lt;p&gt;Le &lt;a href="https://www.youtube.com/watch?v=AnKeIzmox0s" title="la victoire de st Augustin sur Pélage par Michel Onfray"&gt; débat&lt;/a&gt; entre Pelage et Augustin a finalement conduit à plusieurs conciles et décrets ecclésiastiques condamnant  le pélagianisme comme une hérésie. Malgré cela, les idées de Pelage ont continué à influencer certains courants de pensée chrétienne ou religuieux comme Fauste de Riez, et la controverse pélagienne a laissé une marque durable sur l'histoire théologique de l'Église.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F81" s="7" t="s">
         <v>668</v>
@@ -6935,8 +7013,10 @@
       <c r="D83" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="E83" s="9" t="s">
-        <v>686</v>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hypatie"  style="color:#6A142A"  title=" Wikipedia"&gt;HYPATIE d'Alexandrie&lt;/a&gt; était est une figure emblématique de l'Antiquité tardive, connue pour ses contributions à la philosophie, aux mathématiques et à l'astronomie. Elle est souvent considérée comme l'une des  &lt;a href="https://laviedesidees.fr/Hypatie-d-Alexandrie-femme-antique-figures-contemporaines" style="color:#88A1E9" title="Hypatie d’Alexandrie : femme antique, figures contemporaines par College de France"&gt;premières femmes&lt;/a&gt; scientifiques de l'histoire. Elle était la fille de Théon d'Alexandrie, un mathématicien et astronome renommé qui a joué un rôle crucial dans l'éducation de sa fille et elle a rapidement surpassé son père en renommée et en compétence, devenant une enseignante respectée et une érudite de premier plan. &lt;/p&gt; &lt;p&gt; Elle  a  &lt;a href="https://www.youtube.com/watch?v=gXk4fZ41Dyc" style="color:#88A1E9" title="La vie mystérieuse d'Hypatie : grande philosophe et mathématicienne ! par Kidaia"&gt;édité&lt;/a&gt; des œuvres mathématiques importantes, notamment les "Éléments" d'Euclide et les "Coniques" d'Apollonius de Perga et a travaillé sur des traités d'astronomie, collaborant avec son père pour réviser et commenter l'"Almageste" de Ptolémée. Elle a peut-être aussi contribué à la conception de &lt;a href="https://www.youtube.com/watch?v=c6Ab5oMIMoc"title="L'Astrolabe par Institut du monde arabe"&gt;" l'Astrolabe "&lt;/a&gt;, un instrument utilisé pour mesurer la position des astres. &lt;/p&gt; &lt;p&gt; Hypatie était une adepte du néoplatonisme, une école de pensée philosophique qui cherchait à synthétiser les idées de Platon avec d'autres traditions philosophiques et religieuses. Elle a dirigé une école néoplatonicienne à Alexandrie, attirant des étudiants de tout l'Empire romain. &lt;/p&gt; &lt;p&gt; En tant que païenne et symbole de la science et de la philosophie antiques, elle est devenue une cible pour les chrétiens radicaux et a été brutalement assassinée par une foule dirigée par des partisans de l'évêque Cyrille d'Alexandrie. Sa mort est souvent considérée comme un tournant symbolique dans le déclin de la culture païenne et de la liberté intellectuelle dans l'Empire romain. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title=" Hypatie d'Alexandrie, enseigner les maths envers et contre tout par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25546-14.01.2025-ITEMA_23980317-2025F54134E0003-NET_MFI_25ED747B-707B-4A53-94F6-7EEB0584D30D-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F83" s="7" t="s">
         <v>687</v>
@@ -7347,8 +7427,10 @@
       <c r="D92" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="E92" s="10" t="s">
-        <v>756</v>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Damascios" style="color:#6A142A" title="Wikipedia"&gt;DAMASCIOS   le Diadoque&lt;/a&gt;, né à Damas fut le dernier scholarque de l'Académie platonicienne d'Athènes,   Élève de Marinos de Néapolis et d'Isidore d'Alexandrie, il succéda à ce dernier comme scholarchos vers 515, jusqu'à la fermeture de l'école par l'empereur Justinien en 529. Philosophe néoplatonicien d'une érudition exceptionnelle, il incarne la résistance de la pensée grecque face au triomphe du christianisme.&lt;/p&gt; &lt;p&gt;Disciple d'Isidore de Gaza et d'autres maîtres alexandrins, il dirigea l'École d'Athènes et rédigea des œuvres d'une grande complexité spéculative, notamment les &lt;em&gt;Problèmes et Solutions concernant les Premiers Principes&lt;/em&gt; et un commentaire sur le &lt;em&gt;Parménide&lt;/em&gt; de Platon.   Auteur de la Vie d'Isidore (biographie philosophique et critique du christianisme), du Traité des premiers principes (sur l'ontologie), de commentaires sur le Parménide de Platon et les Chaldaica, ses écrits préservent la tradition néoplatonicienne tardive. &lt;/p&gt; &lt;p&gt;   Il poussa la dialectique néoplatonicienne jusqu'à ses limites, affirmant que le Premier Principe — l'Un — est absolument ineffable, au-delà de toute pensée et de tout être.&lt;/p&gt; &lt;p&gt;Après la fermeture de l'Académie, Damascios s'exila en Perse avec Simplicius et d'autres philosophes, à la cour du roi sassanide Khosrô Ier. Il représente la fin d'une époque : la clôture du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; antique, dont il fut l'un des penseurs les plus profonds et les plus radicaux.&lt;/p&gt; Critiquant Proclus, Damascios dépassa l'Un-Bien pour poser un principe ineffable (to aprorrhēton), absolu et sans relation, au-delà de toute connaissance. Son ontologie distingue l'Ineffable, l'Un, l'Intellect et l'Âme, influençant les théologies apophatiques ultérieures. &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F92" s="7" t="s">
         <v>757</v>
@@ -7394,8 +7476,13 @@
       <c r="D93" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="E93" s="9" t="s">
-        <v>763</v>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bo%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;Anicius Manlius BOÈCE&lt;/a&gt;, ou Boèce de Rome, était un philosophe, théologien et homme d'État Romain éduqué à Athènes et a été influencé par la philosophie grecque de Platon et d'Aristote.  &lt;/p&gt; &lt;p&gt; Il a vécu à une époque où l'Empire romain d'Occident était en déclin et où la culture classique était menacée par les invasions barbares et la montée du christianisme. 
+Il est connu pour son œuvre majeure, &lt;a  href="https://remacle.org/bloodwolf/philosophes/boece/livre3.htm#:~:text=J'entends%20par%20l%C3%A0%20ce,aurait%20encore%20mati%C3%A8re%20%C3%A0%20d%C3%A9sir." style="color:#88A1E9"  title="La consolation philosophique par Remacle"&gt;"La Consolation de la Philosophie"&lt;/a&gt;, qui a été écrite alors qu'il était en prison, en attente de son exécution pour des accusations de trahison envers le roi ostrogoth Théodoric le Grand.&lt;/p&gt; &lt;p&gt;  Dans cette œuvre, Boèce est consolé par la Philosophie personnifiée, qui lui enseigne que le véritable bonheur peut être trouvé dans &lt;a  href="https://www.youtube.com/watch?v=Bx-_WsSfylw&amp;t=1619s&amp;ab_channel=%C3%89CLAIRBRUT" style="color:#88A1E9"  title="Une âme dénuée du monde par Eclair Brut"&gt;la sagesse&lt;/a&gt; et la connaissance de Dieu, plutôt que dans la richesse et le pouvoir.&lt;/p&gt; &lt;p&gt;
+Il a également écrit sur des sujets tels que la musique, la logique et la théologie. Il a traduit plusieurs œuvres grecques en latin, y compris les œuvres d'Aristote et de Platon, ce qui a permis à la pensée grecque de survivre à la chute de l'Empire romain et de se transmettre à l'Europe médiévale.&lt;/p&gt; &lt;p&gt;
+Il a été exécuté en 524, mais son œuvre a continué d'être étudiée et appréciée tout au long du Moyen Âge et de la Renaissance. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F93" s="7" t="s">
         <v>764</v>
@@ -7573,8 +7660,10 @@
       <c r="D97" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="E97" s="10" t="s">
-        <v>795</v>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Philopon" style="color:#6A142A" title="Wikipedia"&gt;Jean PHILOPON&lt;/a&gt; fut l'un des penseurs les plus novateurs de l'Antiquité tardive. Philosophe et théologien chrétien monophysite d'Alexandrie, disciple d'Ammonios fils d'Hermias, il est célèbre pour ses vastes commentaires des œuvres d'&lt;a href="https://fr.wikipedia.org/wiki/Aristote" style="color:#6A142A" title="Aristote sur Wikipedia"&gt;Aristote&lt;/a&gt;, qu'il soumit à une critique audacieuse au nom de la physique et de la foi chrétienne.&lt;/p&gt; &lt;p&gt;  Il est un des premiers grands commentateurs d’Aristote en grec, mais il s’en distingue nettement sur des questions comme l’éternité du monde. Dans ses traités Contre Proclus (529) et De la création du monde, il défend l’idée que le monde a été créé ex nihilo dans le temps, ce qui l’oppose à la conception aristotélicienne d’un univers éternel, affirmant que le cosmos fut créé à partir du néant — en accord avec le dogme chrétien. Il développa également la théorie de l'&lt;em&gt;impetus&lt;/em&gt;, ancêtre du concept d'inertie : un projectile lancé reçoit une force interne qui le maintient en mouvement, préfigurant ainsi la physique galiléenne six siècles avant Galilée.&lt;/p&gt; &lt;p&gt;       Sur le plan théologique, il soutient une lecture allégorique de la Bible et cherche à harmoniser Platon, Aristote et Ptolémée avec la cosmologie chrétienne, en s’opposant notamment à la vision « étagée » du monde de Cosmas Indicopleustès. Il se rapproche d’abord du monophysisme, puis adhère au courant dit « trithéite » (tendance au sein du christianisme oriental qui insiste sur la distinction des trois personnes divines), ce qui lui vaudra une condamnation par certains milieux orthodoxes et monophysites.   &lt;/p&gt; &lt;p&gt; Il est une figure de carrefour entre philosophie grecque et théologie chrétienne. Sa lecture critique d'Aristote, qu'il commentait tout en le contestant, influença profondément les penseurs arabes médiévaux et, via eux, la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_scientifique" style="color:#6A142A" title="Révolution scientifique sur Wikipedia"&gt;révolution scientifique&lt;/a&gt; de la Renaissance. Il fut condamné pour hérésie (trithéisme) mais son héritage philosophique demeure immense.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F97" s="7" t="s">
         <v>796</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -5983,11 +5983,15 @@
       <c r="E61" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>500</v>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ca2cJql73D4</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Vie et oeuvre de Philodème" par Michel Onfray</t>
+        </is>
       </c>
       <c r="H61" s="9" t="s">
         <v>501</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3909,8 +3909,10 @@
       <c r="K15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>25</v>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Présocratique ; Pluralisme</t>
+        </is>
       </c>
       <c r="M15" s="11" t="s">
         <v>111</v>
@@ -4548,8 +4550,10 @@
       <c r="K29" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="L29" s="2" t="s">
-        <v>236</v>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platonisme ; Dualisme</t>
+        </is>
       </c>
       <c r="M29" s="2" t="s">
         <v>237</v>
@@ -4923,8 +4927,10 @@
       <c r="K37" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="L37" s="2" t="s">
-        <v>302</v>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aristotélisme ; Essentialisme</t>
+        </is>
       </c>
       <c r="M37" s="2" t="s">
         <v>303</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3227,7 +3227,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="6.39"/>
@@ -7988,6 +7988,62 @@
       <c r="P103">
         <v>2</v>
       </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="7">
+        <v>-450</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-400</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 450 A JC – 400 A JC</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRATYLE</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cratyle" title=" Wikipedia"&gt;CRATYLE&lt;/a&gt; est un philosophe grec d’Athènes, de la fin du Ve siècle av. J.-C., partisan radical de la pensée d’&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclite" title=" Wikipedia"&gt;Héraclite&lt;/a&gt;. Selon Aristote, Platon l’aurait fréquenté dans sa jeunesse, avant de rencontrer Socrate, et en aurait retenu l’idée que les choses sensibles sont dans un flux perpétuel, et qu’il ne peut donc y avoir de science à leur sujet.&lt;/p&gt; &lt;p&gt;Cratyle pousse le &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclit%C3%A9isme" title=" Wikipedia"&gt;mobilisme&lt;/a&gt; jusqu’à ses conséquences extrêmes. Héraclite disait qu’on ne peut entrer deux fois dans le même fleuve ; Cratyle lui reproche d’avoir été trop timide : on ne peut pas même y entrer une seule fois. Puisque tout change sans cesse, même pendant qu’on parle, aucune parole ne peut dire vrai. Selon Aristote, il finit par ne plus rien dire du tout et se contentait de remuer le doigt.&lt;/p&gt; &lt;p&gt;Platon a donné son nom à l’un de ses dialogues, le &lt;em&gt;Cratyle&lt;/em&gt;, consacré à la justesse des noms. Cratyle y soutient que chaque chose a un nom juste par nature, qui exprime son essence, contre Hermogène, pour qui les noms ne sont que des conventions. Socrate examine les deux thèses avec ironie, se livre à de savoureuses étymologies, et conclut qu’il vaut mieux connaître les choses par elles-mêmes que par leurs noms. Le débat entre la nature et la convention des signes traverse ensuite toute l’histoire de la philosophie du langage, jusqu’à Saussure.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/cratyle-mini.webp</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langage ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobilisme</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe grec, héraclitéen radical, qui a donné son nom au dialogue de Platon sur le langage.</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P104"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3383,8 +3383,10 @@
       <c r="D5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>30</v>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thal%C3%A8s"  style="color:#6A142A"  title=" Wikipedia"&gt;THALÈS DE MILET&lt;/a&gt; (vers 625-545 av. J.-C.) est traditionnellement considéré comme le premier philosophe grec, le premier des &lt;a href="https://www.youtube.com/watch?v=WMNWlH7NO0M&amp;ab_channel=Philosophistoria"  style="color:#88A1E9"  title="Les philosophes présocratiques par Philosophistoria"&gt;présocratiques&lt;/a&gt;. Il vit à Milet, riche cité grecque d’Ionie, sur la côte de l’actuelle Turquie, et compte parmi les « Sept Sages » de la Grèce. Il n’a sans doute rien écrit : nous le connaissons par Hérodote, Platon et surtout Aristote.&lt;/p&gt; &lt;p&gt;Sa grande nouveauté est d’expliquer le monde par un principe naturel, et non par les mythes. Il cherche l’&lt;em&gt;archè&lt;/em&gt;, le principe dont toutes choses viennent, et répond : &lt;a href="https://www.youtube.com/watch?v=8C2nDaxex-E&amp;ab_channel=LesCapsulesd%27Olen"   title="l'Arkhè par les Capsules d'Olen"&gt;l’eau&lt;/a&gt;. Peut-être avait-il remarqué que toute vie a besoin d’humidité et que l’eau peut être liquide, solide ou vapeur ; il pensait aussi que la terre flotte sur l’eau. Il disait encore que « tout est plein de dieux » et que l’aimant a une âme, puisqu’il met le fer en mouvement. Savant, il aurait prédit l’éclipse de soleil de 585 av. J.-C. et mesuré la hauteur des pyramides d’Égypte grâce à leur ombre ; le théorème des proportions qui porte son nom lui est attribué. Platon raconte qu’à force de regarder les étoiles, il tomba dans un puits, ce qui fit rire une servante. Aristote rapporte au contraire qu’ayant prévu une belle récolte d’olives, il loua tous les pressoirs et fit fortune, pour montrer que les philosophes pourraient s’enrichir s’ils le voulaient.&lt;/p&gt; &lt;p&gt;Ses successeurs à Milet, Anaximandre et Anaximène, poursuivent sa recherche : &lt;a href="https://www.youtube.com/watch?v=mnmXpuZmeTc"   title="Thales la naissance de la philosophie par parole de philosophe"&gt;sa philosophie&lt;/a&gt; marque le début de la pensée rationnelle grecque.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F5" s="7" t="s">
         <v>31</v>
@@ -3578,9 +3580,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Pythagore"  style="color:#6A142A"  title=" Wikipedia"&gt; PYTHAGORE&lt;/a&gt; était un philosophe, mathématicien et musicien grec célèbre pour ses contributions à la théorie des nombres, en particulier le fameux "théorème de Pythagore". Il a fondé une école de pensée dans le sud de l'Italie, où ses membres, appelés les  &lt;a href="https://www.normalesup.org/~adanchin/causeries/Pythagoriciens.html"  style="color:#88A1E9"  title="Pythagoriciens par Pierre Duhem"&gt; pythagoriciens&lt;/a&gt;, croyaient que les nombres étaient la clé de l'univers et que toute chose était régie par des lois mathématiques.  &lt;/p&gt; &lt;p&gt; Il croyait également en la &lt;a href="https://www.youtube.com/watch?v=_K28O2yEweI&amp;ab_channel=LaM%C3%A9moth%C3%A8que"  style="color:#88A1E9"  title="Transmigration des âmes par La Mémothèque"&gt; transmigration des âmes&lt;/a&gt;, l'idée que les âmes peuvent passer d'un corps à un autre, et que la purification de l'âme à travers l'éducation et la pratique de la vertu peut conduire à l'harmonie avec l'univers. &lt;/p&gt; &lt;p&gt; Pour lui, la musique était un moyen important d'atteindre cette harmonie, les sons et les vibrations pouvaient affecter l'âme de manière profonde. &lt;/p&gt; &lt;p&gt;  La philosophie pythagoricienne comprenait également des idées sur l'importance de l'équilibre et de l'harmonie dans tous les aspects de la vie, y compris la santé, la politique et la société. &lt;/p&gt; &lt;p&gt;
-Il lui a été crédité de nombreux autres développements mathématiques, notamment la découverte des propriétés des proportions musicales et la mise en évidence de la relation entre la longueur d'une corde et la hauteur de la note qu'elle produit. &lt;/p&gt; &lt;audio controls title="Pythagore est l'ancêtre des végétariens par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2016/05/s20/net-fi-e5fc1669-4513-4bb0-915b-d87efce86894.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-&lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pythagore"  style="color:#6A142A"  title=" Wikipedia"&gt;PYTHAGORE&lt;/a&gt; (vers 580-495 av. J.-C.) est un philosophe et mathématicien grec, l’une des figures les plus mystérieuses de l’Antiquité. Né à Samos, il quitte l’île vers 530 et s’installe à &lt;a href="https://fr.wikipedia.org/wiki/Crotone" title=" Wikipedia"&gt;Crotone&lt;/a&gt;, dans le sud de l’Italie. Il y fonde une communauté, à la fois école, confrérie religieuse et groupe politique, dont les membres, les &lt;a href="https://www.normalesup.org/~adanchin/causeries/Pythagoriciens.html"  style="color:#88A1E9"  title="Pythagoriciens par Pierre Duhem"&gt;pythagoriciens&lt;/a&gt;, partagent leurs biens, observent le silence, suivent un régime végétarien et des règles strictes. Les femmes y sont admises.&lt;/p&gt; &lt;p&gt;Pythagore n’a rien écrit, et ses disciples lui ont attribué beaucoup de leurs propres découvertes. Il enseigne la &lt;a href="https://www.youtube.com/watch?v=_K28O2yEweI&amp;ab_channel=LaM%C3%A9moth%C3%A8que"  style="color:#88A1E9"  title="Transmigration des âmes par La Mémothèque"&gt;transmigration des âmes&lt;/a&gt; : l’âme, immortelle, passe d’un corps à l’autre, y compris dans des animaux, et doit se purifier pour échapper au cycle des renaissances. Pour les pythagoriciens, « tout est nombre » : l’ordre du monde s’exprime en rapports numériques. Ils découvrent que les accords musicaux correspondent à des rapports simples entre les longueurs de corde, 2/1 pour l’octave, 3/2 pour la quinte, 4/3 pour la quarte, et imaginent une « harmonie des sphères » produite par le mouvement des astres. Le célèbre théorème était connu des Babyloniens bien avant eux, mais ils en auraient donné une démonstration. La tradition fait de Pythagore l’inventeur du mot « philosophe », celui qui aime la sagesse sans prétendre la posséder.&lt;/p&gt; &lt;p&gt;Vers 500 av. J.-C., une révolte chasse les pythagoriciens de Crotone. Leur pensée marque profondément Platon, puis Kepler, qui cherchera l’harmonie mathématique du monde.&lt;/p&gt;  &lt;audio controls title="Pythagore est l'ancêtre des végétariens par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2016/05/s20/net-fi-e5fc1669-4513-4bb0-915b-d87efce86894.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F9" s="7" t="s">
@@ -3746,11 +3746,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclite"  style="color:#6A142A"  title=" Wikipedia"&gt;HÉRACLITE&lt;/a&gt; était un philosophe présocratique Grec de &lt;a href="https://archive.org/details/histoiredelaphil00mall/page/116/mode/2up" style="color:#88A1E9"   title="L'école Ionienne par internet archive"&gt; l'école Ionienne&lt;/a&gt; et dont le courant de pensée est le &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclit%C3%A9isme"  style="color:#88A1E9"  title="Le Mobilisme par Wikipedia"&gt;Mobilisme&lt;/a&gt;. Il connu pour ses écrits fragmentaires, dont le plus connue est celle de la "doctrine du flux perpétuel" ou &lt;a href="http://www.etienne-barilier.name/Conferences/2011/Panta_rhei%20.pdf"  style="color:#88A1E9"  title="Conférence 'panta rhei' par Etienne Barilier"&gt;"panta rhei"&lt;/a&gt;, qui signifie "tout coule". Selon cette idée, &lt;a href="https://www.youtube.com/watch?v=rbgWLqDwEjs&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Rien n'est figé par Le Précepteur"&gt;rien n'est figé&lt;/a&gt;, tout est en mouvement constant et tout change dans le monde, en disant que "rien ne se crée, rien ne se perd, tout se transforme". &lt;/p&gt; &lt;p&gt; 
-Il a également affirmé que le monde était gouverné par une loi universelle, appelée &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1986_num_99_470_1455"  style="color:#88A1E9"  title="Le Logos selon Héraclite par Persée"&gt;"Logos"&lt;/a&gt;, qui est souvent traduit comme "parole" ou "raison" et qui régissait tout dans l'univers, y compris les êtres humains. Le Logos était à la fois ordre et chaos, car il était à la fois créateur et destructeur.   &lt;/p&gt; &lt;p&gt;                                       
-Pour lui, le monde est gouverné par des lois naturelles, plutôt que par des dieux capricieux et irrationnels et il avait une vision pessimiste de la nature humaine, affirmant que les êtres humains sont souvent gouvernés par leurs passions et leurs désirs, plutôt que par &lt;a href="https://www.youtube.com/watch?v=-fzeW9YP8TI&amp;ab_channel=Lepayssanschemin"  style="color:#88A1E9"  title="L'éveil de la raison par Le pays sans chemin"&gt;la raison&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; 
-Bien que peu de ses écrits aient survécu jusqu'à nos jours, sa pensée a eu une influence durable sur la philosophie et elle a inspiré notamment Platon et Aristote, ainsi que des philosophes modernes tels que Friedrich Nietzsche et Martin Heidegger.  &lt;/p&gt; &lt;audio controls title="Thèmes et controverses- l'héritage d'Héraclite par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/10/s41/RF_CD1E6508-A3E8-4B48-BFCF-A6BC3A6CA34B_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-&lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclite"  style="color:#6A142A"  title=" Wikipedia"&gt;HÉRACLITE&lt;/a&gt; d’Éphèse (vers 544-480 av. J.-C.) est un philosophe présocratique grec de &lt;a href="https://archive.org/details/histoiredelaphil00mall/page/116/mode/2up" style="color:#88A1E9"   title="L'école Ionienne par internet archive"&gt;l’école ionienne&lt;/a&gt;. Issu d’une famille royale de la cité, il aurait cédé son titre à son frère pour se consacrer à la réflexion, méprisant la foule comme les savants réputés. Son livre, déposé, dit-on, dans le temple d’Artémis, ne nous est parvenu qu’en une centaine de fragments, aphorismes si énigmatiques qu’on l’a surnommé « l’Obscur ».&lt;/p&gt; &lt;p&gt;Héraclite est le penseur du devenir, d’où le nom de &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclit%C3%A9isme"  style="color:#88A1E9"  title="Le Mobilisme par Wikipedia"&gt;mobilisme&lt;/a&gt; donné à sa doctrine, résumée plus tard par la formule &lt;a href="http://www.etienne-barilier.name/Conferences/2011/Panta_rhei%20.pdf"  style="color:#88A1E9"  title="Conférence 'panta rhei' par Etienne Barilier"&gt;&lt;em&gt;panta rhei&lt;/em&gt;&lt;/a&gt;, « tout s’écoule » : « On ne se baigne jamais deux fois dans le même fleuve. » &lt;a href="https://www.youtube.com/watch?v=rbgWLqDwEjs&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Rien n'est figé par Le Précepteur"&gt;Rien n’est figé&lt;/a&gt; : le jour et la nuit, la vie et la mort, le chaud et le froid passent l’un dans l’autre. Ce changement n’est pourtant pas un désordre : il est réglé par le &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1986_num_99_470_1455"  style="color:#88A1E9"  title="Le Logos selon Héraclite par Persée"&gt;&lt;em&gt;logos&lt;/em&gt;&lt;/a&gt;, la raison ou la loi commune de toutes choses, que la plupart des hommes ne comprennent pas. Le monde naît de la lutte des contraires : « La guerre est le père de toutes choses. » L’harmonie elle-même est une tension, comme celle de l’arc ou de la lyre. Le feu, toujours changeant et toujours le même, en est le symbole : le monde est « un feu toujours vivant, qui s’allume avec mesure et s’éteint avec mesure ». Héraclite invite chacun à suivre &lt;a href="https://www.youtube.com/watch?v=-fzeW9YP8TI&amp;ab_channel=Lepayssanschemin"  style="color:#88A1E9"  title="L'éveil de la raison par Le pays sans chemin"&gt;la raison&lt;/a&gt; commune plutôt que ses opinions : « Le caractère, pour l’homme, est son destin. »&lt;/p&gt; &lt;p&gt;Platon, les stoïciens, puis Hegel, Nietzsche et Heidegger ont vu en lui l’un des plus profonds penseurs grecs.&lt;/p&gt;  &lt;audio controls title="Thèmes et controverses- l'héritage d'Héraclite par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/10/s41/RF_CD1E6508-A3E8-4B48-BFCF-A6BC3A6CA34B_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F12" s="7" t="s">
@@ -4298,8 +4294,10 @@
       <c r="D24" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>187</v>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Euclide_de_M%C3%A9gare"   title=" Wikipedia"&gt;EUCLIDE de Mégare&lt;/a&gt; (vers 435-365 av. J.-C.) est un philosophe grec, disciple de Socrate et fondateur de &lt;a href="https://www.youtube.com/watch?v=RGVwwTCSsqg" style="color:#88A1E9" title="Euclides and the Megarian School par Foolish Musings "&gt;l’école mégarique&lt;/a&gt; ; il ne faut pas le confondre avec &lt;a href="https://www.youtube.com/watch?v=enZpq8jvFEs" style="color:#88A1E9" title="L'AXIOMATIQUE - Les Éléments d'Euclide par Monsieur Phi "&gt;Euclide le mathématicien&lt;/a&gt;, auteur des &lt;em&gt;Éléments&lt;/em&gt;, qui vécut un siècle plus tard. On raconte que, lorsque les Mégariens furent interdits de séjour à Athènes, il venait la nuit, déguisé en femme, pour écouter Socrate. Il assiste à la mort de son maître, en 399 av. J.-C., et accueille ensuite à Mégare Platon et d’autres disciples qui fuient Athènes.&lt;/p&gt; &lt;p&gt;Ses écrits, des dialogues, sont perdus. Il réunit l’éthique de Socrate et la métaphysique de &lt;a href="https://fr.wikipedia.org/wiki/Parm%C3%A9nide" title=" Wikipedia"&gt;Parménide&lt;/a&gt; : le Bien est un, toujours semblable à lui-même, même s’il reçoit plusieurs noms, sagesse, Dieu, intellect. Ce qui s’oppose au Bien n’existe pas. Comme les Éléates, Euclide se méfie du changement et du multiple, et privilégie l’être immuable. Il est surtout un redoutable dialecticien : il attaque les conclusions de ses adversaires plutôt que leurs prémisses, et rejette le raisonnement par analogie. Ses successeurs font de l’école mégarique un foyer de la logique grecque. Eubulide invente des paradoxes restés célèbres : celui du menteur, « je mens » ; celui du tas, à partir de combien de grains a-t-on un tas ? ; ou celui du chauve. Diodore Cronos réfléchit sur le possible et le nécessaire avec son « argument dominateur », et Philon définit l’implication logique d’une manière très proche de la logique moderne.&lt;/p&gt; &lt;p&gt;Le mégarique Stilpon eut pour élève Zénon de Kition, le fondateur du stoïcisme, qui hérita de ce goût pour la logique.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F24" s="7" t="s">
         <v>188</v>
@@ -5360,8 +5358,10 @@
       <c r="D47" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="E47" s="9" t="s">
-        <v>382</v>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Z%C3%A9non_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;ZENON de Kition&lt;/a&gt; (vers 334-262 av. J.-C.) est le fondateur de l’école &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcienne&lt;/a&gt;. Né à Kition, dans l’île de Chypre, il arrive à Athènes vers 312 av. J.-C. après un naufrage. Selon la légende, il lit chez un libraire les souvenirs de Xénophon sur Socrate et demande où trouver de tels hommes : le libraire lui montre le cynique Cratès qui passait. Zénon suit ses leçons, puis celles du mégarique Stilpon et des platoniciens.&lt;/p&gt; &lt;p&gt;Vers 300 av. J.-C., il enseigne sous le Portique peint d’Athènes, la &lt;em&gt;Stoa poikilè&lt;/em&gt;, d’où le nom de stoïcisme. Ses livres sont perdus. Il divise la philosophie en trois parties, que les stoïciens comparent à un jardin : la logique en est la clôture, la physique les arbres, l’éthique les fruits. Le monde est un tout vivant, ordonné par une raison divine, le &lt;em&gt;logos&lt;/em&gt;, présente en toute chose comme un feu artiste. Le but de la vie est de « vivre en accord avec la nature », c’est-à-dire avec la raison. La vertu est le seul bien, le vice le seul mal ; la santé, la richesse ou la réputation sont « indifférentes ». Les passions, comme la peur, le chagrin ou la colère, sont des jugements erronés et des élans excessifs : le sage s’en libère et atteint la tranquillité. Pour expliquer la connaissance, Zénon montre sa main ouverte, puis la ferme peu à peu jusqu’à serrer le poing : la sensation, l’assentiment, la compréhension, la science.&lt;/p&gt; &lt;p&gt;Les Athéniens honorent sa vertu d’une couronne d’or. Ses successeurs, Cléanthe et Chrysippe, développent sa doctrine, qui marquera Sénèque, Épictète et Marc Aurèle.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F47" s="7" t="s">
         <v>383</v>
@@ -6415,8 +6415,10 @@
       <c r="D70" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="E70" s="9" t="s">
-        <v>577</v>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89pict%C3%A8te"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICTETE&lt;/a&gt; (vers 50-vers 125) est un philosophe &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcien&lt;/a&gt; grec, né esclave à Hiérapolis, en Phrygie. À Rome, il appartient à Épaphrodite, affranchi de Néron, qui lui permet de suivre les leçons du stoïcien Musonius Rufus. Affranchi, il enseigne à son tour, jusqu’à ce que l’empereur Domitien chasse les philosophes de Rome vers 93 ; il ouvre alors une école à Nicopolis, en Épire, où il enseigne jusqu’à sa mort.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit. Son disciple &lt;a href="https://fr.wikipedia.org/wiki/Arrien" title=" Wikipedia"&gt;Arrien&lt;/a&gt; a noté ses leçons dans &lt;a href="https://www.youtube.com/watch?v=2tUxNx_oMn4&amp;ab_channel=KarlBaudoin"  style="color:#88A1E9"  title="Les Entretiens d'Epictète par Karl Baudouin"&gt;les &lt;em&gt;Entretiens&lt;/em&gt;&lt;/a&gt; et en a tiré un bref résumé, &lt;a href="https://www.youtube.com/watch?v=qN4m4bbZIGU&amp;t=51s&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Le manuel d'Epictète par Le Précepteur"&gt;le &lt;em&gt;Manuel&lt;/em&gt;&lt;/a&gt;. Tout part d’une distinction : il y a &lt;a href="https://www.youtube.com/watch?v=7Zc85Kc4Xqw&amp;ab_channel=KarlBaudoin"  title="Le manuel d'Epictète par Karl Baudouin"&gt;ce qui dépend de nous&lt;/a&gt;, nos jugements, nos désirs, nos refus, et ce qui ne dépend pas de nous, le corps, les biens, la réputation, les charges, les événements. Le malheur vient de ce que nous voulons maîtriser ce qui nous échappe. « Ce qui trouble les hommes, ce ne sont pas les choses, mais les jugements qu’ils portent sur les choses » : la mort n’est pas terrible, c’est l’opinion que nous en avons qui l’est. La liberté est donc intérieure, et l’esclave peut être plus libre que son maître. Le sage s’exerce chaque jour à bien juger, à désirer seulement ce qui dépend de lui, et à jouer son rôle dans le monde comme un acteur joue celui que l’auteur lui a donné. On résume sa morale par la formule « supporte et abstiens-toi ».&lt;/p&gt; &lt;p&gt;Lu par &lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le" title=" Wikipedia"&gt;Marc Aurèle&lt;/a&gt;, puis par Pascal et Montaigne, il inspire encore les thérapies cognitives d’aujourd’hui, qui apprennent à modifier nos jugements pour apaiser nos émotions.&lt;/p&gt;  &lt;audio controls title="Epictète ou savoir choisir par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-07.01.2026-ITEMA_24365714-2026C48904S0007-NET_MFC_C2619D7A-778C-4505-B127-925270631DD9-21-6f25ae2ae83c473a68406d0d4d07fa43.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F70" s="7" t="s">
         <v>65</v>
@@ -6510,7 +6512,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le"  style="color:#6A142A"  title=" Wikipedia"&gt;Marc AURÈLE&lt;/a&gt; était un empereur romain considéré comme l'un des plus justes et des plus sages.&lt;/p&gt; &lt;p&gt; Il était connu pour son livre &lt;a href="https://fr.wikipedia.org/wiki/Pens%C3%A9es_pour_moi-m%C3%AAme"  title="Les pensées pour moi même de Marc AURELE "&gt;"Méditations" &lt;/a&gt; ou « &lt;em&gt;Les pensées pour moi même&lt;/em&gt;, qui reflète ses pensées sur la philosophie stoïcienne et qui est considéré comme un classique de la littérature spirituelle ont été rédigées en grec, probablement comme  &lt;a href="https://www.youtube.com/watch?v=KKSRqzRdBx0"  title="Les pensées pour moi même Marc AURELE par Kosmos"&gt;un journal intime &lt;/a&gt; ou un exercice personnel, et non comme un livre destiné à la publication. Il  appartient au stoïcisme, une philosophie qui insiste sur la maîtrise de soi, le devoir et l’acceptation de ce qu’on ne contrôle pas. &lt;p&gt; Dans ses écrits, il a souligné l'importance de la sagesse, de la vertu et de la modération, et a exhorté les gens à rester calmes et à rester imperméables aux émotions négatives telles que la peur, la colère et la tristesse.&lt;/p&gt; &lt;p&gt; Il a également abordé des sujets tels que la mort, la justice, la responsabilité et le devoir. &lt;a href="https://www.youtube.com/watch?v=1OeNwG_bxWg&amp;ab_channel=FranceCulture"   title="Les pensées de Marc AURELE au quotidien par France Culture"&gt;"De nos jours"&lt;/a&gt;, ses idées sont encore étudiées et appréciées pour leur pertinence et leur sagesse, et sont considérées comme un élément fondamental de la philosophie stoïcienne moderne. &lt;/p&gt; &lt;p&gt;   Il est important à la fois pour l’histoire romaine et pour la philosophie, car il incarne un rare mélange de pouvoir politique et de réflexion morale. Son influence perdure surtout grâce à ses écrits, souvent lus aujourd’hui comme un guide de vie stoïcienne,&lt;/p&gt;  &lt;audio controls title="Pensée pour moi même par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.01.2016-ITEMA_20899513-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le"  style="color:#6A142A"  title=" Wikipedia"&gt;Marc AURÈLE&lt;/a&gt; (121-180) est un empereur romain et un philosophe stoïcien, le seul « empereur philosophe » de l’histoire romaine. Adopté par l’empereur Antonin le Pieux, il reçoit la meilleure éducation de son temps ; son maître Junius Rusticus lui fait lire les &lt;em&gt;Entretiens&lt;/em&gt; d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89pict%C3%A8te" title=" Wikipedia"&gt;Épictète&lt;/a&gt;, qui le marquent pour toujours. Empereur de 161 à sa mort, il passe une grande partie de son règne à défendre les frontières du Danube, au milieu d’une terrible épidémie.&lt;/p&gt; &lt;p&gt;C’est sous la tente, pendant ces campagnes, qu’il écrit en grec ses &lt;a href="https://fr.wikipedia.org/wiki/Pens%C3%A9es_pour_moi-m%C3%AAme"  title="Les pensées pour moi même de Marc AURELE "&gt;&lt;em&gt;Pensées pour moi-même&lt;/em&gt;&lt;/a&gt;, en douze livres. Ce n’est pas un traité destiné au public, mais &lt;a href="https://www.youtube.com/watch?v=KKSRqzRdBx0"  title="Les pensées pour moi même Marc AURELE par Kosmos"&gt;un journal intime&lt;/a&gt; d’exercices spirituels : il s’y rappelle les principes du stoïcisme pour mieux les vivre. Tout change et passe vite, les empires comme les hommes ; la mort est un phénomène naturel qu’il ne faut pas craindre. Le monde est un tout ordonné par la raison, et ce qui arrive doit être accepté comme une part de cet ordre. Ce qui nous trouble, ce ne sont pas les choses, mais nos jugements sur elles : il suffit de les corriger pour retrouver la paix dans cette « citadelle intérieure » que rien ne peut forcer. Marc Aurèle s’exhorte aussi à la justice et à la bienveillance : tous les hommes sont parents, membres d’une même cité universelle, et il faut instruire les méchants plutôt que s’irriter contre eux. « Dès l’aurore, dis-toi d’avance : je rencontrerai un indiscret, un ingrat, un insolent… »&lt;/p&gt; &lt;p&gt;Lu par Montaigne et Frédéric II, il connaît un vif succès &lt;a href="https://www.youtube.com/watch?v=1OeNwG_bxWg&amp;ab_channel=FranceCulture"   title="Les pensées de Marc AURELE au quotidien par France Culture"&gt;de nos jours&lt;/a&gt;, grâce notamment à Pierre Hadot, qui a montré dans &lt;em&gt;La Citadelle intérieure&lt;/em&gt; (1992) la portée de ces exercices.&lt;/p&gt;  &lt;audio controls title="Pensée pour moi même par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.01.2016-ITEMA_20899513-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F72" s="7" t="s">
@@ -6603,8 +6605,10 @@
       <c r="D74" s="8" t="s">
         <v>608</v>
       </c>
-      <c r="E74" s="9" t="s">
-        <v>609</v>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Plotin"  style="color:#6A142A"  title=" Wikipedia"&gt;PLOTIN&lt;/a&gt; (205-270) est le plus grand philosophe de l’Antiquité tardive et le fondateur du néoplatonisme. Né en Égypte, il étudie à Alexandrie pendant onze ans auprès d’&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas" title=" Wikipedia"&gt;Ammonios Saccas&lt;/a&gt;, puis suit l’expédition de l’empereur Gordien III contre la Perse pour connaître la sagesse des Perses et des Indiens. Il s’installe à Rome vers 245 et y ouvre une école fréquentée par des sénateurs et des médecins.&lt;/p&gt; &lt;p&gt;Ses 54 traités ont été classés par son disciple &lt;a href="https://fr.wikipedia.org/wiki/Porphyre_de_Tyr" title=" Wikipedia"&gt;Porphyre&lt;/a&gt; en six groupes de neuf, les &lt;a href="https://www.youtube.com/watch?v=_UTBOMazrcE&amp;t=699s&amp;ab_channel=R%C3%A9sonance%5Bs%5D"  style="color:#88A1E9"  title="Les Ennéades de Plotin: Au commencement était l'Un par Résonance"&gt;&lt;em&gt;Ennéades&lt;/em&gt;&lt;/a&gt;. Plotin y relit Platon pour en tirer un système : &lt;a href="https://www.youtube.com/watch?v=nZblkRaDj-Q&amp;ab_channel=PhiloCloud"  style="color:#88A1E9"  title="Au commencement était l'Un par PhiloCloud"&gt;au commencement est l’Un&lt;/a&gt;, principe absolument simple, au-delà de l’être et de la pensée, que l’on ne peut nommer. De lui procède, comme la lumière du soleil, l’Intellect, qui contient les Idées, puis l’Âme, qui anime le monde sensible ; la matière, au plus bas, n’est presque rien, une absence de forme. Tout être vient de l’Un et aspire à y retourner. L’âme humaine, tombée dans le corps, peut remonter vers sa source par la vertu, la philosophie et la contemplation de la beauté, jusqu’à l’union avec l’Un, une extase que Plotin aurait connue quatre fois. C’est une ascension où l’Intellect, &lt;a href="https://books.openedition.org/vrin/4250?lang=fr"  style="color:#88A1E9"  title="Une méthaphysique de l'amour par OpenEdition"&gt;« embrasé d’amour »&lt;/a&gt;, s’oublie lui-même : « Retranche tout. »&lt;/p&gt; &lt;p&gt;Ses dernières paroles auraient été : « Tâchez de faire remonter le divin qui est en vous au divin qui est dans l’univers. » Par Augustin et le Pseudo-Denys, il marque la mystique chrétienne, et Marsile Ficin le traduit à la Renaissance.&lt;/p&gt;  &lt;audio controls title="La beauté est elle d'abord intérieure ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-04.04.2019-ITEMA_22027092-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F74" s="7" t="s">
         <v>610</v>
@@ -7160,8 +7164,10 @@
       <c r="D86" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="E86" s="12" t="s">
-        <v>709</v>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Proclus"   title="Proclus par Wikipédia"&gt;PROCLUS&lt;/a&gt; (412-485) est un philosophe &lt;a href="https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D"   title="Le Néoplatonisme par Anne Baudart"&gt;néoplatonicien grec&lt;/a&gt;, l’un des derniers grands penseurs de l’Antiquité. Né à Constantinople, il étudie à Alexandrie, puis à Athènes auprès de Syrianus, auquel il succède à la tête de l’école platonicienne : on l’appelle le « diadoque », le successeur. Il la dirige près de cinquante ans. Végétarien, très pieux, il célèbre les fêtes de tous les peuples, car le philosophe doit être, disait-il, « le prêtre du monde entier ».&lt;/p&gt; &lt;p&gt;Il laisse un grand nombre d’&lt;a href="https://remacle.org/bloodwolf/philosophes/proclus/table.htm"   title="Proclus par Philippe Remacle"&gt;ouvrages&lt;/a&gt;, dont des commentaires de Platon, sur le &lt;em&gt;Timée&lt;/em&gt;, la &lt;em&gt;République&lt;/em&gt;, le &lt;em&gt;Parménide&lt;/em&gt; ou l’&lt;em&gt;Alcibiade&lt;/em&gt;, et un commentaire du premier livre d’Euclide, précieuse source sur l’histoire de la géométrie. Dans les &lt;a href="https://www.youtube.com/watch?v=SJK1kbyXXno"   title="Les éléments de Théologie de Proclus par LabEx HaStec"&gt;&lt;em&gt;Éléments de théologie&lt;/em&gt;&lt;/a&gt;, il expose son système en 211 propositions démontrées à la manière des mathématiciens ; la &lt;em&gt;Théologie platonicienne&lt;/em&gt; le développe. Au sommet se trouve l’Un, principe absolument simple et indicible. De lui procèdent les hénades, qui sont les dieux, puis l’Intellect, l’Âme et enfin la nature et la matière. Tout se déploie selon un même rythme à trois temps : chaque réalité demeure dans sa cause, en procède, puis se retourne vers elle. L’âme humaine peut ainsi remonter vers l’Un par la philosophie, mais aussi par la théurgie, les rites qui unissent aux dieux.&lt;/p&gt; &lt;p&gt;À travers le Pseudo-Denys et le &lt;em&gt;Livre des causes&lt;/em&gt;, adaptation arabe de ses &lt;em&gt;Éléments&lt;/em&gt;, sa pensée marque le Moyen Âge, de Thomas d’Aquin à Maître Eckhart, puis Nicolas de Cues et Hegel.&lt;/p&gt;  &lt;audio controls title=" Proclus, un philosophe étoilé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F86" s="7" t="s">
         <v>710</v>
@@ -7209,8 +7215,10 @@
       <c r="D87" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="E87" s="12" t="s">
-        <v>717</v>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie" style="color:#6A142A" title="Wikipedia"&gt;HERMIAS d’Alexandrie&lt;/a&gt; est un philosophe néoplatonicien du Ve siècle, maillon important entre les écoles d’Athènes et d’Alexandrie. Né à Alexandrie, il part étudier à Athènes auprès du grand &lt;a href="https://fr.wikipedia.org/wiki/Syrianos" title="Syrianus sur Wikipedia"&gt;Syrianus&lt;/a&gt;, qui dirige alors l’école platonicienne ; il y a pour condisciple le jeune Proclus. Il épouse Aidésia, une parente de son maître, réputée pour sa culture et sa piété.&lt;/p&gt; &lt;p&gt;Revenu à Alexandrie, il y enseigne la philosophie, payé par la cité. Son seul ouvrage conservé est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes qu’il avait prises aux cours de Syrianus ; c’est le seul commentaire antique de ce dialogue qui nous soit parvenu. Le &lt;em&gt;Phèdre&lt;/em&gt; traite de l’amour, de la beauté et de l’âme, que Platon compare à un attelage ailé conduit par un cocher. Hermias en donne une lecture à la fois métaphysique et religieuse : les différentes formes de « délire » divin dont parle Socrate, prophétique, mystique, poétique et amoureux, sont autant d’étapes qui permettent à l’âme de remonter vers les dieux et vers l’Un. L’amour de la beauté sensible devient ainsi le point de départ d’une ascension spirituelle. Le philosophe Damascius le décrit comme un homme travailleur et d’une grande droiture, plus fidèle à ses maîtres qu’original.&lt;/p&gt; &lt;p&gt;Hermias meurt assez jeune. Aidésia emmène alors leurs deux fils, Ammonios et Héliodore, étudier à Athènes auprès de Proclus. Ammonios d’Alexandrie deviendra l’un des grands maîtres du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et formera à son tour toute une génération de commentateurs d’Aristote.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F87" s="7" t="s">
         <v>718</v>
@@ -7535,8 +7543,10 @@
       <c r="D94" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="E94" s="15" t="s">
-        <v>772</v>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hermias_de_Ph%C3%A9nicie" style="color:#6A142A" title="Wikipedia"&gt;HERMIAS de Phénicie&lt;/a&gt; est un philosophe néoplatonicien du VIe siècle, membre de l’école d’Athènes à l’époque où elle est dirigée par Damascius. Nous ne savons presque rien de lui, sinon sa participation à l’un des épisodes les plus célèbres de la fin de la philosophie antique : l’exil des derniers philosophes païens en Perse.&lt;/p&gt; &lt;p&gt;En 529, l’empereur chrétien Justinien interdit aux païens d’enseigner et d’occuper des fonctions publiques. L’école platonicienne d’Athènes, héritière de l’Académie de Platon, ne peut plus fonctionner, et ses biens sont menacés. Vers 531, sept philosophes décident de quitter l’Empire : Damascius, Simplicius de Cilicie, Priscien de Lydie, Eulamios de Phrygie, Isidore de Gaza, Diogène de Phénicie et Hermias, son compatriote. Ils se rendent à la cour du roi sassanide &lt;a href="https://fr.wikipedia.org/wiki/Khosro_Ier" title=" Wikipedia"&gt;Khosro Ier&lt;/a&gt;, réputé ami de la philosophie, qui faisait traduire Platon et Aristote. L’historien byzantin Agathias, qui raconte leur voyage, les appelle « la fleur la plus noble des philosophes de notre temps ». Mais la Perse les déçoit : ils y trouvent l’injustice et des mœurs qui les choquent, et le roi lui-même leur paraît moins philosophe qu’on ne le disait. En 532, le traité de paix entre Khosro et Justinien prévoit qu’ils pourront rentrer dans l’Empire sans être forcés de renoncer à leurs croyances.&lt;/p&gt; &lt;p&gt;Aucune œuvre d’Hermias ne nous est parvenue. On ignore où les exilés finirent leur vie ; certains historiens pensent qu’une partie d’entre eux s’installa à Harran, aux confins de l’Empire, où la tradition platonicienne se serait maintenue jusqu’à l’époque islamique.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F94" s="7" t="s">
         <v>773</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3339,8 +3339,10 @@
       <c r="D4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>19</v>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pittacos_de_Mytil%C3%A8ne"  title=" Wikipedia"&gt;PITTACOS de Mytilène&lt;/a&gt; (vers 640-568 av. J.-C.) est un homme d’État grec, compté parmi les &lt;a href="https://fr.wikipedia.org/wiki/Sept_sages_de_Gr%C3%A8ce"  style="color:#88A1E9"  title="les 7 Sages par Wikipédia"&gt;« Sept Sages »&lt;/a&gt; de la Grèce. Contrairement à Thalès, son contemporain, il n’est pas un philosophe de la nature comme ceux de &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_ionienne_(philosophie)"    title="L'école Ionienne par Wikipedia"&gt;l’école ionienne&lt;/a&gt; : sa sagesse est pratique et politique. Il vit à Mytilène, la principale cité de l’île de Lesbos, alors déchirée par les luttes entre familles aristocratiques et par les tyrannies.&lt;/p&gt; &lt;p&gt;Vers 612 av. J.-C., il participe au renversement du tyran Mélanchros. Dans la guerre qui oppose Mytilène à Athènes, il tue en combat singulier le général athénien Phrynon, en l’enveloppant d’un filet. Les Mytiléniens, pour mettre fin aux guerres civiles, lui confient alors pendant dix ans les pleins pouvoirs comme « arbitre » (&lt;em&gt;aisymnète&lt;/em&gt;). Il donne à la cité des lois sévères : l’une d’elles punit doublement les fautes commises en état d’ivresse, pour décourager l’ivrognerie. Puis, sa tâche accomplie, il renonce de lui-même au pouvoir, geste rare qui fit sa réputation de sagesse. Le poète Alcée, son adversaire politique, l’attaqua violemment dans ses vers ; Pittacos lui pardonna, en disant que le pardon vaut mieux que la vengeance. Plusieurs maximes lui sont attribuées : « Connais l’occasion », « Le pouvoir révèle l’homme », « Il est difficile d’être bon », ou encore « Ne fais pas toi-même ce que tu reproches à ton voisin », proche de la règle d’or.&lt;/p&gt; &lt;p&gt;Platon discute l’une de ses maximes dans le &lt;em&gt;Protagoras&lt;/em&gt;. Pittacos incarne l’idéal grec de mesure : le pouvoir au service de la paix civile, et non de l’ambition personnelle.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F4" s="7" t="s">
         <v>20</v>
@@ -4764,8 +4766,10 @@
       <c r="D34" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>274</v>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ar%C3%A9t%C3%A9_de_Cyr%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;ARÉTÉ de Cyrène&lt;/a&gt; (IVe siècle av. J.-C.) est l’une des premières &lt;a href="https://www.youtube.com/watch?v=9vy8w9K-YgQ" style="color:#88A1E9" title="Arete Of Cyrene 1st Woman Philosopher Before BC par Celebrities World"&gt;femmes philosophes&lt;/a&gt; connues de la Grèce antique. Fille d’Aristippe de Cyrène, disciple de Socrate et fondateur de l’école cyrénaïque, elle reçoit de son père une formation philosophique et prend une place centrale dans la transmission de sa doctrine.&lt;/p&gt; &lt;p&gt;Nous la connaissons surtout par l’historien Diogène Laërce et par d’autres sources tardives, et aucun de ses écrits ne nous est parvenu. Son rôle principal est d’avoir formé son propre fils, Aristippe le Jeune, surnommé « l’instruit par sa mère » (&lt;em&gt;Mêtrodidaktos&lt;/em&gt;), qui donnera à l’école sa forme systématique. &lt;a href="https://www.youtube.com/watch?v=Rp7sm07EJBY&amp;t=324s" style="color:#88A1E9" title="Les Cyrénaîsme par Alain Bajoumée"&gt;Les cyrénaïques&lt;/a&gt; font du plaisir le seul bien et de la douleur le seul mal. Ils fondent cette morale sur une théorie de la connaissance : nous ne connaissons que nos propres sensations, non les choses qui les causent. Le plaisir est un « mouvement doux », la douleur un « mouvement rude » ; le plaisir présent, corporel et vif, est le seul dont nous soyons sûrs, car le passé n’est plus et l’avenir est incertain. Mais le sage cyrénaïque n’est pas un débauché : il cherche à maîtriser le plaisir sans s’en rendre esclave, et à rester libre en toutes circonstances. Une lettre attribuée à Aristippe, sans doute apocryphe, conseille à Arété de gérer ses biens avec mesure et de veiller à l’éducation de son fils.&lt;/p&gt; &lt;p&gt;Des auteurs plus tardifs lui ont prêté une longue carrière d’enseignante et de nombreux livres, sans preuve. Elle reste cependant le symbole de la place des femmes dans la philosophie antique, aux côtés d’Hipparchia ou de Théano.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F34" s="7" t="s">
         <v>275</v>
@@ -5407,8 +5411,10 @@
       <c r="D48" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="E48" s="9" t="s">
-        <v>391</v>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9anthe"  style="color:#6A142A"  title=" Wikipedia"&gt;CLÉANTHE&lt;/a&gt; (vers 330-232 av. J.-C.) est un philosophe stoïcien grec, successeur de Zénon de Kition à la tête de l’école du Portique. Né à Assos, en Asie Mineure, ancien pugiliste, il arrive à Athènes presque sans ressources ; pour payer ses études, il tire de l’eau la nuit dans les jardins, ce qui lui vaut le surnom de « puiseur d’eau ». Il suit l’enseignement de Zénon pendant dix-neuf ans. Ses camarades le surnomment « l’âne », parce qu’il apprend lentement, mais il répond qu’il est le seul à pouvoir porter le fardeau de Zénon.&lt;/p&gt; &lt;p&gt;Il dirige l’école de 262 à sa mort. Moins brillant dialecticien que son successeur Chrysippe, il apporte pourtant des idées propres, surtout en physique et en théologie. Pour lui, l’univers est un être vivant animé par un souffle de feu, dont la tension maintient l’unité de toutes choses ; le soleil en est la partie directrice. Il défend une morale exigeante : la vertu est le seul bien, et le plaisir n’est pas conforme à la nature. Son œuvre la plus célèbre est l’&lt;a href="https://www.persee.fr/doc/rea_0035-2004_1998_num_100_1_4719" style="color:#88A1E9" title="L'universel &amp; le singulier. L'hymne à Zeus de Cléanthe. par Persée"&gt;&lt;em&gt;Hymne à Zeus&lt;/em&gt;&lt;/a&gt;, poème où Zeus est identifié à la raison universelle qui gouverne le monde : seuls les méchants s’en écartent, par ignorance. Une autre prière, citée par Épictète et traduite par Sénèque, résume l’attitude stoïcienne : « Conduis-moi, Zeus, et toi, Destinée, là où vous m’avez fixé ma place. » Sénèque en tire la formule : « Le destin conduit celui qui consent, il traîne celui qui résiste. »&lt;/p&gt; &lt;p&gt;Il meurt très âgé, en jeûnant. Hume a donné son nom au défenseur de &lt;a href="https://www.youtube.com/watch?v=HBbaB-X6xCI" style="color:#88A1E9" title=" L'argument a posteriori 1/2 : le raisonnement par analogie de Cléanthe par Gresza"&gt;l’argument par analogie&lt;/a&gt; dans ses &lt;em&gt;Dialogues sur la religion naturelle&lt;/em&gt;.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F48" s="7" t="s">
         <v>392</v>
@@ -5495,8 +5501,10 @@
       <c r="D50" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="E50" s="9" t="s">
-        <v>407</v>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Wikipedia"&gt;ARCÉSILAS de Pitane&lt;/a&gt; fut l'un des philosophes les plus originaux de l'Antiquité, fondateur de la Moyenne Académie. En prenant la direction de l'Académie platonicienne vers 268 av. J.-C., il en transforma radicalement l'esprit en introduisant le scepticisme comme méthode philosophique fondamentale.&lt;/p&gt; &lt;p&gt;S'inspirant de &lt;a href="https://fr.wikipedia.org/wiki/Pyrrhon_d%27%C3%89lis" style="color:#6A142A" title="Pyrrhon sur Wikipedia"&gt;Pyrrhon d'Élis&lt;/a&gt; et de la pratique dialectique de Socrate, Arcésilas défendit la thèse que la suspension du jugement (&lt;em&gt;épochè&lt;/em&gt;) est la seule attitude raisonnable face à l'incertitude de la connaissance. Il combattit vigoureusement le dogmatisme stoïcien de Zénon de Kition, notamment la notion de « représentation compréhensive » (&lt;em&gt;phantasia kataleptike&lt;/em&gt;) censée fonder la certitude.&lt;/p&gt; &lt;p&gt;Fidèle à l'esprit socratique, Arcésilas n'écrivit rien. Il enseignait oralement, par le dialogue et la réfutation. Sa pensée est connue par les rapports de Cicéron, Sextus Empiricus et Diogène Laërce. Sa maxime : &lt;em&gt;« Suspendre son jugement est ce qu'il y a de plus sage »&lt;/em&gt;. Il incarne la résistance intellectuelle au dogmatisme et reste une référence majeure pour toute philosophie du doute. Né à Pitane, en Éolide, il étudie d’abord auprès de Théophraste, au Lycée, avant de rejoindre l’Académie de Polémon et de Crantor. Sa méthode consiste à argumenter pour et contre chaque thèse, jusqu’à montrer qu’elles se valent. Pour agir sans rien affirmer, il suffit, selon lui, de suivre ce qui paraît raisonnable. Un stoïcien se moquait de lui en le comparant à une chimère : « Platon par-devant, Pyrrhon par-derrière, Diodore au milieu ».&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F50" s="7" t="s">
         <v>408</v>
@@ -5627,8 +5635,10 @@
       <c r="D53" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>433</v>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s" style="color:#6A142A" title="Wikipedia"&gt;LACYDÈS de Cyrène&lt;/a&gt; (mort vers 205 av. J.-C.) est un philosophe grec, successeur d’&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Arcésilas sur Wikipedia"&gt;Arcésilas de Pitane&lt;/a&gt; à la tête de l’Académie, l’école fondée à Athènes par Platon. Originaire de Cyrène, en Libye actuelle, il vient étudier à Athènes et devient le disciple d’Arcésilas, auquel il succède vers 241 av. J.-C.&lt;/p&gt; &lt;p&gt;Il enseigne dans un jardin de l’Académie aménagé pour lui par le roi Attale Ier de Pergame, admirateur de la philosophie, et qu’on appelle le &lt;em&gt;Lacydion&lt;/em&gt;. Invité à la cour de ce roi, il refuse de s’y rendre, en disant que les portraits des rois se regardent de loin. Lacydès reste fidèle au &lt;a href="https://www.youtube.com/watch?v=kG3klWpBf2Y"  title="Le sceptisisme de la nouvelle-académie"&gt;scepticisme académique&lt;/a&gt; de son maître. Contre les stoïciens, qui croient à des perceptions si claires qu’elles garantissent la vérité, les académiciens soutiennent que rien ne peut être connu avec certitude : toute impression vraie pourrait être imitée par une impression fausse. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et se contenter de ce qui paraît raisonnable. Une anecdote rapportée par les Anciens illustre, avec humour, les difficultés de cette position : ses esclaves volaient ses provisions puis remettaient les scellés intacts ; pris sur le fait, ils lui auraient opposé sa propre doctrine : comment pouvait-il être sûr de ce qu’il voyait ?&lt;/p&gt; &lt;p&gt;Atteint de paralysie dans sa vieillesse, il confie de son vivant la direction de l’école à ses disciples Téléclès et Évandre, cas rare dans l’histoire de l’Académie. Selon Diogène Laërce, il aurait écrit des traités sur la philosophie et sur la nature, aujourd’hui perdus.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F53" s="7" t="s">
         <v>434</v>
@@ -5671,8 +5681,10 @@
       <c r="D54" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="E54" s="9" t="s">
-        <v>441</v>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89vandre_(philosophe)" title="Wikipedia"&gt;ÉVANDRE&lt;/a&gt; (IIIe siècle av. J.-C.) est un philosophe grec originaire de Phocée, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de &lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s_de_Cyr%C3%A8ne" title=" Wikipedia"&gt;Lacydès de Cyrène&lt;/a&gt;, il reçoit de lui, avec Téléclès, la direction de l’école du vivant même de leur maître : Lacydès, malade, la leur confie vers 224 av. J.-C. Évandre et Téléclès la dirigent ensemble, cas rare dans l’histoire de l’institution.&lt;/p&gt; &lt;p&gt;Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par &lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" title=" Wikipedia"&gt;Arcésilas&lt;/a&gt;. Celui-ci avait donné à l’école platonicienne une orientation sceptique, en s’appuyant sur le Socrate qui affirmait ne rien savoir. Contre les stoïciens, qui pensaient que certaines représentations sont si évidentes qu’elles garantissent la vérité, les académiciens soutiennent qu’aucune perception ne permet de distinguer avec certitude le vrai du faux : un rêve, une illusion ou un jumeau peuvent produire la même impression qu’une perception exacte. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et ne rien affirmer. Pour agir, il suffit de suivre ce qui paraît raisonnable. Les académiciens enseignaient en argumentant pour et contre chaque thèse, afin de montrer que les deux positions se valent et d’exercer l’esprit critique de leurs élèves. Évandre transmet cet héritage à une génération d’étudiants.&lt;/p&gt; &lt;p&gt;Aucun de ses écrits ne nous est parvenu. Il a pour successeur Hégésinous de Pergame, qui forme à son tour &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant penseur de la Nouvelle Académie.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F54" s="7" t="s">
         <v>442</v>
@@ -5717,8 +5729,10 @@
       <c r="D55" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="E55" s="12" t="s">
-        <v>450</v>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame" title="Wikipedia"&gt;Hégésinous de PERGAME&lt;/a&gt; (IIe siècle av. J.-C.) est un philosophe grec, chef de l’Académie, l’école fondée à Athènes par Platon. Originaire de Pergame, en Asie Mineure, il succède à Évandre et Téléclès, qui avaient dirigé ensemble l’école, et il a pour élève et successeur &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant dialecticien de l’Antiquité.&lt;/p&gt; &lt;p&gt;Nous ne connaissons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu : son nom nous est connu par les listes des chefs successifs de l’Académie et par Cicéron, qui indique que Carnéade l’eut pour maître. Il appartient à la période sceptique de l’Académie, inaugurée par Arcésilas. Les académiciens de ce temps refusent d’affirmer quoi que ce soit avec certitude. Contre les stoïciens, qui croient que certaines perceptions portent en elles la marque de leur vérité, ils montrent qu’une perception vraie pourrait toujours être imitée par une perception fausse, comme dans le rêve ou l’illusion. Il faut donc suspendre son jugement. Mais cela n’empêche pas de vivre : pour agir, on peut suivre ce qui paraît raisonnable. L’enseignement de l’Académie se fait par la discussion contradictoire, en argumentant pour et contre chaque thèse. C’est cette méthode que Carnéade portera à son sommet : envoyé à Rome en ambassade en 155 av. J.-C., il fit scandale en défendant un jour la justice, puis en la réfutant le lendemain.&lt;/p&gt; &lt;p&gt;Hégésinous est ainsi un maillon de la transmission entre la Moyenne et la Nouvelle Académie, durant la période de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique" style="color:#6A142A" title="Philosophie hellénistique sur Wikipedia"&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F55" s="7" t="s">
         <v>451</v>
@@ -5761,8 +5775,10 @@
       <c r="D56" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="E56" s="12" t="s">
-        <v>458</v>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Wikipedia"&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href="https://fr.wikipedia.org/wiki/Dialectique" title="Dialectique par Wikipedia"&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272" title="Opinion et certitude par Persee"&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron" style="color:#6A142A" title="Cicéron sur Wikipedia"&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il. Formé à la dialectique par le stoïcien Diogène de Babylone, il étudie de près l’œuvre de Chrysippe pour mieux la réfuter, au point de dire : « Sans Chrysippe, je ne serais pas. » Il distingue trois degrés de vraisemblance : la représentation simplement probable, celle qui n’est contredite par aucune autre, et celle qui a été examinée sous tous ses aspects. Il critique aussi la divination, le destin et la providence des stoïciens. Son disciple Clitomaque a mis par écrit son enseignement.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F56" s="7" t="s">
         <v>459</v>
@@ -5854,8 +5870,10 @@
       <c r="D58" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="E58" s="12" t="s">
-        <v>474</v>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s" title="Wikipedia"&gt;TÉLÉCLÈS&lt;/a&gt; (mort vers 167 av. J.-C.) est un philosophe grec, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de Lacydès de Cyrène, il reçoit de lui, avec son condisciple Évandre, la direction de l’école du vivant même de leur maître, que la maladie empêchait d’enseigner. Les deux philosophes la dirigent ensemble, une organisation collégiale rare dans l’histoire de l’Académie.&lt;/p&gt; &lt;p&gt;Nous ne savons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu. Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par Arcésilas, qui avait donné à l’école de Platon une orientation sceptique en s’inspirant du Socrate qui affirmait ne rien savoir. Les académiciens de cette époque s’opposent avant tout aux stoïciens. Ceux-ci soutiennent qu’il existe des représentations « compréhensives », si claires et si distinctes qu’elles garantissent leur propre vérité et fondent la science. Les académiciens répondent qu’aucune perception ne peut être distinguée avec certitude d’une perception trompeuse : un rêve, une illusion d’optique ou deux jumeaux suffisent à le montrer. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;), mais il peut agir en suivant ce qui lui paraît raisonnable ou vraisemblable. L’enseignement se fait par la discussion : on argumente pour et contre chaque thèse, afin d’exercer l’esprit critique.&lt;/p&gt; &lt;p&gt;Après Téléclès et Évandre, la direction passe à Hégésinous de Pergame, puis à &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" style="color:#6A142A" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, qui donnera à l’Académie un éclat nouveau et portera le scepticisme jusqu’à Rome.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F58" s="7" t="s">
         <v>475</v>
@@ -5898,8 +5916,10 @@
       <c r="D59" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="E59" s="12" t="s">
-        <v>482</v>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes"  title=" Wikipedia"&gt;PANÉTIUS DE RHODES&lt;/a&gt; (vers 185-109 av. J.-C.) est un philosophe stoïcien grec, qui a adapté le stoïcisme au monde romain. Issu d’une grande famille de Rhodes, il étudie à Athènes auprès de Diogène de Babylone, puis s’installe à Rome, où il devient l’ami et le conseiller de Scipion Émilien, le vainqueur de Carthage. Il prend ensuite la tête de l’école stoïcienne d’Athènes, de 129 à sa mort.&lt;/p&gt; &lt;p&gt;Panétius assouplit la &lt;a href="https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie"  title="Le Stoïcisme par apprendre la philo"&gt;pensée stoïcienne&lt;/a&gt; et la rapproche de Platon et d’Aristote, qu’il admire. Il abandonne plusieurs thèses de ses prédécesseurs : il doute de la divination, nie la conflagration universelle qui devait périodiquement détruire le monde, qu’il juge éternel, et refuse l’immortalité de l’âme. Surtout, il s’intéresse moins au sage idéal, presque introuvable, qu’à l’homme ordinaire qui progresse vers la sagesse. Sa morale part de la nature humaine : chacun porte en lui des tendances fondamentales où s’unissent la nature et la raison, la recherche de la vérité, le goût de l’ordre, le désir de grandeur d’âme et le sens de la communauté. Chacun doit aussi tenir compte de sa propre nature, de ses talents et de sa situation, comme un acteur choisit le rôle qui lui convient. Il en tire une éthique des « devoirs », les actions convenables de la vie quotidienne et de la vie publique, fondée sur la justice, la bienveillance et le sens de la mesure.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Du devoir&lt;/em&gt; est perdu, mais Cicéron l’a largement repris dans son &lt;em&gt;De officiis&lt;/em&gt;, l’un des livres de morale les plus lus en Europe jusqu’au XIXe siècle. Panétius a ainsi donné au stoïcisme le visage humaniste qu’adopteront les élites romaines.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F59" s="7" t="s">
         <v>483</v>
@@ -5986,8 +6006,10 @@
       <c r="D61" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="E61" s="9" t="s">
-        <v>498</v>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philod%C3%A8me_de_Gadara" title="Wikipedia"&gt;PHILODÈME de Gadara&lt;/a&gt; était un philosophe et poète épicurien, originaire de Gadara en Syrie (l'actuelle Jordanie). Élève de Zénon de Sidon à Athènes, il s'installa en Campanie sous la protection du mécène romain Lucius Calpurnius Pison, proche de César, et anima un cercle intellectuel brillant qui accueillit le jeune Virgile et ses amis poètes.&lt;/p&gt; &lt;p&gt;Il défendit et enrichit la philosophie d'&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure" title="Épicure sur Wikipedia"&gt;Épicure&lt;/a&gt; en l'appliquant à des domaines nouveaux : la rhétorique, la musique, l'esthétique et la critique littéraire. Ses traités, longtemps perdus, ont été miraculeusement retrouvés dans la &lt;em&gt;Villa des Papyrus&lt;/em&gt; d'Herculanum, ensevelie par l'éruption du Vésuve en 79 apr. J.-C. Ces rouleaux carbonisés, partiellement déchiffrés grâce aux techniques modernes, constituent une source irremplaçable sur l'épicurisme tardif.&lt;/p&gt; &lt;p&gt;Philodème concilia la rigueur philosophique épicurienne — recherche de l'&lt;em&gt;ataraxie&lt;/em&gt; et du plaisir vertueux — avec une sensibilité poétique et artistique raffinée. Il représente l'épicurisme dans sa version la plus ouverte au monde des arts et de la culture romaine. Ses traités abordent aussi la morale : la colère, la mort, qu’il ne faut pas craindre, ou la « franchise » avec laquelle le maître corrige ses disciples. Poète, il a laissé une trentaine d’épigrammes, souvent amoureuses, conservées dans l’&lt;em&gt;Anthologie grecque&lt;/em&gt;. Les quelque 1 800 rouleaux de la villa, découverts à partir de 1752, sont aujourd’hui déchiffrés grâce à l’imagerie scientifique et à l’intelligence artificielle, sans qu’on ait besoin de les dérouler.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
@@ -6081,8 +6103,10 @@
       <c r="D63" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="E63" s="9" t="s">
-        <v>517</v>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lucr%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;LUCRÈCE&lt;/a&gt; (vers 98-55 av. J.-C.) est un poète et philosophe romain, disciple d’Épicure, auteur d’un seul livre, l’un des chefs-d’œuvre de la littérature latine : &lt;em&gt;De la nature des choses&lt;/em&gt; (&lt;em&gt;De rerum natura&lt;/em&gt;). Nous ne savons presque rien de sa vie. La légende, rapportée par saint Jérôme, selon laquelle il serait devenu fou après avoir bu un philtre d’amour et se serait suicidé, a sans doute été inventée par ses adversaires.&lt;/p&gt; &lt;p&gt;Son poème, en six livres et près de 7 400 vers, expose la doctrine de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picurisme"  style="color:#88A1E9"  title="Epicurisme par Wikipedia"&gt;épicurisme&lt;/a&gt; pour délivrer les hommes de la peur. Rien ne naît de rien, rien ne retourne au néant : tout ce qui existe est fait d’atomes, invisibles et éternels, qui se meuvent dans le vide. En tombant, ils s’écartent parfois légèrement de leur trajectoire : ce &lt;a href="https://www.youtube.com/watch?v=7iQzfXtB4wc&amp;ab_channel=Coursitout"  style="color:#88A1E9"  title="Le clinamen par Coursitout"&gt;&lt;em&gt;clinamen&lt;/em&gt;&lt;/a&gt; explique la rencontre des atomes, la formation des mondes et la liberté humaine. L’âme elle-même est faite d’atomes très fins &lt;a href="https://www.youtube.com/watch?v=VKJsOwjD5P4&amp;ab_channel=librairiemollat"  style="color:#88A1E9"  title="Bernard Combeaud - Lucrèce, la naissance des choses"&gt;et se disperse&lt;/a&gt; à la mort. Il n’y a donc rien à craindre après la mort : « la mort n’est rien pour nous ». Les dieux existent, mais ne s’occupent pas des hommes. Lucrèce dénonce avec force la superstition, qui pousse au crime, comme le sacrifice d’Iphigénie par son propre père : « Tant la religion a pu inspirer de maux ! » Il décrit aussi la naissance de la vie et des sociétés humaines, du langage et des arts, et finit son poème par la terrible peste d’Athènes. Le bonheur est la paix de l’âme, que procurent des plaisirs simples et l’amitié.&lt;/p&gt; &lt;p&gt;Retrouvé en 1417 par l’humaniste Pogge, le poème a marqué Montaigne, Gassendi, les libertins et les Lumières.&lt;/p&gt;  &lt;audio controls title="Comment maîtriser ses passions ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-12.09.2016-ITEMA_21073425-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F63" s="7" t="s">
         <v>518</v>
@@ -6280,8 +6304,10 @@
       <c r="D67" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="E67" s="12" t="s">
-        <v>552</v>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes" style="color:#6A142A" title="Wikipedia"&gt;AMMONIOS d’Athènes&lt;/a&gt; est un philosophe platonicien du Ier siècle, originaire d’Égypte, qui enseigna à Athènes et fut le maître de &lt;a href="https://fr.wikipedia.org/wiki/Plutarque" style="color:#6A142A" title="Plutarque sur Wikipedia"&gt;Plutarque&lt;/a&gt;. Celui-ci suivit ses leçons vers 66-67, à l’époque où l’empereur Néron visitait la Grèce. Ammonios était aussi un citoyen influent d’Athènes, où des inscriptions montrent qu’il exerça plusieurs fois la haute fonction de stratège.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit, et nous le connaissons presque uniquement par Plutarque, qui le met en scène dans plusieurs de ses dialogues comme un maître sage et bienveillant. Dans le traité &lt;em&gt;Sur l’E de Delphes&lt;/em&gt;, Plutarque et ses amis s’interrogent sur la lettre E gravée à l’entrée du temple d’Apollon. Ammonios conclut la discussion en y voyant le mot grec &lt;em&gt;ei&lt;/em&gt;, « tu es » : c’est la salutation que l’homme adresse au dieu. Seul le dieu « est » véritablement, éternel, un et immuable, alors que nous, soumis au temps et au changement, ne faisons que devenir et disparaître. Le précepte « Connais-toi toi-même », inscrit au même endroit, répond à ce salut en rappelant à l’homme sa faiblesse. Cette opposition entre l’être divin et le devenir humain est au cœur du platonisme de l’époque. Ammonios s’intéressait aussi aux mathématiques et à la science de la nature, et il voulait unir la philosophie à une piété religieuse fidèle aux traditions grecques.&lt;/p&gt; &lt;p&gt;Il appartient au « moyen platonisme », qui prépare, entre Platon et Plotin, le &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt;. Il ne faut pas le confondre avec Ammonios Saccas, maître de Plotin, ni avec Ammonios d’Alexandrie.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F67" s="7" t="s">
         <v>553</v>
@@ -6561,7 +6587,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas"  title="Wikipedia"&gt;Ammonios SACCAS&lt;/a&gt; était un philosophe grec dont on connaît mal sa vie car il n’a laissé aucun écrit direct. Son surnom “Saccas” est souvent expliqué comme un surnom lié à une origine modeste ou à un métier manuel, même si l’étymologie exacte reste discutée, &lt;/p&gt;&lt;p&gt; On le considère souvent comme le fondateur de l’école néoplatonicienne de Rome, surtout parce qu’il a formé Plotin, qui a ensuite systématisé cette philosophie. Les sources anciennes lui attribuent aussi l’idée que Platon et Aristote convergent sur l’essentiel, ce qui en fait une figure de réconciliation philosophique. &lt;/p&gt; &lt;p&gt; Comme il n’a rien écrit, sa doctrine est reconstruite à partir de témoignages, surtout ceux de Plotin et d’auteurs tardifs. On lui associe une philosophie centrée sur l’unité du réel, la purification de l’âme, et une vie tournée vers la contemplation intellectuelle.&lt;/p&gt; &lt;p&gt;  Il  est souvent qualifié de  &lt;a href="https://www.youtube.com/watch?v=hSIeYrZa-X4"title=" Ammonios SACCAS maitre de Plotin  par Vox Temporis"&gt;“maître silencieux”&lt;/a&gt;parce que sa pensée est très influente, mais presque entièrement indirecte. Il se situe à la charnière entre le platonisme tardif et le néoplatonisme de Plotin.&lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas"  title="Wikipedia"&gt;Ammonios SACCAS&lt;/a&gt; (vers 175-242) est un philosophe platonicien d’Alexandrie, maître de Plotin et l’un des inspirateurs du néoplatonisme. Son surnom de Saccas, le « porteur de sacs », rappelle peut-être qu’il fut d’abord portefaix sur les quais du port. Selon le philosophe Porphyre, il serait né dans une famille chrétienne et aurait ensuite choisi la philosophie grecque, ce que contestent les auteurs chrétiens.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit, et sa doctrine nous échappe en grande partie. Nous savons surtout qu’il fut un maître exceptionnel. Porphyre raconte que Plotin, à vingt-huit ans, avait suivi sans satisfaction les cours des professeurs les plus réputés d’Alexandrie, jusqu’à ce qu’un ami le conduise chez Ammonios. En sortant, Plotin s’écria : « Voilà celui que je cherchais ! » Il resta onze ans auprès de lui. Ammonios eut aussi pour élèves le philosophe Origène, à ne pas confondre avec le théologien chrétien du même nom, Érennius et peut-être le critique Longin. Ses disciples s’engagèrent à ne pas divulguer son enseignement, promesse que Plotin ne rompit qu’après les autres. Des auteurs plus tardifs lui attribuent l’idée que Platon et Aristote s’accordent sur l’essentiel, et une réflexion sur l’union de l’âme et du corps : l’âme, réalité spirituelle, s’unit au corps sans se mélanger à lui ni se corrompre. On le surnommait « l’instruit par Dieu ».&lt;/p&gt; &lt;p&gt;On l’appelle souvent le &lt;a href="https://www.youtube.com/watch?v=hSIeYrZa-X4"title=" Ammonios SACCAS maitre de Plotin  par Vox Temporis"&gt;« maître silencieux »&lt;/a&gt; : sans laisser une ligne, il a marqué, à travers Plotin, toute la tradition néoplatonicienne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F73" s="7" t="s">
@@ -6839,7 +6865,7 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9mistios"  style="color:#6A142A"  title=" Wikipedia"&gt;THÉMISTIOS&lt;/a&gt; était un philosophe, homme politique  romain connu pour ses talents d'orateur et ses contributions à la philosophie néoplatonicienne, ainsi que pour &lt;a href="https://www.youtube.com/watch?v=JdIUtCSF-JA" style="color:#88A1E9" title="«L’œuvre de Thémistios et son importance pour l’histoire de la philosophie» par Histoire de la mémoire et des idées"&gt;son rôle &lt;/a&gt; dans la vie politique et culturelle de son époque. Il  a vécu pendant une période de transition importante dans l'Empire romain, marquée par la montée du christianisme et le déclin progressif du paganisme. &lt;/p&gt; &lt;p&gt; Ses &lt;a href="https://www.persee.fr/doc/topoi_1764-0733_2006_mel_7_1_2980" style="color:#88A1E9" title="Thémistios et ses adversaires : le témoignage du discours  par Persée"&gt;écrits &lt;/a&gt; reflètent une profonde connaissance de la philosophie grecque, en particulier ses "&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_12_5759" style="color:#88A1E9" title=" d'Aristote par Themistius par Persée"&gt;paraphrases des traités d'Aristote &lt;/a&gt;", qui visaient à rendre la pensée du philosophe plus accessible à ses contemporains. Il croyait en l'harmonie entre la raison et la révélation, et soutenait que la philosophie pouvait coexister avec la religion. Cette position lui a permis de maintenir un dialogue avec les chrétiens tout en restant fidèle à ses racines païennes.&lt;/p&gt; &lt;p&gt;  Son travail et son influence reflète les tensions et les transformations de son époque, tout en témoignant d'une quête constante de sagesse et de conciliation entre les différentes traditions philosophiques et religieuses. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9mistios"  style="color:#6A142A"  title=" Wikipedia"&gt;THÉMISTIOS&lt;/a&gt; (vers 317-388) est un philosophe, orateur et homme politique grec de l’Empire romain d’Orient. Fils d’un philosophe de Paphlagonie, il enseigne à Constantinople, la nouvelle capitale, et y devient sénateur en 355. Bien que resté païen, il sert successivement six empereurs, presque tous chrétiens, de Constance II à Théodose, qui le nomme préfet de la ville et lui confie l’éducation de son fils.&lt;/p&gt; &lt;p&gt;Il est d’abord connu pour ses &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_12_5759" style="color:#88A1E9" title=" d'Aristote par Themistius par Persée"&gt;paraphrases d’Aristote&lt;/a&gt;, des résumés commentés qui reformulent avec clarté les traités du philosophe : les &lt;em&gt;Seconds Analytiques&lt;/em&gt;, la &lt;em&gt;Physique&lt;/em&gt;, le traité &lt;em&gt;De l’âme&lt;/em&gt; et une partie de la &lt;em&gt;Métaphysique&lt;/em&gt;. Traduites en arabe, en hébreu puis en latin, elles ont été lues par Averroès et Thomas d’Aquin, en particulier pour la question de l’intellect. Thémistios est aussi un grand orateur. Dans ses &lt;a href="https://www.persee.fr/doc/topoi_1764-0733_2006_mel_7_1_2980" style="color:#88A1E9" title="Thémistios et ses adversaires : le témoignage du discours  par Persée"&gt;discours&lt;/a&gt;, adressés aux empereurs ou au Sénat, il défend une idée haute du rôle du philosophe : il ne doit pas fuir la cité, mais conseiller le pouvoir et rappeler au prince qu’il doit être une « loi vivante », juste et humain. Dans un discours célèbre adressé à l’empereur Jovien, en 364, il plaide pour la tolérance religieuse : Dieu, dit-il, se réjouit de la diversité des cultes, comme le chef d’une armée de la diversité de ses troupes, et nul ne doit être contraint dans sa foi.&lt;/p&gt; &lt;p&gt;Païen respecté des chrétiens, il illustre &lt;a href="https://www.youtube.com/watch?v=JdIUtCSF-JA" style="color:#88A1E9" title="«L’œuvre de Thémistios et son importance pour l’histoire de la philosophie» par Histoire de la mémoire et des idées"&gt;son rôle&lt;/a&gt; de médiateur entre la culture grecque et le nouvel Empire chrétien.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F79" s="7" t="s">
@@ -7264,8 +7290,10 @@
       <c r="D88" s="8" t="s">
         <v>724</v>
       </c>
-      <c r="E88" s="9" t="s">
-        <v>725</v>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aid%C3%A9sia_(philosophe)" style="color:#6A142A" title="Wikipedia"&gt;AIDÉSIA&lt;/a&gt; (Ve siècle) est une philosophe néoplatonicienne d’Alexandrie, l’une des rares femmes philosophes de l’Antiquité tardive dont le souvenir nous soit parvenu. Parente du philosophe Syrianus, qui dirigeait l’école platonicienne d’Athènes, elle aurait dû épouser Proclus, son disciple, mais celui-ci, averti par un songe, renonça au mariage. Syrianus la donna alors pour épouse à un autre de ses élèves, &lt;a href="https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie" style="color:#6A142A" title="Hermias d'Alexandrie sur Wikipedia"&gt;Hermias d’Alexandrie&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Nous la connaissons par Damascius, le dernier chef de l’école d’Athènes, qui en parle dans sa &lt;em&gt;Vie d’Isidore&lt;/em&gt;. Il la décrit comme la plus belle et la plus vertueuse des femmes de son temps, connue pour sa piété envers les dieux et sa générosité envers les pauvres, au point de distribuer presque tous ses biens. Après la mort prématurée d’Hermias, elle se consacre à l’éducation de leurs deux fils, Ammonios et Héliodore. Elle les accompagne à Athènes pour qu’ils y suivent l’enseignement de Proclus, qui les accueille avec affection en souvenir de son maître. Ammonios deviendra le grand maître de l’école d’Alexandrie, où il formera à son tour de nombreux commentateurs d’Aristote, comme Jean Philopon. Aidésia vit jusqu’à un âge avancé, respectée de tous. À sa mort, le jeune Damascius, alors étudiant à Alexandrie, compose et prononce son éloge funèbre, en vers.&lt;/p&gt; &lt;p&gt;Sa vie témoigne du rôle des femmes dans les familles de philosophes néoplatoniciens, véritables dynasties intellectuelles, à l’image d’&lt;a href="https://fr.wikipedia.org/wiki/Hypatie"   title=" Wikipedia"&gt;HYPATIE d’Alexandrie&lt;/a&gt;, victime des violences religieuses en 415.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F88" s="7" t="s">
         <v>726</v>
@@ -7313,8 +7341,10 @@
       <c r="D89" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="E89" s="9" t="s">
-        <v>733</v>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marinos_de_N%C3%A9apolis" style="color:#6A142A" title="Wikipedia"&gt;MARINOS de Néapolis&lt;/a&gt; (Ve siècle) est un philosophe néoplatonicien, disciple et successeur de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" style="color:#6A142A" title="Proclus sur Wikipedia"&gt;Proclus&lt;/a&gt; à la tête de l’école platonicienne d’Athènes. Né à Néapolis, l’actuelle Naplouse, en Palestine, dans une famille samaritaine, il abandonne la religion de ses pères pour les cultes grecs et vient étudier à Athènes. Proclus le choisit pour lui succéder, et il dirige l’école après la mort de son maître, en 485.&lt;/p&gt; &lt;p&gt;Il est surtout connu pour sa &lt;em&gt;Vie de Proclus&lt;/em&gt;, aussi intitulée &lt;em&gt;Sur le bonheur&lt;/em&gt;, écrite un an après la mort de celui-ci. Plus qu’une simple biographie, c’est un éloge construit selon l’échelle des vertus des néoplatoniciens : vertus naturelles, morales, politiques, purificatrices, contemplatives, et enfin théurgiques, qui unissent l’âme aux dieux. Marinos y montre comment Proclus les a toutes possédées, et livre de précieux détails sur la vie de l’école : l’emploi du temps du maître, qui enseignait, écrivait et priait chaque jour, son régime végétarien, ses jeûnes, ses rites et ses prières au soleil. Marinos a aussi écrit un commentaire des &lt;em&gt;Données&lt;/em&gt; d’Euclide, qui témoigne de son goût pour les mathématiques. Dans l’interprétation du &lt;em&gt;Parménide&lt;/em&gt; de Platon, il s’écarte de son maître : il y voit un dialogue sur les Idées plutôt que sur les dieux, ce que Damascius lui reprochera.&lt;/p&gt; &lt;p&gt;De santé fragile, il confie peu à peu l’enseignement à d’autres. Après lui, l’école passe à Isidore de Gaza, puis à Hégias, avant que &lt;a href="https://fr.wikipedia.org/wiki/Damascios" style="color:#6A142A" title="Damascios sur Wikipedia"&gt;Damascios&lt;/a&gt;, qui avait été son élève, n’en prenne la tête jusqu’à sa fermeture par Justinien en 529.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F89" s="7" t="s">
         <v>734</v>
@@ -7401,8 +7431,10 @@
       <c r="D91" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="E91" s="12" t="s">
-        <v>749</v>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isidore_de_Gaza" title="Wikipedia"&gt;ISIDORE de Gaza&lt;/a&gt; (Ve-VIe siècle) est un philosophe néoplatonicien, l’un des derniers représentants du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme"  title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; païen. Né à Gaza, il étudie à Alexandrie, puis à Athènes auprès de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" title="Proclus sur Wikipedia"&gt;Proclus&lt;/a&gt;, qui dirige l’école platonicienne. Il est le maître et l’ami de &lt;a href="https://fr.wikipedia.org/wiki/Damascios" title="Damascios sur Wikipedia"&gt;Damascius&lt;/a&gt;, le dernier chef de cette école.&lt;/p&gt; &lt;p&gt;Nous le connaissons surtout par la biographie que Damascius lui a consacrée, la &lt;em&gt;Vie d’Isidore&lt;/em&gt;, dont il reste d’importants fragments. Il y apparaît comme un homme profondément religieux, attaché aux cultes et aux traditions des Grecs à une époque où le christianisme est devenu la religion de l’Empire et où les païens sont de plus en plus surveillés. Isidore se méfie des longs commentaires savants et des raisonnements trop subtils : pour lui, la philosophie est avant tout une manière de vivre, une purification de l’âme qui la conduit vers le divin. Il préfère l’inspiration et l’expérience intérieure à l’érudition, et Damascius admire en lui moins le savant que le sage. Après la mort de Proclus, il voyage beaucoup, en Syrie et en Égypte, en compagnie de Damascius. Il accepte un temps de diriger l’école d’Athènes, à la suite de Marinus, mais y renonce bientôt, jugeant le climat défavorable à la philosophie. La &lt;em&gt;Vie d’Isidore&lt;/em&gt; est aussi une précieuse galerie de portraits des philosophes de son temps, comme Hypatie, Aidésia ou Hermias.&lt;/p&gt; &lt;p&gt;Peu après, en 529, l’empereur Justinien interdit aux païens d’enseigner : l’école d’Athènes ferme, et Damascius part avec quelques compagnons en Perse.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F91" s="18" t="s">
         <v>750</v>
@@ -7636,8 +7668,10 @@
       <c r="D96" s="8" t="s">
         <v>786</v>
       </c>
-      <c r="E96" s="9" t="s">
-        <v>787</v>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cassiodore"  style="color:#6A142A"  title=" Wikipedia"&gt;CASSIODORE&lt;/a&gt; (vers 485-580) est un homme d’État, écrivain et savant romain, l’un des grands passeurs de la culture antique au Moyen Âge. Issu d’une famille de hauts fonctionnaires du sud de l’Italie, il fait carrière au service des rois ostrogoths qui gouvernent alors l’Italie, en particulier Théodoric le Grand : il devient consul, puis préfet du prétoire. Ses lettres officielles, réunies dans les &lt;em&gt;Variae&lt;/em&gt; en douze livres, sont une source précieuse sur l’époque.&lt;/p&gt; &lt;p&gt;Il veut concilier les Romains et les Goths, et écrit à cette fin une &lt;em&gt;Histoire des Goths&lt;/em&gt;, aujourd’hui perdue. Après la reconquête de l’Italie par l’empereur Justinien et la ruine de son projet politique, il se retire vers 554 sur ses terres de Calabre, où il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Monast%C3%A8re_de_Vivarium"  style="color:#88A1E9"  title="le monastère de Vivarium par Wikipédia"&gt;monastère de Vivarium&lt;/a&gt;, ainsi nommé à cause de ses viviers à poissons. Il y rassemble une riche bibliothèque et demande aux moines de copier avec soin les manuscrits, chrétiens mais aussi païens, en les corrigeant et en les reliant : le travail du copiste devient une œuvre spirituelle. Pour les guider, il écrit les &lt;a href="https://www.persee.fr/doc/rht_0373-6075_1991_num_21_1991_1362"  style="color:#88A1E9"  title="les Institutions par Persée.fr"&gt;&lt;em&gt;Institutions&lt;/em&gt;&lt;/a&gt;, en deux livres : le premier présente l’étude de la Bible et des Pères de l’Église ; le second résume les sept arts libéraux, la grammaire, la rhétorique, la dialectique, l’arithmétique, la musique, la géométrie et l’astronomie, nécessaires pour bien lire l’Écriture. Il compose aussi un traité &lt;em&gt;De l’âme&lt;/em&gt; et un grand commentaire des Psaumes.&lt;/p&gt; &lt;p&gt;Grâce à lui, le modèle du monastère gardien des livres s’impose en Occident. Les &lt;em&gt;Institutions&lt;/em&gt; serviront de programme d’études pendant tout le Moyen Âge.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F96" s="7" t="s">
         <v>788</v>
@@ -7814,8 +7848,10 @@
       <c r="D100" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="E100" s="12" t="s">
-        <v>818</v>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie" style="color:#6A142A" title="Wikipedia"&gt;EULAMIOS de Phrygie&lt;/a&gt; est un philosophe néoplatonicien du VIe siècle, originaire de Phrygie, en Asie Mineure. Il appartient au dernier cercle des philosophes païens de l’école d’Athènes, réunis autour de Damascius, à l’époque où le christianisme est devenu la religion officielle de l’Empire et où les païens sont de plus en plus écartés de la vie publique.&lt;/p&gt; &lt;p&gt;Comme pour la plupart de ses compagnons, nous ne savons presque rien de sa vie, et aucune de ses œuvres ne nous est parvenue. Son nom nous est connu par l’historien byzantin Agathias, qui raconte l’un des épisodes les plus célèbres de la fin de l’Antiquité. En 529, l’empereur Justinien interdit aux païens d’enseigner. L’école d’Athènes, héritière de l’Académie de Platon, ne peut plus fonctionner. Vers 531, sept philosophes quittent alors l’Empire : Damascius, Simplicius de Cilicie, Priscien de Lydie, Hermias et Diogène de Phénicie, Isidore de Gaza et Eulamios. Ils se rendent à la cour du roi de Perse Khosro Ier, qui passait pour un ami de la sagesse grecque et faisait traduire Platon et Aristote. Mais la Perse les déçoit, et ils souhaitent rentrer. En 532, le traité de paix signé entre Khosro et Justinien prévoit qu’ils pourront revenir dans l’Empire et y vivre sans être obligés de renoncer à leurs croyances. Simplicius écrira ensuite ses grands commentaires d’Aristote, qui sont parmi les plus précieux de l’Antiquité.&lt;/p&gt; &lt;p&gt;Ces derniers maîtres du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; ont transmis la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_antique" style="color:#6A142A" title="Philosophie antique sur Wikipedia"&gt;philosophie antique&lt;/a&gt; aux savants byzantins, syriaques et arabes, et, par eux, au Moyen Âge.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F100" s="7" t="s">
         <v>819</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3437,11 +3437,11 @@
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anaximandre" style="color:#88A1E9"   title="Anaximandre par Wikipédia"&gt; ANAXIMANDRE DE MILET&lt;/a&gt; était un philosophe présocratique de l'école Ionienne et  un contemporain de Thalès, et il est souvent considéré comme l'un des premiers penseurs à développer des idées philosophiques systématiques sur la nature du monde.&lt;/p&gt;&lt;p&gt;
-L'une de ses contributions les plus importantes était sa tentative de fournir une explication naturelle et non mythologique de &lt;a href="https://www.youtube.com/watch?v=5x7J2u5LSh4&amp;t=2s&amp;ab_channel=Coursitout" style="color:#88A1E9"   title="L'origine de l'Univers selon Anaximandre par Coursitout"&gt; l'origine et de la structure de l'univers.&lt;/a&gt;. Il est souvent crédité d'avoir élaboré la première carte géographique du monde connu à l'époque. 
+L'une de ses contributions les plus importantes était sa tentative de fournir une explication naturelle et non mythologique de &lt;a href="https://www.youtube.com/watch?v=5x7J2u5LSh4&amp;t=2s&amp;ab_channel=Coursitout" style="color:#88A1E9"   title="L'origine de l'Univers selon Anaximandre par Coursitout"&gt; l'origine et de la structure de l'univers&lt;/a&gt;. Il est souvent crédité d'avoir élaboré la première carte géographique du monde connu à l'époque. 
 &lt;/p&gt;&lt;p&gt;
 Il est aussi connu pour sa théorie de  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1957_num_70_329_3473" style="color:#88A1E9"   title="Sur la signification de l'apeiron d'Anaximandre par Persée"&gt; "l'apeiron"&lt;/a&gt;, également traduit par le terme "infini" ou "illimité". Selon lui, l'apeiron est l'élément primordial à partir duquel tout provient et dans lequel tout finit. C'est une substance indéfinie et indéterminée, ni de l'eau ni de l'air, qui est à l'origine du cosmos. Il pensait que tous les éléments et les objets de l'univers étaient issus de l'apeiron par des processus de séparation et de condensation.
 &lt;/p&gt;&lt;p&gt;
-Il pensait que la Terre était suspendue dans l'espace, sans soutien visible, et que les étoiles étaient des trous à travers lesquels la lumière du feu intérieur du cosmos brillait. Ces idées ont été radicales pour l'époque et ont contribué à poser les bases de la pensée philosophique et scientifique future.
+Il pensait que la Terre était suspendue dans l'espace, sans soutien visible, et que les étoiles étaient des trous à travers lesquels la lumière du feu intérieur du cosmos brillait. Ces idées ont été radicales pour l'époque et ont contribué à poser les bases de la pensée philosophique et scientifique future. Élève et successeur de Thalès à Milet, il écrit sans doute le premier livre de philosophie en prose. Il en reste une phrase, la plus ancienne de la philosophie grecque : les choses « se rendent justice et réparation de leur injustice, selon l’ordre du temps ». Il pense aussi que les premiers êtres vivants sont nés dans l’eau.
 &lt;/p&gt; &lt;audio controls title="Anaximandre, Héraclite et les autres : au commencement était le feu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-13.09.2021-ITEMA_22772439-2021C12410S0256-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
         </is>
       </c>
@@ -4118,8 +4118,12 @@
       <c r="D20" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>154</v>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/M%C3%A9lissos"  style="color:#6A142A"  title=" Wikipedia"&gt;MÉLISSOS&lt;/a&gt; de Samos (Ve siècle av. J.-C.) est un philosophe grec, le dernier grand représentant de l’école éléatique, &lt;a href="https://www.youtube.com/watch?v=zSetMtIYrCE" style="color:#88A1E9" title=" 
+Melissos and Zenon : Paradoxes of Movement and Being par Discovery"&gt;avec Parménide et Zénon&lt;/a&gt;. Il est aussi un homme d’action : amiral de la flotte de Samos, il remporte en 441 av. J.-C. une victoire navale sur les Athéniens, lors de la révolte de l’île contre Athènes, selon le récit de Plutarque.&lt;/p&gt; &lt;p&gt;De son traité &lt;em&gt;Sur la nature ou sur l’être&lt;/em&gt;, il reste une dizaine de fragments, conservés par le commentateur Simplicius. Mélissos reprend la thèse de Parménide : l’être est, le non-être n’est pas, et rien ne peut naître du néant ni y retourner. L’être est donc éternel, un, immobile et sans changement. Mais il s’écarte de son maître sur un point important. Parménide comparait l’être à une sphère, donc à quelque chose de limité. Mélissos soutient au contraire que l’être est &lt;a href="https://www.youtube.com/shorts/NKQQ7MKH0lM" style="color:#88A1E9" title=" 
+Melissos par Tielessphilo"&gt;infini&lt;/a&gt;, non seulement dans le temps, puisqu’il n’a ni commencement ni fin, mais aussi dans l’espace : s’il avait une limite, il serait limité par autre chose, c’est-à-dire par du vide, et le vide n’est rien. Pour la même raison, le mouvement est impossible, car une chose ne peut se déplacer que dans un espace vide. Il en conclut que les sens nous trompent : nous voyons les choses naître, changer et mourir, mais si elles existaient vraiment, elles devraient être éternelles et immuables comme l’être un. Le monde multiple de l’expérience n’est qu’une apparence.&lt;/p&gt; &lt;p&gt;Aristote juge sa pensée grossière, mais ses arguments, très clairs, ont obligé les atomistes, comme Leucippe et Démocrite, à admettre l’existence du vide pour sauver le mouvement.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F20" s="7" t="s">
         <v>155</v>
@@ -5091,8 +5095,10 @@
       <c r="D41" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="E41" s="9" t="s">
-        <v>330</v>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diodore_Cronos"  style="color:#6A142A"  title=" Wikipedia"&gt;Diodore CRONOS&lt;/a&gt; (mort vers 284 av. J.-C.) est un philosophe grec de l’école mégarique, l’un des plus grands logiciens de l’Antiquité. Né à Iasos, en Carie, il enseigne à Athènes et à Alexandrie. Il eut pour élève Zénon de Kition, le fondateur du stoïcisme, ainsi que ses cinq filles, toutes réputées pour leur talent en dialectique. Son surnom de « Cronos », du nom du vieux dieu, se moquait peut-être de lui comme d’un esprit démodé.&lt;/p&gt; &lt;p&gt;Il est surtout célèbre pour l’« argument dominateur », &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1961_num_74_349_3654_t1_0317_0000_2"  style="color:#88A1E9" title=" Le dominateur et les possibles par Persée"&gt;le Dominateur&lt;/a&gt;, que les Anciens jugeaient le plus redoutable des raisonnements. Il part de trois affirmations qui ne peuvent être vraies ensemble : tout ce qui est passé et vrai est nécessaire, car le passé ne peut plus changer ; l’impossible ne peut pas découler du possible ; et il existe un possible qui n’est pas et ne sera jamais vrai. Diodore rejette la troisième. Il en conclut que le possible est ce qui est ou qui sera, et que ce qui n’arrivera jamais n’était pas possible. Cette thèse semble mener au fatalisme, et les stoïciens, comme Chrysippe, ont cherché à y échapper. Diodore propose aussi une définition de l’implication : « si A, alors B » est vrai lorsqu’il n’a jamais été et ne sera jamais le cas que A soit vrai et B faux. Il défend enfin des arguments contre le mouvement : on ne peut jamais dire d’une chose « elle se meut », seulement « elle s’est mue ». La légende raconte qu’il mourut de dépit pour n’avoir pas su résoudre sur-le-champ une énigme posée par Stilpon devant le roi Ptolémée.&lt;/p&gt; &lt;p&gt;Au XXe siècle, le logicien Arthur Prior s’est inspiré de Diodore pour créer la logique du temps.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F41" s="7" t="s">
         <v>331</v>
@@ -6770,8 +6776,11 @@
       <c r="D77" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="E77" s="9" t="s">
-        <v>632</v>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jamblique" style="color:#6A142A" title="Wikipedia"&gt;JAMBLIQUE de Chalcis&lt;/a&gt; est l'un des penseurs les plus influents du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt;, figure centrale de l'école syrienne. Né à Chalcis en Syrie (l'actuelle Qinnasrin), il fut d'abord l'élève de Porphyre à Rome avant de fonder sa propre école en Syrie, à Apamée, devenant le maître d'une génération de néoplatoniciens.&lt;/p&gt; &lt;p&gt;Jamblique transforma profondément le néoplatonisme en y intégrant la &lt;em&gt;théurgie&lt;/em&gt; — la pratique rituelle permettant l'union avec le divin — comme voie indispensable au côté de la philosophie pure. Dans son œuvre maîtresse, &lt;em&gt;Les Mystères d'Égypte&lt;/em&gt; (&lt;em&gt;De Mysteriis&lt;/em&gt;), il répondit aux critiques de Porphyre en affirmant que la contemplation intellectuelle seule ne suffit pas : les rites sacrés sont nécessaires pour élever l'âme jusqu'au divin. Il développa aussi une hiérarchie complexe des êtres divins.&lt;/p&gt; &lt;p&gt;Jamblique enrichit le système de Plotin par une multiplication des hypostases divines et une intégration systématique des traditions religieuses orientales et chaldéennes. Son influence sur les néoplatoniciens tardifs (Proclus, Damascios) et sur l'&lt;a href="https://fr.wikipedia.org/wiki/Hermétisme" style="color:#6A142A" title="Hermétisme sur Wikipedia"&gt;hermétisme&lt;/a&gt; renaissant fut considérable. L'empereur Julien le tenait pour un maître de sagesse comparable à Platon lui-même. Grand admirateur de Pythagore, il consacre à sa vie et à sa doctrine une série d’ouvrages, dont une &lt;em&gt;Vie de Pythagore&lt;/em&gt; et une &lt;em&gt;Exhortation à la philosophie&lt;/em&gt;. Contre Plotin, il soutient que l’âme humaine descend tout entière dans le corps : elle ne peut donc remonter seule vers le divin et a besoin de l’aide des dieux. Il fixe aussi l’ordre de lecture des dialogues de Platon, que suivront les écoles néoplatoniciennes.&lt;/p&gt;  &lt;audio controls title="Une histoire philosophique : Porphyre et Jamblique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16260-13.03.2021-ITEMA_22601996-2021C6260S0072.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F77" s="7" t="s">
         <v>633</v>
@@ -7387,8 +7396,10 @@
       <c r="D90" s="8" t="s">
         <v>740</v>
       </c>
-      <c r="E90" s="13" t="s">
-        <v>741</v>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)"  style="color:#6A142A"  title=" Wikipedia"&gt;AMMONIOS d’Alexandrie&lt;/a&gt; (vers 440-vers 520) est un philosophe néoplatonicien, le grand maître de l’école d’Alexandrie à la fin de l’Antiquité. Fils des philosophes Hermias et Aidésia, il est emmené jeune à Athènes par sa mère pour y suivre l’enseignement de Proclus, qui dirige l’école platonicienne. Revenu dans sa ville natale, il y enseigne pendant plusieurs décennies, à la tête de l’école d’Alexandrie, tandis que celle d’Athènes est dirigée par les successeurs de Proclus.&lt;/p&gt; &lt;p&gt;Ammonios est avant tout un commentateur d’Aristote. Il considère que la philosophie d’Aristote et celle de Platon s’accordent sur l’essentiel : l’étude d’Aristote, à commencer par sa logique, prépare à celle de Platon, qui conduit jusqu’à la connaissance du divin. Son commentaire du traité &lt;em&gt;De l’interprétation&lt;/em&gt;, qui examine les propositions, la vérité et le temps, nous est parvenu en entier ; on y trouve une discussion célèbre sur les futurs contingents : peut-on dire dès aujourd’hui qu’une bataille navale aura lieu demain, sans supprimer la liberté ? Ses autres leçons nous sont connues par les notes de ses élèves. Il forme en effet toute une génération de commentateurs : Jean Philopon, chrétien, Simplicius, Asclépius et Olympiodore. Dans une ville où les chrétiens sont désormais majoritaires et où les païens sont parfois persécutés, il aurait conclu un accord avec les autorités chrétiennes pour pouvoir continuer à enseigner, ce que lui reprocha Damascius.&lt;/p&gt; &lt;p&gt;L’école d’Alexandrie, en partie chrétienne après lui, a transmis le corpus d’Aristote et ses commentaires aux savants syriaques et arabes, puis à l’Occident médiéval.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F90" s="7" t="s">
         <v>742</v>
@@ -7528,10 +7539,7 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bo%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;Anicius Manlius BOÈCE&lt;/a&gt;, ou Boèce de Rome, était un philosophe, théologien et homme d'État Romain éduqué à Athènes et a été influencé par la philosophie grecque de Platon et d'Aristote.  &lt;/p&gt; &lt;p&gt; Il a vécu à une époque où l'Empire romain d'Occident était en déclin et où la culture classique était menacée par les invasions barbares et la montée du christianisme. 
-Il est connu pour son œuvre majeure, &lt;a  href="https://remacle.org/bloodwolf/philosophes/boece/livre3.htm#:~:text=J'entends%20par%20l%C3%A0%20ce,aurait%20encore%20mati%C3%A8re%20%C3%A0%20d%C3%A9sir." style="color:#88A1E9"  title="La consolation philosophique par Remacle"&gt;"La Consolation de la Philosophie"&lt;/a&gt;, qui a été écrite alors qu'il était en prison, en attente de son exécution pour des accusations de trahison envers le roi ostrogoth Théodoric le Grand.&lt;/p&gt; &lt;p&gt;  Dans cette œuvre, Boèce est consolé par la Philosophie personnifiée, qui lui enseigne que le véritable bonheur peut être trouvé dans &lt;a  href="https://www.youtube.com/watch?v=Bx-_WsSfylw&amp;t=1619s&amp;ab_channel=%C3%89CLAIRBRUT" style="color:#88A1E9"  title="Une âme dénuée du monde par Eclair Brut"&gt;la sagesse&lt;/a&gt; et la connaissance de Dieu, plutôt que dans la richesse et le pouvoir.&lt;/p&gt; &lt;p&gt;
-Il a également écrit sur des sujets tels que la musique, la logique et la théologie. Il a traduit plusieurs œuvres grecques en latin, y compris les œuvres d'Aristote et de Platon, ce qui a permis à la pensée grecque de survivre à la chute de l'Empire romain et de se transmettre à l'Europe médiévale.&lt;/p&gt; &lt;p&gt;
-Il a été exécuté en 524, mais son œuvre a continué d'être étudiée et appréciée tout au long du Moyen Âge et de la Renaissance. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bo%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;Anicius Manlius BOÈCE&lt;/a&gt; (vers 480-524) est un philosophe, théologien et homme d’État romain, souvent appelé « le dernier des Romains et le premier des scolastiques ». Issu de l’une des plus grandes familles de Rome, il vit sous le règne de Théodoric, roi des Ostrogoths, qui gouverne l’Italie : il devient consul en 510, puis maître des offices, la plus haute charge de la cour.&lt;/p&gt; &lt;p&gt;Chrétien et passionné de philosophie grecque, il conçoit un projet immense : traduire en latin toutes les œuvres de Platon et d’Aristote, pour montrer qu’ils s’accordent sur l’essentiel. Il n’a pu en réaliser qu’une partie : la logique d’Aristote et l’&lt;em&gt;Introduction&lt;/em&gt; de Porphyre. Ces traductions seront, pendant six siècles, presque la seule philosophie grecque connue en Occident, et l’une de ses questions, celle de la nature des universaux, lancera la grande querelle médiévale. Il écrit aussi des manuels d’arithmétique et de musique, et de courts traités de théologie, où il définit la personne comme « une substance individuelle de nature raisonnable ». Accusé de trahison pour avoir défendu un sénateur, il est emprisonné à Pavie, puis exécuté en 524. En prison, il écrit &lt;a  href="https://remacle.org/bloodwolf/philosophes/boece/livre3.htm#:~:text=J'entends%20par%20l%C3%A0%20ce,aurait%20encore%20mati%C3%A8re%20%C3%A0%20d%C3%A9sir." style="color:#88A1E9"  title="La consolation philosophique par Remacle"&gt;&lt;em&gt;La Consolation de Philosophie&lt;/em&gt;&lt;/a&gt;. La Philosophie lui apparaît sous les traits d’une femme majestueuse et lui montre que la Fortune, avec sa roue, donne et reprend tout : le vrai bonheur n’est pas dans les richesses ou le pouvoir, mais dans &lt;a  href="https://www.youtube.com/watch?v=Bx-_WsSfylw&amp;t=1619s&amp;ab_channel=%C3%89CLAIRBRUT" style="color:#88A1E9"  title="Une âme dénuée du monde par Eclair Brut"&gt;la sagesse&lt;/a&gt; et en Dieu, le bien suprême. Dieu, éternel, voit tout l’avenir comme un présent, sans supprimer notre liberté.&lt;/p&gt; &lt;p&gt;La &lt;em&gt;Consolation&lt;/em&gt; fut l’un des livres les plus influents de la culture européenne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F93" s="7" t="s">

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3442,7 +3442,7 @@
 Il est aussi connu pour sa théorie de  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1957_num_70_329_3473" style="color:#88A1E9"   title="Sur la signification de l'apeiron d'Anaximandre par Persée"&gt; "l'apeiron"&lt;/a&gt;, également traduit par le terme "infini" ou "illimité". Selon lui, l'apeiron est l'élément primordial à partir duquel tout provient et dans lequel tout finit. C'est une substance indéfinie et indéterminée, ni de l'eau ni de l'air, qui est à l'origine du cosmos. Il pensait que tous les éléments et les objets de l'univers étaient issus de l'apeiron par des processus de séparation et de condensation.
 &lt;/p&gt;&lt;p&gt;
 Il pensait que la Terre était suspendue dans l'espace, sans soutien visible, et que les étoiles étaient des trous à travers lesquels la lumière du feu intérieur du cosmos brillait. Ces idées ont été radicales pour l'époque et ont contribué à poser les bases de la pensée philosophique et scientifique future. Élève et successeur de Thalès à Milet, il écrit sans doute le premier livre de philosophie en prose. Il en reste une phrase, la plus ancienne de la philosophie grecque : les choses « se rendent justice et réparation de leur injustice, selon l’ordre du temps ». Il pense aussi que les premiers êtres vivants sont nés dans l’eau.
-&lt;/p&gt; &lt;audio controls title="Anaximandre, Héraclite et les autres : au commencement était le feu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-13.09.2021-ITEMA_22772439-2021C12410S0256-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+&lt;/p&gt; &lt;audio controls title="Anaximandre, Héraclite et les autres : au commencement était le feu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-13.09.2021-ITEMA_22772439-2021C12410S0256-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F6" s="7" t="s">
@@ -3488,8 +3488,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chilon"  style="color:#6A142A"  title=" Wikipedia"&gt;CHILON de Sparte&lt;/a&gt; était un philosophe grec et l'un des &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2003_num_105_1_5661_t1_0315_0000_3" style="color:#88A1E9" title="Les Sept Sages de la Grèce antique par Persée"&gt;Sept Sages &lt;/a&gt; de la Grèce, un groupe de penseurs et législateurs renommés pour leur  &lt;a href="https://www.youtube.com/watch?v=gW0-ikAVNnE" style="color:#88A1E9" title="Les Sept Sages: Chilon par Karl Baudoin"&gt;sagesse pratique&lt;/a&gt;. Il incarne la sagesse pratique spartiate, centrée sur la modération et la maîtrise de soi. Ses préceptes sont souvent formulés sous forme de maximes : &lt;/p&gt; &lt;p&gt; 
-- "Connais-toi toi-même" : Bien que parfois attribué à Socrate, cette inscription du temple de Delphes aurait été popularisée par Chilon. Elle résume l'idéal de réflexion personnelle et d'humilité. &lt;/p&gt; &lt;p&gt; - "La modération est la meilleure des choses" : Un appel à éviter les excès, en accord avec l'éthique spartiate de discipline. &lt;/p&gt; &lt;p&gt; - "Ne ris pas de ton ennemi" : Mise en garde contre l'arrogance, soulignant que les circonstances peuvent changer. &lt;/p&gt; &lt;p&gt; En tant qu'éphore, Chilon aurait contribué à renforcer les institutions spartiates, comme la Grande Rhêtra (loi fondamentale attribuée à Lycurgue).  Il aurait conseillé la prudence dans les relations extérieures, évitant les guerres inutiles tout en consolidant la puissance de Sparte. &lt;/p&gt; &lt;p&gt;  Il représente l'idéal spartiate de sagesse appliquée, où la philosophie ne se dissocie pas de l'action politique et de la discipline personnelle. Son héritage, bien que fragmentaire, reste un pont entre la pensée archaïque grecque et la philosophie classique. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chilon"  style="color:#6A142A"  title=" Wikipedia"&gt;CHILON de Sparte&lt;/a&gt; était un philosophe grec et l'un des &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2003_num_105_1_5661_t1_0315_0000_3" style="color:#88A1E9" title="Les Sept Sages de la Grèce antique par Persée"&gt;Sept Sages &lt;/a&gt; de la Grèce, un groupe de penseurs et législateurs renommés pour leur  &lt;a href="https://www.youtube.com/watch?v=gW0-ikAVNnE" style="color:#88A1E9" title="Les Sept Sages: Chilon par Karl Baudoin"&gt;sagesse pratique&lt;/a&gt;. Il incarne la sagesse pratique spartiate, centrée sur la modération et la maîtrise de soi. Ses préceptes sont souvent formulés sous forme de maximes : &lt;/p&gt; &lt;p&gt;"Connais-toi toi-même" : Bien que parfois attribué à Socrate, cette inscription du temple de Delphes aurait été popularisée par Chilon. Elle résume l'idéal de réflexion personnelle et d'humilité. &lt;/p&gt; &lt;p&gt;"La modération est la meilleure des choses" : Un appel à éviter les excès, en accord avec l'éthique spartiate de discipline. &lt;/p&gt; &lt;p&gt;"Ne ris pas de ton ennemi" : Mise en garde contre l'arrogance, soulignant que les circonstances peuvent changer. &lt;/p&gt; &lt;p&gt; En tant qu'éphore, Chilon aurait contribué à renforcer les institutions spartiates, comme la Grande Rhêtra (loi fondamentale attribuée à Lycurgue).  Il aurait conseillé la prudence dans les relations extérieures, évitant les guerres inutiles tout en consolidant la puissance de Sparte. &lt;/p&gt; &lt;p&gt;  Il représente l'idéal spartiate de sagesse appliquée, où la philosophie ne se dissocie pas de l'action politique et de la discipline personnelle. Son héritage, bien que fragmentaire, reste un pont entre la pensée archaïque grecque et la philosophie classique. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F7" s="7" t="s">
@@ -3934,8 +3933,11 @@
       <c r="D16" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>115</v>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Protagoras"  title="Protagoras par Wikipédia"&gt; PROTAGORAS&lt;/a&gt;  était un philosophe considéré comme l'un &lt;a href="https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;ab_channel=Bibiclo" style="color:#88A1E9"   title="Les Sophistes par Bobiclo"&gt; des sophistes&lt;/a&gt; les plus célèbres de cette période.&lt;/p&gt; &lt;p&gt;Les sophistes étaient des enseignants itinérants qui offraient &lt;a href="https://www.youtube.com/watch?v=X5bZKSCfc_g&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Rhétorique et relativisme par Alain Bajomée"&gt; des cours de rhétorique&lt;/a&gt;, d'éloquence et de persuader efficacement. Cependant, il a également suscité des débats et des controverses en raison de ses opinions et de ses idées.&lt;/p&gt;
+&lt;p&gt;L'une de ses déclarations les plus célèbres est : "L'homme est la mesure de toutes choses : de celles qui sont, tant quand elles sont en tant qu'elles sont, que de celles qui ne sont pas, tant quand elles ne sont pas en tant qu'elles ne sont pas." Cela suggère que la perception et l'expérience individuelles sont centrales pour la compréhension de la réalité, et que la vérité peut être relative à chaque individu. Cette déclaration forme le fondement de ce que l'on appelle &lt;a href="https://www.youtube.com/watch?v=LxSCq1F7pSk&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Le relativisme par le Précepteur"&gt; le relativisme.&lt;/a&gt;&lt;/p&gt; &lt;p&gt;Il a également abordé des sujets tels que la nature de la justice, l'éducation et le rôle des dieux dans la vie humaine. Ses enseignements ont été critiqués par d'autres philosophes, notamment Socrate et Platon, qui les voyaient vides de fondement rationnel.&lt;/p&gt; &lt;p&gt;Bien qu'il ait laissé peu d'œuvres écrites, sa vision de la relativité de la vérité et de l'importance de la rhétorique a contribué à façonner les débats sur la nature de la connaissance et de la réalité dans la philosophie grecque antique.&lt;/p&gt;  &lt;audio controls title="Platon vs. Protagoras: l'homme est il la mesure de toutes choses? par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/09/s40/NET_FC_f081bba4-88ba-4b62-930d-2c30e49863d9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F16" s="7" t="s">
         <v>116</v>
@@ -3978,8 +3980,11 @@
       <c r="D17" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>125</v>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Z%C3%A9non_d%27%C3%89l%C3%A9e"  title=" Wikipedia"&gt;ZÉNON d'Élée&lt;/a&gt; était  est un philosophie grec, principalement connu pour ses paradoxes qui ont influencé la pensée philosophique et mathématique pendant des siècles. Il visent à défendre les &lt;a href="https://www.youtube.com/watch?v=0rtwZaOyk-k&amp;t=67s"  style="color:#88A1E9" title="  ZÉNON et les paradoxes par Alain Bajoumée"&gt;thèses de Parménide&lt;/a&gt; en montrant les contradictions et les absurdités qui découlent de la croyance en la pluralité et le mouvement. Ses arguments sont souvent considérés comme des défis intellectuels pour comprendre la nature de l'espace, du temps et du mouvement. &lt;/p&gt; &lt;p&gt; Il a formulé  &lt;a href="https://www.youtube.com/watch?v=Gfci1UTuxCA"  title="Les 4 paradoxes de Zénon par Maêl Cavan"&gt;plusieurs paradoxes&lt;/a&gt;, dont les plus célèbres sont : &lt;/p&gt; &lt;p&gt;La Dichotomie : Pour parcourir une distance, il faut d'abord parcourir la moitié de cette distance, puis la moitié de la moitié, et ainsi de suite à l'infini. 
+Conclusion : Le mouvement ne peut jamais commencer, car il y a une infinité de distances à parcourir. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=2yfRRIbvF0g"  title=" Le paradoxe d'Achille et de la tortue par Coursitout"&gt;Achille et la tortue&lt;/a&gt; : Achille, le coureur le plus rapide, ne peut jamais rattraper une tortue qui a une avance, car il doit d'abord atteindre le point de départ de la tortue, puis le point suivant où elle se sera déplacée, et ainsi de suite.  Conclusion : Le mouvement est une illusion. &lt;/p&gt; &lt;p&gt;La flèche : À chaque instant, une flèche en vol occupe une position précise dans l'espace, immobile par rapport à cet instant. Conclusion : Si le temps est composé d'instants, la flèche ne bouge jamais réellement. &lt;/p&gt; &lt;p&gt; Le stade : Ce paradoxe met en évidence des contradictions dans la notion de relativité du mouvement en imaginant des objets se déplaçant dans des directions opposées. &lt;/p&gt; &lt;p&gt; Les paradoxes de Zénon ne visent pas à nier l'existence du mouvement ou de la pluralité, mais à montrer que ces concepts, tels que nous les comprenons, conduisent à des contradictions logiques. Ils soutiennent ainsi la thèse de Parménide selon laquelle la réalité est une et immuable, et que les apparences sensibles sont trompeuses.  Avec le développement du calcul infinitésimal, ils ont été partiellement résolus en montrant que des séries infinies peuvent converger vers une limite finie. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F17" s="7" t="s">
         <v>126</v>
@@ -4027,8 +4032,11 @@
       <c r="D18" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>134</v>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gorgias" title=" Wikipedia"&gt;GORGIAS&lt;/a&gt; était un philosophe présocratique et l'une des figures les plus importantes de la &lt;a href="https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;t=184s" title=" Les sophistes par Bibiclo"&gt;sophistique&lt;/a&gt;.  Contrairement aux philosophes comme Platon ou Aristote, qui cherchaient à découvrir des vérités universelles en mettant l'accent sur l'importance de l'opinion et de la persuasion dans les affaires humaines.  Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;"Sur le Non-Être ou sur la Nature" : Il développe une argumentation radicale qui remet en question la possibilité même de la connaissance et de la communication.&lt;/p&gt; &lt;p&gt;Il soutient trois thèses principales : Rien n'existe. Si quelque chose existait, nous ne pourrions pas le connaître. Si nous pouvions le connaître, nous ne pourrions pas le communiquer aux autres. &lt;/p&gt; &lt;p&gt; Ces thèses sont souvent interprétées comme une critique de l'ontologie éléatique, notamment des idées de Parménide, qui affirmait que l'être est un et immuable. &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89loge_d%27H%C3%A9l%C3%A8ne "  title=" Gorgias Eloge d’Helene  parWikipedia"&gt;"Éloge d'Hélène"&lt;/a&gt;  : Dans ce discours, Il défend Hélène de Troie, souvent considérée comme responsable de la guerre de Troie. Il utilise des arguments rhétoriques pour montrer qu'elle ne peut être tenue pour responsable, car elle a été soit victime de la volonté des dieux, soit de la séduction de Pâris, soit de la force.  &lt;/p&gt; &lt;p&gt;"Défense de Palamède" : Dans ce discours, il défend Palamède, un héros grec accusé de trahison par Ulysse. Il utilise des arguments logiques et rhétoriques pour démontrer son l'innocence, montrant ainsi la puissance de la parole pour influencer les jugements. &lt;p&gt; Il  est souvent considéré comme un relativiste et un sceptique. Il met en doute la possibilité de connaître la vérité absolue et souligne l'importance de la persuasion dans les affaires humaines. Sa philosophie a eu une influence significative sur la pensée grecque, notamment sur Platon, qui le critique sévèrement dans son dialogue "Gorgias". Platon y oppose la recherche de la vérité à l'art de la persuasion, qu'il associe à la sophistique. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F18" s="7" t="s">
         <v>135</v>
@@ -4071,8 +4079,10 @@
       <c r="D19" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>144</v>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Socrate"  style="color:#6A142A"  title=" Wikipedia"&gt;SOCRATE&lt;/a&gt; est considéré comme l'un des &lt;a href="https://www.youtube.com/watch?v=oMCwc1u3sd4&amp;ab_channel=Diligoinveritate%28Fr%29" style="color:#88A1E9"   title="La naissance de la Philosophie par Planète"&gt;pères de la philosophie  morale occidentale&lt;/a&gt; et de la méthode dialectique. Il n'a pas laissé de textes écrits, mais ses idées ont été transmises à travers les dialogues de Platon, qui était l'un de ses disciples les plus célèbres.&lt;/p&gt; &lt;p&gt; Sa philosophie de l'école met l'accent le &lt;a href="https://www.youtube.com/watch?v=iP6zV74nYzM" style="color:#88A1E9"   title="La face sombre de la démocratie l'avertissement de Socrate que nous ignorons par C'est Stoique"&gt; bien être de la cité&lt;/a&gt; et sur l'importance de la connaissance de soi et de la recherche de la vérité par le biais de la discussion et de l'examen critique. &lt;/p&gt;&lt;p&gt;  Sa méthode de questionnement appelée  &lt;a href="https://www.youtube.com/watch?v=QJFdcQYBkDY&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="La Maïeutique par le Précepteur"&gt; Maïeutique&lt;/a&gt;, qui consiste à poser des questions pour amener son interlocuteur à examiner ses croyances et à découvrir la vérité par lui-même. Il ne prétendait pas détenir des réponses, mais cherchait à stimuler la réflexion critique. &lt;/p&gt; &lt;p&gt;Ironie socratique : Il feignait souvent l'ignorance pour inciter les autres à exposer leurs idées.&lt;/p&gt; &lt;p&gt;Questionnement : Il posait des questions comme "Qu'est-ce que la justice ?" ou "Qu'est-ce que le courage ?" pour explorer des concepts fondamentaux. &lt;/p&gt; &lt;p&gt;  Il croyait que la vertu est une forme de connaissance et que nul ne fait le mal volontairement. Selon lui, si les gens comprenaient vraiment ce qui est bien, ils agiraient en conséquence. Sers citations les plus célèbres : &lt;/p&gt; &lt;p&gt;Connais-toi toi-même : Cette maxime, inscrite au fronton du temple de Delphes, résume l'importance qu'il accordait à l'introspection et à la connaissance de soi. &lt;/p&gt; &lt;p&gt;La vie examinée : Il affirmait que "une vie sans examen ne vaut pas la peine d'être vécue", soulignant l'importance de la réflexion philosophique.&lt;/p&gt; &lt;p&gt; Il fut accusé d'empiété et de corruption de la jeunesse par Mélétos, un poète de son époque et &lt;a href="https://www.youtube.com/watch?v=3h_6zy58acE&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Son procès et sa condamnation à mort par le Précepteur"&gt;condamné à mort&lt;/a&gt; après un procès où il accepta son sort.  Il a révolutionné la pensée occidentale en mettant l'accent sur la raison, l'éthique et l'importance de questionner les certitudes. Son héritage continue d'inspirer les philosophes et les chercheurs de vérité à travers les âges.&lt;/p&gt;  &lt;audio controls title="Socrate est il de son temps par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-17.07.2023-ITEMA_23428681-2022C48904S0325-NET_MFC_3B8967BE-C9AF-46ED-A1B8-02CA5C79BDCD-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F19" s="7" t="s">
         <v>145</v>
@@ -4355,7 +4365,7 @@
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antisth%C3%A8ne" style="color:#6A142A"   title="Antisthène par Wikipédia"&gt; ANTISTHÈNE &lt;/a&gt; était un philosophe disciple de Socrate et il a eu une influence significative sur le développement de la philosophie morale et éthique en cherchant à préserver et à développer les idées de son maître, en mettant l'accent sur la vertu personnelle et l'authenticité. &lt;/p&gt;
 &lt;p&gt; Il est considéré comme le fondateur de &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=133s&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Comprendre les Cyniques par Alain Bajomée"&gt; l'école de pensée cynique.&lt;/a&gt; Après la mort de Socrate, il a développé ses propres idées en reprenant certains des thèmes centraux de l'enseignement de Socrate et a donné à l'école le nom de "cynique", qui dérive du mot grec "kynikos", signifiant "chien". Ce nom faisait référence à l'accent mis sur la vie simple et naturelle détachée des désirs matériels et des plaisirs superficiels, ainsi qu'à la critique des conventions sociales. Il croyait que le bonheur réside dans la maîtrise de soi et dans le rejet des biens matériels. Il vivait lui-même une vie ascétique et rejetait les besoins et les désirs superflus. &lt;/p&gt;
-&lt;p&gt; Il pensait que la sagesse et la vertu étaient atteintes par la pratique de la philosophie et l'engagement dans une vie vertueuse et critiquait ouvertement les normes sociales et les valeurs conventionnelles de la société grecque de l'époque. Il remettait en question la poursuite des richesses matérielles, du prestige social et du pouvoir, préférant se concentrer sur la recherche de la véritable vertu et du bonheur. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;
+&lt;p&gt; Il pensait que la sagesse et la vertu étaient atteintes par la pratique de la philosophie et l'engagement dans une vie vertueuse et critiquait ouvertement les normes sociales et les valeurs conventionnelles de la société grecque de l'époque. Il remettait en question la poursuite des richesses matérielles, du prestige social et du pouvoir, préférant se concentrer sur la recherche de la véritable vertu et du bonheur. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4400,8 +4410,10 @@
       <c r="D26" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>206</v>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isocrate"  style="color:#6A142A"  title=" Wikipedia"&gt;ISOCRATE&lt;/a&gt; était un orateur et philosophe grec souvent éclipsé par des figures comme Platon ou Aristote, mais son impact sur l'éducation, la rhétorique et la pensée politique est considérable. Il  se distingue par  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2007_num_109_2_6552"  style="color:#88A1E9" title="La πλεονεξία chez Isocrate  par Persée"&gt;son approche&lt;/a&gt; pragmatique de la philosophie contrairement à Platon, qui cherche la vérité absolue, lui se concentre sur l'utilité pratique de la connaissance.  En 390 av. J.-C., il fonde une école à Athènes, rivale de l'Académie de Platon, qui attire des étudiants de toute la Grèce, dont certains deviendront des figures importantes, comme les orateurs Hypéride et Lycurgue.&lt;/p&gt; &lt;p&gt; Pour lui, la rhétorique n'est pas seulement un art de persuader, mais un moyen de former des citoyens éclairés et de promouvoir la justice. Il croit que la parole bien maîtrisée peut améliorer la société en encourageant le débat raisonné et en renforçant les institutions. Il rejette l'individualisme excessif et prône un équilibre entre les intérêts personnels et ceux de la communauté.  Il a laissé une vingtaine de discours et &lt;a href="https://www.persee.fr/doc/ktema_0221-5896_2016_num_41_1_1487"  style="color:#88A1E9" title=" Isocrate et Sparte par Persée"&gt;plusieurs lettres&lt;/a&gt;, dont les plus célèbres sont : &lt;/p&gt; &lt;p&gt;Le Panégyrique d'Athènes : Un plaidoyer pour l'unité grecque sous l'hégémonie athénienne. &lt;/p&gt; &lt;p&gt;Sur la paix : Un appel à la modération et à la coopération entre les cités grecques.&lt;/p&gt; &lt;p&gt;L'Éloge d'Hélène : Une défense rhétorique de la figure d'Hélène de Troie. &lt;/p&gt; &lt;p&gt;Le Philippe : Une lettre adressée à Philippe II de Macédoine, l'exhortant à unifier la Grèce. &lt;/p&gt; &lt;p&gt; Il aura marqué l'histoire de la pensée occidentale à plusieurs titres, son modèle éducatif, centré sur la rhétorique et la culture générale, a influencé l'éducation libérale en Occident et en politique, ses idées sur l'unité grecque et la coopération internationale résonnent encore aujourd'hui.&lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F26" s="7" t="s">
         <v>207</v>
@@ -4445,8 +4457,11 @@
       <c r="D27" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>214</v>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristippe_de_Cyr%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTIPPE de Cyrène&lt;/a&gt; était un philosophe grec antique, fondateur de  &lt;a href="https://www.youtube.com/watch?v=Rp7sm07EJBY&amp;t=270s" style="color:#88A1E9" title=" Les CYRÉNAÏQUES en 8 minutes par Alain Bajoumée"&gt;l'école cyrénaïque&lt;/a&gt;, une école de pensée qui met l'accent sur la recherche du plaisir comme but principal de la vie, une forme &lt;a href="https://www.youtube.com/watch?v=HOE8sDMhGUE" style="color:#88A1E9" title=" L'hédonisme sans mesure: la philosophie du plaisir par philosophie"&gt;d'hédonisme&lt;/a&gt;. Cependant, contrairement à l'hédonisme moderne souvent associé à la recherche effrénée du plaisir, la philosophie d'Aristippe est plus subtile et contextuelle : &lt;/p&gt;
+&lt;p&gt;Poursuite du plaisir : Pour lui, le plaisir est le bien suprême. Il croyait que le but de la vie était de maximiser le plaisir et de minimiser la douleur. Cependant, il distinguait entre les plaisirs physiques et les plaisirs intellectuels, et il valorisait particulièrement les plaisirs immédiats et concrets. &lt;/p&gt; &lt;p&gt;Adaptabilité et flexibilité : Il enseignait l'importance de s'adapter aux circonstances. Il croyait que la sagesse consistait à savoir profiter des plaisirs disponibles tout en évitant les douleurs inutiles. Cette idée est souvent résumée par sa maxime : "Posséder sans être possédé." &lt;/p&gt; &lt;p&gt;Indépendance émotionnelle : Il prônait une forme de détachement émotionnel. Il croyait que l'on devait être capable de jouir des plaisirs sans devenir esclave de ses désirs. Cette idée est proche de la notion de "ataraxie" (tranquillité de l'âme) que l'on retrouve plus tard dans l'épicurisme. &lt;/p&gt; &lt;p&gt;Critique des conventions sociales : Il était connu pour son mépris des conventions sociales et des normes traditionnelles et croyait que les individus devaient vivre selon leurs propres termes, sans se soucier excessivement de l'opinion des autres. &lt;/p&gt; &lt;p&gt; L'école cyrénaïque a eu une influence limitée par rapport à d'autres écoles philosophiques de l'Antiquité, mais elle a néanmoins contribué à façonner la pensée hédoniste et à influencer des philosophes ultérieurs comme Épicure.  &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F27" s="7" t="s">
         <v>215</v>
@@ -4535,7 +4550,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Platon"  style="color:#6A142A"  title=" Wikipedia"&gt;PLATON&lt;/a&gt; fut  un des plus grands penseurs de l'Antiquité.  Il était l'élève de Socrate, dont la méthode dialectique et la quête de la vérité le marquent profondément. La condamnation à mort de Socrate en 399 av. J.-C. influence sa méfiance envers la démocratie athénienne. &lt;/p&gt; &lt;p&gt; Il fonda  &lt;a href="https://www.youtube.com/watch?v=q0M8zV-XHbQ"  style="color:#88A1E9" title="L'académie de Platon Platon par Luc Ferry"&gt;l'Académie&lt;/a&gt; à Athènes, qui est considérée comme la première institution d'enseignement supérieur de l'histoire où  il y enseigne la philosophie, les mathématiques et les sciences. L'Académie fonctionnera pendant près de 900 ans.&lt;/p&gt; Il développe une philosophie complexe et systématique, centrée sur des concepts clés comme les Idées, &lt;a href="https://www.persee.fr/doc/phlou_0776-5541_1905_num_12_46_1881"  style="color:#88A1E9" title="Dieu, d'après Platon par Persée"&gt;l'âme&lt;/a&gt;, la justice et la connaissance. Ses idées sont principalement exposées sous forme de dialogues, où Socrate est souvent le personnage principal. Il distingue &lt;a href="https://www.youtube.com/watch?v=o5TbXYe64A8&amp;t=18s&amp;ab_channel=AlainBajom%C3%A9e"  style="color:#88A1E9" title="La théorie des idées par Alain Bajomée"&gt;deux mondes&lt;/a&gt; : le monde sensible (celui que nous percevons par les sens) et le monde intelligible (celui des Idées, éternel et immuable). Pour lui, les Idées sont des réalités parfaites et immuables qui existent indépendamment du monde matériel. Par exemple, il existe une Idée de la Beauté, de la Justice ou du Bien, dont les objets sensibles ne sont que des copies imparfaites. &lt;/p&gt; &lt;p&gt;Il a écrit une trentaine de dialogues, dont les plus célèbres sont :  - La République (justice, politique, éducation). - Phédon (immortalité de l'âme). -  &lt;a href="https://www.youtube.com/watch?v=Mbtxr1hsP7A"  title="  Ce que Le Banquet de Platon révèle sur l'amour  par Resumon ça"&gt;Le Banquet &lt;/a&gt;(amour et beauté). - Phèdre (rhétorique et amour). - Ménon (vertu et réminiscence). - Timée (cosmologie et physique). - Critias (mythe de l'Atlantide). - Apologie de Socrate (défense de Socrate lors de son procès). - Phédon (immortalité de l'âme). &lt;/p&gt; &lt;p&gt;  Dans son ouvrage  le plus célèbre  &lt;a href="https://www.youtube.com/watch?v=qSrvZvjPG_w&amp;t=811s&amp;ab_channel=Kosmos"  style="color:#88A1E9" title="La République, c'est quoi par Kosmos"&gt;La République&lt;/a&gt;, il décrit sa vision d'une société idéale où les dirigeants sont des philosophes-rois et où la justice et la vertu sont les principes fondamentaux. Il y présente une métaphore de la condition humaine, l'allégorie de la &lt;a href="https://www.youtube.com/watch?v=N519gbEXbbw&amp;t=13s&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9" title="L'allégorie de la Caverne par le Précepteur "&gt;La Caverne&lt;/a&gt;, lieu où des gens vivent et où ils ne voient que des ombres projetées sur les murs en croyant que c'est la réalité.&lt;/p&gt;    &lt;p&gt; Il reste une figure centrale de la philosophie, dont les idées continuent d'inspirer et de provoquer la réflexion. Sa quête de la vérité, sa vision idéaliste et sa méthode dialectique en font un penseur intemporel. &lt;/p&gt;   &lt;audio controls title="Platon et la politique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.11.2025-ITEMA_24317262-2025C48904S0324-NET_MFC_E07CEF22-5D42-4358-8035-01B7B6D438EF-21-f49f7fca67cbafd4d44c5b4c00fead78.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Platon"  style="color:#6A142A"  title=" Wikipedia"&gt;PLATON&lt;/a&gt; fut  un des plus grands penseurs de l'Antiquité.  Il était l'élève de Socrate, dont la méthode dialectique et la quête de la vérité le marquent profondément. La condamnation à mort de Socrate en 399 av. J.-C. influence sa méfiance envers la démocratie athénienne. &lt;/p&gt; &lt;p&gt; Il fonda  &lt;a href="https://www.youtube.com/watch?v=q0M8zV-XHbQ"  style="color:#88A1E9" title="L'académie de Platon Platon par Luc Ferry"&gt;l'Académie&lt;/a&gt; à Athènes, qui est considérée comme la première institution d'enseignement supérieur de l'histoire où  il y enseigne la philosophie, les mathématiques et les sciences. L'Académie fonctionnera pendant près de 900 ans.&lt;/p&gt; Il développe une philosophie complexe et systématique, centrée sur des concepts clés comme les Idées, &lt;a href="https://www.persee.fr/doc/phlou_0776-5541_1905_num_12_46_1881"  style="color:#88A1E9" title="Dieu, d'après Platon par Persée"&gt;l'âme&lt;/a&gt;, la justice et la connaissance. Ses idées sont principalement exposées sous forme de dialogues, où Socrate est souvent le personnage principal. Il distingue &lt;a href="https://www.youtube.com/watch?v=o5TbXYe64A8&amp;t=18s&amp;ab_channel=AlainBajom%C3%A9e"  style="color:#88A1E9" title="La théorie des idées par Alain Bajomée"&gt;deux mondes&lt;/a&gt; : le monde sensible (celui que nous percevons par les sens) et le monde intelligible (celui des Idées, éternel et immuable). Pour lui, les Idées sont des réalités parfaites et immuables qui existent indépendamment du monde matériel. Par exemple, il existe une Idée de la Beauté, de la Justice ou du Bien, dont les objets sensibles ne sont que des copies imparfaites. &lt;/p&gt; &lt;p&gt;Il a écrit une trentaine de dialogues, dont les plus célèbres sont : La République (justice, politique, éducation). Phédon (immortalité de l'âme). &lt;a href="https://www.youtube.com/watch?v=Mbtxr1hsP7A"  title="  Ce que Le Banquet de Platon révèle sur l'amour  par Resumon ça"&gt;Le Banquet &lt;/a&gt;(amour et beauté). Phèdre (rhétorique et amour). Ménon (vertu et réminiscence). Timée (cosmologie et physique). Critias (mythe de l'Atlantide). Apologie de Socrate (défense de Socrate lors de son procès). Phédon (immortalité de l'âme). &lt;/p&gt; &lt;p&gt;  Dans son ouvrage  le plus célèbre  &lt;a href="https://www.youtube.com/watch?v=qSrvZvjPG_w&amp;t=811s&amp;ab_channel=Kosmos"  style="color:#88A1E9" title="La République, c'est quoi par Kosmos"&gt;La République&lt;/a&gt;, il décrit sa vision d'une société idéale où les dirigeants sont des philosophes-rois et où la justice et la vertu sont les principes fondamentaux. Il y présente une métaphore de la condition humaine, l'allégorie de la &lt;a href="https://www.youtube.com/watch?v=N519gbEXbbw&amp;t=13s&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9" title="L'allégorie de la Caverne par le Précepteur "&gt;La Caverne&lt;/a&gt;, lieu où des gens vivent et où ils ne voient que des ombres projetées sur les murs en croyant que c'est la réalité.&lt;/p&gt; &lt;p&gt; Il reste une figure centrale de la philosophie, dont les idées continuent d'inspirer et de provoquer la réflexion. Sa quête de la vérité, sa vision idéaliste et sa méthode dialectique en font un penseur intemporel. &lt;/p&gt;   &lt;audio controls title="Platon et la politique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.11.2025-ITEMA_24317262-2025C48904S0324-NET_MFC_E07CEF22-5D42-4358-8035-01B7B6D438EF-21-f49f7fca67cbafd4d44c5b4c00fead78.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F29" s="7" t="s">
@@ -4589,7 +4604,7 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Sinope"   title="Diogène de Sinope par Wikipédia"&gt; DIOGÈNE DE SINOPE &lt;/a&gt; était un philosophe grec antique connu pour son mode de vie ascétique et ses provocations intellectuelles. Il est souvent surnommé "Diogène le Cynique" en raison de son affiliation à l'école de pensée cynique, qui prônait le rejet des conventions sociales, le détachement des désirs matériels et une vie en accord avec la nature. Il vivait une vie extrêmement simple et minimaliste et rejetait les besoins conventionnels et matérialistes, préférant se contenter de peu. Il est célèbre pour avoir vécu dans un tonneau (ou grand récipient) à Athènes. &lt;/p&gt;
 &lt;p&gt;Diogène était connu pour &lt;a href="https://www.philo5.com/Les%20philosophes%20Textes/Diogene_OntDitSur.htm#_ftn4"  title="Diogène de Sinope d'après Diogène Laërce par philo5"&gt; défier les normes&lt;/a&gt; sociales et philosophiques de son époque en utilisant souvent des actions et des paroles provocantes pour critiquer la société, remettre en question les valeurs établies et provoquer des réflexions profondes. Par exemple, il se promenait en plein jour avec une lanterne allumée à la recherche d'un "homme honnête", soulignant ainsi l'absence de personnes vertueuses.  &lt;a href="https://www.youtube.com/watch?v=aNUDOhr9yLs"  title=" La philosophie Diogène de Sinope par parole de philosophes "&gt; Il croyait &lt;/a&gt; que la société et ses institutions étaient corrompues et prônait la simplicité et la nature, rejetant les normes artificielles et les désirs superficiels qui causaient souvent des souffrances et des conflits.&lt;/p&gt;
 &lt;p&gt;  Diogène aurait eu une rencontre célèbre avec Alexandre le Grand, qui, impressionné par la renommée de Diogène, l'aurait trouvé dans son tonneau et aurait demandé s'il pouvait faire quelque chose pour lui. Diogène aurait répondu simplement : "Ôte-toi de mon soleil." Cette anecdote illustre l'attitude nonchalante et provocatrice de Diogène. &lt;/p&gt;
-&lt;p&gt;Ses enseignements exacts  ne sont pas bien documentés, car peu de ses écrits ont survécu. Cependant, &lt;a href="https://www.youtube.com/watch?v=epW-8gZwQEk&amp;ab_channel=R%C3%A9sonance%5Bs%5D"  title="Diogène de Sinope, le chien royal par Résonance"&gt;son mode de vie&lt;/a&gt; et ses actions ont eu un impact durable sur la philosophie occidentale en remettant en question les valeurs conventionnelles et en mettant l'accent sur la simplicité et l'authenticité. &lt;/p&gt;   &lt;audio controls title="Osons le cynisme ! retour à Diogène par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/02/s09/LES_NOUVEAUX_CHEMINS_DE_LA_CONNAISSANCE.NET_FC_4EBE3123-A5B5-49FF-96B5-DB4346498425.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+&lt;p&gt;Ses enseignements exacts  ne sont pas bien documentés, car peu de ses écrits ont survécu. Cependant, &lt;a href="https://www.youtube.com/watch?v=epW-8gZwQEk&amp;ab_channel=R%C3%A9sonance%5Bs%5D"  title="Diogène de Sinope, le chien royal par Résonance"&gt;son mode de vie&lt;/a&gt; et ses actions ont eu un impact durable sur la philosophie occidentale en remettant en question les valeurs conventionnelles et en mettant l'accent sur la simplicité et l'authenticité. &lt;/p&gt;   &lt;audio controls title="Osons le cynisme ! retour à Diogène par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/02/s09/LES_NOUVEAUX_CHEMINS_DE_LA_CONNAISSANCE.NET_FC_4EBE3123-A5B5-49FF-96B5-DB4346498425.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F30" s="7" t="s">
@@ -4680,8 +4695,10 @@
       <c r="D32" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>257</v>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Speusippe"  style="color:#6A142A"  title=" Wikipedia"&gt;SPEUSIPPE&lt;/a&gt; était un philosophe grec connu pour être le neveu de Platon et pour avoir succédé à ce dernier à la tête de l'Académie, l'école philosophique qu'il avait fondé. Il est souvent considéré comme un philosophe qui a cherché à développer et à modifier les idées de Platon plutôt que de les suivre strictement. &lt;/p&gt; &lt;p&gt; Il a rejeté la théorie des Formes de Platon, qui postulait l'existence d'entités immuables et éternelles (les Formes) comme fondement de la réalité. À la place, il a proposé une vision plus naturaliste et mathématique de la réalité, mettant l'accent sur les nombres et les  &lt;a href="https://remacle.org/bloodwolf/philosophes/speusippe/fragments.htm"  style="color:#88A1E9" title=" Speusippe fragment par remacle"&gt;principes mathématiques&lt;/a&gt; comme fondements de l'univers.  Il a également développé une théorie des principes premiers, où il distinguait entre l'Un (qui représente l'unité et la simplicité) et la Multiplicité (qui représente la diversité et la complexité). Ces principes étaient considérés comme les fondements de toute existence. &lt;/p&gt; Il a soutenu que le bonheur ne réside pas dans la possession de biens matériels ou de plaisirs, mais dans la réalisation d'une &lt;a href="https://remacle.org/bloodwolf/philosophes/laerce/4speusippe.htm"  style="color:#88A1E9" title=" Speusippe livre IV par Remacle"&gt;harmonie intérieure&lt;/a&gt; et d'une vie vertueuse. Il a mis l'accent sur l'importance de la modération et de l'équilibre dans la vie humaine. Il s'est intéressé à la classification des êtres vivants et a tenté de développer un système pour organiser et comprendre la diversité du monde naturel. Bien que ses travaux dans ce domaine soient peu connus, ils montrent un intérêt pour l'observation et la systématisation de la nature. &lt;/p&gt; &lt;p&gt; Il a dirigé l'Académie pendant environ huit ans, mais son influence a été éclipsée par celle de son successeur, Xénocrate, et par la postérité de Platon. Ses écrits ont été perdus, et nous ne connaissons sa pensée qu'à travers les témoignages d'autres philosophes, tels qu'Aristote, qui a critiqué certaines de ses idées.&lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F32" s="7" t="s">
         <v>258</v>
@@ -4724,8 +4741,10 @@
       <c r="D33" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>265</v>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eubulide"  style="color:#6A142A"  title=" Wikipedia"&gt;EUBULIDE de Milet&lt;/a&gt;  était un philosophe grec antique appartenant à l'école mégarique, une école de philosophie fondée par Euclide de Mégare, un disciple de Socrate. L'école mégarique est connue pour son intérêt pour la logique et les arguments dialectiques. &lt;/p&gt; &lt;p&gt; Eubulide est surtout connu pour ses paradoxes, qui ont été conçus pour mettre en lumière les difficultés et les ambiguïtés dans le langage et la pensée. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=CIgkTJYt1b0"  style="color:#88A1E9" title="Le paradoxe du menteur par Logique Contradictoire"&gt;Le paradoxe du menteur&lt;/a&gt; : Ce paradoxe met en scène une personne qui déclare "Je mens". Si la personne dit la vérité, alors elle ment, ce qui est une contradiction. Si elle ment, alors elle dit la vérité, ce qui est également une contradiction. Ce paradoxe a des implications profondes pour la logique et la sémantique. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=2tn152iCDpk"  title="Le paradoxe du Sorite par Philosophie Analytique"&gt;Le paradoxe du sorite&lt;/a&gt; (ou paradoxe du tas) : Ce paradoxe questionne à quel moment un tas de grains cesse d'être un tas lorsqu'on enlève un grain à la fois. Il soulève des questions sur les limites floues et les définitions vagues. &lt;/p&gt; &lt;p&gt;Le paradoxe de l'électre : Ce paradoxe explore les problèmes de connaissance et de reconnaissance. Si Electre sait que son frère Oreste est dans la pièce, mais ne reconnaît pas Oreste lorsqu'elle le voit, peut-on dire qu'elle sait vraiment qu'il est là ? &lt;/p&gt; &lt;p&gt;Le paradoxe du voilé : Ce paradoxe pose la question de savoir si on peut reconnaître quelqu'un qui est voilé. Si on ne peut pas le reconnaître, comment peut-on savoir que c'est la même personne ? &lt;/p&gt; &lt;p&gt;  Les paradoxes d'Eubulide ont eu une influence durable sur la philosophie, en particulier dans les domaines de la logique, de la sémantique et de l'épistémologie. Ils ont été étudiés et discutés par de nombreux philosophes ultérieurs, y compris les stoïciens et les sceptiques, et continuent d'être un sujet de débat dans la philosophie contemporaine. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F33" s="7" t="s">
         <v>266</v>
@@ -4912,8 +4931,11 @@
       <c r="D37" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>298</v>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristote"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTOTE&lt;/a&gt; est l'un des philosophes les plus influents de l'histoire occidentale. Disciple de Platon et précepteur d'Alexandre le Grand, il a contribué à de nombreux domaines de la connaissance, notamment la philosophie, la science, la logique,  &lt;a href="https://www.youtube.com/watch?v=Zo1J19uk-Cc" style="color:#88A1E9"   title=" L'éthique de la vertu d'Aristote par Coursitout"&gt; l'éthique&lt;/a&gt;, la politique, la métaphysique, la biologie et la physique. Il a fondé sa propre école, &lt;a href="https://fr.wikipedia.org/wiki/Lyc%C3%A9e_(%C3%A9cole_philosophique)" style="color:#88A1E9"   title="Le Lycée par wikipedia"&gt;le Lycée&lt;/a&gt;. &lt;/p&gt;&lt;p&gt; Ses travaux sont organisés en plusieurs catégories : &lt;/p&gt;&lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=4fhmo_C1VIA" style="color:#88A1E9"   title="ARISTOTE - Les principes de la logique par le Précepteur"&gt; La Logique&lt;/a&gt; : Il est considéré comme le père de la logique formelle.  Il établit une classification des concepts en dix catégories (substance, quantité, qualité, relation, etc.). &lt;/p&gt; &lt;p&gt;La Métaphysique : Il  explore la nature de l'être et de la réalité dans son ouvrage Métaphysique. Il introduit les concepts de &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1946_num_44_3_4064" style="color:#88A1E9"   title="        La première doctrine de la substance : la substance selon Aristotee par  Persée"&gt;"substance"&lt;/a&gt;  (ce qui existe par soi-même) et d'"accident" (ce qui modifie la substance). Il propose une théorie des quatre causes (matérielle, formelle, efficiente et finale) pour expliquer pourquoi les choses existent et changent. &lt;/p&gt; &lt;p&gt;La Politique :  Dans "Politique", il analyse les différentes formes de gouvernement (monarchie, aristocratie, démocratie) et leurs dérives (tyrannie, oligarchie, démagogie). Il défend l'idée que l'homme est un "animal politique" destiné à vivre en société. &lt;/p&gt; La Science et la Biologie : Contrairement à Platon, qui privilégie les idées abstraites, il s'appuie sur l'observation et l'expérience pour étudier la nature.  Il est l'un des premiers à classer les animaux selon leurs caractéristiques communes. &lt;/p&gt; &lt;p&gt;Rhétorique :   Il étudie l'art de persuader, distinguant trois types de preuves : l'ethos (caractère de l'orateur), le pathos (émotions du public) et le logos (argumentation logique). &lt;/p&gt; &lt;p&gt; Il  privilégie &lt;a href="https://www.youtube.com/watch?v=CdOxw_GRKWk&amp;t=173s&amp;ab_channel=CULTUREG" style="color:#88A1E9"   title="L'Empirisme par Culture G"&gt;l' Empirisme&lt;/a&gt;  par l'observation et l'expérience pour comprendre le monde, contrairement à l'idéalisme de Platon. Il  croit que tout dans la nature a une fin ou un but (telos), ce qui influence sa vision du monde. &lt;/p&gt; &lt;p&gt;  Dans son oeuvre "l'Organon", il développe des concepts de logique comme le syllogisme, un raisonnement déductif composé de deux prémisses et d'une conclusion. &lt;/p&gt; &lt;p&gt; Il a également étudié les phénomènes physiques tels que la chute des corps et le mouvement des astres et a développé une logique formelle, qui est encore utilisée aujourd'hui.&lt;/p&gt; &lt;p&gt; Il a soutenu que le but de la vie humaine est l'accomplissement de la "vertu", qui est un état de caractère qui permet de vivre de manière équilibrée et heureuse ainsi qu'une théorie de la politique où il dit que &lt;a href="https://www.youtube.com/watch?v=djOrZrEDMto&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'homme est un animal politique par le Précepteur"&gt; L'homme est un animal politique&lt;/a&gt; et qu'il existe différents types de régimes  (démocratie, oligarchie, monarchie) et que le meilleur est celui qui est gouverné par des personnes vertueuses.   &lt;/p&gt;         &lt;/p&gt; &lt;p&gt;                       &lt;audio controls title="Raison et réalité: l'être avec Aristote par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-07.05.2022-ITEMA_23018730-2020C3372E0467-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;                                            
+</t>
+        </is>
       </c>
       <c r="F37" s="7" t="s">
         <v>299</v>
@@ -4963,8 +4985,11 @@
       <c r="D38" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>307</v>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristippe_le_Jeune"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTIPPE le Jeune&lt;/a&gt; était un philosophe grec moins connue que son grand-père, Aristippe de Cyrène, fondateur de l'école &lt;a href="https://www.youtube.com/watch?v=I5PEbJhoUEs" style="color:#88A1E9" title="Aristippe le Cyrénaïque vu sous l'angle d'Ibiza par Chroniques philosophique "&gt;philosophique cyrénaïque&lt;/a&gt;. Les informations sur lui sont relativement limitées et souvent entremêlées avec celles de son grand-père, ce qui rend difficile une distinction claire entre leurs contributions respectives. &lt;/p&gt; &lt;p&gt;  Il  est souvent crédité d'avoir systématisé et formalisé les enseignements de son grand-père, contribuant ainsi à l'évolution de la pensée cyrénaïque. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=QNRG_j24a5U" style="color:#88A1E9" title="L'Hédonisme par la Philosophie du Bonheur "&gt;Hédonisme&lt;/a&gt; : Comme son grand-père, il soutenait que le plaisir est le but ultime de la vie. Cependant, il a peut-être développé une approche plus nuancée, en distinguant entre différents types de plaisirs et en mettant l'accent sur la modération. &lt;/p&gt;
+&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pr%C3%A9sentisme" style="color:#88A1E9" title="Le Présentisme par Wikipedia "&gt;Présentisme&lt;/a&gt; : Il croyait en l'importance de vivre dans le moment présent. Il considérait que le passé est irréversible et le futur incertain, donc le présent est le seul moment où l'on peut véritablement expérimenter le plaisir. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.axiologie.org/nihilisme-definition/valeur-subjective/proposition-9.html" style="color:#88A1E9" title="Le subjectivisme par Axiologie "&gt;Subjectivisme&lt;/a&gt; : Il a également contribué à la théorie de la connaissance des cyrénaïques, qui soutient que la seule certitude que nous avons est celle de nos propres sensations et expériences subjectives. Cette idée a des implications profondes pour l'épistémologie et la philosophie de l'esprit. &lt;/p&gt; &lt;p&gt; Il est une figure importante dans l'histoire de la philosophie grecque, principalement pour son rôle dans la systématisation et la promotion des idées hédonistes de l'école cyrénaïque. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F38" s="7" t="s">
         <v>308</v>
@@ -5007,8 +5032,12 @@
       <c r="D39" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>315</v>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ophraste"  style="color:#6A142A"  title=" Wikipedia"&gt;THÉOPHRASTE&lt;/a&gt; était un philosophe et naturaliste grec de l'Antiquité, souvent considéré comme le père de la botanique. Il fut un disciple d'Aristote et lui succéda à la tête du Lycée.  Il a écrit sur de nombreux sujets, notamment la logique, la métaphysique, l'éthique et la physique. Il a remis en question certaines des catégories aristotéliciennes et a exploré des questions liées à la causalité et à la nature de l'âme. &lt;/p&gt; &lt;p&gt; Il est célèbre pour ses  &lt;a href="https://www.youtube.com/watch?v=_8w0rzsq7io" style="color:#88A1E9" title="  Approches philosophique et botanique de la croissance végétale chez Théophraste par UMR 8546"&gt;travaux en botanique&lt;/a&gt;, qui constituent une avancée majeure dans l'étude scientifique des plantes. Ses deux principaux ouvrages sur le sujet sont : &lt;/p&gt;
+&lt;p&gt;"Histoire des plantes" : Une encyclopédie en neuf livres qui décrit les caractéristiques, les classifications et les utilisations des plantes. Il y aborde des sujets comme la morphologie, la reproduction et la croissance des végétaux. &lt;/p&gt; &lt;p&gt;"Causes des plantes" : Un traité en six livres qui explore les causes naturelles des phénomènes végétaux, comme la germination, la floraison et la fructification. &lt;/p&gt; &lt;p&gt; 
+Il a classé les plantes en fonction de leurs caractéristiques morphologiques et de leurs usages, jetant les bases de la &lt;a href="https://www.youtube.com/watch?v=E7uRf4fU_pk" style="color:#88A1E9" title="  Histoire de la botanique en 5 mn par Terre D'Avalonne"&gt;taxonomie végétale&lt;/a&gt;. Il a également étudié les relations entre les plantes et leur environnement, anticipant certaines idées de l'écologie moderne. &lt;/p&gt; &lt;p&gt; Outre la botanique, il a écrit sur des sujets variés tels que la minéralogie, la météorologie et la zoologie. Son ouvrage "Sur les pierres" est le premier traité sur les minéraux et leurs propriétés. &lt;/p&gt; &lt;p&gt;  Il  était connu pour son approche empirique et systématique, héritée d'Aristote. Il observait attentivement les phénomènes naturels et cherchait à les expliquer de manière rationnelle. Son style d'écriture était clair et méthodique, ce qui a contribué à la diffusion de ses idées. &lt;/p&gt;  </t>
+        </is>
       </c>
       <c r="F39" s="7" t="s">
         <v>316</v>
@@ -5051,8 +5080,10 @@
       <c r="D40" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="E40" s="9" t="s">
-        <v>324</v>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Crat%C3%A8s_de_Th%C3%A8bes"  style="color:#6A142A"  title=" Wikipedia"&gt;CRATÈS de Thèbes&lt;/a&gt; était un philosophe  grec, disciple de Diogène de Sinope et contemporain d'Alexandre le Grand. Il est connu pour avoir radicalement transformé sa vie en renonçant à sa richesse et en adoptant un mode de vie simple et ascétique, conformément aux principes du &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=134s" style="color:#88A1E9" title=" Les Cynique en 5 mn par Alain Bajomée"&gt;Cynisme&lt;/a&gt;, une école philosophique qui prône la simplicité, l'autosuffisance et le mépris des conventions sociales. &lt;/p&gt; &lt;p&gt;Rejet des biens matériels : Il croyait que la richesse et les possessions matérielles étaient des sources de troubles et d'esclavage. En vivant dans la pauvreté volontaire, il cherchait à atteindre une liberté intérieure et une indépendance vis-à-vis des désirs superflus. &lt;/p&gt; &lt;p&gt;Vie en harmonie avec la nature : Comme les autres cyniques, il prônait un retour à une vie simple, en accord avec la nature. Il rejetait les artifices de la société et vivait de manière frugale, souvent dans la rue ou dans des lieux publics. &lt;/p&gt; &lt;p&gt;Critique des conventions sociales : Il remettait en question les normes sociales, y compris les institutions comme le mariage, la propriété et les hiérarchies sociales. Son mariage avec Hipparchia était une manifestation de cette critique, car il défiait les attentes traditionnelles. &lt;/p&gt; &lt;p&gt;Bienveillance et humour : Contrairement à Diogène, qui était souvent perçu comme provocateur et abrupt, il était connu pour sa gentillesse et son humour. Il était surnommé "l'ouvreur de portes" parce qu'il entrait chez les gens pour leur donner des conseils philosophiques, toujours avec bienveillance. &lt;/p&gt; &lt;p&gt; Ses œuvres étaient souvent satiriques et utilisaient l'humour pour transmettre des messages philosophiques. Par exemple, il a écrit un poème décrivant une cité idéale appelée "Péra", symbolisant une communauté où les biens matériels n'ont aucune importance. &lt;/p&gt; &lt;p&gt; Il est resté une figure respectée dans la tradition philosophique, notamment pour son engagement envers la vertu et sa capacité à vivre selon ses principes. Bien que le cynisme en tant qu'école philosophique ait décliné après l'Antiquité, les idées ont influencé d'autres courants, comme le stoïcisme, et continuent d'inspirer ceux qui cherchent à vivre une vie simple et authentique. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F40" s="7" t="s">
         <v>325</v>
@@ -5187,8 +5218,10 @@
       <c r="D43" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="E43" s="9" t="s">
-        <v>347</v>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stilpon_de_M%C3%A9gare"  style="color:#6A142A"  title=" Wikipedia"&gt;STILPON de Mégare&lt;/a&gt; était est un philosophe, spécialisée dans la dialectique de type éristique. Il est associé à l'école mégarique, fondée par Euclide de Mégare et était connu pour son éloquence et sa capacité à débattre, ce qui lui a valu une grande renommée dans le monde grec. &lt;/p&gt; &lt;p&gt; Les Mégariques étaient connus pour leur intérêt pour les paradoxes et les arguments sophistiqués. &lt;/p&gt; &lt;p&gt;Critique des universaux : Il est surtout connu pour sa critique des idées platoniciennes, en particulier la théorie des Formes. Il soutenait que les concepts généraux (comme "l'homme" ou "le bien") ne peuvent pas exister indépendamment des choses particulières. Pour lui, seules les choses individuelles sont réelles, et les universaux ne sont que des noms ou des constructions mentales. &lt;/p&gt; &lt;p&gt;Réfutation des catégories : Il a également critiqué la théorie des catégories d'Aristote, arguant que les distinctions entre les catégories (comme la substance, la qualité, la quantité) étaient artificielles et ne reflétaient pas la réalité. &lt;/p&gt; &lt;p&gt;Éthique et autosuffisance : Comme d'autres philosophes de son époque, il s'intéressait à l'éthique. Il prônait l'autosuffisance (autarkeia) et la tranquillité de l'âme (ataraxia). Il croyait que le bonheur pouvait être atteint en se libérant des désirs inutiles et en se concentrant sur ce qui est véritablement important. &lt;/p&gt; &lt;p&gt;Dialectique et logique : Il était un maître de la dialectique et utilisait souvent des arguments logiques pour déconstruire les positions de ses adversaires. Il était connu pour sa capacité à réduire les arguments de ses interlocuteurs à l'absurde, ce qui en faisait un redoutable débatteur. &lt;/p&gt; &lt;p&gt; Il était un philosophe dialecticien et éthique, dont les idées ont influencé plusieurs courants philosophiques ultérieurs. Bien que son œuvre ne nous soit pas parvenue directement, sa réputation de penseur rigoureux et son impact sur la philosophie antique sont indéniables. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F43" s="7" t="s">
         <v>348</v>
@@ -5277,8 +5310,10 @@
       <c r="D45" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="E45" s="14" t="s">
-        <v>364</v>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9donisme" style="color:#88A1E9"   title="L'hédonisme par Wikipédia"&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href="https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur"   title="L'épicurisme par le Précepteur"&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href="https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'épicurisme par le Précepteur"&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href="https://www.youtube.com/watch?v=cb1YHXSuxlM"   title="La philosophie du bonheur par Parole de philosophe"&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées "atomes".&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt; &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title="Est il bien raisonnable d'avoir peur de la mort par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F45" s="7" t="s">
         <v>365</v>
@@ -5553,8 +5588,10 @@
       <c r="D51" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="E51" s="9" t="s">
-        <v>415</v>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Persaios_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;PERSAIOS de Kition&lt;/a&gt;  était un disciple direct de Zénon de Cition, le fondateur du stoïcisme, et a joué un rôle important dans la diffusion des idées stoïciennes, bien que sa vie et son œuvre restent mal documentées en raison du peu de sources qui nous sont parvenues. Il aurait été l'esclave ou le pupille de Zénon avant de devenir son disciple et ami. Cette relation étroite avec le fondateur du stoïcisme lui a permis de jouer un rôle important dans les premiers développements de l'école. &lt;/p&gt; &lt;p&gt;  En tant que conseiller du roi Antigone II Gonatas, il a cherché à mettre en œuvre les idéaux stoïciens de vertu et de raison dans la gouvernance. Cela reflète une tendance du stoïcisme à s'engager dans le monde réel plutôt qu'à rester confiné à des spéculations abstraites. Il a écrit un ouvrage intitulé "Sur la royauté", dans lequel il explorait les qualités nécessaires pour être un bon roi selon les principes stoïciens. Pour lui, un dirigeant idéal devait être vertueux, rationnel et guidé par l'intérêt général plutôt que par des désirs égoïstes. &lt;/p&gt; &lt;p&gt; Contrairement à certains philosophes qui se concentraient sur des débats théoriques, il insistait sur l'importance de vivre selon les principes stoïciens dans la vie quotidienne.Il a critiqué la poursuite des plaisirs, une idée qui rejoint l'enseignement stoïcien selon lequel les plaisirs corporels et matériels sont des distractions par rapport à la vertu et à la raison. Il a soutenu que le bonheur véritable ne peut être trouvé que dans la sagesse et la maîtrise de soi. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F51" s="7" t="s">
         <v>416</v>
@@ -5829,10 +5866,7 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sextus_Empiricus"  title=" Wikipedia"&gt;Sextus EMPIRICUS&lt;/a&gt;  était un philosophe et médecin grec et  une figure importante du scepticisme, souvent appelé "pyrrhonisme" en référence à Pyrrhon d'Élis. Contrairement à d'autres formes de scepticisme, qui peuvent aboutir à une négation de la possibilité de connaître la vérité, le &lt;a href="https://www.youtube.com/watch?v=Xvgfo_ADlPM"  title=" Sextus Empiricus, Esquisses pyrrhoniennes, Ne rien affirmer et l'enseignement inexistant par Koalemos"&gt;pyrrhonisme&lt;/a&gt; propose de suspendre tout jugement sur la nature ultime des choses, car il considère que les arguments pour et contre toute proposition sont également convaincants. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2002_num_100_4_7456_t1_0797_0000_2" title="Sextus Empiricus, Esquisses pyrrhoniennes. Introduction, traduction et commentaires par Pierre Pellegrin par Persée"&gt;"Les Esquisses pyrrhoniennes"&lt;/a&gt;, il présente une introduction systématique au scepticisme pyrrhonien. L'ouvrage est divisé en trois livres : &lt;/p&gt; 
-&lt;p&gt; - Livre I : Il expose les principes fondamentaux du scepticisme, y compris la distinction entre le scepticisme pyrrhonien et d'autres formes de scepticisme, comme celui de l'Académie. Il explique également les concepts clés tels que l'épochè (suspension du jugement), les tropes (modes d'argumentation sceptique), et l'ataraxie. &lt;/p&gt; 
-&lt;p&gt; - Livre II : Il traite de la critique sceptique des dogmatismes philosophiques, en particulier dans les domaines de la logique, de la physique et de l'éthique. Il montre comment les arguments des dogmatiques peuvent être contredits, ce qui justifie la suspension du jugement. &lt;/p&gt; 
-&lt;p&gt; - Livre III : Il approfondit la critique des dogmatismes, en se concentrant sur des questions spécifiques comme la causalité, la divinité, et la nature du bien et du mal. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/spira_0994-3722_2007_num_39_1_1264_t14_0182_0000_2" style="color:#88A1E9" title=" Sur le Contre les professeurs de Sextus Empiricus par Persée"&gt;"Contre les professeurs"&lt;/a&gt;, il s'attaque à diverses disciplines intellectuelles de son époque, notamment la grammaire, la rhétorique, la géométrie, l'arithmétique, l'astronomie et la musique. Il soutient qu'elles ne peuvent pas prétendre à une connaissance certaine ou absolue. Son but est de montrer que les prétentions à la vérité dans ces domaines sont infondées. &lt;/p&gt; &lt;p&gt; Il  est également connu pour avoir systématisé &lt;a href="https://hal.science/hal-03091658v1/document" style="color:#88A1E9" title=" Sextus Empiricus et les tropes par Hall science"&gt;les "tropes"&lt;/a&gt;, des arguments ou modes de raisonnement qui justifient la suspension du jugement. Ce sont des outils dialectiques qui montrent comment les perceptions et les jugements varient selon les circonstances, les individus, les cultures, etc. &lt;/p&gt; &lt;p&gt;Ses écrits ont été redécouverts à la Renaissance et ont joué un rôle clé dans le développement de la pensée sceptique moderne, influençant des philosophes comme Montaigne, Descartes et Hume. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sextus_Empiricus"  title=" Wikipedia"&gt;Sextus EMPIRICUS&lt;/a&gt;  était un philosophe et médecin grec et  une figure importante du scepticisme, souvent appelé "pyrrhonisme" en référence à Pyrrhon d'Élis. Contrairement à d'autres formes de scepticisme, qui peuvent aboutir à une négation de la possibilité de connaître la vérité, le &lt;a href="https://www.youtube.com/watch?v=Xvgfo_ADlPM"  title=" Sextus Empiricus, Esquisses pyrrhoniennes, Ne rien affirmer et l'enseignement inexistant par Koalemos"&gt;pyrrhonisme&lt;/a&gt; propose de suspendre tout jugement sur la nature ultime des choses, car il considère que les arguments pour et contre toute proposition sont également convaincants. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2002_num_100_4_7456_t1_0797_0000_2" title="Sextus Empiricus, Esquisses pyrrhoniennes. Introduction, traduction et commentaires par Pierre Pellegrin par Persée"&gt;"Les Esquisses pyrrhoniennes"&lt;/a&gt;, il présente une introduction systématique au scepticisme pyrrhonien. L'ouvrage est divisé en trois livres : &lt;/p&gt; &lt;p&gt;Livre I : Il expose les principes fondamentaux du scepticisme, y compris la distinction entre le scepticisme pyrrhonien et d'autres formes de scepticisme, comme celui de l'Académie. Il explique également les concepts clés tels que l'épochè (suspension du jugement), les tropes (modes d'argumentation sceptique), et l'ataraxie. &lt;/p&gt; &lt;p&gt;Livre II : Il traite de la critique sceptique des dogmatismes philosophiques, en particulier dans les domaines de la logique, de la physique et de l'éthique. Il montre comment les arguments des dogmatiques peuvent être contredits, ce qui justifie la suspension du jugement. &lt;/p&gt; &lt;p&gt;Livre III : Il approfondit la critique des dogmatismes, en se concentrant sur des questions spécifiques comme la causalité, la divinité, et la nature du bien et du mal. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/spira_0994-3722_2007_num_39_1_1264_t14_0182_0000_2" style="color:#88A1E9" title=" Sur le Contre les professeurs de Sextus Empiricus par Persée"&gt;"Contre les professeurs"&lt;/a&gt;, il s'attaque à diverses disciplines intellectuelles de son époque, notamment la grammaire, la rhétorique, la géométrie, l'arithmétique, l'astronomie et la musique. Il soutient qu'elles ne peuvent pas prétendre à une connaissance certaine ou absolue. Son but est de montrer que les prétentions à la vérité dans ces domaines sont infondées. &lt;/p&gt; &lt;p&gt; Il  est également connu pour avoir systématisé &lt;a href="https://hal.science/hal-03091658v1/document" style="color:#88A1E9" title=" Sextus Empiricus et les tropes par Hall science"&gt;les "tropes"&lt;/a&gt;, des arguments ou modes de raisonnement qui justifient la suspension du jugement. Ce sont des outils dialectiques qui montrent comment les perceptions et les jugements varient selon les circonstances, les individus, les cultures, etc. &lt;/p&gt; &lt;p&gt;Ses écrits ont été redécouverts à la Renaissance et ont joué un rôle clé dans le développement de la pensée sceptique moderne, influençant des philosophes comme Montaigne, Descartes et Hume. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F57" s="7" t="s">
@@ -5968,8 +6002,10 @@
       <c r="D60" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E60" s="12" t="s">
-        <v>490</v>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Posidonios"  title=" Wikipedia"&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770"  title="Posidonius d'Apamée théoricien de la géométrie par Persée"&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href="https://www.youtube.com/watch?v=EqU-kD8dW4Y" title="Grèce antique - 33 La civilisation hellénistique par Yannick Rub"&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289"  title="La philosophiede Posidonius par Persee"&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt;  </t>
+        </is>
       </c>
       <c r="F60" s="7" t="s">
         <v>491</v>
@@ -6062,8 +6098,14 @@
       <c r="D62" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="E62" s="9" t="s">
-        <v>508</v>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron"  style="color:#6A142A"  title=" Wikipedia"&gt; Marcus CICERON&lt;/a&gt; était un philosophe &lt;a href="https://fr.wiktionary.org/wiki/%C3%A9clectique"  style="color:#88A1E9"  title="L'éclectisme par Wiktionnaire"&gt;Électique&lt;/a&gt; Romain et le premier a rédiger en latin des ouvrages à une époque où le grec domine dans le monde intellectuel. Il est l'héritier d'une triple tradition : sceptique, stoïcienne et platonicienne. &lt;/p&gt; &lt;p&gt; 
+On connait sa théorie de la "nature humaine" qui selon lui est orientée vers la recherche du bien car les êtres humains sont naturellement doués d'une raison qui leur permet de discerner le bien du mal. Il a écrit de nombreux traités philosophiques, dont &lt;a href="https://fr.wikipedia.org/wiki/De_finibus_bonorum_et_malorumf"  title="bien et maux par wikipedia"&gt;De Finibus Bonorum et Malorum&lt;/a&gt; (Sur les fins ultimes du bien et du mal) ainsi que "De Oratore", qui décrit l'art de la persuasion et la façon dont il peut être utilisé pour influencer les autres. &lt;/p&gt; &lt;p&gt;  
+Il était un défenseur de la République romaine et pensait que le gouvernement devait être fondé sur des principes de justice et d'équité et que les citoyens devaient avoir le droit de participer aux décisions qui affectent leur vie. Il a écrit &lt;a href="https://www.youtube.com/watch?v=QNGtL85-rNg&amp;ab_channel=H%C3%A9rodeAtticus"  style="color:#88A1E9"  title="L'a carrière politique par Herode Atticus"&gt;De Republica&lt;/a&gt; (Sur la République), qui décrit les principes de gouvernement et d'organisation politique qu'il croyait être essentiels à une société juste et équilibrée. Il a soutenu que de la vertu comme la prudence, la justice, la tempérance et le courage sont la source ultime du bonheur et qu'on doit les cultiver pour réaliser leur plein potentiel en tant qu'êtres humains. &lt;/p&gt; &lt;p&gt; 
+Malheureusement, lorsque Marc Antoine a pris le pouvoir à Rome; il a été déclaré ennemi de l'État et a été exécuté peu de temps après.  &lt;/p&gt;   &lt;audio controls title="L'art de persuader par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23118-25.05.2022-ITEMA_23037575-2022C12410S0145-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F62" s="7" t="s">
         <v>509</v>
@@ -6158,16 +6200,11 @@
       <c r="E64" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89n%C3%A9sid%C3%A8me"  style="color:#6A142A"  title=" Wikipedia"&gt;ÉNÉSIDÈME&lt;/a&gt; était un philosophe grec de la tradition sceptique.  Il vécu à une époque où le &lt;a href="https://www.youtube.com/watch?v=_En3Pz6sWL8" style="color:#88A1E9" title="Scepticisme et interpedendance par PHILOSOPHIA"&gt;scepticisme&lt;/a&gt; philosophique était en plein essor, en réaction aux dogmatismes des écoles philosophiques comme le stoïcisme et l'épicurisme.  &lt;/p&gt; &lt;p&gt; Il a systématisé les  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1918_num_20_2_2006" style="color:#88A1E9" title="Pour l'histoire du scepticisme antique : les tropes d'Énésidème contre la logique inductive par Persée"&gt;arguments sceptiques&lt;/a&gt; dans ce qu'on appelle les &lt;a href="https://guykarl.canalblog.com/archives/2012/08/31/25001663.html" style="color:#88A1E9" title="PYRRHONISME : les dix tropes d' ENESIDEME par Le jardin Philosophe"&gt;"Dix Modes"&lt;/a&gt;, qui visent à montrer que nos perceptions et nos jugements sont influencés par divers facteurs, rendant impossible l'accès à une connaissance certaine : &lt;/p&gt;
-&lt;p&gt; - La diversité des animaux : Les espèces perçoivent le monde de manière différente, ce qui suggère que nos perceptions ne reflètent pas nécessairement la réalité objective. &lt;/p&gt;
-&lt;p&gt; - La diversité des humains : Parmi les humains, les perceptions et les jugements varient considérablement, ce qui rend difficile de déterminer quelle perception est "correcte". &lt;/p&gt; 
-&lt;p&gt; - La diversité des sens : Les différents sens peuvent donner des informations contradictoires sur un même objet. &lt;/p&gt;
-&lt;p&gt; - Les circonstances : Les conditions dans lesquelles nous percevons quelque chose peuvent influencer notre perception. &lt;/p&gt;
-&lt;p&gt; - Les positions et distances : La position et la distance par rapport à un objet peuvent altérer notre perception de celui-ci. &lt;/p&gt; 
-&lt;p&gt; - Les mélanges : Les objets ne sont jamais perçus isolément, mais toujours dans un contexte qui peut influencer notre perception. &lt;/p&gt;
-&lt;p&gt; - Les quantités et constitutions : La quantité et la composition d'un objet peuvent affecter la manière dont nous le percevons. &lt;/p&gt; 
-&lt;p&gt; - La relation : Tout est perçu en relation avec autre chose, ce qui rend difficile de connaître la nature intrinsèque d'un objet.&lt;/p&gt; 
-&lt;p&gt; -  La fréquence ou la rareté : La fréquence avec laquelle nous rencontrons quelque chose peut influencer notre perception de sa valeur ou de sa nature. &lt;/p&gt; 
-&lt;p&gt; - Les coutumes et les croyances : Les habitudes culturelles et les croyances peuvent profondément influencer nos perceptions et nos jugements. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Ses arguments mettent en lumière les limites de notre capacité à connaître le monde de manière certaine et nous invitent à adopter une attitude plus humble et critique face à nos propres perceptions et jugements. &lt;/p&gt; </t>
+&lt;p&gt;La diversité des animaux : Les espèces perçoivent le monde de manière différente, ce qui suggère que nos perceptions ne reflètent pas nécessairement la réalité objective. &lt;/p&gt;
+&lt;p&gt;La diversité des humains : Parmi les humains, les perceptions et les jugements varient considérablement, ce qui rend difficile de déterminer quelle perception est "correcte". &lt;/p&gt; &lt;p&gt;La diversité des sens : Les différents sens peuvent donner des informations contradictoires sur un même objet. &lt;/p&gt;
+&lt;p&gt;Les circonstances : Les conditions dans lesquelles nous percevons quelque chose peuvent influencer notre perception. &lt;/p&gt;
+&lt;p&gt;Les positions et distances : La position et la distance par rapport à un objet peuvent altérer notre perception de celui-ci. &lt;/p&gt; &lt;p&gt;Les mélanges : Les objets ne sont jamais perçus isolément, mais toujours dans un contexte qui peut influencer notre perception. &lt;/p&gt;
+&lt;p&gt;Les quantités et constitutions : La quantité et la composition d'un objet peuvent affecter la manière dont nous le percevons. &lt;/p&gt; &lt;p&gt;La relation : Tout est perçu en relation avec autre chose, ce qui rend difficile de connaître la nature intrinsèque d'un objet.&lt;/p&gt; &lt;p&gt;La fréquence ou la rareté : La fréquence avec laquelle nous rencontrons quelque chose peut influencer notre perception de sa valeur ou de sa nature. &lt;/p&gt; &lt;p&gt;Les coutumes et les croyances : Les habitudes culturelles et les croyances peuvent profondément influencer nos perceptions et nos jugements. &lt;/p&gt; &lt;p&gt; Ses arguments mettent en lumière les limites de notre capacité à connaître le monde de manière certaine et nous invitent à adopter une attitude plus humble et critique face à nos propres perceptions et jugements. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F64" s="7" t="s">
@@ -6211,8 +6248,11 @@
       <c r="D65" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="E65" s="9" t="s">
-        <v>533</v>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philon_d%27Alexandrie"  style="color:#6A142A"  title=" Wikipedia"&gt;PHILON d'Alexandrie&lt;/a&gt;  était un philosophe juif hellénisé qui d'harmonisa la philosophie grecque, en particulier le platonisme et le stoïcisme, avec les enseignements de la Bible hébraïque. &lt;/p&gt; &lt;p&gt; Il a écrit de nombreux traités et des commentaires allégoriques sur les livres de la Torah et a interprété les textes bibliques à travers le prisme de la philosophie grecque, cherchant à dégager des significations philosophiques et morales profondes. Dans son œuvre &lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1962_num_161_1_7742" style="color:#88A1E9" title="Philon d'Alexandrie, De opificio mundi par Persée"&gt;"De Opificio Mundi"&lt;/a&gt;, il explore la Genèse en utilisant des concepts platoniciens. &lt;/p&gt; &lt;p&gt; Il tente de montrer que les enseignements de la Torah sont en harmonie avec les idées des grands philosophes grecs. Certaines de ses œuvres défendent la religion juive contre les critiques des païens et des autres philosophes. Par exemple, dans  &lt;a href="https://www.persee.fr/doc/rjuiv_0484-8616_1968_num_127_1_1588 " style="color:#88A1E9" title="        Schadenfreude chez Philon d'Alexandrie ? Note sur In Flaccum  par Persée"&gt;"Contre Flaccus"&lt;/a&gt; et "L'Ambassade à Gaius", il décrit les persécutions subies par les Juifs d'Alexandrie et plaide pour leurs droits. &lt;/p&gt; &lt;p&gt; Il est souvent considéré comme un précurseur de la philosophie religieuse et de la théologie mystique. &lt;/p&gt; &lt;p&gt;Dieu et le Logos : Il décrit Dieu comme transcendant et inconnaissable, mais il introduit également le concept du Logos comme un intermédiaire entre Dieu et le monde. Le Logos est à la fois la raison divine qui ordonne l'univers et le moyen par lequel Dieu interagit avec le monde. &lt;/p&gt;
+&lt;p&gt;Allégorie : Il utilise largement l'interprétation allégorique pour expliquer les textes bibliques. Il croit que les récits bibliques ont un sens littéral, mais aussi un sens spirituel plus profond qui peut être découvert par l'interprétation philosophique. &lt;/p&gt; &lt;p&gt;Éthique et Vertu : Il insiste sur l'importance de la vertu et de la vie morale. Il croit que l'étude de la philosophie et la pratique des vertus permettent à l'âme de se rapprocher de Dieu. &lt;/p&gt; &lt;p&gt; Bien qu'il soit resté fidèle au judaïsme, sa pensée a eu une influence significative sur les premiers penseurs chrétiens, tels que Clément d'Alexandrie et Origène. Son concept du Logos a notamment influencé la christologie chrétienne. &lt;/p&gt; &lt;p&gt; </t>
+        </is>
       </c>
       <c r="F65" s="7" t="s">
         <v>534</v>
@@ -6260,7 +6300,7 @@
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que" title=" Wikipedia"&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href="https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Stoïcisme par le Précepteur"&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=J3wZoqElCgs" title="Who is Seneca par Daily Stoic "&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href="https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin" title="La vie Heureuse par Karl Baudoin"&gt; "une vie heureuse".&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : - De la brièveté de la vie (consideration sur l’usage du temps). - De la colère (sur la maîtrise de cette passion destructive). - De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt; Sénèque est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href="https://www.youtube.com/watch?v=d_cge9OwVAs" title="La vie philosophique de Sénèque par Kosmos"&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title="Les lettres à Lucilius – Senèque  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que" title=" Wikipedia"&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href="https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Stoïcisme par le Précepteur"&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=J3wZoqElCgs" title="Who is Seneca par Daily Stoic "&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href="https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin" title="La vie Heureuse par Karl Baudoin"&gt; "une vie heureuse".&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : De la brièveté de la vie (consideration sur l’usage du temps). De la colère (sur la maîtrise de cette passion destructive). De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt; Sénèque est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href="https://www.youtube.com/watch?v=d_cge9OwVAs" title="La vie philosophique de Sénèque par Kosmos"&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title="Les lettres à Lucilius – Senèque  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
@@ -6358,7 +6398,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apollonios_de_Tyane"  style="color:#6A142A"  title=" Wikipedia"&gt; Apollonios de Tyane&lt;/a&gt;, né à Tyane en Cappadoce (Turquie),   est une figure emblématique de l’Antiquité, à la croisée de la philosophie, de la spiritualité et du mysticisme, souvent décrit comme un philosophe, thaumaturge et ascète.  Il est principalement associé au &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_pythagoricienne" title="Phytagorisme par wikipedia "&gt; pythagorisme&lt;/a&gt;, un courant philosophique inspiré des enseignements de Pythagore, pratique et ascétique, visant à transformer la vie par des principes éthiques rigoureux et une quête de sagesse. Il prônait une vie fondée sur la pureté, la discipline et l’harmonie universelle,  adoptant un mode de vie ascétique caractérisé par le végétarisme, l’abstinence de vin et un dévouement à la recherche de la sagesse. &lt;/p&gt;  &lt;p&gt;   Comme de nombreux philosophes de son temps, il a entrepris de longs voyages pour acquérir des connaissances. Il se rendit notamment en Égypte, en Inde, en Mésopotamie et en Grèce. En Inde, il aurait rencontré des sages et des brahmanes qui auraient influencé sa pensée, assimilant et intégrant à sa pensée des éléments de traditions diverses.  &lt;/p&gt; &lt;p&gt; Au cours des siècles, il a souvent été comparé à Jésus-Christ, en raison des similitudes perçues entre leurs vies (miracles, ascétisme, message spirituel). Certains penseurs païens de l'Antiquité ont même présenté &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1999_num_1_3_1959" style="color:#88A1E9" title="Mythe avorté d'une sagesse totale par Persée "&gt; Apollonios&lt;/a&gt; comme une alternative païenne à Jésus, bien que les deux figures soient très différentes dans leur contexte et leur message. &lt;/p&gt; &lt;p&gt;Il incarte une forme de tolérance religieuse cosidérant que l'on peut reconnaitre sa religion dans la religion de l'autre.&lt;/p&gt; &lt;p&gt;  Sa vie, relatée par &lt;a href="https://fr.wikipedia.org/wiki/Philostrate_d%27Ath%C3%A8nes" style="color:#88A1E9" title="Philostrate par Wikipedia "&gt; Philostrate&lt;/a&gt; dans  &lt;a href="https://fr.wikipedia.org/wiki/Vie_d%27Apollonios_de_Tyane" style="color:#88A1E9" title="Vie d'Apollonios de Tyare par Wikipedia "&gt; Vie d’Apollonios de Tyane&lt;/a&gt;, mêle éléments historiques et légendaires. Profondément spirituel, il prônait une piété réfléchie et critiquait les pratiques religieuses vides de sens, notamment les sacrifices sanglants, préférant une relation intérieure avec le divin et des rituels plus éthiques. Convaincu de l’immortalité de l’âme et de la réincarnation, il voyait la philosophie comme une voie vers la purification spirituelle et morale. &lt;/p&gt; &lt;p&gt;Son engagement ne se limitait pas à la sphère personnelle : il joua un rôle actif dans la société en critiquant les tyrans, en défendant la justice et en conseillant les gouvernants. Considéré par ses contemporains comme un thaumaturge, il aurait accompli des miracles tels que des guérisons, des prédictions et des résurrections, bien que ces récits soient teintés de légende. Sa pensée et sa vie incarnaient une quête universelle de vérité et d'harmonie, cherchant à unifier les enseignements philosophiques et spirituels dans une vision globale.&lt;/p&gt; &lt;p&gt; Apollonios demeure une figure complexe, à mi-chemin entre le philosophe et le sage mystique, dont l'héritage, bien que controversé, continue d'inspirer les amateurs de sagesse antique. &lt;/p&gt;   
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apollonios_de_Tyane"  style="color:#6A142A"  title=" Wikipedia"&gt; Apollonios de Tyane&lt;/a&gt;, né à Tyane en Cappadoce (Turquie),   est une figure emblématique de l’Antiquité, à la croisée de la philosophie, de la spiritualité et du mysticisme, souvent décrit comme un philosophe, thaumaturge et ascète.  Il est principalement associé au &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_pythagoricienne" title="Phytagorisme par wikipedia "&gt; pythagorisme&lt;/a&gt;, un courant philosophique inspiré des enseignements de Pythagore, pratique et ascétique, visant à transformer la vie par des principes éthiques rigoureux et une quête de sagesse. Il prônait une vie fondée sur la pureté, la discipline et l’harmonie universelle,  adoptant un mode de vie ascétique caractérisé par le végétarisme, l’abstinence de vin et un dévouement à la recherche de la sagesse. &lt;/p&gt; &lt;p&gt;   Comme de nombreux philosophes de son temps, il a entrepris de longs voyages pour acquérir des connaissances. Il se rendit notamment en Égypte, en Inde, en Mésopotamie et en Grèce. En Inde, il aurait rencontré des sages et des brahmanes qui auraient influencé sa pensée, assimilant et intégrant à sa pensée des éléments de traditions diverses.  &lt;/p&gt; &lt;p&gt; Au cours des siècles, il a souvent été comparé à Jésus-Christ, en raison des similitudes perçues entre leurs vies (miracles, ascétisme, message spirituel). Certains penseurs païens de l'Antiquité ont même présenté &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1999_num_1_3_1959" style="color:#88A1E9" title="Mythe avorté d'une sagesse totale par Persée "&gt; Apollonios&lt;/a&gt; comme une alternative païenne à Jésus, bien que les deux figures soient très différentes dans leur contexte et leur message. &lt;/p&gt; &lt;p&gt;Il incarte une forme de tolérance religieuse cosidérant que l'on peut reconnaitre sa religion dans la religion de l'autre.&lt;/p&gt; &lt;p&gt;  Sa vie, relatée par &lt;a href="https://fr.wikipedia.org/wiki/Philostrate_d%27Ath%C3%A8nes" style="color:#88A1E9" title="Philostrate par Wikipedia "&gt; Philostrate&lt;/a&gt; dans  &lt;a href="https://fr.wikipedia.org/wiki/Vie_d%27Apollonios_de_Tyane" style="color:#88A1E9" title="Vie d'Apollonios de Tyare par Wikipedia "&gt; Vie d’Apollonios de Tyane&lt;/a&gt;, mêle éléments historiques et légendaires. Profondément spirituel, il prônait une piété réfléchie et critiquait les pratiques religieuses vides de sens, notamment les sacrifices sanglants, préférant une relation intérieure avec le divin et des rituels plus éthiques. Convaincu de l’immortalité de l’âme et de la réincarnation, il voyait la philosophie comme une voie vers la purification spirituelle et morale. &lt;/p&gt; &lt;p&gt;Son engagement ne se limitait pas à la sphère personnelle : il joua un rôle actif dans la société en critiquant les tyrans, en défendant la justice et en conseillant les gouvernants. Considéré par ses contemporains comme un thaumaturge, il aurait accompli des miracles tels que des guérisons, des prédictions et des résurrections, bien que ces récits soient teintés de légende. Sa pensée et sa vie incarnaient une quête universelle de vérité et d'harmonie, cherchant à unifier les enseignements philosophiques et spirituels dans une vision globale.&lt;/p&gt; &lt;p&gt; Apollonios demeure une figure complexe, à mi-chemin entre le philosophe et le sage mystique, dont l'héritage, bien que controversé, continue d'inspirer les amateurs de sagesse antique. &lt;/p&gt;   
 </t>
         </is>
       </c>
@@ -6403,8 +6443,10 @@
       <c r="D69" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="E69" s="9" t="s">
-        <v>570</v>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Plutarque"  style="color:#6A142A"  title=" Wikipedia"&gt;PLUTARQUE&lt;/a&gt; était un philosophe, biographe et moraliste grec  célèbre pour ses &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1979_num_1_3_3621"  style="color:#88A1E9" title="La pensée de Plutarque dans les Vies  par Olivier Roland"&gt;œuvres&lt;/a&gt;  biographiques et philosophiques. Il  a vécu à une époque où la Grèce était sous domination romaine, mais la culture grecque restait très influente dans l'Empire. &lt;/p&gt;Philosophe éclectique profondément influencé par le platonisme, il croyait en l'importance de la vertu, de la modération et de la recherche de la sagesse. Il insiste sur la nécessité de vivre une vie vertueuse et équilibrée et aborde des thèmes comme la colère, la jalousie, et la manière de cultiver la paix intérieure. Il s'intéresse aux croyances religieuses et aux mythes, cherchant souvent à en donner une interprétation morale ou philosophique.&lt;p&gt; Il  est surtout connu pour deux collections d'œuvres : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=cOdbv-wbRWQ&amp;t=10s"  style="color:#88A1E9" title="Les Vies Parallèles des Hommes Illustres de Plutarque par Olivier Roland"&gt;Vies parallèles&lt;/a&gt; : Cette série de biographies compare des figures célèbres de l'histoire grecque et romaine. Chaque paire de vies met en parallèle un Grec et un Romain, suivie d'une comparaison qui souligne les similitudes et les différences entre les deux personnages. Parmi les paires les plus connues, on trouve Alexandre le Grand et Jules César, Thésée et Romulus, ou encore Démosthène et Cicéron. Son objectif  n'était pas seulement historique, mais aussi moral et éducatif. &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C5%92uvres_morales"  style="color:#88A1E9" title="Œuvres morales par Wikipedia"&gt;Moralia&lt;/a&gt;  : Cette collection regroupe des essais et des traités sur des sujets variés, allant de la philosophie morale à la religion, en passant par la politique, l'éducation et les sciences naturelles, la tranquillité de l'âme, l'amour, la superstition. &lt;/p&gt; &lt;p&gt; Il est connu pour son &lt;a href="https://www.youtube.com/watch?v=n7uLx5rVmm0"  style="color:#88A1E9" title="La Sérénité intérieure | PLUTARQUE  par Les Choses au Claire"&gt;style clair&lt;/a&gt; et accessible, qui combine profondeur philosophique et récit vivant. Ses biographies sont à la fois instructives et divertissantes, mêlant anecdotes, réflexions morales et détails historiques. Il  reste une figure majeure de la littérature et de la philosophie antique. Ses œuvres, à la fois biographiques et philosophiques, continuent d'être étudiées et appréciées pour leur richesse, leur sagesse et leur pertinence intemporelle. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title="  Actualité de Plutarque par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16278-17.12.2016-ITEMA_21168598-2016C6278E0292-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F69" s="7" t="s">
         <v>571</v>
@@ -6688,8 +6730,11 @@
       <c r="D75" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="E75" s="9" t="s">
-        <v>617</v>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Longin_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;LONGIN&lt;/a&gt; était un philosophe, rhéteur et critique littéraire grec de l'Antiquité tardive. Bien que sa vie et son œuvre soient peu documentée, il est connu pour son traité &lt;a href="https://remacle.org/bloodwolf/erudits/longin/sublime.htm" style="color:#88A1E9" title=" Login : traite du sublime par Remacle"&gt;"Du Sublime"&lt;/a&gt;, un texte majeur sur l'esthétique et la rhétorique. Ce texte explore la notion de sublime, un concept esthétique qui désigne ce qui élève l'âme, inspire l'admiration et transcende le banal. Le sublime se manifeste dans la littérature, l'art et la rhétorique, et il est souvent associé à la grandeur, à l'intensité émotionnelle et à la puissance expressive. Ses principales idées : &lt;p&gt; 
+&lt;p&gt;Le sublime est une qualité qui transcende la simple beauté ou l'élégance. Il provoque une émotion intense et une élévation spirituelle chez le lecteur ou l'auditeur. Il se manifeste dans des œuvres qui inspirent l'admiration, la crainte ou l'émerveillement. &lt;/p&gt; &lt;p&gt;Sources du sublime : Il identifie cinq sources principales du sublime : &lt;/p&gt; &lt;p&gt;La grandeur de la pensée : des idées profondes et élevées. &lt;/p&gt; &lt;p&gt;L'émotion intense : la capacité à toucher les sentiments du public. &lt;/p&gt; &lt;p&gt;Les figures de style : l'utilisation habile de métaphores, d'hyperboles, etc. &lt;/p&gt; &lt;p&gt;La noblesse de l'expression : un langage élégant et approprié. &lt;/p&gt; &lt;p&gt;La structure et l'arrangement : une composition harmonieuse et puissante. &lt;/p&gt; &lt;p&gt; Son analyse des techniques littéraires et de l'impact émotionnel de la parole a influencé la théorie rhétorique. "Du Sublime" est l'un des premiers textes à aborder la critique littéraire sous un angle esthétique et psychologique, en se concentrant sur l'effet des œuvres sur le public. Bien que sa vie soit mal documentée, son influence sur la pensée occidentale, en particulier dans les domaines de l'esthétique et de la rhétorique, est indéniable. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F75" s="7" t="s">
         <v>618</v>
@@ -6732,8 +6777,10 @@
       <c r="D76" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="E76" s="9" t="s">
-        <v>625</v>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Porphyre_de_Tyr"  style="color:#6A142A"  title=" Wikipedia"&gt;PORPHYRE de Tyr&lt;/a&gt; était un philosophe néoplatonicien romain, érudit et polémiste d'origine phénicienne, né à Tyr, dans l'actuel Liban. Il est surtout connu pour son rôle dans le développement et la diffusion de la philosophie néoplatonicienne, ainsi que pour ses critiques du christianisme. Il est né sous le nom de Malchus (qui signifie "roi" en phénicien), mais il a adopté le nom de Porphyre (du grec porphyra, "pourpre", en référence à la pourpre tyrienne, une teinture prestigieuse produite dans sa ville natale). &lt;/p&gt; &lt;p&gt; Il est surtout connu pour avoir édité et publié les &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1924_num_22_5_5497"  style="color:#88A1E9" title="Les Ennéades de Plotin par Persée"&gt;Ennéades de Plotin&lt;/a&gt;, une collection systématique des écrits de son maître. Ses propres contributions philosophiques  : &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isagog%C3%A8"  style="color:#88A1E9" title="Isagogè par Wikipedia"&gt;L'Isagogè&lt;/a&gt; : Une introduction aux Catégories d'Aristote, qui est devenue un texte fondamental dans l'enseignement de la logique médiévale, tant dans le monde islamique qu'en Europe. &lt;/p&gt; &lt;p&gt;Commentaires sur Aristote et Platon : Porphyre a écrit des commentaires sur les œuvres d'Aristote et de Platon, cherchant à harmoniser leurs philosophies. &lt;/p&gt; &lt;p&gt;Philosophie religieuse : Il a exploré des thèmes comme la nature de l'âme, la purification spirituelle et la relation entre l'homme et le divin. &lt;/p&gt; &lt;p&gt; Il  est également connu pour son ouvrage &lt;a href="https://www.persee.fr/doc/reg_0035-2039_2014_num_127_2_8359_t16_0629_0000_2"  style="color:#88A1E9" title=" Le traité de Porphyre contre les chrétiens  par Persée"&gt;"Contre les chrétiens"&lt;/a&gt;, une critique virulente du christianisme naissant. Dans ce texte, il attaquait les doctrines chrétiennes, les Écritures et la figure de Jésus, qu'il considérait comme un personnage historique plutôt que divin. Malheureusement, l'ouvrage n'a survécu qu'à travers des citations et des réfutations par des auteurs chrétiens comme Eusèbe de Césarée et Augustin d'Hippone. &lt;/p&gt; &lt;p&gt; Porphyre de Tyr est une figure majeure de la philosophie antique, dont l'œuvre a servi de pont entre la pensée grecque classique et les développements intellectuels ultérieurs. Son engagement envers le néoplatonisme, ses contributions à la logique et ses critiques du christianisme en font un penseur complexe et influent, dont l'héritage continue d'être étudié et débattu. &lt;/p&gt;  &lt;/p&gt;   &lt;audio controls title=" Une histoire philosophique, feat. Porphyre et Jamblique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16260-13.03.2021-ITEMA_22601996-2021C6260S0072.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F76" s="7" t="s">
         <v>626</v>
@@ -6825,10 +6872,7 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marius_Victorinus"  style="color:#6A142A"  title=" Wikipedia"&gt;Marius VICTORINUS&lt;/a&gt; était un philosophe, africain de naissance puis romain enseignant la rhétorique et la philosophie.  Il s'est converti au Christianisme après avoir étudié les Écritures. Sa conversion a été perçue comme un symbole de la capacité du christianisme à attirer même les intellectuels les plus érudits. Il  a laissé une œuvre variée, à la fois philosophique et  &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1957_num_70_66_20268" style="color:#88A1E9" title=" Oeuvres théologiques de Marius Victorinus par Persée"&gt;théologique. &lt;/a&gt;&lt;p&gt; - Avant sa conversion :  Il a écrit des commentaires sur des textes philosophiques grecs, notamment ceux d'Aristote et de Platon. Ces travaux montrent sa maîtrise de la philosophie néoplatonicienne, qui a profondément influencé sa pensée.  Il a traduit et adapté des œuvres néoplatoniciennes, comme celles de Plotin et de Porphyre, contribuant à diffuser ces idées dans le monde latin. &lt;/p&gt; &lt;p&gt; -  Après sa conversion :  Il s'est concentré sur des questions théologiques, en particulier sur la Trinité et la nature du Christ et de &lt;a href="https://www.youtube.com/watch?v=DCbfSqUZFs0" style="color:#88A1E9" title=" La notion de pré-étant selon Marius Victorinus  par Hervé Pasqua"&gt;l'être&lt;/a&gt;. Ses œuvres les plus importantes incluent : &lt;/p&gt; 
-&lt;dd&gt; - Adversus Arium : Une défense de l'orthodoxie nicéenne contre  &lt;a href="https://fr.wikipedia.org/wiki/Arianisme" style="color:#88A1E9" title=" Arianisme par Wikipédia"&gt;l'arianisme&lt;/a&gt;, qui niait la divinité du Christ. &lt;/dd&gt; 
-&lt;dd&gt; - De generatione divini Verbi  : Un traité sur la relation entre le Père et le Fils dans la Trinité. &lt;/dd&gt; 
-&lt;dd&gt; - De Trinitate : Une exploration approfondie de la doctrine trinitaire, influencée par la philosophie néoplatonicienne. &lt;/dd&gt;  &lt;p&gt; Son utilisation des concepts néoplatoniciens pour expliquer des doctrines chrétiennes complexes, comme la Trinité, a influencé des théologiens ultérieurs, notamment saint Augustin. Il  a également contribué à la formation d'un langage théologique latin, en adaptant des concepts philosophiques grecs à la pensée chrétienne. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marius_Victorinus"  style="color:#6A142A"  title=" Wikipedia"&gt;Marius VICTORINUS&lt;/a&gt; était un philosophe, africain de naissance puis romain enseignant la rhétorique et la philosophie.  Il s'est converti au Christianisme après avoir étudié les Écritures. Sa conversion a été perçue comme un symbole de la capacité du christianisme à attirer même les intellectuels les plus érudits. Il  a laissé une œuvre variée, à la fois philosophique et  &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1957_num_70_66_20268" style="color:#88A1E9" title=" Oeuvres théologiques de Marius Victorinus par Persée"&gt;théologique. &lt;/a&gt;&lt;p&gt;Avant sa conversion :  Il a écrit des commentaires sur des textes philosophiques grecs, notamment ceux d'Aristote et de Platon. Ces travaux montrent sa maîtrise de la philosophie néoplatonicienne, qui a profondément influencé sa pensée.  Il a traduit et adapté des œuvres néoplatoniciennes, comme celles de Plotin et de Porphyre, contribuant à diffuser ces idées dans le monde latin. &lt;/p&gt; &lt;p&gt;Après sa conversion :  Il s'est concentré sur des questions théologiques, en particulier sur la Trinité et la nature du Christ et de &lt;a href="https://www.youtube.com/watch?v=DCbfSqUZFs0" style="color:#88A1E9" title=" La notion de pré-étant selon Marius Victorinus  par Hervé Pasqua"&gt;l'être&lt;/a&gt;. Ses œuvres les plus importantes incluent : &lt;/p&gt; &lt;p&gt;Adversus Arium : Une défense de l'orthodoxie nicéenne contre  &lt;a href="https://fr.wikipedia.org/wiki/Arianisme" style="color:#88A1E9" title=" Arianisme par Wikipédia"&gt;l'arianisme&lt;/a&gt;, qui niait la divinité du Christ. &lt;/p&gt; &lt;p&gt;De generatione divini Verbi  : Un traité sur la relation entre le Père et le Fils dans la Trinité. &lt;/p&gt; &lt;p&gt;De Trinitate : Une exploration approfondie de la doctrine trinitaire, influencée par la philosophie néoplatonicienne. &lt;/p&gt; &lt;p&gt; Son utilisation des concepts néoplatoniciens pour expliquer des doctrines chrétiennes complexes, comme la Trinité, a influencé des théologiens ultérieurs, notamment saint Augustin. Il  a également contribué à la formation d'un langage théologique latin, en adaptant des concepts philosophiques grecs à la pensée chrétienne. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F78" s="7" t="s">
@@ -6918,8 +6962,10 @@
       <c r="D80" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="E80" s="9" t="s">
-        <v>658</v>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_de_Nysse"  style="color:#6A142A"  title=" Wikipedia"&gt;GRÉGOIRE de Nysse&lt;/a&gt; était un religieux et un mystique turc connu pour ses contributions à la &lt;a href="https://www.youtube.com/watch?v=-fOGBAaiNFE" style="color:#88A1E9" title="LA TRINITÉ EXPLIQUÉE  par Frere Paul Adrien"&gt;théologie trinitaire&lt;/a&gt; et à la mystique chrétienne. Il a insisté sur l'unité et l'égalité des trois personnes de la Trinité et a développé des arguments sophistiqués pour expliquer comment ils sont distinctes mais partagent une même essence divine. Il a également exploré la nature infinie de Dieu, soulignant qu'il est au-delà de toute compréhension humaine. Cette idée a influencé la tradition apophatique &lt;a href="https://www.youtube.com/watch?v=iSBm7R1Hlr4" style="color:#88A1E9" title="La théologie négative par Resonances"&gt;(ou théologie négative)&lt;/a&gt; dans le christianisme, qui soutient que Dieu ne peut être défini que par ce qu'il n'est pas. &lt;/p&gt; &lt;p&gt; Il a écrit abondamment sur la nature humaine et la destinée de l'âme  : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/scrip_0036-9772_1985_num_39_2_1409" style="color:#88A1E9" title="Deux fragments anciens (en minuscule de type « Anastase ») du De hominis opificio de Grégoire de Nysse par Persée"&gt;"De hominis opificio"&lt;/a&gt; :  il explore la création de l'homme à l'image de Dieu et la restauration de cette image à travers le Christ.&lt;/p&gt; &lt;p&gt;"La Vie de Moïse" :  il utilise l'histoire biblique de Moïse comme une allégorie pour décrire le cheminement de l'âme vers Dieu. Il décrit l'ascension spirituelle comme un processus infini, où l'âme est toujours en mouvement vers Dieu, sans jamais pouvoir l'atteindre complètement. &lt;/p&gt; &lt;p&gt;Contre Eunome : Une défense de la doctrine nicéenne contre les arguments de l'arien Eunome. &lt;/p&gt; &lt;p&gt;La Grande Catéchèse : Un exposé systématique de la foi chrétienne, destiné à l'instruction des catéchumènes. &lt;/p&gt; &lt;p&gt;Sur l'âme et la résurrection : Un dialogue sur la nature de l'âme et la résurrection, influencé par les dialogues platoniciens. &lt;/p&gt; &lt;p&gt; Il  a eu une influence durable sur la théologie chrétienne, en particulier dans les domaines de la mystique, de l'anthropologie théologique et de la doctrine trinitaire. Il est vénéré comme un saint dans les Églises catholique, orthodoxe et anglicane, et sa fête est célébrée le 9 mars dans l'Église catholique et le 10 janvier dans l'Église orthodoxe. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F80" s="7" t="s">
         <v>659</v>
@@ -6968,8 +7014,7 @@
       <c r="E81" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9lage_(h%C3%A9r%C3%A9siarque)"  style="color:#6A142A"  title=" Wikipedia"&gt;PÉLAGE&lt;/a&gt;  également connu sous le nom Pelagius en latin, était un moine et théologien britannique surtout connu pour avoir été au cœur d'une controverse théologique majeure dans l'histoire de l'Église chrétienne, connue sous le nom de &lt;a href="https://www.la-croix.com/Religion/Religion-et-spiritualite/Comprendre-pelagianisme-2018-11-17-1200983747" title="comprendre le Pélage par la Croix"&gt; pélagianisme&lt;/a&gt;. 
-Originaire des îles britanniques, actif principalement à Rome et en Afrique du Nord au début du Ve siècle, il était profondément engagé dans la vie monastique et était reconnu pour son ascétisme rigoureux. &lt;/p&gt;
-&lt;p&gt;La principale controverse associée à Pelage concernait la question de la nature du péché, de la grâce et du libre arbitre. Pelage soutenait que les êtres humains avaient la capacité intrinsèque de choisir le bien et d'éviter le péché sans l'aide de la grâce divine. Il rejetait l'idée du péché originel, enseignant que chaque personne naissait dans un état d'innocence et avait la possibilité de vivre une vie sans péché.&lt;/p&gt;
+Originaire des îles britanniques, actif principalement à Rome et en Afrique du Nord au début du Ve siècle, il était profondément engagé dans la vie monastique et était reconnu pour son ascétisme rigoureux. &lt;/p&gt; &lt;p&gt;La principale controverse associée à Pelage concernait la question de la nature du péché, de la grâce et du libre arbitre. Pelage soutenait que les êtres humains avaient la capacité intrinsèque de choisir le bien et d'éviter le péché sans l'aide de la grâce divine. Il rejetait l'idée du péché originel, enseignant que chaque personne naissait dans un état d'innocence et avait la possibilité de vivre une vie sans péché.&lt;/p&gt;
 &lt;p&gt;Ces enseignements ont été fermement contestés par des figures théologiques importantes de l'époque, notamment Augustin d'Hippone. Augustin affirmait que la nature humaine était corrompue par le péché originel et que la grâce divine était nécessaire pour la rédemption et la sanctification des individus. Il considérait les enseignements de Pelage comme hérétiques et dangereux pour la foi chrétienne. &lt;/p&gt;
 &lt;p&gt;Le &lt;a href="https://www.youtube.com/watch?v=AnKeIzmox0s" title="la victoire de st Augustin sur Pélage par Michel Onfray"&gt; débat&lt;/a&gt; entre Pelage et Augustin a finalement conduit à plusieurs conciles et décrets ecclésiastiques condamnant  le pélagianisme comme une hérésie. Malgré cela, les idées de Pelage ont continué à influencer certains courants de pensée chrétienne ou religuieux comme Fauste de Riez, et la controverse pélagienne a laissé une marque durable sur l'histoire théologique de l'Église.&lt;/p&gt;</t>
         </is>
@@ -7113,8 +7158,11 @@
       <c r="D84" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="E84" s="11" t="s">
-        <v>694</v>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Syrianos" title="Wikipedia"&gt;SYRIANOS&lt;/a&gt;  est un philosophe néoplatonicien grec, chef de l’école néoplatonicienne d’Athènes après Plutarque d’Athènes et maître de Proclus. Il appartient à la génération intermédiaire qui relie Porphyre–Jamblique à Proclus, et joue un rôle central dans la structuration théologique du néoplatonisme tardif. Formé sous Plutarque d’Athènes, Syrianos en devient le successeur comme scolarque (chef d’école) à sa mort vers 432. Il enseigne à Athènes une doctrine platonicienne fortement imprégnée de pythagorisme et de théurgie, et forme plusieurs penseurs importants, dont Hermias d’Alexandrie, Proclus et, plus tard, Marinos de Néapolis. &lt;/p&gt; &lt;p&gt; Il vise à unifier la tradition orphique, pythagoricienne, platonicienne et les « Oracles chaldaïques » en une théologie harmonieuse, en montrant que tous  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2022_num_124_2_7100_t11_0584_0000_1" title="Sur les états de cause par Persée"&gt;ces courants expriment &lt;/a&gt; fondamentalement la même vérité divine. Il articule la réalité en trois niveaux : le plan intelligible (les Formes pures), le plan discursif (le niveau intermédiaire, demiurgique, où les formes agissent comme principes), le plan sensible (le monde physique). &lt;/p&gt; Il marque une étape décisive dans la « théologisation » progressive du platonisme tardif : il privilégie la théurgie (la pratique rituelle et symbolique) autant que la simple contemplation philosophique, ce qui le rapproche de Jamblique et annonce Proclus. De nombreux penseurs ultérieurs, y compris Damascios et les auteurs de la tradition arabe et médiévale, reprennent ou transforment ses idées sur la hiérarchie des principes et la structure des niveaux de réalité. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F84" s="1" t="s">
         <v>695</v>
@@ -7156,8 +7204,11 @@
       <c r="D85" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="E85" s="17" t="s">
-        <v>701</v>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Syn%C3%A9sios_de_Cyr%C3%A8ne"   title=" Wikipédia"&gt; SYNÉSIOS de Cyrène&lt;/a&gt; était un philosophe  néoplatonicien, écrivain et évêque chrétien de la fin de l’Antiquité, originaire de Cyrène dans la Cyrénaïque (actuelle Libye). Il est connu à la fois comme  &lt;a href="https://www.youtube.com/watch?v=cPXvYhOuVwc" title="Synesius of Cyrene par Sun of Antiquity"&gt;homme de lettres &lt;/a&gt; païen‑platonicien puis comme évêque de Ptolémaïs, incarnant un cas emblématique de passage entre paganisme hellénistique et christianisme tardif. &lt;/p&gt; &lt;p&gt; Il est un chrétien platonisant : il articule la tradition néoplatonicienne (Platon, Plotin, Porphyre) avec la foi chrétienne, notamment dans ses hymnes et ses traités. Dans ses Hymnes, il célèbre Dieu comme principe suprême et source de lumière, en reprenant des images platoniciennes de l’Un et du Bien, mais dans un cadre monothéiste. Dans le Traité sur les songes (vers 403), il défend l’idée que les rêves sont des oracles véritables, à condition d’être « déchiffrés » par une intelligence philosophique et morale ; il accorde une grande importance à l’imagination et à l’âme dans la communication divine. &lt;/p&gt; &lt;p&gt; Il  joue un rôle important dans la vie politique de la Cyrénaïque : il participe à une ambassade devant l’empereur à Constantinople entre 399 et 402, où il rédige notamment le Discours sur la royauté et les Récits égyptiens, des  &lt;a href="https://www.persee.fr/doc/etaf_0768-2352_1987_mon_1_1" title="Synesios de Cyrène et la Cyrénaique du bas-empire par Persée"&gt;textes allégoriques &lt;/a&gt; qui mêlent politique, philosophie et rhétorique. &lt;/p&gt; Sa correspondance (environ 150 lettres conservées) est une source précieuse sur la vie intellectuelle et religieuse de l’Antiquité tardive, les rapports entre philosophie et foi, et le rôle de personnages comme Hypatie. Il  incarne une figure de transition entre le monde païen néoplatonicien et le christianisme tardif, unissant la rigueur philosophique, l’art rhétorique et une spiritualité syncrétique très caractéristique de son époque. &lt;/p&gt;
+</t>
+        </is>
       </c>
       <c r="F85" s="1" t="s">
         <v>702</v>
@@ -7768,8 +7819,10 @@
       <c r="D98" s="8" t="s">
         <v>802</v>
       </c>
-      <c r="E98" s="14" t="s">
-        <v>803</v>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Priscien_de_Lydie" style="color:#6A142A" title="Wikipedia"&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href="https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316" title="la géographie et les originesnéoplatonisme sur Persee"&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité : « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F98" s="7" t="s">
         <v>804</v>
@@ -7812,8 +7865,10 @@
       <c r="D99" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="E99" s="9" t="s">
-        <v>810</v>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympiodore_le_Jeune"  style="color:#6A142A"  title=" Wikipedia"&gt;OLYMPIODORE le Jeune&lt;/a&gt; était un philosophe néoplatonicien grec connu comme grand commentateur de Platon et d’Aristote, dernier représentant important de la tradition platonicienne païenne à Alexandrie. &lt;/p&gt; &lt;p&gt; Il laisse surtout des commentaires sur des dialogues de Platon : Phédon, Gorgias, Philebos et &lt;a href="https://www.youtube.com/watch?v=KauBLoVOcNs" style="color:#88A1E9" title=" hat is philosophy? Olympiodorus' Commentary on the First Alcibiades par Abbas the Alchemist"&gt;l’Alcibiade&lt;/a&gt;. Il commente également Aristote et compose une introduction à la philosophie aristotélicienne, destinée à guider les étudiants dans la lecture du Stagirite. Son style est souvent décrit comme clair et pédagogique : il systématise les thèmes, expose les objections de manière ordonnée, et adapte la tradition néoplatonicienne à un public plus large.&lt;/p&gt; &lt;p&gt; Il adhère à une hiérarchie de l’être allant de l’Un aux Intelligibles, à l’Âme et au monde sensible, mais il insiste particulièrement sur la pédagogie des vertus et de la purification de l’âme. Dans ses analyses morales, il distingue plusieurs niveaux de vertus que l’âme doit gravir pour se détacher progressivement du corps et se rapprocher du divin. Un thème marquant est son développement d’une "échelle des vertus" en sept degrés : vertus naturelles, morales, politiques, purificatrices, contemplatives, paradigmatiques et hiératiques. Les vertus politiques et purificatrices organisent la vie en société et la maîtrise des passions, tandis que les vertus contemplatives et théurgiques visent l’union de l’âme avec les réalités intelligibles et le divin. &lt;/p&gt; &lt;p&gt; Tout en restant païen, il opère une forme d’accommodement avec un environnement chrétien : il évite en général l’affrontement frontal, et certains thèmes se laissent aisément intégrer dans une culture chrétienne. Cela explique probablement que &lt;a href="https://books.openedition.org/pulg/18286?lang=fr" style="color:#88A1E9" title="  L’École d’Olympiodore et les problèmes critiques connexes par OpenEdition"&gt;son enseignement&lt;/a&gt; ait pu continuer à Alexandrie après la fermeture des grandes écoles païennes d’Athènes. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F99" s="7" t="s">
         <v>811</v>
@@ -7902,8 +7957,10 @@
       <c r="D101" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="E101" s="14" t="s">
-        <v>825</v>
+      <c r="E101" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie" title="Wikipedia"&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F101" s="7" t="s">
         <v>773</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3488,7 +3488,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chilon"  style="color:#6A142A"  title=" Wikipedia"&gt;CHILON de Sparte&lt;/a&gt; était un philosophe grec et l'un des &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2003_num_105_1_5661_t1_0315_0000_3" style="color:#88A1E9" title="Les Sept Sages de la Grèce antique par Persée"&gt;Sept Sages &lt;/a&gt; de la Grèce, un groupe de penseurs et législateurs renommés pour leur  &lt;a href="https://www.youtube.com/watch?v=gW0-ikAVNnE" style="color:#88A1E9" title="Les Sept Sages: Chilon par Karl Baudoin"&gt;sagesse pratique&lt;/a&gt;. Il incarne la sagesse pratique spartiate, centrée sur la modération et la maîtrise de soi. Ses préceptes sont souvent formulés sous forme de maximes : &lt;/p&gt; &lt;p&gt;"Connais-toi toi-même" : Bien que parfois attribué à Socrate, cette inscription du temple de Delphes aurait été popularisée par Chilon. Elle résume l'idéal de réflexion personnelle et d'humilité. &lt;/p&gt; &lt;p&gt;"La modération est la meilleure des choses" : Un appel à éviter les excès, en accord avec l'éthique spartiate de discipline. &lt;/p&gt; &lt;p&gt;"Ne ris pas de ton ennemi" : Mise en garde contre l'arrogance, soulignant que les circonstances peuvent changer. &lt;/p&gt; &lt;p&gt; En tant qu'éphore, Chilon aurait contribué à renforcer les institutions spartiates, comme la Grande Rhêtra (loi fondamentale attribuée à Lycurgue).  Il aurait conseillé la prudence dans les relations extérieures, évitant les guerres inutiles tout en consolidant la puissance de Sparte. &lt;/p&gt; &lt;p&gt;  Il représente l'idéal spartiate de sagesse appliquée, où la philosophie ne se dissocie pas de l'action politique et de la discipline personnelle. Son héritage, bien que fragmentaire, reste un pont entre la pensée archaïque grecque et la philosophie classique. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chilon"  style="color:#6A142A"  title=" Wikipedia"&gt;CHILON de Sparte&lt;/a&gt; est un homme politique et un sage spartiate du VIe siècle av. J.-C., compté parmi les &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2003_num_105_1_5661_t1_0315_0000_3" style="color:#88A1E9" title="Les Sept Sages de la Grèce antique par Persée"&gt;Sept Sages&lt;/a&gt; de la Grèce, ces penseurs et législateurs célèbres pour leur &lt;a href="https://www.youtube.com/watch?v=gW0-ikAVNnE" style="color:#88A1E9" title="Les Sept Sages: Chilon par Karl Baudoin"&gt;sagesse pratique&lt;/a&gt;. Selon Diogène Laërce, il fut éphore, l’un des cinq magistrats élus chaque année à Sparte, vers 556 av. J.-C., et l’on disait qu’il avait le premier associé les éphores aux rois dans le gouvernement de la cité.&lt;/p&gt; &lt;p&gt;Il incarne la sagesse spartiate, faite de modération, de maîtrise de soi et de brièveté : son style était si concis que l’on parlait de « manière chilonienne ». La tradition lui attribue plusieurs maximes gravées au temple d’Apollon à Delphes, dont le célèbre « Connais-toi toi-même », que l’on prête aussi à Thalès, et « Rien de trop ». D’autres préceptes lui sont attribués : « Ne dis pas de mal des morts », « Honore la vieillesse », « Maîtrise ta colère » ou « Ne te moque pas d’un homme dans le malheur ».&lt;/p&gt; &lt;p&gt;En politique, il aurait conseillé la prudence dans les relations extérieures. Hérodote rapporte qu’il jugeait dangereuse pour Sparte l’île de Cythère, si proche de ses côtes, au point de souhaiter qu’elle soit engloutie par la mer. Selon la légende, il mourut de joie à Olympie en embrassant son fils, vainqueur au pugilat, et les Spartiates lui élevèrent un sanctuaire, où il fut honoré comme un héros. Son héritage, fragmentaire, relie la sagesse archaïque grecque à la philosophie morale classique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F7" s="7" t="s">
@@ -5898,14 +5898,18 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="n">
-        <v>-204</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>472</v>
+      <c r="A58" s="7">
+        <v>-240</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-167</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 240 A JC - 167 A JC</t>
+        </is>
       </c>
       <c r="D58" s="8" t="s">
         <v>473</v>
@@ -6101,7 +6105,7 @@
       <c r="E62" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron"  style="color:#6A142A"  title=" Wikipedia"&gt; Marcus CICERON&lt;/a&gt; était un philosophe &lt;a href="https://fr.wiktionary.org/wiki/%C3%A9clectique"  style="color:#88A1E9"  title="L'éclectisme par Wiktionnaire"&gt;Électique&lt;/a&gt; Romain et le premier a rédiger en latin des ouvrages à une époque où le grec domine dans le monde intellectuel. Il est l'héritier d'une triple tradition : sceptique, stoïcienne et platonicienne. &lt;/p&gt; &lt;p&gt; 
-On connait sa théorie de la "nature humaine" qui selon lui est orientée vers la recherche du bien car les êtres humains sont naturellement doués d'une raison qui leur permet de discerner le bien du mal. Il a écrit de nombreux traités philosophiques, dont &lt;a href="https://fr.wikipedia.org/wiki/De_finibus_bonorum_et_malorumf"  title="bien et maux par wikipedia"&gt;De Finibus Bonorum et Malorum&lt;/a&gt; (Sur les fins ultimes du bien et du mal) ainsi que "De Oratore", qui décrit l'art de la persuasion et la façon dont il peut être utilisé pour influencer les autres. &lt;/p&gt; &lt;p&gt;  
+On connait sa théorie de la "nature humaine" qui selon lui est orientée vers la recherche du bien car les êtres humains sont naturellement doués d'une raison qui leur permet de discerner le bien du mal. Il a écrit de nombreux traités philosophiques, dont &lt;a href="https://fr.wikipedia.org/wiki/De_finibus_bonorum_et_malorum"  title="bien et maux par wikipedia"&gt;De Finibus Bonorum et Malorum&lt;/a&gt; (Sur les fins ultimes du bien et du mal) ainsi que "De Oratore", qui décrit l'art de la persuasion et la façon dont il peut être utilisé pour influencer les autres. &lt;/p&gt; &lt;p&gt;  
 Il était un défenseur de la République romaine et pensait que le gouvernement devait être fondé sur des principes de justice et d'équité et que les citoyens devaient avoir le droit de participer aux décisions qui affectent leur vie. Il a écrit &lt;a href="https://www.youtube.com/watch?v=QNGtL85-rNg&amp;ab_channel=H%C3%A9rodeAtticus"  style="color:#88A1E9"  title="L'a carrière politique par Herode Atticus"&gt;De Republica&lt;/a&gt; (Sur la République), qui décrit les principes de gouvernement et d'organisation politique qu'il croyait être essentiels à une société juste et équilibrée. Il a soutenu que de la vertu comme la prudence, la justice, la tempérance et le courage sont la source ultime du bonheur et qu'on doit les cultiver pour réaliser leur plein potentiel en tant qu'êtres humains. &lt;/p&gt; &lt;p&gt; 
 Malheureusement, lorsque Marc Antoine a pris le pouvoir à Rome; il a été déclaré ennemi de l'État et a été exécuté peu de temps après.  &lt;/p&gt;   &lt;audio controls title="L'art de persuader par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23118-25.05.2022-ITEMA_23037575-2022C12410S0145-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
@@ -7289,14 +7293,18 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="n">
-        <v>415</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>714</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>715</v>
+      <c r="A87" s="7">
+        <v>410</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 410 – avant 470</t>
+        </is>
       </c>
       <c r="D87" s="8" t="s">
         <v>716</v>
@@ -8010,7 +8018,7 @@
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diotime_de_Mantinée"  title=" Wikipedia"&gt;DIOTIME de Mantinée&lt;/a&gt; est une prêtresse et une sage du Ve siècle avant J.-C., connue uniquement par le &lt;em&gt;Banquet&lt;/em&gt; de Platon. Socrate y raconte que, dans sa jeunesse, c'est elle qui lui a enseigné tout ce qu'il sait sur l'amour. Aucune autre source antique ne la mentionne, et son nom, « honorée par Zeus », ainsi que son origine, Mantinée, qui évoque le mot grec pour « devin », laissent penser qu'elle pourrait être une invention de Platon.&lt;/p&gt; &lt;p&gt;Son discours est pourtant le sommet du dialogue. Diotime explique qu'Éros n'est pas un dieu mais un « grand démon », un intermédiaire entre les mortels et les immortels, fils de Pauvreté et d'Expédient : il manque de ce qu'il désire et cherche sans cesse à l'obtenir. Aimer, c'est désirer posséder le bien pour toujours, et donc vouloir engendrer dans la beauté, par les enfants ou par les œuvres de l'esprit.&lt;/p&gt; &lt;p&gt;Le choix de Platon de faire parler une femme n'est pas anodin : dans un banquet où ne siègent que des hommes, c'est une étrangère, prêtresse et savante, qui détient la vérité la plus haute. Socrate, qui d'ordinaire interroge les autres, se présente ici comme un élève qu'elle corrige et fait progresser. La méthode de Diotime ressemble d'ailleurs à celle de Socrate lui-même : elle pose des questions, relève les contradictions et conduit pas à pas son interlocuteur vers la vérité.&lt;/p&gt; &lt;p&gt;Elle décrit ensuite la célèbre « échelle de l'amour » : de l'amour d'un beau corps, on s'élève à celui de tous les beaux corps, puis des belles âmes, des belles lois, des belles connaissances, jusqu'à la contemplation de la Beauté en soi, éternelle et parfaite. Réelle ou imaginée, Diotime reste la femme qui, chez Platon, enseigne au plus grand des philosophes l'une des idées les plus influentes de l'histoire de la pensée.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diotime"  title=" Wikipedia"&gt;DIOTIME de Mantinée&lt;/a&gt; est une prêtresse et une sage du Ve siècle avant J.-C., connue uniquement par le &lt;em&gt;Banquet&lt;/em&gt; de Platon. Socrate y raconte que, dans sa jeunesse, c'est elle qui lui a enseigné tout ce qu'il sait sur l'amour. Aucune autre source antique ne la mentionne, et son nom, « honorée par Zeus », ainsi que son origine, Mantinée, qui évoque le mot grec pour « devin », laissent penser qu'elle pourrait être une invention de Platon.&lt;/p&gt; &lt;p&gt;Son discours est pourtant le sommet du dialogue. Diotime explique qu'Éros n'est pas un dieu mais un « grand démon », un intermédiaire entre les mortels et les immortels, fils de Pauvreté et d'Expédient : il manque de ce qu'il désire et cherche sans cesse à l'obtenir. Aimer, c'est désirer posséder le bien pour toujours, et donc vouloir engendrer dans la beauté, par les enfants ou par les œuvres de l'esprit.&lt;/p&gt; &lt;p&gt;Le choix de Platon de faire parler une femme n'est pas anodin : dans un banquet où ne siègent que des hommes, c'est une étrangère, prêtresse et savante, qui détient la vérité la plus haute. Socrate, qui d'ordinaire interroge les autres, se présente ici comme un élève qu'elle corrige et fait progresser. La méthode de Diotime ressemble d'ailleurs à celle de Socrate lui-même : elle pose des questions, relève les contradictions et conduit pas à pas son interlocuteur vers la vérité.&lt;/p&gt; &lt;p&gt;Elle décrit ensuite la célèbre « échelle de l'amour » : de l'amour d'un beau corps, on s'élève à celui de tous les beaux corps, puis des belles âmes, des belles lois, des belles connaissances, jusqu'à la contemplation de la Beauté en soi, éternelle et parfaite. Réelle ou imaginée, Diotime reste la femme qui, chez Platon, enseigne au plus grand des philosophes l'une des idées les plus influentes de l'histoire de la pensée.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -8129,7 +8129,7 @@
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cratyle" title=" Wikipedia"&gt;CRATYLE&lt;/a&gt; est un philosophe grec d’Athènes, de la fin du Ve siècle av. J.-C., partisan radical de la pensée d’&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclite" title=" Wikipedia"&gt;Héraclite&lt;/a&gt;. Selon Aristote, Platon l’aurait fréquenté dans sa jeunesse, avant de rencontrer Socrate, et en aurait retenu l’idée que les choses sensibles sont dans un flux perpétuel, et qu’il ne peut donc y avoir de science à leur sujet.&lt;/p&gt; &lt;p&gt;Cratyle pousse le &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclit%C3%A9isme" title=" Wikipedia"&gt;mobilisme&lt;/a&gt; jusqu’à ses conséquences extrêmes. Héraclite disait qu’on ne peut entrer deux fois dans le même fleuve ; Cratyle lui reproche d’avoir été trop timide : on ne peut pas même y entrer une seule fois. Puisque tout change sans cesse, même pendant qu’on parle, aucune parole ne peut dire vrai. Selon Aristote, il finit par ne plus rien dire du tout et se contentait de remuer le doigt.&lt;/p&gt; &lt;p&gt;Platon a donné son nom à l’un de ses dialogues, le &lt;em&gt;Cratyle&lt;/em&gt;, consacré à la justesse des noms. Cratyle y soutient que chaque chose a un nom juste par nature, qui exprime son essence, contre Hermogène, pour qui les noms ne sont que des conventions. Socrate examine les deux thèses avec ironie, se livre à de savoureuses étymologies, et conclut qu’il vaut mieux connaître les choses par elles-mêmes que par leurs noms. Le débat entre la nature et la convention des signes traverse ensuite toute l’histoire de la philosophie du langage, jusqu’à Saussure.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cratyle" title=" Wikipedia"&gt;CRATYLE&lt;/a&gt; est un philosophe grec d’Athènes, de la fin du Ve siècle av. J.-C., partisan radical de la pensée d’&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclite" title=" Wikipedia"&gt;Héraclite&lt;/a&gt;. Selon Aristote, Platon l’aurait fréquenté dans sa jeunesse, avant de rencontrer Socrate, et en aurait retenu l’idée que les choses sensibles sont dans un flux perpétuel, et qu’il ne peut donc y avoir de science à leur sujet.&lt;/p&gt; &lt;p&gt;Cratyle pousse le &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclit%C3%A9isme" title=" Wikipedia"&gt;mobilisme&lt;/a&gt; jusqu’à ses conséquences extrêmes. Héraclite disait qu’on ne peut entrer deux fois dans le même fleuve ; Cratyle lui reproche d’avoir été trop timide : on ne peut pas même y entrer une seule fois. Puisque tout change sans cesse, même pendant qu’on parle, aucune parole ne peut dire vrai. Selon Aristote, il finit par ne plus rien dire du tout et se contentait de remuer le doigt. Pour Aristote, ce geste muet montre où mène le refus de toute affirmation stable : à l’impossibilité même de parler.&lt;/p&gt; &lt;p&gt;Platon a donné son nom à l’un de ses dialogues, le &lt;em&gt;Cratyle&lt;/em&gt;, consacré à la justesse des noms. Cratyle y soutient que chaque chose a un nom juste par nature, qui exprime son essence, contre Hermogène, pour qui les noms ne sont que des conventions. Socrate examine les deux thèses avec ironie, se livre à de savoureuses étymologies, et conclut qu’il vaut mieux connaître les choses par elles-mêmes que par leurs noms. Le débat entre la nature et la convention des signes traverse ensuite toute l’histoire de la philosophie du langage, jusqu’à Saussure. Pour Platon, la leçon est claire : si tout s’écoulait, il n’y aurait rien à connaître, d’où la nécessité des Idées, réalités immuables.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3935,8 +3935,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Protagoras"  title="Protagoras par Wikipédia"&gt; PROTAGORAS&lt;/a&gt;  était un philosophe considéré comme l'un &lt;a href="https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;ab_channel=Bibiclo" style="color:#88A1E9"   title="Les Sophistes par Bobiclo"&gt; des sophistes&lt;/a&gt; les plus célèbres de cette période.&lt;/p&gt; &lt;p&gt;Les sophistes étaient des enseignants itinérants qui offraient &lt;a href="https://www.youtube.com/watch?v=X5bZKSCfc_g&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Rhétorique et relativisme par Alain Bajomée"&gt; des cours de rhétorique&lt;/a&gt;, d'éloquence et de persuader efficacement. Cependant, il a également suscité des débats et des controverses en raison de ses opinions et de ses idées.&lt;/p&gt;
-&lt;p&gt;L'une de ses déclarations les plus célèbres est : "L'homme est la mesure de toutes choses : de celles qui sont, tant quand elles sont en tant qu'elles sont, que de celles qui ne sont pas, tant quand elles ne sont pas en tant qu'elles ne sont pas." Cela suggère que la perception et l'expérience individuelles sont centrales pour la compréhension de la réalité, et que la vérité peut être relative à chaque individu. Cette déclaration forme le fondement de ce que l'on appelle &lt;a href="https://www.youtube.com/watch?v=LxSCq1F7pSk&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Le relativisme par le Précepteur"&gt; le relativisme.&lt;/a&gt;&lt;/p&gt; &lt;p&gt;Il a également abordé des sujets tels que la nature de la justice, l'éducation et le rôle des dieux dans la vie humaine. Ses enseignements ont été critiqués par d'autres philosophes, notamment Socrate et Platon, qui les voyaient vides de fondement rationnel.&lt;/p&gt; &lt;p&gt;Bien qu'il ait laissé peu d'œuvres écrites, sa vision de la relativité de la vérité et de l'importance de la rhétorique a contribué à façonner les débats sur la nature de la connaissance et de la réalité dans la philosophie grecque antique.&lt;/p&gt;  &lt;audio controls title="Platon vs. Protagoras: l'homme est il la mesure de toutes choses? par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/09/s40/NET_FC_f081bba4-88ba-4b62-930d-2c30e49863d9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Protagoras"  title="Protagoras par Wikipédia"&gt;PROTAGORAS&lt;/a&gt; d’Abdère (vers 490 - vers 420 av. J.-C.) est le plus célèbre &lt;a href="https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;ab_channel=Bibiclo" style="color:#88A1E9"   title="Les Sophistes par Bobiclo"&gt;des sophistes&lt;/a&gt;, ces maîtres itinérants qui enseignaient, contre rémunération, l’art de bien parler et de réussir dans la cité. Il séjourne souvent à Athènes, où il fréquente Périclès, qui lui aurait confié la rédaction des lois de Thourioi, colonie fondée en 444 av. J.-C. Platon lui consacre un dialogue, le &lt;em&gt;Protagoras&lt;/em&gt;, et discute sa pensée dans le &lt;em&gt;Théétète&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Il donne &lt;a href="https://www.youtube.com/watch?v=X5bZKSCfc_g&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Rhétorique et relativisme par Alain Bajomée"&gt;des cours de rhétorique&lt;/a&gt; et d’éloquence, et promet de rendre ses élèves meilleurs citoyens. Sa formule la plus célèbre ouvre son traité &lt;em&gt;La Vérité&lt;/em&gt; : « L’homme est la mesure de toutes choses : de celles qui sont, qu’elles sont, de celles qui ne sont pas, qu’elles ne sont pas. » Le vent est froid pour qui a froid, chaud pour qui a chaud : chaque perception est vraie pour celui qui l’éprouve. Cette thèse fonde ce que l’on appelle &lt;a href="https://www.youtube.com/watch?v=LxSCq1F7pSk&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Le relativisme par le Précepteur"&gt;le relativisme&lt;/a&gt;. Il enseigne aussi que sur tout sujet on peut soutenir deux thèses opposées, et qu’il faut savoir rendre plus forte la thèse la plus faible.&lt;/p&gt; &lt;p&gt;Sur les dieux, il se déclare incapable de savoir s’ils existent ou non, « car beaucoup de choses empêchent de le savoir : l’obscurité de la question et la brièveté de la vie humaine ». Selon une tradition tardive, ce livre lui aurait valu d’être accusé d’impiété à Athènes. Socrate et Platon lui reprochent de réduire la vérité à l’opinion, mais il reste le premier penseur à faire de l’homme le centre de la réflexion philosophique.&lt;/p&gt;  &lt;audio controls title="Platon vs. Protagoras: l'homme est il la mesure de toutes choses? par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/09/s40/NET_FC_f081bba4-88ba-4b62-930d-2c30e49863d9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F16" s="7" t="s">
@@ -4363,9 +4362,9 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antisth%C3%A8ne" style="color:#6A142A"   title="Antisthène par Wikipédia"&gt; ANTISTHÈNE &lt;/a&gt; était un philosophe disciple de Socrate et il a eu une influence significative sur le développement de la philosophie morale et éthique en cherchant à préserver et à développer les idées de son maître, en mettant l'accent sur la vertu personnelle et l'authenticité. &lt;/p&gt;
-&lt;p&gt; Il est considéré comme le fondateur de &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=133s&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Comprendre les Cyniques par Alain Bajomée"&gt; l'école de pensée cynique.&lt;/a&gt; Après la mort de Socrate, il a développé ses propres idées en reprenant certains des thèmes centraux de l'enseignement de Socrate et a donné à l'école le nom de "cynique", qui dérive du mot grec "kynikos", signifiant "chien". Ce nom faisait référence à l'accent mis sur la vie simple et naturelle détachée des désirs matériels et des plaisirs superficiels, ainsi qu'à la critique des conventions sociales. Il croyait que le bonheur réside dans la maîtrise de soi et dans le rejet des biens matériels. Il vivait lui-même une vie ascétique et rejetait les besoins et les désirs superflus. &lt;/p&gt;
-&lt;p&gt; Il pensait que la sagesse et la vertu étaient atteintes par la pratique de la philosophie et l'engagement dans une vie vertueuse et critiquait ouvertement les normes sociales et les valeurs conventionnelles de la société grecque de l'époque. Il remettait en question la poursuite des richesses matérielles, du prestige social et du pouvoir, préférant se concentrer sur la recherche de la véritable vertu et du bonheur. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antisth%C3%A8ne" style="color:#6A142A"   title="Antisthène par Wikipédia"&gt; ANTISTHÈNE &lt;/a&gt; était un philosophe disciple de Socrate et il a eu une influence significative sur le développement de la philosophie morale et éthique en cherchant à préserver et à développer les idées de son maître, en mettant l'accent sur la vertu personnelle et l'authenticité. Né à Athènes d’une mère thrace, il suit d’abord le sophiste Gorgias, avant de devenir l’un des plus fidèles disciples de Socrate. &lt;/p&gt;
+&lt;p&gt; Il est considéré comme le fondateur de &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=133s&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Comprendre les Cyniques par Alain Bajomée"&gt; l'école de pensée cynique.&lt;/a&gt; Après la mort de Socrate, il a développé ses propres idées en reprenant certains des thèmes centraux de l’enseignement de Socrate. Le nom de « cynique » viendrait du gymnase du Cynosarge, où il enseignait, ou du grec &lt;em&gt;kunikos&lt;/em&gt;, « semblable au chien » ; il fait référence à l'accent mis sur la vie simple et naturelle détachée des désirs matériels et des plaisirs superficiels, ainsi qu'à la critique des conventions sociales. Il croyait que le bonheur réside dans la maîtrise de soi et dans le rejet des biens matériels. Il vivait lui-même une vie ascétique et rejetait les besoins et les désirs superflus. &lt;/p&gt;
+&lt;p&gt; Il pensait que la sagesse et la vertu étaient atteintes par la pratique de la philosophie et l'engagement dans une vie vertueuse et critiquait ouvertement les normes sociales et les valeurs conventionnelles de la société grecque de l'époque. Il remettait en question la poursuite des richesses matérielles, du prestige social et du pouvoir, préférant se concentrer sur la recherche de la véritable vertu et du bonheur. Diogène de Sinope, son disciple selon la tradition, poussera cet idéal jusqu’à la provocation. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4840,8 +4839,10 @@
       <c r="D35" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>283</v>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/X%C3%A9nocrate"  style="color:#6A142A"  title=" Wikipedia"&gt;XÉNOCRATE&lt;/a&gt; était un philosophe grec, disciple de Platon et un membre éminent de l'Académie platonicienne, qu'il dirigea après Speusippe. Né à Chalcédoine, il dirige l’école de 339 av. J.-C. à sa mort, en 314. Il est considéré comme un représentant de la "vieille Académie", c'est-à-dire de la période où l'Académie platonicienne restait proche des enseignements originaux de Platon. Sa philosophie s'inscrit dans cette tradition, mais il a  développé des  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1948_num_50_3_3399" style="color:#88A1E9" title="Xénocrate et les Orphiques  par persée"&gt;idées originales&lt;/a&gt;, notamment en métaphysique, en éthique et en cosmologie. &lt;/p&gt; &lt;p&gt; Il a interprété les Idées comme des nombres, une approche qui influencera plus tard le néoplatonisme. Il a divisé la réalité en trois niveaux : le monde intelligible (celui des Idées), le monde sensible (celui des phénomènes) et le monde intermédiaire (celui de l'âme et des mathématiques). Il a également développé une cosmologie inspirée de Platon, en particulier du  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1953_num_66_309_3305" style="color:#88A1E9" title=" Les dimensions de l'univers platonicien d'après Timée en 5 mn par persée"&gt;Timée&lt;/a&gt;, et a soutenu que l'univers était organisé de manière harmonieuse par une intelligence divine. Il définit l’âme comme « un nombre qui se meut lui-même », et serait le premier à avoir divisé la philosophie en trois parties : la physique, l’éthique et la logique. &lt;/p&gt; &lt;p&gt; Il  a développé une conception hiérarchisée des dieux, distinguant les dieux suprêmes (comme le Démiurge du Timée de Platon) des dieux inférieurs et des démons. Il  a joué un rôle important dans la transmission et l'interprétation de la philosophie platonicienne. Bien que sa pensée ait été éclipsée par celle d'Aristote et des néoplatoniciens, il a influencé des philosophes ultérieurs comme Plotin et Proclus. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F35" s="7" t="s">
         <v>284</v>
@@ -5498,8 +5499,10 @@
       <c r="D49" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="E49" s="9" t="s">
-        <v>399</v>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bion_de_Borysth%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;BION de Borysthène&lt;/a&gt; était un écrivain et un philosophe cynique grec connu pour ses idées critiques envers les conventions sociales et pour son style de vie ascétique, caractéristique des philosophes cyniques. Il était d'origine modeste, selon certaines sources et cette condition sociale a probablement influencé sa critique acerbe des hiérarchies et des conventions sociales. &lt;/p&gt; &lt;p&gt; Après avoir été vendu comme esclave, il fut libéré et reçut une éducation philosophique auprès de divers maîtres, et peut-être aussi auprès de représentants d'autres écoles philosophiques, comme les académiciens ou les péripatéticiens. Cette diversité d'influences se reflète dans sa   &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme" title="eclectisme par wikipedia"&gt;pensée éclectique&lt;/a&gt;. Il suit en effet tour à tour l’Académie, le cynique Cratès, le cyrénaïque Théodore l’Athée et le péripatéticien Théophraste.  Il adopta le mode de vie cynique, caractérisé par un rejet des richesses, des plaisirs matériels et des conventions sociales. &lt;/p&gt; &lt;p&gt; Il était également un écrivain talentueux, connu pour ses &lt;em&gt;Diatribes&lt;/em&gt;, des discours philosophiques souvent satiriques et moralisateurs.  &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1978_num_1_1_3417_t1_0102_0000_2" style="color:#88A1E9" title="Jan Fredrik Kindstrand, Bion of Borysthenes. A collection of the Fragments with introduction and commentary  par Persée"&gt;Ses textes&lt;/a&gt; ont influencé des auteurs ultérieurs, comme Horace et Sénèque, qui ont repris certains de ses thèmes et de ses techniques littéraires. Ératosthène disait de lui qu’il fut le premier à habiller la philosophie de vêtements fleuris. Il vécut un temps à la cour du roi de Macédoine Antigone Gonatas. &lt;/p&gt; &lt;p&gt; Il incarne l'esprit cynique par excellence : libre, provocateur et profondément critique envers les conventions sociales. Sa vie et son œuvre témoignent d'une quête de vérité et d'authenticité, qui continue de résonner aujourd'hui. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F49" s="7" t="s">
         <v>400</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -7694,8 +7694,10 @@
       <c r="D95" s="8" t="s">
         <v>778</v>
       </c>
-      <c r="E95" s="12" t="s">
-        <v>779</v>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Simplicius_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698" style="color:#88A1E9" title="A propos de la biographie de Simplicius par Persée"&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le "Manuel d’Épictète" et, selon la tradition, sur "De l’âme". Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href="https://www.youtube.com/watch?v=C17VYcyLkiY" style="color:#88A1E9" title="SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions"&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.   Transmis et traduits dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F95" s="7" t="s">
         <v>780</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -5021,14 +5021,18 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="n">
-        <v>-370</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>313</v>
+      <c r="A39" s="7">
+        <v>-372</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-288</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 372 A JC - 288 A JC</t>
+        </is>
       </c>
       <c r="D39" s="8" t="s">
         <v>314</v>
@@ -5855,14 +5859,18 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n">
-        <v>-210</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>464</v>
+      <c r="A57" s="7">
+        <v>160</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 160 – vers 210</t>
+        </is>
       </c>
       <c r="D57" s="8" t="s">
         <v>465</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -4347,20 +4347,154 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7">
+        <v>-450</v>
+      </c>
+      <c r="B25" s="7">
+        <v>-400</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ve siècle A JC</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIOTIME de Mantinée</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diotime" title=" Wikipedia"&gt;DIOTIME de Mantinée&lt;/a&gt; est une prêtresse et une sage du Ve siècle avant J.-C., connue uniquement par le &lt;em&gt;Banquet&lt;/em&gt; de Platon. Socrate y raconte que, dans sa jeunesse, c'est elle qui lui a enseigné tout ce qu'il sait sur l'amour. Aucune autre source&lt;a href="https://www.youtube.com/watch?v=6fOSzE0LLaM" title="Diotima de Mantinée et Platon: L'amour, l'idéal et l'ascension vers le Bien (discussion IA) par L'altruisme"&gt; antique ne la mentionne&lt;/a&gt;, et son nom, « honorée par Zeus », ainsi que son origine, Mantinée, qui évoque le mot grec pour « devin », laissent penser qu'elle pourrait être une invention de Platon.&lt;/p&gt; &lt;p&gt;Son discours est pourtant le sommet du dialogue. Diotime explique qu'Éros n'est pas un dieu mais un « grand démon », un intermédiaire entre les mortels et les immortels, fils de Pauvreté et d'Expédient : il manque de ce qu'il désire et cherche sans cesse à l'obtenir. Aimer, c'est désirer posséder le bien pour toujours, et donc vouloir engendrer dans la beauté, par les enfants ou par les œuvres de l'esprit.&lt;/p&gt; &lt;p&gt;Le choix de Platon de faire parler une femme n'est pas anodin : dans un banquet où ne siègent que des hommes, c'est une étrangère, prêtresse et savante, qui détient la vérité la plus haute. Socrate, qui d'ordinaire interroge les autres, se présente ici comme un élève qu'elle corrige et fait progresser. La méthode de Diotime ressemble d'ailleurs à celle de Socrate lui-même : elle pose des questions, relève les contradictions et conduit pas à pas son interlocuteur vers la vérité.&lt;/p&gt; &lt;p&gt;Elle décrit ensuite la célèbre « échelle de l'amour » : de l'amour d'un beau corps, on s'élève à celui de tous les beaux corps, puis des belles âmes, des belles lois, des belles connaissances, jusqu'à la contemplation de la Beauté en soi, éternelle et parfaite. Réelle ou imaginée, &lt;a href="https://www.persee.fr/doc/bude_1247-6862_1954_num_13_4_5049" title="Socrate et Diotime par persée"&gt;Diotime reste la femme &lt;/a&gt;qui, chez Platon, enseigne au plus grand des philosophes l'une des idées les plus influentes de l'histoire de la pensée.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xQ_rep6SFzM</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Philosophie - Diotime ou la philosophe ayant inspiré l'amour platonicien" par Coursitout</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/diotimedemantinee-mini.webp</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; esthetique</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platonisme</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prêtresse et sage qui, dans le Banquet de Platon, enseigne à Socrate la nature de l'amour.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7">
+        <v>-450</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-400</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 450 A JC – 400 A JC</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRATYLE</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cratyle" title=" Wikipedia"&gt;CRATYLE&lt;/a&gt; est un philosophe grec d’Athènes, de la fin du Ve siècle av. J.-C., partisan radical de la pensée d’&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclite" title=" Wikipedia"&gt;Héraclite&lt;/a&gt;. Selon Aristote, Platon l’aurait fréquenté dans sa jeunesse, avant de rencontrer Socrate, et en aurait retenu l’idée que les choses sensibles sont dans un flux perpétuel, et qu’il ne peut donc y avoir de science à leur sujet.&lt;/p&gt; &lt;p&gt;Il pousse le &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclit%C3%A9isme" title=" Wikipedia"&gt;mobilisme&lt;/a&gt; jusqu’à ses conséquences extrêmes. Héraclite disait qu’on ne peut entrer deux fois dans le même fleuve ; Cratyle lui reproche d’avoir été trop timide : on ne peut pas même y entrer une seule fois. Puisque tout change sans cesse, même pendant qu’on parle, aucune parole ne peut dire vrai. Selon Aristote, il finit par ne plus rien dire du tout et se contentait de remuer le doigt. Pour Aristote, ce geste muet montre où mène le refus de toute affirmation stable : à l’impossibilité même de parler.&lt;/p&gt; &lt;p&gt;Platon a donné son nom à l’un de ses dialogues, &lt;a href="https://www.artyuiop.fr/artyuiop/Platon_-_Cratyle_files/artyuiop95-Platon-Cratyle-trad._Victor_Cousin.pdf" title="Cratyle par artyuiop"&gt;le &lt;em&gt;Cratyle&lt;/em&gt;,&lt;/a&gt; consacré à la justesse des noms. Il y soutient que chaque chose a un nom juste par nature, qui exprime son essence, contre Hermogène, pour qui les noms ne sont que des conventions. Socrate examine les deux thèses avec ironie, se livre à de savoureuses étymologies, et conclut qu’il vaut mieux connaître les choses par elles-mêmes que par leurs noms. Le débat entre la nature et la convention des signes traverse ensuite toute l’histoire de la philosophie du langage, jusqu’à Saussure. Pour Platon, la leçon est claire : si tout s’écoulait, il n’y aurait rien à connaître, d’où la nécessité des Idées, réalités immuables.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">txurJe1ifBg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"CRATYLE (1) de PLATON : Première Philosophie du LANGAGE, de la Nature et de l'Origine des Mots" par Frère Ismaël</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/cratyle-mini.webp</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langage ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobilisme</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe grec, héraclitéen radical, qui a donné son nom au dialogue de Platon sur le langage.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P26"/>
+    </row>
+    <row r="27" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="n">
         <v>-445</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B27" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C27" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D27" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antisth%C3%A8ne" style="color:#6A142A"   title="Antisthène par Wikipédia"&gt; ANTISTHÈNE &lt;/a&gt; était un philosophe disciple de Socrate et il a eu une influence significative sur le développement de la philosophie morale et éthique en cherchant à préserver et à développer les idées de son maître, en mettant l'accent sur la vertu personnelle et l'authenticité. Né à Athènes d’une mère thrace, il suit d’abord le sophiste Gorgias, avant de devenir l’un des plus fidèles disciples de Socrate. &lt;/p&gt;
 &lt;p&gt; Il est considéré comme le fondateur de &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=133s&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Comprendre les Cyniques par Alain Bajomée"&gt; l'école de pensée cynique.&lt;/a&gt; Après la mort de Socrate, il a développé ses propres idées en reprenant certains des thèmes centraux de l’enseignement de Socrate. Le nom de « cynique » viendrait du gymnase du Cynosarge, où il enseignait, ou du grec &lt;em&gt;kunikos&lt;/em&gt;, « semblable au chien » ; il fait référence à l'accent mis sur la vie simple et naturelle détachée des désirs matériels et des plaisirs superficiels, ainsi qu'à la critique des conventions sociales. Il croyait que le bonheur réside dans la maîtrise de soi et dans le rejet des biens matériels. Il vivait lui-même une vie ascétique et rejetait les besoins et les désirs superflus. &lt;/p&gt;
@@ -4368,108 +4502,14 @@
 </t>
         </is>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F27" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G27" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H27" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
-        <v>-436</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isocrate"  style="color:#6A142A"  title=" Wikipedia"&gt;ISOCRATE&lt;/a&gt; était un orateur et philosophe grec souvent éclipsé par des figures comme Platon ou Aristote, mais son impact sur l'éducation, la rhétorique et la pensée politique est considérable. Il  se distingue par  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2007_num_109_2_6552"  style="color:#88A1E9" title="La πλεονεξία chez Isocrate  par Persée"&gt;son approche&lt;/a&gt; pragmatique de la philosophie contrairement à Platon, qui cherche la vérité absolue, lui se concentre sur l'utilité pratique de la connaissance.  En 390 av. J.-C., il fonde une école à Athènes, rivale de l'Académie de Platon, qui attire des étudiants de toute la Grèce, dont certains deviendront des figures importantes, comme les orateurs Hypéride et Lycurgue.&lt;/p&gt; &lt;p&gt; Pour lui, la rhétorique n'est pas seulement un art de persuader, mais un moyen de former des citoyens éclairés et de promouvoir la justice. Il croit que la parole bien maîtrisée peut améliorer la société en encourageant le débat raisonné et en renforçant les institutions. Il rejette l'individualisme excessif et prône un équilibre entre les intérêts personnels et ceux de la communauté.  Il a laissé une vingtaine de discours et &lt;a href="https://www.persee.fr/doc/ktema_0221-5896_2016_num_41_1_1487"  style="color:#88A1E9" title=" Isocrate et Sparte par Persée"&gt;plusieurs lettres&lt;/a&gt;, dont les plus célèbres sont : &lt;/p&gt; &lt;p&gt;Le Panégyrique d'Athènes : Un plaidoyer pour l'unité grecque sous l'hégémonie athénienne. &lt;/p&gt; &lt;p&gt;Sur la paix : Un appel à la modération et à la coopération entre les cités grecques.&lt;/p&gt; &lt;p&gt;L'Éloge d'Hélène : Une défense rhétorique de la figure d'Hélène de Troie. &lt;/p&gt; &lt;p&gt;Le Philippe : Une lettre adressée à Philippe II de Macédoine, l'exhortant à unifier la Grèce. &lt;/p&gt; &lt;p&gt; Il aura marqué l'histoire de la pensée occidentale à plusieurs titres, son modèle éducatif, centré sur la rhétorique et la culture générale, a influencé l'éducation libérale en Occident et en politique, ses idées sur l'unité grecque et la coopération internationale résonnent encore aujourd'hui.&lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P26"/>
-    </row>
-    <row r="27" customFormat="false" ht="154.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
-        <v>-435</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristippe_de_Cyr%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTIPPE de Cyrène&lt;/a&gt; était un philosophe grec antique, fondateur de  &lt;a href="https://www.youtube.com/watch?v=Rp7sm07EJBY&amp;t=270s" style="color:#88A1E9" title=" Les CYRÉNAÏQUES en 8 minutes par Alain Bajoumée"&gt;l'école cyrénaïque&lt;/a&gt;, une école de pensée qui met l'accent sur la recherche du plaisir comme but principal de la vie, une forme &lt;a href="https://www.youtube.com/watch?v=HOE8sDMhGUE" style="color:#88A1E9" title=" L'hédonisme sans mesure: la philosophie du plaisir par philosophie"&gt;d'hédonisme&lt;/a&gt;. Cependant, contrairement à l'hédonisme moderne souvent associé à la recherche effrénée du plaisir, la philosophie d'Aristippe est plus subtile et contextuelle : &lt;/p&gt;
-&lt;p&gt;Poursuite du plaisir : Pour lui, le plaisir est le bien suprême. Il croyait que le but de la vie était de maximiser le plaisir et de minimiser la douleur. Cependant, il distinguait entre les plaisirs physiques et les plaisirs intellectuels, et il valorisait particulièrement les plaisirs immédiats et concrets. &lt;/p&gt; &lt;p&gt;Adaptabilité et flexibilité : Il enseignait l'importance de s'adapter aux circonstances. Il croyait que la sagesse consistait à savoir profiter des plaisirs disponibles tout en évitant les douleurs inutiles. Cette idée est souvent résumée par sa maxime : "Posséder sans être possédé." &lt;/p&gt; &lt;p&gt;Indépendance émotionnelle : Il prônait une forme de détachement émotionnel. Il croyait que l'on devait être capable de jouir des plaisirs sans devenir esclave de ses désirs. Cette idée est proche de la notion de "ataraxie" (tranquillité de l'âme) que l'on retrouve plus tard dans l'épicurisme. &lt;/p&gt; &lt;p&gt;Critique des conventions sociales : Il était connu pour son mépris des conventions sociales et des normes traditionnelles et croyait que les individus devaient vivre selon leurs propres termes, sans se soucier excessivement de l'opinion des autres. &lt;/p&gt; &lt;p&gt; L'école cyrénaïque a eu une influence limitée par rapport à d'autres écoles philosophiques de l'Antiquité, mais elle a néanmoins contribué à façonner la pensée hédoniste et à influencer des philosophes ultérieurs comme Épicure.  &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>217</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="2" t="s">
@@ -4479,10 +4519,10 @@
         <v>200</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4490,115 +4530,209 @@
         </is>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="n">
-        <v>-430</v>
+        <v>-436</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>223</v>
+        <v>205</v>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isocrate"  style="color:#6A142A"  title=" Wikipedia"&gt;ISOCRATE&lt;/a&gt; était un orateur et philosophe grec souvent éclipsé par des figures comme Platon ou Aristote, mais son impact sur l'éducation, la rhétorique et la pensée politique est considérable. Il  se distingue par  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2007_num_109_2_6552"  style="color:#88A1E9" title="La πλεονεξία chez Isocrate  par Persée"&gt;son approche&lt;/a&gt; pragmatique de la philosophie contrairement à Platon, qui cherche la vérité absolue, lui se concentre sur l'utilité pratique de la connaissance.  En 390 av. J.-C., il fonde une école à Athènes, rivale de l'Académie de Platon, qui attire des étudiants de toute la Grèce, dont certains deviendront des figures importantes, comme les orateurs Hypéride et Lycurgue.&lt;/p&gt; &lt;p&gt; Pour lui, la rhétorique n'est pas seulement un art de persuader, mais un moyen de former des citoyens éclairés et de promouvoir la justice. Il croit que la parole bien maîtrisée peut améliorer la société en encourageant le débat raisonné et en renforçant les institutions. Il rejette l'individualisme excessif et prône un équilibre entre les intérêts personnels et ceux de la communauté.  Il a laissé une vingtaine de discours et &lt;a href="https://www.persee.fr/doc/ktema_0221-5896_2016_num_41_1_1487"  style="color:#88A1E9" title=" Isocrate et Sparte par Persée"&gt;plusieurs lettres&lt;/a&gt;, dont les plus célèbres sont : &lt;/p&gt; &lt;p&gt;Le Panégyrique d'Athènes : Un plaidoyer pour l'unité grecque sous l'hégémonie athénienne. &lt;/p&gt; &lt;p&gt;Sur la paix : Un appel à la modération et à la coopération entre les cités grecques.&lt;/p&gt; &lt;p&gt;L'Éloge d'Hélène : Une défense rhétorique de la figure d'Hélène de Troie. &lt;/p&gt; &lt;p&gt;Le Philippe : Une lettre adressée à Philippe II de Macédoine, l'exhortant à unifier la Grèce. &lt;/p&gt; &lt;p&gt; Il aura marqué l'histoire de la pensée occidentale à plusieurs titres, son modèle éducatif, centré sur la rhétorique et la culture générale, a influencé l'éducation libérale en Occident et en politique, ses idées sur l'unité grecque et la coopération internationale résonnent encore aujourd'hui.&lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F28" s="7" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="232.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P28"/>
+    </row>
+    <row r="29" customFormat="false" ht="154.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
-        <v>-428</v>
+        <v>-435</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Platon"  style="color:#6A142A"  title=" Wikipedia"&gt;PLATON&lt;/a&gt; fut  un des plus grands penseurs de l'Antiquité.  Il était l'élève de Socrate, dont la méthode dialectique et la quête de la vérité le marquent profondément. La condamnation à mort de Socrate en 399 av. J.-C. influence sa méfiance envers la démocratie athénienne. &lt;/p&gt; &lt;p&gt; Il fonda  &lt;a href="https://www.youtube.com/watch?v=q0M8zV-XHbQ"  style="color:#88A1E9" title="L'académie de Platon Platon par Luc Ferry"&gt;l'Académie&lt;/a&gt; à Athènes, qui est considérée comme la première institution d'enseignement supérieur de l'histoire où  il y enseigne la philosophie, les mathématiques et les sciences. L'Académie fonctionnera pendant près de 900 ans.&lt;/p&gt; Il développe une philosophie complexe et systématique, centrée sur des concepts clés comme les Idées, &lt;a href="https://www.persee.fr/doc/phlou_0776-5541_1905_num_12_46_1881"  style="color:#88A1E9" title="Dieu, d'après Platon par Persée"&gt;l'âme&lt;/a&gt;, la justice et la connaissance. Ses idées sont principalement exposées sous forme de dialogues, où Socrate est souvent le personnage principal. Il distingue &lt;a href="https://www.youtube.com/watch?v=o5TbXYe64A8&amp;t=18s&amp;ab_channel=AlainBajom%C3%A9e"  style="color:#88A1E9" title="La théorie des idées par Alain Bajomée"&gt;deux mondes&lt;/a&gt; : le monde sensible (celui que nous percevons par les sens) et le monde intelligible (celui des Idées, éternel et immuable). Pour lui, les Idées sont des réalités parfaites et immuables qui existent indépendamment du monde matériel. Par exemple, il existe une Idée de la Beauté, de la Justice ou du Bien, dont les objets sensibles ne sont que des copies imparfaites. &lt;/p&gt; &lt;p&gt;Il a écrit une trentaine de dialogues, dont les plus célèbres sont : La République (justice, politique, éducation). Phédon (immortalité de l'âme). &lt;a href="https://www.youtube.com/watch?v=Mbtxr1hsP7A"  title="  Ce que Le Banquet de Platon révèle sur l'amour  par Resumon ça"&gt;Le Banquet &lt;/a&gt;(amour et beauté). Phèdre (rhétorique et amour). Ménon (vertu et réminiscence). Timée (cosmologie et physique). Critias (mythe de l'Atlantide). Apologie de Socrate (défense de Socrate lors de son procès). Phédon (immortalité de l'âme). &lt;/p&gt; &lt;p&gt;  Dans son ouvrage  le plus célèbre  &lt;a href="https://www.youtube.com/watch?v=qSrvZvjPG_w&amp;t=811s&amp;ab_channel=Kosmos"  style="color:#88A1E9" title="La République, c'est quoi par Kosmos"&gt;La République&lt;/a&gt;, il décrit sa vision d'une société idéale où les dirigeants sont des philosophes-rois et où la justice et la vertu sont les principes fondamentaux. Il y présente une métaphore de la condition humaine, l'allégorie de la &lt;a href="https://www.youtube.com/watch?v=N519gbEXbbw&amp;t=13s&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9" title="L'allégorie de la Caverne par le Précepteur "&gt;La Caverne&lt;/a&gt;, lieu où des gens vivent et où ils ne voient que des ombres projetées sur les murs en croyant que c'est la réalité.&lt;/p&gt; &lt;p&gt; Il reste une figure centrale de la philosophie, dont les idées continuent d'inspirer et de provoquer la réflexion. Sa quête de la vérité, sa vision idéaliste et sa méthode dialectique en font un penseur intemporel. &lt;/p&gt;   &lt;audio controls title="Platon et la politique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.11.2025-ITEMA_24317262-2025C48904S0324-NET_MFC_E07CEF22-5D42-4358-8035-01B7B6D438EF-21-f49f7fca67cbafd4d44c5b4c00fead78.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        <v>213</v>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristippe_de_Cyr%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTIPPE de Cyrène&lt;/a&gt; était un philosophe grec antique, fondateur de  &lt;a href="https://www.youtube.com/watch?v=Rp7sm07EJBY&amp;t=270s" style="color:#88A1E9" title=" Les CYRÉNAÏQUES en 8 minutes par Alain Bajoumée"&gt;l'école cyrénaïque&lt;/a&gt;, une école de pensée qui met l'accent sur la recherche du plaisir comme but principal de la vie, une forme &lt;a href="https://www.youtube.com/watch?v=HOE8sDMhGUE" style="color:#88A1E9" title=" L'hédonisme sans mesure: la philosophie du plaisir par philosophie"&gt;d'hédonisme&lt;/a&gt;. Cependant, contrairement à l'hédonisme moderne souvent associé à la recherche effrénée du plaisir, la philosophie d'Aristippe est plus subtile et contextuelle : &lt;/p&gt;
+&lt;p&gt;Poursuite du plaisir : Pour lui, le plaisir est le bien suprême. Il croyait que le but de la vie était de maximiser le plaisir et de minimiser la douleur. Cependant, il distinguait entre les plaisirs physiques et les plaisirs intellectuels, et il valorisait particulièrement les plaisirs immédiats et concrets. &lt;/p&gt; &lt;p&gt;Adaptabilité et flexibilité : Il enseignait l'importance de s'adapter aux circonstances. Il croyait que la sagesse consistait à savoir profiter des plaisirs disponibles tout en évitant les douleurs inutiles. Cette idée est souvent résumée par sa maxime : "Posséder sans être possédé." &lt;/p&gt; &lt;p&gt;Indépendance émotionnelle : Il prônait une forme de détachement émotionnel. Il croyait que l'on devait être capable de jouir des plaisirs sans devenir esclave de ses désirs. Cette idée est proche de la notion de "ataraxie" (tranquillité de l'âme) que l'on retrouve plus tard dans l'épicurisme. &lt;/p&gt; &lt;p&gt;Critique des conventions sociales : Il était connu pour son mépris des conventions sociales et des normes traditionnelles et croyait que les individus devaient vivre selon leurs propres termes, sans se soucier excessivement de l'opinion des autres. &lt;/p&gt; &lt;p&gt; L'école cyrénaïque a eu une influence limitée par rapport à d'autres écoles philosophiques de l'Antiquité, mais elle a néanmoins contribué à façonner la pensée hédoniste et à influencer des philosophes ultérieurs comme Épicure.  &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F29" s="7" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="n">
+        <v>-430</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="I30" s="9"/>
+      <c r="J30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="232.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="n">
+        <v>-428</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Platon"  style="color:#6A142A"  title=" Wikipedia"&gt;PLATON&lt;/a&gt; fut  un des plus grands penseurs de l'Antiquité.  Il était l'élève de Socrate, dont la méthode dialectique et la quête de la vérité le marquent profondément. La condamnation à mort de Socrate en 399 av. J.-C. influence sa méfiance envers la démocratie athénienne. &lt;/p&gt; &lt;p&gt; Il fonda  &lt;a href="https://www.youtube.com/watch?v=q0M8zV-XHbQ"  style="color:#88A1E9" title="L'académie de Platon Platon par Luc Ferry"&gt;l'Académie&lt;/a&gt; à Athènes, qui est considérée comme la première institution d'enseignement supérieur de l'histoire où  il y enseigne la philosophie, les mathématiques et les sciences. L'Académie fonctionnera pendant près de 900 ans.&lt;/p&gt; Il développe une philosophie complexe et systématique, centrée sur des concepts clés comme les Idées, &lt;a href="https://www.persee.fr/doc/phlou_0776-5541_1905_num_12_46_1881"  style="color:#88A1E9" title="Dieu, d'après Platon par Persée"&gt;l'âme&lt;/a&gt;, la justice et la connaissance. Ses idées sont principalement exposées sous forme de dialogues, où Socrate est souvent le personnage principal. Il distingue &lt;a href="https://www.youtube.com/watch?v=o5TbXYe64A8&amp;t=18s&amp;ab_channel=AlainBajom%C3%A9e"  style="color:#88A1E9" title="La théorie des idées par Alain Bajomée"&gt;deux mondes&lt;/a&gt; : le monde sensible (celui que nous percevons par les sens) et le monde intelligible (celui des Idées, éternel et immuable). Pour lui, les Idées sont des réalités parfaites et immuables qui existent indépendamment du monde matériel. Par exemple, il existe une Idée de la Beauté, de la Justice ou du Bien, dont les objets sensibles ne sont que des copies imparfaites. &lt;/p&gt; &lt;p&gt;Il a écrit une trentaine de dialogues, dont les plus célèbres sont : La République (justice, politique, éducation). Phédon (immortalité de l'âme). &lt;a href="https://www.youtube.com/watch?v=Mbtxr1hsP7A"  title="  Ce que Le Banquet de Platon révèle sur l'amour  par Resumon ça"&gt;Le Banquet &lt;/a&gt;(amour et beauté). Phèdre (rhétorique et amour). Ménon (vertu et réminiscence). Timée (cosmologie et physique). Critias (mythe de l'Atlantide). Apologie de Socrate (défense de Socrate lors de son procès). Phédon (immortalité de l'âme). &lt;/p&gt; &lt;p&gt;  Dans son ouvrage  le plus célèbre  &lt;a href="https://www.youtube.com/watch?v=qSrvZvjPG_w&amp;t=811s&amp;ab_channel=Kosmos"  style="color:#88A1E9" title="La République, c'est quoi par Kosmos"&gt;La République&lt;/a&gt;, il décrit sa vision d'une société idéale où les dirigeants sont des philosophes-rois et où la justice et la vertu sont les principes fondamentaux. Il y présente une métaphore de la condition humaine, l'allégorie de la &lt;a href="https://www.youtube.com/watch?v=N519gbEXbbw&amp;t=13s&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9" title="L'allégorie de la Caverne par le Précepteur "&gt;La Caverne&lt;/a&gt;, lieu où des gens vivent et où ils ne voient que des ombres projetées sur les murs en croyant que c'est la réalité.&lt;/p&gt; &lt;p&gt; Il reste une figure centrale de la philosophie, dont les idées continuent d'inspirer et de provoquer la réflexion. Sa quête de la vérité, sa vision idéaliste et sa méthode dialectique en font un penseur intemporel. &lt;/p&gt;   &lt;audio controls title="Platon et la politique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.11.2025-ITEMA_24317262-2025C48904S0324-NET_MFC_E07CEF22-5D42-4358-8035-01B7B6D438EF-21-f49f7fca67cbafd4d44c5b4c00fead78.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="I31" s="9"/>
+      <c r="J31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Platonisme ; Dualisme</t>
         </is>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P29">
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P31">
         <v>3</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="n">
+    <row r="32" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="n">
         <v>-412</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B32" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C32" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D32" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Sinope"   title="Diogène de Sinope par Wikipédia"&gt; DIOGÈNE DE SINOPE &lt;/a&gt; était un philosophe grec antique connu pour son mode de vie ascétique et ses provocations intellectuelles. Il est souvent surnommé "Diogène le Cynique" en raison de son affiliation à l'école de pensée cynique, qui prônait le rejet des conventions sociales, le détachement des désirs matériels et une vie en accord avec la nature. Il vivait une vie extrêmement simple et minimaliste et rejetait les besoins conventionnels et matérialistes, préférant se contenter de peu. Il est célèbre pour avoir vécu dans un tonneau (ou grand récipient) à Athènes. &lt;/p&gt;
 &lt;p&gt;Diogène était connu pour &lt;a href="https://www.philo5.com/Les%20philosophes%20Textes/Diogene_OntDitSur.htm#_ftn4"  title="Diogène de Sinope d'après Diogène Laërce par philo5"&gt; défier les normes&lt;/a&gt; sociales et philosophiques de son époque en utilisant souvent des actions et des paroles provocantes pour critiquer la société, remettre en question les valeurs établies et provoquer des réflexions profondes. Par exemple, il se promenait en plein jour avec une lanterne allumée à la recherche d'un "homme honnête", soulignant ainsi l'absence de personnes vertueuses.  &lt;a href="https://www.youtube.com/watch?v=aNUDOhr9yLs"  title=" La philosophie Diogène de Sinope par parole de philosophes "&gt; Il croyait &lt;/a&gt; que la société et ses institutions étaient corrompues et prônait la simplicité et la nature, rejetant les normes artificielles et les désirs superficiels qui causaient souvent des souffrances et des conflits.&lt;/p&gt;
@@ -4606,168 +4740,76 @@
 &lt;p&gt;Ses enseignements exacts  ne sont pas bien documentés, car peu de ses écrits ont survécu. Cependant, &lt;a href="https://www.youtube.com/watch?v=epW-8gZwQEk&amp;ab_channel=R%C3%A9sonance%5Bs%5D"  title="Diogène de Sinope, le chien royal par Résonance"&gt;son mode de vie&lt;/a&gt; et ses actions ont eu un impact durable sur la philosophie occidentale en remettant en question les valeurs conventionnelles et en mettant l'accent sur la simplicité et l'authenticité. &lt;/p&gt;   &lt;audio controls title="Osons le cynisme ! retour à Diogène par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/02/s09/LES_NOUVEAUX_CHEMINS_DE_LA_CONNAISSANCE.NET_FC_4EBE3123-A5B5-49FF-96B5-DB4346498425.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F32" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G32" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="H30" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="n">
-        <v>-408</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="n">
-        <v>-407</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Speusippe"  style="color:#6A142A"  title=" Wikipedia"&gt;SPEUSIPPE&lt;/a&gt; était un philosophe grec connu pour être le neveu de Platon et pour avoir succédé à ce dernier à la tête de l'Académie, l'école philosophique qu'il avait fondé. Il est souvent considéré comme un philosophe qui a cherché à développer et à modifier les idées de Platon plutôt que de les suivre strictement. &lt;/p&gt; &lt;p&gt; Il a rejeté la théorie des Formes de Platon, qui postulait l'existence d'entités immuables et éternelles (les Formes) comme fondement de la réalité. À la place, il a proposé une vision plus naturaliste et mathématique de la réalité, mettant l'accent sur les nombres et les  &lt;a href="https://remacle.org/bloodwolf/philosophes/speusippe/fragments.htm"  style="color:#88A1E9" title=" Speusippe fragment par remacle"&gt;principes mathématiques&lt;/a&gt; comme fondements de l'univers.  Il a également développé une théorie des principes premiers, où il distinguait entre l'Un (qui représente l'unité et la simplicité) et la Multiplicité (qui représente la diversité et la complexité). Ces principes étaient considérés comme les fondements de toute existence. &lt;/p&gt; Il a soutenu que le bonheur ne réside pas dans la possession de biens matériels ou de plaisirs, mais dans la réalisation d'une &lt;a href="https://remacle.org/bloodwolf/philosophes/laerce/4speusippe.htm"  style="color:#88A1E9" title=" Speusippe livre IV par Remacle"&gt;harmonie intérieure&lt;/a&gt; et d'une vie vertueuse. Il a mis l'accent sur l'importance de la modération et de l'équilibre dans la vie humaine. Il s'est intéressé à la classification des êtres vivants et a tenté de développer un système pour organiser et comprendre la diversité du monde naturel. Bien que ses travaux dans ce domaine soient peu connus, ils montrent un intérêt pour l'observation et la systématisation de la nature. &lt;/p&gt; &lt;p&gt; Il a dirigé l'Académie pendant environ huit ans, mais son influence a été éclipsée par celle de son successeur, Xénocrate, et par la postérité de Platon. Ses écrits ont été perdus, et nous ne connaissons sa pensée qu'à travers les témoignages d'autres philosophes, tels qu'Aristote, qui a critiqué certaines de ses idées.&lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>260</v>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sinope-mini.webp</t>
+        </is>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="152.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
-        <v>-405</v>
+        <v>-408</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eubulide"  style="color:#6A142A"  title=" Wikipedia"&gt;EUBULIDE de Milet&lt;/a&gt;  était un philosophe grec antique appartenant à l'école mégarique, une école de philosophie fondée par Euclide de Mégare, un disciple de Socrate. L'école mégarique est connue pour son intérêt pour la logique et les arguments dialectiques. &lt;/p&gt; &lt;p&gt; Eubulide est surtout connu pour ses paradoxes, qui ont été conçus pour mettre en lumière les difficultés et les ambiguïtés dans le langage et la pensée. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=CIgkTJYt1b0"  style="color:#88A1E9" title="Le paradoxe du menteur par Logique Contradictoire"&gt;Le paradoxe du menteur&lt;/a&gt; : Ce paradoxe met en scène une personne qui déclare "Je mens". Si la personne dit la vérité, alors elle ment, ce qui est une contradiction. Si elle ment, alors elle dit la vérité, ce qui est également une contradiction. Ce paradoxe a des implications profondes pour la logique et la sémantique. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=2tn152iCDpk"  title="Le paradoxe du Sorite par Philosophie Analytique"&gt;Le paradoxe du sorite&lt;/a&gt; (ou paradoxe du tas) : Ce paradoxe questionne à quel moment un tas de grains cesse d'être un tas lorsqu'on enlève un grain à la fois. Il soulève des questions sur les limites floues et les définitions vagues. &lt;/p&gt; &lt;p&gt;Le paradoxe de l'électre : Ce paradoxe explore les problèmes de connaissance et de reconnaissance. Si Electre sait que son frère Oreste est dans la pièce, mais ne reconnaît pas Oreste lorsqu'elle le voit, peut-on dire qu'elle sait vraiment qu'il est là ? &lt;/p&gt; &lt;p&gt;Le paradoxe du voilé : Ce paradoxe pose la question de savoir si on peut reconnaître quelqu'un qui est voilé. Si on ne peut pas le reconnaître, comment peut-on savoir que c'est la même personne ? &lt;/p&gt; &lt;p&gt;  Les paradoxes d'Eubulide ont eu une influence durable sur la philosophie, en particulier dans les domaines de la logique, de la sémantique et de l'épistémologie. Ils ont été étudiés et discutés par de nombreux philosophes ultérieurs, y compris les stoïciens et les sceptiques, et continuent d'être un sujet de débat dans la philosophie contemporaine. &lt;/p&gt; </t>
-        </is>
+        <v>247</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>248</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>267</v>
+        <v>249</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>250</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Socratisme ; École mégarique</t>
-        </is>
+        <v>252</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4775,50 +4817,45 @@
         </is>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
-        <v>-400</v>
+        <v>-407</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ar%C3%A9t%C3%A9_de_Cyr%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;ARÉTÉ de Cyrène&lt;/a&gt; (IVe siècle av. J.-C.) est l’une des premières &lt;a href="https://www.youtube.com/watch?v=9vy8w9K-YgQ" style="color:#88A1E9" title="Arete Of Cyrene 1st Woman Philosopher Before BC par Celebrities World"&gt;femmes philosophes&lt;/a&gt; connues de la Grèce antique. Fille d’Aristippe de Cyrène, disciple de Socrate et fondateur de l’école cyrénaïque, elle reçoit de son père une formation philosophique et prend une place centrale dans la transmission de sa doctrine.&lt;/p&gt; &lt;p&gt;Nous la connaissons surtout par l’historien Diogène Laërce et par d’autres sources tardives, et aucun de ses écrits ne nous est parvenu. Son rôle principal est d’avoir formé son propre fils, Aristippe le Jeune, surnommé « l’instruit par sa mère » (&lt;em&gt;Mêtrodidaktos&lt;/em&gt;), qui donnera à l’école sa forme systématique. &lt;a href="https://www.youtube.com/watch?v=Rp7sm07EJBY&amp;t=324s" style="color:#88A1E9" title="Les Cyrénaîsme par Alain Bajoumée"&gt;Les cyrénaïques&lt;/a&gt; font du plaisir le seul bien et de la douleur le seul mal. Ils fondent cette morale sur une théorie de la connaissance : nous ne connaissons que nos propres sensations, non les choses qui les causent. Le plaisir est un « mouvement doux », la douleur un « mouvement rude » ; le plaisir présent, corporel et vif, est le seul dont nous soyons sûrs, car le passé n’est plus et l’avenir est incertain. Mais le sage cyrénaïque n’est pas un débauché : il cherche à maîtriser le plaisir sans s’en rendre esclave, et à rester libre en toutes circonstances. Une lettre attribuée à Aristippe, sans doute apocryphe, conseille à Arété de gérer ses biens avec mesure et de veiller à l’éducation de son fils.&lt;/p&gt; &lt;p&gt;Des auteurs plus tardifs lui ont prêté une longue carrière d’enseignante et de nombreux livres, sans preuve. Elle reste cependant le symbole de la place des femmes dans la philosophie antique, aux côtés d’Hipparchia ou de Théano.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Speusippe"  style="color:#6A142A"  title=" Wikipedia"&gt;SPEUSIPPE&lt;/a&gt; était un philosophe grec connu pour être le neveu de Platon et pour avoir succédé à ce dernier à la tête de l'Académie, l'école philosophique qu'il avait fondé. Il est souvent considéré comme un philosophe qui a cherché à développer et à modifier les idées de Platon plutôt que de les suivre strictement. &lt;/p&gt; &lt;p&gt; Il a rejeté la théorie des Formes de Platon, qui postulait l'existence d'entités immuables et éternelles (les Formes) comme fondement de la réalité. À la place, il a proposé une vision plus naturaliste et mathématique de la réalité, mettant l'accent sur les nombres et les  &lt;a href="https://remacle.org/bloodwolf/philosophes/speusippe/fragments.htm"  style="color:#88A1E9" title=" Speusippe fragment par remacle"&gt;principes mathématiques&lt;/a&gt; comme fondements de l'univers.  Il a également développé une théorie des principes premiers, où il distinguait entre l'Un (qui représente l'unité et la simplicité) et la Multiplicité (qui représente la diversité et la complexité). Ces principes étaient considérés comme les fondements de toute existence. &lt;/p&gt; Il a soutenu que le bonheur ne réside pas dans la possession de biens matériels ou de plaisirs, mais dans la réalisation d'une &lt;a href="https://remacle.org/bloodwolf/philosophes/laerce/4speusippe.htm"  style="color:#88A1E9" title=" Speusippe livre IV par Remacle"&gt;harmonie intérieure&lt;/a&gt; et d'une vie vertueuse. Il a mis l'accent sur l'importance de la modération et de l'équilibre dans la vie humaine. Il s'est intéressé à la classification des êtres vivants et a tenté de développer un système pour organiser et comprendre la diversité du monde naturel. Bien que ses travaux dans ce domaine soient peu connus, ils montrent un intérêt pour l'observation et la systématisation de la nature. &lt;/p&gt; &lt;p&gt; Il a dirigé l'Académie pendant environ huit ans, mais son influence a été éclipsée par celle de son successeur, Xénocrate, et par la postérité de Platon. Ses écrits ont été perdus, et nous ne connaissons sa pensée qu'à travers les témoignages d'autres philosophes, tels qu'Aristote, qui a critiqué certaines de ses idées.&lt;/p&gt; </t>
         </is>
       </c>
       <c r="F34" s="7" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
+        <v>261</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4826,45 +4863,47 @@
         </is>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="152.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
-        <v>-396</v>
+        <v>-405</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/X%C3%A9nocrate"  style="color:#6A142A"  title=" Wikipedia"&gt;XÉNOCRATE&lt;/a&gt; était un philosophe grec, disciple de Platon et un membre éminent de l'Académie platonicienne, qu'il dirigea après Speusippe. Né à Chalcédoine, il dirige l’école de 339 av. J.-C. à sa mort, en 314. Il est considéré comme un représentant de la "vieille Académie", c'est-à-dire de la période où l'Académie platonicienne restait proche des enseignements originaux de Platon. Sa philosophie s'inscrit dans cette tradition, mais il a  développé des  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1948_num_50_3_3399" style="color:#88A1E9" title="Xénocrate et les Orphiques  par persée"&gt;idées originales&lt;/a&gt;, notamment en métaphysique, en éthique et en cosmologie. &lt;/p&gt; &lt;p&gt; Il a interprété les Idées comme des nombres, une approche qui influencera plus tard le néoplatonisme. Il a divisé la réalité en trois niveaux : le monde intelligible (celui des Idées), le monde sensible (celui des phénomènes) et le monde intermédiaire (celui de l'âme et des mathématiques). Il a également développé une cosmologie inspirée de Platon, en particulier du  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1953_num_66_309_3305" style="color:#88A1E9" title=" Les dimensions de l'univers platonicien d'après Timée en 5 mn par persée"&gt;Timée&lt;/a&gt;, et a soutenu que l'univers était organisé de manière harmonieuse par une intelligence divine. Il définit l’âme comme « un nombre qui se meut lui-même », et serait le premier à avoir divisé la philosophie en trois parties : la physique, l’éthique et la logique. &lt;/p&gt; &lt;p&gt; Il  a développé une conception hiérarchisée des dieux, distinguant les dieux suprêmes (comme le Démiurge du Timée de Platon) des dieux inférieurs et des démons. Il  a joué un rôle important dans la transmission et l'interprétation de la philosophie platonicienne. Bien que sa pensée ait été éclipsée par celle d'Aristote et des néoplatoniciens, il a influencé des philosophes ultérieurs comme Plotin et Proclus. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eubulide"  style="color:#6A142A"  title=" Wikipedia"&gt;EUBULIDE de Milet&lt;/a&gt;  était un philosophe grec antique appartenant à l'école mégarique, une école de philosophie fondée par Euclide de Mégare, un disciple de Socrate. L'école mégarique est connue pour son intérêt pour la logique et les arguments dialectiques. &lt;/p&gt; &lt;p&gt; Eubulide est surtout connu pour ses paradoxes, qui ont été conçus pour mettre en lumière les difficultés et les ambiguïtés dans le langage et la pensée. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=CIgkTJYt1b0"  style="color:#88A1E9" title="Le paradoxe du menteur par Logique Contradictoire"&gt;Le paradoxe du menteur&lt;/a&gt; : Ce paradoxe met en scène une personne qui déclare "Je mens". Si la personne dit la vérité, alors elle ment, ce qui est une contradiction. Si elle ment, alors elle dit la vérité, ce qui est également une contradiction. Ce paradoxe a des implications profondes pour la logique et la sémantique. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=2tn152iCDpk"  title="Le paradoxe du Sorite par Philosophie Analytique"&gt;Le paradoxe du sorite&lt;/a&gt; (ou paradoxe du tas) : Ce paradoxe questionne à quel moment un tas de grains cesse d'être un tas lorsqu'on enlève un grain à la fois. Il soulève des questions sur les limites floues et les définitions vagues. &lt;/p&gt; &lt;p&gt;Le paradoxe de l'électre : Ce paradoxe explore les problèmes de connaissance et de reconnaissance. Si Electre sait que son frère Oreste est dans la pièce, mais ne reconnaît pas Oreste lorsqu'elle le voit, peut-on dire qu'elle sait vraiment qu'il est là ? &lt;/p&gt; &lt;p&gt;Le paradoxe du voilé : Ce paradoxe pose la question de savoir si on peut reconnaître quelqu'un qui est voilé. Si on ne peut pas le reconnaître, comment peut-on savoir que c'est la même personne ? &lt;/p&gt; &lt;p&gt;  Les paradoxes d'Eubulide ont eu une influence durable sur la philosophie, en particulier dans les domaines de la logique, de la sémantique et de l'épistémologie. Ils ont été étudiés et discutés par de nombreux philosophes ultérieurs, y compris les stoïciens et les sceptiques, et continuent d'être un sujet de débat dans la philosophie contemporaine. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F35" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>285</v>
+        <v>266</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>267</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>236</v>
+        <v>269</v>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; École mégarique</t>
+        </is>
       </c>
       <c r="M35" s="2" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4872,293 +4911,296 @@
         </is>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
-        <v>-385</v>
+        <v>-400</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>291</v>
+        <v>273</v>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ar%C3%A9t%C3%A9_de_Cyr%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;ARÉTÉ de Cyrène&lt;/a&gt; (IVe siècle av. J.-C.) est l’une des premières &lt;a href="https://www.youtube.com/watch?v=9vy8w9K-YgQ" style="color:#88A1E9" title="Arete Of Cyrene 1st Woman Philosopher Before BC par Celebrities World"&gt;femmes philosophes&lt;/a&gt; connues de la Grèce antique. Fille d’Aristippe de Cyrène, disciple de Socrate et fondateur de l’école cyrénaïque, elle reçoit de son père une formation philosophique et prend une place centrale dans la transmission de sa doctrine.&lt;/p&gt; &lt;p&gt;Nous la connaissons surtout par l’historien Diogène Laërce et par d’autres sources tardives, et aucun de ses écrits ne nous est parvenu. Son rôle principal est d’avoir formé son propre fils, Aristippe le Jeune, surnommé « l’instruit par sa mère » (&lt;em&gt;Mêtrodidaktos&lt;/em&gt;), qui donnera à l’école sa forme systématique. &lt;a href="https://www.youtube.com/watch?v=Rp7sm07EJBY&amp;t=324s" style="color:#88A1E9" title="Les Cyrénaîsme par Alain Bajoumée"&gt;Les cyrénaïques&lt;/a&gt; font du plaisir le seul bien et de la douleur le seul mal. Ils fondent cette morale sur une théorie de la connaissance : nous ne connaissons que nos propres sensations, non les choses qui les causent. Le plaisir est un « mouvement doux », la douleur un « mouvement rude » ; le plaisir présent, corporel et vif, est le seul dont nous soyons sûrs, car le passé n’est plus et l’avenir est incertain. Mais le sage cyrénaïque n’est pas un débauché : il cherche à maîtriser le plaisir sans s’en rendre esclave, et à rester libre en toutes circonstances. Une lettre attribuée à Aristippe, sans doute apocryphe, conseille à Arété de gérer ses biens avec mesure et de veiller à l’éducation de son fils.&lt;/p&gt; &lt;p&gt;Des auteurs plus tardifs lui ont prêté une longue carrière d’enseignante et de nombreux livres, sans preuve. Elle reste cependant le symbole de la place des femmes dans la philosophie antique, aux côtés d’Hipparchia ou de Théano.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F36" s="7" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>295</v>
+        <v>279</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="37" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
-        <v>-384</v>
+        <v>-396</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristote"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTOTE&lt;/a&gt; est l'un des philosophes les plus influents de l'histoire occidentale. Disciple de Platon et précepteur d'Alexandre le Grand, il a contribué à de nombreux domaines de la connaissance, notamment la philosophie, la science, la logique,  &lt;a href="https://www.youtube.com/watch?v=Zo1J19uk-Cc" style="color:#88A1E9"   title=" L'éthique de la vertu d'Aristote par Coursitout"&gt; l'éthique&lt;/a&gt;, la politique, la métaphysique, la biologie et la physique. Il a fondé sa propre école, &lt;a href="https://fr.wikipedia.org/wiki/Lyc%C3%A9e_(%C3%A9cole_philosophique)" style="color:#88A1E9"   title="Le Lycée par wikipedia"&gt;le Lycée&lt;/a&gt;. &lt;/p&gt;&lt;p&gt; Ses travaux sont organisés en plusieurs catégories : &lt;/p&gt;&lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=4fhmo_C1VIA" style="color:#88A1E9"   title="ARISTOTE - Les principes de la logique par le Précepteur"&gt; La Logique&lt;/a&gt; : Il est considéré comme le père de la logique formelle.  Il établit une classification des concepts en dix catégories (substance, quantité, qualité, relation, etc.). &lt;/p&gt; &lt;p&gt;La Métaphysique : Il  explore la nature de l'être et de la réalité dans son ouvrage Métaphysique. Il introduit les concepts de &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1946_num_44_3_4064" style="color:#88A1E9"   title="        La première doctrine de la substance : la substance selon Aristotee par  Persée"&gt;"substance"&lt;/a&gt;  (ce qui existe par soi-même) et d'"accident" (ce qui modifie la substance). Il propose une théorie des quatre causes (matérielle, formelle, efficiente et finale) pour expliquer pourquoi les choses existent et changent. &lt;/p&gt; &lt;p&gt;La Politique :  Dans "Politique", il analyse les différentes formes de gouvernement (monarchie, aristocratie, démocratie) et leurs dérives (tyrannie, oligarchie, démagogie). Il défend l'idée que l'homme est un "animal politique" destiné à vivre en société. &lt;/p&gt; La Science et la Biologie : Contrairement à Platon, qui privilégie les idées abstraites, il s'appuie sur l'observation et l'expérience pour étudier la nature.  Il est l'un des premiers à classer les animaux selon leurs caractéristiques communes. &lt;/p&gt; &lt;p&gt;Rhétorique :   Il étudie l'art de persuader, distinguant trois types de preuves : l'ethos (caractère de l'orateur), le pathos (émotions du public) et le logos (argumentation logique). &lt;/p&gt; &lt;p&gt; Il  privilégie &lt;a href="https://www.youtube.com/watch?v=CdOxw_GRKWk&amp;t=173s&amp;ab_channel=CULTUREG" style="color:#88A1E9"   title="L'Empirisme par Culture G"&gt;l' Empirisme&lt;/a&gt;  par l'observation et l'expérience pour comprendre le monde, contrairement à l'idéalisme de Platon. Il  croit que tout dans la nature a une fin ou un but (telos), ce qui influence sa vision du monde. &lt;/p&gt; &lt;p&gt;  Dans son oeuvre "l'Organon", il développe des concepts de logique comme le syllogisme, un raisonnement déductif composé de deux prémisses et d'une conclusion. &lt;/p&gt; &lt;p&gt; Il a également étudié les phénomènes physiques tels que la chute des corps et le mouvement des astres et a développé une logique formelle, qui est encore utilisée aujourd'hui.&lt;/p&gt; &lt;p&gt; Il a soutenu que le but de la vie humaine est l'accomplissement de la "vertu", qui est un état de caractère qui permet de vivre de manière équilibrée et heureuse ainsi qu'une théorie de la politique où il dit que &lt;a href="https://www.youtube.com/watch?v=djOrZrEDMto&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'homme est un animal politique par le Précepteur"&gt; L'homme est un animal politique&lt;/a&gt; et qu'il existe différents types de régimes  (démocratie, oligarchie, monarchie) et que le meilleur est celui qui est gouverné par des personnes vertueuses.   &lt;/p&gt;         &lt;/p&gt; &lt;p&gt;                       &lt;audio controls title="Raison et réalité: l'être avec Aristote par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-07.05.2022-ITEMA_23018730-2020C3372E0467-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;                                            
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/X%C3%A9nocrate"  style="color:#6A142A"  title=" Wikipedia"&gt;XÉNOCRATE&lt;/a&gt; était un philosophe grec, disciple de Platon et un membre éminent de l'Académie platonicienne, qu'il dirigea après Speusippe. Né à Chalcédoine, il dirige l’école de 339 av. J.-C. à sa mort, en 314. Il est considéré comme un représentant de la "vieille Académie", c'est-à-dire de la période où l'Académie platonicienne restait proche des enseignements originaux de Platon. Sa philosophie s'inscrit dans cette tradition, mais il a  développé des  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1948_num_50_3_3399" style="color:#88A1E9" title="Xénocrate et les Orphiques  par persée"&gt;idées originales&lt;/a&gt;, notamment en métaphysique, en éthique et en cosmologie. &lt;/p&gt; &lt;p&gt; Il a interprété les Idées comme des nombres, une approche qui influencera plus tard le néoplatonisme. Il a divisé la réalité en trois niveaux : le monde intelligible (celui des Idées), le monde sensible (celui des phénomènes) et le monde intermédiaire (celui de l'âme et des mathématiques). Il a également développé une cosmologie inspirée de Platon, en particulier du  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1953_num_66_309_3305" style="color:#88A1E9" title=" Les dimensions de l'univers platonicien d'après Timée en 5 mn par persée"&gt;Timée&lt;/a&gt;, et a soutenu que l'univers était organisé de manière harmonieuse par une intelligence divine. Il définit l’âme comme « un nombre qui se meut lui-même », et serait le premier à avoir divisé la philosophie en trois parties : la physique, l’éthique et la logique. &lt;/p&gt; &lt;p&gt; Il  a développé une conception hiérarchisée des dieux, distinguant les dieux suprêmes (comme le Démiurge du Timée de Platon) des dieux inférieurs et des démons. Il  a joué un rôle important dans la transmission et l'interprétation de la philosophie platonicienne. Bien que sa pensée ait été éclipsée par celle d'Aristote et des néoplatoniciens, il a influencé des philosophes ultérieurs comme Plotin et Proclus. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F37" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"La philosophie d'Aristote" par Voyages Endormis</t>
-        </is>
+        <v>284</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aristotélisme ; Essentialisme</t>
-        </is>
+        <v>174</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P37">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="38" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
-        <v>-380</v>
+        <v>-385</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristippe_le_Jeune"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTIPPE le Jeune&lt;/a&gt; était un philosophe grec moins connue que son grand-père, Aristippe de Cyrène, fondateur de l'école &lt;a href="https://www.youtube.com/watch?v=I5PEbJhoUEs" style="color:#88A1E9" title="Aristippe le Cyrénaïque vu sous l'angle d'Ibiza par Chroniques philosophique "&gt;philosophique cyrénaïque&lt;/a&gt;. Les informations sur lui sont relativement limitées et souvent entremêlées avec celles de son grand-père, ce qui rend difficile une distinction claire entre leurs contributions respectives. &lt;/p&gt; &lt;p&gt;  Il  est souvent crédité d'avoir systématisé et formalisé les enseignements de son grand-père, contribuant ainsi à l'évolution de la pensée cyrénaïque. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=QNRG_j24a5U" style="color:#88A1E9" title="L'Hédonisme par la Philosophie du Bonheur "&gt;Hédonisme&lt;/a&gt; : Comme son grand-père, il soutenait que le plaisir est le but ultime de la vie. Cependant, il a peut-être développé une approche plus nuancée, en distinguant entre différents types de plaisirs et en mettant l'accent sur la modération. &lt;/p&gt;
-&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pr%C3%A9sentisme" style="color:#88A1E9" title="Le Présentisme par Wikipedia "&gt;Présentisme&lt;/a&gt; : Il croyait en l'importance de vivre dans le moment présent. Il considérait que le passé est irréversible et le futur incertain, donc le présent est le seul moment où l'on peut véritablement expérimenter le plaisir. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.axiologie.org/nihilisme-definition/valeur-subjective/proposition-9.html" style="color:#88A1E9" title="Le subjectivisme par Axiologie "&gt;Subjectivisme&lt;/a&gt; : Il a également contribué à la théorie de la connaissance des cyrénaïques, qui soutient que la seule certitude que nous avons est celle de nos propres sensations et expériences subjectives. Cette idée a des implications profondes pour l'épistémologie et la philosophie de l'esprit. &lt;/p&gt; &lt;p&gt; Il est une figure importante dans l'histoire de la philosophie grecque, principalement pour son rôle dans la systématisation et la promotion des idées hédonistes de l'école cyrénaïque. &lt;/p&gt; </t>
-        </is>
+        <v>290</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>291</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>310</v>
+        <v>293</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>294</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="n">
+        <v>-384</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristote"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTOTE&lt;/a&gt; est l'un des philosophes les plus influents de l'histoire occidentale. Disciple de Platon et précepteur d'Alexandre le Grand, il a contribué à de nombreux domaines de la connaissance, notamment la philosophie, la science, la logique,  &lt;a href="https://www.youtube.com/watch?v=Zo1J19uk-Cc" style="color:#88A1E9"   title=" L'éthique de la vertu d'Aristote par Coursitout"&gt; l'éthique&lt;/a&gt;, la politique, la métaphysique, la biologie et la physique. Il a fondé sa propre école, &lt;a href="https://fr.wikipedia.org/wiki/Lyc%C3%A9e_(%C3%A9cole_philosophique)" style="color:#88A1E9"   title="Le Lycée par wikipedia"&gt;le Lycée&lt;/a&gt;. &lt;/p&gt;&lt;p&gt; Ses travaux sont organisés en plusieurs catégories : &lt;/p&gt;&lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=4fhmo_C1VIA" style="color:#88A1E9"   title="ARISTOTE - Les principes de la logique par le Précepteur"&gt; La Logique&lt;/a&gt; : Il est considéré comme le père de la logique formelle.  Il établit une classification des concepts en dix catégories (substance, quantité, qualité, relation, etc.). &lt;/p&gt; &lt;p&gt;La Métaphysique : Il  explore la nature de l'être et de la réalité dans son ouvrage Métaphysique. Il introduit les concepts de &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1946_num_44_3_4064" style="color:#88A1E9"   title="        La première doctrine de la substance : la substance selon Aristotee par  Persée"&gt;"substance"&lt;/a&gt;  (ce qui existe par soi-même) et d'"accident" (ce qui modifie la substance). Il propose une théorie des quatre causes (matérielle, formelle, efficiente et finale) pour expliquer pourquoi les choses existent et changent. &lt;/p&gt; &lt;p&gt;La Politique :  Dans "Politique", il analyse les différentes formes de gouvernement (monarchie, aristocratie, démocratie) et leurs dérives (tyrannie, oligarchie, démagogie). Il défend l'idée que l'homme est un "animal politique" destiné à vivre en société. &lt;/p&gt; La Science et la Biologie : Contrairement à Platon, qui privilégie les idées abstraites, il s'appuie sur l'observation et l'expérience pour étudier la nature.  Il est l'un des premiers à classer les animaux selon leurs caractéristiques communes. &lt;/p&gt; &lt;p&gt;Rhétorique :   Il étudie l'art de persuader, distinguant trois types de preuves : l'ethos (caractère de l'orateur), le pathos (émotions du public) et le logos (argumentation logique). &lt;/p&gt; &lt;p&gt; Il  privilégie &lt;a href="https://www.youtube.com/watch?v=CdOxw_GRKWk&amp;t=173s&amp;ab_channel=CULTUREG" style="color:#88A1E9"   title="L'Empirisme par Culture G"&gt;l' Empirisme&lt;/a&gt;  par l'observation et l'expérience pour comprendre le monde, contrairement à l'idéalisme de Platon. Il  croit que tout dans la nature a une fin ou un but (telos), ce qui influence sa vision du monde. &lt;/p&gt; &lt;p&gt;  Dans son oeuvre "l'Organon", il développe des concepts de logique comme le syllogisme, un raisonnement déductif composé de deux prémisses et d'une conclusion. &lt;/p&gt; &lt;p&gt; Il a également étudié les phénomènes physiques tels que la chute des corps et le mouvement des astres et a développé une logique formelle, qui est encore utilisée aujourd'hui.&lt;/p&gt; &lt;p&gt; Il a soutenu que le but de la vie humaine est l'accomplissement de la "vertu", qui est un état de caractère qui permet de vivre de manière équilibrée et heureuse ainsi qu'une théorie de la politique où il dit que &lt;a href="https://www.youtube.com/watch?v=djOrZrEDMto&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'homme est un animal politique par le Précepteur"&gt; L'homme est un animal politique&lt;/a&gt; et qu'il existe différents types de régimes  (démocratie, oligarchie, monarchie) et que le meilleur est celui qui est gouverné par des personnes vertueuses.   &lt;/p&gt;         &lt;/p&gt; &lt;p&gt;                       &lt;audio controls title="Raison et réalité: l'être avec Aristote par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-07.05.2022-ITEMA_23018730-2020C3372E0467-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;                                            
+</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La philosophie d'Aristote" par Voyages Endormis</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="I39" s="9"/>
+      <c r="J39" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aristotélisme ; Essentialisme</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="n">
+        <v>-380</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristippe_le_Jeune"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTIPPE le Jeune&lt;/a&gt; était un philosophe grec moins connue que son grand-père, Aristippe de Cyrène, fondateur de l'école &lt;a href="https://www.youtube.com/watch?v=I5PEbJhoUEs" style="color:#88A1E9" title="Aristippe le Cyrénaïque vu sous l'angle d'Ibiza par Chroniques philosophique "&gt;philosophique cyrénaïque&lt;/a&gt;. Les informations sur lui sont relativement limitées et souvent entremêlées avec celles de son grand-père, ce qui rend difficile une distinction claire entre leurs contributions respectives. &lt;/p&gt; &lt;p&gt;  Il  est souvent crédité d'avoir systématisé et formalisé les enseignements de son grand-père, contribuant ainsi à l'évolution de la pensée cyrénaïque. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=QNRG_j24a5U" style="color:#88A1E9" title="L'Hédonisme par la Philosophie du Bonheur "&gt;Hédonisme&lt;/a&gt; : Comme son grand-père, il soutenait que le plaisir est le but ultime de la vie. Cependant, il a peut-être développé une approche plus nuancée, en distinguant entre différents types de plaisirs et en mettant l'accent sur la modération. &lt;/p&gt;
+&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pr%C3%A9sentisme" style="color:#88A1E9" title="Le Présentisme par Wikipedia "&gt;Présentisme&lt;/a&gt; : Il croyait en l'importance de vivre dans le moment présent. Il considérait que le passé est irréversible et le futur incertain, donc le présent est le seul moment où l'on peut véritablement expérimenter le plaisir. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.axiologie.org/nihilisme-definition/valeur-subjective/proposition-9.html" style="color:#88A1E9" title="Le subjectivisme par Axiologie "&gt;Subjectivisme&lt;/a&gt; : Il a également contribué à la théorie de la connaissance des cyrénaïques, qui soutient que la seule certitude que nous avons est celle de nos propres sensations et expériences subjectives. Cette idée a des implications profondes pour l'épistémologie et la philosophie de l'esprit. &lt;/p&gt; &lt;p&gt; Il est une figure importante dans l'histoire de la philosophie grecque, principalement pour son rôle dans la systématisation et la promotion des idées hédonistes de l'école cyrénaïque. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="I40" s="9"/>
+      <c r="J40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K40" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="M40" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7">
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7">
         <v>-372</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">-288</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">vers 372 A JC - 288 A JC</t>
         </is>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D41" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ophraste"  style="color:#6A142A"  title=" Wikipedia"&gt;THÉOPHRASTE&lt;/a&gt; était un philosophe et naturaliste grec de l'Antiquité, souvent considéré comme le père de la botanique. Il fut un disciple d'Aristote et lui succéda à la tête du Lycée.  Il a écrit sur de nombreux sujets, notamment la logique, la métaphysique, l'éthique et la physique. Il a remis en question certaines des catégories aristotéliciennes et a exploré des questions liées à la causalité et à la nature de l'âme. &lt;/p&gt; &lt;p&gt; Il est célèbre pour ses  &lt;a href="https://www.youtube.com/watch?v=_8w0rzsq7io" style="color:#88A1E9" title="  Approches philosophique et botanique de la croissance végétale chez Théophraste par UMR 8546"&gt;travaux en botanique&lt;/a&gt;, qui constituent une avancée majeure dans l'étude scientifique des plantes. Ses deux principaux ouvrages sur le sujet sont : &lt;/p&gt;
 &lt;p&gt;"Histoire des plantes" : Une encyclopédie en neuf livres qui décrit les caractéristiques, les classifications et les utilisations des plantes. Il y aborde des sujets comme la morphologie, la reproduction et la croissance des végétaux. &lt;/p&gt; &lt;p&gt;"Causes des plantes" : Un traité en six livres qui explore les causes naturelles des phénomènes végétaux, comme la germination, la floraison et la fructification. &lt;/p&gt; &lt;p&gt; 
 Il a classé les plantes en fonction de leurs caractéristiques morphologiques et de leurs usages, jetant les bases de la &lt;a href="https://www.youtube.com/watch?v=E7uRf4fU_pk" style="color:#88A1E9" title="  Histoire de la botanique en 5 mn par Terre D'Avalonne"&gt;taxonomie végétale&lt;/a&gt;. Il a également étudié les relations entre les plantes et leur environnement, anticipant certaines idées de l'écologie moderne. &lt;/p&gt; &lt;p&gt; Outre la botanique, il a écrit sur des sujets variés tels que la minéralogie, la météorologie et la zoologie. Son ouvrage "Sur les pierres" est le premier traité sur les minéraux et leurs propriétés. &lt;/p&gt; &lt;p&gt;  Il  était connu pour son approche empirique et systématique, héritée d'Aristote. Il observait attentivement les phénomènes naturels et cherchait à les expliquer de manière rationnelle. Son style d'écriture était clair et méthodique, ce qui a contribué à la diffusion de ses idées. &lt;/p&gt;  </t>
         </is>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F41" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G41" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H41" s="9" t="s">
         <v>318</v>
-      </c>
-      <c r="I39" s="9"/>
-      <c r="J39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="n">
-        <v>-365</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Crat%C3%A8s_de_Th%C3%A8bes"  style="color:#6A142A"  title=" Wikipedia"&gt;CRATÈS de Thèbes&lt;/a&gt; était un philosophe  grec, disciple de Diogène de Sinope et contemporain d'Alexandre le Grand. Il est connu pour avoir radicalement transformé sa vie en renonçant à sa richesse et en adoptant un mode de vie simple et ascétique, conformément aux principes du &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=134s" style="color:#88A1E9" title=" Les Cynique en 5 mn par Alain Bajomée"&gt;Cynisme&lt;/a&gt;, une école philosophique qui prône la simplicité, l'autosuffisance et le mépris des conventions sociales. &lt;/p&gt; &lt;p&gt;Rejet des biens matériels : Il croyait que la richesse et les possessions matérielles étaient des sources de troubles et d'esclavage. En vivant dans la pauvreté volontaire, il cherchait à atteindre une liberté intérieure et une indépendance vis-à-vis des désirs superflus. &lt;/p&gt; &lt;p&gt;Vie en harmonie avec la nature : Comme les autres cyniques, il prônait un retour à une vie simple, en accord avec la nature. Il rejetait les artifices de la société et vivait de manière frugale, souvent dans la rue ou dans des lieux publics. &lt;/p&gt; &lt;p&gt;Critique des conventions sociales : Il remettait en question les normes sociales, y compris les institutions comme le mariage, la propriété et les hiérarchies sociales. Son mariage avec Hipparchia était une manifestation de cette critique, car il défiait les attentes traditionnelles. &lt;/p&gt; &lt;p&gt;Bienveillance et humour : Contrairement à Diogène, qui était souvent perçu comme provocateur et abrupt, il était connu pour sa gentillesse et son humour. Il était surnommé "l'ouvreur de portes" parce qu'il entrait chez les gens pour leur donner des conseils philosophiques, toujours avec bienveillance. &lt;/p&gt; &lt;p&gt; Ses œuvres étaient souvent satiriques et utilisaient l'humour pour transmettre des messages philosophiques. Par exemple, il a écrit un poème décrivant une cité idéale appelée "Péra", symbolisant une communauté où les biens matériels n'ont aucune importance. &lt;/p&gt; &lt;p&gt; Il est resté une figure respectée dans la tradition philosophique, notamment pour son engagement envers la vertu et sa capacité à vivre selon ses principes. Bien que le cynisme en tant qu'école philosophique ait décliné après l'Antiquité, les idées ont influencé d'autres courants, comme le stoïcisme, et continuent d'inspirer ceux qui cherchent à vivre une vie simple et authentique. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="I40" s="9"/>
-      <c r="J40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="n">
-        <v>-365</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diodore_Cronos"  style="color:#6A142A"  title=" Wikipedia"&gt;Diodore CRONOS&lt;/a&gt; (mort vers 284 av. J.-C.) est un philosophe grec de l’école mégarique, l’un des plus grands logiciens de l’Antiquité. Né à Iasos, en Carie, il enseigne à Athènes et à Alexandrie. Il eut pour élève Zénon de Kition, le fondateur du stoïcisme, ainsi que ses cinq filles, toutes réputées pour leur talent en dialectique. Son surnom de « Cronos », du nom du vieux dieu, se moquait peut-être de lui comme d’un esprit démodé.&lt;/p&gt; &lt;p&gt;Il est surtout célèbre pour l’« argument dominateur », &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1961_num_74_349_3654_t1_0317_0000_2"  style="color:#88A1E9" title=" Le dominateur et les possibles par Persée"&gt;le Dominateur&lt;/a&gt;, que les Anciens jugeaient le plus redoutable des raisonnements. Il part de trois affirmations qui ne peuvent être vraies ensemble : tout ce qui est passé et vrai est nécessaire, car le passé ne peut plus changer ; l’impossible ne peut pas découler du possible ; et il existe un possible qui n’est pas et ne sera jamais vrai. Diodore rejette la troisième. Il en conclut que le possible est ce qui est ou qui sera, et que ce qui n’arrivera jamais n’était pas possible. Cette thèse semble mener au fatalisme, et les stoïciens, comme Chrysippe, ont cherché à y échapper. Diodore propose aussi une définition de l’implication : « si A, alors B » est vrai lorsqu’il n’a jamais été et ne sera jamais le cas que A soit vrai et B faux. Il défend enfin des arguments contre le mouvement : on ne peut jamais dire d’une chose « elle se meut », seulement « elle s’est mue ». La légende raconte qu’il mourut de dépit pour n’avoir pas su résoudre sur-le-champ une énigme posée par Stilpon devant le roi Ptolémée.&lt;/p&gt; &lt;p&gt;Au XXe siècle, le logicien Arthur Prior s’est inspiré de Diodore pour créer la logique du temps.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Socratisme ; École mégarique</t>
-        </is>
+        <v>319</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5166,43 +5208,45 @@
         </is>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="221.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
-        <v>-362</v>
+        <v>-365</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>338</v>
+        <v>323</v>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Crat%C3%A8s_de_Th%C3%A8bes"  style="color:#6A142A"  title=" Wikipedia"&gt;CRATÈS de Thèbes&lt;/a&gt; était un philosophe  grec, disciple de Diogène de Sinope et contemporain d'Alexandre le Grand. Il est connu pour avoir radicalement transformé sa vie en renonçant à sa richesse et en adoptant un mode de vie simple et ascétique, conformément aux principes du &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=134s" style="color:#88A1E9" title=" Les Cynique en 5 mn par Alain Bajomée"&gt;Cynisme&lt;/a&gt;, une école philosophique qui prône la simplicité, l'autosuffisance et le mépris des conventions sociales. &lt;/p&gt; &lt;p&gt;Rejet des biens matériels : Il croyait que la richesse et les possessions matérielles étaient des sources de troubles et d'esclavage. En vivant dans la pauvreté volontaire, il cherchait à atteindre une liberté intérieure et une indépendance vis-à-vis des désirs superflus. &lt;/p&gt; &lt;p&gt;Vie en harmonie avec la nature : Comme les autres cyniques, il prônait un retour à une vie simple, en accord avec la nature. Il rejetait les artifices de la société et vivait de manière frugale, souvent dans la rue ou dans des lieux publics. &lt;/p&gt; &lt;p&gt;Critique des conventions sociales : Il remettait en question les normes sociales, y compris les institutions comme le mariage, la propriété et les hiérarchies sociales. Son mariage avec Hipparchia était une manifestation de cette critique, car il défiait les attentes traditionnelles. &lt;/p&gt; &lt;p&gt;Bienveillance et humour : Contrairement à Diogène, qui était souvent perçu comme provocateur et abrupt, il était connu pour sa gentillesse et son humour. Il était surnommé "l'ouvreur de portes" parce qu'il entrait chez les gens pour leur donner des conseils philosophiques, toujours avec bienveillance. &lt;/p&gt; &lt;p&gt; Ses œuvres étaient souvent satiriques et utilisaient l'humour pour transmettre des messages philosophiques. Par exemple, il a écrit un poème décrivant une cité idéale appelée "Péra", symbolisant une communauté où les biens matériels n'ont aucune importance. &lt;/p&gt; &lt;p&gt; Il est resté une figure respectée dans la tradition philosophique, notamment pour son engagement envers la vertu et sa capacité à vivre selon ses principes. Bien que le cynisme en tant qu'école philosophique ait décliné après l'Antiquité, les idées ont influencé d'autres courants, comme le stoïcisme, et continuent d'inspirer ceux qui cherchent à vivre une vie simple et authentique. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F42" s="7" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>342</v>
+        <v>201</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5210,39 +5254,39 @@
         </is>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
-        <v>-360</v>
+        <v>-365</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stilpon_de_M%C3%A9gare"  style="color:#6A142A"  title=" Wikipedia"&gt;STILPON de Mégare&lt;/a&gt; était est un philosophe, spécialisée dans la dialectique de type éristique. Il est associé à l'école mégarique, fondée par Euclide de Mégare et était connu pour son éloquence et sa capacité à débattre, ce qui lui a valu une grande renommée dans le monde grec. &lt;/p&gt; &lt;p&gt; Les Mégariques étaient connus pour leur intérêt pour les paradoxes et les arguments sophistiqués. &lt;/p&gt; &lt;p&gt;Critique des universaux : Il est surtout connu pour sa critique des idées platoniciennes, en particulier la théorie des Formes. Il soutenait que les concepts généraux (comme "l'homme" ou "le bien") ne peuvent pas exister indépendamment des choses particulières. Pour lui, seules les choses individuelles sont réelles, et les universaux ne sont que des noms ou des constructions mentales. &lt;/p&gt; &lt;p&gt;Réfutation des catégories : Il a également critiqué la théorie des catégories d'Aristote, arguant que les distinctions entre les catégories (comme la substance, la qualité, la quantité) étaient artificielles et ne reflétaient pas la réalité. &lt;/p&gt; &lt;p&gt;Éthique et autosuffisance : Comme d'autres philosophes de son époque, il s'intéressait à l'éthique. Il prônait l'autosuffisance (autarkeia) et la tranquillité de l'âme (ataraxia). Il croyait que le bonheur pouvait être atteint en se libérant des désirs inutiles et en se concentrant sur ce qui est véritablement important. &lt;/p&gt; &lt;p&gt;Dialectique et logique : Il était un maître de la dialectique et utilisait souvent des arguments logiques pour déconstruire les positions de ses adversaires. Il était connu pour sa capacité à réduire les arguments de ses interlocuteurs à l'absurde, ce qui en faisait un redoutable débatteur. &lt;/p&gt; &lt;p&gt; Il était un philosophe dialecticien et éthique, dont les idées ont influencé plusieurs courants philosophiques ultérieurs. Bien que son œuvre ne nous soit pas parvenue directement, sa réputation de penseur rigoureux et son impact sur la philosophie antique sont indéniables. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diodore_Cronos"  style="color:#6A142A"  title=" Wikipedia"&gt;Diodore CRONOS&lt;/a&gt; (mort vers 284 av. J.-C.) est un philosophe grec de l’école mégarique, l’un des plus grands logiciens de l’Antiquité. Né à Iasos, en Carie, il enseigne à Athènes et à Alexandrie. Il eut pour élève Zénon de Kition, le fondateur du stoïcisme, ainsi que ses cinq filles, toutes réputées pour leur talent en dialectique. Son surnom de « Cronos », du nom du vieux dieu, se moquait peut-être de lui comme d’un esprit démodé.&lt;/p&gt; &lt;p&gt;Il est surtout célèbre pour l’« argument dominateur », &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1961_num_74_349_3654_t1_0317_0000_2"  style="color:#88A1E9" title=" Le dominateur et les possibles par Persée"&gt;le Dominateur&lt;/a&gt;, que les Anciens jugeaient le plus redoutable des raisonnements. Il part de trois affirmations qui ne peuvent être vraies ensemble : tout ce qui est passé et vrai est nécessaire, car le passé ne peut plus changer ; l’impossible ne peut pas découler du possible ; et il existe un possible qui n’est pas et ne sera jamais vrai. Diodore rejette la troisième. Il en conclut que le possible est ce qui est ou qui sera, et que ce qui n’arrivera jamais n’était pas possible. Cette thèse semble mener au fatalisme, et les stoïciens, comme Chrysippe, ont cherché à y échapper. Diodore propose aussi une définition de l’implication : « si A, alors B » est vrai lorsqu’il n’a jamais été et ne sera jamais le cas que A soit vrai et B faux. Il défend enfin des arguments contre le mouvement : on ne peut jamais dire d’une chose « elle se meut », seulement « elle s’est mue ». La légende raconte qu’il mourut de dépit pour n’avoir pas su résoudre sur-le-champ une énigme posée par Stilpon devant le roi Ptolémée.&lt;/p&gt; &lt;p&gt;Au XXe siècle, le logicien Arthur Prior s’est inspiré de Diodore pour créer la logique du temps.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F43" s="7" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>351</v>
+        <v>269</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -5250,7 +5294,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5258,43 +5302,43 @@
         </is>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="221.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
-        <v>-360</v>
+        <v>-362</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>359</v>
+        <v>252</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>302</v>
+        <v>342</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5302,92 +5346,91 @@
         </is>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
-        <v>-341</v>
+        <v>-360</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9donisme" style="color:#88A1E9"   title="L'hédonisme par Wikipédia"&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href="https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur"   title="L'épicurisme par le Précepteur"&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href="https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'épicurisme par le Précepteur"&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href="https://www.youtube.com/watch?v=cb1YHXSuxlM"   title="La philosophie du bonheur par Parole de philosophe"&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées "atomes".&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt; &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title="Est il bien raisonnable d'avoir peur de la mort par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        <v>346</v>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stilpon_de_M%C3%A9gare"  style="color:#6A142A"  title=" Wikipedia"&gt;STILPON de Mégare&lt;/a&gt; était est un philosophe, spécialisée dans la dialectique de type éristique. Il est associé à l'école mégarique, fondée par Euclide de Mégare et était connu pour son éloquence et sa capacité à débattre, ce qui lui a valu une grande renommée dans le monde grec. &lt;/p&gt; &lt;p&gt; Les Mégariques étaient connus pour leur intérêt pour les paradoxes et les arguments sophistiqués. &lt;/p&gt; &lt;p&gt;Critique des universaux : Il est surtout connu pour sa critique des idées platoniciennes, en particulier la théorie des Formes. Il soutenait que les concepts généraux (comme "l'homme" ou "le bien") ne peuvent pas exister indépendamment des choses particulières. Pour lui, seules les choses individuelles sont réelles, et les universaux ne sont que des noms ou des constructions mentales. &lt;/p&gt; &lt;p&gt;Réfutation des catégories : Il a également critiqué la théorie des catégories d'Aristote, arguant que les distinctions entre les catégories (comme la substance, la qualité, la quantité) étaient artificielles et ne reflétaient pas la réalité. &lt;/p&gt; &lt;p&gt;Éthique et autosuffisance : Comme d'autres philosophes de son époque, il s'intéressait à l'éthique. Il prônait l'autosuffisance (autarkeia) et la tranquillité de l'âme (ataraxia). Il croyait que le bonheur pouvait être atteint en se libérant des désirs inutiles et en se concentrant sur ce qui est véritablement important. &lt;/p&gt; &lt;p&gt;Dialectique et logique : Il était un maître de la dialectique et utilisait souvent des arguments logiques pour déconstruire les positions de ses adversaires. Il était connu pour sa capacité à réduire les arguments de ses interlocuteurs à l'absurde, ce qui en faisait un redoutable débatteur. &lt;/p&gt; &lt;p&gt; Il était un philosophe dialecticien et éthique, dont les idées ont influencé plusieurs courants philosophiques ultérieurs. Bien que son œuvre ne nous soit pas parvenue directement, sa réputation de penseur rigoureux et son impact sur la philosophie antique sont indéniables. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F45" s="7" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>369</v>
+        <v>351</v>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; École mégarique</t>
+        </is>
       </c>
       <c r="M45" s="2" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="46" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
-        <v>-340</v>
+        <v>-360</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>371</v>
+        <v>304</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -5395,32 +5438,32 @@
         </is>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
-        <v>-334</v>
+        <v>-341</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Z%C3%A9non_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;ZENON de Kition&lt;/a&gt; (vers 334-262 av. J.-C.) est le fondateur de l’école &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcienne&lt;/a&gt;. Né à Kition, dans l’île de Chypre, il arrive à Athènes vers 312 av. J.-C. après un naufrage. Selon la légende, il lit chez un libraire les souvenirs de Xénophon sur Socrate et demande où trouver de tels hommes : le libraire lui montre le cynique Cratès qui passait. Zénon suit ses leçons, puis celles du mégarique Stilpon et des platoniciens.&lt;/p&gt; &lt;p&gt;Vers 300 av. J.-C., il enseigne sous le Portique peint d’Athènes, la &lt;em&gt;Stoa poikilè&lt;/em&gt;, d’où le nom de stoïcisme. Ses livres sont perdus. Il divise la philosophie en trois parties, que les stoïciens comparent à un jardin : la logique en est la clôture, la physique les arbres, l’éthique les fruits. Le monde est un tout vivant, ordonné par une raison divine, le &lt;em&gt;logos&lt;/em&gt;, présente en toute chose comme un feu artiste. Le but de la vie est de « vivre en accord avec la nature », c’est-à-dire avec la raison. La vertu est le seul bien, le vice le seul mal ; la santé, la richesse ou la réputation sont « indifférentes ». Les passions, comme la peur, le chagrin ou la colère, sont des jugements erronés et des élans excessifs : le sage s’en libère et atteint la tranquillité. Pour expliquer la connaissance, Zénon montre sa main ouverte, puis la ferme peu à peu jusqu’à serrer le poing : la sensation, l’assentiment, la compréhension, la science.&lt;/p&gt; &lt;p&gt;Les Athéniens honorent sa vertu d’une couronne d’or. Ses successeurs, Cléanthe et Chrysippe, développent sa doctrine, qui marquera Sénèque, Épictète et Marc Aurèle.&lt;/p&gt;</t>
+        <v>363</v>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9donisme" style="color:#88A1E9"   title="L'hédonisme par Wikipédia"&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href="https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur"   title="L'épicurisme par le Précepteur"&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href="https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'épicurisme par le Précepteur"&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href="https://www.youtube.com/watch?v=cb1YHXSuxlM"   title="La philosophie du bonheur par Parole de philosophe"&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées "atomes".&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt; &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title="Est il bien raisonnable d'avoir peur de la mort par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F47" s="7" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="2" t="s">
@@ -5430,10 +5473,10 @@
         <v>368</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -5441,35 +5484,33 @@
         </is>
       </c>
       <c r="P47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
-        <v>-330</v>
+        <v>-340</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9anthe"  style="color:#6A142A"  title=" Wikipedia"&gt;CLÉANTHE&lt;/a&gt; (vers 330-232 av. J.-C.) est un philosophe stoïcien grec, successeur de Zénon de Kition à la tête de l’école du Portique. Né à Assos, en Asie Mineure, ancien pugiliste, il arrive à Athènes presque sans ressources ; pour payer ses études, il tire de l’eau la nuit dans les jardins, ce qui lui vaut le surnom de « puiseur d’eau ». Il suit l’enseignement de Zénon pendant dix-neuf ans. Ses camarades le surnomment « l’âne », parce qu’il apprend lentement, mais il répond qu’il est le seul à pouvoir porter le fardeau de Zénon.&lt;/p&gt; &lt;p&gt;Il dirige l’école de 262 à sa mort. Moins brillant dialecticien que son successeur Chrysippe, il apporte pourtant des idées propres, surtout en physique et en théologie. Pour lui, l’univers est un être vivant animé par un souffle de feu, dont la tension maintient l’unité de toutes choses ; le soleil en est la partie directrice. Il défend une morale exigeante : la vertu est le seul bien, et le plaisir n’est pas conforme à la nature. Son œuvre la plus célèbre est l’&lt;a href="https://www.persee.fr/doc/rea_0035-2004_1998_num_100_1_4719" style="color:#88A1E9" title="L'universel &amp; le singulier. L'hymne à Zeus de Cléanthe. par Persée"&gt;&lt;em&gt;Hymne à Zeus&lt;/em&gt;&lt;/a&gt;, poème où Zeus est identifié à la raison universelle qui gouverne le monde : seuls les méchants s’en écartent, par ignorance. Une autre prière, citée par Épictète et traduite par Sénèque, résume l’attitude stoïcienne : « Conduis-moi, Zeus, et toi, Destinée, là où vous m’avez fixé ma place. » Sénèque en tire la formule : « Le destin conduit celui qui consent, il traîne celui qui résiste. »&lt;/p&gt; &lt;p&gt;Il meurt très âgé, en jeûnant. Hume a donné son nom au défenseur de &lt;a href="https://www.youtube.com/watch?v=HBbaB-X6xCI" style="color:#88A1E9" title=" L'argument a posteriori 1/2 : le raisonnement par analogie de Cléanthe par Gresza"&gt;l’argument par analogie&lt;/a&gt; dans ses &lt;em&gt;Dialogues sur la religion naturelle&lt;/em&gt;.&lt;/p&gt;</t>
-        </is>
+        <v>373</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>374</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="2" t="s">
@@ -5479,10 +5520,10 @@
         <v>368</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>386</v>
+        <v>278</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -5490,91 +5531,94 @@
         </is>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
-        <v>-325</v>
+        <v>-334</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bion_de_Borysth%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;BION de Borysthène&lt;/a&gt; était un écrivain et un philosophe cynique grec connu pour ses idées critiques envers les conventions sociales et pour son style de vie ascétique, caractéristique des philosophes cyniques. Il était d'origine modeste, selon certaines sources et cette condition sociale a probablement influencé sa critique acerbe des hiérarchies et des conventions sociales. &lt;/p&gt; &lt;p&gt; Après avoir été vendu comme esclave, il fut libéré et reçut une éducation philosophique auprès de divers maîtres, et peut-être aussi auprès de représentants d'autres écoles philosophiques, comme les académiciens ou les péripatéticiens. Cette diversité d'influences se reflète dans sa   &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme" title="eclectisme par wikipedia"&gt;pensée éclectique&lt;/a&gt;. Il suit en effet tour à tour l’Académie, le cynique Cratès, le cyrénaïque Théodore l’Athée et le péripatéticien Théophraste.  Il adopta le mode de vie cynique, caractérisé par un rejet des richesses, des plaisirs matériels et des conventions sociales. &lt;/p&gt; &lt;p&gt; Il était également un écrivain talentueux, connu pour ses &lt;em&gt;Diatribes&lt;/em&gt;, des discours philosophiques souvent satiriques et moralisateurs.  &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1978_num_1_1_3417_t1_0102_0000_2" style="color:#88A1E9" title="Jan Fredrik Kindstrand, Bion of Borysthenes. A collection of the Fragments with introduction and commentary  par Persée"&gt;Ses textes&lt;/a&gt; ont influencé des auteurs ultérieurs, comme Horace et Sénèque, qui ont repris certains de ses thèmes et de ses techniques littéraires. Ératosthène disait de lui qu’il fut le premier à habiller la philosophie de vêtements fleuris. Il vécut un temps à la cour du roi de Macédoine Antigone Gonatas. &lt;/p&gt; &lt;p&gt; Il incarne l'esprit cynique par excellence : libre, provocateur et profondément critique envers les conventions sociales. Sa vie et son œuvre témoignent d'une quête de vérité et d'authenticité, qui continue de résonner aujourd'hui. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Z%C3%A9non_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;ZENON de Kition&lt;/a&gt; (vers 334-262 av. J.-C.) est le fondateur de l’école &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcienne&lt;/a&gt;. Né à Kition, dans l’île de Chypre, il arrive à Athènes vers 312 av. J.-C. après un naufrage. Selon la légende, il lit chez un libraire les souvenirs de Xénophon sur Socrate et demande où trouver de tels hommes : le libraire lui montre le cynique Cratès qui passait. Zénon suit ses leçons, puis celles du mégarique Stilpon et des platoniciens.&lt;/p&gt; &lt;p&gt;Vers 300 av. J.-C., il enseigne sous le Portique peint d’Athènes, la &lt;em&gt;Stoa poikilè&lt;/em&gt;, d’où le nom de stoïcisme. Ses livres sont perdus. Il divise la philosophie en trois parties, que les stoïciens comparent à un jardin : la logique en est la clôture, la physique les arbres, l’éthique les fruits. Le monde est un tout vivant, ordonné par une raison divine, le &lt;em&gt;logos&lt;/em&gt;, présente en toute chose comme un feu artiste. Le but de la vie est de « vivre en accord avec la nature », c’est-à-dire avec la raison. La vertu est le seul bien, le vice le seul mal ; la santé, la richesse ou la réputation sont « indifférentes ». Les passions, comme la peur, le chagrin ou la colère, sont des jugements erronés et des élans excessifs : le sage s’en libère et atteint la tranquillité. Pour expliquer la connaissance, Zénon montre sa main ouverte, puis la ferme peu à peu jusqu’à serrer le poing : la sensation, l’assentiment, la compréhension, la science.&lt;/p&gt; &lt;p&gt;Les Athéniens honorent sa vertu d’une couronne d’or. Ses successeurs, Cléanthe et Chrysippe, développent sa doctrine, qui marquera Sénèque, Épictète et Marc Aurèle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F49" s="7" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>200</v>
+        <v>368</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>201</v>
+        <v>386</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
-        <v>-315</v>
+        <v>-330</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Wikipedia"&gt;ARCÉSILAS de Pitane&lt;/a&gt; fut l'un des philosophes les plus originaux de l'Antiquité, fondateur de la Moyenne Académie. En prenant la direction de l'Académie platonicienne vers 268 av. J.-C., il en transforma radicalement l'esprit en introduisant le scepticisme comme méthode philosophique fondamentale.&lt;/p&gt; &lt;p&gt;S'inspirant de &lt;a href="https://fr.wikipedia.org/wiki/Pyrrhon_d%27%C3%89lis" style="color:#6A142A" title="Pyrrhon sur Wikipedia"&gt;Pyrrhon d'Élis&lt;/a&gt; et de la pratique dialectique de Socrate, Arcésilas défendit la thèse que la suspension du jugement (&lt;em&gt;épochè&lt;/em&gt;) est la seule attitude raisonnable face à l'incertitude de la connaissance. Il combattit vigoureusement le dogmatisme stoïcien de Zénon de Kition, notamment la notion de « représentation compréhensive » (&lt;em&gt;phantasia kataleptike&lt;/em&gt;) censée fonder la certitude.&lt;/p&gt; &lt;p&gt;Fidèle à l'esprit socratique, Arcésilas n'écrivit rien. Il enseignait oralement, par le dialogue et la réfutation. Sa pensée est connue par les rapports de Cicéron, Sextus Empiricus et Diogène Laërce. Sa maxime : &lt;em&gt;« Suspendre son jugement est ce qu'il y a de plus sage »&lt;/em&gt;. Il incarne la résistance intellectuelle au dogmatisme et reste une référence majeure pour toute philosophie du doute. Né à Pitane, en Éolide, il étudie d’abord auprès de Théophraste, au Lycée, avant de rejoindre l’Académie de Polémon et de Crantor. Sa méthode consiste à argumenter pour et contre chaque thèse, jusqu’à montrer qu’elles se valent. Pour agir sans rien affirmer, il suffit, selon lui, de suivre ce qui paraît raisonnable. Un stoïcien se moquait de lui en le comparant à une chimère : « Platon par-devant, Pyrrhon par-derrière, Diodore au milieu ».&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9anthe"  style="color:#6A142A"  title=" Wikipedia"&gt;CLÉANTHE&lt;/a&gt; (vers 330-232 av. J.-C.) est un philosophe stoïcien grec, successeur de Zénon de Kition à la tête de l’école du Portique. Né à Assos, en Asie Mineure, ancien pugiliste, il arrive à Athènes presque sans ressources ; pour payer ses études, il tire de l’eau la nuit dans les jardins, ce qui lui vaut le surnom de « puiseur d’eau ». Il suit l’enseignement de Zénon pendant dix-neuf ans. Ses camarades le surnomment « l’âne », parce qu’il apprend lentement, mais il répond qu’il est le seul à pouvoir porter le fardeau de Zénon.&lt;/p&gt; &lt;p&gt;Il dirige l’école de 262 à sa mort. Moins brillant dialecticien que son successeur Chrysippe, il apporte pourtant des idées propres, surtout en physique et en théologie. Pour lui, l’univers est un être vivant animé par un souffle de feu, dont la tension maintient l’unité de toutes choses ; le soleil en est la partie directrice. Il défend une morale exigeante : la vertu est le seul bien, et le plaisir n’est pas conforme à la nature. Son œuvre la plus célèbre est l’&lt;a href="https://www.persee.fr/doc/rea_0035-2004_1998_num_100_1_4719" style="color:#88A1E9" title="L'universel &amp; le singulier. L'hymne à Zeus de Cléanthe. par Persée"&gt;&lt;em&gt;Hymne à Zeus&lt;/em&gt;&lt;/a&gt;, poème où Zeus est identifié à la raison universelle qui gouverne le monde : seuls les méchants s’en écartent, par ignorance. Une autre prière, citée par Épictète et traduite par Sénèque, résume l’attitude stoïcienne : « Conduis-moi, Zeus, et toi, Destinée, là où vous m’avez fixé ma place. » Sénèque en tire la formule : « Le destin conduit celui qui consent, il traîne celui qui résiste. »&lt;/p&gt; &lt;p&gt;Il meurt très âgé, en jeûnant. Hume a donné son nom au défenseur de &lt;a href="https://www.youtube.com/watch?v=HBbaB-X6xCI" style="color:#88A1E9" title=" L'argument a posteriori 1/2 : le raisonnement par analogie de Cléanthe par Gresza"&gt;l’argument par analogie&lt;/a&gt; dans ses &lt;em&gt;Dialogues sur la religion naturelle&lt;/em&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F50" s="7" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>252</v>
+        <v>368</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -5582,45 +5626,45 @@
         </is>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
-        <v>-306</v>
+        <v>-325</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Persaios_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;PERSAIOS de Kition&lt;/a&gt;  était un disciple direct de Zénon de Cition, le fondateur du stoïcisme, et a joué un rôle important dans la diffusion des idées stoïciennes, bien que sa vie et son œuvre restent mal documentées en raison du peu de sources qui nous sont parvenues. Il aurait été l'esclave ou le pupille de Zénon avant de devenir son disciple et ami. Cette relation étroite avec le fondateur du stoïcisme lui a permis de jouer un rôle important dans les premiers développements de l'école. &lt;/p&gt; &lt;p&gt;  En tant que conseiller du roi Antigone II Gonatas, il a cherché à mettre en œuvre les idéaux stoïciens de vertu et de raison dans la gouvernance. Cela reflète une tendance du stoïcisme à s'engager dans le monde réel plutôt qu'à rester confiné à des spéculations abstraites. Il a écrit un ouvrage intitulé "Sur la royauté", dans lequel il explorait les qualités nécessaires pour être un bon roi selon les principes stoïciens. Pour lui, un dirigeant idéal devait être vertueux, rationnel et guidé par l'intérêt général plutôt que par des désirs égoïstes. &lt;/p&gt; &lt;p&gt; Contrairement à certains philosophes qui se concentraient sur des débats théoriques, il insistait sur l'importance de vivre selon les principes stoïciens dans la vie quotidienne.Il a critiqué la poursuite des plaisirs, une idée qui rejoint l'enseignement stoïcien selon lequel les plaisirs corporels et matériels sont des distractions par rapport à la vertu et à la raison. Il a soutenu que le bonheur véritable ne peut être trouvé que dans la sagesse et la maîtrise de soi. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bion_de_Borysth%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;BION de Borysthène&lt;/a&gt; était un écrivain et un philosophe cynique grec connu pour ses idées critiques envers les conventions sociales et pour son style de vie ascétique, caractéristique des philosophes cyniques. Il était d'origine modeste, selon certaines sources et cette condition sociale a probablement influencé sa critique acerbe des hiérarchies et des conventions sociales. &lt;/p&gt; &lt;p&gt; Après avoir été vendu comme esclave, il fut libéré et reçut une éducation philosophique auprès de divers maîtres, et peut-être aussi auprès de représentants d'autres écoles philosophiques, comme les académiciens ou les péripatéticiens. Cette diversité d'influences se reflète dans sa   &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme" title="eclectisme par wikipedia"&gt;pensée éclectique&lt;/a&gt;. Il suit en effet tour à tour l’Académie, le cynique Cratès, le cyrénaïque Théodore l’Athée et le péripatéticien Théophraste.  Il adopta le mode de vie cynique, caractérisé par un rejet des richesses, des plaisirs matériels et des conventions sociales. &lt;/p&gt; &lt;p&gt; Il était également un écrivain talentueux, connu pour ses &lt;em&gt;Diatribes&lt;/em&gt;, des discours philosophiques souvent satiriques et moralisateurs.  &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1978_num_1_1_3417_t1_0102_0000_2" style="color:#88A1E9" title="Jan Fredrik Kindstrand, Bion of Borysthenes. A collection of the Fragments with introduction and commentary  par Persée"&gt;Ses textes&lt;/a&gt; ont influencé des auteurs ultérieurs, comme Horace et Sénèque, qui ont repris certains de ses thèmes et de ses techniques littéraires. Ératosthène disait de lui qu’il fut le premier à habiller la philosophie de vêtements fleuris. Il vécut un temps à la cour du roi de Macédoine Antigone Gonatas. &lt;/p&gt; &lt;p&gt; Il incarne l'esprit cynique par excellence : libre, provocateur et profondément critique envers les conventions sociales. Sa vie et son œuvre témoignent d'une quête de vérité et d'authenticité, qui continue de résonner aujourd'hui. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F51" s="7" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>386</v>
+        <v>201</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -5628,43 +5672,45 @@
         </is>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="209.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
-        <v>-281</v>
+        <v>-315</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>423</v>
+        <v>406</v>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Wikipedia"&gt;ARCÉSILAS de Pitane&lt;/a&gt; fut l'un des philosophes les plus originaux de l'Antiquité, fondateur de la Moyenne Académie. En prenant la direction de l'Académie platonicienne vers 268 av. J.-C., il en transforma radicalement l'esprit en introduisant le scepticisme comme méthode philosophique fondamentale.&lt;/p&gt; &lt;p&gt;S'inspirant de &lt;a href="https://fr.wikipedia.org/wiki/Pyrrhon_d%27%C3%89lis" style="color:#6A142A" title="Pyrrhon sur Wikipedia"&gt;Pyrrhon d'Élis&lt;/a&gt; et de la pratique dialectique de Socrate, Arcésilas défendit la thèse que la suspension du jugement (&lt;em&gt;épochè&lt;/em&gt;) est la seule attitude raisonnable face à l'incertitude de la connaissance. Il combattit vigoureusement le dogmatisme stoïcien de Zénon de Kition, notamment la notion de « représentation compréhensive » (&lt;em&gt;phantasia kataleptike&lt;/em&gt;) censée fonder la certitude.&lt;/p&gt; &lt;p&gt;Fidèle à l'esprit socratique, Arcésilas n'écrivit rien. Il enseignait oralement, par le dialogue et la réfutation. Sa pensée est connue par les rapports de Cicéron, Sextus Empiricus et Diogène Laërce. Sa maxime : &lt;em&gt;« Suspendre son jugement est ce qu'il y a de plus sage »&lt;/em&gt;. Il incarne la résistance intellectuelle au dogmatisme et reste une référence majeure pour toute philosophie du doute. Né à Pitane, en Éolide, il étudie d’abord auprès de Théophraste, au Lycée, avant de rejoindre l’Académie de Polémon et de Crantor. Sa méthode consiste à argumenter pour et contre chaque thèse, jusqu’à montrer qu’elles se valent. Pour agir sans rien affirmer, il suffit, selon lui, de suivre ce qui paraît raisonnable. Un stoïcien se moquait de lui en le comparant à une chimère : « Platon par-devant, Pyrrhon par-derrière, Diodore au milieu ».&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F52" s="7" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>427</v>
+        <v>252</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>428</v>
+        <v>342</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -5672,45 +5718,45 @@
         </is>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
-        <v>-280</v>
+        <v>-306</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s" style="color:#6A142A" title="Wikipedia"&gt;LACYDÈS de Cyrène&lt;/a&gt; (mort vers 205 av. J.-C.) est un philosophe grec, successeur d’&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Arcésilas sur Wikipedia"&gt;Arcésilas de Pitane&lt;/a&gt; à la tête de l’Académie, l’école fondée à Athènes par Platon. Originaire de Cyrène, en Libye actuelle, il vient étudier à Athènes et devient le disciple d’Arcésilas, auquel il succède vers 241 av. J.-C.&lt;/p&gt; &lt;p&gt;Il enseigne dans un jardin de l’Académie aménagé pour lui par le roi Attale Ier de Pergame, admirateur de la philosophie, et qu’on appelle le &lt;em&gt;Lacydion&lt;/em&gt;. Invité à la cour de ce roi, il refuse de s’y rendre, en disant que les portraits des rois se regardent de loin. Lacydès reste fidèle au &lt;a href="https://www.youtube.com/watch?v=kG3klWpBf2Y"  title="Le sceptisisme de la nouvelle-académie"&gt;scepticisme académique&lt;/a&gt; de son maître. Contre les stoïciens, qui croient à des perceptions si claires qu’elles garantissent la vérité, les académiciens soutiennent que rien ne peut être connu avec certitude : toute impression vraie pourrait être imitée par une impression fausse. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et se contenter de ce qui paraît raisonnable. Une anecdote rapportée par les Anciens illustre, avec humour, les difficultés de cette position : ses esclaves volaient ses provisions puis remettaient les scellés intacts ; pris sur le fait, ils lui auraient opposé sa propre doctrine : comment pouvait-il être sûr de ce qu’il voyait ?&lt;/p&gt; &lt;p&gt;Atteint de paralysie dans sa vieillesse, il confie de son vivant la direction de l’école à ses disciples Téléclès et Évandre, cas rare dans l’histoire de l’Académie. Selon Diogène Laërce, il aurait écrit des traités sur la philosophie et sur la nature, aujourd’hui perdus.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Persaios_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;PERSAIOS de Kition&lt;/a&gt;  était un disciple direct de Zénon de Cition, le fondateur du stoïcisme, et a joué un rôle important dans la diffusion des idées stoïciennes, bien que sa vie et son œuvre restent mal documentées en raison du peu de sources qui nous sont parvenues. Il aurait été l'esclave ou le pupille de Zénon avant de devenir son disciple et ami. Cette relation étroite avec le fondateur du stoïcisme lui a permis de jouer un rôle important dans les premiers développements de l'école. &lt;/p&gt; &lt;p&gt;  En tant que conseiller du roi Antigone II Gonatas, il a cherché à mettre en œuvre les idéaux stoïciens de vertu et de raison dans la gouvernance. Cela reflète une tendance du stoïcisme à s'engager dans le monde réel plutôt qu'à rester confiné à des spéculations abstraites. Il a écrit un ouvrage intitulé "Sur la royauté", dans lequel il explorait les qualités nécessaires pour être un bon roi selon les principes stoïciens. Pour lui, un dirigeant idéal devait être vertueux, rationnel et guidé par l'intérêt général plutôt que par des désirs égoïstes. &lt;/p&gt; &lt;p&gt; Contrairement à certains philosophes qui se concentraient sur des débats théoriques, il insistait sur l'importance de vivre selon les principes stoïciens dans la vie quotidienne.Il a critiqué la poursuite des plaisirs, une idée qui rejoint l'enseignement stoïcien selon lequel les plaisirs corporels et matériels sont des distractions par rapport à la vertu et à la raison. Il a soutenu que le bonheur véritable ne peut être trouvé que dans la sagesse et la maîtrise de soi. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F53" s="7" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>252</v>
+        <v>24</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -5718,47 +5764,43 @@
         </is>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="209.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
-        <v>-240</v>
+        <v>-281</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89vandre_(philosophe)" title="Wikipedia"&gt;ÉVANDRE&lt;/a&gt; (IIIe siècle av. J.-C.) est un philosophe grec originaire de Phocée, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de &lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s_de_Cyr%C3%A8ne" title=" Wikipedia"&gt;Lacydès de Cyrène&lt;/a&gt;, il reçoit de lui, avec Téléclès, la direction de l’école du vivant même de leur maître : Lacydès, malade, la leur confie vers 224 av. J.-C. Évandre et Téléclès la dirigent ensemble, cas rare dans l’histoire de l’institution.&lt;/p&gt; &lt;p&gt;Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par &lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" title=" Wikipedia"&gt;Arcésilas&lt;/a&gt;. Celui-ci avait donné à l’école platonicienne une orientation sceptique, en s’appuyant sur le Socrate qui affirmait ne rien savoir. Contre les stoïciens, qui pensaient que certaines représentations sont si évidentes qu’elles garantissent la vérité, les académiciens soutiennent qu’aucune perception ne permet de distinguer avec certitude le vrai du faux : un rêve, une illusion ou un jumeau peuvent produire la même impression qu’une perception exacte. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et ne rien affirmer. Pour agir, il suffit de suivre ce qui paraît raisonnable. Les académiciens enseignaient en argumentant pour et contre chaque thèse, afin de montrer que les deux positions se valent et d’exercer l’esprit critique de leurs élèves. Évandre transmet cet héritage à une génération d’étudiants.&lt;/p&gt; &lt;p&gt;Aucun de ses écrits ne nous est parvenu. Il a pour successeur Hégésinous de Pergame, qui forme à son tour &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant penseur de la Nouvelle Académie.&lt;/p&gt;</t>
-        </is>
+        <v>422</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>423</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>445</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>252</v>
+        <v>427</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>342</v>
+        <v>428</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5766,32 +5808,32 @@
         </is>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
-        <v>-230</v>
+        <v>-280</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame" title="Wikipedia"&gt;Hégésinous de PERGAME&lt;/a&gt; (IIe siècle av. J.-C.) est un philosophe grec, chef de l’Académie, l’école fondée à Athènes par Platon. Originaire de Pergame, en Asie Mineure, il succède à Évandre et Téléclès, qui avaient dirigé ensemble l’école, et il a pour élève et successeur &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant dialecticien de l’Antiquité.&lt;/p&gt; &lt;p&gt;Nous ne connaissons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu : son nom nous est connu par les listes des chefs successifs de l’Académie et par Cicéron, qui indique que Carnéade l’eut pour maître. Il appartient à la période sceptique de l’Académie, inaugurée par Arcésilas. Les académiciens de ce temps refusent d’affirmer quoi que ce soit avec certitude. Contre les stoïciens, qui croient que certaines perceptions portent en elles la marque de leur vérité, ils montrent qu’une perception vraie pourrait toujours être imitée par une perception fausse, comme dans le rêve ou l’illusion. Il faut donc suspendre son jugement. Mais cela n’empêche pas de vivre : pour agir, on peut suivre ce qui paraît raisonnable. L’enseignement de l’Académie se fait par la discussion contradictoire, en argumentant pour et contre chaque thèse. C’est cette méthode que Carnéade portera à son sommet : envoyé à Rome en ambassade en 155 av. J.-C., il fit scandale en défendant un jour la justice, puis en la réfutant le lendemain.&lt;/p&gt; &lt;p&gt;Hégésinous est ainsi un maillon de la transmission entre la Moyenne et la Nouvelle Académie, durant la période de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique" style="color:#6A142A" title="Philosophie hellénistique sur Wikipedia"&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;</t>
+        <v>432</v>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s" style="color:#6A142A" title="Wikipedia"&gt;LACYDÈS de Cyrène&lt;/a&gt; (mort vers 205 av. J.-C.) est un philosophe grec, successeur d’&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Arcésilas sur Wikipedia"&gt;Arcésilas de Pitane&lt;/a&gt; à la tête de l’Académie, l’école fondée à Athènes par Platon. Originaire de Cyrène, en Libye actuelle, il vient étudier à Athènes et devient le disciple d’Arcésilas, auquel il succède vers 241 av. J.-C.&lt;/p&gt; &lt;p&gt;Il enseigne dans un jardin de l’Académie aménagé pour lui par le roi Attale Ier de Pergame, admirateur de la philosophie, et qu’on appelle le &lt;em&gt;Lacydion&lt;/em&gt;. Invité à la cour de ce roi, il refuse de s’y rendre, en disant que les portraits des rois se regardent de loin. Lacydès reste fidèle au &lt;a href="https://www.youtube.com/watch?v=kG3klWpBf2Y"  title="Le sceptisisme de la nouvelle-académie"&gt;scepticisme académique&lt;/a&gt; de son maître. Contre les stoïciens, qui croient à des perceptions si claires qu’elles garantissent la vérité, les académiciens soutiennent que rien ne peut être connu avec certitude : toute impression vraie pourrait être imitée par une impression fausse. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et se contenter de ce qui paraît raisonnable. Une anecdote rapportée par les Anciens illustre, avec humour, les difficultés de cette position : ses esclaves volaient ses provisions puis remettaient les scellés intacts ; pris sur le fait, ils lui auraient opposé sa propre doctrine : comment pouvait-il être sûr de ce qu’il voyait ?&lt;/p&gt; &lt;p&gt;Atteint de paralysie dans sa vieillesse, il confie de son vivant la direction de l’école à ses disciples Téléclès et Évandre, cas rare dans l’histoire de l’Académie. Selon Diogène Laërce, il aurait écrit des traités sur la philosophie et sur la nature, aujourd’hui perdus.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F55" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="G55" s="15" t="s">
-        <v>452</v>
+        <v>434</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>435</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="2" t="s">
@@ -5804,7 +5846,7 @@
         <v>342</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5812,34 +5854,36 @@
         </is>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
-        <v>-213</v>
+        <v>-240</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Wikipedia"&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href="https://fr.wikipedia.org/wiki/Dialectique" title="Dialectique par Wikipedia"&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272" title="Opinion et certitude par Persee"&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron" style="color:#6A142A" title="Cicéron sur Wikipedia"&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il. Formé à la dialectique par le stoïcien Diogène de Babylone, il étudie de près l’œuvre de Chrysippe pour mieux la réfuter, au point de dire : « Sans Chrysippe, je ne serais pas. » Il distingue trois degrés de vraisemblance : la représentation simplement probable, celle qui n’est contredite par aucune autre, et celle qui a été examinée sous tous ses aspects. Il critique aussi la divination, le destin et la providence des stoïciens. Son disciple Clitomaque a mis par écrit son enseignement.&lt;/p&gt;</t>
+        <v>440</v>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89vandre_(philosophe)" title="Wikipedia"&gt;ÉVANDRE&lt;/a&gt; (IIIe siècle av. J.-C.) est un philosophe grec originaire de Phocée, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de &lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s_de_Cyr%C3%A8ne" title=" Wikipedia"&gt;Lacydès de Cyrène&lt;/a&gt;, il reçoit de lui, avec Téléclès, la direction de l’école du vivant même de leur maître : Lacydès, malade, la leur confie vers 224 av. J.-C. Évandre et Téléclès la dirigent ensemble, cas rare dans l’histoire de l’institution.&lt;/p&gt; &lt;p&gt;Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par &lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" title=" Wikipedia"&gt;Arcésilas&lt;/a&gt;. Celui-ci avait donné à l’école platonicienne une orientation sceptique, en s’appuyant sur le Socrate qui affirmait ne rien savoir. Contre les stoïciens, qui pensaient que certaines représentations sont si évidentes qu’elles garantissent la vérité, les académiciens soutiennent qu’aucune perception ne permet de distinguer avec certitude le vrai du faux : un rêve, une illusion ou un jumeau peuvent produire la même impression qu’une perception exacte. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et ne rien affirmer. Pour agir, il suffit de suivre ce qui paraît raisonnable. Les académiciens enseignaient en argumentant pour et contre chaque thèse, afin de montrer que les deux positions se valent et d’exercer l’esprit critique de leurs élèves. Évandre transmet cet héritage à une génération d’étudiants.&lt;/p&gt; &lt;p&gt;Aucun de ses écrits ne nous est parvenu. Il a pour successeur Hégésinous de Pergame, qui forme à son tour &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant penseur de la Nouvelle Académie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F56" s="7" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="I56" s="9"/>
+        <v>444</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>445</v>
+      </c>
       <c r="J56" s="2" t="s">
         <v>23</v>
       </c>
@@ -5850,7 +5894,7 @@
         <v>342</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5858,36 +5902,32 @@
         </is>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7">
-        <v>160</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vers 160 – vers 210</t>
-        </is>
+    <row r="57" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
+        <v>-230</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>448</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sextus_Empiricus"  title=" Wikipedia"&gt;Sextus EMPIRICUS&lt;/a&gt;  était un philosophe et médecin grec et  une figure importante du scepticisme, souvent appelé "pyrrhonisme" en référence à Pyrrhon d'Élis. Contrairement à d'autres formes de scepticisme, qui peuvent aboutir à une négation de la possibilité de connaître la vérité, le &lt;a href="https://www.youtube.com/watch?v=Xvgfo_ADlPM"  title=" Sextus Empiricus, Esquisses pyrrhoniennes, Ne rien affirmer et l'enseignement inexistant par Koalemos"&gt;pyrrhonisme&lt;/a&gt; propose de suspendre tout jugement sur la nature ultime des choses, car il considère que les arguments pour et contre toute proposition sont également convaincants. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2002_num_100_4_7456_t1_0797_0000_2" title="Sextus Empiricus, Esquisses pyrrhoniennes. Introduction, traduction et commentaires par Pierre Pellegrin par Persée"&gt;"Les Esquisses pyrrhoniennes"&lt;/a&gt;, il présente une introduction systématique au scepticisme pyrrhonien. L'ouvrage est divisé en trois livres : &lt;/p&gt; &lt;p&gt;Livre I : Il expose les principes fondamentaux du scepticisme, y compris la distinction entre le scepticisme pyrrhonien et d'autres formes de scepticisme, comme celui de l'Académie. Il explique également les concepts clés tels que l'épochè (suspension du jugement), les tropes (modes d'argumentation sceptique), et l'ataraxie. &lt;/p&gt; &lt;p&gt;Livre II : Il traite de la critique sceptique des dogmatismes philosophiques, en particulier dans les domaines de la logique, de la physique et de l'éthique. Il montre comment les arguments des dogmatiques peuvent être contredits, ce qui justifie la suspension du jugement. &lt;/p&gt; &lt;p&gt;Livre III : Il approfondit la critique des dogmatismes, en se concentrant sur des questions spécifiques comme la causalité, la divinité, et la nature du bien et du mal. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/spira_0994-3722_2007_num_39_1_1264_t14_0182_0000_2" style="color:#88A1E9" title=" Sur le Contre les professeurs de Sextus Empiricus par Persée"&gt;"Contre les professeurs"&lt;/a&gt;, il s'attaque à diverses disciplines intellectuelles de son époque, notamment la grammaire, la rhétorique, la géométrie, l'arithmétique, l'astronomie et la musique. Il soutient qu'elles ne peuvent pas prétendre à une connaissance certaine ou absolue. Son but est de montrer que les prétentions à la vérité dans ces domaines sont infondées. &lt;/p&gt; &lt;p&gt; Il  est également connu pour avoir systématisé &lt;a href="https://hal.science/hal-03091658v1/document" style="color:#88A1E9" title=" Sextus Empiricus et les tropes par Hall science"&gt;les "tropes"&lt;/a&gt;, des arguments ou modes de raisonnement qui justifient la suspension du jugement. Ce sont des outils dialectiques qui montrent comment les perceptions et les jugements varient selon les circonstances, les individus, les cultures, etc. &lt;/p&gt; &lt;p&gt;Ses écrits ont été redécouverts à la Renaissance et ont joué un rôle clé dans le développement de la pensée sceptique moderne, influençant des philosophes comme Montaigne, Descartes et Hume. &lt;/p&gt; </t>
+        <v>449</v>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame" title="Wikipedia"&gt;Hégésinous de PERGAME&lt;/a&gt; (IIe siècle av. J.-C.) est un philosophe grec, chef de l’Académie, l’école fondée à Athènes par Platon. Originaire de Pergame, en Asie Mineure, il succède à Évandre et Téléclès, qui avaient dirigé ensemble l’école, et il a pour élève et successeur &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant dialecticien de l’Antiquité.&lt;/p&gt; &lt;p&gt;Nous ne connaissons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu : son nom nous est connu par les listes des chefs successifs de l’Académie et par Cicéron, qui indique que Carnéade l’eut pour maître. Il appartient à la période sceptique de l’Académie, inaugurée par Arcésilas. Les académiciens de ce temps refusent d’affirmer quoi que ce soit avec certitude. Contre les stoïciens, qui croient que certaines perceptions portent en elles la marque de leur vérité, ils montrent qu’une perception vraie pourrait toujours être imitée par une perception fausse, comme dans le rêve ou l’illusion. Il faut donc suspendre son jugement. Mais cela n’empêche pas de vivre : pour agir, on peut suivre ce qui paraît raisonnable. L’enseignement de l’Académie se fait par la discussion contradictoire, en argumentant pour et contre chaque thèse. C’est cette méthode que Carnéade portera à son sommet : envoyé à Rome en ambassade en 155 av. J.-C., il fit scandale en défendant un jour la justice, puis en la réfutant le lendemain.&lt;/p&gt; &lt;p&gt;Hégésinous est ainsi un maillon de la transmission entre la Moyenne et la Nouvelle Académie, durant la période de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique" style="color:#6A142A" title="Philosophie hellénistique sur Wikipedia"&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F57" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>468</v>
+        <v>451</v>
+      </c>
+      <c r="G57" s="15" t="s">
+        <v>452</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="2" t="s">
@@ -5900,7 +5940,7 @@
         <v>342</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5908,36 +5948,32 @@
         </is>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7">
-        <v>-240</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-167</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vers 240 A JC - 167 A JC</t>
-        </is>
+    <row r="58" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
+        <v>-213</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>456</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s" title="Wikipedia"&gt;TÉLÉCLÈS&lt;/a&gt; (mort vers 167 av. J.-C.) est un philosophe grec, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de Lacydès de Cyrène, il reçoit de lui, avec son condisciple Évandre, la direction de l’école du vivant même de leur maître, que la maladie empêchait d’enseigner. Les deux philosophes la dirigent ensemble, une organisation collégiale rare dans l’histoire de l’Académie.&lt;/p&gt; &lt;p&gt;Nous ne savons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu. Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par Arcésilas, qui avait donné à l’école de Platon une orientation sceptique en s’inspirant du Socrate qui affirmait ne rien savoir. Les académiciens de cette époque s’opposent avant tout aux stoïciens. Ceux-ci soutiennent qu’il existe des représentations « compréhensives », si claires et si distinctes qu’elles garantissent leur propre vérité et fondent la science. Les académiciens répondent qu’aucune perception ne peut être distinguée avec certitude d’une perception trompeuse : un rêve, une illusion d’optique ou deux jumeaux suffisent à le montrer. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;), mais il peut agir en suivant ce qui lui paraît raisonnable ou vraisemblable. L’enseignement se fait par la discussion : on argumente pour et contre chaque thèse, afin d’exercer l’esprit critique.&lt;/p&gt; &lt;p&gt;Après Téléclès et Évandre, la direction passe à Hégésinous de Pergame, puis à &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" style="color:#6A142A" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, qui donnera à l’Académie un éclat nouveau et portera le scepticisme jusqu’à Rome.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Wikipedia"&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href="https://fr.wikipedia.org/wiki/Dialectique" title="Dialectique par Wikipedia"&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272" title="Opinion et certitude par Persee"&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron" style="color:#6A142A" title="Cicéron sur Wikipedia"&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il. Formé à la dialectique par le stoïcien Diogène de Babylone, il étudie de près l’œuvre de Chrysippe pour mieux la réfuter, au point de dire : « Sans Chrysippe, je ne serais pas. » Il distingue trois degrés de vraisemblance : la représentation simplement probable, celle qui n’est contredite par aucune autre, et celle qui a été examinée sous tous ses aspects. Il critique aussi la divination, le destin et la providence des stoïciens. Son disciple Clitomaque a mis par écrit son enseignement.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F58" s="7" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="2" t="s">
@@ -5949,8 +5985,8 @@
       <c r="L58" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="M58" s="11" t="s">
-        <v>478</v>
+      <c r="M58" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5958,45 +5994,49 @@
         </is>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="n">
-        <v>-185</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>480</v>
+    <row r="59" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7">
+        <v>160</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 160 – vers 210</t>
+        </is>
       </c>
       <c r="D59" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes"  title=" Wikipedia"&gt;PANÉTIUS DE RHODES&lt;/a&gt; (vers 185-109 av. J.-C.) est un philosophe stoïcien grec, qui a adapté le stoïcisme au monde romain. Issu d’une grande famille de Rhodes, il étudie à Athènes auprès de Diogène de Babylone, puis s’installe à Rome, où il devient l’ami et le conseiller de Scipion Émilien, le vainqueur de Carthage. Il prend ensuite la tête de l’école stoïcienne d’Athènes, de 129 à sa mort.&lt;/p&gt; &lt;p&gt;Panétius assouplit la &lt;a href="https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie"  title="Le Stoïcisme par apprendre la philo"&gt;pensée stoïcienne&lt;/a&gt; et la rapproche de Platon et d’Aristote, qu’il admire. Il abandonne plusieurs thèses de ses prédécesseurs : il doute de la divination, nie la conflagration universelle qui devait périodiquement détruire le monde, qu’il juge éternel, et refuse l’immortalité de l’âme. Surtout, il s’intéresse moins au sage idéal, presque introuvable, qu’à l’homme ordinaire qui progresse vers la sagesse. Sa morale part de la nature humaine : chacun porte en lui des tendances fondamentales où s’unissent la nature et la raison, la recherche de la vérité, le goût de l’ordre, le désir de grandeur d’âme et le sens de la communauté. Chacun doit aussi tenir compte de sa propre nature, de ses talents et de sa situation, comme un acteur choisit le rôle qui lui convient. Il en tire une éthique des « devoirs », les actions convenables de la vie quotidienne et de la vie publique, fondée sur la justice, la bienveillance et le sens de la mesure.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Du devoir&lt;/em&gt; est perdu, mais Cicéron l’a largement repris dans son &lt;em&gt;De officiis&lt;/em&gt;, l’un des livres de morale les plus lus en Europe jusqu’au XIXe siècle. Panétius a ainsi donné au stoïcisme le visage humaniste qu’adopteront les élites romaines.&lt;/p&gt;</t>
+        <v>465</v>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sextus_Empiricus"  title=" Wikipedia"&gt;Sextus EMPIRICUS&lt;/a&gt;  était un philosophe et médecin grec et  une figure importante du scepticisme, souvent appelé "pyrrhonisme" en référence à Pyrrhon d'Élis. Contrairement à d'autres formes de scepticisme, qui peuvent aboutir à une négation de la possibilité de connaître la vérité, le &lt;a href="https://www.youtube.com/watch?v=Xvgfo_ADlPM"  title=" Sextus Empiricus, Esquisses pyrrhoniennes, Ne rien affirmer et l'enseignement inexistant par Koalemos"&gt;pyrrhonisme&lt;/a&gt; propose de suspendre tout jugement sur la nature ultime des choses, car il considère que les arguments pour et contre toute proposition sont également convaincants. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2002_num_100_4_7456_t1_0797_0000_2" title="Sextus Empiricus, Esquisses pyrrhoniennes. Introduction, traduction et commentaires par Pierre Pellegrin par Persée"&gt;"Les Esquisses pyrrhoniennes"&lt;/a&gt;, il présente une introduction systématique au scepticisme pyrrhonien. L'ouvrage est divisé en trois livres : &lt;/p&gt; &lt;p&gt;Livre I : Il expose les principes fondamentaux du scepticisme, y compris la distinction entre le scepticisme pyrrhonien et d'autres formes de scepticisme, comme celui de l'Académie. Il explique également les concepts clés tels que l'épochè (suspension du jugement), les tropes (modes d'argumentation sceptique), et l'ataraxie. &lt;/p&gt; &lt;p&gt;Livre II : Il traite de la critique sceptique des dogmatismes philosophiques, en particulier dans les domaines de la logique, de la physique et de l'éthique. Il montre comment les arguments des dogmatiques peuvent être contredits, ce qui justifie la suspension du jugement. &lt;/p&gt; &lt;p&gt;Livre III : Il approfondit la critique des dogmatismes, en se concentrant sur des questions spécifiques comme la causalité, la divinité, et la nature du bien et du mal. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/spira_0994-3722_2007_num_39_1_1264_t14_0182_0000_2" style="color:#88A1E9" title=" Sur le Contre les professeurs de Sextus Empiricus par Persée"&gt;"Contre les professeurs"&lt;/a&gt;, il s'attaque à diverses disciplines intellectuelles de son époque, notamment la grammaire, la rhétorique, la géométrie, l'arithmétique, l'astronomie et la musique. Il soutient qu'elles ne peuvent pas prétendre à une connaissance certaine ou absolue. Son but est de montrer que les prétentions à la vérité dans ces domaines sont infondées. &lt;/p&gt; &lt;p&gt; Il  est également connu pour avoir systématisé &lt;a href="https://hal.science/hal-03091658v1/document" style="color:#88A1E9" title=" Sextus Empiricus et les tropes par Hall science"&gt;les "tropes"&lt;/a&gt;, des arguments ou modes de raisonnement qui justifient la suspension du jugement. Ce sont des outils dialectiques qui montrent comment les perceptions et les jugements varient selon les circonstances, les individus, les cultures, etc. &lt;/p&gt; &lt;p&gt;Ses écrits ont été redécouverts à la Renaissance et ont joué un rôle clé dans le développement de la pensée sceptique moderne, influençant des philosophes comme Montaigne, Descartes et Hume. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F59" s="7" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>252</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -6004,45 +6044,49 @@
         </is>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="n">
-        <v>-135</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>488</v>
+    <row r="60" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7">
+        <v>-240</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-167</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 240 A JC - 167 A JC</t>
+        </is>
       </c>
       <c r="D60" s="8" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Posidonios"  title=" Wikipedia"&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770"  title="Posidonius d'Apamée théoricien de la géométrie par Persée"&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href="https://www.youtube.com/watch?v=EqU-kD8dW4Y" title="Grèce antique - 33 La civilisation hellénistique par Yannick Rub"&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289"  title="La philosophiede Posidonius par Persee"&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s" title="Wikipedia"&gt;TÉLÉCLÈS&lt;/a&gt; (mort vers 167 av. J.-C.) est un philosophe grec, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de Lacydès de Cyrène, il reçoit de lui, avec son condisciple Évandre, la direction de l’école du vivant même de leur maître, que la maladie empêchait d’enseigner. Les deux philosophes la dirigent ensemble, une organisation collégiale rare dans l’histoire de l’Académie.&lt;/p&gt; &lt;p&gt;Nous ne savons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu. Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par Arcésilas, qui avait donné à l’école de Platon une orientation sceptique en s’inspirant du Socrate qui affirmait ne rien savoir. Les académiciens de cette époque s’opposent avant tout aux stoïciens. Ceux-ci soutiennent qu’il existe des représentations « compréhensives », si claires et si distinctes qu’elles garantissent leur propre vérité et fondent la science. Les académiciens répondent qu’aucune perception ne peut être distinguée avec certitude d’une perception trompeuse : un rêve, une illusion d’optique ou deux jumeaux suffisent à le montrer. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;), mais il peut agir en suivant ce qui lui paraît raisonnable ou vraisemblable. L’enseignement se fait par la discussion : on argumente pour et contre chaque thèse, afin d’exercer l’esprit critique.&lt;/p&gt; &lt;p&gt;Après Téléclès et Évandre, la direction passe à Hégésinous de Pergame, puis à &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" style="color:#6A142A" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, qui donnera à l’Académie un éclat nouveau et portera le scepticisme jusqu’à Rome.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F60" s="7" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>494</v>
+        <v>342</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>478</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -6050,49 +6094,45 @@
         </is>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
-        <v>-110</v>
+        <v>-185</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philod%C3%A8me_de_Gadara" title="Wikipedia"&gt;PHILODÈME de Gadara&lt;/a&gt; était un philosophe et poète épicurien, originaire de Gadara en Syrie (l'actuelle Jordanie). Élève de Zénon de Sidon à Athènes, il s'installa en Campanie sous la protection du mécène romain Lucius Calpurnius Pison, proche de César, et anima un cercle intellectuel brillant qui accueillit le jeune Virgile et ses amis poètes.&lt;/p&gt; &lt;p&gt;Il défendit et enrichit la philosophie d'&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure" title="Épicure sur Wikipedia"&gt;Épicure&lt;/a&gt; en l'appliquant à des domaines nouveaux : la rhétorique, la musique, l'esthétique et la critique littéraire. Ses traités, longtemps perdus, ont été miraculeusement retrouvés dans la &lt;em&gt;Villa des Papyrus&lt;/em&gt; d'Herculanum, ensevelie par l'éruption du Vésuve en 79 apr. J.-C. Ces rouleaux carbonisés, partiellement déchiffrés grâce aux techniques modernes, constituent une source irremplaçable sur l'épicurisme tardif.&lt;/p&gt; &lt;p&gt;Philodème concilia la rigueur philosophique épicurienne — recherche de l'&lt;em&gt;ataraxie&lt;/em&gt; et du plaisir vertueux — avec une sensibilité poétique et artistique raffinée. Il représente l'épicurisme dans sa version la plus ouverte au monde des arts et de la culture romaine. Ses traités abordent aussi la morale : la colère, la mort, qu’il ne faut pas craindre, ou la « franchise » avec laquelle le maître corrige ses disciples. Poète, il a laissé une trentaine d’épigrammes, souvent amoureuses, conservées dans l’&lt;em&gt;Anthologie grecque&lt;/em&gt;. Les quelque 1 800 rouleaux de la villa, découverts à partir de 1752, sont aujourd’hui déchiffrés grâce à l’imagerie scientifique et à l’intelligence artificielle, sans qu’on ait besoin de les dérouler.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ca2cJql73D4</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Vie et oeuvre de Philodème" par Michel Onfray</t>
-        </is>
+        <v>481</v>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes"  title=" Wikipedia"&gt;PANÉTIUS DE RHODES&lt;/a&gt; (vers 185-109 av. J.-C.) est un philosophe stoïcien grec, qui a adapté le stoïcisme au monde romain. Issu d’une grande famille de Rhodes, il étudie à Athènes auprès de Diogène de Babylone, puis s’installe à Rome, où il devient l’ami et le conseiller de Scipion Émilien, le vainqueur de Carthage. Il prend ensuite la tête de l’école stoïcienne d’Athènes, de 129 à sa mort.&lt;/p&gt; &lt;p&gt;Panétius assouplit la &lt;a href="https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie"  title="Le Stoïcisme par apprendre la philo"&gt;pensée stoïcienne&lt;/a&gt; et la rapproche de Platon et d’Aristote, qu’il admire. Il abandonne plusieurs thèses de ses prédécesseurs : il doute de la divination, nie la conflagration universelle qui devait périodiquement détruire le monde, qu’il juge éternel, et refuse l’immortalité de l’âme. Surtout, il s’intéresse moins au sage idéal, presque introuvable, qu’à l’homme ordinaire qui progresse vers la sagesse. Sa morale part de la nature humaine : chacun porte en lui des tendances fondamentales où s’unissent la nature et la raison, la recherche de la vérité, le goût de l’ordre, le désir de grandeur d’âme et le sens de la communauté. Chacun doit aussi tenir compte de sa propre nature, de ses talents et de sa situation, comme un acteur choisit le rôle qui lui convient. Il en tire une éthique des « devoirs », les actions convenables de la vie quotidienne et de la vie publique, fondée sur la justice, la bienveillance et le sens de la mesure.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Du devoir&lt;/em&gt; est perdu, mais Cicéron l’a largement repris dans son &lt;em&gt;De officiis&lt;/em&gt;, l’un des livres de morale les plus lus en Europe jusqu’au XIXe siècle. Panétius a ainsi donné au stoïcisme le visage humaniste qu’adopteront les élites romaines.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>484</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>502</v>
+        <v>24</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>503</v>
+        <v>386</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -6102,18 +6142,114 @@
     </row>
     <row r="62" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
+        <v>-135</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Posidonios"  title=" Wikipedia"&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770"  title="Posidonius d'Apamée théoricien de la géométrie par Persée"&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href="https://www.youtube.com/watch?v=EqU-kD8dW4Y" title="Grèce antique - 33 La civilisation hellénistique par Yannick Rub"&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289"  title="La philosophiede Posidonius par Persee"&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt;  </t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="I62" s="9"/>
+      <c r="J62" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="n">
+        <v>-110</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philod%C3%A8me_de_Gadara" title="Wikipedia"&gt;PHILODÈME de Gadara&lt;/a&gt; était un philosophe et poète épicurien, originaire de Gadara en Syrie (l'actuelle Jordanie). Élève de Zénon de Sidon à Athènes, il s'installa en Campanie sous la protection du mécène romain Lucius Calpurnius Pison, proche de César, et anima un cercle intellectuel brillant qui accueillit le jeune Virgile et ses amis poètes.&lt;/p&gt; &lt;p&gt;Il défendit et enrichit la philosophie d'&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure" title="Épicure sur Wikipedia"&gt;Épicure&lt;/a&gt; en l'appliquant à des domaines nouveaux : la rhétorique, la musique, l'esthétique et la critique littéraire. Ses traités, longtemps perdus, ont été miraculeusement retrouvés dans la &lt;em&gt;Villa des Papyrus&lt;/em&gt; d'Herculanum, ensevelie par l'éruption du Vésuve en 79 apr. J.-C. Ces rouleaux carbonisés, partiellement déchiffrés grâce aux techniques modernes, constituent une source irremplaçable sur l'épicurisme tardif.&lt;/p&gt; &lt;p&gt;Philodème concilia la rigueur philosophique épicurienne — recherche de l'&lt;em&gt;ataraxie&lt;/em&gt; et du plaisir vertueux — avec une sensibilité poétique et artistique raffinée. Il représente l'épicurisme dans sa version la plus ouverte au monde des arts et de la culture romaine. Ses traités abordent aussi la morale : la colère, la mort, qu’il ne faut pas craindre, ou la « franchise » avec laquelle le maître corrige ses disciples. Poète, il a laissé une trentaine d’épigrammes, souvent amoureuses, conservées dans l’&lt;em&gt;Anthologie grecque&lt;/em&gt;. Les quelque 1 800 rouleaux de la villa, découverts à partir de 1752, sont aujourd’hui déchiffrés grâce à l’imagerie scientifique et à l’intelligence artificielle, sans qu’on ait besoin de les dérouler.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ca2cJql73D4</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Vie et oeuvre de Philodème" par Michel Onfray</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="I63" s="9"/>
+      <c r="J63" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="n">
         <v>-106</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B64" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C64" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D64" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron"  style="color:#6A142A"  title=" Wikipedia"&gt; Marcus CICERON&lt;/a&gt; était un philosophe &lt;a href="https://fr.wiktionary.org/wiki/%C3%A9clectique"  style="color:#88A1E9"  title="L'éclectisme par Wiktionnaire"&gt;Électique&lt;/a&gt; Romain et le premier a rédiger en latin des ouvrages à une époque où le grec domine dans le monde intellectuel. Il est l'héritier d'une triple tradition : sceptique, stoïcienne et platonicienne. &lt;/p&gt; &lt;p&gt; 
 On connait sa théorie de la "nature humaine" qui selon lui est orientée vers la recherche du bien car les êtres humains sont naturellement doués d'une raison qui leur permet de discerner le bien du mal. Il a écrit de nombreux traités philosophiques, dont &lt;a href="https://fr.wikipedia.org/wiki/De_finibus_bonorum_et_malorum"  title="bien et maux par wikipedia"&gt;De Finibus Bonorum et Malorum&lt;/a&gt; (Sur les fins ultimes du bien et du mal) ainsi que "De Oratore", qui décrit l'art de la persuasion et la façon dont il peut être utilisé pour influencer les autres. &lt;/p&gt; &lt;p&gt;  
@@ -6122,97 +6258,97 @@
 </t>
         </is>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F64" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G64" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="H62" s="9" t="s">
+      <c r="H64" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="I62" s="9"/>
-      <c r="J62" s="2" t="s">
+      <c r="I64" s="9"/>
+      <c r="J64" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="K64" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="L62" s="2" t="s">
+      <c r="L64" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="M64" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P62">
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P64">
         <v>2</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n">
+    <row r="65" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="n">
         <v>-94</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B65" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C65" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D65" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lucr%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;LUCRÈCE&lt;/a&gt; (vers 98-55 av. J.-C.) est un poète et philosophe romain, disciple d’Épicure, auteur d’un seul livre, l’un des chefs-d’œuvre de la littérature latine : &lt;em&gt;De la nature des choses&lt;/em&gt; (&lt;em&gt;De rerum natura&lt;/em&gt;). Nous ne savons presque rien de sa vie. La légende, rapportée par saint Jérôme, selon laquelle il serait devenu fou après avoir bu un philtre d’amour et se serait suicidé, a sans doute été inventée par ses adversaires.&lt;/p&gt; &lt;p&gt;Son poème, en six livres et près de 7 400 vers, expose la doctrine de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picurisme"  style="color:#88A1E9"  title="Epicurisme par Wikipedia"&gt;épicurisme&lt;/a&gt; pour délivrer les hommes de la peur. Rien ne naît de rien, rien ne retourne au néant : tout ce qui existe est fait d’atomes, invisibles et éternels, qui se meuvent dans le vide. En tombant, ils s’écartent parfois légèrement de leur trajectoire : ce &lt;a href="https://www.youtube.com/watch?v=7iQzfXtB4wc&amp;ab_channel=Coursitout"  style="color:#88A1E9"  title="Le clinamen par Coursitout"&gt;&lt;em&gt;clinamen&lt;/em&gt;&lt;/a&gt; explique la rencontre des atomes, la formation des mondes et la liberté humaine. L’âme elle-même est faite d’atomes très fins &lt;a href="https://www.youtube.com/watch?v=VKJsOwjD5P4&amp;ab_channel=librairiemollat"  style="color:#88A1E9"  title="Bernard Combeaud - Lucrèce, la naissance des choses"&gt;et se disperse&lt;/a&gt; à la mort. Il n’y a donc rien à craindre après la mort : « la mort n’est rien pour nous ». Les dieux existent, mais ne s’occupent pas des hommes. Lucrèce dénonce avec force la superstition, qui pousse au crime, comme le sacrifice d’Iphigénie par son propre père : « Tant la religion a pu inspirer de maux ! » Il décrit aussi la naissance de la vie et des sociétés humaines, du langage et des arts, et finit son poème par la terrible peste d’Athènes. Le bonheur est la paix de l’âme, que procurent des plaisirs simples et l’amitié.&lt;/p&gt; &lt;p&gt;Retrouvé en 1417 par l’humaniste Pogge, le poème a marqué Montaigne, Gassendi, les libertins et les Lumières.&lt;/p&gt;  &lt;audio controls title="Comment maîtriser ses passions ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-12.09.2016-ITEMA_21073425-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F65" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="G65" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="H63" s="9" t="s">
+      <c r="H65" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="I63" s="9"/>
-      <c r="J63" s="2" t="s">
+      <c r="I65" s="9"/>
+      <c r="J65" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="K63" s="2" t="s">
+      <c r="K65" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L63" s="2" t="s">
+      <c r="L65" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="M63" s="2" t="s">
+      <c r="M65" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="n">
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="n">
         <v>-80</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B66" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C66" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D66" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89n%C3%A9sid%C3%A8me"  style="color:#6A142A"  title=" Wikipedia"&gt;ÉNÉSIDÈME&lt;/a&gt; était un philosophe grec de la tradition sceptique.  Il vécu à une époque où le &lt;a href="https://www.youtube.com/watch?v=_En3Pz6sWL8" style="color:#88A1E9" title="Scepticisme et interpedendance par PHILOSOPHIA"&gt;scepticisme&lt;/a&gt; philosophique était en plein essor, en réaction aux dogmatismes des écoles philosophiques comme le stoïcisme et l'épicurisme.  &lt;/p&gt; &lt;p&gt; Il a systématisé les  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1918_num_20_2_2006" style="color:#88A1E9" title="Pour l'histoire du scepticisme antique : les tropes d'Énésidème contre la logique inductive par Persée"&gt;arguments sceptiques&lt;/a&gt; dans ce qu'on appelle les &lt;a href="https://guykarl.canalblog.com/archives/2012/08/31/25001663.html" style="color:#88A1E9" title="PYRRHONISME : les dix tropes d' ENESIDEME par Le jardin Philosophe"&gt;"Dix Modes"&lt;/a&gt;, qui visent à montrer que nos perceptions et nos jugements sont influencés par divers facteurs, rendant impossible l'accès à une connaissance certaine : &lt;/p&gt;
 &lt;p&gt;La diversité des animaux : Les espèces perçoivent le monde de manière différente, ce qui suggère que nos perceptions ne reflètent pas nécessairement la réalité objective. &lt;/p&gt;
@@ -6222,268 +6358,175 @@
 &lt;p&gt;Les quantités et constitutions : La quantité et la composition d'un objet peuvent affecter la manière dont nous le percevons. &lt;/p&gt; &lt;p&gt;La relation : Tout est perçu en relation avec autre chose, ce qui rend difficile de connaître la nature intrinsèque d'un objet.&lt;/p&gt; &lt;p&gt;La fréquence ou la rareté : La fréquence avec laquelle nous rencontrons quelque chose peut influencer notre perception de sa valeur ou de sa nature. &lt;/p&gt; &lt;p&gt;Les coutumes et les croyances : Les habitudes culturelles et les croyances peuvent profondément influencer nos perceptions et nos jugements. &lt;/p&gt; &lt;p&gt; Ses arguments mettent en lumière les limites de notre capacité à connaître le monde de manière certaine et nous invitent à adopter une attitude plus humble et critique face à nos propres perceptions et jugements. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F66" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="G66" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="H64" s="9" t="s">
+      <c r="H66" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="I64" s="9"/>
-      <c r="J64" s="2" t="s">
+      <c r="I66" s="9"/>
+      <c r="J66" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K64" s="2" t="s">
+      <c r="K66" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="L64" s="2" t="s">
+      <c r="L66" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="M64" s="2" t="s">
+      <c r="M66" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="n">
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7" t="n">
         <v>-20</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B67" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C67" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D67" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philon_d%27Alexandrie"  style="color:#6A142A"  title=" Wikipedia"&gt;PHILON d'Alexandrie&lt;/a&gt;  était un philosophe juif hellénisé qui d'harmonisa la philosophie grecque, en particulier le platonisme et le stoïcisme, avec les enseignements de la Bible hébraïque. &lt;/p&gt; &lt;p&gt; Il a écrit de nombreux traités et des commentaires allégoriques sur les livres de la Torah et a interprété les textes bibliques à travers le prisme de la philosophie grecque, cherchant à dégager des significations philosophiques et morales profondes. Dans son œuvre &lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1962_num_161_1_7742" style="color:#88A1E9" title="Philon d'Alexandrie, De opificio mundi par Persée"&gt;"De Opificio Mundi"&lt;/a&gt;, il explore la Genèse en utilisant des concepts platoniciens. &lt;/p&gt; &lt;p&gt; Il tente de montrer que les enseignements de la Torah sont en harmonie avec les idées des grands philosophes grecs. Certaines de ses œuvres défendent la religion juive contre les critiques des païens et des autres philosophes. Par exemple, dans  &lt;a href="https://www.persee.fr/doc/rjuiv_0484-8616_1968_num_127_1_1588 " style="color:#88A1E9" title="        Schadenfreude chez Philon d'Alexandrie ? Note sur In Flaccum  par Persée"&gt;"Contre Flaccus"&lt;/a&gt; et "L'Ambassade à Gaius", il décrit les persécutions subies par les Juifs d'Alexandrie et plaide pour leurs droits. &lt;/p&gt; &lt;p&gt; Il est souvent considéré comme un précurseur de la philosophie religieuse et de la théologie mystique. &lt;/p&gt; &lt;p&gt;Dieu et le Logos : Il décrit Dieu comme transcendant et inconnaissable, mais il introduit également le concept du Logos comme un intermédiaire entre Dieu et le monde. Le Logos est à la fois la raison divine qui ordonne l'univers et le moyen par lequel Dieu interagit avec le monde. &lt;/p&gt;
 &lt;p&gt;Allégorie : Il utilise largement l'interprétation allégorique pour expliquer les textes bibliques. Il croit que les récits bibliques ont un sens littéral, mais aussi un sens spirituel plus profond qui peut être découvert par l'interprétation philosophique. &lt;/p&gt; &lt;p&gt;Éthique et Vertu : Il insiste sur l'importance de la vertu et de la vie morale. Il croit que l'étude de la philosophie et la pratique des vertus permettent à l'âme de se rapprocher de Dieu. &lt;/p&gt; &lt;p&gt; Bien qu'il soit resté fidèle au judaïsme, sa pensée a eu une influence significative sur les premiers penseurs chrétiens, tels que Clément d'Alexandrie et Origène. Son concept du Logos a notamment influencé la christologie chrétienne. &lt;/p&gt; &lt;p&gt; </t>
         </is>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F67" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="G65" s="9" t="s">
+      <c r="G67" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="H65" s="9" t="s">
+      <c r="H67" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="I65" s="9"/>
-      <c r="J65" s="2" t="s">
+      <c r="I67" s="9"/>
+      <c r="J67" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="K65" s="2" t="s">
+      <c r="K67" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L65" s="2" t="s">
+      <c r="L67" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="M65" s="2" t="s">
+      <c r="M67" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="N65" s="0" t="s">
+      <c r="N67" s="0" t="s">
         <v>540</v>
       </c>
-      <c r="O65" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="n">
+      <c r="O67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7" t="n">
         <v>-4</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B68" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C68" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D68" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que" title=" Wikipedia"&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href="https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Stoïcisme par le Précepteur"&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=J3wZoqElCgs" title="Who is Seneca par Daily Stoic "&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href="https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin" title="La vie Heureuse par Karl Baudoin"&gt; "une vie heureuse".&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : De la brièveté de la vie (consideration sur l’usage du temps). De la colère (sur la maîtrise de cette passion destructive). De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt; Sénèque est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href="https://www.youtube.com/watch?v=d_cge9OwVAs" title="La vie philosophique de Sénèque par Kosmos"&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title="Les lettres à Lucilius – Senèque  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F68" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="G66" s="9" t="inlineStr">
+      <c r="G68" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">"Sénèque – Pourquoi vous gaspillez votre vie par Voyages Endormis</t>
         </is>
       </c>
-      <c r="H66" s="9" t="s">
+      <c r="H68" s="9" t="s">
         <v>547</v>
-      </c>
-      <c r="I66" s="9"/>
-      <c r="J66" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P66">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes" style="color:#6A142A" title="Wikipedia"&gt;AMMONIOS d’Athènes&lt;/a&gt; est un philosophe platonicien du Ier siècle, originaire d’Égypte, qui enseigna à Athènes et fut le maître de &lt;a href="https://fr.wikipedia.org/wiki/Plutarque" style="color:#6A142A" title="Plutarque sur Wikipedia"&gt;Plutarque&lt;/a&gt;. Celui-ci suivit ses leçons vers 66-67, à l’époque où l’empereur Néron visitait la Grèce. Ammonios était aussi un citoyen influent d’Athènes, où des inscriptions montrent qu’il exerça plusieurs fois la haute fonction de stratège.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit, et nous le connaissons presque uniquement par Plutarque, qui le met en scène dans plusieurs de ses dialogues comme un maître sage et bienveillant. Dans le traité &lt;em&gt;Sur l’E de Delphes&lt;/em&gt;, Plutarque et ses amis s’interrogent sur la lettre E gravée à l’entrée du temple d’Apollon. Ammonios conclut la discussion en y voyant le mot grec &lt;em&gt;ei&lt;/em&gt;, « tu es » : c’est la salutation que l’homme adresse au dieu. Seul le dieu « est » véritablement, éternel, un et immuable, alors que nous, soumis au temps et au changement, ne faisons que devenir et disparaître. Le précepte « Connais-toi toi-même », inscrit au même endroit, répond à ce salut en rappelant à l’homme sa faiblesse. Cette opposition entre l’être divin et le devenir humain est au cœur du platonisme de l’époque. Ammonios s’intéressait aussi aux mathématiques et à la science de la nature, et il voulait unir la philosophie à une piété religieuse fidèle aux traditions grecques.&lt;/p&gt; &lt;p&gt;Il appartient au « moyen platonisme », qui prépare, entre Platon et Plotin, le &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt;. Il ne faut pas le confondre avec Ammonios Saccas, maître de Plotin, ni avec Ammonios d’Alexandrie.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="I67" s="9"/>
-      <c r="J67" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apollonios_de_Tyane"  style="color:#6A142A"  title=" Wikipedia"&gt; Apollonios de Tyane&lt;/a&gt;, né à Tyane en Cappadoce (Turquie),   est une figure emblématique de l’Antiquité, à la croisée de la philosophie, de la spiritualité et du mysticisme, souvent décrit comme un philosophe, thaumaturge et ascète.  Il est principalement associé au &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_pythagoricienne" title="Phytagorisme par wikipedia "&gt; pythagorisme&lt;/a&gt;, un courant philosophique inspiré des enseignements de Pythagore, pratique et ascétique, visant à transformer la vie par des principes éthiques rigoureux et une quête de sagesse. Il prônait une vie fondée sur la pureté, la discipline et l’harmonie universelle,  adoptant un mode de vie ascétique caractérisé par le végétarisme, l’abstinence de vin et un dévouement à la recherche de la sagesse. &lt;/p&gt; &lt;p&gt;   Comme de nombreux philosophes de son temps, il a entrepris de longs voyages pour acquérir des connaissances. Il se rendit notamment en Égypte, en Inde, en Mésopotamie et en Grèce. En Inde, il aurait rencontré des sages et des brahmanes qui auraient influencé sa pensée, assimilant et intégrant à sa pensée des éléments de traditions diverses.  &lt;/p&gt; &lt;p&gt; Au cours des siècles, il a souvent été comparé à Jésus-Christ, en raison des similitudes perçues entre leurs vies (miracles, ascétisme, message spirituel). Certains penseurs païens de l'Antiquité ont même présenté &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1999_num_1_3_1959" style="color:#88A1E9" title="Mythe avorté d'une sagesse totale par Persée "&gt; Apollonios&lt;/a&gt; comme une alternative païenne à Jésus, bien que les deux figures soient très différentes dans leur contexte et leur message. &lt;/p&gt; &lt;p&gt;Il incarte une forme de tolérance religieuse cosidérant que l'on peut reconnaitre sa religion dans la religion de l'autre.&lt;/p&gt; &lt;p&gt;  Sa vie, relatée par &lt;a href="https://fr.wikipedia.org/wiki/Philostrate_d%27Ath%C3%A8nes" style="color:#88A1E9" title="Philostrate par Wikipedia "&gt; Philostrate&lt;/a&gt; dans  &lt;a href="https://fr.wikipedia.org/wiki/Vie_d%27Apollonios_de_Tyane" style="color:#88A1E9" title="Vie d'Apollonios de Tyare par Wikipedia "&gt; Vie d’Apollonios de Tyane&lt;/a&gt;, mêle éléments historiques et légendaires. Profondément spirituel, il prônait une piété réfléchie et critiquait les pratiques religieuses vides de sens, notamment les sacrifices sanglants, préférant une relation intérieure avec le divin et des rituels plus éthiques. Convaincu de l’immortalité de l’âme et de la réincarnation, il voyait la philosophie comme une voie vers la purification spirituelle et morale. &lt;/p&gt; &lt;p&gt;Son engagement ne se limitait pas à la sphère personnelle : il joua un rôle actif dans la société en critiquant les tyrans, en défendant la justice et en conseillant les gouvernants. Considéré par ses contemporains comme un thaumaturge, il aurait accompli des miracles tels que des guérisons, des prédictions et des résurrections, bien que ces récits soient teintés de légende. Sa pensée et sa vie incarnaient une quête universelle de vérité et d'harmonie, cherchant à unifier les enseignements philosophiques et spirituels dans une vision globale.&lt;/p&gt; &lt;p&gt; Apollonios demeure une figure complexe, à mi-chemin entre le philosophe et le sage mystique, dont l'héritage, bien que controversé, continue d'inspirer les amateurs de sagesse antique. &lt;/p&gt;   
-</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>563</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>564</v>
+        <v>200</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>565</v>
+        <v>386</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
+      </c>
+      <c r="P68">
+        <v>3</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Plutarque"  style="color:#6A142A"  title=" Wikipedia"&gt;PLUTARQUE&lt;/a&gt; était un philosophe, biographe et moraliste grec  célèbre pour ses &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1979_num_1_3_3621"  style="color:#88A1E9" title="La pensée de Plutarque dans les Vies  par Olivier Roland"&gt;œuvres&lt;/a&gt;  biographiques et philosophiques. Il  a vécu à une époque où la Grèce était sous domination romaine, mais la culture grecque restait très influente dans l'Empire. &lt;/p&gt;Philosophe éclectique profondément influencé par le platonisme, il croyait en l'importance de la vertu, de la modération et de la recherche de la sagesse. Il insiste sur la nécessité de vivre une vie vertueuse et équilibrée et aborde des thèmes comme la colère, la jalousie, et la manière de cultiver la paix intérieure. Il s'intéresse aux croyances religieuses et aux mythes, cherchant souvent à en donner une interprétation morale ou philosophique.&lt;p&gt; Il  est surtout connu pour deux collections d'œuvres : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=cOdbv-wbRWQ&amp;t=10s"  style="color:#88A1E9" title="Les Vies Parallèles des Hommes Illustres de Plutarque par Olivier Roland"&gt;Vies parallèles&lt;/a&gt; : Cette série de biographies compare des figures célèbres de l'histoire grecque et romaine. Chaque paire de vies met en parallèle un Grec et un Romain, suivie d'une comparaison qui souligne les similitudes et les différences entre les deux personnages. Parmi les paires les plus connues, on trouve Alexandre le Grand et Jules César, Thésée et Romulus, ou encore Démosthène et Cicéron. Son objectif  n'était pas seulement historique, mais aussi moral et éducatif. &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C5%92uvres_morales"  style="color:#88A1E9" title="Œuvres morales par Wikipedia"&gt;Moralia&lt;/a&gt;  : Cette collection regroupe des essais et des traités sur des sujets variés, allant de la philosophie morale à la religion, en passant par la politique, l'éducation et les sciences naturelles, la tranquillité de l'âme, l'amour, la superstition. &lt;/p&gt; &lt;p&gt; Il est connu pour son &lt;a href="https://www.youtube.com/watch?v=n7uLx5rVmm0"  style="color:#88A1E9" title="La Sérénité intérieure | PLUTARQUE  par Les Choses au Claire"&gt;style clair&lt;/a&gt; et accessible, qui combine profondeur philosophique et récit vivant. Ses biographies sont à la fois instructives et divertissantes, mêlant anecdotes, réflexions morales et détails historiques. Il  reste une figure majeure de la littérature et de la philosophie antique. Ses œuvres, à la fois biographiques et philosophiques, continuent d'être étudiées et appréciées pour leur richesse, leur sagesse et leur pertinence intemporelle. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title="  Actualité de Plutarque par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16278-17.12.2016-ITEMA_21168598-2016C6278E0292-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        <v>551</v>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes" style="color:#6A142A" title="Wikipedia"&gt;AMMONIOS d’Athènes&lt;/a&gt; est un philosophe platonicien du Ier siècle, originaire d’Égypte, qui enseigna à Athènes et fut le maître de &lt;a href="https://fr.wikipedia.org/wiki/Plutarque" style="color:#6A142A" title="Plutarque sur Wikipedia"&gt;Plutarque&lt;/a&gt;. Celui-ci suivit ses leçons vers 66-67, à l’époque où l’empereur Néron visitait la Grèce. Ammonios était aussi un citoyen influent d’Athènes, où des inscriptions montrent qu’il exerça plusieurs fois la haute fonction de stratège.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit, et nous le connaissons presque uniquement par Plutarque, qui le met en scène dans plusieurs de ses dialogues comme un maître sage et bienveillant. Dans le traité &lt;em&gt;Sur l’E de Delphes&lt;/em&gt;, Plutarque et ses amis s’interrogent sur la lettre E gravée à l’entrée du temple d’Apollon. Ammonios conclut la discussion en y voyant le mot grec &lt;em&gt;ei&lt;/em&gt;, « tu es » : c’est la salutation que l’homme adresse au dieu. Seul le dieu « est » véritablement, éternel, un et immuable, alors que nous, soumis au temps et au changement, ne faisons que devenir et disparaître. Le précepte « Connais-toi toi-même », inscrit au même endroit, répond à ce salut en rappelant à l’homme sa faiblesse. Cette opposition entre l’être divin et le devenir humain est au cœur du platonisme de l’époque. Ammonios s’intéressait aussi aux mathématiques et à la science de la nature, et il voulait unir la philosophie à une piété religieuse fidèle aux traditions grecques.&lt;/p&gt; &lt;p&gt;Il appartient au « moyen platonisme », qui prépare, entre Platon et Plotin, le &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt;. Il ne faut pas le confondre avec Ammonios Saccas, maître de Plotin, ni avec Ammonios d’Alexandrie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F69" s="7" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>368</v>
+        <v>59</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>236</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6491,94 +6534,92 @@
         </is>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89pict%C3%A8te"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICTETE&lt;/a&gt; (vers 50-vers 125) est un philosophe &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcien&lt;/a&gt; grec, né esclave à Hiérapolis, en Phrygie. À Rome, il appartient à Épaphrodite, affranchi de Néron, qui lui permet de suivre les leçons du stoïcien Musonius Rufus. Affranchi, il enseigne à son tour, jusqu’à ce que l’empereur Domitien chasse les philosophes de Rome vers 93 ; il ouvre alors une école à Nicopolis, en Épire, où il enseigne jusqu’à sa mort.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit. Son disciple &lt;a href="https://fr.wikipedia.org/wiki/Arrien" title=" Wikipedia"&gt;Arrien&lt;/a&gt; a noté ses leçons dans &lt;a href="https://www.youtube.com/watch?v=2tUxNx_oMn4&amp;ab_channel=KarlBaudoin"  style="color:#88A1E9"  title="Les Entretiens d'Epictète par Karl Baudouin"&gt;les &lt;em&gt;Entretiens&lt;/em&gt;&lt;/a&gt; et en a tiré un bref résumé, &lt;a href="https://www.youtube.com/watch?v=qN4m4bbZIGU&amp;t=51s&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Le manuel d'Epictète par Le Précepteur"&gt;le &lt;em&gt;Manuel&lt;/em&gt;&lt;/a&gt;. Tout part d’une distinction : il y a &lt;a href="https://www.youtube.com/watch?v=7Zc85Kc4Xqw&amp;ab_channel=KarlBaudoin"  title="Le manuel d'Epictète par Karl Baudouin"&gt;ce qui dépend de nous&lt;/a&gt;, nos jugements, nos désirs, nos refus, et ce qui ne dépend pas de nous, le corps, les biens, la réputation, les charges, les événements. Le malheur vient de ce que nous voulons maîtriser ce qui nous échappe. « Ce qui trouble les hommes, ce ne sont pas les choses, mais les jugements qu’ils portent sur les choses » : la mort n’est pas terrible, c’est l’opinion que nous en avons qui l’est. La liberté est donc intérieure, et l’esclave peut être plus libre que son maître. Le sage s’exerce chaque jour à bien juger, à désirer seulement ce qui dépend de lui, et à jouer son rôle dans le monde comme un acteur joue celui que l’auteur lui a donné. On résume sa morale par la formule « supporte et abstiens-toi ».&lt;/p&gt; &lt;p&gt;Lu par &lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le" title=" Wikipedia"&gt;Marc Aurèle&lt;/a&gt;, puis par Pascal et Montaigne, il inspire encore les thérapies cognitives d’aujourd’hui, qui apprennent à modifier nos jugements pour apaiser nos émotions.&lt;/p&gt;  &lt;audio controls title="Epictète ou savoir choisir par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-07.01.2026-ITEMA_24365714-2026C48904S0007-NET_MFC_C2619D7A-778C-4505-B127-925270631DD9-21-6f25ae2ae83c473a68406d0d4d07fa43.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apollonios_de_Tyane"  style="color:#6A142A"  title=" Wikipedia"&gt; Apollonios de Tyane&lt;/a&gt;, né à Tyane en Cappadoce (Turquie),   est une figure emblématique de l’Antiquité, à la croisée de la philosophie, de la spiritualité et du mysticisme, souvent décrit comme un philosophe, thaumaturge et ascète.  Il est principalement associé au &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_pythagoricienne" title="Phytagorisme par wikipedia "&gt; pythagorisme&lt;/a&gt;, un courant philosophique inspiré des enseignements de Pythagore, pratique et ascétique, visant à transformer la vie par des principes éthiques rigoureux et une quête de sagesse. Il prônait une vie fondée sur la pureté, la discipline et l’harmonie universelle,  adoptant un mode de vie ascétique caractérisé par le végétarisme, l’abstinence de vin et un dévouement à la recherche de la sagesse. &lt;/p&gt; &lt;p&gt;   Comme de nombreux philosophes de son temps, il a entrepris de longs voyages pour acquérir des connaissances. Il se rendit notamment en Égypte, en Inde, en Mésopotamie et en Grèce. En Inde, il aurait rencontré des sages et des brahmanes qui auraient influencé sa pensée, assimilant et intégrant à sa pensée des éléments de traditions diverses.  &lt;/p&gt; &lt;p&gt; Au cours des siècles, il a souvent été comparé à Jésus-Christ, en raison des similitudes perçues entre leurs vies (miracles, ascétisme, message spirituel). Certains penseurs païens de l'Antiquité ont même présenté &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1999_num_1_3_1959" style="color:#88A1E9" title="Mythe avorté d'une sagesse totale par Persée "&gt; Apollonios&lt;/a&gt; comme une alternative païenne à Jésus, bien que les deux figures soient très différentes dans leur contexte et leur message. &lt;/p&gt; &lt;p&gt;Il incarte une forme de tolérance religieuse cosidérant que l'on peut reconnaitre sa religion dans la religion de l'autre.&lt;/p&gt; &lt;p&gt;  Sa vie, relatée par &lt;a href="https://fr.wikipedia.org/wiki/Philostrate_d%27Ath%C3%A8nes" style="color:#88A1E9" title="Philostrate par Wikipedia "&gt; Philostrate&lt;/a&gt; dans  &lt;a href="https://fr.wikipedia.org/wiki/Vie_d%27Apollonios_de_Tyane" style="color:#88A1E9" title="Vie d'Apollonios de Tyare par Wikipedia "&gt; Vie d’Apollonios de Tyane&lt;/a&gt;, mêle éléments historiques et légendaires. Profondément spirituel, il prônait une piété réfléchie et critiquait les pratiques religieuses vides de sens, notamment les sacrifices sanglants, préférant une relation intérieure avec le divin et des rituels plus éthiques. Convaincu de l’immortalité de l’âme et de la réincarnation, il voyait la philosophie comme une voie vers la purification spirituelle et morale. &lt;/p&gt; &lt;p&gt;Son engagement ne se limitait pas à la sphère personnelle : il joua un rôle actif dans la société en critiquant les tyrans, en défendant la justice et en conseillant les gouvernants. Considéré par ses contemporains comme un thaumaturge, il aurait accompli des miracles tels que des guérisons, des prédictions et des résurrections, bien que ces récits soient teintés de légende. Sa pensée et sa vie incarnaient une quête universelle de vérité et d'harmonie, cherchant à unifier les enseignements philosophiques et spirituels dans une vision globale.&lt;/p&gt; &lt;p&gt; Apollonios demeure une figure complexe, à mi-chemin entre le philosophe et le sage mystique, dont l'héritage, bien que controversé, continue d'inspirer les amateurs de sagesse antique. &lt;/p&gt;   
+</t>
         </is>
       </c>
       <c r="F70" s="7" t="s">
-        <v>65</v>
+        <v>561</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>200</v>
+        <v>564</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>386</v>
+        <v>565</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P70">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="71" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicomaque_de_G%C3%A9rase"  style="color:#6A142A"  title=" Wikipedia"&gt;NICOMAQUE de Gérase&lt;/a&gt; était un mathématicien et philosophe néo-pythagoricien grec mettant l'accent sur l'importance des nombres et de leurs propriétés dans la compréhension de l'univers. Pour lui, ils n'étaient pas de simples outils de calcul, mais des  &lt;a href="https://www.youtube.com/watch?v=Jbuap2Pahbg" style="color:#88A1E9" title=" Pourquoi rééditer l'Introduction arithmétique de Nicomaque de Gerasa en France ?  par LabEx HaStec"&gt;principes fondamentaux &lt;/a&gt; qui sous-tendent la réalité. Il cherchait à réduire les Formes platoniciennes et les catégories aristotéliciennes aux propriétés formelles des nombres. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus célèbre et le plus influent "Introduction à l'arithmétique" est un manuel fondamental qui a servi de base à l'arithmétique pendant une grande partie du Moyen Âge, notamment grâce à sa traduction et adaptation par Boèce (vers 505) dans son "De institutione arithmetica". Ce traité aborde des concepts comme les nombres figurés, les nombres parfaits, abondants et déficients, et la théorie des nombres en général. &lt;/p&gt; &lt;p&gt;  Dans son deuxième ovrage " Théologie de l'arithmétique", il  explore les significations mystiques et philosophiques des nombres, rattachant les propriétés numériques à des concepts divins et cosmologiques.   Il était également théoricien de la musique et musicologue où dans  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1956_num_69_324_3426" style="color:#88A1E9" title=" L'hexatonique grec d'après Nicomaque  par Persée"&gt; 'L'hexatonique"&lt;/a&gt;, il témoigne de son intérêt pour les relations mathématiques sous-jacentes à l'harmonie musicale. &lt;/p&gt; &lt;p&gt; Il  est une figure essentielle pour comprendre la philosophie et les mathématiques de l'Antiquité tardive, en particulier le courant néo-pythagoricien qui cherchait à concilier les doctrines platoniciennes et aristotéliciennes avec la mystique des nombres. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Plutarque"  style="color:#6A142A"  title=" Wikipedia"&gt;PLUTARQUE&lt;/a&gt; était un philosophe, biographe et moraliste grec  célèbre pour ses &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1979_num_1_3_3621"  style="color:#88A1E9" title="La pensée de Plutarque dans les Vies  par Olivier Roland"&gt;œuvres&lt;/a&gt;  biographiques et philosophiques. Il  a vécu à une époque où la Grèce était sous domination romaine, mais la culture grecque restait très influente dans l'Empire. &lt;/p&gt;Philosophe éclectique profondément influencé par le platonisme, il croyait en l'importance de la vertu, de la modération et de la recherche de la sagesse. Il insiste sur la nécessité de vivre une vie vertueuse et équilibrée et aborde des thèmes comme la colère, la jalousie, et la manière de cultiver la paix intérieure. Il s'intéresse aux croyances religieuses et aux mythes, cherchant souvent à en donner une interprétation morale ou philosophique.&lt;p&gt; Il  est surtout connu pour deux collections d'œuvres : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=cOdbv-wbRWQ&amp;t=10s"  style="color:#88A1E9" title="Les Vies Parallèles des Hommes Illustres de Plutarque par Olivier Roland"&gt;Vies parallèles&lt;/a&gt; : Cette série de biographies compare des figures célèbres de l'histoire grecque et romaine. Chaque paire de vies met en parallèle un Grec et un Romain, suivie d'une comparaison qui souligne les similitudes et les différences entre les deux personnages. Parmi les paires les plus connues, on trouve Alexandre le Grand et Jules César, Thésée et Romulus, ou encore Démosthène et Cicéron. Son objectif  n'était pas seulement historique, mais aussi moral et éducatif. &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C5%92uvres_morales"  style="color:#88A1E9" title="Œuvres morales par Wikipedia"&gt;Moralia&lt;/a&gt;  : Cette collection regroupe des essais et des traités sur des sujets variés, allant de la philosophie morale à la religion, en passant par la politique, l'éducation et les sciences naturelles, la tranquillité de l'âme, l'amour, la superstition. &lt;/p&gt; &lt;p&gt; Il est connu pour son &lt;a href="https://www.youtube.com/watch?v=n7uLx5rVmm0"  style="color:#88A1E9" title="La Sérénité intérieure | PLUTARQUE  par Les Choses au Claire"&gt;style clair&lt;/a&gt; et accessible, qui combine profondeur philosophique et récit vivant. Ses biographies sont à la fois instructives et divertissantes, mêlant anecdotes, réflexions morales et détails historiques. Il  reste une figure majeure de la littérature et de la philosophie antique. Ses œuvres, à la fois biographiques et philosophiques, continuent d'être étudiées et appréciées pour leur richesse, leur sagesse et leur pertinence intemporelle. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title="  Actualité de Plutarque par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16278-17.12.2016-ITEMA_21168598-2016C6278E0292-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F71" s="7" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>34</v>
+        <v>368</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>538</v>
+        <v>236</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6586,36 +6627,36 @@
         </is>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le"  style="color:#6A142A"  title=" Wikipedia"&gt;Marc AURÈLE&lt;/a&gt; (121-180) est un empereur romain et un philosophe stoïcien, le seul « empereur philosophe » de l’histoire romaine. Adopté par l’empereur Antonin le Pieux, il reçoit la meilleure éducation de son temps ; son maître Junius Rusticus lui fait lire les &lt;em&gt;Entretiens&lt;/em&gt; d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89pict%C3%A8te" title=" Wikipedia"&gt;Épictète&lt;/a&gt;, qui le marquent pour toujours. Empereur de 161 à sa mort, il passe une grande partie de son règne à défendre les frontières du Danube, au milieu d’une terrible épidémie.&lt;/p&gt; &lt;p&gt;C’est sous la tente, pendant ces campagnes, qu’il écrit en grec ses &lt;a href="https://fr.wikipedia.org/wiki/Pens%C3%A9es_pour_moi-m%C3%AAme"  title="Les pensées pour moi même de Marc AURELE "&gt;&lt;em&gt;Pensées pour moi-même&lt;/em&gt;&lt;/a&gt;, en douze livres. Ce n’est pas un traité destiné au public, mais &lt;a href="https://www.youtube.com/watch?v=KKSRqzRdBx0"  title="Les pensées pour moi même Marc AURELE par Kosmos"&gt;un journal intime&lt;/a&gt; d’exercices spirituels : il s’y rappelle les principes du stoïcisme pour mieux les vivre. Tout change et passe vite, les empires comme les hommes ; la mort est un phénomène naturel qu’il ne faut pas craindre. Le monde est un tout ordonné par la raison, et ce qui arrive doit être accepté comme une part de cet ordre. Ce qui nous trouble, ce ne sont pas les choses, mais nos jugements sur elles : il suffit de les corriger pour retrouver la paix dans cette « citadelle intérieure » que rien ne peut forcer. Marc Aurèle s’exhorte aussi à la justice et à la bienveillance : tous les hommes sont parents, membres d’une même cité universelle, et il faut instruire les méchants plutôt que s’irriter contre eux. « Dès l’aurore, dis-toi d’avance : je rencontrerai un indiscret, un ingrat, un insolent… »&lt;/p&gt; &lt;p&gt;Lu par Montaigne et Frédéric II, il connaît un vif succès &lt;a href="https://www.youtube.com/watch?v=1OeNwG_bxWg&amp;ab_channel=FranceCulture"   title="Les pensées de Marc AURELE au quotidien par France Culture"&gt;de nos jours&lt;/a&gt;, grâce notamment à Pierre Hadot, qui a montré dans &lt;em&gt;La Citadelle intérieure&lt;/em&gt; (1992) la portée de ces exercices.&lt;/p&gt;  &lt;audio controls title="Pensée pour moi même par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.01.2016-ITEMA_20899513-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        <v>576</v>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89pict%C3%A8te"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICTETE&lt;/a&gt; (vers 50-vers 125) est un philosophe &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcien&lt;/a&gt; grec, né esclave à Hiérapolis, en Phrygie. À Rome, il appartient à Épaphrodite, affranchi de Néron, qui lui permet de suivre les leçons du stoïcien Musonius Rufus. Affranchi, il enseigne à son tour, jusqu’à ce que l’empereur Domitien chasse les philosophes de Rome vers 93 ; il ouvre alors une école à Nicopolis, en Épire, où il enseigne jusqu’à sa mort.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit. Son disciple &lt;a href="https://fr.wikipedia.org/wiki/Arrien" title=" Wikipedia"&gt;Arrien&lt;/a&gt; a noté ses leçons dans &lt;a href="https://www.youtube.com/watch?v=2tUxNx_oMn4&amp;ab_channel=KarlBaudoin"  style="color:#88A1E9"  title="Les Entretiens d'Epictète par Karl Baudouin"&gt;les &lt;em&gt;Entretiens&lt;/em&gt;&lt;/a&gt; et en a tiré un bref résumé, &lt;a href="https://www.youtube.com/watch?v=qN4m4bbZIGU&amp;t=51s&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Le manuel d'Epictète par Le Précepteur"&gt;le &lt;em&gt;Manuel&lt;/em&gt;&lt;/a&gt;. Tout part d’une distinction : il y a &lt;a href="https://www.youtube.com/watch?v=7Zc85Kc4Xqw&amp;ab_channel=KarlBaudoin"  title="Le manuel d'Epictète par Karl Baudouin"&gt;ce qui dépend de nous&lt;/a&gt;, nos jugements, nos désirs, nos refus, et ce qui ne dépend pas de nous, le corps, les biens, la réputation, les charges, les événements. Le malheur vient de ce que nous voulons maîtriser ce qui nous échappe. « Ce qui trouble les hommes, ce ne sont pas les choses, mais les jugements qu’ils portent sur les choses » : la mort n’est pas terrible, c’est l’opinion que nous en avons qui l’est. La liberté est donc intérieure, et l’esclave peut être plus libre que son maître. Le sage s’exerce chaque jour à bien juger, à désirer seulement ce qui dépend de lui, et à jouer son rôle dans le monde comme un acteur joue celui que l’auteur lui a donné. On résume sa morale par la formule « supporte et abstiens-toi ».&lt;/p&gt; &lt;p&gt;Lu par &lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le" title=" Wikipedia"&gt;Marc Aurèle&lt;/a&gt;, puis par Pascal et Montaigne, il inspire encore les thérapies cognitives d’aujourd’hui, qui apprennent à modifier nos jugements pour apaiser nos émotions.&lt;/p&gt;  &lt;audio controls title="Epictète ou savoir choisir par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-07.01.2026-ITEMA_24365714-2026C48904S0007-NET_MFC_C2619D7A-778C-4505-B127-925270631DD9-21-6f25ae2ae83c473a68406d0d4d07fa43.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F72" s="7" t="s">
-        <v>593</v>
+        <v>65</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="2" t="s">
-        <v>512</v>
+        <v>23</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>200</v>
@@ -6624,7 +6665,7 @@
         <v>386</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6635,45 +6676,45 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
-        <v>175</v>
+        <v>60</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas"  title="Wikipedia"&gt;Ammonios SACCAS&lt;/a&gt; (vers 175-242) est un philosophe platonicien d’Alexandrie, maître de Plotin et l’un des inspirateurs du néoplatonisme. Son surnom de Saccas, le « porteur de sacs », rappelle peut-être qu’il fut d’abord portefaix sur les quais du port. Selon le philosophe Porphyre, il serait né dans une famille chrétienne et aurait ensuite choisi la philosophie grecque, ce que contestent les auteurs chrétiens.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit, et sa doctrine nous échappe en grande partie. Nous savons surtout qu’il fut un maître exceptionnel. Porphyre raconte que Plotin, à vingt-huit ans, avait suivi sans satisfaction les cours des professeurs les plus réputés d’Alexandrie, jusqu’à ce qu’un ami le conduise chez Ammonios. En sortant, Plotin s’écria : « Voilà celui que je cherchais ! » Il resta onze ans auprès de lui. Ammonios eut aussi pour élèves le philosophe Origène, à ne pas confondre avec le théologien chrétien du même nom, Érennius et peut-être le critique Longin. Ses disciples s’engagèrent à ne pas divulguer son enseignement, promesse que Plotin ne rompit qu’après les autres. Des auteurs plus tardifs lui attribuent l’idée que Platon et Aristote s’accordent sur l’essentiel, et une réflexion sur l’union de l’âme et du corps : l’âme, réalité spirituelle, s’unit au corps sans se mélanger à lui ni se corrompre. On le surnommait « l’instruit par Dieu ».&lt;/p&gt; &lt;p&gt;On l’appelle souvent le &lt;a href="https://www.youtube.com/watch?v=hSIeYrZa-X4"title=" Ammonios SACCAS maitre de Plotin  par Vox Temporis"&gt;« maître silencieux »&lt;/a&gt; : sans laisser une ligne, il a marqué, à travers Plotin, toute la tradition néoplatonicienne.&lt;/p&gt;</t>
+        <v>583</v>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicomaque_de_G%C3%A9rase"  style="color:#6A142A"  title=" Wikipedia"&gt;NICOMAQUE de Gérase&lt;/a&gt; était un mathématicien et philosophe néo-pythagoricien grec mettant l'accent sur l'importance des nombres et de leurs propriétés dans la compréhension de l'univers. Pour lui, ils n'étaient pas de simples outils de calcul, mais des  &lt;a href="https://www.youtube.com/watch?v=Jbuap2Pahbg" style="color:#88A1E9" title=" Pourquoi rééditer l'Introduction arithmétique de Nicomaque de Gerasa en France ?  par LabEx HaStec"&gt;principes fondamentaux &lt;/a&gt; qui sous-tendent la réalité. Il cherchait à réduire les Formes platoniciennes et les catégories aristotéliciennes aux propriétés formelles des nombres. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus célèbre et le plus influent "Introduction à l'arithmétique" est un manuel fondamental qui a servi de base à l'arithmétique pendant une grande partie du Moyen Âge, notamment grâce à sa traduction et adaptation par Boèce (vers 505) dans son "De institutione arithmetica". Ce traité aborde des concepts comme les nombres figurés, les nombres parfaits, abondants et déficients, et la théorie des nombres en général. &lt;/p&gt; &lt;p&gt;  Dans son deuxième ovrage " Théologie de l'arithmétique", il  explore les significations mystiques et philosophiques des nombres, rattachant les propriétés numériques à des concepts divins et cosmologiques.   Il était également théoricien de la musique et musicologue où dans  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1956_num_69_324_3426" style="color:#88A1E9" title=" L'hexatonique grec d'après Nicomaque  par Persée"&gt; 'L'hexatonique"&lt;/a&gt;, il témoigne de son intérêt pour les relations mathématiques sous-jacentes à l'harmonie musicale. &lt;/p&gt; &lt;p&gt; Il  est une figure essentielle pour comprendre la philosophie et les mathématiques de l'Antiquité tardive, en particulier le courant néo-pythagoricien qui cherchait à concilier les doctrines platoniciennes et aristotéliciennes avec la mystique des nombres. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F73" s="7" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="2" t="s">
-        <v>604</v>
+        <v>23</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6681,47 +6722,45 @@
         </is>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
-        <v>205</v>
+        <v>121</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Plotin"  style="color:#6A142A"  title=" Wikipedia"&gt;PLOTIN&lt;/a&gt; (205-270) est le plus grand philosophe de l’Antiquité tardive et le fondateur du néoplatonisme. Né en Égypte, il étudie à Alexandrie pendant onze ans auprès d’&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas" title=" Wikipedia"&gt;Ammonios Saccas&lt;/a&gt;, puis suit l’expédition de l’empereur Gordien III contre la Perse pour connaître la sagesse des Perses et des Indiens. Il s’installe à Rome vers 245 et y ouvre une école fréquentée par des sénateurs et des médecins.&lt;/p&gt; &lt;p&gt;Ses 54 traités ont été classés par son disciple &lt;a href="https://fr.wikipedia.org/wiki/Porphyre_de_Tyr" title=" Wikipedia"&gt;Porphyre&lt;/a&gt; en six groupes de neuf, les &lt;a href="https://www.youtube.com/watch?v=_UTBOMazrcE&amp;t=699s&amp;ab_channel=R%C3%A9sonance%5Bs%5D"  style="color:#88A1E9"  title="Les Ennéades de Plotin: Au commencement était l'Un par Résonance"&gt;&lt;em&gt;Ennéades&lt;/em&gt;&lt;/a&gt;. Plotin y relit Platon pour en tirer un système : &lt;a href="https://www.youtube.com/watch?v=nZblkRaDj-Q&amp;ab_channel=PhiloCloud"  style="color:#88A1E9"  title="Au commencement était l'Un par PhiloCloud"&gt;au commencement est l’Un&lt;/a&gt;, principe absolument simple, au-delà de l’être et de la pensée, que l’on ne peut nommer. De lui procède, comme la lumière du soleil, l’Intellect, qui contient les Idées, puis l’Âme, qui anime le monde sensible ; la matière, au plus bas, n’est presque rien, une absence de forme. Tout être vient de l’Un et aspire à y retourner. L’âme humaine, tombée dans le corps, peut remonter vers sa source par la vertu, la philosophie et la contemplation de la beauté, jusqu’à l’union avec l’Un, une extase que Plotin aurait connue quatre fois. C’est une ascension où l’Intellect, &lt;a href="https://books.openedition.org/vrin/4250?lang=fr"  style="color:#88A1E9"  title="Une méthaphysique de l'amour par OpenEdition"&gt;« embrasé d’amour »&lt;/a&gt;, s’oublie lui-même : « Retranche tout. »&lt;/p&gt; &lt;p&gt;Ses dernières paroles auraient été : « Tâchez de faire remonter le divin qui est en vous au divin qui est dans l’univers. » Par Augustin et le Pseudo-Denys, il marque la mystique chrétienne, et Marsile Ficin le traduit à la Renaissance.&lt;/p&gt;  &lt;audio controls title="La beauté est elle d'abord intérieure ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-04.04.2019-ITEMA_22027092-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        <v>591</v>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le"  style="color:#6A142A"  title=" Wikipedia"&gt;Marc AURÈLE&lt;/a&gt; (121-180) est un empereur romain et un philosophe stoïcien, le seul « empereur philosophe » de l’histoire romaine. Adopté par l’empereur Antonin le Pieux, il reçoit la meilleure éducation de son temps ; son maître Junius Rusticus lui fait lire les &lt;em&gt;Entretiens&lt;/em&gt; d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89pict%C3%A8te" title=" Wikipedia"&gt;Épictète&lt;/a&gt;, qui le marquent pour toujours. Empereur de 161 à sa mort, il passe une grande partie de son règne à défendre les frontières du Danube, au milieu d’une terrible épidémie.&lt;/p&gt; &lt;p&gt;C’est sous la tente, pendant ces campagnes, qu’il écrit en grec ses &lt;a href="https://fr.wikipedia.org/wiki/Pens%C3%A9es_pour_moi-m%C3%AAme"  title="Les pensées pour moi même de Marc AURELE "&gt;&lt;em&gt;Pensées pour moi-même&lt;/em&gt;&lt;/a&gt;, en douze livres. Ce n’est pas un traité destiné au public, mais &lt;a href="https://www.youtube.com/watch?v=KKSRqzRdBx0"  title="Les pensées pour moi même Marc AURELE par Kosmos"&gt;un journal intime&lt;/a&gt; d’exercices spirituels : il s’y rappelle les principes du stoïcisme pour mieux les vivre. Tout change et passe vite, les empires comme les hommes ; la mort est un phénomène naturel qu’il ne faut pas craindre. Le monde est un tout ordonné par la raison, et ce qui arrive doit être accepté comme une part de cet ordre. Ce qui nous trouble, ce ne sont pas les choses, mais nos jugements sur elles : il suffit de les corriger pour retrouver la paix dans cette « citadelle intérieure » que rien ne peut forcer. Marc Aurèle s’exhorte aussi à la justice et à la bienveillance : tous les hommes sont parents, membres d’une même cité universelle, et il faut instruire les méchants plutôt que s’irriter contre eux. « Dès l’aurore, dis-toi d’avance : je rencontrerai un indiscret, un ingrat, un insolent… »&lt;/p&gt; &lt;p&gt;Lu par Montaigne et Frédéric II, il connaît un vif succès &lt;a href="https://www.youtube.com/watch?v=1OeNwG_bxWg&amp;ab_channel=FranceCulture"   title="Les pensées de Marc AURELE au quotidien par France Culture"&gt;de nos jours&lt;/a&gt;, grâce notamment à Pierre Hadot, qui a montré dans &lt;em&gt;La Citadelle intérieure&lt;/em&gt; (1992) la portée de ces exercices.&lt;/p&gt;  &lt;audio controls title="Pensée pour moi même par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.01.2016-ITEMA_20899513-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F74" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"L’ascension de Plotin" par Vox Temporis</t>
-        </is>
+        <v>593</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>594</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="2" t="s">
-        <v>604</v>
+        <v>512</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>538</v>
+        <v>386</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6732,231 +6771,236 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="186.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas"  title="Wikipedia"&gt;Ammonios SACCAS&lt;/a&gt; (vers 175-242) est un philosophe platonicien d’Alexandrie, maître de Plotin et l’un des inspirateurs du néoplatonisme. Son surnom de Saccas, le « porteur de sacs », rappelle peut-être qu’il fut d’abord portefaix sur les quais du port. Selon le philosophe Porphyre, il serait né dans une famille chrétienne et aurait ensuite choisi la philosophie grecque, ce que contestent les auteurs chrétiens.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit, et sa doctrine nous échappe en grande partie. Nous savons surtout qu’il fut un maître exceptionnel. Porphyre raconte que Plotin, à vingt-huit ans, avait suivi sans satisfaction les cours des professeurs les plus réputés d’Alexandrie, jusqu’à ce qu’un ami le conduise chez Ammonios. En sortant, Plotin s’écria : « Voilà celui que je cherchais ! » Il resta onze ans auprès de lui. Ammonios eut aussi pour élèves le philosophe Origène, à ne pas confondre avec le théologien chrétien du même nom, Érennius et peut-être le critique Longin. Ses disciples s’engagèrent à ne pas divulguer son enseignement, promesse que Plotin ne rompit qu’après les autres. Des auteurs plus tardifs lui attribuent l’idée que Platon et Aristote s’accordent sur l’essentiel, et une réflexion sur l’union de l’âme et du corps : l’âme, réalité spirituelle, s’unit au corps sans se mélanger à lui ni se corrompre. On le surnommait « l’instruit par Dieu ».&lt;/p&gt; &lt;p&gt;On l’appelle souvent le &lt;a href="https://www.youtube.com/watch?v=hSIeYrZa-X4"title=" Ammonios SACCAS maitre de Plotin  par Vox Temporis"&gt;« maître silencieux »&lt;/a&gt; : sans laisser une ligne, il a marqué, à travers Plotin, toute la tradition néoplatonicienne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="I75" s="9"/>
+      <c r="J75" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="7" t="n">
+        <v>205</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Plotin"  style="color:#6A142A"  title=" Wikipedia"&gt;PLOTIN&lt;/a&gt; (205-270) est le plus grand philosophe de l’Antiquité tardive et le fondateur du néoplatonisme. Né en Égypte, il étudie à Alexandrie pendant onze ans auprès d’&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas" title=" Wikipedia"&gt;Ammonios Saccas&lt;/a&gt;, puis suit l’expédition de l’empereur Gordien III contre la Perse pour connaître la sagesse des Perses et des Indiens. Il s’installe à Rome vers 245 et y ouvre une école fréquentée par des sénateurs et des médecins.&lt;/p&gt; &lt;p&gt;Ses 54 traités ont été classés par son disciple &lt;a href="https://fr.wikipedia.org/wiki/Porphyre_de_Tyr" title=" Wikipedia"&gt;Porphyre&lt;/a&gt; en six groupes de neuf, les &lt;a href="https://www.youtube.com/watch?v=_UTBOMazrcE&amp;t=699s&amp;ab_channel=R%C3%A9sonance%5Bs%5D"  style="color:#88A1E9"  title="Les Ennéades de Plotin: Au commencement était l'Un par Résonance"&gt;&lt;em&gt;Ennéades&lt;/em&gt;&lt;/a&gt;. Plotin y relit Platon pour en tirer un système : &lt;a href="https://www.youtube.com/watch?v=nZblkRaDj-Q&amp;ab_channel=PhiloCloud"  style="color:#88A1E9"  title="Au commencement était l'Un par PhiloCloud"&gt;au commencement est l’Un&lt;/a&gt;, principe absolument simple, au-delà de l’être et de la pensée, que l’on ne peut nommer. De lui procède, comme la lumière du soleil, l’Intellect, qui contient les Idées, puis l’Âme, qui anime le monde sensible ; la matière, au plus bas, n’est presque rien, une absence de forme. Tout être vient de l’Un et aspire à y retourner. L’âme humaine, tombée dans le corps, peut remonter vers sa source par la vertu, la philosophie et la contemplation de la beauté, jusqu’à l’union avec l’Un, une extase que Plotin aurait connue quatre fois. C’est une ascension où l’Intellect, &lt;a href="https://books.openedition.org/vrin/4250?lang=fr"  style="color:#88A1E9"  title="Une méthaphysique de l'amour par OpenEdition"&gt;« embrasé d’amour »&lt;/a&gt;, s’oublie lui-même : « Retranche tout. »&lt;/p&gt; &lt;p&gt;Ses dernières paroles auraient été : « Tâchez de faire remonter le divin qui est en vous au divin qui est dans l’univers. » Par Augustin et le Pseudo-Denys, il marque la mystique chrétienne, et Marsile Ficin le traduit à la Renaissance.&lt;/p&gt;  &lt;audio controls title="La beauté est elle d'abord intérieure ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-04.04.2019-ITEMA_22027092-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L’ascension de Plotin" par Vox Temporis</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="I76" s="9"/>
+      <c r="J76" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="186.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="n">
         <v>213</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B77" s="7" t="s">
         <v>614</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C77" s="7" t="s">
         <v>615</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D77" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="E77" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Longin_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;LONGIN&lt;/a&gt; était un philosophe, rhéteur et critique littéraire grec de l'Antiquité tardive. Bien que sa vie et son œuvre soient peu documentée, il est connu pour son traité &lt;a href="https://remacle.org/bloodwolf/erudits/longin/sublime.htm" style="color:#88A1E9" title=" Login : traite du sublime par Remacle"&gt;"Du Sublime"&lt;/a&gt;, un texte majeur sur l'esthétique et la rhétorique. Ce texte explore la notion de sublime, un concept esthétique qui désigne ce qui élève l'âme, inspire l'admiration et transcende le banal. Le sublime se manifeste dans la littérature, l'art et la rhétorique, et il est souvent associé à la grandeur, à l'intensité émotionnelle et à la puissance expressive. Ses principales idées : &lt;p&gt; 
 &lt;p&gt;Le sublime est une qualité qui transcende la simple beauté ou l'élégance. Il provoque une émotion intense et une élévation spirituelle chez le lecteur ou l'auditeur. Il se manifeste dans des œuvres qui inspirent l'admiration, la crainte ou l'émerveillement. &lt;/p&gt; &lt;p&gt;Sources du sublime : Il identifie cinq sources principales du sublime : &lt;/p&gt; &lt;p&gt;La grandeur de la pensée : des idées profondes et élevées. &lt;/p&gt; &lt;p&gt;L'émotion intense : la capacité à toucher les sentiments du public. &lt;/p&gt; &lt;p&gt;Les figures de style : l'utilisation habile de métaphores, d'hyperboles, etc. &lt;/p&gt; &lt;p&gt;La noblesse de l'expression : un langage élégant et approprié. &lt;/p&gt; &lt;p&gt;La structure et l'arrangement : une composition harmonieuse et puissante. &lt;/p&gt; &lt;p&gt; Son analyse des techniques littéraires et de l'impact émotionnel de la parole a influencé la théorie rhétorique. "Du Sublime" est l'un des premiers textes à aborder la critique littéraire sous un angle esthétique et psychologique, en se concentrant sur l'effet des œuvres sur le public. Bien que sa vie soit mal documentée, son influence sur la pensée occidentale, en particulier dans les domaines de l'esthétique et de la rhétorique, est indéniable. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="F77" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="G75" s="15" t="s">
+      <c r="G77" s="15" t="s">
         <v>619</v>
       </c>
-      <c r="H75" s="9" t="s">
+      <c r="H77" s="9" t="s">
         <v>620</v>
       </c>
-      <c r="I75" s="9"/>
-      <c r="J75" s="2" t="s">
+      <c r="I77" s="9"/>
+      <c r="J77" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K75" s="2" t="s">
+      <c r="K77" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="L75" s="2" t="s">
+      <c r="L77" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="M75" s="2" t="s">
+      <c r="M77" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="n">
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="n">
         <v>234</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B78" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C78" s="7" t="s">
         <v>623</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="D78" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="E76" s="9" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Porphyre_de_Tyr"  style="color:#6A142A"  title=" Wikipedia"&gt;PORPHYRE de Tyr&lt;/a&gt; était un philosophe néoplatonicien romain, érudit et polémiste d'origine phénicienne, né à Tyr, dans l'actuel Liban. Il est surtout connu pour son rôle dans le développement et la diffusion de la philosophie néoplatonicienne, ainsi que pour ses critiques du christianisme. Il est né sous le nom de Malchus (qui signifie "roi" en phénicien), mais il a adopté le nom de Porphyre (du grec porphyra, "pourpre", en référence à la pourpre tyrienne, une teinture prestigieuse produite dans sa ville natale). &lt;/p&gt; &lt;p&gt; Il est surtout connu pour avoir édité et publié les &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1924_num_22_5_5497"  style="color:#88A1E9" title="Les Ennéades de Plotin par Persée"&gt;Ennéades de Plotin&lt;/a&gt;, une collection systématique des écrits de son maître. Ses propres contributions philosophiques  : &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isagog%C3%A8"  style="color:#88A1E9" title="Isagogè par Wikipedia"&gt;L'Isagogè&lt;/a&gt; : Une introduction aux Catégories d'Aristote, qui est devenue un texte fondamental dans l'enseignement de la logique médiévale, tant dans le monde islamique qu'en Europe. &lt;/p&gt; &lt;p&gt;Commentaires sur Aristote et Platon : Porphyre a écrit des commentaires sur les œuvres d'Aristote et de Platon, cherchant à harmoniser leurs philosophies. &lt;/p&gt; &lt;p&gt;Philosophie religieuse : Il a exploré des thèmes comme la nature de l'âme, la purification spirituelle et la relation entre l'homme et le divin. &lt;/p&gt; &lt;p&gt; Il  est également connu pour son ouvrage &lt;a href="https://www.persee.fr/doc/reg_0035-2039_2014_num_127_2_8359_t16_0629_0000_2"  style="color:#88A1E9" title=" Le traité de Porphyre contre les chrétiens  par Persée"&gt;"Contre les chrétiens"&lt;/a&gt;, une critique virulente du christianisme naissant. Dans ce texte, il attaquait les doctrines chrétiennes, les Écritures et la figure de Jésus, qu'il considérait comme un personnage historique plutôt que divin. Malheureusement, l'ouvrage n'a survécu qu'à travers des citations et des réfutations par des auteurs chrétiens comme Eusèbe de Césarée et Augustin d'Hippone. &lt;/p&gt; &lt;p&gt; Porphyre de Tyr est une figure majeure de la philosophie antique, dont l'œuvre a servi de pont entre la pensée grecque classique et les développements intellectuels ultérieurs. Son engagement envers le néoplatonisme, ses contributions à la logique et ses critiques du christianisme en font un penseur complexe et influent, dont l'héritage continue d'être étudié et débattu. &lt;/p&gt;  &lt;/p&gt;   &lt;audio controls title=" Une histoire philosophique, feat. Porphyre et Jamblique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16260-13.03.2021-ITEMA_22601996-2021C6260S0072.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F76" s="7" t="s">
+      <c r="F78" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="G76" s="9" t="s">
+      <c r="G78" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="H76" s="9" t="s">
+      <c r="H78" s="9" t="s">
         <v>628</v>
       </c>
-      <c r="I76" s="9"/>
-      <c r="J76" s="2" t="s">
+      <c r="I78" s="9"/>
+      <c r="J78" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="K78" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L76" s="2" t="s">
+      <c r="L78" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="M76" s="2" t="s">
+      <c r="M78" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="7" t="n">
         <v>245</v>
       </c>
-      <c r="B77" s="7" t="n">
+      <c r="B79" s="7" t="n">
         <v>325</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C79" s="7" t="s">
         <v>630</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D79" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="E77" s="9" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jamblique" style="color:#6A142A" title="Wikipedia"&gt;JAMBLIQUE de Chalcis&lt;/a&gt; est l'un des penseurs les plus influents du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt;, figure centrale de l'école syrienne. Né à Chalcis en Syrie (l'actuelle Qinnasrin), il fut d'abord l'élève de Porphyre à Rome avant de fonder sa propre école en Syrie, à Apamée, devenant le maître d'une génération de néoplatoniciens.&lt;/p&gt; &lt;p&gt;Jamblique transforma profondément le néoplatonisme en y intégrant la &lt;em&gt;théurgie&lt;/em&gt; — la pratique rituelle permettant l'union avec le divin — comme voie indispensable au côté de la philosophie pure. Dans son œuvre maîtresse, &lt;em&gt;Les Mystères d'Égypte&lt;/em&gt; (&lt;em&gt;De Mysteriis&lt;/em&gt;), il répondit aux critiques de Porphyre en affirmant que la contemplation intellectuelle seule ne suffit pas : les rites sacrés sont nécessaires pour élever l'âme jusqu'au divin. Il développa aussi une hiérarchie complexe des êtres divins.&lt;/p&gt; &lt;p&gt;Jamblique enrichit le système de Plotin par une multiplication des hypostases divines et une intégration systématique des traditions religieuses orientales et chaldéennes. Son influence sur les néoplatoniciens tardifs (Proclus, Damascios) et sur l'&lt;a href="https://fr.wikipedia.org/wiki/Hermétisme" style="color:#6A142A" title="Hermétisme sur Wikipedia"&gt;hermétisme&lt;/a&gt; renaissant fut considérable. L'empereur Julien le tenait pour un maître de sagesse comparable à Platon lui-même. Grand admirateur de Pythagore, il consacre à sa vie et à sa doctrine une série d’ouvrages, dont une &lt;em&gt;Vie de Pythagore&lt;/em&gt; et une &lt;em&gt;Exhortation à la philosophie&lt;/em&gt;. Contre Plotin, il soutient que l’âme humaine descend tout entière dans le corps : elle ne peut donc remonter seule vers le divin et a besoin de l’aide des dieux. Il fixe aussi l’ordre de lecture des dialogues de Platon, que suivront les écoles néoplatoniciennes.&lt;/p&gt;  &lt;audio controls title="Une histoire philosophique : Porphyre et Jamblique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16260-13.03.2021-ITEMA_22601996-2021C6260S0072.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F79" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="G77" s="9" t="s">
+      <c r="G79" s="9" t="s">
         <v>634</v>
       </c>
-      <c r="H77" s="12" t="s">
+      <c r="H79" s="12" t="s">
         <v>635</v>
-      </c>
-      <c r="I77" s="9"/>
-      <c r="J77" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="n">
-        <v>290</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>639</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marius_Victorinus"  style="color:#6A142A"  title=" Wikipedia"&gt;Marius VICTORINUS&lt;/a&gt; était un philosophe, africain de naissance puis romain enseignant la rhétorique et la philosophie.  Il s'est converti au Christianisme après avoir étudié les Écritures. Sa conversion a été perçue comme un symbole de la capacité du christianisme à attirer même les intellectuels les plus érudits. Il  a laissé une œuvre variée, à la fois philosophique et  &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1957_num_70_66_20268" style="color:#88A1E9" title=" Oeuvres théologiques de Marius Victorinus par Persée"&gt;théologique. &lt;/a&gt;&lt;p&gt;Avant sa conversion :  Il a écrit des commentaires sur des textes philosophiques grecs, notamment ceux d'Aristote et de Platon. Ces travaux montrent sa maîtrise de la philosophie néoplatonicienne, qui a profondément influencé sa pensée.  Il a traduit et adapté des œuvres néoplatoniciennes, comme celles de Plotin et de Porphyre, contribuant à diffuser ces idées dans le monde latin. &lt;/p&gt; &lt;p&gt;Après sa conversion :  Il s'est concentré sur des questions théologiques, en particulier sur la Trinité et la nature du Christ et de &lt;a href="https://www.youtube.com/watch?v=DCbfSqUZFs0" style="color:#88A1E9" title=" La notion de pré-étant selon Marius Victorinus  par Hervé Pasqua"&gt;l'être&lt;/a&gt;. Ses œuvres les plus importantes incluent : &lt;/p&gt; &lt;p&gt;Adversus Arium : Une défense de l'orthodoxie nicéenne contre  &lt;a href="https://fr.wikipedia.org/wiki/Arianisme" style="color:#88A1E9" title=" Arianisme par Wikipédia"&gt;l'arianisme&lt;/a&gt;, qui niait la divinité du Christ. &lt;/p&gt; &lt;p&gt;De generatione divini Verbi  : Un traité sur la relation entre le Père et le Fils dans la Trinité. &lt;/p&gt; &lt;p&gt;De Trinitate : Une exploration approfondie de la doctrine trinitaire, influencée par la philosophie néoplatonicienne. &lt;/p&gt; &lt;p&gt; Son utilisation des concepts néoplatoniciens pour expliquer des doctrines chrétiennes complexes, comme la Trinité, a influencé des théologiens ultérieurs, notamment saint Augustin. Il  a également contribué à la formation d'un langage théologique latin, en adaptant des concepts philosophiques grecs à la pensée chrétienne. &lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="I78" s="9"/>
-      <c r="J78" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
-        <v>317</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9mistios"  style="color:#6A142A"  title=" Wikipedia"&gt;THÉMISTIOS&lt;/a&gt; (vers 317-388) est un philosophe, orateur et homme politique grec de l’Empire romain d’Orient. Fils d’un philosophe de Paphlagonie, il enseigne à Constantinople, la nouvelle capitale, et y devient sénateur en 355. Bien que resté païen, il sert successivement six empereurs, presque tous chrétiens, de Constance II à Théodose, qui le nomme préfet de la ville et lui confie l’éducation de son fils.&lt;/p&gt; &lt;p&gt;Il est d’abord connu pour ses &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_12_5759" style="color:#88A1E9" title=" d'Aristote par Themistius par Persée"&gt;paraphrases d’Aristote&lt;/a&gt;, des résumés commentés qui reformulent avec clarté les traités du philosophe : les &lt;em&gt;Seconds Analytiques&lt;/em&gt;, la &lt;em&gt;Physique&lt;/em&gt;, le traité &lt;em&gt;De l’âme&lt;/em&gt; et une partie de la &lt;em&gt;Métaphysique&lt;/em&gt;. Traduites en arabe, en hébreu puis en latin, elles ont été lues par Averroès et Thomas d’Aquin, en particulier pour la question de l’intellect. Thémistios est aussi un grand orateur. Dans ses &lt;a href="https://www.persee.fr/doc/topoi_1764-0733_2006_mel_7_1_2980" style="color:#88A1E9" title="Thémistios et ses adversaires : le témoignage du discours  par Persée"&gt;discours&lt;/a&gt;, adressés aux empereurs ou au Sénat, il défend une idée haute du rôle du philosophe : il ne doit pas fuir la cité, mais conseiller le pouvoir et rappeler au prince qu’il doit être une « loi vivante », juste et humain. Dans un discours célèbre adressé à l’empereur Jovien, en 364, il plaide pour la tolérance religieuse : Dieu, dit-il, se réjouit de la diversité des cultes, comme le chef d’une armée de la diversité de ses troupes, et nul ne doit être contraint dans sa foi.&lt;/p&gt; &lt;p&gt;Païen respecté des chrétiens, il illustre &lt;a href="https://www.youtube.com/watch?v=JdIUtCSF-JA" style="color:#88A1E9" title="«L’œuvre de Thémistios et son importance pour l’histoire de la philosophie» par Histoire de la mémoire et des idées"&gt;son rôle&lt;/a&gt; de médiateur entre la culture grecque et le nouvel Empire chrétien.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>652</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="2" t="s">
-        <v>23</v>
+        <v>636</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>653</v>
+        <v>76</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>302</v>
+        <v>538</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -6964,69 +7008,161 @@
         </is>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
-        <v>335</v>
+        <v>290</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>657</v>
+        <v>640</v>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_de_Nysse"  style="color:#6A142A"  title=" Wikipedia"&gt;GRÉGOIRE de Nysse&lt;/a&gt; était un religieux et un mystique turc connu pour ses contributions à la &lt;a href="https://www.youtube.com/watch?v=-fOGBAaiNFE" style="color:#88A1E9" title="LA TRINITÉ EXPLIQUÉE  par Frere Paul Adrien"&gt;théologie trinitaire&lt;/a&gt; et à la mystique chrétienne. Il a insisté sur l'unité et l'égalité des trois personnes de la Trinité et a développé des arguments sophistiqués pour expliquer comment ils sont distinctes mais partagent une même essence divine. Il a également exploré la nature infinie de Dieu, soulignant qu'il est au-delà de toute compréhension humaine. Cette idée a influencé la tradition apophatique &lt;a href="https://www.youtube.com/watch?v=iSBm7R1Hlr4" style="color:#88A1E9" title="La théologie négative par Resonances"&gt;(ou théologie négative)&lt;/a&gt; dans le christianisme, qui soutient que Dieu ne peut être défini que par ce qu'il n'est pas. &lt;/p&gt; &lt;p&gt; Il a écrit abondamment sur la nature humaine et la destinée de l'âme  : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/scrip_0036-9772_1985_num_39_2_1409" style="color:#88A1E9" title="Deux fragments anciens (en minuscule de type « Anastase ») du De hominis opificio de Grégoire de Nysse par Persée"&gt;"De hominis opificio"&lt;/a&gt; :  il explore la création de l'homme à l'image de Dieu et la restauration de cette image à travers le Christ.&lt;/p&gt; &lt;p&gt;"La Vie de Moïse" :  il utilise l'histoire biblique de Moïse comme une allégorie pour décrire le cheminement de l'âme vers Dieu. Il décrit l'ascension spirituelle comme un processus infini, où l'âme est toujours en mouvement vers Dieu, sans jamais pouvoir l'atteindre complètement. &lt;/p&gt; &lt;p&gt;Contre Eunome : Une défense de la doctrine nicéenne contre les arguments de l'arien Eunome. &lt;/p&gt; &lt;p&gt;La Grande Catéchèse : Un exposé systématique de la foi chrétienne, destiné à l'instruction des catéchumènes. &lt;/p&gt; &lt;p&gt;Sur l'âme et la résurrection : Un dialogue sur la nature de l'âme et la résurrection, influencé par les dialogues platoniciens. &lt;/p&gt; &lt;p&gt; Il  a eu une influence durable sur la théologie chrétienne, en particulier dans les domaines de la mystique, de l'anthropologie théologique et de la doctrine trinitaire. Il est vénéré comme un saint dans les Églises catholique, orthodoxe et anglicane, et sa fête est célébrée le 9 mars dans l'Église catholique et le 10 janvier dans l'Église orthodoxe. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marius_Victorinus"  style="color:#6A142A"  title=" Wikipedia"&gt;Marius VICTORINUS&lt;/a&gt; était un philosophe, africain de naissance puis romain enseignant la rhétorique et la philosophie.  Il s'est converti au Christianisme après avoir étudié les Écritures. Sa conversion a été perçue comme un symbole de la capacité du christianisme à attirer même les intellectuels les plus érudits. Il  a laissé une œuvre variée, à la fois philosophique et  &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1957_num_70_66_20268" style="color:#88A1E9" title=" Oeuvres théologiques de Marius Victorinus par Persée"&gt;théologique. &lt;/a&gt;&lt;p&gt;Avant sa conversion :  Il a écrit des commentaires sur des textes philosophiques grecs, notamment ceux d'Aristote et de Platon. Ces travaux montrent sa maîtrise de la philosophie néoplatonicienne, qui a profondément influencé sa pensée.  Il a traduit et adapté des œuvres néoplatoniciennes, comme celles de Plotin et de Porphyre, contribuant à diffuser ces idées dans le monde latin. &lt;/p&gt; &lt;p&gt;Après sa conversion :  Il s'est concentré sur des questions théologiques, en particulier sur la Trinité et la nature du Christ et de &lt;a href="https://www.youtube.com/watch?v=DCbfSqUZFs0" style="color:#88A1E9" title=" La notion de pré-étant selon Marius Victorinus  par Hervé Pasqua"&gt;l'être&lt;/a&gt;. Ses œuvres les plus importantes incluent : &lt;/p&gt; &lt;p&gt;Adversus Arium : Une défense de l'orthodoxie nicéenne contre  &lt;a href="https://fr.wikipedia.org/wiki/Arianisme" style="color:#88A1E9" title=" Arianisme par Wikipédia"&gt;l'arianisme&lt;/a&gt;, qui niait la divinité du Christ. &lt;/p&gt; &lt;p&gt;De generatione divini Verbi  : Un traité sur la relation entre le Père et le Fils dans la Trinité. &lt;/p&gt; &lt;p&gt;De Trinitate : Une exploration approfondie de la doctrine trinitaire, influencée par la philosophie néoplatonicienne. &lt;/p&gt; &lt;p&gt; Son utilisation des concepts néoplatoniciens pour expliquer des doctrines chrétiennes complexes, comme la Trinité, a influencé des théologiens ultérieurs, notamment saint Augustin. Il  a également contribué à la formation d'un langage théologique latin, en adaptant des concepts philosophiques grecs à la pensée chrétienne. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F80" s="7" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>661</v>
+        <v>644</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="7" t="n">
+        <v>317</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9mistios"  style="color:#6A142A"  title=" Wikipedia"&gt;THÉMISTIOS&lt;/a&gt; (vers 317-388) est un philosophe, orateur et homme politique grec de l’Empire romain d’Orient. Fils d’un philosophe de Paphlagonie, il enseigne à Constantinople, la nouvelle capitale, et y devient sénateur en 355. Bien que resté païen, il sert successivement six empereurs, presque tous chrétiens, de Constance II à Théodose, qui le nomme préfet de la ville et lui confie l’éducation de son fils.&lt;/p&gt; &lt;p&gt;Il est d’abord connu pour ses &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_12_5759" style="color:#88A1E9" title=" d'Aristote par Themistius par Persée"&gt;paraphrases d’Aristote&lt;/a&gt;, des résumés commentés qui reformulent avec clarté les traités du philosophe : les &lt;em&gt;Seconds Analytiques&lt;/em&gt;, la &lt;em&gt;Physique&lt;/em&gt;, le traité &lt;em&gt;De l’âme&lt;/em&gt; et une partie de la &lt;em&gt;Métaphysique&lt;/em&gt;. Traduites en arabe, en hébreu puis en latin, elles ont été lues par Averroès et Thomas d’Aquin, en particulier pour la question de l’intellect. Thémistios est aussi un grand orateur. Dans ses &lt;a href="https://www.persee.fr/doc/topoi_1764-0733_2006_mel_7_1_2980" style="color:#88A1E9" title="Thémistios et ses adversaires : le témoignage du discours  par Persée"&gt;discours&lt;/a&gt;, adressés aux empereurs ou au Sénat, il défend une idée haute du rôle du philosophe : il ne doit pas fuir la cité, mais conseiller le pouvoir et rappeler au prince qu’il doit être une « loi vivante », juste et humain. Dans un discours célèbre adressé à l’empereur Jovien, en 364, il plaide pour la tolérance religieuse : Dieu, dit-il, se réjouit de la diversité des cultes, comme le chef d’une armée de la diversité de ses troupes, et nul ne doit être contraint dans sa foi.&lt;/p&gt; &lt;p&gt;Païen respecté des chrétiens, il illustre &lt;a href="https://www.youtube.com/watch?v=JdIUtCSF-JA" style="color:#88A1E9" title="«L’œuvre de Thémistios et son importance pour l’histoire de la philosophie» par Histoire de la mémoire et des idées"&gt;son rôle&lt;/a&gt; de médiateur entre la culture grecque et le nouvel Empire chrétien.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="I81" s="9"/>
+      <c r="J81" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K80" s="2" t="s">
+      <c r="K81" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="7" t="n">
+        <v>335</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_de_Nysse"  style="color:#6A142A"  title=" Wikipedia"&gt;GRÉGOIRE de Nysse&lt;/a&gt; était un religieux et un mystique turc connu pour ses contributions à la &lt;a href="https://www.youtube.com/watch?v=-fOGBAaiNFE" style="color:#88A1E9" title="LA TRINITÉ EXPLIQUÉE  par Frere Paul Adrien"&gt;théologie trinitaire&lt;/a&gt; et à la mystique chrétienne. Il a insisté sur l'unité et l'égalité des trois personnes de la Trinité et a développé des arguments sophistiqués pour expliquer comment ils sont distinctes mais partagent une même essence divine. Il a également exploré la nature infinie de Dieu, soulignant qu'il est au-delà de toute compréhension humaine. Cette idée a influencé la tradition apophatique &lt;a href="https://www.youtube.com/watch?v=iSBm7R1Hlr4" style="color:#88A1E9" title="La théologie négative par Resonances"&gt;(ou théologie négative)&lt;/a&gt; dans le christianisme, qui soutient que Dieu ne peut être défini que par ce qu'il n'est pas. &lt;/p&gt; &lt;p&gt; Il a écrit abondamment sur la nature humaine et la destinée de l'âme  : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/scrip_0036-9772_1985_num_39_2_1409" style="color:#88A1E9" title="Deux fragments anciens (en minuscule de type « Anastase ») du De hominis opificio de Grégoire de Nysse par Persée"&gt;"De hominis opificio"&lt;/a&gt; :  il explore la création de l'homme à l'image de Dieu et la restauration de cette image à travers le Christ.&lt;/p&gt; &lt;p&gt;"La Vie de Moïse" :  il utilise l'histoire biblique de Moïse comme une allégorie pour décrire le cheminement de l'âme vers Dieu. Il décrit l'ascension spirituelle comme un processus infini, où l'âme est toujours en mouvement vers Dieu, sans jamais pouvoir l'atteindre complètement. &lt;/p&gt; &lt;p&gt;Contre Eunome : Une défense de la doctrine nicéenne contre les arguments de l'arien Eunome. &lt;/p&gt; &lt;p&gt;La Grande Catéchèse : Un exposé systématique de la foi chrétienne, destiné à l'instruction des catéchumènes. &lt;/p&gt; &lt;p&gt;Sur l'âme et la résurrection : Un dialogue sur la nature de l'âme et la résurrection, influencé par les dialogues platoniciens. &lt;/p&gt; &lt;p&gt; Il  a eu une influence durable sur la théologie chrétienne, en particulier dans les domaines de la mystique, de l'anthropologie théologique et de la doctrine trinitaire. Il est vénéré comme un saint dans les Églises catholique, orthodoxe et anglicane, et sa fête est célébrée le 9 mars dans l'Église catholique et le 10 janvier dans l'Église orthodoxe. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="I82" s="9"/>
+      <c r="J82" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K82" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="L80" s="2" t="s">
+      <c r="L82" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="M80" s="2" t="s">
+      <c r="M82" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P80">
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P82">
         <v>2</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="239.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="n">
+    <row r="83" customFormat="false" ht="239.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="7" t="n">
         <v>354</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B83" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C83" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="D83" s="8" t="s">
         <v>666</v>
       </c>
-      <c r="E81" s="9" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9lage_(h%C3%A9r%C3%A9siarque)"  style="color:#6A142A"  title=" Wikipedia"&gt;PÉLAGE&lt;/a&gt;  également connu sous le nom Pelagius en latin, était un moine et théologien britannique surtout connu pour avoir été au cœur d'une controverse théologique majeure dans l'histoire de l'Église chrétienne, connue sous le nom de &lt;a href="https://www.la-croix.com/Religion/Religion-et-spiritualite/Comprendre-pelagianisme-2018-11-17-1200983747" title="comprendre le Pélage par la Croix"&gt; pélagianisme&lt;/a&gt;. 
 Originaire des îles britanniques, actif principalement à Rome et en Afrique du Nord au début du Ve siècle, il était profondément engagé dans la vie monastique et était reconnu pour son ascétisme rigoureux. &lt;/p&gt; &lt;p&gt;La principale controverse associée à Pelage concernait la question de la nature du péché, de la grâce et du libre arbitre. Pelage soutenait que les êtres humains avaient la capacité intrinsèque de choisir le bien et d'éviter le péché sans l'aide de la grâce divine. Il rejetait l'idée du péché originel, enseignant que chaque personne naissait dans un état d'innocence et avait la possibilité de vivre une vie sans péché.&lt;/p&gt;
@@ -7034,354 +7170,252 @@
 &lt;p&gt;Le &lt;a href="https://www.youtube.com/watch?v=AnKeIzmox0s" title="la victoire de st Augustin sur Pélage par Michel Onfray"&gt; débat&lt;/a&gt; entre Pelage et Augustin a finalement conduit à plusieurs conciles et décrets ecclésiastiques condamnant  le pélagianisme comme une hérésie. Malgré cela, les idées de Pelage ont continué à influencer certains courants de pensée chrétienne ou religuieux comme Fauste de Riez, et la controverse pélagienne a laissé une marque durable sur l'histoire théologique de l'Église.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F81" s="7" t="s">
+      <c r="F83" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="G81" s="9" t="s">
+      <c r="G83" s="9" t="s">
         <v>669</v>
       </c>
-      <c r="H81" s="9" t="s">
+      <c r="H83" s="9" t="s">
         <v>670</v>
-      </c>
-      <c r="I81" s="9"/>
-      <c r="J81" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="M81" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7" t="n">
-        <v>354</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>674</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="I82" s="9"/>
-      <c r="J82" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="K82" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L82" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P82">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7" t="n">
-        <v>355</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>683</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>684</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>685</v>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hypatie"  style="color:#6A142A"  title=" Wikipedia"&gt;HYPATIE d'Alexandrie&lt;/a&gt; était est une figure emblématique de l'Antiquité tardive, connue pour ses contributions à la philosophie, aux mathématiques et à l'astronomie. Elle est souvent considérée comme l'une des  &lt;a href="https://laviedesidees.fr/Hypatie-d-Alexandrie-femme-antique-figures-contemporaines" style="color:#88A1E9" title="Hypatie d’Alexandrie : femme antique, figures contemporaines par College de France"&gt;premières femmes&lt;/a&gt; scientifiques de l'histoire. Elle était la fille de Théon d'Alexandrie, un mathématicien et astronome renommé qui a joué un rôle crucial dans l'éducation de sa fille et elle a rapidement surpassé son père en renommée et en compétence, devenant une enseignante respectée et une érudite de premier plan. &lt;/p&gt; &lt;p&gt; Elle  a  &lt;a href="https://www.youtube.com/watch?v=gXk4fZ41Dyc" style="color:#88A1E9" title="La vie mystérieuse d'Hypatie : grande philosophe et mathématicienne ! par Kidaia"&gt;édité&lt;/a&gt; des œuvres mathématiques importantes, notamment les "Éléments" d'Euclide et les "Coniques" d'Apollonius de Perga et a travaillé sur des traités d'astronomie, collaborant avec son père pour réviser et commenter l'"Almageste" de Ptolémée. Elle a peut-être aussi contribué à la conception de &lt;a href="https://www.youtube.com/watch?v=c6Ab5oMIMoc"title="L'Astrolabe par Institut du monde arabe"&gt;" l'Astrolabe "&lt;/a&gt;, un instrument utilisé pour mesurer la position des astres. &lt;/p&gt; &lt;p&gt; Hypatie était une adepte du néoplatonisme, une école de pensée philosophique qui cherchait à synthétiser les idées de Platon avec d'autres traditions philosophiques et religieuses. Elle a dirigé une école néoplatonicienne à Alexandrie, attirant des étudiants de tout l'Empire romain. &lt;/p&gt; &lt;p&gt; En tant que païenne et symbole de la science et de la philosophie antiques, elle est devenue une cible pour les chrétiens radicaux et a été brutalement assassinée par une foule dirigée par des partisans de l'évêque Cyrille d'Alexandrie. Sa mort est souvent considérée comme un tournant symbolique dans le déclin de la culture païenne et de la liberté intellectuelle dans l'Empire romain. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title=" Hypatie d'Alexandrie, enseigner les maths envers et contre tout par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25546-14.01.2025-ITEMA_23980317-2025F54134E0003-NET_MFI_25ED747B-707B-4A53-94F6-7EEB0584D30D-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>687</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>689</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="7" t="n">
+        <v>354</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="I84" s="9"/>
+      <c r="J84" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="7" t="n">
+        <v>355</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hypatie"  style="color:#6A142A"  title=" Wikipedia"&gt;HYPATIE d'Alexandrie&lt;/a&gt; était est une figure emblématique de l'Antiquité tardive, connue pour ses contributions à la philosophie, aux mathématiques et à l'astronomie. Elle est souvent considérée comme l'une des  &lt;a href="https://laviedesidees.fr/Hypatie-d-Alexandrie-femme-antique-figures-contemporaines" style="color:#88A1E9" title="Hypatie d’Alexandrie : femme antique, figures contemporaines par College de France"&gt;premières femmes&lt;/a&gt; scientifiques de l'histoire. Elle était la fille de Théon d'Alexandrie, un mathématicien et astronome renommé qui a joué un rôle crucial dans l'éducation de sa fille et elle a rapidement surpassé son père en renommée et en compétence, devenant une enseignante respectée et une érudite de premier plan. &lt;/p&gt; &lt;p&gt; Elle  a  &lt;a href="https://www.youtube.com/watch?v=gXk4fZ41Dyc" style="color:#88A1E9" title="La vie mystérieuse d'Hypatie : grande philosophe et mathématicienne ! par Kidaia"&gt;édité&lt;/a&gt; des œuvres mathématiques importantes, notamment les "Éléments" d'Euclide et les "Coniques" d'Apollonius de Perga et a travaillé sur des traités d'astronomie, collaborant avec son père pour réviser et commenter l'"Almageste" de Ptolémée. Elle a peut-être aussi contribué à la conception de &lt;a href="https://www.youtube.com/watch?v=c6Ab5oMIMoc"title="L'Astrolabe par Institut du monde arabe"&gt;" l'Astrolabe "&lt;/a&gt;, un instrument utilisé pour mesurer la position des astres. &lt;/p&gt; &lt;p&gt; Hypatie était une adepte du néoplatonisme, une école de pensée philosophique qui cherchait à synthétiser les idées de Platon avec d'autres traditions philosophiques et religieuses. Elle a dirigé une école néoplatonicienne à Alexandrie, attirant des étudiants de tout l'Empire romain. &lt;/p&gt; &lt;p&gt; En tant que païenne et symbole de la science et de la philosophie antiques, elle est devenue une cible pour les chrétiens radicaux et a été brutalement assassinée par une foule dirigée par des partisans de l'évêque Cyrille d'Alexandrie. Sa mort est souvent considérée comme un tournant symbolique dans le déclin de la culture païenne et de la liberté intellectuelle dans l'Empire romain. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title=" Hypatie d'Alexandrie, enseigner les maths envers et contre tout par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25546-14.01.2025-ITEMA_23980317-2025F54134E0003-NET_MFI_25ED747B-707B-4A53-94F6-7EEB0584D30D-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="I85" s="9"/>
+      <c r="J85" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K83" s="2" t="s">
+      <c r="K85" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="L83" s="2" t="s">
+      <c r="L85" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="M83" s="2" t="s">
+      <c r="M85" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="n">
         <v>365</v>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B86" s="1" t="n">
         <v>437</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="E84" s="11" t="inlineStr">
+      <c r="E86" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Syrianos" title="Wikipedia"&gt;SYRIANOS&lt;/a&gt;  est un philosophe néoplatonicien grec, chef de l’école néoplatonicienne d’Athènes après Plutarque d’Athènes et maître de Proclus. Il appartient à la génération intermédiaire qui relie Porphyre–Jamblique à Proclus, et joue un rôle central dans la structuration théologique du néoplatonisme tardif. Formé sous Plutarque d’Athènes, Syrianos en devient le successeur comme scolarque (chef d’école) à sa mort vers 432. Il enseigne à Athènes une doctrine platonicienne fortement imprégnée de pythagorisme et de théurgie, et forme plusieurs penseurs importants, dont Hermias d’Alexandrie, Proclus et, plus tard, Marinos de Néapolis. &lt;/p&gt; &lt;p&gt; Il vise à unifier la tradition orphique, pythagoricienne, platonicienne et les « Oracles chaldaïques » en une théologie harmonieuse, en montrant que tous  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2022_num_124_2_7100_t11_0584_0000_1" title="Sur les états de cause par Persée"&gt;ces courants expriment &lt;/a&gt; fondamentalement la même vérité divine. Il articule la réalité en trois niveaux : le plan intelligible (les Formes pures), le plan discursif (le niveau intermédiaire, demiurgique, où les formes agissent comme principes), le plan sensible (le monde physique). &lt;/p&gt; Il marque une étape décisive dans la « théologisation » progressive du platonisme tardif : il privilégie la théurgie (la pratique rituelle et symbolique) autant que la simple contemplation philosophique, ce qui le rapproche de Jamblique et annonce Proclus. De nombreux penseurs ultérieurs, y compris Damascios et les auteurs de la tradition arabe et médiévale, reprennent ou transforment ses idées sur la hiérarchie des principes et la structure des niveaux de réalité. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F86" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G86" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="H84" s="16" t="s">
+      <c r="H86" s="16" t="s">
         <v>697</v>
       </c>
-      <c r="J84" s="2" t="s">
+      <c r="J86" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K84" s="2" t="s">
+      <c r="K86" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L84" s="2" t="s">
+      <c r="L86" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="M84" s="2" t="s">
+      <c r="M86" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="n">
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B87" s="1" t="n">
         <v>413</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="E85" s="17" t="inlineStr">
+      <c r="E87" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Syn%C3%A9sios_de_Cyr%C3%A8ne"   title=" Wikipédia"&gt; SYNÉSIOS de Cyrène&lt;/a&gt; était un philosophe  néoplatonicien, écrivain et évêque chrétien de la fin de l’Antiquité, originaire de Cyrène dans la Cyrénaïque (actuelle Libye). Il est connu à la fois comme  &lt;a href="https://www.youtube.com/watch?v=cPXvYhOuVwc" title="Synesius of Cyrene par Sun of Antiquity"&gt;homme de lettres &lt;/a&gt; païen‑platonicien puis comme évêque de Ptolémaïs, incarnant un cas emblématique de passage entre paganisme hellénistique et christianisme tardif. &lt;/p&gt; &lt;p&gt; Il est un chrétien platonisant : il articule la tradition néoplatonicienne (Platon, Plotin, Porphyre) avec la foi chrétienne, notamment dans ses hymnes et ses traités. Dans ses Hymnes, il célèbre Dieu comme principe suprême et source de lumière, en reprenant des images platoniciennes de l’Un et du Bien, mais dans un cadre monothéiste. Dans le Traité sur les songes (vers 403), il défend l’idée que les rêves sont des oracles véritables, à condition d’être « déchiffrés » par une intelligence philosophique et morale ; il accorde une grande importance à l’imagination et à l’âme dans la communication divine. &lt;/p&gt; &lt;p&gt; Il  joue un rôle important dans la vie politique de la Cyrénaïque : il participe à une ambassade devant l’empereur à Constantinople entre 399 et 402, où il rédige notamment le Discours sur la royauté et les Récits égyptiens, des  &lt;a href="https://www.persee.fr/doc/etaf_0768-2352_1987_mon_1_1" title="Synesios de Cyrène et la Cyrénaique du bas-empire par Persée"&gt;textes allégoriques &lt;/a&gt; qui mêlent politique, philosophie et rhétorique. &lt;/p&gt; Sa correspondance (environ 150 lettres conservées) est une source précieuse sur la vie intellectuelle et religieuse de l’Antiquité tardive, les rapports entre philosophie et foi, et le rôle de personnages comme Hypatie. Il  incarne une figure de transition entre le monde païen néoplatonicien et le christianisme tardif, unissant la rigueur philosophique, l’art rhétorique et une spiritualité syncrétique très caractéristique de son époque. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F87" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G87" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="H85" s="2" t="s">
+      <c r="H87" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="J85" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K85" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="204" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="7" t="n">
-        <v>412</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>707</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="E86" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Proclus"   title="Proclus par Wikipédia"&gt;PROCLUS&lt;/a&gt; (412-485) est un philosophe &lt;a href="https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D"   title="Le Néoplatonisme par Anne Baudart"&gt;néoplatonicien grec&lt;/a&gt;, l’un des derniers grands penseurs de l’Antiquité. Né à Constantinople, il étudie à Alexandrie, puis à Athènes auprès de Syrianus, auquel il succède à la tête de l’école platonicienne : on l’appelle le « diadoque », le successeur. Il la dirige près de cinquante ans. Végétarien, très pieux, il célèbre les fêtes de tous les peuples, car le philosophe doit être, disait-il, « le prêtre du monde entier ».&lt;/p&gt; &lt;p&gt;Il laisse un grand nombre d’&lt;a href="https://remacle.org/bloodwolf/philosophes/proclus/table.htm"   title="Proclus par Philippe Remacle"&gt;ouvrages&lt;/a&gt;, dont des commentaires de Platon, sur le &lt;em&gt;Timée&lt;/em&gt;, la &lt;em&gt;République&lt;/em&gt;, le &lt;em&gt;Parménide&lt;/em&gt; ou l’&lt;em&gt;Alcibiade&lt;/em&gt;, et un commentaire du premier livre d’Euclide, précieuse source sur l’histoire de la géométrie. Dans les &lt;a href="https://www.youtube.com/watch?v=SJK1kbyXXno"   title="Les éléments de Théologie de Proclus par LabEx HaStec"&gt;&lt;em&gt;Éléments de théologie&lt;/em&gt;&lt;/a&gt;, il expose son système en 211 propositions démontrées à la manière des mathématiciens ; la &lt;em&gt;Théologie platonicienne&lt;/em&gt; le développe. Au sommet se trouve l’Un, principe absolument simple et indicible. De lui procèdent les hénades, qui sont les dieux, puis l’Intellect, l’Âme et enfin la nature et la matière. Tout se déploie selon un même rythme à trois temps : chaque réalité demeure dans sa cause, en procède, puis se retourne vers elle. L’âme humaine peut ainsi remonter vers l’Un par la philosophie, mais aussi par la théurgie, les rites qui unissent aux dieux.&lt;/p&gt; &lt;p&gt;À travers le Pseudo-Denys et le &lt;em&gt;Livre des causes&lt;/em&gt;, adaptation arabe de ses &lt;em&gt;Éléments&lt;/em&gt;, sa pensée marque le Moyen Âge, de Thomas d’Aquin à Maître Eckhart, puis Nicolas de Cues et Hegel.&lt;/p&gt;  &lt;audio controls title=" Proclus, un philosophe étoilé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>710</v>
-      </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Une vie, une œuvre" par Rien ne veut rien dire</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>712</v>
-      </c>
-      <c r="I86" s="9"/>
-      <c r="J86" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="M86" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P86">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7">
-        <v>410</v>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">470</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vers 410 – avant 470</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>716</v>
-      </c>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie" style="color:#6A142A" title="Wikipedia"&gt;HERMIAS d’Alexandrie&lt;/a&gt; est un philosophe néoplatonicien du Ve siècle, maillon important entre les écoles d’Athènes et d’Alexandrie. Né à Alexandrie, il part étudier à Athènes auprès du grand &lt;a href="https://fr.wikipedia.org/wiki/Syrianos" title="Syrianus sur Wikipedia"&gt;Syrianus&lt;/a&gt;, qui dirige alors l’école platonicienne ; il y a pour condisciple le jeune Proclus. Il épouse Aidésia, une parente de son maître, réputée pour sa culture et sa piété.&lt;/p&gt; &lt;p&gt;Revenu à Alexandrie, il y enseigne la philosophie, payé par la cité. Son seul ouvrage conservé est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes qu’il avait prises aux cours de Syrianus ; c’est le seul commentaire antique de ce dialogue qui nous soit parvenu. Le &lt;em&gt;Phèdre&lt;/em&gt; traite de l’amour, de la beauté et de l’âme, que Platon compare à un attelage ailé conduit par un cocher. Hermias en donne une lecture à la fois métaphysique et religieuse : les différentes formes de « délire » divin dont parle Socrate, prophétique, mystique, poétique et amoureux, sont autant d’étapes qui permettent à l’âme de remonter vers les dieux et vers l’Un. L’amour de la beauté sensible devient ainsi le point de départ d’une ascension spirituelle. Le philosophe Damascius le décrit comme un homme travailleur et d’une grande droiture, plus fidèle à ses maîtres qu’original.&lt;/p&gt; &lt;p&gt;Hermias meurt assez jeune. Aidésia emmène alors leurs deux fils, Ammonios et Héliodore, étudier à Athènes auprès de Proclus. Ammonios d’Alexandrie deviendra l’un des grands maîtres du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et formera à son tour toute une génération de commentateurs d’Aristote.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>718</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>719</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="I87" s="9"/>
       <c r="J87" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P87">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="88" customFormat="false" ht="204" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>722</v>
+        <v>706</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>723</v>
+        <v>707</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aid%C3%A9sia_(philosophe)" style="color:#6A142A" title="Wikipedia"&gt;AIDÉSIA&lt;/a&gt; (Ve siècle) est une philosophe néoplatonicienne d’Alexandrie, l’une des rares femmes philosophes de l’Antiquité tardive dont le souvenir nous soit parvenu. Parente du philosophe Syrianus, qui dirigeait l’école platonicienne d’Athènes, elle aurait dû épouser Proclus, son disciple, mais celui-ci, averti par un songe, renonça au mariage. Syrianus la donna alors pour épouse à un autre de ses élèves, &lt;a href="https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie" style="color:#6A142A" title="Hermias d'Alexandrie sur Wikipedia"&gt;Hermias d’Alexandrie&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Nous la connaissons par Damascius, le dernier chef de l’école d’Athènes, qui en parle dans sa &lt;em&gt;Vie d’Isidore&lt;/em&gt;. Il la décrit comme la plus belle et la plus vertueuse des femmes de son temps, connue pour sa piété envers les dieux et sa générosité envers les pauvres, au point de distribuer presque tous ses biens. Après la mort prématurée d’Hermias, elle se consacre à l’éducation de leurs deux fils, Ammonios et Héliodore. Elle les accompagne à Athènes pour qu’ils y suivent l’enseignement de Proclus, qui les accueille avec affection en souvenir de son maître. Ammonios deviendra le grand maître de l’école d’Alexandrie, où il formera à son tour de nombreux commentateurs d’Aristote, comme Jean Philopon. Aidésia vit jusqu’à un âge avancé, respectée de tous. À sa mort, le jeune Damascius, alors étudiant à Alexandrie, compose et prononce son éloge funèbre, en vers.&lt;/p&gt; &lt;p&gt;Sa vie témoigne du rôle des femmes dans les familles de philosophes néoplatoniciens, véritables dynasties intellectuelles, à l’image d’&lt;a href="https://fr.wikipedia.org/wiki/Hypatie"   title=" Wikipedia"&gt;HYPATIE d’Alexandrie&lt;/a&gt;, victime des violences religieuses en 415.&lt;/p&gt;</t>
+        <v>708</v>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Proclus"   title="Proclus par Wikipédia"&gt;PROCLUS&lt;/a&gt; (412-485) est un philosophe &lt;a href="https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D"   title="Le Néoplatonisme par Anne Baudart"&gt;néoplatonicien grec&lt;/a&gt;, l’un des derniers grands penseurs de l’Antiquité. Né à Constantinople, il étudie à Alexandrie, puis à Athènes auprès de Syrianus, auquel il succède à la tête de l’école platonicienne : on l’appelle le « diadoque », le successeur. Il la dirige près de cinquante ans. Végétarien, très pieux, il célèbre les fêtes de tous les peuples, car le philosophe doit être, disait-il, « le prêtre du monde entier ».&lt;/p&gt; &lt;p&gt;Il laisse un grand nombre d’&lt;a href="https://remacle.org/bloodwolf/philosophes/proclus/table.htm"   title="Proclus par Philippe Remacle"&gt;ouvrages&lt;/a&gt;, dont des commentaires de Platon, sur le &lt;em&gt;Timée&lt;/em&gt;, la &lt;em&gt;République&lt;/em&gt;, le &lt;em&gt;Parménide&lt;/em&gt; ou l’&lt;em&gt;Alcibiade&lt;/em&gt;, et un commentaire du premier livre d’Euclide, précieuse source sur l’histoire de la géométrie. Dans les &lt;a href="https://www.youtube.com/watch?v=SJK1kbyXXno"   title="Les éléments de Théologie de Proclus par LabEx HaStec"&gt;&lt;em&gt;Éléments de théologie&lt;/em&gt;&lt;/a&gt;, il expose son système en 211 propositions démontrées à la manière des mathématiciens ; la &lt;em&gt;Théologie platonicienne&lt;/em&gt; le développe. Au sommet se trouve l’Un, principe absolument simple et indicible. De lui procèdent les hénades, qui sont les dieux, puis l’Intellect, l’Âme et enfin la nature et la matière. Tout se déploie selon un même rythme à trois temps : chaque réalité demeure dans sa cause, en procède, puis se retourne vers elle. L’âme humaine peut ainsi remonter vers l’Un par la philosophie, mais aussi par la théurgie, les rites qui unissent aux dieux.&lt;/p&gt; &lt;p&gt;À travers le Pseudo-Denys et le &lt;em&gt;Livre des causes&lt;/em&gt;, adaptation arabe de ses &lt;em&gt;Éléments&lt;/em&gt;, sa pensée marque le Moyen Âge, de Thomas d’Aquin à Maître Eckhart, puis Nicolas de Cues et Hegel.&lt;/p&gt;  &lt;audio controls title=" Proclus, un philosophe étoilé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F88" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>727</v>
+        <v>710</v>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Une vie, une œuvre" par Rien ne veut rien dire</t>
+        </is>
       </c>
       <c r="H88" s="9" t="s">
-        <v>728</v>
+        <v>712</v>
       </c>
       <c r="I88" s="9"/>
       <c r="J88" s="2" t="s">
@@ -7394,45 +7428,47 @@
         <v>538</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
+        <v>713</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7" t="n">
-        <v>435</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>730</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>731</v>
+      <c r="P88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="7">
+        <v>410</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 410 – avant 470</t>
+        </is>
       </c>
       <c r="D89" s="8" t="s">
-        <v>732</v>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marinos_de_N%C3%A9apolis" style="color:#6A142A" title="Wikipedia"&gt;MARINOS de Néapolis&lt;/a&gt; (Ve siècle) est un philosophe néoplatonicien, disciple et successeur de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" style="color:#6A142A" title="Proclus sur Wikipedia"&gt;Proclus&lt;/a&gt; à la tête de l’école platonicienne d’Athènes. Né à Néapolis, l’actuelle Naplouse, en Palestine, dans une famille samaritaine, il abandonne la religion de ses pères pour les cultes grecs et vient étudier à Athènes. Proclus le choisit pour lui succéder, et il dirige l’école après la mort de son maître, en 485.&lt;/p&gt; &lt;p&gt;Il est surtout connu pour sa &lt;em&gt;Vie de Proclus&lt;/em&gt;, aussi intitulée &lt;em&gt;Sur le bonheur&lt;/em&gt;, écrite un an après la mort de celui-ci. Plus qu’une simple biographie, c’est un éloge construit selon l’échelle des vertus des néoplatoniciens : vertus naturelles, morales, politiques, purificatrices, contemplatives, et enfin théurgiques, qui unissent l’âme aux dieux. Marinos y montre comment Proclus les a toutes possédées, et livre de précieux détails sur la vie de l’école : l’emploi du temps du maître, qui enseignait, écrivait et priait chaque jour, son régime végétarien, ses jeûnes, ses rites et ses prières au soleil. Marinos a aussi écrit un commentaire des &lt;em&gt;Données&lt;/em&gt; d’Euclide, qui témoigne de son goût pour les mathématiques. Dans l’interprétation du &lt;em&gt;Parménide&lt;/em&gt; de Platon, il s’écarte de son maître : il y voit un dialogue sur les Idées plutôt que sur les dieux, ce que Damascius lui reprochera.&lt;/p&gt; &lt;p&gt;De santé fragile, il confie peu à peu l’enseignement à d’autres. Après lui, l’école passe à Isidore de Gaza, puis à Hégias, avant que &lt;a href="https://fr.wikipedia.org/wiki/Damascios" style="color:#6A142A" title="Damascios sur Wikipedia"&gt;Damascios&lt;/a&gt;, qui avait été son élève, n’en prenne la tête jusqu’à sa fermeture par Justinien en 529.&lt;/p&gt;</t>
+        <v>716</v>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie" style="color:#6A142A" title="Wikipedia"&gt;HERMIAS d’Alexandrie&lt;/a&gt; est un philosophe néoplatonicien du Ve siècle, maillon important entre les écoles d’Athènes et d’Alexandrie. Né à Alexandrie, il part étudier à Athènes auprès du grand &lt;a href="https://fr.wikipedia.org/wiki/Syrianos" title="Syrianus sur Wikipedia"&gt;Syrianus&lt;/a&gt;, qui dirige alors l’école platonicienne ; il y a pour condisciple le jeune Proclus. Il épouse Aidésia, une parente de son maître, réputée pour sa culture et sa piété.&lt;/p&gt; &lt;p&gt;Revenu à Alexandrie, il y enseigne la philosophie, payé par la cité. Son seul ouvrage conservé est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes qu’il avait prises aux cours de Syrianus ; c’est le seul commentaire antique de ce dialogue qui nous soit parvenu. Le &lt;em&gt;Phèdre&lt;/em&gt; traite de l’amour, de la beauté et de l’âme, que Platon compare à un attelage ailé conduit par un cocher. Hermias en donne une lecture à la fois métaphysique et religieuse : les différentes formes de « délire » divin dont parle Socrate, prophétique, mystique, poétique et amoureux, sont autant d’étapes qui permettent à l’âme de remonter vers les dieux et vers l’Un. L’amour de la beauté sensible devient ainsi le point de départ d’une ascension spirituelle. Le philosophe Damascius le décrit comme un homme travailleur et d’une grande droiture, plus fidèle à ses maîtres qu’original.&lt;/p&gt; &lt;p&gt;Hermias meurt assez jeune. Aidésia emmène alors leurs deux fils, Ammonios et Héliodore, étudier à Athènes auprès de Proclus. Ammonios d’Alexandrie deviendra l’un des grands maîtres du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et formera à son tour toute une génération de commentateurs d’Aristote.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F89" s="7" t="s">
-        <v>734</v>
+        <v>718</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="H89" s="12" t="s">
-        <v>736</v>
+        <v>719</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>720</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="2" t="s">
@@ -7445,53 +7481,61 @@
         <v>538</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="90" customFormat="false" ht="119.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>739</v>
+        <v>723</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="E90" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)"  style="color:#6A142A"  title=" Wikipedia"&gt;AMMONIOS d’Alexandrie&lt;/a&gt; (vers 440-vers 520) est un philosophe néoplatonicien, le grand maître de l’école d’Alexandrie à la fin de l’Antiquité. Fils des philosophes Hermias et Aidésia, il est emmené jeune à Athènes par sa mère pour y suivre l’enseignement de Proclus, qui dirige l’école platonicienne. Revenu dans sa ville natale, il y enseigne pendant plusieurs décennies, à la tête de l’école d’Alexandrie, tandis que celle d’Athènes est dirigée par les successeurs de Proclus.&lt;/p&gt; &lt;p&gt;Ammonios est avant tout un commentateur d’Aristote. Il considère que la philosophie d’Aristote et celle de Platon s’accordent sur l’essentiel : l’étude d’Aristote, à commencer par sa logique, prépare à celle de Platon, qui conduit jusqu’à la connaissance du divin. Son commentaire du traité &lt;em&gt;De l’interprétation&lt;/em&gt;, qui examine les propositions, la vérité et le temps, nous est parvenu en entier ; on y trouve une discussion célèbre sur les futurs contingents : peut-on dire dès aujourd’hui qu’une bataille navale aura lieu demain, sans supprimer la liberté ? Ses autres leçons nous sont connues par les notes de ses élèves. Il forme en effet toute une génération de commentateurs : Jean Philopon, chrétien, Simplicius, Asclépius et Olympiodore. Dans une ville où les chrétiens sont désormais majoritaires et où les païens sont parfois persécutés, il aurait conclu un accord avec les autorités chrétiennes pour pouvoir continuer à enseigner, ce que lui reprocha Damascius.&lt;/p&gt; &lt;p&gt;L’école d’Alexandrie, en partie chrétienne après lui, a transmis le corpus d’Aristote et ses commentaires aux savants syriaques et arabes, puis à l’Occident médiéval.&lt;/p&gt;</t>
+        <v>724</v>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aid%C3%A9sia_(philosophe)" style="color:#6A142A" title="Wikipedia"&gt;AIDÉSIA&lt;/a&gt; (Ve siècle) est une philosophe néoplatonicienne d’Alexandrie, l’une des rares femmes philosophes de l’Antiquité tardive dont le souvenir nous soit parvenu. Parente du philosophe Syrianus, qui dirigeait l’école platonicienne d’Athènes, elle aurait dû épouser Proclus, son disciple, mais celui-ci, averti par un songe, renonça au mariage. Syrianus la donna alors pour épouse à un autre de ses élèves, &lt;a href="https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie" style="color:#6A142A" title="Hermias d'Alexandrie sur Wikipedia"&gt;Hermias d’Alexandrie&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Nous la connaissons par Damascius, le dernier chef de l’école d’Athènes, qui en parle dans sa &lt;em&gt;Vie d’Isidore&lt;/em&gt;. Il la décrit comme la plus belle et la plus vertueuse des femmes de son temps, connue pour sa piété envers les dieux et sa générosité envers les pauvres, au point de distribuer presque tous ses biens. Après la mort prématurée d’Hermias, elle se consacre à l’éducation de leurs deux fils, Ammonios et Héliodore. Elle les accompagne à Athènes pour qu’ils y suivent l’enseignement de Proclus, qui les accueille avec affection en souvenir de son maître. Ammonios deviendra le grand maître de l’école d’Alexandrie, où il formera à son tour de nombreux commentateurs d’Aristote, comme Jean Philopon. Aidésia vit jusqu’à un âge avancé, respectée de tous. À sa mort, le jeune Damascius, alors étudiant à Alexandrie, compose et prononce son éloge funèbre, en vers.&lt;/p&gt; &lt;p&gt;Sa vie témoigne du rôle des femmes dans les familles de philosophes néoplatoniciens, véritables dynasties intellectuelles, à l’image d’&lt;a href="https://fr.wikipedia.org/wiki/Hypatie"   title=" Wikipedia"&gt;HYPATIE d’Alexandrie&lt;/a&gt;, victime des violences religieuses en 415.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F90" s="7" t="s">
-        <v>742</v>
-      </c>
-      <c r="G90" s="15" t="s">
-        <v>743</v>
+        <v>726</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>727</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>745</v>
+        <v>729</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -7499,32 +7543,32 @@
         </is>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="n">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>746</v>
+        <v>730</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="E91" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isidore_de_Gaza" title="Wikipedia"&gt;ISIDORE de Gaza&lt;/a&gt; (Ve-VIe siècle) est un philosophe néoplatonicien, l’un des derniers représentants du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme"  title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; païen. Né à Gaza, il étudie à Alexandrie, puis à Athènes auprès de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" title="Proclus sur Wikipedia"&gt;Proclus&lt;/a&gt;, qui dirige l’école platonicienne. Il est le maître et l’ami de &lt;a href="https://fr.wikipedia.org/wiki/Damascios" title="Damascios sur Wikipedia"&gt;Damascius&lt;/a&gt;, le dernier chef de cette école.&lt;/p&gt; &lt;p&gt;Nous le connaissons surtout par la biographie que Damascius lui a consacrée, la &lt;em&gt;Vie d’Isidore&lt;/em&gt;, dont il reste d’importants fragments. Il y apparaît comme un homme profondément religieux, attaché aux cultes et aux traditions des Grecs à une époque où le christianisme est devenu la religion de l’Empire et où les païens sont de plus en plus surveillés. Isidore se méfie des longs commentaires savants et des raisonnements trop subtils : pour lui, la philosophie est avant tout une manière de vivre, une purification de l’âme qui la conduit vers le divin. Il préfère l’inspiration et l’expérience intérieure à l’érudition, et Damascius admire en lui moins le savant que le sage. Après la mort de Proclus, il voyage beaucoup, en Syrie et en Égypte, en compagnie de Damascius. Il accepte un temps de diriger l’école d’Athènes, à la suite de Marinus, mais y renonce bientôt, jugeant le climat défavorable à la philosophie. La &lt;em&gt;Vie d’Isidore&lt;/em&gt; est aussi une précieuse galerie de portraits des philosophes de son temps, comme Hypatie, Aidésia ou Hermias.&lt;/p&gt; &lt;p&gt;Peu après, en 529, l’empereur Justinien interdit aux païens d’enseigner : l’école d’Athènes ferme, et Damascius part avec quelques compagnons en Perse.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F91" s="18" t="s">
-        <v>750</v>
-      </c>
-      <c r="G91" s="15" t="s">
-        <v>751</v>
+        <v>732</v>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marinos_de_N%C3%A9apolis" style="color:#6A142A" title="Wikipedia"&gt;MARINOS de Néapolis&lt;/a&gt; (Ve siècle) est un philosophe néoplatonicien, disciple et successeur de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" style="color:#6A142A" title="Proclus sur Wikipedia"&gt;Proclus&lt;/a&gt; à la tête de l’école platonicienne d’Athènes. Né à Néapolis, l’actuelle Naplouse, en Palestine, dans une famille samaritaine, il abandonne la religion de ses pères pour les cultes grecs et vient étudier à Athènes. Proclus le choisit pour lui succéder, et il dirige l’école après la mort de son maître, en 485.&lt;/p&gt; &lt;p&gt;Il est surtout connu pour sa &lt;em&gt;Vie de Proclus&lt;/em&gt;, aussi intitulée &lt;em&gt;Sur le bonheur&lt;/em&gt;, écrite un an après la mort de celui-ci. Plus qu’une simple biographie, c’est un éloge construit selon l’échelle des vertus des néoplatoniciens : vertus naturelles, morales, politiques, purificatrices, contemplatives, et enfin théurgiques, qui unissent l’âme aux dieux. Marinos y montre comment Proclus les a toutes possédées, et livre de précieux détails sur la vie de l’école : l’emploi du temps du maître, qui enseignait, écrivait et priait chaque jour, son régime végétarien, ses jeûnes, ses rites et ses prières au soleil. Marinos a aussi écrit un commentaire des &lt;em&gt;Données&lt;/em&gt; d’Euclide, qui témoigne de son goût pour les mathématiques. Dans l’interprétation du &lt;em&gt;Parménide&lt;/em&gt; de Platon, il s’écarte de son maître : il y voit un dialogue sur les Idées plutôt que sur les dieux, ce que Damascius lui reprochera.&lt;/p&gt; &lt;p&gt;De santé fragile, il confie peu à peu l’enseignement à d’autres. Après lui, l’école passe à Isidore de Gaza, puis à Hégias, avant que &lt;a href="https://fr.wikipedia.org/wiki/Damascios" style="color:#6A142A" title="Damascios sur Wikipedia"&gt;Damascios&lt;/a&gt;, qui avait été son élève, n’en prenne la tête jusqu’à sa fermeture par Justinien en 529.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>735</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>697</v>
+        <v>736</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="2" t="s">
@@ -7537,7 +7581,7 @@
         <v>538</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -7545,94 +7589,91 @@
         </is>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="119.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>755</v>
-      </c>
-      <c r="E92" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Damascios" style="color:#6A142A" title="Wikipedia"&gt;DAMASCIOS   le Diadoque&lt;/a&gt;, né à Damas fut le dernier scholarque de l'Académie platonicienne d'Athènes,   Élève de Marinos de Néapolis et d'Isidore d'Alexandrie, il succéda à ce dernier comme scholarchos vers 515, jusqu'à la fermeture de l'école par l'empereur Justinien en 529. Philosophe néoplatonicien d'une érudition exceptionnelle, il incarne la résistance de la pensée grecque face au triomphe du christianisme.&lt;/p&gt; &lt;p&gt;Disciple d'Isidore de Gaza et d'autres maîtres alexandrins, il dirigea l'École d'Athènes et rédigea des œuvres d'une grande complexité spéculative, notamment les &lt;em&gt;Problèmes et Solutions concernant les Premiers Principes&lt;/em&gt; et un commentaire sur le &lt;em&gt;Parménide&lt;/em&gt; de Platon.   Auteur de la Vie d'Isidore (biographie philosophique et critique du christianisme), du Traité des premiers principes (sur l'ontologie), de commentaires sur le Parménide de Platon et les Chaldaica, ses écrits préservent la tradition néoplatonicienne tardive. &lt;/p&gt; &lt;p&gt;   Il poussa la dialectique néoplatonicienne jusqu'à ses limites, affirmant que le Premier Principe — l'Un — est absolument ineffable, au-delà de toute pensée et de tout être.&lt;/p&gt; &lt;p&gt;Après la fermeture de l'Académie, Damascios s'exila en Perse avec Simplicius et d'autres philosophes, à la cour du roi sassanide Khosrô Ier. Il représente la fin d'une époque : la clôture du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; antique, dont il fut l'un des penseurs les plus profonds et les plus radicaux.&lt;/p&gt; Critiquant Proclus, Damascios dépassa l'Un-Bien pour poser un principe ineffable (to aprorrhēton), absolu et sans relation, au-delà de toute connaissance. Son ontologie distingue l'Ineffable, l'Un, l'Intellect et l'Âme, influençant les théologies apophatiques ultérieures. &lt;/p&gt;</t>
+        <v>740</v>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)"  style="color:#6A142A"  title=" Wikipedia"&gt;AMMONIOS d’Alexandrie&lt;/a&gt; (vers 440-vers 520) est un philosophe néoplatonicien, le grand maître de l’école d’Alexandrie à la fin de l’Antiquité. Fils des philosophes Hermias et Aidésia, il est emmené jeune à Athènes par sa mère pour y suivre l’enseignement de Proclus, qui dirige l’école platonicienne. Revenu dans sa ville natale, il y enseigne pendant plusieurs décennies, à la tête de l’école d’Alexandrie, tandis que celle d’Athènes est dirigée par les successeurs de Proclus.&lt;/p&gt; &lt;p&gt;Ammonios est avant tout un commentateur d’Aristote. Il considère que la philosophie d’Aristote et celle de Platon s’accordent sur l’essentiel : l’étude d’Aristote, à commencer par sa logique, prépare à celle de Platon, qui conduit jusqu’à la connaissance du divin. Son commentaire du traité &lt;em&gt;De l’interprétation&lt;/em&gt;, qui examine les propositions, la vérité et le temps, nous est parvenu en entier ; on y trouve une discussion célèbre sur les futurs contingents : peut-on dire dès aujourd’hui qu’une bataille navale aura lieu demain, sans supprimer la liberté ? Ses autres leçons nous sont connues par les notes de ses élèves. Il forme en effet toute une génération de commentateurs : Jean Philopon, chrétien, Simplicius, Asclépius et Olympiodore. Dans une ville où les chrétiens sont désormais majoritaires et où les païens sont parfois persécutés, il aurait conclu un accord avec les autorités chrétiennes pour pouvoir continuer à enseigner, ce que lui reprocha Damascius.&lt;/p&gt; &lt;p&gt;L’école d’Alexandrie, en partie chrétienne après lui, a transmis le corpus d’Aristote et ses commentaires aux savants syriaques et arabes, puis à l’Occident médiéval.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F92" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>758</v>
+        <v>742</v>
+      </c>
+      <c r="G92" s="15" t="s">
+        <v>743</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="I92" s="9"/>
       <c r="J92" s="2" t="s">
-        <v>636</v>
+        <v>23</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>759</v>
+        <v>745</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="93" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bo%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;Anicius Manlius BOÈCE&lt;/a&gt; (vers 480-524) est un philosophe, théologien et homme d’État romain, souvent appelé « le dernier des Romains et le premier des scolastiques ». Issu de l’une des plus grandes familles de Rome, il vit sous le règne de Théodoric, roi des Ostrogoths, qui gouverne l’Italie : il devient consul en 510, puis maître des offices, la plus haute charge de la cour.&lt;/p&gt; &lt;p&gt;Chrétien et passionné de philosophie grecque, il conçoit un projet immense : traduire en latin toutes les œuvres de Platon et d’Aristote, pour montrer qu’ils s’accordent sur l’essentiel. Il n’a pu en réaliser qu’une partie : la logique d’Aristote et l’&lt;em&gt;Introduction&lt;/em&gt; de Porphyre. Ces traductions seront, pendant six siècles, presque la seule philosophie grecque connue en Occident, et l’une de ses questions, celle de la nature des universaux, lancera la grande querelle médiévale. Il écrit aussi des manuels d’arithmétique et de musique, et de courts traités de théologie, où il définit la personne comme « une substance individuelle de nature raisonnable ». Accusé de trahison pour avoir défendu un sénateur, il est emprisonné à Pavie, puis exécuté en 524. En prison, il écrit &lt;a  href="https://remacle.org/bloodwolf/philosophes/boece/livre3.htm#:~:text=J'entends%20par%20l%C3%A0%20ce,aurait%20encore%20mati%C3%A8re%20%C3%A0%20d%C3%A9sir." style="color:#88A1E9"  title="La consolation philosophique par Remacle"&gt;&lt;em&gt;La Consolation de Philosophie&lt;/em&gt;&lt;/a&gt;. La Philosophie lui apparaît sous les traits d’une femme majestueuse et lui montre que la Fortune, avec sa roue, donne et reprend tout : le vrai bonheur n’est pas dans les richesses ou le pouvoir, mais dans &lt;a  href="https://www.youtube.com/watch?v=Bx-_WsSfylw&amp;t=1619s&amp;ab_channel=%C3%89CLAIRBRUT" style="color:#88A1E9"  title="Une âme dénuée du monde par Eclair Brut"&gt;la sagesse&lt;/a&gt; et en Dieu, le bien suprême. Dieu, éternel, voit tout l’avenir comme un présent, sans supprimer notre liberté.&lt;/p&gt; &lt;p&gt;La &lt;em&gt;Consolation&lt;/em&gt; fut l’un des livres les plus influents de la culture européenne.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>764</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>765</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>766</v>
+        <v>748</v>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isidore_de_Gaza" title="Wikipedia"&gt;ISIDORE de Gaza&lt;/a&gt; (Ve-VIe siècle) est un philosophe néoplatonicien, l’un des derniers représentants du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme"  title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; païen. Né à Gaza, il étudie à Alexandrie, puis à Athènes auprès de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" title="Proclus sur Wikipedia"&gt;Proclus&lt;/a&gt;, qui dirige l’école platonicienne. Il est le maître et l’ami de &lt;a href="https://fr.wikipedia.org/wiki/Damascios" title="Damascios sur Wikipedia"&gt;Damascius&lt;/a&gt;, le dernier chef de cette école.&lt;/p&gt; &lt;p&gt;Nous le connaissons surtout par la biographie que Damascius lui a consacrée, la &lt;em&gt;Vie d’Isidore&lt;/em&gt;, dont il reste d’importants fragments. Il y apparaît comme un homme profondément religieux, attaché aux cultes et aux traditions des Grecs à une époque où le christianisme est devenu la religion de l’Empire et où les païens sont de plus en plus surveillés. Isidore se méfie des longs commentaires savants et des raisonnements trop subtils : pour lui, la philosophie est avant tout une manière de vivre, une purification de l’âme qui la conduit vers le divin. Il préfère l’inspiration et l’expérience intérieure à l’érudition, et Damascius admire en lui moins le savant que le sage. Après la mort de Proclus, il voyage beaucoup, en Syrie et en Égypte, en compagnie de Damascius. Il accepte un temps de diriger l’école d’Athènes, à la suite de Marinus, mais y renonce bientôt, jugeant le climat défavorable à la philosophie. La &lt;em&gt;Vie d’Isidore&lt;/em&gt; est aussi une précieuse galerie de portraits des philosophes de son temps, comme Hypatie, Aidésia ou Hermias.&lt;/p&gt; &lt;p&gt;Peu après, en 529, l’empereur Justinien interdit aux païens d’enseigner : l’école d’Athènes ferme, et Damascius part avec quelques compagnons en Perse.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="s">
+        <v>750</v>
+      </c>
+      <c r="G93" s="15" t="s">
+        <v>751</v>
+      </c>
+      <c r="H93" s="12" t="s">
+        <v>697</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="2" t="s">
-        <v>512</v>
+        <v>23</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>767</v>
+        <v>538</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -7640,45 +7681,45 @@
         </is>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>769</v>
+        <v>753</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="E94" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hermias_de_Ph%C3%A9nicie" style="color:#6A142A" title="Wikipedia"&gt;HERMIAS de Phénicie&lt;/a&gt; est un philosophe néoplatonicien du VIe siècle, membre de l’école d’Athènes à l’époque où elle est dirigée par Damascius. Nous ne savons presque rien de lui, sinon sa participation à l’un des épisodes les plus célèbres de la fin de la philosophie antique : l’exil des derniers philosophes païens en Perse.&lt;/p&gt; &lt;p&gt;En 529, l’empereur chrétien Justinien interdit aux païens d’enseigner et d’occuper des fonctions publiques. L’école platonicienne d’Athènes, héritière de l’Académie de Platon, ne peut plus fonctionner, et ses biens sont menacés. Vers 531, sept philosophes décident de quitter l’Empire : Damascius, Simplicius de Cilicie, Priscien de Lydie, Eulamios de Phrygie, Isidore de Gaza, Diogène de Phénicie et Hermias, son compatriote. Ils se rendent à la cour du roi sassanide &lt;a href="https://fr.wikipedia.org/wiki/Khosro_Ier" title=" Wikipedia"&gt;Khosro Ier&lt;/a&gt;, réputé ami de la philosophie, qui faisait traduire Platon et Aristote. L’historien byzantin Agathias, qui raconte leur voyage, les appelle « la fleur la plus noble des philosophes de notre temps ». Mais la Perse les déçoit : ils y trouvent l’injustice et des mœurs qui les choquent, et le roi lui-même leur paraît moins philosophe qu’on ne le disait. En 532, le traité de paix entre Khosro et Justinien prévoit qu’ils pourront rentrer dans l’Empire sans être forcés de renoncer à leurs croyances.&lt;/p&gt; &lt;p&gt;Aucune œuvre d’Hermias ne nous est parvenue. On ignore où les exilés finirent leur vie ; certains historiens pensent qu’une partie d’entre eux s’installa à Harran, aux confins de l’Empire, où la tradition platonicienne se serait maintenue jusqu’à l’époque islamique.&lt;/p&gt;</t>
+        <v>755</v>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Damascios" style="color:#6A142A" title="Wikipedia"&gt;DAMASCIOS   le Diadoque&lt;/a&gt;, né à Damas fut le dernier scholarque de l'Académie platonicienne d'Athènes,   Élève de Marinos de Néapolis et d'Isidore d'Alexandrie, il succéda à ce dernier comme scholarchos vers 515, jusqu'à la fermeture de l'école par l'empereur Justinien en 529. Philosophe néoplatonicien d'une érudition exceptionnelle, il incarne la résistance de la pensée grecque face au triomphe du christianisme.&lt;/p&gt; &lt;p&gt;Disciple d'Isidore de Gaza et d'autres maîtres alexandrins, il dirigea l'École d'Athènes et rédigea des œuvres d'une grande complexité spéculative, notamment les &lt;em&gt;Problèmes et Solutions concernant les Premiers Principes&lt;/em&gt; et un commentaire sur le &lt;em&gt;Parménide&lt;/em&gt; de Platon.   Auteur de la Vie d'Isidore (biographie philosophique et critique du christianisme), du Traité des premiers principes (sur l'ontologie), de commentaires sur le Parménide de Platon et les Chaldaica, ses écrits préservent la tradition néoplatonicienne tardive. &lt;/p&gt; &lt;p&gt;   Il poussa la dialectique néoplatonicienne jusqu'à ses limites, affirmant que le Premier Principe — l'Un — est absolument ineffable, au-delà de toute pensée et de tout être.&lt;/p&gt; &lt;p&gt;Après la fermeture de l'Académie, Damascios s'exila en Perse avec Simplicius et d'autres philosophes, à la cour du roi sassanide Khosrô Ier. Il représente la fin d'une époque : la clôture du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; antique, dont il fut l'un des penseurs les plus profonds et les plus radicaux.&lt;/p&gt; Critiquant Proclus, Damascios dépassa l'Un-Bien pour poser un principe ineffable (to aprorrhēton), absolu et sans relation, au-delà de toute connaissance. Son ontologie distingue l'Ineffable, l'Un, l'Intellect et l'Âme, influençant les théologies apophatiques ultérieures. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F94" s="7" t="s">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>774</v>
-      </c>
-      <c r="H94" s="12" t="s">
-        <v>697</v>
+        <v>758</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>736</v>
       </c>
       <c r="I94" s="9"/>
       <c r="J94" s="2" t="s">
-        <v>23</v>
+        <v>636</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -7689,45 +7730,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
         <v>480</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>778</v>
-      </c>
-      <c r="E95" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Simplicius_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698" style="color:#88A1E9" title="A propos de la biographie de Simplicius par Persée"&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le "Manuel d’Épictète" et, selon la tradition, sur "De l’âme". Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href="https://www.youtube.com/watch?v=C17VYcyLkiY" style="color:#88A1E9" title="SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions"&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.   Transmis et traduits dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; </t>
+        <v>762</v>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bo%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;Anicius Manlius BOÈCE&lt;/a&gt; (vers 480-524) est un philosophe, théologien et homme d’État romain, souvent appelé « le dernier des Romains et le premier des scolastiques ». Issu de l’une des plus grandes familles de Rome, il vit sous le règne de Théodoric, roi des Ostrogoths, qui gouverne l’Italie : il devient consul en 510, puis maître des offices, la plus haute charge de la cour.&lt;/p&gt; &lt;p&gt;Chrétien et passionné de philosophie grecque, il conçoit un projet immense : traduire en latin toutes les œuvres de Platon et d’Aristote, pour montrer qu’ils s’accordent sur l’essentiel. Il n’a pu en réaliser qu’une partie : la logique d’Aristote et l’&lt;em&gt;Introduction&lt;/em&gt; de Porphyre. Ces traductions seront, pendant six siècles, presque la seule philosophie grecque connue en Occident, et l’une de ses questions, celle de la nature des universaux, lancera la grande querelle médiévale. Il écrit aussi des manuels d’arithmétique et de musique, et de courts traités de théologie, où il définit la personne comme « une substance individuelle de nature raisonnable ». Accusé de trahison pour avoir défendu un sénateur, il est emprisonné à Pavie, puis exécuté en 524. En prison, il écrit &lt;a  href="https://remacle.org/bloodwolf/philosophes/boece/livre3.htm#:~:text=J'entends%20par%20l%C3%A0%20ce,aurait%20encore%20mati%C3%A8re%20%C3%A0%20d%C3%A9sir." style="color:#88A1E9"  title="La consolation philosophique par Remacle"&gt;&lt;em&gt;La Consolation de Philosophie&lt;/em&gt;&lt;/a&gt;. La Philosophie lui apparaît sous les traits d’une femme majestueuse et lui montre que la Fortune, avec sa roue, donne et reprend tout : le vrai bonheur n’est pas dans les richesses ou le pouvoir, mais dans &lt;a  href="https://www.youtube.com/watch?v=Bx-_WsSfylw&amp;t=1619s&amp;ab_channel=%C3%89CLAIRBRUT" style="color:#88A1E9"  title="Une âme dénuée du monde par Eclair Brut"&gt;la sagesse&lt;/a&gt; et en Dieu, le bien suprême. Dieu, éternel, voit tout l’avenir comme un présent, sans supprimer notre liberté.&lt;/p&gt; &lt;p&gt;La &lt;em&gt;Consolation&lt;/em&gt; fut l’un des livres les plus influents de la culture européenne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F95" s="7" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>538</v>
+        <v>767</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -7735,78 +7776,81 @@
         </is>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>786</v>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cassiodore"  style="color:#6A142A"  title=" Wikipedia"&gt;CASSIODORE&lt;/a&gt; (vers 485-580) est un homme d’État, écrivain et savant romain, l’un des grands passeurs de la culture antique au Moyen Âge. Issu d’une famille de hauts fonctionnaires du sud de l’Italie, il fait carrière au service des rois ostrogoths qui gouvernent alors l’Italie, en particulier Théodoric le Grand : il devient consul, puis préfet du prétoire. Ses lettres officielles, réunies dans les &lt;em&gt;Variae&lt;/em&gt; en douze livres, sont une source précieuse sur l’époque.&lt;/p&gt; &lt;p&gt;Il veut concilier les Romains et les Goths, et écrit à cette fin une &lt;em&gt;Histoire des Goths&lt;/em&gt;, aujourd’hui perdue. Après la reconquête de l’Italie par l’empereur Justinien et la ruine de son projet politique, il se retire vers 554 sur ses terres de Calabre, où il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Monast%C3%A8re_de_Vivarium"  style="color:#88A1E9"  title="le monastère de Vivarium par Wikipédia"&gt;monastère de Vivarium&lt;/a&gt;, ainsi nommé à cause de ses viviers à poissons. Il y rassemble une riche bibliothèque et demande aux moines de copier avec soin les manuscrits, chrétiens mais aussi païens, en les corrigeant et en les reliant : le travail du copiste devient une œuvre spirituelle. Pour les guider, il écrit les &lt;a href="https://www.persee.fr/doc/rht_0373-6075_1991_num_21_1991_1362"  style="color:#88A1E9"  title="les Institutions par Persée.fr"&gt;&lt;em&gt;Institutions&lt;/em&gt;&lt;/a&gt;, en deux livres : le premier présente l’étude de la Bible et des Pères de l’Église ; le second résume les sept arts libéraux, la grammaire, la rhétorique, la dialectique, l’arithmétique, la musique, la géométrie et l’astronomie, nécessaires pour bien lire l’Écriture. Il compose aussi un traité &lt;em&gt;De l’âme&lt;/em&gt; et un grand commentaire des Psaumes.&lt;/p&gt; &lt;p&gt;Grâce à lui, le modèle du monastère gardien des livres s’impose en Occident. Les &lt;em&gt;Institutions&lt;/em&gt; serviront de programme d’études pendant tout le Moyen Âge.&lt;/p&gt;</t>
+        <v>771</v>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hermias_de_Ph%C3%A9nicie" style="color:#6A142A" title="Wikipedia"&gt;HERMIAS de Phénicie&lt;/a&gt; est un philosophe néoplatonicien du VIe siècle, membre de l’école d’Athènes à l’époque où elle est dirigée par Damascius. Nous ne savons presque rien de lui, sinon sa participation à l’un des épisodes les plus célèbres de la fin de la philosophie antique : l’exil des derniers philosophes païens en Perse.&lt;/p&gt; &lt;p&gt;En 529, l’empereur chrétien Justinien interdit aux païens d’enseigner et d’occuper des fonctions publiques. L’école platonicienne d’Athènes, héritière de l’Académie de Platon, ne peut plus fonctionner, et ses biens sont menacés. Vers 531, sept philosophes décident de quitter l’Empire : Damascius, Simplicius de Cilicie, Priscien de Lydie, Eulamios de Phrygie, Isidore de Gaza, Diogène de Phénicie et Hermias, son compatriote. Ils se rendent à la cour du roi sassanide &lt;a href="https://fr.wikipedia.org/wiki/Khosro_Ier" title=" Wikipedia"&gt;Khosro Ier&lt;/a&gt;, réputé ami de la philosophie, qui faisait traduire Platon et Aristote. L’historien byzantin Agathias, qui raconte leur voyage, les appelle « la fleur la plus noble des philosophes de notre temps ». Mais la Perse les déçoit : ils y trouvent l’injustice et des mœurs qui les choquent, et le roi lui-même leur paraît moins philosophe qu’on ne le disait. En 532, le traité de paix entre Khosro et Justinien prévoit qu’ils pourront rentrer dans l’Empire sans être forcés de renoncer à leurs croyances.&lt;/p&gt; &lt;p&gt;Aucune œuvre d’Hermias ne nous est parvenue. On ignore où les exilés finirent leur vie ; certains historiens pensent qu’une partie d’entre eux s’installa à Harran, aux confins de l’Empire, où la tradition platonicienne se serait maintenue jusqu’à l’époque islamique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F96" s="7" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="H96" s="9" t="s">
-        <v>790</v>
+        <v>774</v>
+      </c>
+      <c r="H96" s="12" t="s">
+        <v>697</v>
       </c>
       <c r="I96" s="9"/>
       <c r="J96" s="2" t="s">
-        <v>512</v>
+        <v>23</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>252</v>
+        <v>59</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>662</v>
+        <v>538</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>794</v>
-      </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Philopon" style="color:#6A142A" title="Wikipedia"&gt;Jean PHILOPON&lt;/a&gt; fut l'un des penseurs les plus novateurs de l'Antiquité tardive. Philosophe et théologien chrétien monophysite d'Alexandrie, disciple d'Ammonios fils d'Hermias, il est célèbre pour ses vastes commentaires des œuvres d'&lt;a href="https://fr.wikipedia.org/wiki/Aristote" style="color:#6A142A" title="Aristote sur Wikipedia"&gt;Aristote&lt;/a&gt;, qu'il soumit à une critique audacieuse au nom de la physique et de la foi chrétienne.&lt;/p&gt; &lt;p&gt;  Il est un des premiers grands commentateurs d’Aristote en grec, mais il s’en distingue nettement sur des questions comme l’éternité du monde. Dans ses traités Contre Proclus (529) et De la création du monde, il défend l’idée que le monde a été créé ex nihilo dans le temps, ce qui l’oppose à la conception aristotélicienne d’un univers éternel, affirmant que le cosmos fut créé à partir du néant — en accord avec le dogme chrétien. Il développa également la théorie de l'&lt;em&gt;impetus&lt;/em&gt;, ancêtre du concept d'inertie : un projectile lancé reçoit une force interne qui le maintient en mouvement, préfigurant ainsi la physique galiléenne six siècles avant Galilée.&lt;/p&gt; &lt;p&gt;       Sur le plan théologique, il soutient une lecture allégorique de la Bible et cherche à harmoniser Platon, Aristote et Ptolémée avec la cosmologie chrétienne, en s’opposant notamment à la vision « étagée » du monde de Cosmas Indicopleustès. Il se rapproche d’abord du monophysisme, puis adhère au courant dit « trithéite » (tendance au sein du christianisme oriental qui insiste sur la distinction des trois personnes divines), ce qui lui vaudra une condamnation par certains milieux orthodoxes et monophysites.   &lt;/p&gt; &lt;p&gt; Il est une figure de carrefour entre philosophie grecque et théologie chrétienne. Sa lecture critique d'Aristote, qu'il commentait tout en le contestant, influença profondément les penseurs arabes médiévaux et, via eux, la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_scientifique" style="color:#6A142A" title="Révolution scientifique sur Wikipedia"&gt;révolution scientifique&lt;/a&gt; de la Renaissance. Il fut condamné pour hérésie (trithéisme) mais son héritage philosophique demeure immense.&lt;/p&gt;</t>
+        <v>778</v>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Simplicius_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698" style="color:#88A1E9" title="A propos de la biographie de Simplicius par Persée"&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le "Manuel d’Épictète" et, selon la tradition, sur "De l’âme". Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href="https://www.youtube.com/watch?v=C17VYcyLkiY" style="color:#88A1E9" title="SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions"&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.   Transmis et traduits dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F97" s="7" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="I97" s="9"/>
       <c r="J97" s="2" t="s">
@@ -7819,7 +7863,7 @@
         <v>538</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -7827,45 +7871,45 @@
         </is>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>802</v>
-      </c>
-      <c r="E98" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Priscien_de_Lydie" style="color:#6A142A" title="Wikipedia"&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href="https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316" title="la géographie et les originesnéoplatonisme sur Persee"&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité : « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;</t>
+        <v>786</v>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cassiodore"  style="color:#6A142A"  title=" Wikipedia"&gt;CASSIODORE&lt;/a&gt; (vers 485-580) est un homme d’État, écrivain et savant romain, l’un des grands passeurs de la culture antique au Moyen Âge. Issu d’une famille de hauts fonctionnaires du sud de l’Italie, il fait carrière au service des rois ostrogoths qui gouvernent alors l’Italie, en particulier Théodoric le Grand : il devient consul, puis préfet du prétoire. Ses lettres officielles, réunies dans les &lt;em&gt;Variae&lt;/em&gt; en douze livres, sont une source précieuse sur l’époque.&lt;/p&gt; &lt;p&gt;Il veut concilier les Romains et les Goths, et écrit à cette fin une &lt;em&gt;Histoire des Goths&lt;/em&gt;, aujourd’hui perdue. Après la reconquête de l’Italie par l’empereur Justinien et la ruine de son projet politique, il se retire vers 554 sur ses terres de Calabre, où il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Monast%C3%A8re_de_Vivarium"  style="color:#88A1E9"  title="le monastère de Vivarium par Wikipédia"&gt;monastère de Vivarium&lt;/a&gt;, ainsi nommé à cause de ses viviers à poissons. Il y rassemble une riche bibliothèque et demande aux moines de copier avec soin les manuscrits, chrétiens mais aussi païens, en les corrigeant et en les reliant : le travail du copiste devient une œuvre spirituelle. Pour les guider, il écrit les &lt;a href="https://www.persee.fr/doc/rht_0373-6075_1991_num_21_1991_1362"  style="color:#88A1E9"  title="les Institutions par Persée.fr"&gt;&lt;em&gt;Institutions&lt;/em&gt;&lt;/a&gt;, en deux livres : le premier présente l’étude de la Bible et des Pères de l’Église ; le second résume les sept arts libéraux, la grammaire, la rhétorique, la dialectique, l’arithmétique, la musique, la géométrie et l’astronomie, nécessaires pour bien lire l’Écriture. Il compose aussi un traité &lt;em&gt;De l’âme&lt;/em&gt; et un grand commentaire des Psaumes.&lt;/p&gt; &lt;p&gt;Grâce à lui, le modèle du monastère gardien des livres s’impose en Occident. Les &lt;em&gt;Institutions&lt;/em&gt; serviront de programme d’études pendant tout le Moyen Âge.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F98" s="7" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>697</v>
+        <v>790</v>
       </c>
       <c r="I98" s="9"/>
       <c r="J98" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>59</v>
+        <v>252</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>538</v>
+        <v>662</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>806</v>
+        <v>791</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -7873,45 +7917,45 @@
         </is>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympiodore_le_Jeune"  style="color:#6A142A"  title=" Wikipedia"&gt;OLYMPIODORE le Jeune&lt;/a&gt; était un philosophe néoplatonicien grec connu comme grand commentateur de Platon et d’Aristote, dernier représentant important de la tradition platonicienne païenne à Alexandrie. &lt;/p&gt; &lt;p&gt; Il laisse surtout des commentaires sur des dialogues de Platon : Phédon, Gorgias, Philebos et &lt;a href="https://www.youtube.com/watch?v=KauBLoVOcNs" style="color:#88A1E9" title=" hat is philosophy? Olympiodorus' Commentary on the First Alcibiades par Abbas the Alchemist"&gt;l’Alcibiade&lt;/a&gt;. Il commente également Aristote et compose une introduction à la philosophie aristotélicienne, destinée à guider les étudiants dans la lecture du Stagirite. Son style est souvent décrit comme clair et pédagogique : il systématise les thèmes, expose les objections de manière ordonnée, et adapte la tradition néoplatonicienne à un public plus large.&lt;/p&gt; &lt;p&gt; Il adhère à une hiérarchie de l’être allant de l’Un aux Intelligibles, à l’Âme et au monde sensible, mais il insiste particulièrement sur la pédagogie des vertus et de la purification de l’âme. Dans ses analyses morales, il distingue plusieurs niveaux de vertus que l’âme doit gravir pour se détacher progressivement du corps et se rapprocher du divin. Un thème marquant est son développement d’une "échelle des vertus" en sept degrés : vertus naturelles, morales, politiques, purificatrices, contemplatives, paradigmatiques et hiératiques. Les vertus politiques et purificatrices organisent la vie en société et la maîtrise des passions, tandis que les vertus contemplatives et théurgiques visent l’union de l’âme avec les réalités intelligibles et le divin. &lt;/p&gt; &lt;p&gt; Tout en restant païen, il opère une forme d’accommodement avec un environnement chrétien : il évite en général l’affrontement frontal, et certains thèmes se laissent aisément intégrer dans une culture chrétienne. Cela explique probablement que &lt;a href="https://books.openedition.org/pulg/18286?lang=fr" style="color:#88A1E9" title="  L’École d’Olympiodore et les problèmes critiques connexes par OpenEdition"&gt;son enseignement&lt;/a&gt; ait pu continuer à Alexandrie après la fermeture des grandes écoles païennes d’Athènes. &lt;/p&gt; </t>
+        <v>794</v>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Philopon" style="color:#6A142A" title="Wikipedia"&gt;Jean PHILOPON&lt;/a&gt; fut l'un des penseurs les plus novateurs de l'Antiquité tardive. Philosophe et théologien chrétien monophysite d'Alexandrie, disciple d'Ammonios fils d'Hermias, il est célèbre pour ses vastes commentaires des œuvres d'&lt;a href="https://fr.wikipedia.org/wiki/Aristote" style="color:#6A142A" title="Aristote sur Wikipedia"&gt;Aristote&lt;/a&gt;, qu'il soumit à une critique audacieuse au nom de la physique et de la foi chrétienne.&lt;/p&gt; &lt;p&gt;  Il est un des premiers grands commentateurs d’Aristote en grec, mais il s’en distingue nettement sur des questions comme l’éternité du monde. Dans ses traités Contre Proclus (529) et De la création du monde, il défend l’idée que le monde a été créé ex nihilo dans le temps, ce qui l’oppose à la conception aristotélicienne d’un univers éternel, affirmant que le cosmos fut créé à partir du néant — en accord avec le dogme chrétien. Il développa également la théorie de l'&lt;em&gt;impetus&lt;/em&gt;, ancêtre du concept d'inertie : un projectile lancé reçoit une force interne qui le maintient en mouvement, préfigurant ainsi la physique galiléenne six siècles avant Galilée.&lt;/p&gt; &lt;p&gt;       Sur le plan théologique, il soutient une lecture allégorique de la Bible et cherche à harmoniser Platon, Aristote et Ptolémée avec la cosmologie chrétienne, en s’opposant notamment à la vision « étagée » du monde de Cosmas Indicopleustès. Il se rapproche d’abord du monophysisme, puis adhère au courant dit « trithéite » (tendance au sein du christianisme oriental qui insiste sur la distinction des trois personnes divines), ce qui lui vaudra une condamnation par certains milieux orthodoxes et monophysites.   &lt;/p&gt; &lt;p&gt; Il est une figure de carrefour entre philosophie grecque et théologie chrétienne. Sa lecture critique d'Aristote, qu'il commentait tout en le contestant, influença profondément les penseurs arabes médiévaux et, via eux, la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_scientifique" style="color:#6A142A" title="Révolution scientifique sur Wikipedia"&gt;révolution scientifique&lt;/a&gt; de la Renaissance. Il fut condamné pour hérésie (trithéisme) mais son héritage philosophique demeure immense.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F99" s="7" t="s">
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -7919,31 +7963,31 @@
         </is>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>817</v>
-      </c>
-      <c r="E100" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie" style="color:#6A142A" title="Wikipedia"&gt;EULAMIOS de Phrygie&lt;/a&gt; est un philosophe néoplatonicien du VIe siècle, originaire de Phrygie, en Asie Mineure. Il appartient au dernier cercle des philosophes païens de l’école d’Athènes, réunis autour de Damascius, à l’époque où le christianisme est devenu la religion officielle de l’Empire et où les païens sont de plus en plus écartés de la vie publique.&lt;/p&gt; &lt;p&gt;Comme pour la plupart de ses compagnons, nous ne savons presque rien de sa vie, et aucune de ses œuvres ne nous est parvenue. Son nom nous est connu par l’historien byzantin Agathias, qui raconte l’un des épisodes les plus célèbres de la fin de l’Antiquité. En 529, l’empereur Justinien interdit aux païens d’enseigner. L’école d’Athènes, héritière de l’Académie de Platon, ne peut plus fonctionner. Vers 531, sept philosophes quittent alors l’Empire : Damascius, Simplicius de Cilicie, Priscien de Lydie, Hermias et Diogène de Phénicie, Isidore de Gaza et Eulamios. Ils se rendent à la cour du roi de Perse Khosro Ier, qui passait pour un ami de la sagesse grecque et faisait traduire Platon et Aristote. Mais la Perse les déçoit, et ils souhaitent rentrer. En 532, le traité de paix signé entre Khosro et Justinien prévoit qu’ils pourront revenir dans l’Empire et y vivre sans être obligés de renoncer à leurs croyances. Simplicius écrira ensuite ses grands commentaires d’Aristote, qui sont parmi les plus précieux de l’Antiquité.&lt;/p&gt; &lt;p&gt;Ces derniers maîtres du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; ont transmis la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_antique" style="color:#6A142A" title="Philosophie antique sur Wikipedia"&gt;philosophie antique&lt;/a&gt; aux savants byzantins, syriaques et arabes, et, par eux, au Moyen Âge.&lt;/p&gt;</t>
+        <v>802</v>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Priscien_de_Lydie" style="color:#6A142A" title="Wikipedia"&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href="https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316" title="la géographie et les originesnéoplatonisme sur Persee"&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité : « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F100" s="7" t="s">
-        <v>819</v>
-      </c>
-      <c r="G100" s="15" t="s">
-        <v>820</v>
-      </c>
-      <c r="H100" s="12" t="s">
+        <v>804</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="H100" s="9" t="s">
         <v>697</v>
       </c>
       <c r="I100" s="9"/>
@@ -7957,7 +8001,7 @@
         <v>538</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -7965,30 +8009,32 @@
         </is>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="n">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="E101" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie" title="Wikipedia"&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;</t>
+        <v>808</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympiodore_le_Jeune"  style="color:#6A142A"  title=" Wikipedia"&gt;OLYMPIODORE le Jeune&lt;/a&gt; était un philosophe néoplatonicien grec connu comme grand commentateur de Platon et d’Aristote, dernier représentant important de la tradition platonicienne païenne à Alexandrie. &lt;/p&gt; &lt;p&gt; Il laisse surtout des commentaires sur des dialogues de Platon : Phédon, Gorgias, Philebos et &lt;a href="https://www.youtube.com/watch?v=KauBLoVOcNs" style="color:#88A1E9" title=" hat is philosophy? Olympiodorus' Commentary on the First Alcibiades par Abbas the Alchemist"&gt;l’Alcibiade&lt;/a&gt;. Il commente également Aristote et compose une introduction à la philosophie aristotélicienne, destinée à guider les étudiants dans la lecture du Stagirite. Son style est souvent décrit comme clair et pédagogique : il systématise les thèmes, expose les objections de manière ordonnée, et adapte la tradition néoplatonicienne à un public plus large.&lt;/p&gt; &lt;p&gt; Il adhère à une hiérarchie de l’être allant de l’Un aux Intelligibles, à l’Âme et au monde sensible, mais il insiste particulièrement sur la pédagogie des vertus et de la purification de l’âme. Dans ses analyses morales, il distingue plusieurs niveaux de vertus que l’âme doit gravir pour se détacher progressivement du corps et se rapprocher du divin. Un thème marquant est son développement d’une "échelle des vertus" en sept degrés : vertus naturelles, morales, politiques, purificatrices, contemplatives, paradigmatiques et hiératiques. Les vertus politiques et purificatrices organisent la vie en société et la maîtrise des passions, tandis que les vertus contemplatives et théurgiques visent l’union de l’âme avec les réalités intelligibles et le divin. &lt;/p&gt; &lt;p&gt; Tout en restant païen, il opère une forme d’accommodement avec un environnement chrétien : il évite en général l’affrontement frontal, et certains thèmes se laissent aisément intégrer dans une culture chrétienne. Cela explique probablement que &lt;a href="https://books.openedition.org/pulg/18286?lang=fr" style="color:#88A1E9" title="  L’École d’Olympiodore et les problèmes critiques connexes par OpenEdition"&gt;son enseignement&lt;/a&gt; ait pu continuer à Alexandrie après la fermeture des grandes écoles païennes d’Athènes. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F101" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="G101" s="9"/>
+        <v>811</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>812</v>
+      </c>
       <c r="H101" s="9" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="2" t="s">
@@ -8001,116 +8047,97 @@
         <v>538</v>
       </c>
       <c r="M101" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="7" t="n">
+        <v>495</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie" style="color:#6A142A" title="Wikipedia"&gt;EULAMIOS de Phrygie&lt;/a&gt; est un philosophe néoplatonicien du VIe siècle, originaire de Phrygie, en Asie Mineure. Il appartient au dernier cercle des philosophes païens de l’école d’Athènes, réunis autour de Damascius, à l’époque où le christianisme est devenu la religion officielle de l’Empire et où les païens sont de plus en plus écartés de la vie publique.&lt;/p&gt; &lt;p&gt;Comme pour la plupart de ses compagnons, nous ne savons presque rien de sa vie, et aucune de ses œuvres ne nous est parvenue. Son nom nous est connu par l’historien byzantin Agathias, qui raconte l’un des épisodes les plus célèbres de la fin de l’Antiquité. En 529, l’empereur Justinien interdit aux païens d’enseigner. L’école d’Athènes, héritière de l’Académie de Platon, ne peut plus fonctionner. Vers 531, sept philosophes quittent alors l’Empire : Damascius, Simplicius de Cilicie, Priscien de Lydie, Hermias et Diogène de Phénicie, Isidore de Gaza et Eulamios. Ils se rendent à la cour du roi de Perse Khosro Ier, qui passait pour un ami de la sagesse grecque et faisait traduire Platon et Aristote. Mais la Perse les déçoit, et ils souhaitent rentrer. En 532, le traité de paix signé entre Khosro et Justinien prévoit qu’ils pourront revenir dans l’Empire et y vivre sans être obligés de renoncer à leurs croyances. Simplicius écrira ensuite ses grands commentaires d’Aristote, qui sont parmi les plus précieux de l’Antiquité.&lt;/p&gt; &lt;p&gt;Ces derniers maîtres du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; ont transmis la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_antique" style="color:#6A142A" title="Philosophie antique sur Wikipedia"&gt;philosophie antique&lt;/a&gt; aux savants byzantins, syriaques et arabes, et, par eux, au Moyen Âge.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="G102" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="H102" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="I102" s="9"/>
+      <c r="J102" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie" title="Wikipedia"&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="G103" s="9"/>
+      <c r="H103" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="I103" s="9"/>
+      <c r="J103" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="M103" s="2" t="s">
         <v>827</v>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P101">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="7">
-        <v>-450</v>
-      </c>
-      <c r="B102" s="7">
-        <v>-400</v>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ve siècle A JC</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIOTIME de Mantinée</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diotime"  title=" Wikipedia"&gt;DIOTIME de Mantinée&lt;/a&gt; est une prêtresse et une sage du Ve siècle avant J.-C., connue uniquement par le &lt;em&gt;Banquet&lt;/em&gt; de Platon. Socrate y raconte que, dans sa jeunesse, c'est elle qui lui a enseigné tout ce qu'il sait sur l'amour. Aucune autre source antique ne la mentionne, et son nom, « honorée par Zeus », ainsi que son origine, Mantinée, qui évoque le mot grec pour « devin », laissent penser qu'elle pourrait être une invention de Platon.&lt;/p&gt; &lt;p&gt;Son discours est pourtant le sommet du dialogue. Diotime explique qu'Éros n'est pas un dieu mais un « grand démon », un intermédiaire entre les mortels et les immortels, fils de Pauvreté et d'Expédient : il manque de ce qu'il désire et cherche sans cesse à l'obtenir. Aimer, c'est désirer posséder le bien pour toujours, et donc vouloir engendrer dans la beauté, par les enfants ou par les œuvres de l'esprit.&lt;/p&gt; &lt;p&gt;Le choix de Platon de faire parler une femme n'est pas anodin : dans un banquet où ne siègent que des hommes, c'est une étrangère, prêtresse et savante, qui détient la vérité la plus haute. Socrate, qui d'ordinaire interroge les autres, se présente ici comme un élève qu'elle corrige et fait progresser. La méthode de Diotime ressemble d'ailleurs à celle de Socrate lui-même : elle pose des questions, relève les contradictions et conduit pas à pas son interlocuteur vers la vérité.&lt;/p&gt; &lt;p&gt;Elle décrit ensuite la célèbre « échelle de l'amour » : de l'amour d'un beau corps, on s'élève à celui de tous les beaux corps, puis des belles âmes, des belles lois, des belles connaissances, jusqu'à la contemplation de la Beauté en soi, éternelle et parfaite. Réelle ou imaginée, Diotime reste la femme qui, chez Platon, enseigne au plus grand des philosophes l'une des idées les plus influentes de l'histoire de la pensée.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grecque</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metaphysique ; esthetique</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platonisme</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prêtresse et sage qui, dans le Banquet de Platon, enseigne à Socrate la nature de l'amour.</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7">
-        <v>-350</v>
-      </c>
-      <c r="B103" s="7">
-        <v>-280</v>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">350 A JC - 280 A JC</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIPPARCHIA de Maronée</t>
-        </is>
-      </c>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hipparchia"  title=" Wikipedia"&gt;HIPPARCHIA de Maronée&lt;/a&gt; (vers 350-280 avant J.-C.) est une philosophe cynique grecque, originaire de Maronée en Thrace. Issue d'une famille aisée, elle tomba amoureuse du philosophe Cratès de Thèbes, disciple de Diogène, qui avait renoncé à toute sa fortune. Ses parents s'opposèrent au mariage ; elle menaça de se tuer. Cratès lui-même tenta de la dissuader en lui montrant sa pauvreté, mais elle choisit de partager sa vie et ses idées.&lt;/p&gt; &lt;p&gt;Le cynisme prônait une vie simple, conforme à la nature, libérée des richesses, des honneurs et des conventions sociales jugées artificielles. Hipparchia vécut ainsi avec Cratès, en public et sans honte, portant le même manteau grossier que lui, et participa comme un homme aux banquets et aux discussions philosophiques, ce qui fit scandale à Athènes.&lt;/p&gt; &lt;p&gt;Selon Diogène Laërce, elle aurait écrit des traités philosophiques, des lettres et des réponses à des questions posées au philosophe Théodore, aujourd'hui perdus. Elle eut avec Cratès au moins deux enfants et continua de mener une vie de philosophe. Pour les anciens, elle était la preuve qu'une femme pouvait choisir librement la vie philosophique la plus exigeante, et plusieurs auteurs, jusqu'à l'époque chrétienne, citèrent son exemple.&lt;/p&gt; &lt;p&gt;Diogène Laërce rapporte une anecdote célèbre : lors d'un banquet, le philosophe Théodore l'Athée voulut l'humilier en lui demandant qui avait donc laissé sa navette sur le métier à tisser. Elle répondit qu'elle avait consacré à l'étude le temps qu'on aurait voulu lui faire perdre au rouet. Hipparchia est ainsi devenue le symbole de la femme qui revendique le droit de penser et de vivre en philosophe.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grecque</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cynisme</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe cynique grecque, épouse de Cratès, qui vécut selon ses idées contre les conventions de son temps.</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -8123,31 +8150,24 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="7">
-        <v>-450</v>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-400</t>
-        </is>
+        <v>-350</v>
+      </c>
+      <c r="B104" s="7">
+        <v>-280</v>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vers 450 A JC – 400 A JC</t>
+          <t xml:space="preserve">350 A JC - 280 A JC</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRATYLE</t>
+          <t xml:space="preserve">HIPPARCHIA de Maronée</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cratyle" title=" Wikipedia"&gt;CRATYLE&lt;/a&gt; est un philosophe grec d’Athènes, de la fin du Ve siècle av. J.-C., partisan radical de la pensée d’&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclite" title=" Wikipedia"&gt;Héraclite&lt;/a&gt;. Selon Aristote, Platon l’aurait fréquenté dans sa jeunesse, avant de rencontrer Socrate, et en aurait retenu l’idée que les choses sensibles sont dans un flux perpétuel, et qu’il ne peut donc y avoir de science à leur sujet.&lt;/p&gt; &lt;p&gt;Cratyle pousse le &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclit%C3%A9isme" title=" Wikipedia"&gt;mobilisme&lt;/a&gt; jusqu’à ses conséquences extrêmes. Héraclite disait qu’on ne peut entrer deux fois dans le même fleuve ; Cratyle lui reproche d’avoir été trop timide : on ne peut pas même y entrer une seule fois. Puisque tout change sans cesse, même pendant qu’on parle, aucune parole ne peut dire vrai. Selon Aristote, il finit par ne plus rien dire du tout et se contentait de remuer le doigt. Pour Aristote, ce geste muet montre où mène le refus de toute affirmation stable : à l’impossibilité même de parler.&lt;/p&gt; &lt;p&gt;Platon a donné son nom à l’un de ses dialogues, le &lt;em&gt;Cratyle&lt;/em&gt;, consacré à la justesse des noms. Cratyle y soutient que chaque chose a un nom juste par nature, qui exprime son essence, contre Hermogène, pour qui les noms ne sont que des conventions. Socrate examine les deux thèses avec ironie, se livre à de savoureuses étymologies, et conclut qu’il vaut mieux connaître les choses par elles-mêmes que par leurs noms. Le débat entre la nature et la convention des signes traverse ensuite toute l’histoire de la philosophie du langage, jusqu’à Saussure. Pour Platon, la leçon est claire : si tout s’écoulait, il n’y aurait rien à connaître, d’où la nécessité des Idées, réalités immuables.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/cratyle-mini.webp</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hipparchia"  title=" Wikipedia"&gt;HIPPARCHIA de Maronée&lt;/a&gt; (vers 350-280 avant J.-C.) est une philosophe cynique grecque, originaire de Maronée en Thrace. Issue d'une famille aisée, elle tomba amoureuse du philosophe Cratès de Thèbes, disciple de Diogène, qui avait renoncé à toute sa fortune. Ses parents s'opposèrent au mariage ; elle menaça de se tuer. Cratès lui-même tenta de la dissuader en lui montrant sa pauvreté, mais elle choisit de partager sa vie et ses idées.&lt;/p&gt; &lt;p&gt;Le cynisme prônait une vie simple, conforme à la nature, libérée des richesses, des honneurs et des conventions sociales jugées artificielles. Hipparchia vécut ainsi avec Cratès, en public et sans honte, portant le même manteau grossier que lui, et participa comme un homme aux banquets et aux discussions philosophiques, ce qui fit scandale à Athènes.&lt;/p&gt; &lt;p&gt;Selon Diogène Laërce, elle aurait écrit des traités philosophiques, des lettres et des réponses à des questions posées au philosophe Théodore, aujourd'hui perdus. Elle eut avec Cratès au moins deux enfants et continua de mener une vie de philosophe. Pour les anciens, elle était la preuve qu'une femme pouvait choisir librement la vie philosophique la plus exigeante, et plusieurs auteurs, jusqu'à l'époque chrétienne, citèrent son exemple.&lt;/p&gt; &lt;p&gt;Diogène Laërce rapporte une anecdote célèbre : lors d'un banquet, le philosophe Théodore l'Athée voulut l'humilier en lui demandant qui avait donc laissé sa navette sur le métier à tisser. Elle répondit qu'elle avait consacré à l'étude le temps qu'on aurait voulu lui faire perdre au rouet. Hipparchia est ainsi devenue le symbole de la femme qui revendique le droit de penser et de vivre en philosophe.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -8157,17 +8177,22 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">langage ; metaphysique</t>
+          <t xml:space="preserve">ethique</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobilisme</t>
+          <t xml:space="preserve">Cynisme</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe grec, héraclitéen radical, qui a donné son nom au dialogue de Platon sur le langage.</t>
+          <t xml:space="preserve">philosophe cynique grecque, épouse de Cratès, qui vécut selon ses idées contre les conventions de son temps.</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8175,7 +8200,9 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P104"/>
+      <c r="P104">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8187,31 +8214,31 @@
     <hyperlink ref="E18" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gorgias&quot; title=&quot; Wikipedia&quot;&gt;GORGIAS&lt;/a&gt; était un philosophe présocratique et l'une des figures les plus importantes de la &lt;a href=&quot;https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;t=184s&quot; title=&quot; Les sophistes par Bibiclo&quot;&gt;sophistique&lt;/a&gt;.  Contrairement aux philosophes comme Platon ou Aristote, qui cherchaient à découvrir des vérités universelles en mettant l'accent sur l'importance de l'opinion et de la persuasion dans les affaires humaines.  Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;  - &quot;Sur le Non-Être ou sur la Nature&quot; : Il développe une argumentation radicale qui remet en question la possibilité même de la connaissance et de la communication.&lt;/p&gt; &lt;p&gt; -  Il soutient trois thèses principales : - Rien n'existe.  - Si quelque chose existait, nous ne pourrions pas le connaître. - Si nous pouvions le connaître, nous ne pourrions pas le communiquer aux autres. &lt;/p&gt; &lt;p&gt; Ces thèses sont souvent interprétées comme une critique de l'ontologie éléatique, notamment des idées de Parménide, qui affirmait que l'être est un et immuable. &lt;/p&gt;  &lt;p&gt; - &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89loge_d%27H%C3%A9l%C3%A8ne &quot;  title=&quot; Gorgias Eloge d’Helene  parWikipedia&quot;&gt;&quot;Éloge d'Hélène&quot;&lt;/a&gt;  : Dans ce discours, Il défend Hélène de Troie, souvent considérée comme responsable de la guerre de Troie. Il utilise des arguments rhétoriques pour montrer qu'elle ne peut être tenue pour responsable, car elle a été soit victime de la volonté des dieux, soit de la séduction de Pâris, soit de la force.  &lt;/p&gt; &lt;p&gt; -  &quot;Défense de Palamède&quot; : Dans ce discours, il défend Palamède, un héros grec accusé de trahison par Ulysse. Il utilise des arguments logiques et rhétoriques pour démontrer son l'innocence, montrant ainsi la puissance de la parole pour influencer les jugements. &lt;p&gt; Il  est souvent considéré comme un relativiste et un sceptique. Il met en doute la possibilité de connaître la vérité absolue et souligne l'importance de la persuasion dans les affaires humaines. Sa philosophie a eu une influence significative sur la pensée grecque, notamment sur Platon, qui le critique sévèrement dans son dialogue &quot;Gorgias&quot;. Platon y oppose la recherche de la vérité à l'art de la persuasion, qu'il associe à la sophistique. &lt;/p&gt; &#10;&#10;"/>
     <hyperlink ref="E22" r:id="rId3" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/D%C3%A9mocrite&quot; title=&quot; Wikipedia&quot;&gt; DÉMOCRITE&lt;/a&gt; était un philosophe Grec connu pour être l'un des fondateurs avec LEUCIPPE de la philosophie  &lt;a href=&quot;https://www.youtube.com/watch?v=AGvcey2B3Vc&amp;t=3s&amp;ab_channel=Coursitout&quot;   title=&quot;l'Atomisme des philosophes Grecs par Coursitout&quot;&gt; atomiste&lt;/a&gt;, une théorie selon laquelle tout dans l'univers est composé de particules indivisibles appelées atomes. Selon lui, ils sont en mouvement perpétuel et se combinent pour former toutes les substances et objets que nous voyons autour de nous.  Il était réputé pour sa grande curiosité intellectuelle et aurait beaucoup voyagé, notamment en Égypte et en Orient, afin d’enrichir ses connaissances. Surnommé parfois « le philosophe rieur », il adoptait une attitude détachée face aux préoccupations humaines, considérant que la sérénité naît de la compréhension du monde et de la maîtrise de soi.  &lt;/p&gt; &lt;p&gt;Il avait une approche &lt;a href=&quot;https://www.youtube.com/watch?v=_uXOu9ZRD4I&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;le matérialisme par Alain Bajomée&quot;&gt; matérialiste&lt;/a&gt; de la réalité et croyait que tout ce qui existe était composé de matière et de vide, et que la perception humaine était basée sur l'interaction entre les atomes et les sens. Il était également connu pour ses idées sur l'éthique et la morale et croyait que le bonheur et la vertu pouvaient être atteints grâce à une vie simple et équilibrée, et que les désirs excessifs et les passions pouvaient entraîner la souffrance. &lt;/p&gt; &lt;p&gt; Sa pensée ne se limite pas à la physique : il développe aussi une réflexion approfondie sur la connaissance en distinguant les qualités « réelles » (comme la forme et le mouvement des atomes) des qualités « sensibles » (comme les couleurs ou les saveurs), qui dépendent de nos perceptions. Cette distinction annonce des débats majeurs de la philosophie moderne. Son influence se retrouvera plus tard chez des penseurs comme Épicure, qui reprendra l’atomisme en y intégrant une dimension éthique centrée sur la recherche du plaisir mesuré et de l’absence de trouble.   &lt;/p&gt; &lt;p&gt; Peu de ses écrits ont survécu jusqu'à nos jours, et la plupart de ce que nous connaissons provient de commentaires ultérieurs et de citations dans les œuvres d'autres philosophes grecs. Cependant, ses contributions à la théorie atomique ont été fondamentales pour la compréhension moderne de la physique et de la chimie. &lt;/p&gt; &lt;audio controls title=&quot;Démocrite contre Platon par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2015/06/s27/net-fi-be35a965-485b-4f98-9b10-0e2051e903ec.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
     <hyperlink ref="E23" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thrasymaque&quot;title=&quot; Wikipedia&quot;&gt;THRASYMAQUE&lt;/a&gt; était un philosophe sophiste grec connue pour son rôle dans &lt;a href=&quot;https://www.youtube.com/watch?v=qSrvZvjPG_w&quot; style=&quot;color:#88A1E9&quot; title=&quot; PLATON-Cest quoi la république par Kosmos &quot;&gt;&quot;La République&quot;&lt;/a&gt; de Platon. Il est l'un des interlocuteurs de Socrate dans ce dialogue, où il défend une vision provocante et cynique de la justice. &lt;/p&gt;&lt;p&gt; Il  affirme que &quot;&lt;a href=&quot;https://www.youtube.com/watch?v=VlLLr8kVya0&quot;  title=&quot;  Qu'est-ce que la Justice en Philosophie ?   par Coursitout &quot;&gt;la justice&lt;/a&gt; n'est rien d'autre que l'intérêt du plus fort&quot;. Selon lui, les lois et les normes sociales sont établies par ceux qui détiennent le pouvoir (les gouvernants, les tyrans, les aristocrates) pour servir leurs propres intérêts. Ainsi, la justice n'est pas une valeur universelle ou objective, mais un outil de domination. Il  va plus loin en affirmant que l'injustice est une vertu. Selon lui, les individus injustes sont plus heureux et plus prospères que les justes, car ils savent exploiter les autres à leur avantage. La justice, au contraire, est une faiblesse qui empêche les individus de réaliser leur plein potentiel. &lt;/p&gt;&lt;p&gt; Il  est souvent vu comme un précurseur du relativisme moral, qui nie l'existence de valeurs universelles. Sa pensée peut être rapprochée du réalisme politique, qui considère que la politique est avant tout une lutte pour le pouvoir et que les notions de justice et de moralité sont secondaires. &lt;/p&gt; &lt;p&gt; Il  incarne une vision cynique et réaliste de la justice, qui &lt;a href=&quot;https://www.persee.fr/doc/antiq_0770-2817_2018_num_87_1_3962&quot; style=&quot;color:#88A1E9&quot; title=&quot;Les difficultés du débat sur la justice entre Socrate et Thrasymaque dans la République par Persée &quot;&gt;contraste fortement&lt;/a&gt; avec l'idéalisme de Socrate. Bien que ses arguments soient finalement réfutés dans le dialogue, ils restent une contribution importante à la philosophie politique, car ils soulèvent des questions fondamentales sur la nature du pouvoir, de la moralité et de la justice. &lt;/p&gt;"/>
-    <hyperlink ref="E31" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eudoxe_de_Cnide&quot;  title=&quot; Wikipedia&quot;&gt;EUDOXE de Cnide&lt;/a&gt; était un mathématicien, astronome et philosophe grec de l'Antiquité, originaire de la ville de Cnide, en Asie Mineure (actuelle Turquie). Il est surtout connu pour   &lt;a href=&quot;https://www.youtube.com/watch?v=YiWuTuTPOEw&quot;  style=&quot;color:#88A1E9&quot; title=&quot; The Fascinating History of Mathematics : Eudoxus of Cnidus par Cambia Math Tutors&quot;&gt;ses travaux &lt;/a&gt;  en géométrie et en théorie des proportions. Ses contributions ont jeté les bases de nombreuses décounidevertes ultérieures, notamment celles d'Euclide. Il a développé une théorie générale des proportions qui permettait de comparer des grandeurs incommensurables. Cette théorie a permis de surmonter les limitations des mathématiques pythagoriciennes, qui étaient basées sur les nombres entiers. Il a étudié les sections coniques et les solides géométriques, contribuant à la compréhension des formes tridimensionnelles. &lt;/p&gt; &lt;p&gt; Il a proposé un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%A9ocentrisme&quot;  title=&quot; geocentrisme par wikipedia&quot;&gt;modèle géocentrique &lt;/a&gt; complexe pour expliquer les mouvements apparents des planètes, du Soleil et de la Lune. Selon ce modèle, chaque corps céleste est attaché à une série de sphères imbriquées, tournant à des vitesses et des angles différents. Ce système permettait de reproduire les mouvements rétrogrades des planètes (lorsqu'elles semblent reculer dans le ciel). Bien que ce modèle ait été remplacé plus tard par celui de Ptolémée, il a marqué une étape importante dans l'histoire de l'astronomie. &lt;/p&gt; &lt;p&gt; Il a soutenu que le plaisir est le bien suprême, une idée qui contraste avec les vues de Platon et d'Aristote. Pour Eudoxe, le plaisir est une fin en soi et non simplement un moyen et a critiqué la théorie des Idées de Platon, arguant que les Idées ne peuvent pas exister séparément des objets concrets. &lt;/p&gt; "/>
-    <hyperlink ref="H38" r:id="rId6" display="https://www.laphilo.fr/pho/aristippel-mini.webp"/>
-    <hyperlink ref="E45" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89picure&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9donisme&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'hédonisme par Wikipédia&quot;&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href=&quot;https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href=&quot;https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href=&quot;https://www.youtube.com/watch?v=cb1YHXSuxlM&quot;   title=&quot;La philosophie du bonheur par Parole de philosophe&quot;&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt;  &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées &quot;atomes&quot;.&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt;  &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title=&quot;Est il bien raisonnable d'avoir peur de la mort par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E55" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame&quot; title=&quot;Wikipedia&quot;&gt;Hégésinous de PERGAME&lt;/a&gt; était un philosophe grec, représentant de la &lt;em&gt;Moyenne Académie&lt;/em&gt; platonicienne. Il succéda à Évandre et Télécès à la direction de l'Académie d'Athènes et fut le maître direct de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt;, qui allait révolutionner la pensée académicienne avec sa Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Comme ses prédécesseurs, Hégésinous s'inscrivait dans la tradition sceptique d'Arcésilas, défendant la suspension du jugement face à l'incertitude radicale de la connaissance humaine. Son enseignement, dont nous ne conservons aucun écrit, fut néanmoins suffisamment stimulant pour former l'un des plus grands dialecticiens de l'Antiquité en la personne de Carnéade.&lt;/p&gt; &lt;p&gt;Hégésinous appartient à cette lignée de scholarques discrets qui assurèrent la survie institutionnelle de l'Académie durant les IIIe et IIe siècles av. J.-C. Son rôle de maillon entre la Moyenne et la Nouvelle Académie est fondamental, même si son nom reste peu connu en dehors des spécialistes de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie hellénistique sur Wikipedia&quot;&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;"/>
-    <hyperlink ref="E56" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Wikipedia&quot;&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Dialectique&quot; title=&quot;Dialectique par Wikipedia&quot;&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272&quot; title=&quot;Opinion et certitude par Persee&quot;&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href=&quot;https://fr.wikipedia.org/wiki/Cic%C3%A9ron&quot; style=&quot;color:#6A142A&quot; title=&quot;Cicéron sur Wikipedia&quot;&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il.&lt;/p&gt;"/>
-    <hyperlink ref="E58" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s&quot; title=&quot;Wikipedia&quot;&gt;TÉLÉCLÈS&lt;/a&gt; était un philosophe grec représentant de la Moyenne Académie platonicienne. Disciple de Lacydès de Cyrène, il dirigea conjointement l'Académie d'Athènes avec Évandre, après que Lacydès leur eut confié la responsabilité de l'École de son vivant.&lt;/p&gt; &lt;p&gt;Très peu de détails biographiques nous sont parvenus sur sa vie et sa pensée. Il s'inscrivait dans la tradition sceptique inaugurée par Arcésilas, défendant l'idée que la raison humaine ne peut accéder à une certitude absolue, et que la sagesse réside dans la suspension du jugement et l'adhésion au vraisemblable. Ses étudiants comprenaient de futurs représentants de la Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Téléclès appartient à ces figures de transition dont le rôle, discret mais essentiel, fut d'assurer la pérennité de l'Académie entre deux grandes figures : Lacydès avant lui et &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; style=&quot;color:#6A142A&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt; après lui. Son passage à la direction de l'École illustre la collégialité qui caractérisait l'organisation de la pensée académicienne.&lt;/p&gt;"/>
-    <hyperlink ref="E59" r:id="rId11" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes&quot;  title=&quot; Wikipedia&quot;&gt;PANÉTIUS DE RHODES&lt;/a&gt;  était un philosophe grec considéré comme le fondateur de l'école Stoïcienne de Rhodes. Il a étudié avec Diogène de Babylone et est devenu plus tard l'un des penseurs de Cicéron, le célèbre orateur et homme politique romain. &lt;/p&gt; &lt;p&gt;  Il a contribué à façonner la  &lt;a href=&quot;https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie&quot;  title=&quot;Le Stoïcisme par apprendre la philo&quot;&gt;pensée stoïcienne&lt;/a&gt; en l'adaptant aux besoins de son temps en la conciliant  avec d'autres courants philosophiques comme l'épicurisme et le scepticisme. Il rompt avec les dogmes stoïciens. « Il nie la conflagration universelle et croit à l'éternité d'un monde que la Providence rend parfait ». &lt;/p&gt; &lt;p&gt; Il se défie de la mantique (la divination) et nie l'immortalité de l'âme. Il reconnaît en nous, à côté des impulsions de l'instinct premier, des tendances fondamentales où s'associent nature et raison. &lt;/p&gt; &lt;p&gt; Il aboutit à un humanisme, il tend à une sérénité morale faite de calme, de mesure, d'harmonie. Il a également développé la notion de justice naturelle, qui est une forme de justice qui découle de la nature même de l'homme et de la société, et qui est différente de la justice conventionnelle établie par les lois et les coutumes.&lt;/p&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E60" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Posidonios&quot;  title=&quot; Wikipedia&quot;&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href=&quot;https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770&quot;  title=&quot;Posidonius d'Apamée théoricien de la géométrie par Persée&quot;&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href=&quot;https://www.youtube.com/watch?v=EqU-kD8dW4Y&quot; title=&quot;Grèce antique - 33 La civilisation hellénistique par Yannick Rub&quot;&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289&quot;  title=&quot;La philosophiede Posidonius par Persee&quot;&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; "/>
-    <hyperlink ref="E66" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que&quot; title=&quot; Wikipedia&quot;&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href=&quot;https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Le Stoïcisme par le Précepteur&quot;&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=J3wZoqElCgs&quot; title=&quot;Who is Seneca par Daily Stoic &quot;&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href=&quot;https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin&quot; title=&quot;La vie Heureuse par Karl Baudoin&quot;&gt; &quot;une vie heureuse&quot;.&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : - De la brièveté de la vie (consideration sur l’usage du temps). - De la colère (sur la maîtrise de cette passion destructive). - De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt;  est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href=&quot;https://www.youtube.com/watch?v=d_cge9OwVAs&quot; title=&quot;La vie philosophique de Sénèque par Kosmos&quot;&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title=&quot;Les lettres à Lucilius – Senèque  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="E67" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;AMMONIOS d'Athènes&lt;/a&gt; était un philosophe platonicien originaire d'Égypte, qui enseigna à Athènes et fut l'un des maîtres de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Plutarque&quot; style=&quot;color:#6A142A&quot; title=&quot;Plutarque sur Wikipedia&quot;&gt;Plutarque&lt;/a&gt;. Représentant du médio-platonisme, il cherchait à concilier la philosophie de Platon avec d'autres courants de pensée de l'Antiquité tardive.&lt;/p&gt; &lt;p&gt;Son enseignement oral laissa une empreinte durable sur ses disciples, bien qu'il n'ait laissé aucun écrit. Il défendait une lecture spirituelle et morale du platonisme, insistant sur la contemplation du Bien et la purification de l'âme. Plutarque, son élève le plus illustre, rapporte ses enseignements dans ses &lt;em&gt;Moralia&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Ammonios d'Athènes appartient à ce courant de platoniciens qui, entre Platon et Plotin, ont préparé le terrain au &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;, en développant une exégèse du &lt;em&gt;Timée&lt;/em&gt; et de la &lt;em&gt;République&lt;/em&gt;. Sa discrétion littéraire contraste avec l'influence considérable qu'il exerça sur le cercle intellectuel d'Athènes de son époque.&lt;/p&gt;"/>
-    <hyperlink ref="H77" r:id="rId15" display="https://www.laphilo.fr/pho/jamblique-mini.webp"/>
-    <hyperlink ref="H84" r:id="rId16" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="H85" r:id="rId17" display="https://www.laphilo.fr/pho/scyrene-mini.webp"/>
-    <hyperlink ref="E86" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot;   title=&quot;Proclus par Wikipédia&quot;&gt; PROCLUS&lt;/a&gt; était un philosophe &lt;a href=&quot;https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D&quot;   title=&quot;Le Néoplatonisme par Anne Baudart&quot;&gt; Néoplatonicien grec&lt;/a&gt; et il est considéré comme l'un des derniers grands philosophes de l'Antiquité classique.&lt;/p&gt;&#10;&lt;p&gt; Sa philosophie est basée sur les enseignements de Platon et d'Aristote. Il a développé une théorie complexe de l'univers qui est basée sur l'idée d'une hiérarchie de réalités. Au sommet de cette hiérarchie se trouve l'Un, qui est la réalité ultime et incompréhensible. Voici les principaux concepts de la philosophie de Proclus :&lt;/p&gt;&#10;&lt;dd&gt;L'Un : Réalité ultime et incompréhensible, qui est la source de toutes choses.&lt;/dd&gt;&#10;&lt;dd&gt;Le Démiurge : Force créatrice qui a donné forme à l'univers.&lt;/dd&gt;&#10;&lt;dd&gt;Les dieux : Intermédiaires entre l'Un et le monde sensible.&lt;/dd&gt;&#10;&lt;dd&gt;Les âmes : Principes vitaux qui animent les êtres vivants.&lt;/dd&gt;&#10;&lt;dd&gt;La matière : Réalité la plus basse de la hiérarchie, source du changement et de la corruption.&lt;/dd&gt;&#10;&lt;p&gt; Il a écrit un grand nombre &lt;a href=&quot;https://remacle.org/bloodwolf/philosophes/proclus/table.htm&quot;   title=&quot;Proclus par Philippe Remacle&quot;&gt; d'ouvrages sur la philosophie&lt;/a&gt;, dont les plus importants sont &lt;a href=&quot;https://www.youtube.com/watch?v=SJK1kbyXXno&quot;   title=&quot;Les éléments de Théologie de Proclus par LabEx HaStec&quot;&gt; les Commentaires sur le Timée de Platon&lt;/a&gt;, les Éléments de théologie et les Hypotyposes platonicae. Ces ouvrages ont été d'une grande influence sur la philosophie occidentale, et ils continuent à être étudiés aujourd'hui. &lt;/p&gt;   &lt;audio controls title=&quot; Proclus, un philosophe étoilé par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;"/>
-    <hyperlink ref="E87" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;HERMIAS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien, élève du grand &lt;a href=&quot;https://fr.wikipedia.org/wiki/Syrianos&quot; title=&quot;Syrianus sur Wikipedia&quot;&gt;Syrianus&lt;/a&gt; à Athènes. De retour à Alexandrie, il y fonda une école philosophique et épousa Aidésia, dont il eut pour fils le célèbre Ammonios d'Alexandrie.&lt;/p&gt; &lt;p&gt;Son œuvre principale est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes prises lors des cours de Syrianus. Cet ouvrage, qui nous est parvenu, offre une interprétation allégorique et métaphysique du dialogue platonicien sur l'amour, l'âme et la beauté, dans la tradition néoplatonicienne.&lt;/p&gt; &lt;p&gt;Hermias s'inscrit dans la lignée des maîtres qui firent d'Alexandrie un foyer majeur de la pensée antique tardive. Son rôle de transmetteur entre l'école d'Athènes et celle d'Alexandrie fut déterminant pour la pérennité du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;. Sa mort prématurée laissa Aidésia seule pour assurer l'avenir philosophique de leurs fils.&lt;/p&gt;"/>
-    <hyperlink ref="H89" r:id="rId20" display="https://www.laphilo.fr/pho/damascios-mini.webp"/>
-    <hyperlink ref="E90" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;AMMONIOS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien de la fin de l'Antiquité, fils d'Hermias et d'Aidésia, tous deux philosophes. Il succéda à Proclos comme tête de l'école néoplatonicienne d'Athènes et dirigea l'école alexandrine, formant une génération de commentateurs d'Aristote comme Olympiodore, Jean Philopon ou Simplicius, dans un contexte de tensions entre païens et chrétiens. Il enseigna l'Aristote aux païens et le Platon aux chrétiens pour favoriser une harmonie entre doctrines. &lt;/p&gt; &lt;p&gt; Spécialiste des commentaires d'Aristote, il défendit une interprétation néoplatonicienne unifiant Aristote et Platon : Aristote prépare à Platon, l'âme s'élève de la matière à l'Intellect divin. Ses écrits, perdus sauf fragments, insistent sur la théurgie et l'exégèse allégorique.&lt;/p&gt; &lt;p&gt; Son école alexandrine préserva le corpus aristotélicien pour l'Islam et l'Occident médiéval. &lt;/p&gt; Aucun texte complet ne survit directement, mais ses leçons sont préservées via les commentaires de ses élèves, comme ceux de Philopon sur l'Isagogè. Il chercha à harmoniser les deux grands penseurs antiques pour préserver la tradition païenne face au christianisme dominant.https://www.ljallamion.fr/spip.php?article6169 &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E91" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isidore_de_Gaza&quot; title=&quot;Wikipedia&quot;&gt;ISIDORE de Gaza&lt;/a&gt; était un philosophe néoplatonicien, né à Gaza en Palestine. Maître de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Damascios&quot; title=&quot;Damascios sur Wikipedia&quot;&gt;Damascios&lt;/a&gt;, le dernier scholarque de l'Académie d'Athènes, il fut l'un des derniers grands représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot;  title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique.&lt;/p&gt; &lt;p&gt;Damascios lui consacra une biographie dans sa &lt;em&gt;Vie d'Isidore&lt;/em&gt; (aussi connue sous le nom de &lt;em&gt;Vie des philosophes&lt;/em&gt;), où il le dépeint comme un personnage d'une grande intégrité morale, attaché aux traditions philosophiques grecques et à la piété envers les dieux, dans un contexte où le christianisme triomphait. Isidore représentait une philosophie vécue comme exercice spirituel, alliant rigueur intellectuelle et pratique ascétique.&lt;/p&gt; &lt;p&gt;Sa pensée s'inscrit dans la grande tradition de l'école néoplatonicienne d'Athènes, héritière de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot; title=&quot;Proclus sur Wikipedia&quot;&gt;Proclus&lt;/a&gt;. Il incarne ces penseurs de la fin du paganisme grec qui, face à la montée de la chrétienté, s'accrochaient à la philosophie comme à une forme de spiritualité rationnelle et contemplative, gardienne de l'héritage intellectuel de la Grèce.&lt;/p&gt;"/>
-    <hyperlink ref="H91" r:id="rId23" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="H94" r:id="rId24" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="E95" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Simplicius_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698&quot; style=&quot;color:#88A1E9&quot; title=&quot;A propos de la biographie de Simplicius par Persée&quot;&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le &quot;Manuel d’Épictète&quot; et, selon la tradition, sur &quot;De l’âme&quot;. Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href=&quot;https://www.youtube.com/watch?v=C17VYcyLkiY&quot; style=&quot;color:#88A1E9&quot; title=&quot;SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions&quot;&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.  &lt;a href=&quot;https://www.youtube.com/watch?v=6a4uQpmGsUg&quot; style=&quot;color:#88A1E9&quot; title=&quot;Simplicius – The Last Guardian of Ancient Philosophy par A time in history&quot;&gt; Transmis et traduits&lt;/a&gt; dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; "/>
-    <hyperlink ref="E98" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Priscien_de_Lydie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316&quot; title=&quot;la géographie et les originesnéoplatonisme sur Persee&quot;&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité :  - « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. - « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;"/>
-    <hyperlink ref="E100" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;EULAMIOS de Phrygie&lt;/a&gt; était un philosophe néoplatonicien du VIe siècle, originaire de Phrygie en Asie Mineure (actuelle Turquie). Il appartient au cercle des derniers représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique, dont il perpétua la tradition après la fermeture de l'Académie d'Athènes par Justinien en 529.&lt;/p&gt; &lt;p&gt;Figure peu documentée de cette période de transition, il s'inscrit dans le mouvement de philosophes néoplatoniciens qui, après l'exil perse et la dispersion de l'école athénienne, continuèrent à enseigner et transmettre la philosophie grecque en dehors des institutions officielles. Ses liens avec les cercles de Damascios et Simplicius laissent penser qu'il participa à la préservation du corpus philosophique antique.&lt;/p&gt; &lt;p&gt;Eulamios représente la philosophie de survie du néoplatonisme face à la christianisation de l'Empire. Comme ses contemporains, il incarne la volonté de maintenir vivante une tradition intellectuelle millénaire, préservant ainsi les conditions de la redécouverte médiévale et renaissante de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_antique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie antique sur Wikipedia&quot;&gt;philosophie antique&lt;/a&gt;.&lt;/p&gt;"/>
-    <hyperlink ref="H100" r:id="rId28" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="E101" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie&quot; title=&quot;Wikipedia&quot;&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.https://fr.wikipedia.org/wiki/Diogène_de_Phénicie    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;"/>
+    <hyperlink ref="E33" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eudoxe_de_Cnide&quot;  title=&quot; Wikipedia&quot;&gt;EUDOXE de Cnide&lt;/a&gt; était un mathématicien, astronome et philosophe grec de l'Antiquité, originaire de la ville de Cnide, en Asie Mineure (actuelle Turquie). Il est surtout connu pour   &lt;a href=&quot;https://www.youtube.com/watch?v=YiWuTuTPOEw&quot;  style=&quot;color:#88A1E9&quot; title=&quot; The Fascinating History of Mathematics : Eudoxus of Cnidus par Cambia Math Tutors&quot;&gt;ses travaux &lt;/a&gt;  en géométrie et en théorie des proportions. Ses contributions ont jeté les bases de nombreuses décounidevertes ultérieures, notamment celles d'Euclide. Il a développé une théorie générale des proportions qui permettait de comparer des grandeurs incommensurables. Cette théorie a permis de surmonter les limitations des mathématiques pythagoriciennes, qui étaient basées sur les nombres entiers. Il a étudié les sections coniques et les solides géométriques, contribuant à la compréhension des formes tridimensionnelles. &lt;/p&gt; &lt;p&gt; Il a proposé un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%A9ocentrisme&quot;  title=&quot; geocentrisme par wikipedia&quot;&gt;modèle géocentrique &lt;/a&gt; complexe pour expliquer les mouvements apparents des planètes, du Soleil et de la Lune. Selon ce modèle, chaque corps céleste est attaché à une série de sphères imbriquées, tournant à des vitesses et des angles différents. Ce système permettait de reproduire les mouvements rétrogrades des planètes (lorsqu'elles semblent reculer dans le ciel). Bien que ce modèle ait été remplacé plus tard par celui de Ptolémée, il a marqué une étape importante dans l'histoire de l'astronomie. &lt;/p&gt; &lt;p&gt; Il a soutenu que le plaisir est le bien suprême, une idée qui contraste avec les vues de Platon et d'Aristote. Pour Eudoxe, le plaisir est une fin en soi et non simplement un moyen et a critiqué la théorie des Idées de Platon, arguant que les Idées ne peuvent pas exister séparément des objets concrets. &lt;/p&gt; "/>
+    <hyperlink ref="H40" r:id="rId6" display="https://www.laphilo.fr/pho/aristippel-mini.webp"/>
+    <hyperlink ref="E47" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89picure&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9donisme&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'hédonisme par Wikipédia&quot;&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href=&quot;https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href=&quot;https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href=&quot;https://www.youtube.com/watch?v=cb1YHXSuxlM&quot;   title=&quot;La philosophie du bonheur par Parole de philosophe&quot;&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt;  &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées &quot;atomes&quot;.&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt;  &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title=&quot;Est il bien raisonnable d'avoir peur de la mort par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E57" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame&quot; title=&quot;Wikipedia&quot;&gt;Hégésinous de PERGAME&lt;/a&gt; était un philosophe grec, représentant de la &lt;em&gt;Moyenne Académie&lt;/em&gt; platonicienne. Il succéda à Évandre et Télécès à la direction de l'Académie d'Athènes et fut le maître direct de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt;, qui allait révolutionner la pensée académicienne avec sa Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Comme ses prédécesseurs, Hégésinous s'inscrivait dans la tradition sceptique d'Arcésilas, défendant la suspension du jugement face à l'incertitude radicale de la connaissance humaine. Son enseignement, dont nous ne conservons aucun écrit, fut néanmoins suffisamment stimulant pour former l'un des plus grands dialecticiens de l'Antiquité en la personne de Carnéade.&lt;/p&gt; &lt;p&gt;Hégésinous appartient à cette lignée de scholarques discrets qui assurèrent la survie institutionnelle de l'Académie durant les IIIe et IIe siècles av. J.-C. Son rôle de maillon entre la Moyenne et la Nouvelle Académie est fondamental, même si son nom reste peu connu en dehors des spécialistes de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie hellénistique sur Wikipedia&quot;&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;"/>
+    <hyperlink ref="E58" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Wikipedia&quot;&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Dialectique&quot; title=&quot;Dialectique par Wikipedia&quot;&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272&quot; title=&quot;Opinion et certitude par Persee&quot;&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href=&quot;https://fr.wikipedia.org/wiki/Cic%C3%A9ron&quot; style=&quot;color:#6A142A&quot; title=&quot;Cicéron sur Wikipedia&quot;&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il.&lt;/p&gt;"/>
+    <hyperlink ref="E60" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s&quot; title=&quot;Wikipedia&quot;&gt;TÉLÉCLÈS&lt;/a&gt; était un philosophe grec représentant de la Moyenne Académie platonicienne. Disciple de Lacydès de Cyrène, il dirigea conjointement l'Académie d'Athènes avec Évandre, après que Lacydès leur eut confié la responsabilité de l'École de son vivant.&lt;/p&gt; &lt;p&gt;Très peu de détails biographiques nous sont parvenus sur sa vie et sa pensée. Il s'inscrivait dans la tradition sceptique inaugurée par Arcésilas, défendant l'idée que la raison humaine ne peut accéder à une certitude absolue, et que la sagesse réside dans la suspension du jugement et l'adhésion au vraisemblable. Ses étudiants comprenaient de futurs représentants de la Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Téléclès appartient à ces figures de transition dont le rôle, discret mais essentiel, fut d'assurer la pérennité de l'Académie entre deux grandes figures : Lacydès avant lui et &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; style=&quot;color:#6A142A&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt; après lui. Son passage à la direction de l'École illustre la collégialité qui caractérisait l'organisation de la pensée académicienne.&lt;/p&gt;"/>
+    <hyperlink ref="E61" r:id="rId11" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes&quot;  title=&quot; Wikipedia&quot;&gt;PANÉTIUS DE RHODES&lt;/a&gt;  était un philosophe grec considéré comme le fondateur de l'école Stoïcienne de Rhodes. Il a étudié avec Diogène de Babylone et est devenu plus tard l'un des penseurs de Cicéron, le célèbre orateur et homme politique romain. &lt;/p&gt; &lt;p&gt;  Il a contribué à façonner la  &lt;a href=&quot;https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie&quot;  title=&quot;Le Stoïcisme par apprendre la philo&quot;&gt;pensée stoïcienne&lt;/a&gt; en l'adaptant aux besoins de son temps en la conciliant  avec d'autres courants philosophiques comme l'épicurisme et le scepticisme. Il rompt avec les dogmes stoïciens. « Il nie la conflagration universelle et croit à l'éternité d'un monde que la Providence rend parfait ». &lt;/p&gt; &lt;p&gt; Il se défie de la mantique (la divination) et nie l'immortalité de l'âme. Il reconnaît en nous, à côté des impulsions de l'instinct premier, des tendances fondamentales où s'associent nature et raison. &lt;/p&gt; &lt;p&gt; Il aboutit à un humanisme, il tend à une sérénité morale faite de calme, de mesure, d'harmonie. Il a également développé la notion de justice naturelle, qui est une forme de justice qui découle de la nature même de l'homme et de la société, et qui est différente de la justice conventionnelle établie par les lois et les coutumes.&lt;/p&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E62" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Posidonios&quot;  title=&quot; Wikipedia&quot;&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href=&quot;https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770&quot;  title=&quot;Posidonius d'Apamée théoricien de la géométrie par Persée&quot;&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href=&quot;https://www.youtube.com/watch?v=EqU-kD8dW4Y&quot; title=&quot;Grèce antique - 33 La civilisation hellénistique par Yannick Rub&quot;&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289&quot;  title=&quot;La philosophiede Posidonius par Persee&quot;&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; "/>
+    <hyperlink ref="E68" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que&quot; title=&quot; Wikipedia&quot;&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href=&quot;https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Le Stoïcisme par le Précepteur&quot;&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=J3wZoqElCgs&quot; title=&quot;Who is Seneca par Daily Stoic &quot;&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href=&quot;https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin&quot; title=&quot;La vie Heureuse par Karl Baudoin&quot;&gt; &quot;une vie heureuse&quot;.&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : - De la brièveté de la vie (consideration sur l’usage du temps). - De la colère (sur la maîtrise de cette passion destructive). - De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt;  est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href=&quot;https://www.youtube.com/watch?v=d_cge9OwVAs&quot; title=&quot;La vie philosophique de Sénèque par Kosmos&quot;&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title=&quot;Les lettres à Lucilius – Senèque  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="E69" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;AMMONIOS d'Athènes&lt;/a&gt; était un philosophe platonicien originaire d'Égypte, qui enseigna à Athènes et fut l'un des maîtres de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Plutarque&quot; style=&quot;color:#6A142A&quot; title=&quot;Plutarque sur Wikipedia&quot;&gt;Plutarque&lt;/a&gt;. Représentant du médio-platonisme, il cherchait à concilier la philosophie de Platon avec d'autres courants de pensée de l'Antiquité tardive.&lt;/p&gt; &lt;p&gt;Son enseignement oral laissa une empreinte durable sur ses disciples, bien qu'il n'ait laissé aucun écrit. Il défendait une lecture spirituelle et morale du platonisme, insistant sur la contemplation du Bien et la purification de l'âme. Plutarque, son élève le plus illustre, rapporte ses enseignements dans ses &lt;em&gt;Moralia&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Ammonios d'Athènes appartient à ce courant de platoniciens qui, entre Platon et Plotin, ont préparé le terrain au &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;, en développant une exégèse du &lt;em&gt;Timée&lt;/em&gt; et de la &lt;em&gt;République&lt;/em&gt;. Sa discrétion littéraire contraste avec l'influence considérable qu'il exerça sur le cercle intellectuel d'Athènes de son époque.&lt;/p&gt;"/>
+    <hyperlink ref="H79" r:id="rId15" display="https://www.laphilo.fr/pho/jamblique-mini.webp"/>
+    <hyperlink ref="H86" r:id="rId16" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="H87" r:id="rId17" display="https://www.laphilo.fr/pho/scyrene-mini.webp"/>
+    <hyperlink ref="E88" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot;   title=&quot;Proclus par Wikipédia&quot;&gt; PROCLUS&lt;/a&gt; était un philosophe &lt;a href=&quot;https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D&quot;   title=&quot;Le Néoplatonisme par Anne Baudart&quot;&gt; Néoplatonicien grec&lt;/a&gt; et il est considéré comme l'un des derniers grands philosophes de l'Antiquité classique.&lt;/p&gt;&#10;&lt;p&gt; Sa philosophie est basée sur les enseignements de Platon et d'Aristote. Il a développé une théorie complexe de l'univers qui est basée sur l'idée d'une hiérarchie de réalités. Au sommet de cette hiérarchie se trouve l'Un, qui est la réalité ultime et incompréhensible. Voici les principaux concepts de la philosophie de Proclus :&lt;/p&gt;&#10;&lt;dd&gt;L'Un : Réalité ultime et incompréhensible, qui est la source de toutes choses.&lt;/dd&gt;&#10;&lt;dd&gt;Le Démiurge : Force créatrice qui a donné forme à l'univers.&lt;/dd&gt;&#10;&lt;dd&gt;Les dieux : Intermédiaires entre l'Un et le monde sensible.&lt;/dd&gt;&#10;&lt;dd&gt;Les âmes : Principes vitaux qui animent les êtres vivants.&lt;/dd&gt;&#10;&lt;dd&gt;La matière : Réalité la plus basse de la hiérarchie, source du changement et de la corruption.&lt;/dd&gt;&#10;&lt;p&gt; Il a écrit un grand nombre &lt;a href=&quot;https://remacle.org/bloodwolf/philosophes/proclus/table.htm&quot;   title=&quot;Proclus par Philippe Remacle&quot;&gt; d'ouvrages sur la philosophie&lt;/a&gt;, dont les plus importants sont &lt;a href=&quot;https://www.youtube.com/watch?v=SJK1kbyXXno&quot;   title=&quot;Les éléments de Théologie de Proclus par LabEx HaStec&quot;&gt; les Commentaires sur le Timée de Platon&lt;/a&gt;, les Éléments de théologie et les Hypotyposes platonicae. Ces ouvrages ont été d'une grande influence sur la philosophie occidentale, et ils continuent à être étudiés aujourd'hui. &lt;/p&gt;   &lt;audio controls title=&quot; Proclus, un philosophe étoilé par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;"/>
+    <hyperlink ref="E89" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;HERMIAS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien, élève du grand &lt;a href=&quot;https://fr.wikipedia.org/wiki/Syrianos&quot; title=&quot;Syrianus sur Wikipedia&quot;&gt;Syrianus&lt;/a&gt; à Athènes. De retour à Alexandrie, il y fonda une école philosophique et épousa Aidésia, dont il eut pour fils le célèbre Ammonios d'Alexandrie.&lt;/p&gt; &lt;p&gt;Son œuvre principale est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes prises lors des cours de Syrianus. Cet ouvrage, qui nous est parvenu, offre une interprétation allégorique et métaphysique du dialogue platonicien sur l'amour, l'âme et la beauté, dans la tradition néoplatonicienne.&lt;/p&gt; &lt;p&gt;Hermias s'inscrit dans la lignée des maîtres qui firent d'Alexandrie un foyer majeur de la pensée antique tardive. Son rôle de transmetteur entre l'école d'Athènes et celle d'Alexandrie fut déterminant pour la pérennité du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;. Sa mort prématurée laissa Aidésia seule pour assurer l'avenir philosophique de leurs fils.&lt;/p&gt;"/>
+    <hyperlink ref="H91" r:id="rId20" display="https://www.laphilo.fr/pho/damascios-mini.webp"/>
+    <hyperlink ref="E92" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;AMMONIOS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien de la fin de l'Antiquité, fils d'Hermias et d'Aidésia, tous deux philosophes. Il succéda à Proclos comme tête de l'école néoplatonicienne d'Athènes et dirigea l'école alexandrine, formant une génération de commentateurs d'Aristote comme Olympiodore, Jean Philopon ou Simplicius, dans un contexte de tensions entre païens et chrétiens. Il enseigna l'Aristote aux païens et le Platon aux chrétiens pour favoriser une harmonie entre doctrines. &lt;/p&gt; &lt;p&gt; Spécialiste des commentaires d'Aristote, il défendit une interprétation néoplatonicienne unifiant Aristote et Platon : Aristote prépare à Platon, l'âme s'élève de la matière à l'Intellect divin. Ses écrits, perdus sauf fragments, insistent sur la théurgie et l'exégèse allégorique.&lt;/p&gt; &lt;p&gt; Son école alexandrine préserva le corpus aristotélicien pour l'Islam et l'Occident médiéval. &lt;/p&gt; Aucun texte complet ne survit directement, mais ses leçons sont préservées via les commentaires de ses élèves, comme ceux de Philopon sur l'Isagogè. Il chercha à harmoniser les deux grands penseurs antiques pour préserver la tradition païenne face au christianisme dominant.https://www.ljallamion.fr/spip.php?article6169 &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E93" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isidore_de_Gaza&quot; title=&quot;Wikipedia&quot;&gt;ISIDORE de Gaza&lt;/a&gt; était un philosophe néoplatonicien, né à Gaza en Palestine. Maître de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Damascios&quot; title=&quot;Damascios sur Wikipedia&quot;&gt;Damascios&lt;/a&gt;, le dernier scholarque de l'Académie d'Athènes, il fut l'un des derniers grands représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot;  title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique.&lt;/p&gt; &lt;p&gt;Damascios lui consacra une biographie dans sa &lt;em&gt;Vie d'Isidore&lt;/em&gt; (aussi connue sous le nom de &lt;em&gt;Vie des philosophes&lt;/em&gt;), où il le dépeint comme un personnage d'une grande intégrité morale, attaché aux traditions philosophiques grecques et à la piété envers les dieux, dans un contexte où le christianisme triomphait. Isidore représentait une philosophie vécue comme exercice spirituel, alliant rigueur intellectuelle et pratique ascétique.&lt;/p&gt; &lt;p&gt;Sa pensée s'inscrit dans la grande tradition de l'école néoplatonicienne d'Athènes, héritière de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot; title=&quot;Proclus sur Wikipedia&quot;&gt;Proclus&lt;/a&gt;. Il incarne ces penseurs de la fin du paganisme grec qui, face à la montée de la chrétienté, s'accrochaient à la philosophie comme à une forme de spiritualité rationnelle et contemplative, gardienne de l'héritage intellectuel de la Grèce.&lt;/p&gt;"/>
+    <hyperlink ref="H93" r:id="rId23" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="H96" r:id="rId24" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="E97" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Simplicius_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698&quot; style=&quot;color:#88A1E9&quot; title=&quot;A propos de la biographie de Simplicius par Persée&quot;&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le &quot;Manuel d’Épictète&quot; et, selon la tradition, sur &quot;De l’âme&quot;. Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href=&quot;https://www.youtube.com/watch?v=C17VYcyLkiY&quot; style=&quot;color:#88A1E9&quot; title=&quot;SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions&quot;&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.  &lt;a href=&quot;https://www.youtube.com/watch?v=6a4uQpmGsUg&quot; style=&quot;color:#88A1E9&quot; title=&quot;Simplicius – The Last Guardian of Ancient Philosophy par A time in history&quot;&gt; Transmis et traduits&lt;/a&gt; dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; "/>
+    <hyperlink ref="E100" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Priscien_de_Lydie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316&quot; title=&quot;la géographie et les originesnéoplatonisme sur Persee&quot;&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité :  - « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. - « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;"/>
+    <hyperlink ref="E102" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;EULAMIOS de Phrygie&lt;/a&gt; était un philosophe néoplatonicien du VIe siècle, originaire de Phrygie en Asie Mineure (actuelle Turquie). Il appartient au cercle des derniers représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique, dont il perpétua la tradition après la fermeture de l'Académie d'Athènes par Justinien en 529.&lt;/p&gt; &lt;p&gt;Figure peu documentée de cette période de transition, il s'inscrit dans le mouvement de philosophes néoplatoniciens qui, après l'exil perse et la dispersion de l'école athénienne, continuèrent à enseigner et transmettre la philosophie grecque en dehors des institutions officielles. Ses liens avec les cercles de Damascios et Simplicius laissent penser qu'il participa à la préservation du corpus philosophique antique.&lt;/p&gt; &lt;p&gt;Eulamios représente la philosophie de survie du néoplatonisme face à la christianisation de l'Empire. Comme ses contemporains, il incarne la volonté de maintenir vivante une tradition intellectuelle millénaire, préservant ainsi les conditions de la redécouverte médiévale et renaissante de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_antique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie antique sur Wikipedia&quot;&gt;philosophie antique&lt;/a&gt;.&lt;/p&gt;"/>
+    <hyperlink ref="H102" r:id="rId28" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="E103" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie&quot; title=&quot;Wikipedia&quot;&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.https://fr.wikipedia.org/wiki/Diogène_de_Phénicie    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -7639,11 +7639,15 @@
       <c r="A93" s="7" t="n">
         <v>453</v>
       </c>
-      <c r="B93" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>747</v>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">453 – 520</t>
+        </is>
       </c>
       <c r="D93" s="8" t="s">
         <v>748</v>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3661,150 +3661,151 @@
         </is>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7">
+        <v>-565</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-500</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">565 A JC - 500 A JC</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7">
         <v>-550</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B12" s="7">
         <v>-480</v>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">VIe siècle A JC</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">THÉANO</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Théano_(pythagoricienne)" title=" Wikipedia"&gt;THÉANO&lt;/a&gt; est une philosophe grecque du VIe siècle avant J.-C., membre de la communauté fondée par Pythagore à Crotone, en Grande-Grèce (le sud de l'Italie). Les sources anciennes la présentent tantôt comme l'épouse de Pythagore et la mère de ses enfants, tantôt comme l'épouse de Brontinos et simple disciple du maître. Il est même possible que plusieurs philosophes pythagoriciennes aient porté ce nom.&lt;/p&gt; &lt;p&gt;L'école pythagoricienne avait ceci de remarquable qu'elle accueillait des femmes, ce qui était rare dans le monde grec. On attribue à Théano des traités &lt;em&gt;De la piété&lt;/em&gt; et &lt;em&gt;De la vertu&lt;/em&gt;, des conseils aux femmes, des apophtegmes et plusieurs lettres. Dans l'une d'elles, elle affirme que le nombre n'est pas la substance des choses mais le principe de leur ordre, ce qui nuance la doctrine attribuée à Pythagore.&lt;/p&gt; &lt;p&gt;La tradition rapporte de nombreuses sentences de Théano sur la vie des femmes et la vertu. À une femme qui lui demandait combien de temps après avoir été avec un homme elle pouvait se rendre au temple, elle aurait répondu : « avec son mari, aussitôt ; avec un autre, jamais ». On lui prête aussi la direction de l'école pythagoricienne après la mort de Pythagore, avec leurs enfants, ce qui ferait d'elle l'une des premières femmes à la tête d'une école de philosophie.&lt;/p&gt; &lt;p&gt;La plupart de ces écrits sont sans doute &lt;a href="https://fr.wikipedia.org/wiki/Apocryphe_biblique" title=" Wikipedia"&gt;apocryphes&lt;/a&gt;, rédigés plusieurs siècles plus tard par des pythagoriciens qui se plaçaient sous son autorité. Leur existence même montre pourtant que Théano était restée, dans la mémoire antique, le modèle de la femme philosophe, alliant sagesse morale, réflexion sur l'harmonie du monde et vie communautaire.&lt;/p&gt;  &lt;audio controls title="la vie et l'oeuvre de Pythagore et de sa femme THEANO"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10212-08.01.2008-ITEMA_20104885-2008F10732S0008-27.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">UktaE9uuYao</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">"Theano (fl. 6th century BCE) | AI Podcast" par AI History of Western Philosophy</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/theano-mini.webp</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Grecque</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Pythagorisme</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">philosophe pythagoricienne, présentée comme l'épouse ou la disciple de Pythagore.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P11">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P12">
         <v>2</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
+    <row r="13" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
         <v>-535</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B13" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D13" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclite"  style="color:#6A142A"  title=" Wikipedia"&gt;HÉRACLITE&lt;/a&gt; d’Éphèse (vers 544-480 av. J.-C.) est un philosophe présocratique grec de &lt;a href="https://archive.org/details/histoiredelaphil00mall/page/116/mode/2up" style="color:#88A1E9"   title="L'école Ionienne par internet archive"&gt;l’école ionienne&lt;/a&gt;. Issu d’une famille royale de la cité, il aurait cédé son titre à son frère pour se consacrer à la réflexion, méprisant la foule comme les savants réputés. Son livre, déposé, dit-on, dans le temple d’Artémis, ne nous est parvenu qu’en une centaine de fragments, aphorismes si énigmatiques qu’on l’a surnommé « l’Obscur ».&lt;/p&gt; &lt;p&gt;Héraclite est le penseur du devenir, d’où le nom de &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclit%C3%A9isme"  style="color:#88A1E9"  title="Le Mobilisme par Wikipedia"&gt;mobilisme&lt;/a&gt; donné à sa doctrine, résumée plus tard par la formule &lt;a href="http://www.etienne-barilier.name/Conferences/2011/Panta_rhei%20.pdf"  style="color:#88A1E9"  title="Conférence 'panta rhei' par Etienne Barilier"&gt;&lt;em&gt;panta rhei&lt;/em&gt;&lt;/a&gt;, « tout s’écoule » : « On ne se baigne jamais deux fois dans le même fleuve. » &lt;a href="https://www.youtube.com/watch?v=rbgWLqDwEjs&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Rien n'est figé par Le Précepteur"&gt;Rien n’est figé&lt;/a&gt; : le jour et la nuit, la vie et la mort, le chaud et le froid passent l’un dans l’autre. Ce changement n’est pourtant pas un désordre : il est réglé par le &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1986_num_99_470_1455"  style="color:#88A1E9"  title="Le Logos selon Héraclite par Persée"&gt;&lt;em&gt;logos&lt;/em&gt;&lt;/a&gt;, la raison ou la loi commune de toutes choses, que la plupart des hommes ne comprennent pas. Le monde naît de la lutte des contraires : « La guerre est le père de toutes choses. » L’harmonie elle-même est une tension, comme celle de l’arc ou de la lyre. Le feu, toujours changeant et toujours le même, en est le symbole : le monde est « un feu toujours vivant, qui s’allume avec mesure et s’éteint avec mesure ». Héraclite invite chacun à suivre &lt;a href="https://www.youtube.com/watch?v=-fzeW9YP8TI&amp;ab_channel=Lepayssanschemin"  style="color:#88A1E9"  title="L'éveil de la raison par Le pays sans chemin"&gt;la raison&lt;/a&gt; commune plutôt que ses opinions : « Le caractère, pour l’homme, est son destin. »&lt;/p&gt; &lt;p&gt;Platon, les stoïciens, puis Hegel, Nietzsche et Heidegger ont vu en lui l’un des plus profonds penseurs grecs.&lt;/p&gt;  &lt;audio controls title="Thèmes et controverses- l'héritage d'Héraclite par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/10/s41/RF_CD1E6508-A3E8-4B48-BFCF-A6BC3A6CA34B_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>-515</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>94</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="2" t="s">
@@ -3813,13 +3814,11 @@
       <c r="K13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Présocratique ; Éléatisme</t>
-        </is>
+      <c r="L13" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -3830,30 +3829,34 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
-        <v>-500</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>97</v>
+        <v>-515</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-470</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">515 A JC - 470 A JC</t>
+        </is>
       </c>
       <c r="D14" s="8" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="2" t="s">
@@ -3862,57 +3865,60 @@
       <c r="K14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>25</v>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Présocratique ; Éléatisme</t>
+        </is>
       </c>
       <c r="M14" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="191.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
-        <v>-495</v>
+        <v>-500</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>107</v>
+        <v>98</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Présocratique ; Pluralisme</t>
-        </is>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>111</v>
+        <v>34</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3920,45 +3926,45 @@
         </is>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="191.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
-        <v>-490</v>
+        <v>-495</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Protagoras"  title="Protagoras par Wikipédia"&gt;PROTAGORAS&lt;/a&gt; d’Abdère (vers 490 - vers 420 av. J.-C.) est le plus célèbre &lt;a href="https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;ab_channel=Bibiclo" style="color:#88A1E9"   title="Les Sophistes par Bobiclo"&gt;des sophistes&lt;/a&gt;, ces maîtres itinérants qui enseignaient, contre rémunération, l’art de bien parler et de réussir dans la cité. Il séjourne souvent à Athènes, où il fréquente Périclès, qui lui aurait confié la rédaction des lois de Thourioi, colonie fondée en 444 av. J.-C. Platon lui consacre un dialogue, le &lt;em&gt;Protagoras&lt;/em&gt;, et discute sa pensée dans le &lt;em&gt;Théétète&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Il donne &lt;a href="https://www.youtube.com/watch?v=X5bZKSCfc_g&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Rhétorique et relativisme par Alain Bajomée"&gt;des cours de rhétorique&lt;/a&gt; et d’éloquence, et promet de rendre ses élèves meilleurs citoyens. Sa formule la plus célèbre ouvre son traité &lt;em&gt;La Vérité&lt;/em&gt; : « L’homme est la mesure de toutes choses : de celles qui sont, qu’elles sont, de celles qui ne sont pas, qu’elles ne sont pas. » Le vent est froid pour qui a froid, chaud pour qui a chaud : chaque perception est vraie pour celui qui l’éprouve. Cette thèse fonde ce que l’on appelle &lt;a href="https://www.youtube.com/watch?v=LxSCq1F7pSk&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Le relativisme par le Précepteur"&gt;le relativisme&lt;/a&gt;. Il enseigne aussi que sur tout sujet on peut soutenir deux thèses opposées, et qu’il faut savoir rendre plus forte la thèse la plus faible.&lt;/p&gt; &lt;p&gt;Sur les dieux, il se déclare incapable de savoir s’ils existent ou non, « car beaucoup de choses empêchent de le savoir : l’obscurité de la question et la brièveté de la vie humaine ». Selon une tradition tardive, ce livre lui aurait valu d’être accusé d’impiété à Athènes. Socrate et Platon lui reprochent de réduire la vérité à l’opinion, mais il reste le premier penseur à faire de l’homme le centre de la réflexion philosophique.&lt;/p&gt;  &lt;audio controls title="Platon vs. Protagoras: l'homme est il la mesure de toutes choses? par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/09/s40/NET_FC_f081bba4-88ba-4b62-930d-2c30e49863d9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
+        <v>106</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>107</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>121</v>
+        <v>59</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Présocratique ; Pluralisme</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3966,228 +3972,228 @@
         </is>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
         <v>-490</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Z%C3%A9non_d%27%C3%89l%C3%A9e"  title=" Wikipedia"&gt;ZÉNON d'Élée&lt;/a&gt; était  est un philosophie grec, principalement connu pour ses paradoxes qui ont influencé la pensée philosophique et mathématique pendant des siècles. Il visent à défendre les &lt;a href="https://www.youtube.com/watch?v=0rtwZaOyk-k&amp;t=67s"  style="color:#88A1E9" title="  ZÉNON et les paradoxes par Alain Bajoumée"&gt;thèses de Parménide&lt;/a&gt; en montrant les contradictions et les absurdités qui découlent de la croyance en la pluralité et le mouvement. Ses arguments sont souvent considérés comme des défis intellectuels pour comprendre la nature de l'espace, du temps et du mouvement. &lt;/p&gt; &lt;p&gt; Il a formulé  &lt;a href="https://www.youtube.com/watch?v=Gfci1UTuxCA"  title="Les 4 paradoxes de Zénon par Maêl Cavan"&gt;plusieurs paradoxes&lt;/a&gt;, dont les plus célèbres sont : &lt;/p&gt; &lt;p&gt;La Dichotomie : Pour parcourir une distance, il faut d'abord parcourir la moitié de cette distance, puis la moitié de la moitié, et ainsi de suite à l'infini. 
-Conclusion : Le mouvement ne peut jamais commencer, car il y a une infinité de distances à parcourir. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=2yfRRIbvF0g"  title=" Le paradoxe d'Achille et de la tortue par Coursitout"&gt;Achille et la tortue&lt;/a&gt; : Achille, le coureur le plus rapide, ne peut jamais rattraper une tortue qui a une avance, car il doit d'abord atteindre le point de départ de la tortue, puis le point suivant où elle se sera déplacée, et ainsi de suite.  Conclusion : Le mouvement est une illusion. &lt;/p&gt; &lt;p&gt;La flèche : À chaque instant, une flèche en vol occupe une position précise dans l'espace, immobile par rapport à cet instant. Conclusion : Si le temps est composé d'instants, la flèche ne bouge jamais réellement. &lt;/p&gt; &lt;p&gt; Le stade : Ce paradoxe met en évidence des contradictions dans la notion de relativité du mouvement en imaginant des objets se déplaçant dans des directions opposées. &lt;/p&gt; &lt;p&gt; Les paradoxes de Zénon ne visent pas à nier l'existence du mouvement ou de la pluralité, mais à montrer que ces concepts, tels que nous les comprenons, conduisent à des contradictions logiques. Ils soutiennent ainsi la thèse de Parménide selon laquelle la réalité est une et immuable, et que les apparences sensibles sont trompeuses.  Avec le développement du calcul infinitésimal, ils ont été partiellement résolus en montrant que des séries infinies peuvent converger vers une limite finie. &lt;/p&gt; </t>
+        <v>114</v>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Protagoras"  title="Protagoras par Wikipédia"&gt;PROTAGORAS&lt;/a&gt; d’Abdère (vers 490 - vers 420 av. J.-C.) est le plus célèbre &lt;a href="https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;ab_channel=Bibiclo" style="color:#88A1E9"   title="Les Sophistes par Bobiclo"&gt;des sophistes&lt;/a&gt;, ces maîtres itinérants qui enseignaient, contre rémunération, l’art de bien parler et de réussir dans la cité. Il séjourne souvent à Athènes, où il fréquente Périclès, qui lui aurait confié la rédaction des lois de Thourioi, colonie fondée en 444 av. J.-C. Platon lui consacre un dialogue, le &lt;em&gt;Protagoras&lt;/em&gt;, et discute sa pensée dans le &lt;em&gt;Théétète&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Il donne &lt;a href="https://www.youtube.com/watch?v=X5bZKSCfc_g&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Rhétorique et relativisme par Alain Bajomée"&gt;des cours de rhétorique&lt;/a&gt; et d’éloquence, et promet de rendre ses élèves meilleurs citoyens. Sa formule la plus célèbre ouvre son traité &lt;em&gt;La Vérité&lt;/em&gt; : « L’homme est la mesure de toutes choses : de celles qui sont, qu’elles sont, de celles qui ne sont pas, qu’elles ne sont pas. » Le vent est froid pour qui a froid, chaud pour qui a chaud : chaque perception est vraie pour celui qui l’éprouve. Cette thèse fonde ce que l’on appelle &lt;a href="https://www.youtube.com/watch?v=LxSCq1F7pSk&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Le relativisme par le Précepteur"&gt;le relativisme&lt;/a&gt;. Il enseigne aussi que sur tout sujet on peut soutenir deux thèses opposées, et qu’il faut savoir rendre plus forte la thèse la plus faible.&lt;/p&gt; &lt;p&gt;Sur les dieux, il se déclare incapable de savoir s’ils existent ou non, « car beaucoup de choses empêchent de le savoir : l’obscurité de la question et la brièveté de la vie humaine ». Selon une tradition tardive, ce livre lui aurait valu d’être accusé d’impiété à Athènes. Socrate et Platon lui reprochent de réduire la vérité à l’opinion, mais il reste le premier penseur à faire de l’homme le centre de la réflexion philosophique.&lt;/p&gt;  &lt;audio controls title="Platon vs. Protagoras: l'homme est il la mesure de toutes choses? par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/09/s40/NET_FC_f081bba4-88ba-4b62-930d-2c30e49863d9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F17" s="7" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Présocratique ; Éléatisme</t>
-        </is>
+        <v>119</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="18" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
-        <v>-480</v>
+        <v>-490</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gorgias" title=" Wikipedia"&gt;GORGIAS&lt;/a&gt; était un philosophe présocratique et l'une des figures les plus importantes de la &lt;a href="https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;t=184s" title=" Les sophistes par Bibiclo"&gt;sophistique&lt;/a&gt;.  Contrairement aux philosophes comme Platon ou Aristote, qui cherchaient à découvrir des vérités universelles en mettant l'accent sur l'importance de l'opinion et de la persuasion dans les affaires humaines.  Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;"Sur le Non-Être ou sur la Nature" : Il développe une argumentation radicale qui remet en question la possibilité même de la connaissance et de la communication.&lt;/p&gt; &lt;p&gt;Il soutient trois thèses principales : Rien n'existe. Si quelque chose existait, nous ne pourrions pas le connaître. Si nous pouvions le connaître, nous ne pourrions pas le communiquer aux autres. &lt;/p&gt; &lt;p&gt; Ces thèses sont souvent interprétées comme une critique de l'ontologie éléatique, notamment des idées de Parménide, qui affirmait que l'être est un et immuable. &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89loge_d%27H%C3%A9l%C3%A8ne "  title=" Gorgias Eloge d’Helene  parWikipedia"&gt;"Éloge d'Hélène"&lt;/a&gt;  : Dans ce discours, Il défend Hélène de Troie, souvent considérée comme responsable de la guerre de Troie. Il utilise des arguments rhétoriques pour montrer qu'elle ne peut être tenue pour responsable, car elle a été soit victime de la volonté des dieux, soit de la séduction de Pâris, soit de la force.  &lt;/p&gt; &lt;p&gt;"Défense de Palamède" : Dans ce discours, il défend Palamède, un héros grec accusé de trahison par Ulysse. Il utilise des arguments logiques et rhétoriques pour démontrer son l'innocence, montrant ainsi la puissance de la parole pour influencer les jugements. &lt;p&gt; Il  est souvent considéré comme un relativiste et un sceptique. Il met en doute la possibilité de connaître la vérité absolue et souligne l'importance de la persuasion dans les affaires humaines. Sa philosophie a eu une influence significative sur la pensée grecque, notamment sur Platon, qui le critique sévèrement dans son dialogue "Gorgias". Platon y oppose la recherche de la vérité à l'art de la persuasion, qu'il associe à la sophistique. &lt;/p&gt; 
-</t>
+        <v>124</v>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Z%C3%A9non_d%27%C3%89l%C3%A9e"  title=" Wikipedia"&gt;ZÉNON d'Élée&lt;/a&gt; était  est un philosophie grec, principalement connu pour ses paradoxes qui ont influencé la pensée philosophique et mathématique pendant des siècles. Il visent à défendre les &lt;a href="https://www.youtube.com/watch?v=0rtwZaOyk-k&amp;t=67s"  style="color:#88A1E9" title="  ZÉNON et les paradoxes par Alain Bajoumée"&gt;thèses de Parménide&lt;/a&gt; en montrant les contradictions et les absurdités qui découlent de la croyance en la pluralité et le mouvement. Ses arguments sont souvent considérés comme des défis intellectuels pour comprendre la nature de l'espace, du temps et du mouvement. &lt;/p&gt; &lt;p&gt; Il a formulé  &lt;a href="https://www.youtube.com/watch?v=Gfci1UTuxCA"  title="Les 4 paradoxes de Zénon par Maêl Cavan"&gt;plusieurs paradoxes&lt;/a&gt;, dont les plus célèbres sont : &lt;/p&gt; &lt;p&gt;La Dichotomie : Pour parcourir une distance, il faut d'abord parcourir la moitié de cette distance, puis la moitié de la moitié, et ainsi de suite à l'infini. 
+Conclusion : Le mouvement ne peut jamais commencer, car il y a une infinité de distances à parcourir. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=2yfRRIbvF0g"  title=" Le paradoxe d'Achille et de la tortue par Coursitout"&gt;Achille et la tortue&lt;/a&gt; : Achille, le coureur le plus rapide, ne peut jamais rattraper une tortue qui a une avance, car il doit d'abord atteindre le point de départ de la tortue, puis le point suivant où elle se sera déplacée, et ainsi de suite.  Conclusion : Le mouvement est une illusion. &lt;/p&gt; &lt;p&gt;La flèche : À chaque instant, une flèche en vol occupe une position précise dans l'espace, immobile par rapport à cet instant. Conclusion : Si le temps est composé d'instants, la flèche ne bouge jamais réellement. &lt;/p&gt; &lt;p&gt; Le stade : Ce paradoxe met en évidence des contradictions dans la notion de relativité du mouvement en imaginant des objets se déplaçant dans des directions opposées. &lt;/p&gt; &lt;p&gt; Les paradoxes de Zénon ne visent pas à nier l'existence du mouvement ou de la pluralité, mais à montrer que ces concepts, tels que nous les comprenons, conduisent à des contradictions logiques. Ils soutiennent ainsi la thèse de Parménide selon laquelle la réalité est une et immuable, et que les apparences sensibles sont trompeuses.  Avec le développement du calcul infinitésimal, ils ont été partiellement résolus en montrant que des séries infinies peuvent converger vers une limite finie. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F18" s="7" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Présocratique ; Éléatisme</t>
+        </is>
       </c>
       <c r="M18" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
-        <v>-470</v>
+        <v>-480</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Socrate"  style="color:#6A142A"  title=" Wikipedia"&gt;SOCRATE&lt;/a&gt; est considéré comme l'un des &lt;a href="https://www.youtube.com/watch?v=oMCwc1u3sd4&amp;ab_channel=Diligoinveritate%28Fr%29" style="color:#88A1E9"   title="La naissance de la Philosophie par Planète"&gt;pères de la philosophie  morale occidentale&lt;/a&gt; et de la méthode dialectique. Il n'a pas laissé de textes écrits, mais ses idées ont été transmises à travers les dialogues de Platon, qui était l'un de ses disciples les plus célèbres.&lt;/p&gt; &lt;p&gt; Sa philosophie de l'école met l'accent le &lt;a href="https://www.youtube.com/watch?v=iP6zV74nYzM" style="color:#88A1E9"   title="La face sombre de la démocratie l'avertissement de Socrate que nous ignorons par C'est Stoique"&gt; bien être de la cité&lt;/a&gt; et sur l'importance de la connaissance de soi et de la recherche de la vérité par le biais de la discussion et de l'examen critique. &lt;/p&gt;&lt;p&gt;  Sa méthode de questionnement appelée  &lt;a href="https://www.youtube.com/watch?v=QJFdcQYBkDY&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="La Maïeutique par le Précepteur"&gt; Maïeutique&lt;/a&gt;, qui consiste à poser des questions pour amener son interlocuteur à examiner ses croyances et à découvrir la vérité par lui-même. Il ne prétendait pas détenir des réponses, mais cherchait à stimuler la réflexion critique. &lt;/p&gt; &lt;p&gt;Ironie socratique : Il feignait souvent l'ignorance pour inciter les autres à exposer leurs idées.&lt;/p&gt; &lt;p&gt;Questionnement : Il posait des questions comme "Qu'est-ce que la justice ?" ou "Qu'est-ce que le courage ?" pour explorer des concepts fondamentaux. &lt;/p&gt; &lt;p&gt;  Il croyait que la vertu est une forme de connaissance et que nul ne fait le mal volontairement. Selon lui, si les gens comprenaient vraiment ce qui est bien, ils agiraient en conséquence. Sers citations les plus célèbres : &lt;/p&gt; &lt;p&gt;Connais-toi toi-même : Cette maxime, inscrite au fronton du temple de Delphes, résume l'importance qu'il accordait à l'introspection et à la connaissance de soi. &lt;/p&gt; &lt;p&gt;La vie examinée : Il affirmait que "une vie sans examen ne vaut pas la peine d'être vécue", soulignant l'importance de la réflexion philosophique.&lt;/p&gt; &lt;p&gt; Il fut accusé d'empiété et de corruption de la jeunesse par Mélétos, un poète de son époque et &lt;a href="https://www.youtube.com/watch?v=3h_6zy58acE&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Son procès et sa condamnation à mort par le Précepteur"&gt;condamné à mort&lt;/a&gt; après un procès où il accepta son sort.  Il a révolutionné la pensée occidentale en mettant l'accent sur la raison, l'éthique et l'importance de questionner les certitudes. Son héritage continue d'inspirer les philosophes et les chercheurs de vérité à travers les âges.&lt;/p&gt;  &lt;audio controls title="Socrate est il de son temps par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-17.07.2023-ITEMA_23428681-2022C48904S0325-NET_MFC_3B8967BE-C9AF-46ED-A1B8-02CA5C79BDCD-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        <v>133</v>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gorgias" title=" Wikipedia"&gt;GORGIAS&lt;/a&gt; était un philosophe présocratique et l'une des figures les plus importantes de la &lt;a href="https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;t=184s" title=" Les sophistes par Bibiclo"&gt;sophistique&lt;/a&gt;.  Contrairement aux philosophes comme Platon ou Aristote, qui cherchaient à découvrir des vérités universelles en mettant l'accent sur l'importance de l'opinion et de la persuasion dans les affaires humaines.  Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;"Sur le Non-Être ou sur la Nature" : Il développe une argumentation radicale qui remet en question la possibilité même de la connaissance et de la communication.&lt;/p&gt; &lt;p&gt;Il soutient trois thèses principales : Rien n'existe. Si quelque chose existait, nous ne pourrions pas le connaître. Si nous pouvions le connaître, nous ne pourrions pas le communiquer aux autres. &lt;/p&gt; &lt;p&gt; Ces thèses sont souvent interprétées comme une critique de l'ontologie éléatique, notamment des idées de Parménide, qui affirmait que l'être est un et immuable. &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89loge_d%27H%C3%A9l%C3%A8ne "  title=" Gorgias Eloge d’Helene  parWikipedia"&gt;"Éloge d'Hélène"&lt;/a&gt;  : Dans ce discours, Il défend Hélène de Troie, souvent considérée comme responsable de la guerre de Troie. Il utilise des arguments rhétoriques pour montrer qu'elle ne peut être tenue pour responsable, car elle a été soit victime de la volonté des dieux, soit de la séduction de Pâris, soit de la force.  &lt;/p&gt; &lt;p&gt;"Défense de Palamède" : Dans ce discours, il défend Palamède, un héros grec accusé de trahison par Ulysse. Il utilise des arguments logiques et rhétoriques pour démontrer son l'innocence, montrant ainsi la puissance de la parole pour influencer les jugements. &lt;p&gt; Il  est souvent considéré comme un relativiste et un sceptique. Il met en doute la possibilité de connaître la vérité absolue et souligne l'importance de la persuasion dans les affaires humaines. Sa philosophie a eu une influence significative sur la pensée grecque, notamment sur Platon, qui le critique sévèrement dans son dialogue "Gorgias". Platon y oppose la recherche de la vérité à l'art de la persuasion, qu'il associe à la sophistique. &lt;/p&gt; 
+</t>
         </is>
       </c>
       <c r="F19" s="7" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="20" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
         <v>-470</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Socrate"  style="color:#6A142A"  title=" Wikipedia"&gt;SOCRATE&lt;/a&gt; est considéré comme l'un des &lt;a href="https://www.youtube.com/watch?v=oMCwc1u3sd4&amp;ab_channel=Diligoinveritate%28Fr%29" style="color:#88A1E9"   title="La naissance de la Philosophie par Planète"&gt;pères de la philosophie  morale occidentale&lt;/a&gt; et de la méthode dialectique. Il n'a pas laissé de textes écrits, mais ses idées ont été transmises à travers les dialogues de Platon, qui était l'un de ses disciples les plus célèbres.&lt;/p&gt; &lt;p&gt; Sa philosophie de l'école met l'accent le &lt;a href="https://www.youtube.com/watch?v=iP6zV74nYzM" style="color:#88A1E9"   title="La face sombre de la démocratie l'avertissement de Socrate que nous ignorons par C'est Stoique"&gt; bien être de la cité&lt;/a&gt; et sur l'importance de la connaissance de soi et de la recherche de la vérité par le biais de la discussion et de l'examen critique. &lt;/p&gt;&lt;p&gt;  Sa méthode de questionnement appelée  &lt;a href="https://www.youtube.com/watch?v=QJFdcQYBkDY&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="La Maïeutique par le Précepteur"&gt; Maïeutique&lt;/a&gt;, qui consiste à poser des questions pour amener son interlocuteur à examiner ses croyances et à découvrir la vérité par lui-même. Il ne prétendait pas détenir des réponses, mais cherchait à stimuler la réflexion critique. &lt;/p&gt; &lt;p&gt;Ironie socratique : Il feignait souvent l'ignorance pour inciter les autres à exposer leurs idées.&lt;/p&gt; &lt;p&gt;Questionnement : Il posait des questions comme "Qu'est-ce que la justice ?" ou "Qu'est-ce que le courage ?" pour explorer des concepts fondamentaux. &lt;/p&gt; &lt;p&gt;  Il croyait que la vertu est une forme de connaissance et que nul ne fait le mal volontairement. Selon lui, si les gens comprenaient vraiment ce qui est bien, ils agiraient en conséquence. Sers citations les plus célèbres : &lt;/p&gt; &lt;p&gt;Connais-toi toi-même : Cette maxime, inscrite au fronton du temple de Delphes, résume l'importance qu'il accordait à l'introspection et à la connaissance de soi. &lt;/p&gt; &lt;p&gt;La vie examinée : Il affirmait que "une vie sans examen ne vaut pas la peine d'être vécue", soulignant l'importance de la réflexion philosophique.&lt;/p&gt; &lt;p&gt; Il fut accusé d'empiété et de corruption de la jeunesse par Mélétos, un poète de son époque et &lt;a href="https://www.youtube.com/watch?v=3h_6zy58acE&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Son procès et sa condamnation à mort par le Précepteur"&gt;condamné à mort&lt;/a&gt; après un procès où il accepta son sort.  Il a révolutionné la pensée occidentale en mettant l'accent sur la raison, l'éthique et l'importance de questionner les certitudes. Son héritage continue d'inspirer les philosophes et les chercheurs de vérité à travers les âges.&lt;/p&gt;  &lt;audio controls title="Socrate est il de son temps par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-17.07.2023-ITEMA_23428681-2022C48904S0325-NET_MFC_3B8967BE-C9AF-46ED-A1B8-02CA5C79BDCD-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="n">
+        <v>-470</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/M%C3%A9lissos"  style="color:#6A142A"  title=" Wikipedia"&gt;MÉLISSOS&lt;/a&gt; de Samos (Ve siècle av. J.-C.) est un philosophe grec, le dernier grand représentant de l’école éléatique, &lt;a href="https://www.youtube.com/watch?v=zSetMtIYrCE" style="color:#88A1E9" title=" 
 Melissos and Zenon : Paradoxes of Movement and Being par Discovery"&gt;avec Parménide et Zénon&lt;/a&gt;. Il est aussi un homme d’action : amiral de la flotte de Samos, il remporte en 441 av. J.-C. une victoire navale sur les Athéniens, lors de la révolte de l’île contre Athènes, selon le récit de Plutarque.&lt;/p&gt; &lt;p&gt;De son traité &lt;em&gt;Sur la nature ou sur l’être&lt;/em&gt;, il reste une dizaine de fragments, conservés par le commentateur Simplicius. Mélissos reprend la thèse de Parménide : l’être est, le non-être n’est pas, et rien ne peut naître du néant ni y retourner. L’être est donc éternel, un, immobile et sans changement. Mais il s’écarte de son maître sur un point important. Parménide comparait l’être à une sphère, donc à quelque chose de limité. Mélissos soutient au contraire que l’être est &lt;a href="https://www.youtube.com/shorts/NKQQ7MKH0lM" style="color:#88A1E9" title=" 
 Melissos par Tielessphilo"&gt;infini&lt;/a&gt;, non seulement dans le temps, puisqu’il n’a ni commencement ni fin, mais aussi dans l’espace : s’il avait une limite, il serait limité par autre chose, c’est-à-dire par du vide, et le vide n’est rien. Pour la même raison, le mouvement est impossible, car une chose ne peut se déplacer que dans un espace vide. Il en conclut que les sens nous trompent : nous voyons les choses naître, changer et mourir, mais si elles existaient vraiment, elles devraient être éternelles et immuables comme l’être un. Le monde multiple de l’expérience n’est qu’une apparence.&lt;/p&gt; &lt;p&gt;Aristote juge sa pensée grossière, mais ses arguments, très clairs, ont obligé les atomistes, comme Leucippe et Démocrite, à admettre l’existence du vide pour sauver le mouvement.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H21" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Présocratique ; Éléatisme</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>-465</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>164</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="2" t="s">
@@ -4196,11 +4202,13 @@
       <c r="K21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>165</v>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Présocratique ; Éléatisme</t>
+        </is>
       </c>
       <c r="M21" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -5346,47 +5354,43 @@
         </is>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
         <v>-360</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>344</v>
+        <v>304</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stilpon_de_M%C3%A9gare"  style="color:#6A142A"  title=" Wikipedia"&gt;STILPON de Mégare&lt;/a&gt; était est un philosophe, spécialisée dans la dialectique de type éristique. Il est associé à l'école mégarique, fondée par Euclide de Mégare et était connu pour son éloquence et sa capacité à débattre, ce qui lui a valu une grande renommée dans le monde grec. &lt;/p&gt; &lt;p&gt; Les Mégariques étaient connus pour leur intérêt pour les paradoxes et les arguments sophistiqués. &lt;/p&gt; &lt;p&gt;Critique des universaux : Il est surtout connu pour sa critique des idées platoniciennes, en particulier la théorie des Formes. Il soutenait que les concepts généraux (comme "l'homme" ou "le bien") ne peuvent pas exister indépendamment des choses particulières. Pour lui, seules les choses individuelles sont réelles, et les universaux ne sont que des noms ou des constructions mentales. &lt;/p&gt; &lt;p&gt;Réfutation des catégories : Il a également critiqué la théorie des catégories d'Aristote, arguant que les distinctions entre les catégories (comme la substance, la qualité, la quantité) étaient artificielles et ne reflétaient pas la réalité. &lt;/p&gt; &lt;p&gt;Éthique et autosuffisance : Comme d'autres philosophes de son époque, il s'intéressait à l'éthique. Il prônait l'autosuffisance (autarkeia) et la tranquillité de l'âme (ataraxia). Il croyait que le bonheur pouvait être atteint en se libérant des désirs inutiles et en se concentrant sur ce qui est véritablement important. &lt;/p&gt; &lt;p&gt;Dialectique et logique : Il était un maître de la dialectique et utilisait souvent des arguments logiques pour déconstruire les positions de ses adversaires. Il était connu pour sa capacité à réduire les arguments de ses interlocuteurs à l'absurde, ce qui en faisait un redoutable débatteur. &lt;/p&gt; &lt;p&gt; Il était un philosophe dialecticien et éthique, dont les idées ont influencé plusieurs courants philosophiques ultérieurs. Bien que son œuvre ne nous soit pas parvenue directement, sa réputation de penseur rigoureux et son impact sur la philosophie antique sont indéniables. &lt;/p&gt; </t>
-        </is>
+        <v>354</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>355</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Socratisme ; École mégarique</t>
-        </is>
+        <v>359</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -5394,43 +5398,47 @@
         </is>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
         <v>-360</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>304</v>
+        <v>344</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>355</v>
+        <v>346</v>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stilpon_de_M%C3%A9gare" style="color:#6A142A" title=" Wikipedia"&gt;STILPON de Mégare&lt;/a&gt; était est un philosophe, spécialisée dans la &lt;a href="https://fr.wikisource.org/wiki/L%E2%80%99Art_d%E2%80%99avoir_toujours_raison/La_dialectique_%C3%A9ristique" title="L’Art d’avoir toujours raison/La dialectique éristique par wikisource"&gt;dialectique de type éristique&lt;/a&gt;. Il est associé à l'école mégarique, fondée par Euclide de Mégare et était connu pour son éloquence et sa capacité à débattre, ce qui lui a valu une grande renommée dans le monde grec. &lt;/p&gt; &lt;p&gt; Les Mégariques étaient connus pour leur intérêt pour les paradoxes et les arguments sophistiqués. &lt;/p&gt; &lt;p&gt;Critique des universaux : Il est surtout connu pour sa critique des idées platoniciennes, en particulier la théorie des Formes. Il soutenait que les concepts généraux (comme "l'homme" ou "le bien") ne peuvent pas exister indépendamment des choses particulières. Pour lui, seules les choses individuelles sont réelles, et les universaux ne sont que des noms ou des constructions mentales. &lt;/p&gt; &lt;p&gt;Réfutation des catégories : Il a également critiqué la théorie des catégories d'Aristote, arguant que les distinctions entre les catégories (comme la substance, la qualité, la quantité) étaient artificielles et ne reflétaient pas la réalité. &lt;/p&gt; &lt;p&gt;Éthique et autosuffisance : Comme d'autres philosophes de son époque, il s'intéressait à l'éthique. Il prônait l'autosuffisance (autarkeia) et la tranquillité de l'âme (ataraxia). Il croyait que le bonheur pouvait être atteint en se libérant des désirs inutiles et en se concentrant sur ce qui est véritablement important. &lt;/p&gt; &lt;p&gt;Dialectique et logique : Il était un maître de la dialectique et utilisait souvent des arguments logiques pour déconstruire les positions de ses adversaires. Il était connu pour sa capacité à réduire les arguments de ses interlocuteurs à l'absurde, ce qui en faisait un redoutable débatteur. &lt;/p&gt; &lt;p&gt; Il était un philosophe dialecticien et éthique, dont les idées ont influencé plusieurs courants philosophiques ultérieurs. Bien que son œuvre ne nous soit pas parvenue directement, sa réputation de penseur rigoureux et son impact sur la philosophie antique sont indéniables. &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F46" s="7" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>302</v>
+        <v>351</v>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; École mégarique</t>
+        </is>
       </c>
       <c r="M46" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -5438,79 +5446,103 @@
         </is>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7">
+        <v>-350</v>
+      </c>
+      <c r="B47" s="7">
+        <v>-280</v>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">350 A JC - 280 A JC</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIPPARCHIA de Maronée</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hipparchia" title=" Wikipedia"&gt;HIPPARCHIA de Maronée&lt;/a&gt; était une philosophe cynique grecque, originaire de Maronée en Thrace. Issue d'une famille aisée, elle tomba amoureuse du philosophe Cratès de Thèbes, disciple de Diogène, qui avait renoncé à toute sa fortune. Ses parents s'opposèrent au mariage ; elle menaça de se tuer. Cratès lui-même tenta de la dissuader en lui montrant sa pauvreté, mais elle choisit de partager sa vie et ses idées.&lt;/p&gt; &lt;p&gt;Le cynisme prônait une vie simple, conforme à la nature, libérée des richesses, des honneurs et des conventions sociales jugées artificielles. Hipparchia vécut ainsi avec Cratès, en public et sans honte, portant le même manteau grossier que lui, et participa comme un homme aux banquets et aux discussions philosophiques, ce qui fit scandale à Athènes.&lt;/p&gt; &lt;p&gt;Selon Diogène Laërce, elle aurait &lt;a href="https://www.philomag.com/articles/hipparchie-la-vie-forte-des-cyniques" title="Hipparchie, “la vie forte des cyniques” par philosophie magazine"&gt;écrit des traités philosophiques&lt;/a&gt;, des lettres et des réponses à des questions posées au philosophe Théodore, aujourd'hui perdus. Elle eut avec Cratès au moins deux enfants et continua de mener une vie de philosophe. Pour les anciens, elle était la preuve qu'une femme pouvait choisir librement la vie philosophique la plus exigeante, et plusieurs auteurs, jusqu'à l'époque chrétienne, citèrent son exemple.&lt;/p&gt; &lt;p&gt;Diogène Laërce rapporte une anecdote célèbre : lors d'un banquet, le philosophe Théodore l'Athée voulut l'humilier en lui demandant qui avait donc laissé sa navette sur le métier à tisser. Elle répondit qu'elle avait consacré à l'étude le temps qu'on aurait voulu lui faire perdre au rouet. Hipparchia est ainsi devenue le symbole de la femme qui revendique le droit de penser et de vivre en philosophe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBK-mTkHjtg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L’Athénienne qui préférait le cynisme à la cuisine | ARTE" par Invitation au voyage</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hipparchiademaronee-mini.webp</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cynisme</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe cynique grecque, épouse de Cratès, qui vécut selon ses idées contre les conventions de son temps.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
         <v>-341</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B48" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C48" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D48" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E48" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9donisme" style="color:#88A1E9"   title="L'hédonisme par Wikipédia"&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href="https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur"   title="L'épicurisme par le Précepteur"&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href="https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'épicurisme par le Précepteur"&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href="https://www.youtube.com/watch?v=cb1YHXSuxlM"   title="La philosophie du bonheur par Parole de philosophe"&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées "atomes".&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt; &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title="Est il bien raisonnable d'avoir peur de la mort par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F48" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G48" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H48" s="9" t="s">
         <v>367</v>
-      </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P47">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="n">
-        <v>-340</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>377</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="2" t="s">
@@ -5520,43 +5552,44 @@
         <v>368</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>278</v>
+        <v>369</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
-        <v>-334</v>
+        <v>-340</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Z%C3%A9non_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;ZENON de Kition&lt;/a&gt; (vers 334-262 av. J.-C.) est le fondateur de l’école &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcienne&lt;/a&gt;. Né à Kition, dans l’île de Chypre, il arrive à Athènes vers 312 av. J.-C. après un naufrage. Selon la légende, il lit chez un libraire les souvenirs de Xénophon sur Socrate et demande où trouver de tels hommes : le libraire lui montre le cynique Cratès qui passait. Zénon suit ses leçons, puis celles du mégarique Stilpon et des platoniciens.&lt;/p&gt; &lt;p&gt;Vers 300 av. J.-C., il enseigne sous le Portique peint d’Athènes, la &lt;em&gt;Stoa poikilè&lt;/em&gt;, d’où le nom de stoïcisme. Ses livres sont perdus. Il divise la philosophie en trois parties, que les stoïciens comparent à un jardin : la logique en est la clôture, la physique les arbres, l’éthique les fruits. Le monde est un tout vivant, ordonné par une raison divine, le &lt;em&gt;logos&lt;/em&gt;, présente en toute chose comme un feu artiste. Le but de la vie est de « vivre en accord avec la nature », c’est-à-dire avec la raison. La vertu est le seul bien, le vice le seul mal ; la santé, la richesse ou la réputation sont « indifférentes ». Les passions, comme la peur, le chagrin ou la colère, sont des jugements erronés et des élans excessifs : le sage s’en libère et atteint la tranquillité. Pour expliquer la connaissance, Zénon montre sa main ouverte, puis la ferme peu à peu jusqu’à serrer le poing : la sensation, l’assentiment, la compréhension, la science.&lt;/p&gt; &lt;p&gt;Les Athéniens honorent sa vertu d’une couronne d’or. Ses successeurs, Cléanthe et Chrysippe, développent sa doctrine, qui marquera Sénèque, Épictète et Marc Aurèle.&lt;/p&gt;</t>
-        </is>
+        <v>373</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>374</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="2" t="s">
@@ -5566,46 +5599,43 @@
         <v>368</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>386</v>
+        <v>278</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="50" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
-        <v>-330</v>
+        <v>-334</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9anthe"  style="color:#6A142A"  title=" Wikipedia"&gt;CLÉANTHE&lt;/a&gt; (vers 330-232 av. J.-C.) est un philosophe stoïcien grec, successeur de Zénon de Kition à la tête de l’école du Portique. Né à Assos, en Asie Mineure, ancien pugiliste, il arrive à Athènes presque sans ressources ; pour payer ses études, il tire de l’eau la nuit dans les jardins, ce qui lui vaut le surnom de « puiseur d’eau ». Il suit l’enseignement de Zénon pendant dix-neuf ans. Ses camarades le surnomment « l’âne », parce qu’il apprend lentement, mais il répond qu’il est le seul à pouvoir porter le fardeau de Zénon.&lt;/p&gt; &lt;p&gt;Il dirige l’école de 262 à sa mort. Moins brillant dialecticien que son successeur Chrysippe, il apporte pourtant des idées propres, surtout en physique et en théologie. Pour lui, l’univers est un être vivant animé par un souffle de feu, dont la tension maintient l’unité de toutes choses ; le soleil en est la partie directrice. Il défend une morale exigeante : la vertu est le seul bien, et le plaisir n’est pas conforme à la nature. Son œuvre la plus célèbre est l’&lt;a href="https://www.persee.fr/doc/rea_0035-2004_1998_num_100_1_4719" style="color:#88A1E9" title="L'universel &amp; le singulier. L'hymne à Zeus de Cléanthe. par Persée"&gt;&lt;em&gt;Hymne à Zeus&lt;/em&gt;&lt;/a&gt;, poème où Zeus est identifié à la raison universelle qui gouverne le monde : seuls les méchants s’en écartent, par ignorance. Une autre prière, citée par Épictète et traduite par Sénèque, résume l’attitude stoïcienne : « Conduis-moi, Zeus, et toi, Destinée, là où vous m’avez fixé ma place. » Sénèque en tire la formule : « Le destin conduit celui qui consent, il traîne celui qui résiste. »&lt;/p&gt; &lt;p&gt;Il meurt très âgé, en jeûnant. Hume a donné son nom au défenseur de &lt;a href="https://www.youtube.com/watch?v=HBbaB-X6xCI" style="color:#88A1E9" title=" L'argument a posteriori 1/2 : le raisonnement par analogie de Cléanthe par Gresza"&gt;l’argument par analogie&lt;/a&gt; dans ses &lt;em&gt;Dialogues sur la religion naturelle&lt;/em&gt;.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Z%C3%A9non_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;ZENON de Kition&lt;/a&gt; (vers 334-262 av. J.-C.) est le fondateur de l’école &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcienne&lt;/a&gt;. Né à Kition, dans l’île de Chypre, il arrive à Athènes vers 312 av. J.-C. après un naufrage. Selon la légende, il lit chez un libraire les souvenirs de Xénophon sur Socrate et demande où trouver de tels hommes : le libraire lui montre le cynique Cratès qui passait. Zénon suit ses leçons, puis celles du mégarique Stilpon et des platoniciens.&lt;/p&gt; &lt;p&gt;Vers 300 av. J.-C., il enseigne sous le Portique peint d’Athènes, la &lt;em&gt;Stoa poikilè&lt;/em&gt;, d’où le nom de stoïcisme. Ses livres sont perdus. Il divise la philosophie en trois parties, que les stoïciens comparent à un jardin : la logique en est la clôture, la physique les arbres, l’éthique les fruits. Le monde est un tout vivant, ordonné par une raison divine, le &lt;em&gt;logos&lt;/em&gt;, présente en toute chose comme un feu artiste. Le but de la vie est de « vivre en accord avec la nature », c’est-à-dire avec la raison. La vertu est le seul bien, le vice le seul mal ; la santé, la richesse ou la réputation sont « indifférentes ». Les passions, comme la peur, le chagrin ou la colère, sont des jugements erronés et des élans excessifs : le sage s’en libère et atteint la tranquillité. Pour expliquer la connaissance, Zénon montre sa main ouverte, puis la ferme peu à peu jusqu’à serrer le poing : la sensation, l’assentiment, la compréhension, la science.&lt;/p&gt; &lt;p&gt;Les Athéniens honorent sa vertu d’une couronne d’or. Ses successeurs, Cléanthe et Chrysippe, développent sa doctrine, qui marquera Sénèque, Épictète et Marc Aurèle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F50" s="7" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="2" t="s">
@@ -5618,53 +5648,56 @@
         <v>386</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
-        <v>-325</v>
+        <v>-330</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bion_de_Borysth%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;BION de Borysthène&lt;/a&gt; était un écrivain et un philosophe cynique grec connu pour ses idées critiques envers les conventions sociales et pour son style de vie ascétique, caractéristique des philosophes cyniques. Il était d'origine modeste, selon certaines sources et cette condition sociale a probablement influencé sa critique acerbe des hiérarchies et des conventions sociales. &lt;/p&gt; &lt;p&gt; Après avoir été vendu comme esclave, il fut libéré et reçut une éducation philosophique auprès de divers maîtres, et peut-être aussi auprès de représentants d'autres écoles philosophiques, comme les académiciens ou les péripatéticiens. Cette diversité d'influences se reflète dans sa   &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme" title="eclectisme par wikipedia"&gt;pensée éclectique&lt;/a&gt;. Il suit en effet tour à tour l’Académie, le cynique Cratès, le cyrénaïque Théodore l’Athée et le péripatéticien Théophraste.  Il adopta le mode de vie cynique, caractérisé par un rejet des richesses, des plaisirs matériels et des conventions sociales. &lt;/p&gt; &lt;p&gt; Il était également un écrivain talentueux, connu pour ses &lt;em&gt;Diatribes&lt;/em&gt;, des discours philosophiques souvent satiriques et moralisateurs.  &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1978_num_1_1_3417_t1_0102_0000_2" style="color:#88A1E9" title="Jan Fredrik Kindstrand, Bion of Borysthenes. A collection of the Fragments with introduction and commentary  par Persée"&gt;Ses textes&lt;/a&gt; ont influencé des auteurs ultérieurs, comme Horace et Sénèque, qui ont repris certains de ses thèmes et de ses techniques littéraires. Ératosthène disait de lui qu’il fut le premier à habiller la philosophie de vêtements fleuris. Il vécut un temps à la cour du roi de Macédoine Antigone Gonatas. &lt;/p&gt; &lt;p&gt; Il incarne l'esprit cynique par excellence : libre, provocateur et profondément critique envers les conventions sociales. Sa vie et son œuvre témoignent d'une quête de vérité et d'authenticité, qui continue de résonner aujourd'hui. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9anthe"  style="color:#6A142A"  title=" Wikipedia"&gt;CLÉANTHE&lt;/a&gt; (vers 330-232 av. J.-C.) est un philosophe stoïcien grec, successeur de Zénon de Kition à la tête de l’école du Portique. Né à Assos, en Asie Mineure, ancien pugiliste, il arrive à Athènes presque sans ressources ; pour payer ses études, il tire de l’eau la nuit dans les jardins, ce qui lui vaut le surnom de « puiseur d’eau ». Il suit l’enseignement de Zénon pendant dix-neuf ans. Ses camarades le surnomment « l’âne », parce qu’il apprend lentement, mais il répond qu’il est le seul à pouvoir porter le fardeau de Zénon.&lt;/p&gt; &lt;p&gt;Il dirige l’école de 262 à sa mort. Moins brillant dialecticien que son successeur Chrysippe, il apporte pourtant des idées propres, surtout en physique et en théologie. Pour lui, l’univers est un être vivant animé par un souffle de feu, dont la tension maintient l’unité de toutes choses ; le soleil en est la partie directrice. Il défend une morale exigeante : la vertu est le seul bien, et le plaisir n’est pas conforme à la nature. Son œuvre la plus célèbre est l’&lt;a href="https://www.persee.fr/doc/rea_0035-2004_1998_num_100_1_4719" style="color:#88A1E9" title="L'universel &amp; le singulier. L'hymne à Zeus de Cléanthe. par Persée"&gt;&lt;em&gt;Hymne à Zeus&lt;/em&gt;&lt;/a&gt;, poème où Zeus est identifié à la raison universelle qui gouverne le monde : seuls les méchants s’en écartent, par ignorance. Une autre prière, citée par Épictète et traduite par Sénèque, résume l’attitude stoïcienne : « Conduis-moi, Zeus, et toi, Destinée, là où vous m’avez fixé ma place. » Sénèque en tire la formule : « Le destin conduit celui qui consent, il traîne celui qui résiste. »&lt;/p&gt; &lt;p&gt;Il meurt très âgé, en jeûnant. Hume a donné son nom au défenseur de &lt;a href="https://www.youtube.com/watch?v=HBbaB-X6xCI" style="color:#88A1E9" title=" L'argument a posteriori 1/2 : le raisonnement par analogie de Cléanthe par Gresza"&gt;l’argument par analogie&lt;/a&gt; dans ses &lt;em&gt;Dialogues sur la religion naturelle&lt;/em&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F51" s="7" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>200</v>
+        <v>368</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>201</v>
+        <v>386</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -5672,45 +5705,45 @@
         </is>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
-        <v>-315</v>
+        <v>-325</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Wikipedia"&gt;ARCÉSILAS de Pitane&lt;/a&gt; fut l'un des philosophes les plus originaux de l'Antiquité, fondateur de la Moyenne Académie. En prenant la direction de l'Académie platonicienne vers 268 av. J.-C., il en transforma radicalement l'esprit en introduisant le scepticisme comme méthode philosophique fondamentale.&lt;/p&gt; &lt;p&gt;S'inspirant de &lt;a href="https://fr.wikipedia.org/wiki/Pyrrhon_d%27%C3%89lis" style="color:#6A142A" title="Pyrrhon sur Wikipedia"&gt;Pyrrhon d'Élis&lt;/a&gt; et de la pratique dialectique de Socrate, Arcésilas défendit la thèse que la suspension du jugement (&lt;em&gt;épochè&lt;/em&gt;) est la seule attitude raisonnable face à l'incertitude de la connaissance. Il combattit vigoureusement le dogmatisme stoïcien de Zénon de Kition, notamment la notion de « représentation compréhensive » (&lt;em&gt;phantasia kataleptike&lt;/em&gt;) censée fonder la certitude.&lt;/p&gt; &lt;p&gt;Fidèle à l'esprit socratique, Arcésilas n'écrivit rien. Il enseignait oralement, par le dialogue et la réfutation. Sa pensée est connue par les rapports de Cicéron, Sextus Empiricus et Diogène Laërce. Sa maxime : &lt;em&gt;« Suspendre son jugement est ce qu'il y a de plus sage »&lt;/em&gt;. Il incarne la résistance intellectuelle au dogmatisme et reste une référence majeure pour toute philosophie du doute. Né à Pitane, en Éolide, il étudie d’abord auprès de Théophraste, au Lycée, avant de rejoindre l’Académie de Polémon et de Crantor. Sa méthode consiste à argumenter pour et contre chaque thèse, jusqu’à montrer qu’elles se valent. Pour agir sans rien affirmer, il suffit, selon lui, de suivre ce qui paraît raisonnable. Un stoïcien se moquait de lui en le comparant à une chimère : « Platon par-devant, Pyrrhon par-derrière, Diodore au milieu ».&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bion_de_Borysth%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;BION de Borysthène&lt;/a&gt; était un écrivain et un philosophe cynique grec connu pour ses idées critiques envers les conventions sociales et pour son style de vie ascétique, caractéristique des philosophes cyniques. Il était d'origine modeste, selon certaines sources et cette condition sociale a probablement influencé sa critique acerbe des hiérarchies et des conventions sociales. &lt;/p&gt; &lt;p&gt; Après avoir été vendu comme esclave, il fut libéré et reçut une éducation philosophique auprès de divers maîtres, et peut-être aussi auprès de représentants d'autres écoles philosophiques, comme les académiciens ou les péripatéticiens. Cette diversité d'influences se reflète dans sa   &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme" title="eclectisme par wikipedia"&gt;pensée éclectique&lt;/a&gt;. Il suit en effet tour à tour l’Académie, le cynique Cratès, le cyrénaïque Théodore l’Athée et le péripatéticien Théophraste.  Il adopta le mode de vie cynique, caractérisé par un rejet des richesses, des plaisirs matériels et des conventions sociales. &lt;/p&gt; &lt;p&gt; Il était également un écrivain talentueux, connu pour ses &lt;em&gt;Diatribes&lt;/em&gt;, des discours philosophiques souvent satiriques et moralisateurs.  &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1978_num_1_1_3417_t1_0102_0000_2" style="color:#88A1E9" title="Jan Fredrik Kindstrand, Bion of Borysthenes. A collection of the Fragments with introduction and commentary  par Persée"&gt;Ses textes&lt;/a&gt; ont influencé des auteurs ultérieurs, comme Horace et Sénèque, qui ont repris certains de ses thèmes et de ses techniques littéraires. Ératosthène disait de lui qu’il fut le premier à habiller la philosophie de vêtements fleuris. Il vécut un temps à la cour du roi de Macédoine Antigone Gonatas. &lt;/p&gt; &lt;p&gt; Il incarne l'esprit cynique par excellence : libre, provocateur et profondément critique envers les conventions sociales. Sa vie et son œuvre témoignent d'une quête de vérité et d'authenticité, qui continue de résonner aujourd'hui. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F52" s="7" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>342</v>
+        <v>201</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -5718,45 +5751,45 @@
         </is>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
-        <v>-306</v>
+        <v>-315</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Persaios_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;PERSAIOS de Kition&lt;/a&gt;  était un disciple direct de Zénon de Cition, le fondateur du stoïcisme, et a joué un rôle important dans la diffusion des idées stoïciennes, bien que sa vie et son œuvre restent mal documentées en raison du peu de sources qui nous sont parvenues. Il aurait été l'esclave ou le pupille de Zénon avant de devenir son disciple et ami. Cette relation étroite avec le fondateur du stoïcisme lui a permis de jouer un rôle important dans les premiers développements de l'école. &lt;/p&gt; &lt;p&gt;  En tant que conseiller du roi Antigone II Gonatas, il a cherché à mettre en œuvre les idéaux stoïciens de vertu et de raison dans la gouvernance. Cela reflète une tendance du stoïcisme à s'engager dans le monde réel plutôt qu'à rester confiné à des spéculations abstraites. Il a écrit un ouvrage intitulé "Sur la royauté", dans lequel il explorait les qualités nécessaires pour être un bon roi selon les principes stoïciens. Pour lui, un dirigeant idéal devait être vertueux, rationnel et guidé par l'intérêt général plutôt que par des désirs égoïstes. &lt;/p&gt; &lt;p&gt; Contrairement à certains philosophes qui se concentraient sur des débats théoriques, il insistait sur l'importance de vivre selon les principes stoïciens dans la vie quotidienne.Il a critiqué la poursuite des plaisirs, une idée qui rejoint l'enseignement stoïcien selon lequel les plaisirs corporels et matériels sont des distractions par rapport à la vertu et à la raison. Il a soutenu que le bonheur véritable ne peut être trouvé que dans la sagesse et la maîtrise de soi. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Wikipedia"&gt;ARCÉSILAS de Pitane&lt;/a&gt; fut l'un des philosophes les plus originaux de l'Antiquité, fondateur de la Moyenne Académie. En prenant la direction de l'Académie platonicienne vers 268 av. J.-C., il en transforma radicalement l'esprit en introduisant le scepticisme comme méthode philosophique fondamentale.&lt;/p&gt; &lt;p&gt;S'inspirant de &lt;a href="https://fr.wikipedia.org/wiki/Pyrrhon_d%27%C3%89lis" style="color:#6A142A" title="Pyrrhon sur Wikipedia"&gt;Pyrrhon d'Élis&lt;/a&gt; et de la pratique dialectique de Socrate, Arcésilas défendit la thèse que la suspension du jugement (&lt;em&gt;épochè&lt;/em&gt;) est la seule attitude raisonnable face à l'incertitude de la connaissance. Il combattit vigoureusement le dogmatisme stoïcien de Zénon de Kition, notamment la notion de « représentation compréhensive » (&lt;em&gt;phantasia kataleptike&lt;/em&gt;) censée fonder la certitude.&lt;/p&gt; &lt;p&gt;Fidèle à l'esprit socratique, Arcésilas n'écrivit rien. Il enseignait oralement, par le dialogue et la réfutation. Sa pensée est connue par les rapports de Cicéron, Sextus Empiricus et Diogène Laërce. Sa maxime : &lt;em&gt;« Suspendre son jugement est ce qu'il y a de plus sage »&lt;/em&gt;. Il incarne la résistance intellectuelle au dogmatisme et reste une référence majeure pour toute philosophie du doute. Né à Pitane, en Éolide, il étudie d’abord auprès de Théophraste, au Lycée, avant de rejoindre l’Académie de Polémon et de Crantor. Sa méthode consiste à argumenter pour et contre chaque thèse, jusqu’à montrer qu’elles se valent. Pour agir sans rien affirmer, il suffit, selon lui, de suivre ce qui paraît raisonnable. Un stoïcien se moquait de lui en le comparant à une chimère : « Platon par-devant, Pyrrhon par-derrière, Diodore au milieu ».&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F53" s="7" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>252</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -5764,43 +5797,45 @@
         </is>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="209.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
-        <v>-281</v>
+        <v>-306</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>423</v>
+        <v>414</v>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Persaios_de_Kition" style="color:#6A142A" title=" Wikipedia"&gt;PERSAIOS de Kition&lt;/a&gt;  était un disciple direct de Zénon de Cition, le fondateur du&lt;a href="https://www.youtube.com/watch?v=Dm5sPn_HmNE" title="Stoïcisme : Les Bases En Trois Minutes par Gianni Bergandi"&gt; stoïcisme&lt;/a&gt;, et a joué un rôle important dans la diffusion des idées stoïciennes, bien que sa vie et son œuvre restent mal documentées en raison du peu de sources qui nous sont parvenues. Il aurait été l'esclave ou le pupille de Zénon avant de devenir son disciple et ami. Cette relation étroite avec le fondateur du stoïcisme lui a permis de jouer un rôle important dans les premiers développements de l'école. &lt;/p&gt; &lt;p&gt;  En tant que conseiller du roi Antigone II Gonatas, il a cherché à mettre en œuvre les idéaux stoïciens de vertu et de raison dans la gouvernance. Cela reflète une tendance du stoïcisme à s'engager dans le monde réel plutôt qu'à rester confiné à des spéculations abstraites. Il a écrit un ouvrage intitulé "Sur la royauté", dans lequel il explorait les qualités nécessaires pour être un bon roi selon les principes stoïciens. Pour lui, un dirigeant idéal devait être vertueux, rationnel et guidé par l'intérêt général plutôt que par des désirs égoïstes. &lt;/p&gt; &lt;p&gt; Contrairement à certains philosophes qui se concentraient sur des débats théoriques, il insistait sur l'importance de vivre selon les principes stoïciens dans la vie quotidienne. Il a critiqué la poursuite des plaisirs, une idée qui rejoint l'enseignement stoïcien selon lequel les plaisirs corporels et matériels sont des distractions par rapport à la vertu et à la raison. Il a soutenu que le bonheur véritable ne peut être trouvé que dans la sagesse et la maîtrise de soi. &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F54" s="7" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>427</v>
+        <v>24</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>428</v>
+        <v>386</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5808,45 +5843,43 @@
         </is>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="209.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
-        <v>-280</v>
+        <v>-281</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s" style="color:#6A142A" title="Wikipedia"&gt;LACYDÈS de Cyrène&lt;/a&gt; (mort vers 205 av. J.-C.) est un philosophe grec, successeur d’&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Arcésilas sur Wikipedia"&gt;Arcésilas de Pitane&lt;/a&gt; à la tête de l’Académie, l’école fondée à Athènes par Platon. Originaire de Cyrène, en Libye actuelle, il vient étudier à Athènes et devient le disciple d’Arcésilas, auquel il succède vers 241 av. J.-C.&lt;/p&gt; &lt;p&gt;Il enseigne dans un jardin de l’Académie aménagé pour lui par le roi Attale Ier de Pergame, admirateur de la philosophie, et qu’on appelle le &lt;em&gt;Lacydion&lt;/em&gt;. Invité à la cour de ce roi, il refuse de s’y rendre, en disant que les portraits des rois se regardent de loin. Lacydès reste fidèle au &lt;a href="https://www.youtube.com/watch?v=kG3klWpBf2Y"  title="Le sceptisisme de la nouvelle-académie"&gt;scepticisme académique&lt;/a&gt; de son maître. Contre les stoïciens, qui croient à des perceptions si claires qu’elles garantissent la vérité, les académiciens soutiennent que rien ne peut être connu avec certitude : toute impression vraie pourrait être imitée par une impression fausse. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et se contenter de ce qui paraît raisonnable. Une anecdote rapportée par les Anciens illustre, avec humour, les difficultés de cette position : ses esclaves volaient ses provisions puis remettaient les scellés intacts ; pris sur le fait, ils lui auraient opposé sa propre doctrine : comment pouvait-il être sûr de ce qu’il voyait ?&lt;/p&gt; &lt;p&gt;Atteint de paralysie dans sa vieillesse, il confie de son vivant la direction de l’école à ses disciples Téléclès et Évandre, cas rare dans l’histoire de l’Académie. Selon Diogène Laërce, il aurait écrit des traités sur la philosophie et sur la nature, aujourd’hui perdus.&lt;/p&gt;</t>
-        </is>
+        <v>422</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>423</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>252</v>
+        <v>427</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>342</v>
+        <v>428</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5854,36 +5887,34 @@
         </is>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
-        <v>-240</v>
+        <v>-280</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89vandre_(philosophe)" title="Wikipedia"&gt;ÉVANDRE&lt;/a&gt; (IIIe siècle av. J.-C.) est un philosophe grec originaire de Phocée, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de &lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s_de_Cyr%C3%A8ne" title=" Wikipedia"&gt;Lacydès de Cyrène&lt;/a&gt;, il reçoit de lui, avec Téléclès, la direction de l’école du vivant même de leur maître : Lacydès, malade, la leur confie vers 224 av. J.-C. Évandre et Téléclès la dirigent ensemble, cas rare dans l’histoire de l’institution.&lt;/p&gt; &lt;p&gt;Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par &lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" title=" Wikipedia"&gt;Arcésilas&lt;/a&gt;. Celui-ci avait donné à l’école platonicienne une orientation sceptique, en s’appuyant sur le Socrate qui affirmait ne rien savoir. Contre les stoïciens, qui pensaient que certaines représentations sont si évidentes qu’elles garantissent la vérité, les académiciens soutiennent qu’aucune perception ne permet de distinguer avec certitude le vrai du faux : un rêve, une illusion ou un jumeau peuvent produire la même impression qu’une perception exacte. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et ne rien affirmer. Pour agir, il suffit de suivre ce qui paraît raisonnable. Les académiciens enseignaient en argumentant pour et contre chaque thèse, afin de montrer que les deux positions se valent et d’exercer l’esprit critique de leurs élèves. Évandre transmet cet héritage à une génération d’étudiants.&lt;/p&gt; &lt;p&gt;Aucun de ses écrits ne nous est parvenu. Il a pour successeur Hégésinous de Pergame, qui forme à son tour &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant penseur de la Nouvelle Académie.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s" style="color:#6A142A" title="Wikipedia"&gt;LACYDÈS de Cyrène&lt;/a&gt; (mort vers 205 av. J.-C.) est un philosophe grec, successeur d’&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Arcésilas sur Wikipedia"&gt;Arcésilas de Pitane&lt;/a&gt; à la tête de l’Académie, l’école fondée à Athènes par Platon. Originaire de Cyrène, en Libye actuelle, il vient étudier à Athènes et devient le disciple d’Arcésilas, auquel il succède vers 241 av. J.-C.&lt;/p&gt; &lt;p&gt;Il enseigne dans un jardin de l’Académie aménagé pour lui par le roi Attale Ier de Pergame, admirateur de la philosophie, et qu’on appelle le &lt;em&gt;Lacydion&lt;/em&gt;. Invité à la cour de ce roi, il refuse de s’y rendre, en disant que les portraits des rois se regardent de loin. Lacydès reste fidèle au &lt;a href="https://www.youtube.com/watch?v=kG3klWpBf2Y"  title="Le sceptisisme de la nouvelle-académie"&gt;scepticisme académique&lt;/a&gt; de son maître. Contre les stoïciens, qui croient à des perceptions si claires qu’elles garantissent la vérité, les académiciens soutiennent que rien ne peut être connu avec certitude : toute impression vraie pourrait être imitée par une impression fausse. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et se contenter de ce qui paraît raisonnable. Une anecdote rapportée par les Anciens illustre, avec humour, les difficultés de cette position : ses esclaves volaient ses provisions puis remettaient les scellés intacts ; pris sur le fait, ils lui auraient opposé sa propre doctrine : comment pouvait-il être sûr de ce qu’il voyait ?&lt;/p&gt; &lt;p&gt;Atteint de paralysie dans sa vieillesse, il confie de son vivant la direction de l’école à ses disciples Téléclès et Évandre, cas rare dans l’histoire de l’Académie. Selon Diogène Laërce, il aurait écrit des traités sur la philosophie et sur la nature, aujourd’hui perdus.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F56" s="7" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>445</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="I56" s="9"/>
       <c r="J56" s="2" t="s">
         <v>23</v>
       </c>
@@ -5894,7 +5925,7 @@
         <v>342</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5902,34 +5933,36 @@
         </is>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
-        <v>-230</v>
+        <v>-240</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame" title="Wikipedia"&gt;Hégésinous de PERGAME&lt;/a&gt; (IIe siècle av. J.-C.) est un philosophe grec, chef de l’Académie, l’école fondée à Athènes par Platon. Originaire de Pergame, en Asie Mineure, il succède à Évandre et Téléclès, qui avaient dirigé ensemble l’école, et il a pour élève et successeur &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant dialecticien de l’Antiquité.&lt;/p&gt; &lt;p&gt;Nous ne connaissons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu : son nom nous est connu par les listes des chefs successifs de l’Académie et par Cicéron, qui indique que Carnéade l’eut pour maître. Il appartient à la période sceptique de l’Académie, inaugurée par Arcésilas. Les académiciens de ce temps refusent d’affirmer quoi que ce soit avec certitude. Contre les stoïciens, qui croient que certaines perceptions portent en elles la marque de leur vérité, ils montrent qu’une perception vraie pourrait toujours être imitée par une perception fausse, comme dans le rêve ou l’illusion. Il faut donc suspendre son jugement. Mais cela n’empêche pas de vivre : pour agir, on peut suivre ce qui paraît raisonnable. L’enseignement de l’Académie se fait par la discussion contradictoire, en argumentant pour et contre chaque thèse. C’est cette méthode que Carnéade portera à son sommet : envoyé à Rome en ambassade en 155 av. J.-C., il fit scandale en défendant un jour la justice, puis en la réfutant le lendemain.&lt;/p&gt; &lt;p&gt;Hégésinous est ainsi un maillon de la transmission entre la Moyenne et la Nouvelle Académie, durant la période de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique" style="color:#6A142A" title="Philosophie hellénistique sur Wikipedia"&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;</t>
+        <v>440</v>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89vandre_(philosophe)" title="Wikipedia"&gt;ÉVANDRE&lt;/a&gt; (IIIe siècle av. J.-C.) est un philosophe grec originaire de Phocée, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de &lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s_de_Cyr%C3%A8ne" title=" Wikipedia"&gt;Lacydès de Cyrène&lt;/a&gt;, il reçoit de lui, avec Téléclès, la direction de l’école du vivant même de leur maître : Lacydès, malade, la leur confie vers 224 av. J.-C. Évandre et Téléclès la dirigent ensemble, cas rare dans l’histoire de l’institution.&lt;/p&gt; &lt;p&gt;Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par &lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" title=" Wikipedia"&gt;Arcésilas&lt;/a&gt;. Celui-ci avait donné à l’école platonicienne une orientation sceptique, en s’appuyant sur le Socrate qui affirmait ne rien savoir. Contre les stoïciens, qui pensaient que certaines représentations sont si évidentes qu’elles garantissent la vérité, les académiciens soutiennent qu’aucune perception ne permet de distinguer avec certitude le vrai du faux : un rêve, une illusion ou un jumeau peuvent produire la même impression qu’une perception exacte. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et ne rien affirmer. Pour agir, il suffit de suivre ce qui paraît raisonnable. Les académiciens enseignaient en argumentant pour et contre chaque thèse, afin de montrer que les deux positions se valent et d’exercer l’esprit critique de leurs élèves. Évandre transmet cet héritage à une génération d’étudiants.&lt;/p&gt; &lt;p&gt;Aucun de ses écrits ne nous est parvenu. Il a pour successeur Hégésinous de Pergame, qui forme à son tour &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant penseur de la Nouvelle Académie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F57" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="G57" s="15" t="s">
-        <v>452</v>
+        <v>442</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>443</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="I57" s="9"/>
+        <v>444</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>445</v>
+      </c>
       <c r="J57" s="2" t="s">
         <v>23</v>
       </c>
@@ -5940,7 +5973,7 @@
         <v>342</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5948,32 +5981,32 @@
         </is>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
-        <v>-213</v>
+        <v>-230</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Wikipedia"&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href="https://fr.wikipedia.org/wiki/Dialectique" title="Dialectique par Wikipedia"&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272" title="Opinion et certitude par Persee"&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron" style="color:#6A142A" title="Cicéron sur Wikipedia"&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il. Formé à la dialectique par le stoïcien Diogène de Babylone, il étudie de près l’œuvre de Chrysippe pour mieux la réfuter, au point de dire : « Sans Chrysippe, je ne serais pas. » Il distingue trois degrés de vraisemblance : la représentation simplement probable, celle qui n’est contredite par aucune autre, et celle qui a été examinée sous tous ses aspects. Il critique aussi la divination, le destin et la providence des stoïciens. Son disciple Clitomaque a mis par écrit son enseignement.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame" title="Wikipedia"&gt;Hégésinous de PERGAME&lt;/a&gt; (IIe siècle av. J.-C.) est un philosophe grec, chef de l’Académie, l’école fondée à Athènes par Platon. Originaire de Pergame, en Asie Mineure, il succède à Évandre et Téléclès, qui avaient dirigé ensemble l’école, et il a pour élève et successeur &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant dialecticien de l’Antiquité.&lt;/p&gt; &lt;p&gt;Nous ne connaissons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu : son nom nous est connu par les listes des chefs successifs de l’Académie et par Cicéron, qui indique que Carnéade l’eut pour maître. Il appartient à la période sceptique de l’Académie, inaugurée par Arcésilas. Les académiciens de ce temps refusent d’affirmer quoi que ce soit avec certitude. Contre les stoïciens, qui croient que certaines perceptions portent en elles la marque de leur vérité, ils montrent qu’une perception vraie pourrait toujours être imitée par une perception fausse, comme dans le rêve ou l’illusion. Il faut donc suspendre son jugement. Mais cela n’empêche pas de vivre : pour agir, on peut suivre ce qui paraît raisonnable. L’enseignement de l’Académie se fait par la discussion contradictoire, en argumentant pour et contre chaque thèse. C’est cette méthode que Carnéade portera à son sommet : envoyé à Rome en ambassade en 155 av. J.-C., il fit scandale en défendant un jour la justice, puis en la réfutant le lendemain.&lt;/p&gt; &lt;p&gt;Hégésinous est ainsi un maillon de la transmission entre la Moyenne et la Nouvelle Académie, durant la période de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique" style="color:#6A142A" title="Philosophie hellénistique sur Wikipedia"&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F58" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>460</v>
+        <v>451</v>
+      </c>
+      <c r="G58" s="15" t="s">
+        <v>452</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="2" t="s">
@@ -5986,7 +6019,7 @@
         <v>342</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5994,36 +6027,32 @@
         </is>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7">
-        <v>160</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vers 160 – vers 210</t>
-        </is>
+    <row r="59" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="n">
+        <v>-213</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>456</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sextus_Empiricus"  title=" Wikipedia"&gt;Sextus EMPIRICUS&lt;/a&gt;  était un philosophe et médecin grec et  une figure importante du scepticisme, souvent appelé "pyrrhonisme" en référence à Pyrrhon d'Élis. Contrairement à d'autres formes de scepticisme, qui peuvent aboutir à une négation de la possibilité de connaître la vérité, le &lt;a href="https://www.youtube.com/watch?v=Xvgfo_ADlPM"  title=" Sextus Empiricus, Esquisses pyrrhoniennes, Ne rien affirmer et l'enseignement inexistant par Koalemos"&gt;pyrrhonisme&lt;/a&gt; propose de suspendre tout jugement sur la nature ultime des choses, car il considère que les arguments pour et contre toute proposition sont également convaincants. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2002_num_100_4_7456_t1_0797_0000_2" title="Sextus Empiricus, Esquisses pyrrhoniennes. Introduction, traduction et commentaires par Pierre Pellegrin par Persée"&gt;"Les Esquisses pyrrhoniennes"&lt;/a&gt;, il présente une introduction systématique au scepticisme pyrrhonien. L'ouvrage est divisé en trois livres : &lt;/p&gt; &lt;p&gt;Livre I : Il expose les principes fondamentaux du scepticisme, y compris la distinction entre le scepticisme pyrrhonien et d'autres formes de scepticisme, comme celui de l'Académie. Il explique également les concepts clés tels que l'épochè (suspension du jugement), les tropes (modes d'argumentation sceptique), et l'ataraxie. &lt;/p&gt; &lt;p&gt;Livre II : Il traite de la critique sceptique des dogmatismes philosophiques, en particulier dans les domaines de la logique, de la physique et de l'éthique. Il montre comment les arguments des dogmatiques peuvent être contredits, ce qui justifie la suspension du jugement. &lt;/p&gt; &lt;p&gt;Livre III : Il approfondit la critique des dogmatismes, en se concentrant sur des questions spécifiques comme la causalité, la divinité, et la nature du bien et du mal. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/spira_0994-3722_2007_num_39_1_1264_t14_0182_0000_2" style="color:#88A1E9" title=" Sur le Contre les professeurs de Sextus Empiricus par Persée"&gt;"Contre les professeurs"&lt;/a&gt;, il s'attaque à diverses disciplines intellectuelles de son époque, notamment la grammaire, la rhétorique, la géométrie, l'arithmétique, l'astronomie et la musique. Il soutient qu'elles ne peuvent pas prétendre à une connaissance certaine ou absolue. Son but est de montrer que les prétentions à la vérité dans ces domaines sont infondées. &lt;/p&gt; &lt;p&gt; Il  est également connu pour avoir systématisé &lt;a href="https://hal.science/hal-03091658v1/document" style="color:#88A1E9" title=" Sextus Empiricus et les tropes par Hall science"&gt;les "tropes"&lt;/a&gt;, des arguments ou modes de raisonnement qui justifient la suspension du jugement. Ce sont des outils dialectiques qui montrent comment les perceptions et les jugements varient selon les circonstances, les individus, les cultures, etc. &lt;/p&gt; &lt;p&gt;Ses écrits ont été redécouverts à la Renaissance et ont joué un rôle clé dans le développement de la pensée sceptique moderne, influençant des philosophes comme Montaigne, Descartes et Hume. &lt;/p&gt; </t>
+        <v>457</v>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Wikipedia"&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href="https://fr.wikipedia.org/wiki/Dialectique" title="Dialectique par Wikipedia"&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272" title="Opinion et certitude par Persee"&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron" style="color:#6A142A" title="Cicéron sur Wikipedia"&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il. Formé à la dialectique par le stoïcien Diogène de Babylone, il étudie de près l’œuvre de Chrysippe pour mieux la réfuter, au point de dire : « Sans Chrysippe, je ne serais pas. » Il distingue trois degrés de vraisemblance : la représentation simplement probable, celle qui n’est contredite par aucune autre, et celle qui a été examinée sous tous ses aspects. Il critique aussi la divination, le destin et la providence des stoïciens. Son disciple Clitomaque a mis par écrit son enseignement.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F59" s="7" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="2" t="s">
@@ -6036,7 +6065,7 @@
         <v>342</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -6044,36 +6073,37 @@
         </is>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7">
-        <v>-240</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-167</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vers 240 A JC - 167 A JC</t>
-        </is>
+    <row r="60" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="n">
+        <v>-80</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s" title="Wikipedia"&gt;TÉLÉCLÈS&lt;/a&gt; (mort vers 167 av. J.-C.) est un philosophe grec, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de Lacydès de Cyrène, il reçoit de lui, avec son condisciple Évandre, la direction de l’école du vivant même de leur maître, que la maladie empêchait d’enseigner. Les deux philosophes la dirigent ensemble, une organisation collégiale rare dans l’histoire de l’Académie.&lt;/p&gt; &lt;p&gt;Nous ne savons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu. Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par Arcésilas, qui avait donné à l’école de Platon une orientation sceptique en s’inspirant du Socrate qui affirmait ne rien savoir. Les académiciens de cette époque s’opposent avant tout aux stoïciens. Ceux-ci soutiennent qu’il existe des représentations « compréhensives », si claires et si distinctes qu’elles garantissent leur propre vérité et fondent la science. Les académiciens répondent qu’aucune perception ne peut être distinguée avec certitude d’une perception trompeuse : un rêve, une illusion d’optique ou deux jumeaux suffisent à le montrer. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;), mais il peut agir en suivant ce qui lui paraît raisonnable ou vraisemblable. L’enseignement se fait par la discussion : on argumente pour et contre chaque thèse, afin d’exercer l’esprit critique.&lt;/p&gt; &lt;p&gt;Après Téléclès et Évandre, la direction passe à Hégésinous de Pergame, puis à &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" style="color:#6A142A" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, qui donnera à l’Académie un éclat nouveau et portera le scepticisme jusqu’à Rome.&lt;/p&gt;</t>
+        <v>524</v>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89n%C3%A9sid%C3%A8me" style="color:#6A142A" title=" Wikipedia"&gt;ÉNÉSIDÈME&lt;/a&gt; était un philosophe grec de la tradition sceptique.  Il vécu à une époque où le &lt;a href="https://www.youtube.com/watch?v=57h2CU3V2fs" title="Le scepticisme : définition, exemples... (expliqué en 2 minutes) par le Savoir Partagé"&gt;&lt;font color="#88a1e9"&gt;scepticisme&lt;/font&gt; &lt;/a&gt;philosophique était en plein essor, en réaction aux dogmatismes des écoles philosophiques comme le stoïcisme et l'épicurisme.  &lt;/p&gt; &lt;p&gt; Il a systématisé les  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1918_num_20_2_2006" style="color:#88A1E9" title="Pour l'histoire du scepticisme antique : les tropes d'Énésidème contre la logique inductive par Persée"&gt;arguments sceptiques&lt;/a&gt; dans ce qu'on appelle les &lt;a href="https://guykarl.canalblog.com/archives/2012/08/31/25001663.html" style="color:#88A1E9" title="PYRRHONISME : les dix tropes d' ENESIDEME par Le jardin Philosophe"&gt;"Dix Modes"&lt;/a&gt;, qui visent à montrer que nos perceptions et nos jugements sont influencés par divers facteurs, rendant impossible l'accès à une connaissance certaine : &lt;/p&gt;
+&lt;p&gt;La diversité des animaux : Les espèces perçoivent le monde de manière différente, ce qui suggère que nos perceptions ne reflètent pas nécessairement la réalité objective. &lt;/p&gt;
+&lt;p&gt;La diversité des humains : Parmi les humains, les perceptions et les jugements varient considérablement, ce qui rend difficile de déterminer quelle perception est "correcte". &lt;/p&gt; &lt;p&gt;La diversité des sens : Les différents sens peuvent donner des informations contradictoires sur un même objet. &lt;/p&gt;
+&lt;p&gt;Les circonstances : Les conditions dans lesquelles nous percevons quelque chose peuvent influencer notre perception. &lt;/p&gt;
+&lt;p&gt;Les positions et distances : La position et la distance par rapport à un objet peuvent altérer notre perception de celui-ci. &lt;/p&gt; &lt;p&gt;Les mélanges : Les objets ne sont jamais perçus isolément, mais toujours dans un contexte qui peut influencer notre perception. &lt;/p&gt;
+&lt;p&gt;Les quantités et constitutions : La quantité et la composition d'un objet peuvent affecter la manière dont nous le percevons. &lt;/p&gt; &lt;p&gt;La relation : Tout est perçu en relation avec autre chose, ce qui rend difficile de connaître la nature intrinsèque d'un objet.&lt;/p&gt; &lt;p&gt;La fréquence ou la rareté : La fréquence avec laquelle nous rencontrons quelque chose peut influencer notre perception de sa valeur ou de sa nature. &lt;/p&gt; &lt;p&gt;Les coutumes et les croyances : Les habitudes culturelles et les croyances peuvent profondément influencer nos perceptions et nos jugements. &lt;/p&gt; &lt;p&gt; Ses arguments mettent en lumière les limites de notre capacité à connaître le monde de manière certaine et nous invitent à adopter une attitude plus humble et critique face à nos propres perceptions et jugements. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F60" s="7" t="s">
-        <v>475</v>
+        <v>526</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>476</v>
+        <v>527</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>477</v>
+        <v>528</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="2" t="s">
@@ -6085,8 +6115,8 @@
       <c r="L60" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="M60" s="11" t="s">
-        <v>478</v>
+      <c r="M60" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -6094,45 +6124,49 @@
         </is>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="n">
-        <v>-185</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>480</v>
+    <row r="61" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7">
+        <v>160</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 160 – vers 210</t>
+        </is>
       </c>
       <c r="D61" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes"  title=" Wikipedia"&gt;PANÉTIUS DE RHODES&lt;/a&gt; (vers 185-109 av. J.-C.) est un philosophe stoïcien grec, qui a adapté le stoïcisme au monde romain. Issu d’une grande famille de Rhodes, il étudie à Athènes auprès de Diogène de Babylone, puis s’installe à Rome, où il devient l’ami et le conseiller de Scipion Émilien, le vainqueur de Carthage. Il prend ensuite la tête de l’école stoïcienne d’Athènes, de 129 à sa mort.&lt;/p&gt; &lt;p&gt;Panétius assouplit la &lt;a href="https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie"  title="Le Stoïcisme par apprendre la philo"&gt;pensée stoïcienne&lt;/a&gt; et la rapproche de Platon et d’Aristote, qu’il admire. Il abandonne plusieurs thèses de ses prédécesseurs : il doute de la divination, nie la conflagration universelle qui devait périodiquement détruire le monde, qu’il juge éternel, et refuse l’immortalité de l’âme. Surtout, il s’intéresse moins au sage idéal, presque introuvable, qu’à l’homme ordinaire qui progresse vers la sagesse. Sa morale part de la nature humaine : chacun porte en lui des tendances fondamentales où s’unissent la nature et la raison, la recherche de la vérité, le goût de l’ordre, le désir de grandeur d’âme et le sens de la communauté. Chacun doit aussi tenir compte de sa propre nature, de ses talents et de sa situation, comme un acteur choisit le rôle qui lui convient. Il en tire une éthique des « devoirs », les actions convenables de la vie quotidienne et de la vie publique, fondée sur la justice, la bienveillance et le sens de la mesure.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Du devoir&lt;/em&gt; est perdu, mais Cicéron l’a largement repris dans son &lt;em&gt;De officiis&lt;/em&gt;, l’un des livres de morale les plus lus en Europe jusqu’au XIXe siècle. Panétius a ainsi donné au stoïcisme le visage humaniste qu’adopteront les élites romaines.&lt;/p&gt;</t>
+        <v>465</v>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sextus_Empiricus"  title=" Wikipedia"&gt;Sextus EMPIRICUS&lt;/a&gt;  était un philosophe et médecin grec et  une figure importante du scepticisme, souvent appelé "pyrrhonisme" en référence à Pyrrhon d'Élis. Contrairement à d'autres formes de scepticisme, qui peuvent aboutir à une négation de la possibilité de connaître la vérité, le &lt;a href="https://www.youtube.com/watch?v=Xvgfo_ADlPM"  title=" Sextus Empiricus, Esquisses pyrrhoniennes, Ne rien affirmer et l'enseignement inexistant par Koalemos"&gt;pyrrhonisme&lt;/a&gt; propose de suspendre tout jugement sur la nature ultime des choses, car il considère que les arguments pour et contre toute proposition sont également convaincants. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2002_num_100_4_7456_t1_0797_0000_2" title="Sextus Empiricus, Esquisses pyrrhoniennes. Introduction, traduction et commentaires par Pierre Pellegrin par Persée"&gt;"Les Esquisses pyrrhoniennes"&lt;/a&gt;, il présente une introduction systématique au scepticisme pyrrhonien. L'ouvrage est divisé en trois livres : &lt;/p&gt; &lt;p&gt;Livre I : Il expose les principes fondamentaux du scepticisme, y compris la distinction entre le scepticisme pyrrhonien et d'autres formes de scepticisme, comme celui de l'Académie. Il explique également les concepts clés tels que l'épochè (suspension du jugement), les tropes (modes d'argumentation sceptique), et l'ataraxie. &lt;/p&gt; &lt;p&gt;Livre II : Il traite de la critique sceptique des dogmatismes philosophiques, en particulier dans les domaines de la logique, de la physique et de l'éthique. Il montre comment les arguments des dogmatiques peuvent être contredits, ce qui justifie la suspension du jugement. &lt;/p&gt; &lt;p&gt;Livre III : Il approfondit la critique des dogmatismes, en se concentrant sur des questions spécifiques comme la causalité, la divinité, et la nature du bien et du mal. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/spira_0994-3722_2007_num_39_1_1264_t14_0182_0000_2" style="color:#88A1E9" title=" Sur le Contre les professeurs de Sextus Empiricus par Persée"&gt;"Contre les professeurs"&lt;/a&gt;, il s'attaque à diverses disciplines intellectuelles de son époque, notamment la grammaire, la rhétorique, la géométrie, l'arithmétique, l'astronomie et la musique. Il soutient qu'elles ne peuvent pas prétendre à une connaissance certaine ou absolue. Son but est de montrer que les prétentions à la vérité dans ces domaines sont infondées. &lt;/p&gt; &lt;p&gt; Il  est également connu pour avoir systématisé &lt;a href="https://hal.science/hal-03091658v1/document" style="color:#88A1E9" title=" Sextus Empiricus et les tropes par Hall science"&gt;les "tropes"&lt;/a&gt;, des arguments ou modes de raisonnement qui justifient la suspension du jugement. Ce sont des outils dialectiques qui montrent comment les perceptions et les jugements varient selon les circonstances, les individus, les cultures, etc. &lt;/p&gt; &lt;p&gt;Ses écrits ont été redécouverts à la Renaissance et ont joué un rôle clé dans le développement de la pensée sceptique moderne, influençant des philosophes comme Montaigne, Descartes et Hume. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F61" s="7" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>252</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -6140,45 +6174,49 @@
         </is>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="n">
-        <v>-135</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>488</v>
+    <row r="62" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7">
+        <v>-240</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-167</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 240 A JC - 167 A JC</t>
+        </is>
       </c>
       <c r="D62" s="8" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Posidonios"  title=" Wikipedia"&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770"  title="Posidonius d'Apamée théoricien de la géométrie par Persée"&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href="https://www.youtube.com/watch?v=EqU-kD8dW4Y" title="Grèce antique - 33 La civilisation hellénistique par Yannick Rub"&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289"  title="La philosophiede Posidonius par Persee"&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s" title="Wikipedia"&gt;TÉLÉCLÈS&lt;/a&gt; (mort vers 167 av. J.-C.) est un philosophe grec, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de Lacydès de Cyrène, il reçoit de lui, avec son condisciple Évandre, la direction de l’école du vivant même de leur maître, que la maladie empêchait d’enseigner. Les deux philosophes la dirigent ensemble, une organisation collégiale rare dans l’histoire de l’Académie.&lt;/p&gt; &lt;p&gt;Nous ne savons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu. Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par Arcésilas, qui avait donné à l’école de Platon une orientation sceptique en s’inspirant du Socrate qui affirmait ne rien savoir. Les académiciens de cette époque s’opposent avant tout aux stoïciens. Ceux-ci soutiennent qu’il existe des représentations « compréhensives », si claires et si distinctes qu’elles garantissent leur propre vérité et fondent la science. Les académiciens répondent qu’aucune perception ne peut être distinguée avec certitude d’une perception trompeuse : un rêve, une illusion d’optique ou deux jumeaux suffisent à le montrer. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;), mais il peut agir en suivant ce qui lui paraît raisonnable ou vraisemblable. L’enseignement se fait par la discussion : on argumente pour et contre chaque thèse, afin d’exercer l’esprit critique.&lt;/p&gt; &lt;p&gt;Après Téléclès et Évandre, la direction passe à Hégésinous de Pergame, puis à &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" style="color:#6A142A" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, qui donnera à l’Académie un éclat nouveau et portera le scepticisme jusqu’à Rome.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F62" s="7" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>494</v>
+        <v>342</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>478</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -6186,49 +6224,45 @@
         </is>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
-        <v>-110</v>
+        <v>-185</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philod%C3%A8me_de_Gadara" title="Wikipedia"&gt;PHILODÈME de Gadara&lt;/a&gt; était un philosophe et poète épicurien, originaire de Gadara en Syrie (l'actuelle Jordanie). Élève de Zénon de Sidon à Athènes, il s'installa en Campanie sous la protection du mécène romain Lucius Calpurnius Pison, proche de César, et anima un cercle intellectuel brillant qui accueillit le jeune Virgile et ses amis poètes.&lt;/p&gt; &lt;p&gt;Il défendit et enrichit la philosophie d'&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure" title="Épicure sur Wikipedia"&gt;Épicure&lt;/a&gt; en l'appliquant à des domaines nouveaux : la rhétorique, la musique, l'esthétique et la critique littéraire. Ses traités, longtemps perdus, ont été miraculeusement retrouvés dans la &lt;em&gt;Villa des Papyrus&lt;/em&gt; d'Herculanum, ensevelie par l'éruption du Vésuve en 79 apr. J.-C. Ces rouleaux carbonisés, partiellement déchiffrés grâce aux techniques modernes, constituent une source irremplaçable sur l'épicurisme tardif.&lt;/p&gt; &lt;p&gt;Philodème concilia la rigueur philosophique épicurienne — recherche de l'&lt;em&gt;ataraxie&lt;/em&gt; et du plaisir vertueux — avec une sensibilité poétique et artistique raffinée. Il représente l'épicurisme dans sa version la plus ouverte au monde des arts et de la culture romaine. Ses traités abordent aussi la morale : la colère, la mort, qu’il ne faut pas craindre, ou la « franchise » avec laquelle le maître corrige ses disciples. Poète, il a laissé une trentaine d’épigrammes, souvent amoureuses, conservées dans l’&lt;em&gt;Anthologie grecque&lt;/em&gt;. Les quelque 1 800 rouleaux de la villa, découverts à partir de 1752, sont aujourd’hui déchiffrés grâce à l’imagerie scientifique et à l’intelligence artificielle, sans qu’on ait besoin de les dérouler.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ca2cJql73D4</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Vie et oeuvre de Philodème" par Michel Onfray</t>
-        </is>
+        <v>481</v>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes"  title=" Wikipedia"&gt;PANÉTIUS DE RHODES&lt;/a&gt; (vers 185-109 av. J.-C.) est un philosophe stoïcien grec, qui a adapté le stoïcisme au monde romain. Issu d’une grande famille de Rhodes, il étudie à Athènes auprès de Diogène de Babylone, puis s’installe à Rome, où il devient l’ami et le conseiller de Scipion Émilien, le vainqueur de Carthage. Il prend ensuite la tête de l’école stoïcienne d’Athènes, de 129 à sa mort.&lt;/p&gt; &lt;p&gt;Panétius assouplit la &lt;a href="https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie"  title="Le Stoïcisme par apprendre la philo"&gt;pensée stoïcienne&lt;/a&gt; et la rapproche de Platon et d’Aristote, qu’il admire. Il abandonne plusieurs thèses de ses prédécesseurs : il doute de la divination, nie la conflagration universelle qui devait périodiquement détruire le monde, qu’il juge éternel, et refuse l’immortalité de l’âme. Surtout, il s’intéresse moins au sage idéal, presque introuvable, qu’à l’homme ordinaire qui progresse vers la sagesse. Sa morale part de la nature humaine : chacun porte en lui des tendances fondamentales où s’unissent la nature et la raison, la recherche de la vérité, le goût de l’ordre, le désir de grandeur d’âme et le sens de la communauté. Chacun doit aussi tenir compte de sa propre nature, de ses talents et de sa situation, comme un acteur choisit le rôle qui lui convient. Il en tire une éthique des « devoirs », les actions convenables de la vie quotidienne et de la vie publique, fondée sur la justice, la bienveillance et le sens de la mesure.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Du devoir&lt;/em&gt; est perdu, mais Cicéron l’a largement repris dans son &lt;em&gt;De officiis&lt;/em&gt;, l’un des livres de morale les plus lus en Europe jusqu’au XIXe siècle. Panétius a ainsi donné au stoïcisme le visage humaniste qu’adopteront les élites romaines.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>484</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>502</v>
+        <v>24</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>503</v>
+        <v>386</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6238,18 +6272,114 @@
     </row>
     <row r="64" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
+        <v>-135</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Posidonios"  title=" Wikipedia"&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770"  title="Posidonius d'Apamée théoricien de la géométrie par Persée"&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href="https://www.youtube.com/watch?v=EqU-kD8dW4Y" title="Grèce antique - 33 La civilisation hellénistique par Yannick Rub"&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289"  title="La philosophiede Posidonius par Persee"&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt;  </t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="I64" s="9"/>
+      <c r="J64" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="n">
+        <v>-110</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philod%C3%A8me_de_Gadara" title="Wikipedia"&gt;PHILODÈME de Gadara&lt;/a&gt; était un philosophe et poète épicurien, originaire de Gadara en Syrie (l'actuelle Jordanie). Élève de Zénon de Sidon à Athènes, il s'installa en Campanie sous la protection du mécène romain Lucius Calpurnius Pison, proche de César, et anima un cercle intellectuel brillant qui accueillit le jeune Virgile et ses amis poètes.&lt;/p&gt; &lt;p&gt;Il défendit et enrichit la philosophie d'&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure" title="Épicure sur Wikipedia"&gt;Épicure&lt;/a&gt; en l'appliquant à des domaines nouveaux : la rhétorique, la musique, l'esthétique et la critique littéraire. Ses traités, longtemps perdus, ont été miraculeusement retrouvés dans la &lt;em&gt;Villa des Papyrus&lt;/em&gt; d'Herculanum, ensevelie par l'éruption du Vésuve en 79 apr. J.-C. Ces rouleaux carbonisés, partiellement déchiffrés grâce aux techniques modernes, constituent une source irremplaçable sur l'épicurisme tardif.&lt;/p&gt; &lt;p&gt;Philodème concilia la rigueur philosophique épicurienne — recherche de l'&lt;em&gt;ataraxie&lt;/em&gt; et du plaisir vertueux — avec une sensibilité poétique et artistique raffinée. Il représente l'épicurisme dans sa version la plus ouverte au monde des arts et de la culture romaine. Ses traités abordent aussi la morale : la colère, la mort, qu’il ne faut pas craindre, ou la « franchise » avec laquelle le maître corrige ses disciples. Poète, il a laissé une trentaine d’épigrammes, souvent amoureuses, conservées dans l’&lt;em&gt;Anthologie grecque&lt;/em&gt;. Les quelque 1 800 rouleaux de la villa, découverts à partir de 1752, sont aujourd’hui déchiffrés grâce à l’imagerie scientifique et à l’intelligence artificielle, sans qu’on ait besoin de les dérouler.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ca2cJql73D4</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Vie et oeuvre de Philodème" par Michel Onfray</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="I65" s="9"/>
+      <c r="J65" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="n">
         <v>-106</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B66" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C66" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D66" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron"  style="color:#6A142A"  title=" Wikipedia"&gt; Marcus CICERON&lt;/a&gt; était un philosophe &lt;a href="https://fr.wiktionary.org/wiki/%C3%A9clectique"  style="color:#88A1E9"  title="L'éclectisme par Wiktionnaire"&gt;Électique&lt;/a&gt; Romain et le premier a rédiger en latin des ouvrages à une époque où le grec domine dans le monde intellectuel. Il est l'héritier d'une triple tradition : sceptique, stoïcienne et platonicienne. &lt;/p&gt; &lt;p&gt; 
 On connait sa théorie de la "nature humaine" qui selon lui est orientée vers la recherche du bien car les êtres humains sont naturellement doués d'une raison qui leur permet de discerner le bien du mal. Il a écrit de nombreux traités philosophiques, dont &lt;a href="https://fr.wikipedia.org/wiki/De_finibus_bonorum_et_malorum"  title="bien et maux par wikipedia"&gt;De Finibus Bonorum et Malorum&lt;/a&gt; (Sur les fins ultimes du bien et du mal) ainsi que "De Oratore", qui décrit l'art de la persuasion et la façon dont il peut être utilisé pour influencer les autres. &lt;/p&gt; &lt;p&gt;  
@@ -6258,322 +6388,224 @@
 </t>
         </is>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F66" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="G66" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="H64" s="9" t="s">
+      <c r="H66" s="9" t="s">
         <v>511</v>
-      </c>
-      <c r="I64" s="9"/>
-      <c r="J64" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P64">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="n">
-        <v>-94</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lucr%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;LUCRÈCE&lt;/a&gt; (vers 98-55 av. J.-C.) est un poète et philosophe romain, disciple d’Épicure, auteur d’un seul livre, l’un des chefs-d’œuvre de la littérature latine : &lt;em&gt;De la nature des choses&lt;/em&gt; (&lt;em&gt;De rerum natura&lt;/em&gt;). Nous ne savons presque rien de sa vie. La légende, rapportée par saint Jérôme, selon laquelle il serait devenu fou après avoir bu un philtre d’amour et se serait suicidé, a sans doute été inventée par ses adversaires.&lt;/p&gt; &lt;p&gt;Son poème, en six livres et près de 7 400 vers, expose la doctrine de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picurisme"  style="color:#88A1E9"  title="Epicurisme par Wikipedia"&gt;épicurisme&lt;/a&gt; pour délivrer les hommes de la peur. Rien ne naît de rien, rien ne retourne au néant : tout ce qui existe est fait d’atomes, invisibles et éternels, qui se meuvent dans le vide. En tombant, ils s’écartent parfois légèrement de leur trajectoire : ce &lt;a href="https://www.youtube.com/watch?v=7iQzfXtB4wc&amp;ab_channel=Coursitout"  style="color:#88A1E9"  title="Le clinamen par Coursitout"&gt;&lt;em&gt;clinamen&lt;/em&gt;&lt;/a&gt; explique la rencontre des atomes, la formation des mondes et la liberté humaine. L’âme elle-même est faite d’atomes très fins &lt;a href="https://www.youtube.com/watch?v=VKJsOwjD5P4&amp;ab_channel=librairiemollat"  style="color:#88A1E9"  title="Bernard Combeaud - Lucrèce, la naissance des choses"&gt;et se disperse&lt;/a&gt; à la mort. Il n’y a donc rien à craindre après la mort : « la mort n’est rien pour nous ». Les dieux existent, mais ne s’occupent pas des hommes. Lucrèce dénonce avec force la superstition, qui pousse au crime, comme le sacrifice d’Iphigénie par son propre père : « Tant la religion a pu inspirer de maux ! » Il décrit aussi la naissance de la vie et des sociétés humaines, du langage et des arts, et finit son poème par la terrible peste d’Athènes. Le bonheur est la paix de l’âme, que procurent des plaisirs simples et l’amitié.&lt;/p&gt; &lt;p&gt;Retrouvé en 1417 par l’humaniste Pogge, le poème a marqué Montaigne, Gassendi, les libertins et les Lumières.&lt;/p&gt;  &lt;audio controls title="Comment maîtriser ses passions ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-12.09.2016-ITEMA_21073425-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="I65" s="9"/>
-      <c r="J65" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="n">
-        <v>-80</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89n%C3%A9sid%C3%A8me"  style="color:#6A142A"  title=" Wikipedia"&gt;ÉNÉSIDÈME&lt;/a&gt; était un philosophe grec de la tradition sceptique.  Il vécu à une époque où le &lt;a href="https://www.youtube.com/watch?v=_En3Pz6sWL8" style="color:#88A1E9" title="Scepticisme et interpedendance par PHILOSOPHIA"&gt;scepticisme&lt;/a&gt; philosophique était en plein essor, en réaction aux dogmatismes des écoles philosophiques comme le stoïcisme et l'épicurisme.  &lt;/p&gt; &lt;p&gt; Il a systématisé les  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1918_num_20_2_2006" style="color:#88A1E9" title="Pour l'histoire du scepticisme antique : les tropes d'Énésidème contre la logique inductive par Persée"&gt;arguments sceptiques&lt;/a&gt; dans ce qu'on appelle les &lt;a href="https://guykarl.canalblog.com/archives/2012/08/31/25001663.html" style="color:#88A1E9" title="PYRRHONISME : les dix tropes d' ENESIDEME par Le jardin Philosophe"&gt;"Dix Modes"&lt;/a&gt;, qui visent à montrer que nos perceptions et nos jugements sont influencés par divers facteurs, rendant impossible l'accès à une connaissance certaine : &lt;/p&gt;
-&lt;p&gt;La diversité des animaux : Les espèces perçoivent le monde de manière différente, ce qui suggère que nos perceptions ne reflètent pas nécessairement la réalité objective. &lt;/p&gt;
-&lt;p&gt;La diversité des humains : Parmi les humains, les perceptions et les jugements varient considérablement, ce qui rend difficile de déterminer quelle perception est "correcte". &lt;/p&gt; &lt;p&gt;La diversité des sens : Les différents sens peuvent donner des informations contradictoires sur un même objet. &lt;/p&gt;
-&lt;p&gt;Les circonstances : Les conditions dans lesquelles nous percevons quelque chose peuvent influencer notre perception. &lt;/p&gt;
-&lt;p&gt;Les positions et distances : La position et la distance par rapport à un objet peuvent altérer notre perception de celui-ci. &lt;/p&gt; &lt;p&gt;Les mélanges : Les objets ne sont jamais perçus isolément, mais toujours dans un contexte qui peut influencer notre perception. &lt;/p&gt;
-&lt;p&gt;Les quantités et constitutions : La quantité et la composition d'un objet peuvent affecter la manière dont nous le percevons. &lt;/p&gt; &lt;p&gt;La relation : Tout est perçu en relation avec autre chose, ce qui rend difficile de connaître la nature intrinsèque d'un objet.&lt;/p&gt; &lt;p&gt;La fréquence ou la rareté : La fréquence avec laquelle nous rencontrons quelque chose peut influencer notre perception de sa valeur ou de sa nature. &lt;/p&gt; &lt;p&gt;Les coutumes et les croyances : Les habitudes culturelles et les croyances peuvent profondément influencer nos perceptions et nos jugements. &lt;/p&gt; &lt;p&gt; Ses arguments mettent en lumière les limites de notre capacité à connaître le monde de manière certaine et nous invitent à adopter une attitude plus humble et critique face à nos propres perceptions et jugements. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>528</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>252</v>
+        <v>182</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
+        <v>-94</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lucr%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;LUCRÈCE&lt;/a&gt; (vers 98-55 av. J.-C.) est un poète et philosophe romain, disciple d’Épicure, auteur d’un seul livre, l’un des chefs-d’œuvre de la littérature latine : &lt;em&gt;De la nature des choses&lt;/em&gt; (&lt;em&gt;De rerum natura&lt;/em&gt;). Nous ne savons presque rien de sa vie. La légende, rapportée par saint Jérôme, selon laquelle il serait devenu fou après avoir bu un philtre d’amour et se serait suicidé, a sans doute été inventée par ses adversaires.&lt;/p&gt; &lt;p&gt;Son poème, en six livres et près de 7 400 vers, expose la doctrine de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picurisme"  style="color:#88A1E9"  title="Epicurisme par Wikipedia"&gt;épicurisme&lt;/a&gt; pour délivrer les hommes de la peur. Rien ne naît de rien, rien ne retourne au néant : tout ce qui existe est fait d’atomes, invisibles et éternels, qui se meuvent dans le vide. En tombant, ils s’écartent parfois légèrement de leur trajectoire : ce &lt;a href="https://www.youtube.com/watch?v=7iQzfXtB4wc&amp;ab_channel=Coursitout"  style="color:#88A1E9"  title="Le clinamen par Coursitout"&gt;&lt;em&gt;clinamen&lt;/em&gt;&lt;/a&gt; explique la rencontre des atomes, la formation des mondes et la liberté humaine. L’âme elle-même est faite d’atomes très fins &lt;a href="https://www.youtube.com/watch?v=VKJsOwjD5P4&amp;ab_channel=librairiemollat"  style="color:#88A1E9"  title="Bernard Combeaud - Lucrèce, la naissance des choses"&gt;et se disperse&lt;/a&gt; à la mort. Il n’y a donc rien à craindre après la mort : « la mort n’est rien pour nous ». Les dieux existent, mais ne s’occupent pas des hommes. Lucrèce dénonce avec force la superstition, qui pousse au crime, comme le sacrifice d’Iphigénie par son propre père : « Tant la religion a pu inspirer de maux ! » Il décrit aussi la naissance de la vie et des sociétés humaines, du langage et des arts, et finit son poème par la terrible peste d’Athènes. Le bonheur est la paix de l’âme, que procurent des plaisirs simples et l’amitié.&lt;/p&gt; &lt;p&gt;Retrouvé en 1417 par l’humaniste Pogge, le poème a marqué Montaigne, Gassendi, les libertins et les Lumières.&lt;/p&gt;  &lt;audio controls title="Comment maîtriser ses passions ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-12.09.2016-ITEMA_21073425-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="I67" s="9"/>
+      <c r="J67" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7" t="n">
         <v>-20</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B68" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C68" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D68" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="E67" s="9" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philon_d%27Alexandrie"  style="color:#6A142A"  title=" Wikipedia"&gt;PHILON d'Alexandrie&lt;/a&gt;  était un philosophe juif hellénisé qui d'harmonisa la philosophie grecque, en particulier le platonisme et le stoïcisme, avec les enseignements de la Bible hébraïque. &lt;/p&gt; &lt;p&gt; Il a écrit de nombreux traités et des commentaires allégoriques sur les livres de la Torah et a interprété les textes bibliques à travers le prisme de la philosophie grecque, cherchant à dégager des significations philosophiques et morales profondes. Dans son œuvre &lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1962_num_161_1_7742" style="color:#88A1E9" title="Philon d'Alexandrie, De opificio mundi par Persée"&gt;"De Opificio Mundi"&lt;/a&gt;, il explore la Genèse en utilisant des concepts platoniciens. &lt;/p&gt; &lt;p&gt; Il tente de montrer que les enseignements de la Torah sont en harmonie avec les idées des grands philosophes grecs. Certaines de ses œuvres défendent la religion juive contre les critiques des païens et des autres philosophes. Par exemple, dans  &lt;a href="https://www.persee.fr/doc/rjuiv_0484-8616_1968_num_127_1_1588 " style="color:#88A1E9" title="        Schadenfreude chez Philon d'Alexandrie ? Note sur In Flaccum  par Persée"&gt;"Contre Flaccus"&lt;/a&gt; et "L'Ambassade à Gaius", il décrit les persécutions subies par les Juifs d'Alexandrie et plaide pour leurs droits. &lt;/p&gt; &lt;p&gt; Il est souvent considéré comme un précurseur de la philosophie religieuse et de la théologie mystique. &lt;/p&gt; &lt;p&gt;Dieu et le Logos : Il décrit Dieu comme transcendant et inconnaissable, mais il introduit également le concept du Logos comme un intermédiaire entre Dieu et le monde. Le Logos est à la fois la raison divine qui ordonne l'univers et le moyen par lequel Dieu interagit avec le monde. &lt;/p&gt;
 &lt;p&gt;Allégorie : Il utilise largement l'interprétation allégorique pour expliquer les textes bibliques. Il croit que les récits bibliques ont un sens littéral, mais aussi un sens spirituel plus profond qui peut être découvert par l'interprétation philosophique. &lt;/p&gt; &lt;p&gt;Éthique et Vertu : Il insiste sur l'importance de la vertu et de la vie morale. Il croit que l'étude de la philosophie et la pratique des vertus permettent à l'âme de se rapprocher de Dieu. &lt;/p&gt; &lt;p&gt; Bien qu'il soit resté fidèle au judaïsme, sa pensée a eu une influence significative sur les premiers penseurs chrétiens, tels que Clément d'Alexandrie et Origène. Son concept du Logos a notamment influencé la christologie chrétienne. &lt;/p&gt; &lt;p&gt; </t>
         </is>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F68" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="G68" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="H67" s="9" t="s">
+      <c r="H68" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="I67" s="9"/>
-      <c r="J67" s="2" t="s">
+      <c r="I68" s="9"/>
+      <c r="J68" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="K67" s="2" t="s">
+      <c r="K68" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L67" s="2" t="s">
+      <c r="L68" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="M67" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="N67" s="0" t="s">
+      <c r="N68" s="0" t="s">
         <v>540</v>
       </c>
-      <c r="O67" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="n">
+      <c r="O68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="7" t="n">
         <v>-4</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B69" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C69" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D69" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="E68" s="13" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que" title=" Wikipedia"&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href="https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Stoïcisme par le Précepteur"&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=J3wZoqElCgs" title="Who is Seneca par Daily Stoic "&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href="https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin" title="La vie Heureuse par Karl Baudoin"&gt; "une vie heureuse".&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : De la brièveté de la vie (consideration sur l’usage du temps). De la colère (sur la maîtrise de cette passion destructive). De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt; Sénèque est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href="https://www.youtube.com/watch?v=d_cge9OwVAs" title="La vie philosophique de Sénèque par Kosmos"&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title="Les lettres à Lucilius – Senèque  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="F69" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="G68" s="9" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">"Sénèque – Pourquoi vous gaspillez votre vie par Voyages Endormis</t>
         </is>
       </c>
-      <c r="H68" s="9" t="s">
+      <c r="H69" s="9" t="s">
         <v>547</v>
-      </c>
-      <c r="I68" s="9"/>
-      <c r="J68" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P68">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes" style="color:#6A142A" title="Wikipedia"&gt;AMMONIOS d’Athènes&lt;/a&gt; est un philosophe platonicien du Ier siècle, originaire d’Égypte, qui enseigna à Athènes et fut le maître de &lt;a href="https://fr.wikipedia.org/wiki/Plutarque" style="color:#6A142A" title="Plutarque sur Wikipedia"&gt;Plutarque&lt;/a&gt;. Celui-ci suivit ses leçons vers 66-67, à l’époque où l’empereur Néron visitait la Grèce. Ammonios était aussi un citoyen influent d’Athènes, où des inscriptions montrent qu’il exerça plusieurs fois la haute fonction de stratège.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit, et nous le connaissons presque uniquement par Plutarque, qui le met en scène dans plusieurs de ses dialogues comme un maître sage et bienveillant. Dans le traité &lt;em&gt;Sur l’E de Delphes&lt;/em&gt;, Plutarque et ses amis s’interrogent sur la lettre E gravée à l’entrée du temple d’Apollon. Ammonios conclut la discussion en y voyant le mot grec &lt;em&gt;ei&lt;/em&gt;, « tu es » : c’est la salutation que l’homme adresse au dieu. Seul le dieu « est » véritablement, éternel, un et immuable, alors que nous, soumis au temps et au changement, ne faisons que devenir et disparaître. Le précepte « Connais-toi toi-même », inscrit au même endroit, répond à ce salut en rappelant à l’homme sa faiblesse. Cette opposition entre l’être divin et le devenir humain est au cœur du platonisme de l’époque. Ammonios s’intéressait aussi aux mathématiques et à la science de la nature, et il voulait unir la philosophie à une piété religieuse fidèle aux traditions grecques.&lt;/p&gt; &lt;p&gt;Il appartient au « moyen platonisme », qui prépare, entre Platon et Plotin, le &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt;. Il ne faut pas le confondre avec Ammonios Saccas, maître de Plotin, ni avec Ammonios d’Alexandrie.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>555</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>236</v>
+        <v>386</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apollonios_de_Tyane"  style="color:#6A142A"  title=" Wikipedia"&gt; Apollonios de Tyane&lt;/a&gt;, né à Tyane en Cappadoce (Turquie),   est une figure emblématique de l’Antiquité, à la croisée de la philosophie, de la spiritualité et du mysticisme, souvent décrit comme un philosophe, thaumaturge et ascète.  Il est principalement associé au &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_pythagoricienne" title="Phytagorisme par wikipedia "&gt; pythagorisme&lt;/a&gt;, un courant philosophique inspiré des enseignements de Pythagore, pratique et ascétique, visant à transformer la vie par des principes éthiques rigoureux et une quête de sagesse. Il prônait une vie fondée sur la pureté, la discipline et l’harmonie universelle,  adoptant un mode de vie ascétique caractérisé par le végétarisme, l’abstinence de vin et un dévouement à la recherche de la sagesse. &lt;/p&gt; &lt;p&gt;   Comme de nombreux philosophes de son temps, il a entrepris de longs voyages pour acquérir des connaissances. Il se rendit notamment en Égypte, en Inde, en Mésopotamie et en Grèce. En Inde, il aurait rencontré des sages et des brahmanes qui auraient influencé sa pensée, assimilant et intégrant à sa pensée des éléments de traditions diverses.  &lt;/p&gt; &lt;p&gt; Au cours des siècles, il a souvent été comparé à Jésus-Christ, en raison des similitudes perçues entre leurs vies (miracles, ascétisme, message spirituel). Certains penseurs païens de l'Antiquité ont même présenté &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1999_num_1_3_1959" style="color:#88A1E9" title="Mythe avorté d'une sagesse totale par Persée "&gt; Apollonios&lt;/a&gt; comme une alternative païenne à Jésus, bien que les deux figures soient très différentes dans leur contexte et leur message. &lt;/p&gt; &lt;p&gt;Il incarte une forme de tolérance religieuse cosidérant que l'on peut reconnaitre sa religion dans la religion de l'autre.&lt;/p&gt; &lt;p&gt;  Sa vie, relatée par &lt;a href="https://fr.wikipedia.org/wiki/Philostrate_d%27Ath%C3%A8nes" style="color:#88A1E9" title="Philostrate par Wikipedia "&gt; Philostrate&lt;/a&gt; dans  &lt;a href="https://fr.wikipedia.org/wiki/Vie_d%27Apollonios_de_Tyane" style="color:#88A1E9" title="Vie d'Apollonios de Tyare par Wikipedia "&gt; Vie d’Apollonios de Tyane&lt;/a&gt;, mêle éléments historiques et légendaires. Profondément spirituel, il prônait une piété réfléchie et critiquait les pratiques religieuses vides de sens, notamment les sacrifices sanglants, préférant une relation intérieure avec le divin et des rituels plus éthiques. Convaincu de l’immortalité de l’âme et de la réincarnation, il voyait la philosophie comme une voie vers la purification spirituelle et morale. &lt;/p&gt; &lt;p&gt;Son engagement ne se limitait pas à la sphère personnelle : il joua un rôle actif dans la société en critiquant les tyrans, en défendant la justice et en conseillant les gouvernants. Considéré par ses contemporains comme un thaumaturge, il aurait accompli des miracles tels que des guérisons, des prédictions et des résurrections, bien que ces récits soient teintés de légende. Sa pensée et sa vie incarnaient une quête universelle de vérité et d'harmonie, cherchant à unifier les enseignements philosophiques et spirituels dans une vision globale.&lt;/p&gt; &lt;p&gt; Apollonios demeure une figure complexe, à mi-chemin entre le philosophe et le sage mystique, dont l'héritage, bien que controversé, continue d'inspirer les amateurs de sagesse antique. &lt;/p&gt;   
-</t>
+        <v>551</v>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes" style="color:#6A142A" title="Wikipedia"&gt;AMMONIOS d’Athènes&lt;/a&gt; est un philosophe platonicien du Ier siècle, originaire d’Égypte, qui enseigna à Athènes et fut le maître de &lt;a href="https://fr.wikipedia.org/wiki/Plutarque" style="color:#6A142A" title="Plutarque sur Wikipedia"&gt;Plutarque&lt;/a&gt;. Celui-ci suivit ses leçons vers 66-67, à l’époque où l’empereur Néron visitait la Grèce. Ammonios était aussi un citoyen influent d’Athènes, où des inscriptions montrent qu’il exerça plusieurs fois la haute fonction de stratège.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit, et nous le connaissons presque uniquement par Plutarque, qui le met en scène dans plusieurs de ses dialogues comme un maître sage et bienveillant. Dans le traité &lt;em&gt;Sur l’E de Delphes&lt;/em&gt;, Plutarque et ses amis s’interrogent sur la lettre E gravée à l’entrée du temple d’Apollon. Ammonios conclut la discussion en y voyant le mot grec &lt;em&gt;ei&lt;/em&gt;, « tu es » : c’est la salutation que l’homme adresse au dieu. Seul le dieu « est » véritablement, éternel, un et immuable, alors que nous, soumis au temps et au changement, ne faisons que devenir et disparaître. Le précepte « Connais-toi toi-même », inscrit au même endroit, répond à ce salut en rappelant à l’homme sa faiblesse. Cette opposition entre l’être divin et le devenir humain est au cœur du platonisme de l’époque. Ammonios s’intéressait aussi aux mathématiques et à la science de la nature, et il voulait unir la philosophie à une piété religieuse fidèle aux traditions grecques.&lt;/p&gt; &lt;p&gt;Il appartient au « moyen platonisme », qui prépare, entre Platon et Plotin, le &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt;. Il ne faut pas le confondre avec Ammonios Saccas, maître de Plotin, ni avec Ammonios d’Alexandrie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F70" s="7" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>564</v>
+        <v>59</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>565</v>
+        <v>236</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6581,45 +6613,46 @@
         </is>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Plutarque"  style="color:#6A142A"  title=" Wikipedia"&gt;PLUTARQUE&lt;/a&gt; était un philosophe, biographe et moraliste grec  célèbre pour ses &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1979_num_1_3_3621"  style="color:#88A1E9" title="La pensée de Plutarque dans les Vies  par Olivier Roland"&gt;œuvres&lt;/a&gt;  biographiques et philosophiques. Il  a vécu à une époque où la Grèce était sous domination romaine, mais la culture grecque restait très influente dans l'Empire. &lt;/p&gt;Philosophe éclectique profondément influencé par le platonisme, il croyait en l'importance de la vertu, de la modération et de la recherche de la sagesse. Il insiste sur la nécessité de vivre une vie vertueuse et équilibrée et aborde des thèmes comme la colère, la jalousie, et la manière de cultiver la paix intérieure. Il s'intéresse aux croyances religieuses et aux mythes, cherchant souvent à en donner une interprétation morale ou philosophique.&lt;p&gt; Il  est surtout connu pour deux collections d'œuvres : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=cOdbv-wbRWQ&amp;t=10s"  style="color:#88A1E9" title="Les Vies Parallèles des Hommes Illustres de Plutarque par Olivier Roland"&gt;Vies parallèles&lt;/a&gt; : Cette série de biographies compare des figures célèbres de l'histoire grecque et romaine. Chaque paire de vies met en parallèle un Grec et un Romain, suivie d'une comparaison qui souligne les similitudes et les différences entre les deux personnages. Parmi les paires les plus connues, on trouve Alexandre le Grand et Jules César, Thésée et Romulus, ou encore Démosthène et Cicéron. Son objectif  n'était pas seulement historique, mais aussi moral et éducatif. &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C5%92uvres_morales"  style="color:#88A1E9" title="Œuvres morales par Wikipedia"&gt;Moralia&lt;/a&gt;  : Cette collection regroupe des essais et des traités sur des sujets variés, allant de la philosophie morale à la religion, en passant par la politique, l'éducation et les sciences naturelles, la tranquillité de l'âme, l'amour, la superstition. &lt;/p&gt; &lt;p&gt; Il est connu pour son &lt;a href="https://www.youtube.com/watch?v=n7uLx5rVmm0"  style="color:#88A1E9" title="La Sérénité intérieure | PLUTARQUE  par Les Choses au Claire"&gt;style clair&lt;/a&gt; et accessible, qui combine profondeur philosophique et récit vivant. Ses biographies sont à la fois instructives et divertissantes, mêlant anecdotes, réflexions morales et détails historiques. Il  reste une figure majeure de la littérature et de la philosophie antique. Ses œuvres, à la fois biographiques et philosophiques, continuent d'être étudiées et appréciées pour leur richesse, leur sagesse et leur pertinence intemporelle. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title="  Actualité de Plutarque par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16278-17.12.2016-ITEMA_21168598-2016C6278E0292-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apollonios_de_Tyane"  style="color:#6A142A"  title=" Wikipedia"&gt; Apollonios de Tyane&lt;/a&gt;, né à Tyane en Cappadoce (Turquie),   est une figure emblématique de l’Antiquité, à la croisée de la philosophie, de la spiritualité et du mysticisme, souvent décrit comme un philosophe, thaumaturge et ascète.  Il est principalement associé au &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_pythagoricienne" title="Phytagorisme par wikipedia "&gt; pythagorisme&lt;/a&gt;, un courant philosophique inspiré des enseignements de Pythagore, pratique et ascétique, visant à transformer la vie par des principes éthiques rigoureux et une quête de sagesse. Il prônait une vie fondée sur la pureté, la discipline et l’harmonie universelle,  adoptant un mode de vie ascétique caractérisé par le végétarisme, l’abstinence de vin et un dévouement à la recherche de la sagesse. &lt;/p&gt; &lt;p&gt;   Comme de nombreux philosophes de son temps, il a entrepris de longs voyages pour acquérir des connaissances. Il se rendit notamment en Égypte, en Inde, en Mésopotamie et en Grèce. En Inde, il aurait rencontré des sages et des brahmanes qui auraient influencé sa pensée, assimilant et intégrant à sa pensée des éléments de traditions diverses.  &lt;/p&gt; &lt;p&gt; Au cours des siècles, il a souvent été comparé à Jésus-Christ, en raison des similitudes perçues entre leurs vies (miracles, ascétisme, message spirituel). Certains penseurs païens de l'Antiquité ont même présenté &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1999_num_1_3_1959" style="color:#88A1E9" title="Mythe avorté d'une sagesse totale par Persée "&gt; Apollonios&lt;/a&gt; comme une alternative païenne à Jésus, bien que les deux figures soient très différentes dans leur contexte et leur message. &lt;/p&gt; &lt;p&gt;Il incarte une forme de tolérance religieuse cosidérant que l'on peut reconnaitre sa religion dans la religion de l'autre.&lt;/p&gt; &lt;p&gt;  Sa vie, relatée par &lt;a href="https://fr.wikipedia.org/wiki/Philostrate_d%27Ath%C3%A8nes" style="color:#88A1E9" title="Philostrate par Wikipedia "&gt; Philostrate&lt;/a&gt; dans  &lt;a href="https://fr.wikipedia.org/wiki/Vie_d%27Apollonios_de_Tyane" style="color:#88A1E9" title="Vie d'Apollonios de Tyare par Wikipedia "&gt; Vie d’Apollonios de Tyane&lt;/a&gt;, mêle éléments historiques et légendaires. Profondément spirituel, il prônait une piété réfléchie et critiquait les pratiques religieuses vides de sens, notamment les sacrifices sanglants, préférant une relation intérieure avec le divin et des rituels plus éthiques. Convaincu de l’immortalité de l’âme et de la réincarnation, il voyait la philosophie comme une voie vers la purification spirituelle et morale. &lt;/p&gt; &lt;p&gt;Son engagement ne se limitait pas à la sphère personnelle : il joua un rôle actif dans la société en critiquant les tyrans, en défendant la justice et en conseillant les gouvernants. Considéré par ses contemporains comme un thaumaturge, il aurait accompli des miracles tels que des guérisons, des prédictions et des résurrections, bien que ces récits soient teintés de légende. Sa pensée et sa vie incarnaient une quête universelle de vérité et d'harmonie, cherchant à unifier les enseignements philosophiques et spirituels dans une vision globale.&lt;/p&gt; &lt;p&gt; Apollonios demeure une figure complexe, à mi-chemin entre le philosophe et le sage mystique, dont l'héritage, bien que controversé, continue d'inspirer les amateurs de sagesse antique. &lt;/p&gt;   
+</t>
         </is>
       </c>
       <c r="F71" s="7" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>368</v>
+        <v>564</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>236</v>
+        <v>565</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6627,224 +6660,222 @@
         </is>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>567</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89pict%C3%A8te"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICTETE&lt;/a&gt; (vers 50-vers 125) est un philosophe &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcien&lt;/a&gt; grec, né esclave à Hiérapolis, en Phrygie. À Rome, il appartient à Épaphrodite, affranchi de Néron, qui lui permet de suivre les leçons du stoïcien Musonius Rufus. Affranchi, il enseigne à son tour, jusqu’à ce que l’empereur Domitien chasse les philosophes de Rome vers 93 ; il ouvre alors une école à Nicopolis, en Épire, où il enseigne jusqu’à sa mort.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit. Son disciple &lt;a href="https://fr.wikipedia.org/wiki/Arrien" title=" Wikipedia"&gt;Arrien&lt;/a&gt; a noté ses leçons dans &lt;a href="https://www.youtube.com/watch?v=2tUxNx_oMn4&amp;ab_channel=KarlBaudoin"  style="color:#88A1E9"  title="Les Entretiens d'Epictète par Karl Baudouin"&gt;les &lt;em&gt;Entretiens&lt;/em&gt;&lt;/a&gt; et en a tiré un bref résumé, &lt;a href="https://www.youtube.com/watch?v=qN4m4bbZIGU&amp;t=51s&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Le manuel d'Epictète par Le Précepteur"&gt;le &lt;em&gt;Manuel&lt;/em&gt;&lt;/a&gt;. Tout part d’une distinction : il y a &lt;a href="https://www.youtube.com/watch?v=7Zc85Kc4Xqw&amp;ab_channel=KarlBaudoin"  title="Le manuel d'Epictète par Karl Baudouin"&gt;ce qui dépend de nous&lt;/a&gt;, nos jugements, nos désirs, nos refus, et ce qui ne dépend pas de nous, le corps, les biens, la réputation, les charges, les événements. Le malheur vient de ce que nous voulons maîtriser ce qui nous échappe. « Ce qui trouble les hommes, ce ne sont pas les choses, mais les jugements qu’ils portent sur les choses » : la mort n’est pas terrible, c’est l’opinion que nous en avons qui l’est. La liberté est donc intérieure, et l’esclave peut être plus libre que son maître. Le sage s’exerce chaque jour à bien juger, à désirer seulement ce qui dépend de lui, et à jouer son rôle dans le monde comme un acteur joue celui que l’auteur lui a donné. On résume sa morale par la formule « supporte et abstiens-toi ».&lt;/p&gt; &lt;p&gt;Lu par &lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le" title=" Wikipedia"&gt;Marc Aurèle&lt;/a&gt;, puis par Pascal et Montaigne, il inspire encore les thérapies cognitives d’aujourd’hui, qui apprennent à modifier nos jugements pour apaiser nos émotions.&lt;/p&gt;  &lt;audio controls title="Epictète ou savoir choisir par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-07.01.2026-ITEMA_24365714-2026C48904S0007-NET_MFC_C2619D7A-778C-4505-B127-925270631DD9-21-6f25ae2ae83c473a68406d0d4d07fa43.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Plutarque"  style="color:#6A142A"  title=" Wikipedia"&gt;PLUTARQUE&lt;/a&gt; était un philosophe, biographe et moraliste grec  célèbre pour ses &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1979_num_1_3_3621"  style="color:#88A1E9" title="La pensée de Plutarque dans les Vies  par Olivier Roland"&gt;œuvres&lt;/a&gt;  biographiques et philosophiques. Il  a vécu à une époque où la Grèce était sous domination romaine, mais la culture grecque restait très influente dans l'Empire. &lt;/p&gt;Philosophe éclectique profondément influencé par le platonisme, il croyait en l'importance de la vertu, de la modération et de la recherche de la sagesse. Il insiste sur la nécessité de vivre une vie vertueuse et équilibrée et aborde des thèmes comme la colère, la jalousie, et la manière de cultiver la paix intérieure. Il s'intéresse aux croyances religieuses et aux mythes, cherchant souvent à en donner une interprétation morale ou philosophique.&lt;p&gt; Il  est surtout connu pour deux collections d'œuvres : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=cOdbv-wbRWQ&amp;t=10s"  style="color:#88A1E9" title="Les Vies Parallèles des Hommes Illustres de Plutarque par Olivier Roland"&gt;Vies parallèles&lt;/a&gt; : Cette série de biographies compare des figures célèbres de l'histoire grecque et romaine. Chaque paire de vies met en parallèle un Grec et un Romain, suivie d'une comparaison qui souligne les similitudes et les différences entre les deux personnages. Parmi les paires les plus connues, on trouve Alexandre le Grand et Jules César, Thésée et Romulus, ou encore Démosthène et Cicéron. Son objectif  n'était pas seulement historique, mais aussi moral et éducatif. &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C5%92uvres_morales"  style="color:#88A1E9" title="Œuvres morales par Wikipedia"&gt;Moralia&lt;/a&gt;  : Cette collection regroupe des essais et des traités sur des sujets variés, allant de la philosophie morale à la religion, en passant par la politique, l'éducation et les sciences naturelles, la tranquillité de l'âme, l'amour, la superstition. &lt;/p&gt; &lt;p&gt; Il est connu pour son &lt;a href="https://www.youtube.com/watch?v=n7uLx5rVmm0"  style="color:#88A1E9" title="La Sérénité intérieure | PLUTARQUE  par Les Choses au Claire"&gt;style clair&lt;/a&gt; et accessible, qui combine profondeur philosophique et récit vivant. Ses biographies sont à la fois instructives et divertissantes, mêlant anecdotes, réflexions morales et détails historiques. Il  reste une figure majeure de la littérature et de la philosophie antique. Ses œuvres, à la fois biographiques et philosophiques, continuent d'être étudiées et appréciées pour leur richesse, leur sagesse et leur pertinence intemporelle. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title="  Actualité de Plutarque par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16278-17.12.2016-ITEMA_21168598-2016C6278E0292-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F72" s="7" t="s">
-        <v>65</v>
+        <v>571</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>200</v>
+        <v>368</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>386</v>
+        <v>236</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P72">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="73" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicomaque_de_G%C3%A9rase"  style="color:#6A142A"  title=" Wikipedia"&gt;NICOMAQUE de Gérase&lt;/a&gt; était un mathématicien et philosophe néo-pythagoricien grec mettant l'accent sur l'importance des nombres et de leurs propriétés dans la compréhension de l'univers. Pour lui, ils n'étaient pas de simples outils de calcul, mais des  &lt;a href="https://www.youtube.com/watch?v=Jbuap2Pahbg" style="color:#88A1E9" title=" Pourquoi rééditer l'Introduction arithmétique de Nicomaque de Gerasa en France ?  par LabEx HaStec"&gt;principes fondamentaux &lt;/a&gt; qui sous-tendent la réalité. Il cherchait à réduire les Formes platoniciennes et les catégories aristotéliciennes aux propriétés formelles des nombres. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus célèbre et le plus influent "Introduction à l'arithmétique" est un manuel fondamental qui a servi de base à l'arithmétique pendant une grande partie du Moyen Âge, notamment grâce à sa traduction et adaptation par Boèce (vers 505) dans son "De institutione arithmetica". Ce traité aborde des concepts comme les nombres figurés, les nombres parfaits, abondants et déficients, et la théorie des nombres en général. &lt;/p&gt; &lt;p&gt;  Dans son deuxième ovrage " Théologie de l'arithmétique", il  explore les significations mystiques et philosophiques des nombres, rattachant les propriétés numériques à des concepts divins et cosmologiques.   Il était également théoricien de la musique et musicologue où dans  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1956_num_69_324_3426" style="color:#88A1E9" title=" L'hexatonique grec d'après Nicomaque  par Persée"&gt; 'L'hexatonique"&lt;/a&gt;, il témoigne de son intérêt pour les relations mathématiques sous-jacentes à l'harmonie musicale. &lt;/p&gt; &lt;p&gt; Il  est une figure essentielle pour comprendre la philosophie et les mathématiques de l'Antiquité tardive, en particulier le courant néo-pythagoricien qui cherchait à concilier les doctrines platoniciennes et aristotéliciennes avec la mystique des nombres. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89pict%C3%A8te"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICTETE&lt;/a&gt; (vers 50-vers 125) est un philosophe &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcien&lt;/a&gt; grec, né esclave à Hiérapolis, en Phrygie. À Rome, il appartient à Épaphrodite, affranchi de Néron, qui lui permet de suivre les leçons du stoïcien Musonius Rufus. Affranchi, il enseigne à son tour, jusqu’à ce que l’empereur Domitien chasse les philosophes de Rome vers 93 ; il ouvre alors une école à Nicopolis, en Épire, où il enseigne jusqu’à sa mort.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit. Son disciple &lt;a href="https://fr.wikipedia.org/wiki/Arrien" title=" Wikipedia"&gt;Arrien&lt;/a&gt; a noté ses leçons dans &lt;a href="https://www.youtube.com/watch?v=2tUxNx_oMn4&amp;ab_channel=KarlBaudoin"  style="color:#88A1E9"  title="Les Entretiens d'Epictète par Karl Baudouin"&gt;les &lt;em&gt;Entretiens&lt;/em&gt;&lt;/a&gt; et en a tiré un bref résumé, &lt;a href="https://www.youtube.com/watch?v=qN4m4bbZIGU&amp;t=51s&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Le manuel d'Epictète par Le Précepteur"&gt;le &lt;em&gt;Manuel&lt;/em&gt;&lt;/a&gt;. Tout part d’une distinction : il y a &lt;a href="https://www.youtube.com/watch?v=7Zc85Kc4Xqw&amp;ab_channel=KarlBaudoin"  title="Le manuel d'Epictète par Karl Baudouin"&gt;ce qui dépend de nous&lt;/a&gt;, nos jugements, nos désirs, nos refus, et ce qui ne dépend pas de nous, le corps, les biens, la réputation, les charges, les événements. Le malheur vient de ce que nous voulons maîtriser ce qui nous échappe. « Ce qui trouble les hommes, ce ne sont pas les choses, mais les jugements qu’ils portent sur les choses » : la mort n’est pas terrible, c’est l’opinion que nous en avons qui l’est. La liberté est donc intérieure, et l’esclave peut être plus libre que son maître. Le sage s’exerce chaque jour à bien juger, à désirer seulement ce qui dépend de lui, et à jouer son rôle dans le monde comme un acteur joue celui que l’auteur lui a donné. On résume sa morale par la formule « supporte et abstiens-toi ».&lt;/p&gt; &lt;p&gt;Lu par &lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le" title=" Wikipedia"&gt;Marc Aurèle&lt;/a&gt;, puis par Pascal et Montaigne, il inspire encore les thérapies cognitives d’aujourd’hui, qui apprennent à modifier nos jugements pour apaiser nos émotions.&lt;/p&gt;  &lt;audio controls title="Epictète ou savoir choisir par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-07.01.2026-ITEMA_24365714-2026C48904S0007-NET_MFC_C2619D7A-778C-4505-B127-925270631DD9-21-6f25ae2ae83c473a68406d0d4d07fa43.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F73" s="7" t="s">
-        <v>585</v>
+        <v>65</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>538</v>
+        <v>386</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le"  style="color:#6A142A"  title=" Wikipedia"&gt;Marc AURÈLE&lt;/a&gt; (121-180) est un empereur romain et un philosophe stoïcien, le seul « empereur philosophe » de l’histoire romaine. Adopté par l’empereur Antonin le Pieux, il reçoit la meilleure éducation de son temps ; son maître Junius Rusticus lui fait lire les &lt;em&gt;Entretiens&lt;/em&gt; d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89pict%C3%A8te" title=" Wikipedia"&gt;Épictète&lt;/a&gt;, qui le marquent pour toujours. Empereur de 161 à sa mort, il passe une grande partie de son règne à défendre les frontières du Danube, au milieu d’une terrible épidémie.&lt;/p&gt; &lt;p&gt;C’est sous la tente, pendant ces campagnes, qu’il écrit en grec ses &lt;a href="https://fr.wikipedia.org/wiki/Pens%C3%A9es_pour_moi-m%C3%AAme"  title="Les pensées pour moi même de Marc AURELE "&gt;&lt;em&gt;Pensées pour moi-même&lt;/em&gt;&lt;/a&gt;, en douze livres. Ce n’est pas un traité destiné au public, mais &lt;a href="https://www.youtube.com/watch?v=KKSRqzRdBx0"  title="Les pensées pour moi même Marc AURELE par Kosmos"&gt;un journal intime&lt;/a&gt; d’exercices spirituels : il s’y rappelle les principes du stoïcisme pour mieux les vivre. Tout change et passe vite, les empires comme les hommes ; la mort est un phénomène naturel qu’il ne faut pas craindre. Le monde est un tout ordonné par la raison, et ce qui arrive doit être accepté comme une part de cet ordre. Ce qui nous trouble, ce ne sont pas les choses, mais nos jugements sur elles : il suffit de les corriger pour retrouver la paix dans cette « citadelle intérieure » que rien ne peut forcer. Marc Aurèle s’exhorte aussi à la justice et à la bienveillance : tous les hommes sont parents, membres d’une même cité universelle, et il faut instruire les méchants plutôt que s’irriter contre eux. « Dès l’aurore, dis-toi d’avance : je rencontrerai un indiscret, un ingrat, un insolent… »&lt;/p&gt; &lt;p&gt;Lu par Montaigne et Frédéric II, il connaît un vif succès &lt;a href="https://www.youtube.com/watch?v=1OeNwG_bxWg&amp;ab_channel=FranceCulture"   title="Les pensées de Marc AURELE au quotidien par France Culture"&gt;de nos jours&lt;/a&gt;, grâce notamment à Pierre Hadot, qui a montré dans &lt;em&gt;La Citadelle intérieure&lt;/em&gt; (1992) la portée de ces exercices.&lt;/p&gt;  &lt;audio controls title="Pensée pour moi même par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.01.2016-ITEMA_20899513-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        <v>583</v>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicomaque_de_G%C3%A9rase"  style="color:#6A142A"  title=" Wikipedia"&gt;NICOMAQUE de Gérase&lt;/a&gt; était un mathématicien et philosophe néo-pythagoricien grec mettant l'accent sur l'importance des nombres et de leurs propriétés dans la compréhension de l'univers. Pour lui, ils n'étaient pas de simples outils de calcul, mais des  &lt;a href="https://www.youtube.com/watch?v=Jbuap2Pahbg" style="color:#88A1E9" title=" Pourquoi rééditer l'Introduction arithmétique de Nicomaque de Gerasa en France ?  par LabEx HaStec"&gt;principes fondamentaux &lt;/a&gt; qui sous-tendent la réalité. Il cherchait à réduire les Formes platoniciennes et les catégories aristotéliciennes aux propriétés formelles des nombres. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus célèbre et le plus influent "Introduction à l'arithmétique" est un manuel fondamental qui a servi de base à l'arithmétique pendant une grande partie du Moyen Âge, notamment grâce à sa traduction et adaptation par Boèce (vers 505) dans son "De institutione arithmetica". Ce traité aborde des concepts comme les nombres figurés, les nombres parfaits, abondants et déficients, et la théorie des nombres en général. &lt;/p&gt; &lt;p&gt;  Dans son deuxième ovrage " Théologie de l'arithmétique", il  explore les significations mystiques et philosophiques des nombres, rattachant les propriétés numériques à des concepts divins et cosmologiques.   Il était également théoricien de la musique et musicologue où dans  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1956_num_69_324_3426" style="color:#88A1E9" title=" L'hexatonique grec d'après Nicomaque  par Persée"&gt; 'L'hexatonique"&lt;/a&gt;, il témoigne de son intérêt pour les relations mathématiques sous-jacentes à l'harmonie musicale. &lt;/p&gt; &lt;p&gt; Il  est une figure essentielle pour comprendre la philosophie et les mathématiques de l'Antiquité tardive, en particulier le courant néo-pythagoricien qui cherchait à concilier les doctrines platoniciennes et aristotéliciennes avec la mystique des nombres. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F74" s="7" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="2" t="s">
-        <v>512</v>
+        <v>23</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>386</v>
+        <v>538</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P74">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="75" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas"  title="Wikipedia"&gt;Ammonios SACCAS&lt;/a&gt; (vers 175-242) est un philosophe platonicien d’Alexandrie, maître de Plotin et l’un des inspirateurs du néoplatonisme. Son surnom de Saccas, le « porteur de sacs », rappelle peut-être qu’il fut d’abord portefaix sur les quais du port. Selon le philosophe Porphyre, il serait né dans une famille chrétienne et aurait ensuite choisi la philosophie grecque, ce que contestent les auteurs chrétiens.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit, et sa doctrine nous échappe en grande partie. Nous savons surtout qu’il fut un maître exceptionnel. Porphyre raconte que Plotin, à vingt-huit ans, avait suivi sans satisfaction les cours des professeurs les plus réputés d’Alexandrie, jusqu’à ce qu’un ami le conduise chez Ammonios. En sortant, Plotin s’écria : « Voilà celui que je cherchais ! » Il resta onze ans auprès de lui. Ammonios eut aussi pour élèves le philosophe Origène, à ne pas confondre avec le théologien chrétien du même nom, Érennius et peut-être le critique Longin. Ses disciples s’engagèrent à ne pas divulguer son enseignement, promesse que Plotin ne rompit qu’après les autres. Des auteurs plus tardifs lui attribuent l’idée que Platon et Aristote s’accordent sur l’essentiel, et une réflexion sur l’union de l’âme et du corps : l’âme, réalité spirituelle, s’unit au corps sans se mélanger à lui ni se corrompre. On le surnommait « l’instruit par Dieu ».&lt;/p&gt; &lt;p&gt;On l’appelle souvent le &lt;a href="https://www.youtube.com/watch?v=hSIeYrZa-X4"title=" Ammonios SACCAS maitre de Plotin  par Vox Temporis"&gt;« maître silencieux »&lt;/a&gt; : sans laisser une ligne, il a marqué, à travers Plotin, toute la tradition néoplatonicienne.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Aur%C3%A8le"  style="color:#6A142A"  title=" Wikipedia"&gt;Marc AURÈLE&lt;/a&gt; (121-180) est un empereur romain et un philosophe stoïcien, le seul « empereur philosophe » de l’histoire romaine. Adopté par l’empereur Antonin le Pieux, il reçoit la meilleure éducation de son temps ; son maître Junius Rusticus lui fait lire les &lt;em&gt;Entretiens&lt;/em&gt; d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89pict%C3%A8te" title=" Wikipedia"&gt;Épictète&lt;/a&gt;, qui le marquent pour toujours. Empereur de 161 à sa mort, il passe une grande partie de son règne à défendre les frontières du Danube, au milieu d’une terrible épidémie.&lt;/p&gt; &lt;p&gt;C’est sous la tente, pendant ces campagnes, qu’il écrit en grec ses &lt;a href="https://fr.wikipedia.org/wiki/Pens%C3%A9es_pour_moi-m%C3%AAme"  title="Les pensées pour moi même de Marc AURELE "&gt;&lt;em&gt;Pensées pour moi-même&lt;/em&gt;&lt;/a&gt;, en douze livres. Ce n’est pas un traité destiné au public, mais &lt;a href="https://www.youtube.com/watch?v=KKSRqzRdBx0"  title="Les pensées pour moi même Marc AURELE par Kosmos"&gt;un journal intime&lt;/a&gt; d’exercices spirituels : il s’y rappelle les principes du stoïcisme pour mieux les vivre. Tout change et passe vite, les empires comme les hommes ; la mort est un phénomène naturel qu’il ne faut pas craindre. Le monde est un tout ordonné par la raison, et ce qui arrive doit être accepté comme une part de cet ordre. Ce qui nous trouble, ce ne sont pas les choses, mais nos jugements sur elles : il suffit de les corriger pour retrouver la paix dans cette « citadelle intérieure » que rien ne peut forcer. Marc Aurèle s’exhorte aussi à la justice et à la bienveillance : tous les hommes sont parents, membres d’une même cité universelle, et il faut instruire les méchants plutôt que s’irriter contre eux. « Dès l’aurore, dis-toi d’avance : je rencontrerai un indiscret, un ingrat, un insolent… »&lt;/p&gt; &lt;p&gt;Lu par Montaigne et Frédéric II, il connaît un vif succès &lt;a href="https://www.youtube.com/watch?v=1OeNwG_bxWg&amp;ab_channel=FranceCulture"   title="Les pensées de Marc AURELE au quotidien par France Culture"&gt;de nos jours&lt;/a&gt;, grâce notamment à Pierre Hadot, qui a montré dans &lt;em&gt;La Citadelle intérieure&lt;/em&gt; (1992) la portée de ces exercices.&lt;/p&gt;  &lt;audio controls title="Pensée pour moi même par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.01.2016-ITEMA_20899513-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F75" s="7" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="2" t="s">
-        <v>604</v>
+        <v>512</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>538</v>
+        <v>386</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Plotin"  style="color:#6A142A"  title=" Wikipedia"&gt;PLOTIN&lt;/a&gt; (205-270) est le plus grand philosophe de l’Antiquité tardive et le fondateur du néoplatonisme. Né en Égypte, il étudie à Alexandrie pendant onze ans auprès d’&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas" title=" Wikipedia"&gt;Ammonios Saccas&lt;/a&gt;, puis suit l’expédition de l’empereur Gordien III contre la Perse pour connaître la sagesse des Perses et des Indiens. Il s’installe à Rome vers 245 et y ouvre une école fréquentée par des sénateurs et des médecins.&lt;/p&gt; &lt;p&gt;Ses 54 traités ont été classés par son disciple &lt;a href="https://fr.wikipedia.org/wiki/Porphyre_de_Tyr" title=" Wikipedia"&gt;Porphyre&lt;/a&gt; en six groupes de neuf, les &lt;a href="https://www.youtube.com/watch?v=_UTBOMazrcE&amp;t=699s&amp;ab_channel=R%C3%A9sonance%5Bs%5D"  style="color:#88A1E9"  title="Les Ennéades de Plotin: Au commencement était l'Un par Résonance"&gt;&lt;em&gt;Ennéades&lt;/em&gt;&lt;/a&gt;. Plotin y relit Platon pour en tirer un système : &lt;a href="https://www.youtube.com/watch?v=nZblkRaDj-Q&amp;ab_channel=PhiloCloud"  style="color:#88A1E9"  title="Au commencement était l'Un par PhiloCloud"&gt;au commencement est l’Un&lt;/a&gt;, principe absolument simple, au-delà de l’être et de la pensée, que l’on ne peut nommer. De lui procède, comme la lumière du soleil, l’Intellect, qui contient les Idées, puis l’Âme, qui anime le monde sensible ; la matière, au plus bas, n’est presque rien, une absence de forme. Tout être vient de l’Un et aspire à y retourner. L’âme humaine, tombée dans le corps, peut remonter vers sa source par la vertu, la philosophie et la contemplation de la beauté, jusqu’à l’union avec l’Un, une extase que Plotin aurait connue quatre fois. C’est une ascension où l’Intellect, &lt;a href="https://books.openedition.org/vrin/4250?lang=fr"  style="color:#88A1E9"  title="Une méthaphysique de l'amour par OpenEdition"&gt;« embrasé d’amour »&lt;/a&gt;, s’oublie lui-même : « Retranche tout. »&lt;/p&gt; &lt;p&gt;Ses dernières paroles auraient été : « Tâchez de faire remonter le divin qui est en vous au divin qui est dans l’univers. » Par Augustin et le Pseudo-Denys, il marque la mystique chrétienne, et Marsile Ficin le traduit à la Renaissance.&lt;/p&gt;  &lt;audio controls title="La beauté est elle d'abord intérieure ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-04.04.2019-ITEMA_22027092-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        <v>599</v>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas"  title="Wikipedia"&gt;Ammonios SACCAS&lt;/a&gt; (vers 175-242) est un philosophe platonicien d’Alexandrie, maître de Plotin et l’un des inspirateurs du néoplatonisme. Son surnom de Saccas, le « porteur de sacs », rappelle peut-être qu’il fut d’abord portefaix sur les quais du port. Selon le philosophe Porphyre, il serait né dans une famille chrétienne et aurait ensuite choisi la philosophie grecque, ce que contestent les auteurs chrétiens.&lt;/p&gt; &lt;p&gt;Il n’a rien écrit, et sa doctrine nous échappe en grande partie. Nous savons surtout qu’il fut un maître exceptionnel. Porphyre raconte que Plotin, à vingt-huit ans, avait suivi sans satisfaction les cours des professeurs les plus réputés d’Alexandrie, jusqu’à ce qu’un ami le conduise chez Ammonios. En sortant, Plotin s’écria : « Voilà celui que je cherchais ! » Il resta onze ans auprès de lui. Ammonios eut aussi pour élèves le philosophe Origène, à ne pas confondre avec le théologien chrétien du même nom, Érennius et peut-être le critique Longin. Ses disciples s’engagèrent à ne pas divulguer son enseignement, promesse que Plotin ne rompit qu’après les autres. Des auteurs plus tardifs lui attribuent l’idée que Platon et Aristote s’accordent sur l’essentiel, et une réflexion sur l’union de l’âme et du corps : l’âme, réalité spirituelle, s’unit au corps sans se mélanger à lui ni se corrompre. On le surnommait « l’instruit par Dieu ».&lt;/p&gt; &lt;p&gt;On l’appelle souvent le &lt;a href="https://www.youtube.com/watch?v=hSIeYrZa-X4"title=" Ammonios SACCAS maitre de Plotin  par Vox Temporis"&gt;« maître silencieux »&lt;/a&gt; : sans laisser une ligne, il a marqué, à travers Plotin, toute la tradition néoplatonicienne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F76" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"L’ascension de Plotin" par Vox Temporis</t>
-        </is>
+        <v>601</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>602</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="I76" s="9"/>
       <c r="J76" s="2" t="s">
@@ -6857,187 +6888,189 @@
         <v>538</v>
       </c>
       <c r="M76" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="n">
+        <v>205</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Plotin"  style="color:#6A142A"  title=" Wikipedia"&gt;PLOTIN&lt;/a&gt; (205-270) est le plus grand philosophe de l’Antiquité tardive et le fondateur du néoplatonisme. Né en Égypte, il étudie à Alexandrie pendant onze ans auprès d’&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_Saccas" title=" Wikipedia"&gt;Ammonios Saccas&lt;/a&gt;, puis suit l’expédition de l’empereur Gordien III contre la Perse pour connaître la sagesse des Perses et des Indiens. Il s’installe à Rome vers 245 et y ouvre une école fréquentée par des sénateurs et des médecins.&lt;/p&gt; &lt;p&gt;Ses 54 traités ont été classés par son disciple &lt;a href="https://fr.wikipedia.org/wiki/Porphyre_de_Tyr" title=" Wikipedia"&gt;Porphyre&lt;/a&gt; en six groupes de neuf, les &lt;a href="https://www.youtube.com/watch?v=_UTBOMazrcE&amp;t=699s&amp;ab_channel=R%C3%A9sonance%5Bs%5D"  style="color:#88A1E9"  title="Les Ennéades de Plotin: Au commencement était l'Un par Résonance"&gt;&lt;em&gt;Ennéades&lt;/em&gt;&lt;/a&gt;. Plotin y relit Platon pour en tirer un système : &lt;a href="https://www.youtube.com/watch?v=nZblkRaDj-Q&amp;ab_channel=PhiloCloud"  style="color:#88A1E9"  title="Au commencement était l'Un par PhiloCloud"&gt;au commencement est l’Un&lt;/a&gt;, principe absolument simple, au-delà de l’être et de la pensée, que l’on ne peut nommer. De lui procède, comme la lumière du soleil, l’Intellect, qui contient les Idées, puis l’Âme, qui anime le monde sensible ; la matière, au plus bas, n’est presque rien, une absence de forme. Tout être vient de l’Un et aspire à y retourner. L’âme humaine, tombée dans le corps, peut remonter vers sa source par la vertu, la philosophie et la contemplation de la beauté, jusqu’à l’union avec l’Un, une extase que Plotin aurait connue quatre fois. C’est une ascension où l’Intellect, &lt;a href="https://books.openedition.org/vrin/4250?lang=fr"  style="color:#88A1E9"  title="Une méthaphysique de l'amour par OpenEdition"&gt;« embrasé d’amour »&lt;/a&gt;, s’oublie lui-même : « Retranche tout. »&lt;/p&gt; &lt;p&gt;Ses dernières paroles auraient été : « Tâchez de faire remonter le divin qui est en vous au divin qui est dans l’univers. » Par Augustin et le Pseudo-Denys, il marque la mystique chrétienne, et Marsile Ficin le traduit à la Renaissance.&lt;/p&gt;  &lt;audio controls title="La beauté est elle d'abord intérieure ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-04.04.2019-ITEMA_22027092-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L’ascension de Plotin" par Vox Temporis</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="I77" s="9"/>
+      <c r="J77" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="M77" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P76">
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P77">
         <v>3</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="186.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
+    <row r="78" customFormat="false" ht="186.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="n">
         <v>213</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B78" s="7" t="s">
         <v>614</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C78" s="7" t="s">
         <v>615</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D78" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="E77" s="9" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Longin_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;LONGIN&lt;/a&gt; était un philosophe, rhéteur et critique littéraire grec de l'Antiquité tardive. Bien que sa vie et son œuvre soient peu documentée, il est connu pour son traité &lt;a href="https://remacle.org/bloodwolf/erudits/longin/sublime.htm" style="color:#88A1E9" title=" Login : traite du sublime par Remacle"&gt;"Du Sublime"&lt;/a&gt;, un texte majeur sur l'esthétique et la rhétorique. Ce texte explore la notion de sublime, un concept esthétique qui désigne ce qui élève l'âme, inspire l'admiration et transcende le banal. Le sublime se manifeste dans la littérature, l'art et la rhétorique, et il est souvent associé à la grandeur, à l'intensité émotionnelle et à la puissance expressive. Ses principales idées : &lt;p&gt; 
 &lt;p&gt;Le sublime est une qualité qui transcende la simple beauté ou l'élégance. Il provoque une émotion intense et une élévation spirituelle chez le lecteur ou l'auditeur. Il se manifeste dans des œuvres qui inspirent l'admiration, la crainte ou l'émerveillement. &lt;/p&gt; &lt;p&gt;Sources du sublime : Il identifie cinq sources principales du sublime : &lt;/p&gt; &lt;p&gt;La grandeur de la pensée : des idées profondes et élevées. &lt;/p&gt; &lt;p&gt;L'émotion intense : la capacité à toucher les sentiments du public. &lt;/p&gt; &lt;p&gt;Les figures de style : l'utilisation habile de métaphores, d'hyperboles, etc. &lt;/p&gt; &lt;p&gt;La noblesse de l'expression : un langage élégant et approprié. &lt;/p&gt; &lt;p&gt;La structure et l'arrangement : une composition harmonieuse et puissante. &lt;/p&gt; &lt;p&gt; Son analyse des techniques littéraires et de l'impact émotionnel de la parole a influencé la théorie rhétorique. "Du Sublime" est l'un des premiers textes à aborder la critique littéraire sous un angle esthétique et psychologique, en se concentrant sur l'effet des œuvres sur le public. Bien que sa vie soit mal documentée, son influence sur la pensée occidentale, en particulier dans les domaines de l'esthétique et de la rhétorique, est indéniable. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F78" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="G77" s="15" t="s">
+      <c r="G78" s="15" t="s">
         <v>619</v>
       </c>
-      <c r="H77" s="9" t="s">
+      <c r="H78" s="9" t="s">
         <v>620</v>
-      </c>
-      <c r="I77" s="9"/>
-      <c r="J77" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="n">
-        <v>234</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>623</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>624</v>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Porphyre_de_Tyr"  style="color:#6A142A"  title=" Wikipedia"&gt;PORPHYRE de Tyr&lt;/a&gt; était un philosophe néoplatonicien romain, érudit et polémiste d'origine phénicienne, né à Tyr, dans l'actuel Liban. Il est surtout connu pour son rôle dans le développement et la diffusion de la philosophie néoplatonicienne, ainsi que pour ses critiques du christianisme. Il est né sous le nom de Malchus (qui signifie "roi" en phénicien), mais il a adopté le nom de Porphyre (du grec porphyra, "pourpre", en référence à la pourpre tyrienne, une teinture prestigieuse produite dans sa ville natale). &lt;/p&gt; &lt;p&gt; Il est surtout connu pour avoir édité et publié les &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1924_num_22_5_5497"  style="color:#88A1E9" title="Les Ennéades de Plotin par Persée"&gt;Ennéades de Plotin&lt;/a&gt;, une collection systématique des écrits de son maître. Ses propres contributions philosophiques  : &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isagog%C3%A8"  style="color:#88A1E9" title="Isagogè par Wikipedia"&gt;L'Isagogè&lt;/a&gt; : Une introduction aux Catégories d'Aristote, qui est devenue un texte fondamental dans l'enseignement de la logique médiévale, tant dans le monde islamique qu'en Europe. &lt;/p&gt; &lt;p&gt;Commentaires sur Aristote et Platon : Porphyre a écrit des commentaires sur les œuvres d'Aristote et de Platon, cherchant à harmoniser leurs philosophies. &lt;/p&gt; &lt;p&gt;Philosophie religieuse : Il a exploré des thèmes comme la nature de l'âme, la purification spirituelle et la relation entre l'homme et le divin. &lt;/p&gt; &lt;p&gt; Il  est également connu pour son ouvrage &lt;a href="https://www.persee.fr/doc/reg_0035-2039_2014_num_127_2_8359_t16_0629_0000_2"  style="color:#88A1E9" title=" Le traité de Porphyre contre les chrétiens  par Persée"&gt;"Contre les chrétiens"&lt;/a&gt;, une critique virulente du christianisme naissant. Dans ce texte, il attaquait les doctrines chrétiennes, les Écritures et la figure de Jésus, qu'il considérait comme un personnage historique plutôt que divin. Malheureusement, l'ouvrage n'a survécu qu'à travers des citations et des réfutations par des auteurs chrétiens comme Eusèbe de Césarée et Augustin d'Hippone. &lt;/p&gt; &lt;p&gt; Porphyre de Tyr est une figure majeure de la philosophie antique, dont l'œuvre a servi de pont entre la pensée grecque classique et les développements intellectuels ultérieurs. Son engagement envers le néoplatonisme, ses contributions à la logique et ses critiques du christianisme en font un penseur complexe et influent, dont l'héritage continue d'être étudié et débattu. &lt;/p&gt;  &lt;/p&gt;   &lt;audio controls title=" Une histoire philosophique, feat. Porphyre et Jamblique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16260-13.03.2021-ITEMA_22601996-2021C6260S0072.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>626</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>628</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>76</v>
+        <v>359</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M78" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="7" t="n">
+        <v>234</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Porphyre_de_Tyr"  style="color:#6A142A"  title=" Wikipedia"&gt;PORPHYRE de Tyr&lt;/a&gt; était un philosophe néoplatonicien romain, érudit et polémiste d'origine phénicienne, né à Tyr, dans l'actuel Liban. Il est surtout connu pour son rôle dans le développement et la diffusion de la philosophie néoplatonicienne, ainsi que pour ses critiques du christianisme. Il est né sous le nom de Malchus (qui signifie "roi" en phénicien), mais il a adopté le nom de Porphyre (du grec porphyra, "pourpre", en référence à la pourpre tyrienne, une teinture prestigieuse produite dans sa ville natale). &lt;/p&gt; &lt;p&gt; Il est surtout connu pour avoir édité et publié les &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1924_num_22_5_5497"  style="color:#88A1E9" title="Les Ennéades de Plotin par Persée"&gt;Ennéades de Plotin&lt;/a&gt;, une collection systématique des écrits de son maître. Ses propres contributions philosophiques  : &lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isagog%C3%A8"  style="color:#88A1E9" title="Isagogè par Wikipedia"&gt;L'Isagogè&lt;/a&gt; : Une introduction aux Catégories d'Aristote, qui est devenue un texte fondamental dans l'enseignement de la logique médiévale, tant dans le monde islamique qu'en Europe. &lt;/p&gt; &lt;p&gt;Commentaires sur Aristote et Platon : Porphyre a écrit des commentaires sur les œuvres d'Aristote et de Platon, cherchant à harmoniser leurs philosophies. &lt;/p&gt; &lt;p&gt;Philosophie religieuse : Il a exploré des thèmes comme la nature de l'âme, la purification spirituelle et la relation entre l'homme et le divin. &lt;/p&gt; &lt;p&gt; Il  est également connu pour son ouvrage &lt;a href="https://www.persee.fr/doc/reg_0035-2039_2014_num_127_2_8359_t16_0629_0000_2"  style="color:#88A1E9" title=" Le traité de Porphyre contre les chrétiens  par Persée"&gt;"Contre les chrétiens"&lt;/a&gt;, une critique virulente du christianisme naissant. Dans ce texte, il attaquait les doctrines chrétiennes, les Écritures et la figure de Jésus, qu'il considérait comme un personnage historique plutôt que divin. Malheureusement, l'ouvrage n'a survécu qu'à travers des citations et des réfutations par des auteurs chrétiens comme Eusèbe de Césarée et Augustin d'Hippone. &lt;/p&gt; &lt;p&gt; Porphyre de Tyr est une figure majeure de la philosophie antique, dont l'œuvre a servi de pont entre la pensée grecque classique et les développements intellectuels ultérieurs. Son engagement envers le néoplatonisme, ses contributions à la logique et ses critiques du christianisme en font un penseur complexe et influent, dont l'héritage continue d'être étudié et débattu. &lt;/p&gt;  &lt;/p&gt;   &lt;audio controls title=" Une histoire philosophique, feat. Porphyre et Jamblique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16260-13.03.2021-ITEMA_22601996-2021C6260S0072.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="I79" s="9"/>
+      <c r="J79" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="M79" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="7" t="n">
         <v>245</v>
       </c>
-      <c r="B79" s="7" t="n">
+      <c r="B80" s="7" t="n">
         <v>325</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C80" s="7" t="s">
         <v>630</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="D80" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="E79" s="9" t="inlineStr">
+      <c r="E80" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jamblique" style="color:#6A142A" title="Wikipedia"&gt;JAMBLIQUE de Chalcis&lt;/a&gt; est l'un des penseurs les plus influents du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt;, figure centrale de l'école syrienne. Né à Chalcis en Syrie (l'actuelle Qinnasrin), il fut d'abord l'élève de Porphyre à Rome avant de fonder sa propre école en Syrie, à Apamée, devenant le maître d'une génération de néoplatoniciens.&lt;/p&gt; &lt;p&gt;Jamblique transforma profondément le néoplatonisme en y intégrant la &lt;em&gt;théurgie&lt;/em&gt; — la pratique rituelle permettant l'union avec le divin — comme voie indispensable au côté de la philosophie pure. Dans son œuvre maîtresse, &lt;em&gt;Les Mystères d'Égypte&lt;/em&gt; (&lt;em&gt;De Mysteriis&lt;/em&gt;), il répondit aux critiques de Porphyre en affirmant que la contemplation intellectuelle seule ne suffit pas : les rites sacrés sont nécessaires pour élever l'âme jusqu'au divin. Il développa aussi une hiérarchie complexe des êtres divins.&lt;/p&gt; &lt;p&gt;Jamblique enrichit le système de Plotin par une multiplication des hypostases divines et une intégration systématique des traditions religieuses orientales et chaldéennes. Son influence sur les néoplatoniciens tardifs (Proclus, Damascios) et sur l'&lt;a href="https://fr.wikipedia.org/wiki/Hermétisme" style="color:#6A142A" title="Hermétisme sur Wikipedia"&gt;hermétisme&lt;/a&gt; renaissant fut considérable. L'empereur Julien le tenait pour un maître de sagesse comparable à Platon lui-même. Grand admirateur de Pythagore, il consacre à sa vie et à sa doctrine une série d’ouvrages, dont une &lt;em&gt;Vie de Pythagore&lt;/em&gt; et une &lt;em&gt;Exhortation à la philosophie&lt;/em&gt;. Contre Plotin, il soutient que l’âme humaine descend tout entière dans le corps : elle ne peut donc remonter seule vers le divin et a besoin de l’aide des dieux. Il fixe aussi l’ordre de lecture des dialogues de Platon, que suivront les écoles néoplatoniciennes.&lt;/p&gt;  &lt;audio controls title="Une histoire philosophique : Porphyre et Jamblique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16260-13.03.2021-ITEMA_22601996-2021C6260S0072.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="F80" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="G79" s="9" t="s">
+      <c r="G80" s="9" t="s">
         <v>634</v>
       </c>
-      <c r="H79" s="12" t="s">
+      <c r="H80" s="12" t="s">
         <v>635</v>
-      </c>
-      <c r="I79" s="9"/>
-      <c r="J79" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="n">
-        <v>290</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>639</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marius_Victorinus"  style="color:#6A142A"  title=" Wikipedia"&gt;Marius VICTORINUS&lt;/a&gt; était un philosophe, africain de naissance puis romain enseignant la rhétorique et la philosophie.  Il s'est converti au Christianisme après avoir étudié les Écritures. Sa conversion a été perçue comme un symbole de la capacité du christianisme à attirer même les intellectuels les plus érudits. Il  a laissé une œuvre variée, à la fois philosophique et  &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1957_num_70_66_20268" style="color:#88A1E9" title=" Oeuvres théologiques de Marius Victorinus par Persée"&gt;théologique. &lt;/a&gt;&lt;p&gt;Avant sa conversion :  Il a écrit des commentaires sur des textes philosophiques grecs, notamment ceux d'Aristote et de Platon. Ces travaux montrent sa maîtrise de la philosophie néoplatonicienne, qui a profondément influencé sa pensée.  Il a traduit et adapté des œuvres néoplatoniciennes, comme celles de Plotin et de Porphyre, contribuant à diffuser ces idées dans le monde latin. &lt;/p&gt; &lt;p&gt;Après sa conversion :  Il s'est concentré sur des questions théologiques, en particulier sur la Trinité et la nature du Christ et de &lt;a href="https://www.youtube.com/watch?v=DCbfSqUZFs0" style="color:#88A1E9" title=" La notion de pré-étant selon Marius Victorinus  par Hervé Pasqua"&gt;l'être&lt;/a&gt;. Ses œuvres les plus importantes incluent : &lt;/p&gt; &lt;p&gt;Adversus Arium : Une défense de l'orthodoxie nicéenne contre  &lt;a href="https://fr.wikipedia.org/wiki/Arianisme" style="color:#88A1E9" title=" Arianisme par Wikipédia"&gt;l'arianisme&lt;/a&gt;, qui niait la divinité du Christ. &lt;/p&gt; &lt;p&gt;De generatione divini Verbi  : Un traité sur la relation entre le Père et le Fils dans la Trinité. &lt;/p&gt; &lt;p&gt;De Trinitate : Une exploration approfondie de la doctrine trinitaire, influencée par la philosophie néoplatonicienne. &lt;/p&gt; &lt;p&gt; Son utilisation des concepts néoplatoniciens pour expliquer des doctrines chrétiennes complexes, comme la Trinité, a influencé des théologiens ultérieurs, notamment saint Augustin. Il  a également contribué à la formation d'un langage théologique latin, en adaptant des concepts philosophiques grecs à la pensée chrétienne. &lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>644</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="2" t="s">
-        <v>512</v>
+        <v>636</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>76</v>
@@ -7046,7 +7079,7 @@
         <v>538</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7054,45 +7087,45 @@
         </is>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
-        <v>317</v>
+        <v>290</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9mistios"  style="color:#6A142A"  title=" Wikipedia"&gt;THÉMISTIOS&lt;/a&gt; (vers 317-388) est un philosophe, orateur et homme politique grec de l’Empire romain d’Orient. Fils d’un philosophe de Paphlagonie, il enseigne à Constantinople, la nouvelle capitale, et y devient sénateur en 355. Bien que resté païen, il sert successivement six empereurs, presque tous chrétiens, de Constance II à Théodose, qui le nomme préfet de la ville et lui confie l’éducation de son fils.&lt;/p&gt; &lt;p&gt;Il est d’abord connu pour ses &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_12_5759" style="color:#88A1E9" title=" d'Aristote par Themistius par Persée"&gt;paraphrases d’Aristote&lt;/a&gt;, des résumés commentés qui reformulent avec clarté les traités du philosophe : les &lt;em&gt;Seconds Analytiques&lt;/em&gt;, la &lt;em&gt;Physique&lt;/em&gt;, le traité &lt;em&gt;De l’âme&lt;/em&gt; et une partie de la &lt;em&gt;Métaphysique&lt;/em&gt;. Traduites en arabe, en hébreu puis en latin, elles ont été lues par Averroès et Thomas d’Aquin, en particulier pour la question de l’intellect. Thémistios est aussi un grand orateur. Dans ses &lt;a href="https://www.persee.fr/doc/topoi_1764-0733_2006_mel_7_1_2980" style="color:#88A1E9" title="Thémistios et ses adversaires : le témoignage du discours  par Persée"&gt;discours&lt;/a&gt;, adressés aux empereurs ou au Sénat, il défend une idée haute du rôle du philosophe : il ne doit pas fuir la cité, mais conseiller le pouvoir et rappeler au prince qu’il doit être une « loi vivante », juste et humain. Dans un discours célèbre adressé à l’empereur Jovien, en 364, il plaide pour la tolérance religieuse : Dieu, dit-il, se réjouit de la diversité des cultes, comme le chef d’une armée de la diversité de ses troupes, et nul ne doit être contraint dans sa foi.&lt;/p&gt; &lt;p&gt;Païen respecté des chrétiens, il illustre &lt;a href="https://www.youtube.com/watch?v=JdIUtCSF-JA" style="color:#88A1E9" title="«L’œuvre de Thémistios et son importance pour l’histoire de la philosophie» par Histoire de la mémoire et des idées"&gt;son rôle&lt;/a&gt; de médiateur entre la culture grecque et le nouvel Empire chrétien.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marius_Victorinus"  style="color:#6A142A"  title=" Wikipedia"&gt;Marius VICTORINUS&lt;/a&gt; était un philosophe, africain de naissance puis romain enseignant la rhétorique et la philosophie.  Il s'est converti au Christianisme après avoir étudié les Écritures. Sa conversion a été perçue comme un symbole de la capacité du christianisme à attirer même les intellectuels les plus érudits. Il  a laissé une œuvre variée, à la fois philosophique et  &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1957_num_70_66_20268" style="color:#88A1E9" title=" Oeuvres théologiques de Marius Victorinus par Persée"&gt;théologique. &lt;/a&gt;&lt;p&gt;Avant sa conversion :  Il a écrit des commentaires sur des textes philosophiques grecs, notamment ceux d'Aristote et de Platon. Ces travaux montrent sa maîtrise de la philosophie néoplatonicienne, qui a profondément influencé sa pensée.  Il a traduit et adapté des œuvres néoplatoniciennes, comme celles de Plotin et de Porphyre, contribuant à diffuser ces idées dans le monde latin. &lt;/p&gt; &lt;p&gt;Après sa conversion :  Il s'est concentré sur des questions théologiques, en particulier sur la Trinité et la nature du Christ et de &lt;a href="https://www.youtube.com/watch?v=DCbfSqUZFs0" style="color:#88A1E9" title=" La notion de pré-étant selon Marius Victorinus  par Hervé Pasqua"&gt;l'être&lt;/a&gt;. Ses œuvres les plus importantes incluent : &lt;/p&gt; &lt;p&gt;Adversus Arium : Une défense de l'orthodoxie nicéenne contre  &lt;a href="https://fr.wikipedia.org/wiki/Arianisme" style="color:#88A1E9" title=" Arianisme par Wikipédia"&gt;l'arianisme&lt;/a&gt;, qui niait la divinité du Christ. &lt;/p&gt; &lt;p&gt;De generatione divini Verbi  : Un traité sur la relation entre le Père et le Fils dans la Trinité. &lt;/p&gt; &lt;p&gt;De Trinitate : Une exploration approfondie de la doctrine trinitaire, influencée par la philosophie néoplatonicienne. &lt;/p&gt; &lt;p&gt; Son utilisation des concepts néoplatoniciens pour expliquer des doctrines chrétiennes complexes, comme la Trinité, a influencé des théologiens ultérieurs, notamment saint Augustin. Il  a également contribué à la formation d'un langage théologique latin, en adaptant des concepts philosophiques grecs à la pensée chrétienne. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F81" s="7" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>653</v>
+        <v>76</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>302</v>
+        <v>538</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7100,69 +7133,115 @@
         </is>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_de_Nysse"  style="color:#6A142A"  title=" Wikipedia"&gt;GRÉGOIRE de Nysse&lt;/a&gt; était un religieux et un mystique turc connu pour ses contributions à la &lt;a href="https://www.youtube.com/watch?v=-fOGBAaiNFE" style="color:#88A1E9" title="LA TRINITÉ EXPLIQUÉE  par Frere Paul Adrien"&gt;théologie trinitaire&lt;/a&gt; et à la mystique chrétienne. Il a insisté sur l'unité et l'égalité des trois personnes de la Trinité et a développé des arguments sophistiqués pour expliquer comment ils sont distinctes mais partagent une même essence divine. Il a également exploré la nature infinie de Dieu, soulignant qu'il est au-delà de toute compréhension humaine. Cette idée a influencé la tradition apophatique &lt;a href="https://www.youtube.com/watch?v=iSBm7R1Hlr4" style="color:#88A1E9" title="La théologie négative par Resonances"&gt;(ou théologie négative)&lt;/a&gt; dans le christianisme, qui soutient que Dieu ne peut être défini que par ce qu'il n'est pas. &lt;/p&gt; &lt;p&gt; Il a écrit abondamment sur la nature humaine et la destinée de l'âme  : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/scrip_0036-9772_1985_num_39_2_1409" style="color:#88A1E9" title="Deux fragments anciens (en minuscule de type « Anastase ») du De hominis opificio de Grégoire de Nysse par Persée"&gt;"De hominis opificio"&lt;/a&gt; :  il explore la création de l'homme à l'image de Dieu et la restauration de cette image à travers le Christ.&lt;/p&gt; &lt;p&gt;"La Vie de Moïse" :  il utilise l'histoire biblique de Moïse comme une allégorie pour décrire le cheminement de l'âme vers Dieu. Il décrit l'ascension spirituelle comme un processus infini, où l'âme est toujours en mouvement vers Dieu, sans jamais pouvoir l'atteindre complètement. &lt;/p&gt; &lt;p&gt;Contre Eunome : Une défense de la doctrine nicéenne contre les arguments de l'arien Eunome. &lt;/p&gt; &lt;p&gt;La Grande Catéchèse : Un exposé systématique de la foi chrétienne, destiné à l'instruction des catéchumènes. &lt;/p&gt; &lt;p&gt;Sur l'âme et la résurrection : Un dialogue sur la nature de l'âme et la résurrection, influencé par les dialogues platoniciens. &lt;/p&gt; &lt;p&gt; Il  a eu une influence durable sur la théologie chrétienne, en particulier dans les domaines de la mystique, de l'anthropologie théologique et de la doctrine trinitaire. Il est vénéré comme un saint dans les Églises catholique, orthodoxe et anglicane, et sa fête est célébrée le 9 mars dans l'Église catholique et le 10 janvier dans l'Église orthodoxe. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9mistios"  style="color:#6A142A"  title=" Wikipedia"&gt;THÉMISTIOS&lt;/a&gt; (vers 317-388) est un philosophe, orateur et homme politique grec de l’Empire romain d’Orient. Fils d’un philosophe de Paphlagonie, il enseigne à Constantinople, la nouvelle capitale, et y devient sénateur en 355. Bien que resté païen, il sert successivement six empereurs, presque tous chrétiens, de Constance II à Théodose, qui le nomme préfet de la ville et lui confie l’éducation de son fils.&lt;/p&gt; &lt;p&gt;Il est d’abord connu pour ses &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_12_5759" style="color:#88A1E9" title=" d'Aristote par Themistius par Persée"&gt;paraphrases d’Aristote&lt;/a&gt;, des résumés commentés qui reformulent avec clarté les traités du philosophe : les &lt;em&gt;Seconds Analytiques&lt;/em&gt;, la &lt;em&gt;Physique&lt;/em&gt;, le traité &lt;em&gt;De l’âme&lt;/em&gt; et une partie de la &lt;em&gt;Métaphysique&lt;/em&gt;. Traduites en arabe, en hébreu puis en latin, elles ont été lues par Averroès et Thomas d’Aquin, en particulier pour la question de l’intellect. Thémistios est aussi un grand orateur. Dans ses &lt;a href="https://www.persee.fr/doc/topoi_1764-0733_2006_mel_7_1_2980" style="color:#88A1E9" title="Thémistios et ses adversaires : le témoignage du discours  par Persée"&gt;discours&lt;/a&gt;, adressés aux empereurs ou au Sénat, il défend une idée haute du rôle du philosophe : il ne doit pas fuir la cité, mais conseiller le pouvoir et rappeler au prince qu’il doit être une « loi vivante », juste et humain. Dans un discours célèbre adressé à l’empereur Jovien, en 364, il plaide pour la tolérance religieuse : Dieu, dit-il, se réjouit de la diversité des cultes, comme le chef d’une armée de la diversité de ses troupes, et nul ne doit être contraint dans sa foi.&lt;/p&gt; &lt;p&gt;Païen respecté des chrétiens, il illustre &lt;a href="https://www.youtube.com/watch?v=JdIUtCSF-JA" style="color:#88A1E9" title="«L’œuvre de Thémistios et son importance pour l’histoire de la philosophie» par Histoire de la mémoire et des idées"&gt;son rôle&lt;/a&gt; de médiateur entre la culture grecque et le nouvel Empire chrétien.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F82" s="7" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K82" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="7" t="n">
+        <v>335</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_de_Nysse"  style="color:#6A142A"  title=" Wikipedia"&gt;GRÉGOIRE de Nysse&lt;/a&gt; était un religieux et un mystique turc connu pour ses contributions à la &lt;a href="https://www.youtube.com/watch?v=-fOGBAaiNFE" style="color:#88A1E9" title="LA TRINITÉ EXPLIQUÉE  par Frere Paul Adrien"&gt;théologie trinitaire&lt;/a&gt; et à la mystique chrétienne. Il a insisté sur l'unité et l'égalité des trois personnes de la Trinité et a développé des arguments sophistiqués pour expliquer comment ils sont distinctes mais partagent une même essence divine. Il a également exploré la nature infinie de Dieu, soulignant qu'il est au-delà de toute compréhension humaine. Cette idée a influencé la tradition apophatique &lt;a href="https://www.youtube.com/watch?v=iSBm7R1Hlr4" style="color:#88A1E9" title="La théologie négative par Resonances"&gt;(ou théologie négative)&lt;/a&gt; dans le christianisme, qui soutient que Dieu ne peut être défini que par ce qu'il n'est pas. &lt;/p&gt; &lt;p&gt; Il a écrit abondamment sur la nature humaine et la destinée de l'âme  : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/scrip_0036-9772_1985_num_39_2_1409" style="color:#88A1E9" title="Deux fragments anciens (en minuscule de type « Anastase ») du De hominis opificio de Grégoire de Nysse par Persée"&gt;"De hominis opificio"&lt;/a&gt; :  il explore la création de l'homme à l'image de Dieu et la restauration de cette image à travers le Christ.&lt;/p&gt; &lt;p&gt;"La Vie de Moïse" :  il utilise l'histoire biblique de Moïse comme une allégorie pour décrire le cheminement de l'âme vers Dieu. Il décrit l'ascension spirituelle comme un processus infini, où l'âme est toujours en mouvement vers Dieu, sans jamais pouvoir l'atteindre complètement. &lt;/p&gt; &lt;p&gt;Contre Eunome : Une défense de la doctrine nicéenne contre les arguments de l'arien Eunome. &lt;/p&gt; &lt;p&gt;La Grande Catéchèse : Un exposé systématique de la foi chrétienne, destiné à l'instruction des catéchumènes. &lt;/p&gt; &lt;p&gt;Sur l'âme et la résurrection : Un dialogue sur la nature de l'âme et la résurrection, influencé par les dialogues platoniciens. &lt;/p&gt; &lt;p&gt; Il  a eu une influence durable sur la théologie chrétienne, en particulier dans les domaines de la mystique, de l'anthropologie théologique et de la doctrine trinitaire. Il est vénéré comme un saint dans les Églises catholique, orthodoxe et anglicane, et sa fête est célébrée le 9 mars dans l'Église catholique et le 10 janvier dans l'Église orthodoxe. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="I83" s="9"/>
+      <c r="J83" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K83" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="L82" s="2" t="s">
+      <c r="L83" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="M82" s="2" t="s">
+      <c r="M83" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P82">
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P83">
         <v>2</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="239.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7" t="n">
+    <row r="84" customFormat="false" ht="239.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="7" t="n">
         <v>354</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B84" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C84" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="D83" s="8" t="s">
+      <c r="D84" s="8" t="s">
         <v>666</v>
       </c>
-      <c r="E83" s="9" t="inlineStr">
+      <c r="E84" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9lage_(h%C3%A9r%C3%A9siarque)"  style="color:#6A142A"  title=" Wikipedia"&gt;PÉLAGE&lt;/a&gt;  également connu sous le nom Pelagius en latin, était un moine et théologien britannique surtout connu pour avoir été au cœur d'une controverse théologique majeure dans l'histoire de l'Église chrétienne, connue sous le nom de &lt;a href="https://www.la-croix.com/Religion/Religion-et-spiritualite/Comprendre-pelagianisme-2018-11-17-1200983747" title="comprendre le Pélage par la Croix"&gt; pélagianisme&lt;/a&gt;. 
 Originaire des îles britanniques, actif principalement à Rome et en Afrique du Nord au début du Ve siècle, il était profondément engagé dans la vie monastique et était reconnu pour son ascétisme rigoureux. &lt;/p&gt; &lt;p&gt;La principale controverse associée à Pelage concernait la question de la nature du péché, de la grâce et du libre arbitre. Pelage soutenait que les êtres humains avaient la capacité intrinsèque de choisir le bien et d'éviter le péché sans l'aide de la grâce divine. Il rejetait l'idée du péché originel, enseignant que chaque personne naissait dans un état d'innocence et avait la possibilité de vivre une vie sans péché.&lt;/p&gt;
@@ -7170,254 +7249,206 @@
 &lt;p&gt;Le &lt;a href="https://www.youtube.com/watch?v=AnKeIzmox0s" title="la victoire de st Augustin sur Pélage par Michel Onfray"&gt; débat&lt;/a&gt; entre Pelage et Augustin a finalement conduit à plusieurs conciles et décrets ecclésiastiques condamnant  le pélagianisme comme une hérésie. Malgré cela, les idées de Pelage ont continué à influencer certains courants de pensée chrétienne ou religuieux comme Fauste de Riez, et la controverse pélagienne a laissé une marque durable sur l'histoire théologique de l'Église.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F83" s="7" t="s">
+      <c r="F84" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="G83" s="9" t="s">
+      <c r="G84" s="9" t="s">
         <v>669</v>
       </c>
-      <c r="H83" s="9" t="s">
+      <c r="H84" s="9" t="s">
         <v>670</v>
-      </c>
-      <c r="I83" s="9"/>
-      <c r="J83" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7" t="n">
-        <v>354</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>674</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>680</v>
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="2" t="s">
-        <v>512</v>
+        <v>671</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>76</v>
+        <v>672</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>681</v>
+        <v>662</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P84">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="85" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>685</v>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hypatie"  style="color:#6A142A"  title=" Wikipedia"&gt;HYPATIE d'Alexandrie&lt;/a&gt; était est une figure emblématique de l'Antiquité tardive, connue pour ses contributions à la philosophie, aux mathématiques et à l'astronomie. Elle est souvent considérée comme l'une des  &lt;a href="https://laviedesidees.fr/Hypatie-d-Alexandrie-femme-antique-figures-contemporaines" style="color:#88A1E9" title="Hypatie d’Alexandrie : femme antique, figures contemporaines par College de France"&gt;premières femmes&lt;/a&gt; scientifiques de l'histoire. Elle était la fille de Théon d'Alexandrie, un mathématicien et astronome renommé qui a joué un rôle crucial dans l'éducation de sa fille et elle a rapidement surpassé son père en renommée et en compétence, devenant une enseignante respectée et une érudite de premier plan. &lt;/p&gt; &lt;p&gt; Elle  a  &lt;a href="https://www.youtube.com/watch?v=gXk4fZ41Dyc" style="color:#88A1E9" title="La vie mystérieuse d'Hypatie : grande philosophe et mathématicienne ! par Kidaia"&gt;édité&lt;/a&gt; des œuvres mathématiques importantes, notamment les "Éléments" d'Euclide et les "Coniques" d'Apollonius de Perga et a travaillé sur des traités d'astronomie, collaborant avec son père pour réviser et commenter l'"Almageste" de Ptolémée. Elle a peut-être aussi contribué à la conception de &lt;a href="https://www.youtube.com/watch?v=c6Ab5oMIMoc"title="L'Astrolabe par Institut du monde arabe"&gt;" l'Astrolabe "&lt;/a&gt;, un instrument utilisé pour mesurer la position des astres. &lt;/p&gt; &lt;p&gt; Hypatie était une adepte du néoplatonisme, une école de pensée philosophique qui cherchait à synthétiser les idées de Platon avec d'autres traditions philosophiques et religieuses. Elle a dirigé une école néoplatonicienne à Alexandrie, attirant des étudiants de tout l'Empire romain. &lt;/p&gt; &lt;p&gt; En tant que païenne et symbole de la science et de la philosophie antiques, elle est devenue une cible pour les chrétiens radicaux et a été brutalement assassinée par une foule dirigée par des partisans de l'évêque Cyrille d'Alexandrie. Sa mort est souvent considérée comme un tournant symbolique dans le déclin de la culture païenne et de la liberté intellectuelle dans l'Empire romain. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title=" Hypatie d'Alexandrie, enseigner les maths envers et contre tout par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25546-14.01.2025-ITEMA_23980317-2025F54134E0003-NET_MFI_25ED747B-707B-4A53-94F6-7EEB0584D30D-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
-        </is>
+        <v>676</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>677</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="7" t="n">
+        <v>355</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hypatie"  style="color:#6A142A"  title=" Wikipedia"&gt;HYPATIE d'Alexandrie&lt;/a&gt; était est une figure emblématique de l'Antiquité tardive, connue pour ses contributions à la philosophie, aux mathématiques et à l'astronomie. Elle est souvent considérée comme l'une des  &lt;a href="https://laviedesidees.fr/Hypatie-d-Alexandrie-femme-antique-figures-contemporaines" style="color:#88A1E9" title="Hypatie d’Alexandrie : femme antique, figures contemporaines par College de France"&gt;premières femmes&lt;/a&gt; scientifiques de l'histoire. Elle était la fille de Théon d'Alexandrie, un mathématicien et astronome renommé qui a joué un rôle crucial dans l'éducation de sa fille et elle a rapidement surpassé son père en renommée et en compétence, devenant une enseignante respectée et une érudite de premier plan. &lt;/p&gt; &lt;p&gt; Elle  a  &lt;a href="https://www.youtube.com/watch?v=gXk4fZ41Dyc" style="color:#88A1E9" title="La vie mystérieuse d'Hypatie : grande philosophe et mathématicienne ! par Kidaia"&gt;édité&lt;/a&gt; des œuvres mathématiques importantes, notamment les "Éléments" d'Euclide et les "Coniques" d'Apollonius de Perga et a travaillé sur des traités d'astronomie, collaborant avec son père pour réviser et commenter l'"Almageste" de Ptolémée. Elle a peut-être aussi contribué à la conception de &lt;a href="https://www.youtube.com/watch?v=c6Ab5oMIMoc"title="L'Astrolabe par Institut du monde arabe"&gt;" l'Astrolabe "&lt;/a&gt;, un instrument utilisé pour mesurer la position des astres. &lt;/p&gt; &lt;p&gt; Hypatie était une adepte du néoplatonisme, une école de pensée philosophique qui cherchait à synthétiser les idées de Platon avec d'autres traditions philosophiques et religieuses. Elle a dirigé une école néoplatonicienne à Alexandrie, attirant des étudiants de tout l'Empire romain. &lt;/p&gt; &lt;p&gt; En tant que païenne et symbole de la science et de la philosophie antiques, elle est devenue une cible pour les chrétiens radicaux et a été brutalement assassinée par une foule dirigée par des partisans de l'évêque Cyrille d'Alexandrie. Sa mort est souvent considérée comme un tournant symbolique dans le déclin de la culture païenne et de la liberté intellectuelle dans l'Empire romain. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title=" Hypatie d'Alexandrie, enseigner les maths envers et contre tout par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25546-14.01.2025-ITEMA_23980317-2025F54134E0003-NET_MFI_25ED747B-707B-4A53-94F6-7EEB0584D30D-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="I86" s="9"/>
+      <c r="J86" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K85" s="2" t="s">
+      <c r="K86" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="L85" s="2" t="s">
+      <c r="L86" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="M85" s="2" t="s">
+      <c r="M86" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="n">
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="n">
         <v>365</v>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B87" s="1" t="n">
         <v>437</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="E86" s="11" t="inlineStr">
+      <c r="E87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Syrianos" title="Wikipedia"&gt;SYRIANOS&lt;/a&gt;  est un philosophe néoplatonicien grec, chef de l’école néoplatonicienne d’Athènes après Plutarque d’Athènes et maître de Proclus. Il appartient à la génération intermédiaire qui relie Porphyre–Jamblique à Proclus, et joue un rôle central dans la structuration théologique du néoplatonisme tardif. Formé sous Plutarque d’Athènes, Syrianos en devient le successeur comme scolarque (chef d’école) à sa mort vers 432. Il enseigne à Athènes une doctrine platonicienne fortement imprégnée de pythagorisme et de théurgie, et forme plusieurs penseurs importants, dont Hermias d’Alexandrie, Proclus et, plus tard, Marinos de Néapolis. &lt;/p&gt; &lt;p&gt; Il vise à unifier la tradition orphique, pythagoricienne, platonicienne et les « Oracles chaldaïques » en une théologie harmonieuse, en montrant que tous  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2022_num_124_2_7100_t11_0584_0000_1" title="Sur les états de cause par Persée"&gt;ces courants expriment &lt;/a&gt; fondamentalement la même vérité divine. Il articule la réalité en trois niveaux : le plan intelligible (les Formes pures), le plan discursif (le niveau intermédiaire, demiurgique, où les formes agissent comme principes), le plan sensible (le monde physique). &lt;/p&gt; Il marque une étape décisive dans la « théologisation » progressive du platonisme tardif : il privilégie la théurgie (la pratique rituelle et symbolique) autant que la simple contemplation philosophique, ce qui le rapproche de Jamblique et annonce Proclus. De nombreux penseurs ultérieurs, y compris Damascios et les auteurs de la tradition arabe et médiévale, reprennent ou transforment ses idées sur la hiérarchie des principes et la structure des niveaux de réalité. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F87" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G87" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="H86" s="16" t="s">
+      <c r="H87" s="16" t="s">
         <v>697</v>
       </c>
-      <c r="J86" s="2" t="s">
+      <c r="J87" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K86" s="2" t="s">
+      <c r="K87" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L86" s="2" t="s">
+      <c r="L87" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="M86" s="2" t="s">
+      <c r="M87" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="n">
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B88" s="1" t="n">
         <v>413</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="E87" s="17" t="inlineStr">
+      <c r="E88" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Syn%C3%A9sios_de_Cyr%C3%A8ne"   title=" Wikipédia"&gt; SYNÉSIOS de Cyrène&lt;/a&gt; était un philosophe  néoplatonicien, écrivain et évêque chrétien de la fin de l’Antiquité, originaire de Cyrène dans la Cyrénaïque (actuelle Libye). Il est connu à la fois comme  &lt;a href="https://www.youtube.com/watch?v=cPXvYhOuVwc" title="Synesius of Cyrene par Sun of Antiquity"&gt;homme de lettres &lt;/a&gt; païen‑platonicien puis comme évêque de Ptolémaïs, incarnant un cas emblématique de passage entre paganisme hellénistique et christianisme tardif. &lt;/p&gt; &lt;p&gt; Il est un chrétien platonisant : il articule la tradition néoplatonicienne (Platon, Plotin, Porphyre) avec la foi chrétienne, notamment dans ses hymnes et ses traités. Dans ses Hymnes, il célèbre Dieu comme principe suprême et source de lumière, en reprenant des images platoniciennes de l’Un et du Bien, mais dans un cadre monothéiste. Dans le Traité sur les songes (vers 403), il défend l’idée que les rêves sont des oracles véritables, à condition d’être « déchiffrés » par une intelligence philosophique et morale ; il accorde une grande importance à l’imagination et à l’âme dans la communication divine. &lt;/p&gt; &lt;p&gt; Il  joue un rôle important dans la vie politique de la Cyrénaïque : il participe à une ambassade devant l’empereur à Constantinople entre 399 et 402, où il rédige notamment le Discours sur la royauté et les Récits égyptiens, des  &lt;a href="https://www.persee.fr/doc/etaf_0768-2352_1987_mon_1_1" title="Synesios de Cyrène et la Cyrénaique du bas-empire par Persée"&gt;textes allégoriques &lt;/a&gt; qui mêlent politique, philosophie et rhétorique. &lt;/p&gt; Sa correspondance (environ 150 lettres conservées) est une source précieuse sur la vie intellectuelle et religieuse de l’Antiquité tardive, les rapports entre philosophie et foi, et le rôle de personnages comme Hypatie. Il  incarne une figure de transition entre le monde païen néoplatonicien et le christianisme tardif, unissant la rigueur philosophique, l’art rhétorique et une spiritualité syncrétique très caractéristique de son époque. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H88" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="J87" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="M87" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="204" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7" t="n">
-        <v>412</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>707</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="E88" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Proclus"   title="Proclus par Wikipédia"&gt;PROCLUS&lt;/a&gt; (412-485) est un philosophe &lt;a href="https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D"   title="Le Néoplatonisme par Anne Baudart"&gt;néoplatonicien grec&lt;/a&gt;, l’un des derniers grands penseurs de l’Antiquité. Né à Constantinople, il étudie à Alexandrie, puis à Athènes auprès de Syrianus, auquel il succède à la tête de l’école platonicienne : on l’appelle le « diadoque », le successeur. Il la dirige près de cinquante ans. Végétarien, très pieux, il célèbre les fêtes de tous les peuples, car le philosophe doit être, disait-il, « le prêtre du monde entier ».&lt;/p&gt; &lt;p&gt;Il laisse un grand nombre d’&lt;a href="https://remacle.org/bloodwolf/philosophes/proclus/table.htm"   title="Proclus par Philippe Remacle"&gt;ouvrages&lt;/a&gt;, dont des commentaires de Platon, sur le &lt;em&gt;Timée&lt;/em&gt;, la &lt;em&gt;République&lt;/em&gt;, le &lt;em&gt;Parménide&lt;/em&gt; ou l’&lt;em&gt;Alcibiade&lt;/em&gt;, et un commentaire du premier livre d’Euclide, précieuse source sur l’histoire de la géométrie. Dans les &lt;a href="https://www.youtube.com/watch?v=SJK1kbyXXno"   title="Les éléments de Théologie de Proclus par LabEx HaStec"&gt;&lt;em&gt;Éléments de théologie&lt;/em&gt;&lt;/a&gt;, il expose son système en 211 propositions démontrées à la manière des mathématiciens ; la &lt;em&gt;Théologie platonicienne&lt;/em&gt; le développe. Au sommet se trouve l’Un, principe absolument simple et indicible. De lui procèdent les hénades, qui sont les dieux, puis l’Intellect, l’Âme et enfin la nature et la matière. Tout se déploie selon un même rythme à trois temps : chaque réalité demeure dans sa cause, en procède, puis se retourne vers elle. L’âme humaine peut ainsi remonter vers l’Un par la philosophie, mais aussi par la théurgie, les rites qui unissent aux dieux.&lt;/p&gt; &lt;p&gt;À travers le Pseudo-Denys et le &lt;em&gt;Livre des causes&lt;/em&gt;, adaptation arabe de ses &lt;em&gt;Éléments&lt;/em&gt;, sa pensée marque le Moyen Âge, de Thomas d’Aquin à Maître Eckhart, puis Nicolas de Cues et Hegel.&lt;/p&gt;  &lt;audio controls title=" Proclus, un philosophe étoilé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>710</v>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Une vie, une œuvre" par Rien ne veut rien dire</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>712</v>
-      </c>
-      <c r="I88" s="9"/>
       <c r="J88" s="2" t="s">
         <v>23</v>
       </c>
@@ -7428,60 +7459,55 @@
         <v>538</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P88">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7">
-        <v>410</v>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">470</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vers 410 – avant 470</t>
-        </is>
+    </row>
+    <row r="89" customFormat="false" ht="204" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="7" t="n">
+        <v>412</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>707</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie" style="color:#6A142A" title="Wikipedia"&gt;HERMIAS d’Alexandrie&lt;/a&gt; est un philosophe néoplatonicien du Ve siècle, maillon important entre les écoles d’Athènes et d’Alexandrie. Né à Alexandrie, il part étudier à Athènes auprès du grand &lt;a href="https://fr.wikipedia.org/wiki/Syrianos" title="Syrianus sur Wikipedia"&gt;Syrianus&lt;/a&gt;, qui dirige alors l’école platonicienne ; il y a pour condisciple le jeune Proclus. Il épouse Aidésia, une parente de son maître, réputée pour sa culture et sa piété.&lt;/p&gt; &lt;p&gt;Revenu à Alexandrie, il y enseigne la philosophie, payé par la cité. Son seul ouvrage conservé est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes qu’il avait prises aux cours de Syrianus ; c’est le seul commentaire antique de ce dialogue qui nous soit parvenu. Le &lt;em&gt;Phèdre&lt;/em&gt; traite de l’amour, de la beauté et de l’âme, que Platon compare à un attelage ailé conduit par un cocher. Hermias en donne une lecture à la fois métaphysique et religieuse : les différentes formes de « délire » divin dont parle Socrate, prophétique, mystique, poétique et amoureux, sont autant d’étapes qui permettent à l’âme de remonter vers les dieux et vers l’Un. L’amour de la beauté sensible devient ainsi le point de départ d’une ascension spirituelle. Le philosophe Damascius le décrit comme un homme travailleur et d’une grande droiture, plus fidèle à ses maîtres qu’original.&lt;/p&gt; &lt;p&gt;Hermias meurt assez jeune. Aidésia emmène alors leurs deux fils, Ammonios et Héliodore, étudier à Athènes auprès de Proclus. Ammonios d’Alexandrie deviendra l’un des grands maîtres du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et formera à son tour toute une génération de commentateurs d’Aristote.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Proclus"   title="Proclus par Wikipédia"&gt;PROCLUS&lt;/a&gt; (412-485) est un philosophe &lt;a href="https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D"   title="Le Néoplatonisme par Anne Baudart"&gt;néoplatonicien grec&lt;/a&gt;, l’un des derniers grands penseurs de l’Antiquité. Né à Constantinople, il étudie à Alexandrie, puis à Athènes auprès de Syrianus, auquel il succède à la tête de l’école platonicienne : on l’appelle le « diadoque », le successeur. Il la dirige près de cinquante ans. Végétarien, très pieux, il célèbre les fêtes de tous les peuples, car le philosophe doit être, disait-il, « le prêtre du monde entier ».&lt;/p&gt; &lt;p&gt;Il laisse un grand nombre d’&lt;a href="https://remacle.org/bloodwolf/philosophes/proclus/table.htm"   title="Proclus par Philippe Remacle"&gt;ouvrages&lt;/a&gt;, dont des commentaires de Platon, sur le &lt;em&gt;Timée&lt;/em&gt;, la &lt;em&gt;République&lt;/em&gt;, le &lt;em&gt;Parménide&lt;/em&gt; ou l’&lt;em&gt;Alcibiade&lt;/em&gt;, et un commentaire du premier livre d’Euclide, précieuse source sur l’histoire de la géométrie. Dans les &lt;a href="https://www.youtube.com/watch?v=SJK1kbyXXno"   title="Les éléments de Théologie de Proclus par LabEx HaStec"&gt;&lt;em&gt;Éléments de théologie&lt;/em&gt;&lt;/a&gt;, il expose son système en 211 propositions démontrées à la manière des mathématiciens ; la &lt;em&gt;Théologie platonicienne&lt;/em&gt; le développe. Au sommet se trouve l’Un, principe absolument simple et indicible. De lui procèdent les hénades, qui sont les dieux, puis l’Intellect, l’Âme et enfin la nature et la matière. Tout se déploie selon un même rythme à trois temps : chaque réalité demeure dans sa cause, en procède, puis se retourne vers elle. L’âme humaine peut ainsi remonter vers l’Un par la philosophie, mais aussi par la théurgie, les rites qui unissent aux dieux.&lt;/p&gt; &lt;p&gt;À travers le Pseudo-Denys et le &lt;em&gt;Livre des causes&lt;/em&gt;, adaptation arabe de ses &lt;em&gt;Éléments&lt;/em&gt;, sa pensée marque le Moyen Âge, de Thomas d’Aquin à Maître Eckhart, puis Nicolas de Cues et Hegel.&lt;/p&gt;  &lt;audio controls title=" Proclus, un philosophe étoilé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F89" s="7" t="s">
-        <v>718</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>719</v>
+        <v>710</v>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Une vie, une œuvre" par Rien ne veut rien dire</t>
+        </is>
       </c>
       <c r="H89" s="9" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -7492,96 +7518,103 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="7" t="n">
-        <v>420</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>722</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>723</v>
+    <row r="90" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="7">
+        <v>410</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 410 – avant 470</t>
+        </is>
       </c>
       <c r="D90" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aid%C3%A9sia_(philosophe)" style="color:#6A142A" title="Wikipedia"&gt;AIDÉSIA&lt;/a&gt; (Ve siècle) est une philosophe néoplatonicienne d’Alexandrie, l’une des rares femmes philosophes de l’Antiquité tardive dont le souvenir nous soit parvenu. Parente du philosophe Syrianus, qui dirigeait l’école platonicienne d’Athènes, elle aurait dû épouser Proclus, son disciple, mais celui-ci, averti par un songe, renonça au mariage. Syrianus la donna alors pour épouse à un autre de ses élèves, &lt;a href="https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie" style="color:#6A142A" title="Hermias d'Alexandrie sur Wikipedia"&gt;Hermias d’Alexandrie&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Nous la connaissons par Damascius, le dernier chef de l’école d’Athènes, qui en parle dans sa &lt;em&gt;Vie d’Isidore&lt;/em&gt;. Il la décrit comme la plus belle et la plus vertueuse des femmes de son temps, connue pour sa piété envers les dieux et sa générosité envers les pauvres, au point de distribuer presque tous ses biens. Après la mort prématurée d’Hermias, elle se consacre à l’éducation de leurs deux fils, Ammonios et Héliodore. Elle les accompagne à Athènes pour qu’ils y suivent l’enseignement de Proclus, qui les accueille avec affection en souvenir de son maître. Ammonios deviendra le grand maître de l’école d’Alexandrie, où il formera à son tour de nombreux commentateurs d’Aristote, comme Jean Philopon. Aidésia vit jusqu’à un âge avancé, respectée de tous. À sa mort, le jeune Damascius, alors étudiant à Alexandrie, compose et prononce son éloge funèbre, en vers.&lt;/p&gt; &lt;p&gt;Sa vie témoigne du rôle des femmes dans les familles de philosophes néoplatoniciens, véritables dynasties intellectuelles, à l’image d’&lt;a href="https://fr.wikipedia.org/wiki/Hypatie"   title=" Wikipedia"&gt;HYPATIE d’Alexandrie&lt;/a&gt;, victime des violences religieuses en 415.&lt;/p&gt;</t>
+        <v>716</v>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie" style="color:#6A142A" title="Wikipedia"&gt;HERMIAS d’Alexandrie&lt;/a&gt; est un philosophe néoplatonicien du Ve siècle, maillon important entre les écoles d’Athènes et d’Alexandrie. Né à Alexandrie, il part étudier à Athènes auprès du grand &lt;a href="https://fr.wikipedia.org/wiki/Syrianos" title="Syrianus sur Wikipedia"&gt;Syrianus&lt;/a&gt;, qui dirige alors l’école platonicienne ; il y a pour condisciple le jeune Proclus. Il épouse Aidésia, une parente de son maître, réputée pour sa culture et sa piété.&lt;/p&gt; &lt;p&gt;Revenu à Alexandrie, il y enseigne la philosophie, payé par la cité. Son seul ouvrage conservé est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes qu’il avait prises aux cours de Syrianus ; c’est le seul commentaire antique de ce dialogue qui nous soit parvenu. Le &lt;em&gt;Phèdre&lt;/em&gt; traite de l’amour, de la beauté et de l’âme, que Platon compare à un attelage ailé conduit par un cocher. Hermias en donne une lecture à la fois métaphysique et religieuse : les différentes formes de « délire » divin dont parle Socrate, prophétique, mystique, poétique et amoureux, sont autant d’étapes qui permettent à l’âme de remonter vers les dieux et vers l’Un. L’amour de la beauté sensible devient ainsi le point de départ d’une ascension spirituelle. Le philosophe Damascius le décrit comme un homme travailleur et d’une grande droiture, plus fidèle à ses maîtres qu’original.&lt;/p&gt; &lt;p&gt;Hermias meurt assez jeune. Aidésia emmène alors leurs deux fils, Ammonios et Héliodore, étudier à Athènes auprès de Proclus. Ammonios d’Alexandrie deviendra l’un des grands maîtres du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et formera à son tour toute une génération de commentateurs d’Aristote.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F90" s="7" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
+        <v>721</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="n">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marinos_de_N%C3%A9apolis" style="color:#6A142A" title="Wikipedia"&gt;MARINOS de Néapolis&lt;/a&gt; (Ve siècle) est un philosophe néoplatonicien, disciple et successeur de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" style="color:#6A142A" title="Proclus sur Wikipedia"&gt;Proclus&lt;/a&gt; à la tête de l’école platonicienne d’Athènes. Né à Néapolis, l’actuelle Naplouse, en Palestine, dans une famille samaritaine, il abandonne la religion de ses pères pour les cultes grecs et vient étudier à Athènes. Proclus le choisit pour lui succéder, et il dirige l’école après la mort de son maître, en 485.&lt;/p&gt; &lt;p&gt;Il est surtout connu pour sa &lt;em&gt;Vie de Proclus&lt;/em&gt;, aussi intitulée &lt;em&gt;Sur le bonheur&lt;/em&gt;, écrite un an après la mort de celui-ci. Plus qu’une simple biographie, c’est un éloge construit selon l’échelle des vertus des néoplatoniciens : vertus naturelles, morales, politiques, purificatrices, contemplatives, et enfin théurgiques, qui unissent l’âme aux dieux. Marinos y montre comment Proclus les a toutes possédées, et livre de précieux détails sur la vie de l’école : l’emploi du temps du maître, qui enseignait, écrivait et priait chaque jour, son régime végétarien, ses jeûnes, ses rites et ses prières au soleil. Marinos a aussi écrit un commentaire des &lt;em&gt;Données&lt;/em&gt; d’Euclide, qui témoigne de son goût pour les mathématiques. Dans l’interprétation du &lt;em&gt;Parménide&lt;/em&gt; de Platon, il s’écarte de son maître : il y voit un dialogue sur les Idées plutôt que sur les dieux, ce que Damascius lui reprochera.&lt;/p&gt; &lt;p&gt;De santé fragile, il confie peu à peu l’enseignement à d’autres. Après lui, l’école passe à Isidore de Gaza, puis à Hégias, avant que &lt;a href="https://fr.wikipedia.org/wiki/Damascios" style="color:#6A142A" title="Damascios sur Wikipedia"&gt;Damascios&lt;/a&gt;, qui avait été son élève, n’en prenne la tête jusqu’à sa fermeture par Justinien en 529.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aid%C3%A9sia_(philosophe)" style="color:#6A142A" title="Wikipedia"&gt;AIDÉSIA&lt;/a&gt; (Ve siècle) est une philosophe néoplatonicienne d’Alexandrie, l’une des rares femmes philosophes de l’Antiquité tardive dont le souvenir nous soit parvenu. Parente du philosophe Syrianus, qui dirigeait l’école platonicienne d’Athènes, elle aurait dû épouser Proclus, son disciple, mais celui-ci, averti par un songe, renonça au mariage. Syrianus la donna alors pour épouse à un autre de ses élèves, &lt;a href="https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie" style="color:#6A142A" title="Hermias d'Alexandrie sur Wikipedia"&gt;Hermias d’Alexandrie&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Nous la connaissons par Damascius, le dernier chef de l’école d’Athènes, qui en parle dans sa &lt;em&gt;Vie d’Isidore&lt;/em&gt;. Il la décrit comme la plus belle et la plus vertueuse des femmes de son temps, connue pour sa piété envers les dieux et sa générosité envers les pauvres, au point de distribuer presque tous ses biens. Après la mort prématurée d’Hermias, elle se consacre à l’éducation de leurs deux fils, Ammonios et Héliodore. Elle les accompagne à Athènes pour qu’ils y suivent l’enseignement de Proclus, qui les accueille avec affection en souvenir de son maître. Ammonios deviendra le grand maître de l’école d’Alexandrie, où il formera à son tour de nombreux commentateurs d’Aristote, comme Jean Philopon. Aidésia vit jusqu’à un âge avancé, respectée de tous. À sa mort, le jeune Damascius, alors étudiant à Alexandrie, compose et prononce son éloge funèbre, en vers.&lt;/p&gt; &lt;p&gt;Sa vie témoigne du rôle des femmes dans les familles de philosophes néoplatoniciens, véritables dynasties intellectuelles, à l’image d’&lt;a href="https://fr.wikipedia.org/wiki/Hypatie"   title=" Wikipedia"&gt;HYPATIE d’Alexandrie&lt;/a&gt;, victime des violences religieuses en 415.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F91" s="7" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="H91" s="12" t="s">
-        <v>736</v>
+        <v>727</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>728</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>737</v>
+        <v>729</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -7589,45 +7622,45 @@
         </is>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="119.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="E92" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)"  style="color:#6A142A"  title=" Wikipedia"&gt;AMMONIOS d’Alexandrie&lt;/a&gt; (vers 440-vers 520) est un philosophe néoplatonicien, le grand maître de l’école d’Alexandrie à la fin de l’Antiquité. Fils des philosophes Hermias et Aidésia, il est emmené jeune à Athènes par sa mère pour y suivre l’enseignement de Proclus, qui dirige l’école platonicienne. Revenu dans sa ville natale, il y enseigne pendant plusieurs décennies, à la tête de l’école d’Alexandrie, tandis que celle d’Athènes est dirigée par les successeurs de Proclus.&lt;/p&gt; &lt;p&gt;Ammonios est avant tout un commentateur d’Aristote. Il considère que la philosophie d’Aristote et celle de Platon s’accordent sur l’essentiel : l’étude d’Aristote, à commencer par sa logique, prépare à celle de Platon, qui conduit jusqu’à la connaissance du divin. Son commentaire du traité &lt;em&gt;De l’interprétation&lt;/em&gt;, qui examine les propositions, la vérité et le temps, nous est parvenu en entier ; on y trouve une discussion célèbre sur les futurs contingents : peut-on dire dès aujourd’hui qu’une bataille navale aura lieu demain, sans supprimer la liberté ? Ses autres leçons nous sont connues par les notes de ses élèves. Il forme en effet toute une génération de commentateurs : Jean Philopon, chrétien, Simplicius, Asclépius et Olympiodore. Dans une ville où les chrétiens sont désormais majoritaires et où les païens sont parfois persécutés, il aurait conclu un accord avec les autorités chrétiennes pour pouvoir continuer à enseigner, ce que lui reprocha Damascius.&lt;/p&gt; &lt;p&gt;L’école d’Alexandrie, en partie chrétienne après lui, a transmis le corpus d’Aristote et ses commentaires aux savants syriaques et arabes, puis à l’Occident médiéval.&lt;/p&gt;</t>
+        <v>732</v>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marinos_de_N%C3%A9apolis" style="color:#6A142A" title="Wikipedia"&gt;MARINOS de Néapolis&lt;/a&gt; (Ve siècle) est un philosophe néoplatonicien, disciple et successeur de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" style="color:#6A142A" title="Proclus sur Wikipedia"&gt;Proclus&lt;/a&gt; à la tête de l’école platonicienne d’Athènes. Né à Néapolis, l’actuelle Naplouse, en Palestine, dans une famille samaritaine, il abandonne la religion de ses pères pour les cultes grecs et vient étudier à Athènes. Proclus le choisit pour lui succéder, et il dirige l’école après la mort de son maître, en 485.&lt;/p&gt; &lt;p&gt;Il est surtout connu pour sa &lt;em&gt;Vie de Proclus&lt;/em&gt;, aussi intitulée &lt;em&gt;Sur le bonheur&lt;/em&gt;, écrite un an après la mort de celui-ci. Plus qu’une simple biographie, c’est un éloge construit selon l’échelle des vertus des néoplatoniciens : vertus naturelles, morales, politiques, purificatrices, contemplatives, et enfin théurgiques, qui unissent l’âme aux dieux. Marinos y montre comment Proclus les a toutes possédées, et livre de précieux détails sur la vie de l’école : l’emploi du temps du maître, qui enseignait, écrivait et priait chaque jour, son régime végétarien, ses jeûnes, ses rites et ses prières au soleil. Marinos a aussi écrit un commentaire des &lt;em&gt;Données&lt;/em&gt; d’Euclide, qui témoigne de son goût pour les mathématiques. Dans l’interprétation du &lt;em&gt;Parménide&lt;/em&gt; de Platon, il s’écarte de son maître : il y voit un dialogue sur les Idées plutôt que sur les dieux, ce que Damascius lui reprochera.&lt;/p&gt; &lt;p&gt;De santé fragile, il confie peu à peu l’enseignement à d’autres. Après lui, l’école passe à Isidore de Gaza, puis à Hégias, avant que &lt;a href="https://fr.wikipedia.org/wiki/Damascios" style="color:#6A142A" title="Damascios sur Wikipedia"&gt;Damascios&lt;/a&gt;, qui avait été son élève, n’en prenne la tête jusqu’à sa fermeture par Justinien en 529.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F92" s="7" t="s">
-        <v>742</v>
-      </c>
-      <c r="G92" s="15" t="s">
-        <v>743</v>
-      </c>
-      <c r="H92" s="9" t="s">
-        <v>744</v>
+        <v>734</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="H92" s="12" t="s">
+        <v>736</v>
       </c>
       <c r="I92" s="9"/>
       <c r="J92" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -7635,49 +7668,45 @@
         </is>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="119.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
-        <v>453</v>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">520</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">453 – 520</t>
-        </is>
+        <v>440</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>739</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="E93" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isidore_de_Gaza" title="Wikipedia"&gt;ISIDORE de Gaza&lt;/a&gt; (Ve-VIe siècle) est un philosophe néoplatonicien, l’un des derniers représentants du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme"  title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; païen. Né à Gaza, il étudie à Alexandrie, puis à Athènes auprès de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" title="Proclus sur Wikipedia"&gt;Proclus&lt;/a&gt;, qui dirige l’école platonicienne. Il est le maître et l’ami de &lt;a href="https://fr.wikipedia.org/wiki/Damascios" title="Damascios sur Wikipedia"&gt;Damascius&lt;/a&gt;, le dernier chef de cette école.&lt;/p&gt; &lt;p&gt;Nous le connaissons surtout par la biographie que Damascius lui a consacrée, la &lt;em&gt;Vie d’Isidore&lt;/em&gt;, dont il reste d’importants fragments. Il y apparaît comme un homme profondément religieux, attaché aux cultes et aux traditions des Grecs à une époque où le christianisme est devenu la religion de l’Empire et où les païens sont de plus en plus surveillés. Isidore se méfie des longs commentaires savants et des raisonnements trop subtils : pour lui, la philosophie est avant tout une manière de vivre, une purification de l’âme qui la conduit vers le divin. Il préfère l’inspiration et l’expérience intérieure à l’érudition, et Damascius admire en lui moins le savant que le sage. Après la mort de Proclus, il voyage beaucoup, en Syrie et en Égypte, en compagnie de Damascius. Il accepte un temps de diriger l’école d’Athènes, à la suite de Marinus, mais y renonce bientôt, jugeant le climat défavorable à la philosophie. La &lt;em&gt;Vie d’Isidore&lt;/em&gt; est aussi une précieuse galerie de portraits des philosophes de son temps, comme Hypatie, Aidésia ou Hermias.&lt;/p&gt; &lt;p&gt;Peu après, en 529, l’empereur Justinien interdit aux païens d’enseigner : l’école d’Athènes ferme, et Damascius part avec quelques compagnons en Perse.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F93" s="18" t="s">
-        <v>750</v>
+        <v>740</v>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)"  style="color:#6A142A"  title=" Wikipedia"&gt;AMMONIOS d’Alexandrie&lt;/a&gt; (vers 440-vers 520) est un philosophe néoplatonicien, le grand maître de l’école d’Alexandrie à la fin de l’Antiquité. Fils des philosophes Hermias et Aidésia, il est emmené jeune à Athènes par sa mère pour y suivre l’enseignement de Proclus, qui dirige l’école platonicienne. Revenu dans sa ville natale, il y enseigne pendant plusieurs décennies, à la tête de l’école d’Alexandrie, tandis que celle d’Athènes est dirigée par les successeurs de Proclus.&lt;/p&gt; &lt;p&gt;Ammonios est avant tout un commentateur d’Aristote. Il considère que la philosophie d’Aristote et celle de Platon s’accordent sur l’essentiel : l’étude d’Aristote, à commencer par sa logique, prépare à celle de Platon, qui conduit jusqu’à la connaissance du divin. Son commentaire du traité &lt;em&gt;De l’interprétation&lt;/em&gt;, qui examine les propositions, la vérité et le temps, nous est parvenu en entier ; on y trouve une discussion célèbre sur les futurs contingents : peut-on dire dès aujourd’hui qu’une bataille navale aura lieu demain, sans supprimer la liberté ? Ses autres leçons nous sont connues par les notes de ses élèves. Il forme en effet toute une génération de commentateurs : Jean Philopon, chrétien, Simplicius, Asclépius et Olympiodore. Dans une ville où les chrétiens sont désormais majoritaires et où les païens sont parfois persécutés, il aurait conclu un accord avec les autorités chrétiennes pour pouvoir continuer à enseigner, ce que lui reprocha Damascius.&lt;/p&gt; &lt;p&gt;L’école d’Alexandrie, en partie chrétienne après lui, a transmis le corpus d’Aristote et ses commentaires aux savants syriaques et arabes, puis à l’Occident médiéval.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>742</v>
       </c>
       <c r="G93" s="15" t="s">
-        <v>751</v>
-      </c>
-      <c r="H93" s="12" t="s">
-        <v>697</v>
+        <v>743</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>744</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -7685,235 +7714,239 @@
         </is>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
-        <v>458</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>753</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>754</v>
+        <v>453</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">453 – 520</t>
+        </is>
       </c>
       <c r="D94" s="8" t="s">
-        <v>755</v>
-      </c>
-      <c r="E94" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Damascios" style="color:#6A142A" title="Wikipedia"&gt;DAMASCIOS   le Diadoque&lt;/a&gt;, né à Damas fut le dernier scholarque de l'Académie platonicienne d'Athènes,   Élève de Marinos de Néapolis et d'Isidore d'Alexandrie, il succéda à ce dernier comme scholarchos vers 515, jusqu'à la fermeture de l'école par l'empereur Justinien en 529. Philosophe néoplatonicien d'une érudition exceptionnelle, il incarne la résistance de la pensée grecque face au triomphe du christianisme.&lt;/p&gt; &lt;p&gt;Disciple d'Isidore de Gaza et d'autres maîtres alexandrins, il dirigea l'École d'Athènes et rédigea des œuvres d'une grande complexité spéculative, notamment les &lt;em&gt;Problèmes et Solutions concernant les Premiers Principes&lt;/em&gt; et un commentaire sur le &lt;em&gt;Parménide&lt;/em&gt; de Platon.   Auteur de la Vie d'Isidore (biographie philosophique et critique du christianisme), du Traité des premiers principes (sur l'ontologie), de commentaires sur le Parménide de Platon et les Chaldaica, ses écrits préservent la tradition néoplatonicienne tardive. &lt;/p&gt; &lt;p&gt;   Il poussa la dialectique néoplatonicienne jusqu'à ses limites, affirmant que le Premier Principe — l'Un — est absolument ineffable, au-delà de toute pensée et de tout être.&lt;/p&gt; &lt;p&gt;Après la fermeture de l'Académie, Damascios s'exila en Perse avec Simplicius et d'autres philosophes, à la cour du roi sassanide Khosrô Ier. Il représente la fin d'une époque : la clôture du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; antique, dont il fut l'un des penseurs les plus profonds et les plus radicaux.&lt;/p&gt; Critiquant Proclus, Damascios dépassa l'Un-Bien pour poser un principe ineffable (to aprorrhēton), absolu et sans relation, au-delà de toute connaissance. Son ontologie distingue l'Ineffable, l'Un, l'Intellect et l'Âme, influençant les théologies apophatiques ultérieures. &lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>736</v>
+        <v>748</v>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isidore_de_Gaza" title="Wikipedia"&gt;ISIDORE de Gaza&lt;/a&gt; (Ve-VIe siècle) est un philosophe néoplatonicien, l’un des derniers représentants du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme"  title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; païen. Né à Gaza, il étudie à Alexandrie, puis à Athènes auprès de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" title="Proclus sur Wikipedia"&gt;Proclus&lt;/a&gt;, qui dirige l’école platonicienne. Il est le maître et l’ami de &lt;a href="https://fr.wikipedia.org/wiki/Damascios" title="Damascios sur Wikipedia"&gt;Damascius&lt;/a&gt;, le dernier chef de cette école.&lt;/p&gt; &lt;p&gt;Nous le connaissons surtout par la biographie que Damascius lui a consacrée, la &lt;em&gt;Vie d’Isidore&lt;/em&gt;, dont il reste d’importants fragments. Il y apparaît comme un homme profondément religieux, attaché aux cultes et aux traditions des Grecs à une époque où le christianisme est devenu la religion de l’Empire et où les païens sont de plus en plus surveillés. Isidore se méfie des longs commentaires savants et des raisonnements trop subtils : pour lui, la philosophie est avant tout une manière de vivre, une purification de l’âme qui la conduit vers le divin. Il préfère l’inspiration et l’expérience intérieure à l’érudition, et Damascius admire en lui moins le savant que le sage. Après la mort de Proclus, il voyage beaucoup, en Syrie et en Égypte, en compagnie de Damascius. Il accepte un temps de diriger l’école d’Athènes, à la suite de Marinus, mais y renonce bientôt, jugeant le climat défavorable à la philosophie. La &lt;em&gt;Vie d’Isidore&lt;/em&gt; est aussi une précieuse galerie de portraits des philosophes de son temps, comme Hypatie, Aidésia ou Hermias.&lt;/p&gt; &lt;p&gt;Peu après, en 529, l’empereur Justinien interdit aux païens d’enseigner : l’école d’Athènes ferme, et Damascius part avec quelques compagnons en Perse.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="s">
+        <v>750</v>
+      </c>
+      <c r="G94" s="15" t="s">
+        <v>751</v>
+      </c>
+      <c r="H94" s="12" t="s">
+        <v>697</v>
       </c>
       <c r="I94" s="9"/>
       <c r="J94" s="2" t="s">
-        <v>636</v>
+        <v>23</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="95" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bo%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;Anicius Manlius BOÈCE&lt;/a&gt; (vers 480-524) est un philosophe, théologien et homme d’État romain, souvent appelé « le dernier des Romains et le premier des scolastiques ». Issu de l’une des plus grandes familles de Rome, il vit sous le règne de Théodoric, roi des Ostrogoths, qui gouverne l’Italie : il devient consul en 510, puis maître des offices, la plus haute charge de la cour.&lt;/p&gt; &lt;p&gt;Chrétien et passionné de philosophie grecque, il conçoit un projet immense : traduire en latin toutes les œuvres de Platon et d’Aristote, pour montrer qu’ils s’accordent sur l’essentiel. Il n’a pu en réaliser qu’une partie : la logique d’Aristote et l’&lt;em&gt;Introduction&lt;/em&gt; de Porphyre. Ces traductions seront, pendant six siècles, presque la seule philosophie grecque connue en Occident, et l’une de ses questions, celle de la nature des universaux, lancera la grande querelle médiévale. Il écrit aussi des manuels d’arithmétique et de musique, et de courts traités de théologie, où il définit la personne comme « une substance individuelle de nature raisonnable ». Accusé de trahison pour avoir défendu un sénateur, il est emprisonné à Pavie, puis exécuté en 524. En prison, il écrit &lt;a  href="https://remacle.org/bloodwolf/philosophes/boece/livre3.htm#:~:text=J'entends%20par%20l%C3%A0%20ce,aurait%20encore%20mati%C3%A8re%20%C3%A0%20d%C3%A9sir." style="color:#88A1E9"  title="La consolation philosophique par Remacle"&gt;&lt;em&gt;La Consolation de Philosophie&lt;/em&gt;&lt;/a&gt;. La Philosophie lui apparaît sous les traits d’une femme majestueuse et lui montre que la Fortune, avec sa roue, donne et reprend tout : le vrai bonheur n’est pas dans les richesses ou le pouvoir, mais dans &lt;a  href="https://www.youtube.com/watch?v=Bx-_WsSfylw&amp;t=1619s&amp;ab_channel=%C3%89CLAIRBRUT" style="color:#88A1E9"  title="Une âme dénuée du monde par Eclair Brut"&gt;la sagesse&lt;/a&gt; et en Dieu, le bien suprême. Dieu, éternel, voit tout l’avenir comme un présent, sans supprimer notre liberté.&lt;/p&gt; &lt;p&gt;La &lt;em&gt;Consolation&lt;/em&gt; fut l’un des livres les plus influents de la culture européenne.&lt;/p&gt;</t>
+        <v>755</v>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Damascios" style="color:#6A142A" title="Wikipedia"&gt;DAMASCIOS   le Diadoque&lt;/a&gt;, né à Damas fut le dernier scholarque de l'Académie platonicienne d'Athènes,   Élève de Marinos de Néapolis et d'Isidore d'Alexandrie, il succéda à ce dernier comme scholarchos vers 515, jusqu'à la fermeture de l'école par l'empereur Justinien en 529. Philosophe néoplatonicien d'une érudition exceptionnelle, il incarne la résistance de la pensée grecque face au triomphe du christianisme.&lt;/p&gt; &lt;p&gt;Disciple d'Isidore de Gaza et d'autres maîtres alexandrins, il dirigea l'École d'Athènes et rédigea des œuvres d'une grande complexité spéculative, notamment les &lt;em&gt;Problèmes et Solutions concernant les Premiers Principes&lt;/em&gt; et un commentaire sur le &lt;em&gt;Parménide&lt;/em&gt; de Platon.   Auteur de la Vie d'Isidore (biographie philosophique et critique du christianisme), du Traité des premiers principes (sur l'ontologie), de commentaires sur le Parménide de Platon et les Chaldaica, ses écrits préservent la tradition néoplatonicienne tardive. &lt;/p&gt; &lt;p&gt;   Il poussa la dialectique néoplatonicienne jusqu'à ses limites, affirmant que le Premier Principe — l'Un — est absolument ineffable, au-delà de toute pensée et de tout être.&lt;/p&gt; &lt;p&gt;Après la fermeture de l'Académie, Damascios s'exila en Perse avec Simplicius et d'autres philosophes, à la cour du roi sassanide Khosrô Ier. Il représente la fin d'une époque : la clôture du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; antique, dont il fut l'un des penseurs les plus profonds et les plus radicaux.&lt;/p&gt; Critiquant Proclus, Damascios dépassa l'Un-Bien pour poser un principe ineffable (to aprorrhēton), absolu et sans relation, au-delà de toute connaissance. Son ontologie distingue l'Ineffable, l'Un, l'Intellect et l'Âme, influençant les théologies apophatiques ultérieures. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F95" s="7" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>766</v>
+        <v>736</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="2" t="s">
-        <v>512</v>
+        <v>636</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>767</v>
+        <v>538</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="96" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="E96" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hermias_de_Ph%C3%A9nicie" style="color:#6A142A" title="Wikipedia"&gt;HERMIAS de Phénicie&lt;/a&gt; est un philosophe néoplatonicien du VIe siècle, membre de l’école d’Athènes à l’époque où elle est dirigée par Damascius. Nous ne savons presque rien de lui, sinon sa participation à l’un des épisodes les plus célèbres de la fin de la philosophie antique : l’exil des derniers philosophes païens en Perse.&lt;/p&gt; &lt;p&gt;En 529, l’empereur chrétien Justinien interdit aux païens d’enseigner et d’occuper des fonctions publiques. L’école platonicienne d’Athènes, héritière de l’Académie de Platon, ne peut plus fonctionner, et ses biens sont menacés. Vers 531, sept philosophes décident de quitter l’Empire : Damascius, Simplicius de Cilicie, Priscien de Lydie, Eulamios de Phrygie, Isidore de Gaza, Diogène de Phénicie et Hermias, son compatriote. Ils se rendent à la cour du roi sassanide &lt;a href="https://fr.wikipedia.org/wiki/Khosro_Ier" title=" Wikipedia"&gt;Khosro Ier&lt;/a&gt;, réputé ami de la philosophie, qui faisait traduire Platon et Aristote. L’historien byzantin Agathias, qui raconte leur voyage, les appelle « la fleur la plus noble des philosophes de notre temps ». Mais la Perse les déçoit : ils y trouvent l’injustice et des mœurs qui les choquent, et le roi lui-même leur paraît moins philosophe qu’on ne le disait. En 532, le traité de paix entre Khosro et Justinien prévoit qu’ils pourront rentrer dans l’Empire sans être forcés de renoncer à leurs croyances.&lt;/p&gt; &lt;p&gt;Aucune œuvre d’Hermias ne nous est parvenue. On ignore où les exilés finirent leur vie ; certains historiens pensent qu’une partie d’entre eux s’installa à Harran, aux confins de l’Empire, où la tradition platonicienne se serait maintenue jusqu’à l’époque islamique.&lt;/p&gt;</t>
+        <v>762</v>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bo%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;Anicius Manlius BOÈCE&lt;/a&gt; (vers 480-524) est un philosophe, théologien et homme d’État romain, souvent appelé « le dernier des Romains et le premier des scolastiques ». Issu de l’une des plus grandes familles de Rome, il vit sous le règne de Théodoric, roi des Ostrogoths, qui gouverne l’Italie : il devient consul en 510, puis maître des offices, la plus haute charge de la cour.&lt;/p&gt; &lt;p&gt;Chrétien et passionné de philosophie grecque, il conçoit un projet immense : traduire en latin toutes les œuvres de Platon et d’Aristote, pour montrer qu’ils s’accordent sur l’essentiel. Il n’a pu en réaliser qu’une partie : la logique d’Aristote et l’&lt;em&gt;Introduction&lt;/em&gt; de Porphyre. Ces traductions seront, pendant six siècles, presque la seule philosophie grecque connue en Occident, et l’une de ses questions, celle de la nature des universaux, lancera la grande querelle médiévale. Il écrit aussi des manuels d’arithmétique et de musique, et de courts traités de théologie, où il définit la personne comme « une substance individuelle de nature raisonnable ». Accusé de trahison pour avoir défendu un sénateur, il est emprisonné à Pavie, puis exécuté en 524. En prison, il écrit &lt;a  href="https://remacle.org/bloodwolf/philosophes/boece/livre3.htm#:~:text=J'entends%20par%20l%C3%A0%20ce,aurait%20encore%20mati%C3%A8re%20%C3%A0%20d%C3%A9sir." style="color:#88A1E9"  title="La consolation philosophique par Remacle"&gt;&lt;em&gt;La Consolation de Philosophie&lt;/em&gt;&lt;/a&gt;. La Philosophie lui apparaît sous les traits d’une femme majestueuse et lui montre que la Fortune, avec sa roue, donne et reprend tout : le vrai bonheur n’est pas dans les richesses ou le pouvoir, mais dans &lt;a  href="https://www.youtube.com/watch?v=Bx-_WsSfylw&amp;t=1619s&amp;ab_channel=%C3%89CLAIRBRUT" style="color:#88A1E9"  title="Une âme dénuée du monde par Eclair Brut"&gt;la sagesse&lt;/a&gt; et en Dieu, le bien suprême. Dieu, éternel, voit tout l’avenir comme un présent, sans supprimer notre liberté.&lt;/p&gt; &lt;p&gt;La &lt;em&gt;Consolation&lt;/em&gt; fut l’un des livres les plus influents de la culture européenne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F96" s="7" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>774</v>
-      </c>
-      <c r="H96" s="12" t="s">
-        <v>697</v>
+        <v>765</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>766</v>
       </c>
       <c r="I96" s="9"/>
       <c r="J96" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>538</v>
+        <v>767</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P96">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="97" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>778</v>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Simplicius_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698" style="color:#88A1E9" title="A propos de la biographie de Simplicius par Persée"&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le "Manuel d’Épictète" et, selon la tradition, sur "De l’âme". Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href="https://www.youtube.com/watch?v=C17VYcyLkiY" style="color:#88A1E9" title="SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions"&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.   Transmis et traduits dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; </t>
+        <v>771</v>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hermias_de_Ph%C3%A9nicie" style="color:#6A142A" title="Wikipedia"&gt;HERMIAS de Phénicie&lt;/a&gt; est un philosophe néoplatonicien du VIe siècle, membre de l’école d’Athènes à l’époque où elle est dirigée par Damascius. Nous ne savons presque rien de lui, sinon sa participation à l’un des épisodes les plus célèbres de la fin de la philosophie antique : l’exil des derniers philosophes païens en Perse.&lt;/p&gt; &lt;p&gt;En 529, l’empereur chrétien Justinien interdit aux païens d’enseigner et d’occuper des fonctions publiques. L’école platonicienne d’Athènes, héritière de l’Académie de Platon, ne peut plus fonctionner, et ses biens sont menacés. Vers 531, sept philosophes décident de quitter l’Empire : Damascius, Simplicius de Cilicie, Priscien de Lydie, Eulamios de Phrygie, Isidore de Gaza, Diogène de Phénicie et Hermias, son compatriote. Ils se rendent à la cour du roi sassanide &lt;a href="https://fr.wikipedia.org/wiki/Khosro_Ier" title=" Wikipedia"&gt;Khosro Ier&lt;/a&gt;, réputé ami de la philosophie, qui faisait traduire Platon et Aristote. L’historien byzantin Agathias, qui raconte leur voyage, les appelle « la fleur la plus noble des philosophes de notre temps ». Mais la Perse les déçoit : ils y trouvent l’injustice et des mœurs qui les choquent, et le roi lui-même leur paraît moins philosophe qu’on ne le disait. En 532, le traité de paix entre Khosro et Justinien prévoit qu’ils pourront rentrer dans l’Empire sans être forcés de renoncer à leurs croyances.&lt;/p&gt; &lt;p&gt;Aucune œuvre d’Hermias ne nous est parvenue. On ignore où les exilés finirent leur vie ; certains historiens pensent qu’une partie d’entre eux s’installa à Harran, aux confins de l’Empire, où la tradition platonicienne se serait maintenue jusqu’à l’époque islamique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F97" s="7" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>781</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>782</v>
+        <v>774</v>
+      </c>
+      <c r="H97" s="12" t="s">
+        <v>697</v>
       </c>
       <c r="I97" s="9"/>
       <c r="J97" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>786</v>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cassiodore"  style="color:#6A142A"  title=" Wikipedia"&gt;CASSIODORE&lt;/a&gt; (vers 485-580) est un homme d’État, écrivain et savant romain, l’un des grands passeurs de la culture antique au Moyen Âge. Issu d’une famille de hauts fonctionnaires du sud de l’Italie, il fait carrière au service des rois ostrogoths qui gouvernent alors l’Italie, en particulier Théodoric le Grand : il devient consul, puis préfet du prétoire. Ses lettres officielles, réunies dans les &lt;em&gt;Variae&lt;/em&gt; en douze livres, sont une source précieuse sur l’époque.&lt;/p&gt; &lt;p&gt;Il veut concilier les Romains et les Goths, et écrit à cette fin une &lt;em&gt;Histoire des Goths&lt;/em&gt;, aujourd’hui perdue. Après la reconquête de l’Italie par l’empereur Justinien et la ruine de son projet politique, il se retire vers 554 sur ses terres de Calabre, où il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Monast%C3%A8re_de_Vivarium"  style="color:#88A1E9"  title="le monastère de Vivarium par Wikipédia"&gt;monastère de Vivarium&lt;/a&gt;, ainsi nommé à cause de ses viviers à poissons. Il y rassemble une riche bibliothèque et demande aux moines de copier avec soin les manuscrits, chrétiens mais aussi païens, en les corrigeant et en les reliant : le travail du copiste devient une œuvre spirituelle. Pour les guider, il écrit les &lt;a href="https://www.persee.fr/doc/rht_0373-6075_1991_num_21_1991_1362"  style="color:#88A1E9"  title="les Institutions par Persée.fr"&gt;&lt;em&gt;Institutions&lt;/em&gt;&lt;/a&gt;, en deux livres : le premier présente l’étude de la Bible et des Pères de l’Église ; le second résume les sept arts libéraux, la grammaire, la rhétorique, la dialectique, l’arithmétique, la musique, la géométrie et l’astronomie, nécessaires pour bien lire l’Écriture. Il compose aussi un traité &lt;em&gt;De l’âme&lt;/em&gt; et un grand commentaire des Psaumes.&lt;/p&gt; &lt;p&gt;Grâce à lui, le modèle du monastère gardien des livres s’impose en Occident. Les &lt;em&gt;Institutions&lt;/em&gt; serviront de programme d’études pendant tout le Moyen Âge.&lt;/p&gt;</t>
+        <v>778</v>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Simplicius_(philosophe)"  style="color:#6A142A"  title=" Wikipedia"&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698" style="color:#88A1E9" title="A propos de la biographie de Simplicius par Persée"&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le "Manuel d’Épictète" et, selon la tradition, sur "De l’âme". Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href="https://www.youtube.com/watch?v=C17VYcyLkiY" style="color:#88A1E9" title="SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions"&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.   Transmis et traduits dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F98" s="7" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="I98" s="9"/>
       <c r="J98" s="2" t="s">
-        <v>512</v>
+        <v>23</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>252</v>
+        <v>34</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>662</v>
+        <v>538</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -7921,45 +7954,45 @@
         </is>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
         <v>490</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>794</v>
-      </c>
-      <c r="E99" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Philopon" style="color:#6A142A" title="Wikipedia"&gt;Jean PHILOPON&lt;/a&gt; fut l'un des penseurs les plus novateurs de l'Antiquité tardive. Philosophe et théologien chrétien monophysite d'Alexandrie, disciple d'Ammonios fils d'Hermias, il est célèbre pour ses vastes commentaires des œuvres d'&lt;a href="https://fr.wikipedia.org/wiki/Aristote" style="color:#6A142A" title="Aristote sur Wikipedia"&gt;Aristote&lt;/a&gt;, qu'il soumit à une critique audacieuse au nom de la physique et de la foi chrétienne.&lt;/p&gt; &lt;p&gt;  Il est un des premiers grands commentateurs d’Aristote en grec, mais il s’en distingue nettement sur des questions comme l’éternité du monde. Dans ses traités Contre Proclus (529) et De la création du monde, il défend l’idée que le monde a été créé ex nihilo dans le temps, ce qui l’oppose à la conception aristotélicienne d’un univers éternel, affirmant que le cosmos fut créé à partir du néant — en accord avec le dogme chrétien. Il développa également la théorie de l'&lt;em&gt;impetus&lt;/em&gt;, ancêtre du concept d'inertie : un projectile lancé reçoit une force interne qui le maintient en mouvement, préfigurant ainsi la physique galiléenne six siècles avant Galilée.&lt;/p&gt; &lt;p&gt;       Sur le plan théologique, il soutient une lecture allégorique de la Bible et cherche à harmoniser Platon, Aristote et Ptolémée avec la cosmologie chrétienne, en s’opposant notamment à la vision « étagée » du monde de Cosmas Indicopleustès. Il se rapproche d’abord du monophysisme, puis adhère au courant dit « trithéite » (tendance au sein du christianisme oriental qui insiste sur la distinction des trois personnes divines), ce qui lui vaudra une condamnation par certains milieux orthodoxes et monophysites.   &lt;/p&gt; &lt;p&gt; Il est une figure de carrefour entre philosophie grecque et théologie chrétienne. Sa lecture critique d'Aristote, qu'il commentait tout en le contestant, influença profondément les penseurs arabes médiévaux et, via eux, la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_scientifique" style="color:#6A142A" title="Révolution scientifique sur Wikipedia"&gt;révolution scientifique&lt;/a&gt; de la Renaissance. Il fut condamné pour hérésie (trithéisme) mais son héritage philosophique demeure immense.&lt;/p&gt;</t>
+        <v>786</v>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cassiodore"  style="color:#6A142A"  title=" Wikipedia"&gt;CASSIODORE&lt;/a&gt; (vers 485-580) est un homme d’État, écrivain et savant romain, l’un des grands passeurs de la culture antique au Moyen Âge. Issu d’une famille de hauts fonctionnaires du sud de l’Italie, il fait carrière au service des rois ostrogoths qui gouvernent alors l’Italie, en particulier Théodoric le Grand : il devient consul, puis préfet du prétoire. Ses lettres officielles, réunies dans les &lt;em&gt;Variae&lt;/em&gt; en douze livres, sont une source précieuse sur l’époque.&lt;/p&gt; &lt;p&gt;Il veut concilier les Romains et les Goths, et écrit à cette fin une &lt;em&gt;Histoire des Goths&lt;/em&gt;, aujourd’hui perdue. Après la reconquête de l’Italie par l’empereur Justinien et la ruine de son projet politique, il se retire vers 554 sur ses terres de Calabre, où il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Monast%C3%A8re_de_Vivarium"  style="color:#88A1E9"  title="le monastère de Vivarium par Wikipédia"&gt;monastère de Vivarium&lt;/a&gt;, ainsi nommé à cause de ses viviers à poissons. Il y rassemble une riche bibliothèque et demande aux moines de copier avec soin les manuscrits, chrétiens mais aussi païens, en les corrigeant et en les reliant : le travail du copiste devient une œuvre spirituelle. Pour les guider, il écrit les &lt;a href="https://www.persee.fr/doc/rht_0373-6075_1991_num_21_1991_1362"  style="color:#88A1E9"  title="les Institutions par Persée.fr"&gt;&lt;em&gt;Institutions&lt;/em&gt;&lt;/a&gt;, en deux livres : le premier présente l’étude de la Bible et des Pères de l’Église ; le second résume les sept arts libéraux, la grammaire, la rhétorique, la dialectique, l’arithmétique, la musique, la géométrie et l’astronomie, nécessaires pour bien lire l’Écriture. Il compose aussi un traité &lt;em&gt;De l’âme&lt;/em&gt; et un grand commentaire des Psaumes.&lt;/p&gt; &lt;p&gt;Grâce à lui, le modèle du monastère gardien des livres s’impose en Occident. Les &lt;em&gt;Institutions&lt;/em&gt; serviront de programme d’études pendant tout le Moyen Âge.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F99" s="7" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="2" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>538</v>
+        <v>662</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -7967,45 +8000,45 @@
         </is>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>802</v>
-      </c>
-      <c r="E100" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Priscien_de_Lydie" style="color:#6A142A" title="Wikipedia"&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href="https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316" title="la géographie et les originesnéoplatonisme sur Persee"&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité : « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;</t>
+        <v>794</v>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Philopon" style="color:#6A142A" title="Wikipedia"&gt;Jean PHILOPON&lt;/a&gt; fut l'un des penseurs les plus novateurs de l'Antiquité tardive. Philosophe et théologien chrétien monophysite d'Alexandrie, disciple d'Ammonios fils d'Hermias, il est célèbre pour ses vastes commentaires des œuvres d'&lt;a href="https://fr.wikipedia.org/wiki/Aristote" style="color:#6A142A" title="Aristote sur Wikipedia"&gt;Aristote&lt;/a&gt;, qu'il soumit à une critique audacieuse au nom de la physique et de la foi chrétienne.&lt;/p&gt; &lt;p&gt;  Il est un des premiers grands commentateurs d’Aristote en grec, mais il s’en distingue nettement sur des questions comme l’éternité du monde. Dans ses traités Contre Proclus (529) et De la création du monde, il défend l’idée que le monde a été créé ex nihilo dans le temps, ce qui l’oppose à la conception aristotélicienne d’un univers éternel, affirmant que le cosmos fut créé à partir du néant — en accord avec le dogme chrétien. Il développa également la théorie de l'&lt;em&gt;impetus&lt;/em&gt;, ancêtre du concept d'inertie : un projectile lancé reçoit une force interne qui le maintient en mouvement, préfigurant ainsi la physique galiléenne six siècles avant Galilée.&lt;/p&gt; &lt;p&gt;       Sur le plan théologique, il soutient une lecture allégorique de la Bible et cherche à harmoniser Platon, Aristote et Ptolémée avec la cosmologie chrétienne, en s’opposant notamment à la vision « étagée » du monde de Cosmas Indicopleustès. Il se rapproche d’abord du monophysisme, puis adhère au courant dit « trithéite » (tendance au sein du christianisme oriental qui insiste sur la distinction des trois personnes divines), ce qui lui vaudra une condamnation par certains milieux orthodoxes et monophysites.   &lt;/p&gt; &lt;p&gt; Il est une figure de carrefour entre philosophie grecque et théologie chrétienne. Sa lecture critique d'Aristote, qu'il commentait tout en le contestant, influença profondément les penseurs arabes médiévaux et, via eux, la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_scientifique" style="color:#6A142A" title="Révolution scientifique sur Wikipedia"&gt;révolution scientifique&lt;/a&gt; de la Renaissance. Il fut condamné pour hérésie (trithéisme) mais son héritage philosophique demeure immense.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F100" s="7" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>697</v>
+        <v>798</v>
       </c>
       <c r="I100" s="9"/>
       <c r="J100" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>538</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -8013,32 +8046,32 @@
         </is>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="n">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="E101" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympiodore_le_Jeune"  style="color:#6A142A"  title=" Wikipedia"&gt;OLYMPIODORE le Jeune&lt;/a&gt; était un philosophe néoplatonicien grec connu comme grand commentateur de Platon et d’Aristote, dernier représentant important de la tradition platonicienne païenne à Alexandrie. &lt;/p&gt; &lt;p&gt; Il laisse surtout des commentaires sur des dialogues de Platon : Phédon, Gorgias, Philebos et &lt;a href="https://www.youtube.com/watch?v=KauBLoVOcNs" style="color:#88A1E9" title=" hat is philosophy? Olympiodorus' Commentary on the First Alcibiades par Abbas the Alchemist"&gt;l’Alcibiade&lt;/a&gt;. Il commente également Aristote et compose une introduction à la philosophie aristotélicienne, destinée à guider les étudiants dans la lecture du Stagirite. Son style est souvent décrit comme clair et pédagogique : il systématise les thèmes, expose les objections de manière ordonnée, et adapte la tradition néoplatonicienne à un public plus large.&lt;/p&gt; &lt;p&gt; Il adhère à une hiérarchie de l’être allant de l’Un aux Intelligibles, à l’Âme et au monde sensible, mais il insiste particulièrement sur la pédagogie des vertus et de la purification de l’âme. Dans ses analyses morales, il distingue plusieurs niveaux de vertus que l’âme doit gravir pour se détacher progressivement du corps et se rapprocher du divin. Un thème marquant est son développement d’une "échelle des vertus" en sept degrés : vertus naturelles, morales, politiques, purificatrices, contemplatives, paradigmatiques et hiératiques. Les vertus politiques et purificatrices organisent la vie en société et la maîtrise des passions, tandis que les vertus contemplatives et théurgiques visent l’union de l’âme avec les réalités intelligibles et le divin. &lt;/p&gt; &lt;p&gt; Tout en restant païen, il opère une forme d’accommodement avec un environnement chrétien : il évite en général l’affrontement frontal, et certains thèmes se laissent aisément intégrer dans une culture chrétienne. Cela explique probablement que &lt;a href="https://books.openedition.org/pulg/18286?lang=fr" style="color:#88A1E9" title="  L’École d’Olympiodore et les problèmes critiques connexes par OpenEdition"&gt;son enseignement&lt;/a&gt; ait pu continuer à Alexandrie après la fermeture des grandes écoles païennes d’Athènes. &lt;/p&gt; </t>
+        <v>802</v>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Priscien_de_Lydie" style="color:#6A142A" title="Wikipedia"&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href="https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316" title="la géographie et les originesnéoplatonisme sur Persee"&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité : « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F101" s="7" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>813</v>
+        <v>697</v>
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="2" t="s">
@@ -8051,7 +8084,7 @@
         <v>538</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -8059,32 +8092,32 @@
         </is>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="n">
         <v>495</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>817</v>
-      </c>
-      <c r="E102" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie" style="color:#6A142A" title="Wikipedia"&gt;EULAMIOS de Phrygie&lt;/a&gt; est un philosophe néoplatonicien du VIe siècle, originaire de Phrygie, en Asie Mineure. Il appartient au dernier cercle des philosophes païens de l’école d’Athènes, réunis autour de Damascius, à l’époque où le christianisme est devenu la religion officielle de l’Empire et où les païens sont de plus en plus écartés de la vie publique.&lt;/p&gt; &lt;p&gt;Comme pour la plupart de ses compagnons, nous ne savons presque rien de sa vie, et aucune de ses œuvres ne nous est parvenue. Son nom nous est connu par l’historien byzantin Agathias, qui raconte l’un des épisodes les plus célèbres de la fin de l’Antiquité. En 529, l’empereur Justinien interdit aux païens d’enseigner. L’école d’Athènes, héritière de l’Académie de Platon, ne peut plus fonctionner. Vers 531, sept philosophes quittent alors l’Empire : Damascius, Simplicius de Cilicie, Priscien de Lydie, Hermias et Diogène de Phénicie, Isidore de Gaza et Eulamios. Ils se rendent à la cour du roi de Perse Khosro Ier, qui passait pour un ami de la sagesse grecque et faisait traduire Platon et Aristote. Mais la Perse les déçoit, et ils souhaitent rentrer. En 532, le traité de paix signé entre Khosro et Justinien prévoit qu’ils pourront revenir dans l’Empire et y vivre sans être obligés de renoncer à leurs croyances. Simplicius écrira ensuite ses grands commentaires d’Aristote, qui sont parmi les plus précieux de l’Antiquité.&lt;/p&gt; &lt;p&gt;Ces derniers maîtres du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; ont transmis la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_antique" style="color:#6A142A" title="Philosophie antique sur Wikipedia"&gt;philosophie antique&lt;/a&gt; aux savants byzantins, syriaques et arabes, et, par eux, au Moyen Âge.&lt;/p&gt;</t>
+        <v>809</v>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympiodore_le_Jeune"  style="color:#6A142A"  title=" Wikipedia"&gt;OLYMPIODORE le Jeune&lt;/a&gt; était un philosophe néoplatonicien grec connu comme grand commentateur de Platon et d’Aristote, dernier représentant important de la tradition platonicienne païenne à Alexandrie. &lt;/p&gt; &lt;p&gt; Il laisse surtout des commentaires sur des dialogues de Platon : Phédon, Gorgias, Philebos et &lt;a href="https://www.youtube.com/watch?v=KauBLoVOcNs" style="color:#88A1E9" title=" hat is philosophy? Olympiodorus' Commentary on the First Alcibiades par Abbas the Alchemist"&gt;l’Alcibiade&lt;/a&gt;. Il commente également Aristote et compose une introduction à la philosophie aristotélicienne, destinée à guider les étudiants dans la lecture du Stagirite. Son style est souvent décrit comme clair et pédagogique : il systématise les thèmes, expose les objections de manière ordonnée, et adapte la tradition néoplatonicienne à un public plus large.&lt;/p&gt; &lt;p&gt; Il adhère à une hiérarchie de l’être allant de l’Un aux Intelligibles, à l’Âme et au monde sensible, mais il insiste particulièrement sur la pédagogie des vertus et de la purification de l’âme. Dans ses analyses morales, il distingue plusieurs niveaux de vertus que l’âme doit gravir pour se détacher progressivement du corps et se rapprocher du divin. Un thème marquant est son développement d’une "échelle des vertus" en sept degrés : vertus naturelles, morales, politiques, purificatrices, contemplatives, paradigmatiques et hiératiques. Les vertus politiques et purificatrices organisent la vie en société et la maîtrise des passions, tandis que les vertus contemplatives et théurgiques visent l’union de l’âme avec les réalités intelligibles et le divin. &lt;/p&gt; &lt;p&gt; Tout en restant païen, il opère une forme d’accommodement avec un environnement chrétien : il évite en général l’affrontement frontal, et certains thèmes se laissent aisément intégrer dans une culture chrétienne. Cela explique probablement que &lt;a href="https://books.openedition.org/pulg/18286?lang=fr" style="color:#88A1E9" title="  L’École d’Olympiodore et les problèmes critiques connexes par OpenEdition"&gt;son enseignement&lt;/a&gt; ait pu continuer à Alexandrie après la fermeture des grandes écoles païennes d’Athènes. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F102" s="7" t="s">
-        <v>819</v>
-      </c>
-      <c r="G102" s="15" t="s">
-        <v>820</v>
-      </c>
-      <c r="H102" s="12" t="s">
-        <v>697</v>
+        <v>811</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>812</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>813</v>
       </c>
       <c r="I102" s="9"/>
       <c r="J102" s="2" t="s">
@@ -8097,7 +8130,7 @@
         <v>538</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -8105,30 +8138,32 @@
         </is>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="n">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie" title="Wikipedia"&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;</t>
+        <v>816</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie" style="color:#6A142A" title="Wikipedia"&gt;EULAMIOS de Phrygie&lt;/a&gt; est un philosophe néoplatonicien du VIe siècle, originaire de Phrygie, en Asie Mineure. Il appartient au dernier cercle des philosophes païens de l’école d’Athènes, réunis autour de Damascius, à l’époque où le christianisme est devenu la religion officielle de l’Empire et où les païens sont de plus en plus écartés de la vie publique.&lt;/p&gt; &lt;p&gt;Comme pour la plupart de ses compagnons, nous ne savons presque rien de sa vie, et aucune de ses œuvres ne nous est parvenue. Son nom nous est connu par l’historien byzantin Agathias, qui raconte l’un des épisodes les plus célèbres de la fin de l’Antiquité. En 529, l’empereur Justinien interdit aux païens d’enseigner. L’école d’Athènes, héritière de l’Académie de Platon, ne peut plus fonctionner. Vers 531, sept philosophes quittent alors l’Empire : Damascius, Simplicius de Cilicie, Priscien de Lydie, Hermias et Diogène de Phénicie, Isidore de Gaza et Eulamios. Ils se rendent à la cour du roi de Perse Khosro Ier, qui passait pour un ami de la sagesse grecque et faisait traduire Platon et Aristote. Mais la Perse les déçoit, et ils souhaitent rentrer. En 532, le traité de paix signé entre Khosro et Justinien prévoit qu’ils pourront revenir dans l’Empire et y vivre sans être obligés de renoncer à leurs croyances. Simplicius écrira ensuite ses grands commentaires d’Aristote, qui sont parmi les plus précieux de l’Antiquité.&lt;/p&gt; &lt;p&gt;Ces derniers maîtres du &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" style="color:#6A142A" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; ont transmis la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_antique" style="color:#6A142A" title="Philosophie antique sur Wikipedia"&gt;philosophie antique&lt;/a&gt; aux savants byzantins, syriaques et arabes, et, par eux, au Moyen Âge.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F103" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9" t="s">
-        <v>826</v>
+        <v>819</v>
+      </c>
+      <c r="G103" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="H103" s="12" t="s">
+        <v>697</v>
       </c>
       <c r="I103" s="9"/>
       <c r="J103" s="2" t="s">
@@ -8141,63 +8176,51 @@
         <v>538</v>
       </c>
       <c r="M103" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie" title="Wikipedia"&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme sur Wikipedia"&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="G104" s="9"/>
+      <c r="H104" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="I104" s="9"/>
+      <c r="J104" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="M104" s="2" t="s">
         <v>827</v>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="7">
-        <v>-350</v>
-      </c>
-      <c r="B104" s="7">
-        <v>-280</v>
-      </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">350 A JC - 280 A JC</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIPPARCHIA de Maronée</t>
-        </is>
-      </c>
-      <c r="E104" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hipparchia"  title=" Wikipedia"&gt;HIPPARCHIA de Maronée&lt;/a&gt; (vers 350-280 avant J.-C.) est une philosophe cynique grecque, originaire de Maronée en Thrace. Issue d'une famille aisée, elle tomba amoureuse du philosophe Cratès de Thèbes, disciple de Diogène, qui avait renoncé à toute sa fortune. Ses parents s'opposèrent au mariage ; elle menaça de se tuer. Cratès lui-même tenta de la dissuader en lui montrant sa pauvreté, mais elle choisit de partager sa vie et ses idées.&lt;/p&gt; &lt;p&gt;Le cynisme prônait une vie simple, conforme à la nature, libérée des richesses, des honneurs et des conventions sociales jugées artificielles. Hipparchia vécut ainsi avec Cratès, en public et sans honte, portant le même manteau grossier que lui, et participa comme un homme aux banquets et aux discussions philosophiques, ce qui fit scandale à Athènes.&lt;/p&gt; &lt;p&gt;Selon Diogène Laërce, elle aurait écrit des traités philosophiques, des lettres et des réponses à des questions posées au philosophe Théodore, aujourd'hui perdus. Elle eut avec Cratès au moins deux enfants et continua de mener une vie de philosophe. Pour les anciens, elle était la preuve qu'une femme pouvait choisir librement la vie philosophique la plus exigeante, et plusieurs auteurs, jusqu'à l'époque chrétienne, citèrent son exemple.&lt;/p&gt; &lt;p&gt;Diogène Laërce rapporte une anecdote célèbre : lors d'un banquet, le philosophe Théodore l'Athée voulut l'humilier en lui demandant qui avait donc laissé sa navette sur le métier à tisser. Elle répondit qu'elle avait consacré à l'étude le temps qu'on aurait voulu lui faire perdre au rouet. Hipparchia est ainsi devenue le symbole de la femme qui revendique le droit de penser et de vivre en philosophe.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grecque</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cynisme</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe cynique grecque, épouse de Cratès, qui vécut selon ses idées contre les conventions de son temps.</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -8214,35 +8237,35 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E16" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Protagoras&quot;  title=&quot;Protagoras par Wikipédia&quot;&gt; PROTAGORAS&lt;/a&gt;  était un philosophe considéré comme l'un &lt;a href=&quot;https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;ab_channel=Bibiclo&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Les Sophistes par Bobiclo&quot;&gt; des sophistes&lt;/a&gt; les plus célèbres de cette période.&lt;/p&gt;&#10;&#10;&lt;p&gt;Les sophistes étaient des enseignants itinérants qui offraient &lt;a href=&quot;https://www.youtube.com/watch?v=X5bZKSCfc_g&amp;ab_channel=AlainBajom%C3%A9e&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Rhétorique et relativisme par Alain Bajomée&quot;&gt; des cours de rhétorique&lt;/a&gt;, d'éloquence et de persuader efficacement. Cependant, il a également suscité des débats et des controverses en raison de ses opinions et de ses idées.&lt;/p&gt;&#10;&lt;p&gt;L'une de ses déclarations les plus célèbres est : &quot;L'homme est la mesure de toutes choses : de celles qui sont, tant quand elles sont en tant qu'elles sont, que de celles qui ne sont pas, tant quand elles ne sont pas en tant qu'elles ne sont pas.&quot; Cela suggère que la perception et l'expérience individuelles sont centrales pour la compréhension de la réalité, et que la vérité peut être relative à chaque individu. Cette déclaration forme le fondement de ce que l'on appelle &lt;a href=&quot;https://www.youtube.com/watch?v=LxSCq1F7pSk&amp;ab_channel=LePr%C3%A9cepteur&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Le relativisme par le Précepteur&quot;&gt; le relativisme.&lt;/a&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Il a également abordé des sujets tels que la nature de la justice, l'éducation et le rôle des dieux dans la vie humaine. Ses enseignements ont été critiqués par d'autres philosophes, notamment Socrate et Platon, qui les voyaient vides de fondement rationnel.&lt;/p&gt;&#10;&#10;&lt;p&gt;Bien qu'il ait laissé peu d'œuvres écrites, sa vision de la relativité de la vérité et de l'importance de la rhétorique a contribué à façonner les débats sur la nature de la connaissance et de la réalité dans la philosophie grecque antique.&lt;/p&gt;  &lt;audio controls title=&quot;Platon vs. Protagoras: l'homme est il la mesure de toutes choses? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/09/s40/NET_FC_f081bba4-88ba-4b62-930d-2c30e49863d9.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E18" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gorgias&quot; title=&quot; Wikipedia&quot;&gt;GORGIAS&lt;/a&gt; était un philosophe présocratique et l'une des figures les plus importantes de la &lt;a href=&quot;https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;t=184s&quot; title=&quot; Les sophistes par Bibiclo&quot;&gt;sophistique&lt;/a&gt;.  Contrairement aux philosophes comme Platon ou Aristote, qui cherchaient à découvrir des vérités universelles en mettant l'accent sur l'importance de l'opinion et de la persuasion dans les affaires humaines.  Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;  - &quot;Sur le Non-Être ou sur la Nature&quot; : Il développe une argumentation radicale qui remet en question la possibilité même de la connaissance et de la communication.&lt;/p&gt; &lt;p&gt; -  Il soutient trois thèses principales : - Rien n'existe.  - Si quelque chose existait, nous ne pourrions pas le connaître. - Si nous pouvions le connaître, nous ne pourrions pas le communiquer aux autres. &lt;/p&gt; &lt;p&gt; Ces thèses sont souvent interprétées comme une critique de l'ontologie éléatique, notamment des idées de Parménide, qui affirmait que l'être est un et immuable. &lt;/p&gt;  &lt;p&gt; - &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89loge_d%27H%C3%A9l%C3%A8ne &quot;  title=&quot; Gorgias Eloge d’Helene  parWikipedia&quot;&gt;&quot;Éloge d'Hélène&quot;&lt;/a&gt;  : Dans ce discours, Il défend Hélène de Troie, souvent considérée comme responsable de la guerre de Troie. Il utilise des arguments rhétoriques pour montrer qu'elle ne peut être tenue pour responsable, car elle a été soit victime de la volonté des dieux, soit de la séduction de Pâris, soit de la force.  &lt;/p&gt; &lt;p&gt; -  &quot;Défense de Palamède&quot; : Dans ce discours, il défend Palamède, un héros grec accusé de trahison par Ulysse. Il utilise des arguments logiques et rhétoriques pour démontrer son l'innocence, montrant ainsi la puissance de la parole pour influencer les jugements. &lt;p&gt; Il  est souvent considéré comme un relativiste et un sceptique. Il met en doute la possibilité de connaître la vérité absolue et souligne l'importance de la persuasion dans les affaires humaines. Sa philosophie a eu une influence significative sur la pensée grecque, notamment sur Platon, qui le critique sévèrement dans son dialogue &quot;Gorgias&quot;. Platon y oppose la recherche de la vérité à l'art de la persuasion, qu'il associe à la sophistique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E17" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Protagoras&quot;  title=&quot;Protagoras par Wikipédia&quot;&gt; PROTAGORAS&lt;/a&gt;  était un philosophe considéré comme l'un &lt;a href=&quot;https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;ab_channel=Bibiclo&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Les Sophistes par Bobiclo&quot;&gt; des sophistes&lt;/a&gt; les plus célèbres de cette période.&lt;/p&gt;&#10;&#10;&lt;p&gt;Les sophistes étaient des enseignants itinérants qui offraient &lt;a href=&quot;https://www.youtube.com/watch?v=X5bZKSCfc_g&amp;ab_channel=AlainBajom%C3%A9e&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Rhétorique et relativisme par Alain Bajomée&quot;&gt; des cours de rhétorique&lt;/a&gt;, d'éloquence et de persuader efficacement. Cependant, il a également suscité des débats et des controverses en raison de ses opinions et de ses idées.&lt;/p&gt;&#10;&lt;p&gt;L'une de ses déclarations les plus célèbres est : &quot;L'homme est la mesure de toutes choses : de celles qui sont, tant quand elles sont en tant qu'elles sont, que de celles qui ne sont pas, tant quand elles ne sont pas en tant qu'elles ne sont pas.&quot; Cela suggère que la perception et l'expérience individuelles sont centrales pour la compréhension de la réalité, et que la vérité peut être relative à chaque individu. Cette déclaration forme le fondement de ce que l'on appelle &lt;a href=&quot;https://www.youtube.com/watch?v=LxSCq1F7pSk&amp;ab_channel=LePr%C3%A9cepteur&quot; style=&quot;color:#88A1E9&quot;   title=&quot;Le relativisme par le Précepteur&quot;&gt; le relativisme.&lt;/a&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Il a également abordé des sujets tels que la nature de la justice, l'éducation et le rôle des dieux dans la vie humaine. Ses enseignements ont été critiqués par d'autres philosophes, notamment Socrate et Platon, qui les voyaient vides de fondement rationnel.&lt;/p&gt;&#10;&#10;&lt;p&gt;Bien qu'il ait laissé peu d'œuvres écrites, sa vision de la relativité de la vérité et de l'importance de la rhétorique a contribué à façonner les débats sur la nature de la connaissance et de la réalité dans la philosophie grecque antique.&lt;/p&gt;  &lt;audio controls title=&quot;Platon vs. Protagoras: l'homme est il la mesure de toutes choses? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/09/s40/NET_FC_f081bba4-88ba-4b62-930d-2c30e49863d9.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E19" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gorgias&quot; title=&quot; Wikipedia&quot;&gt;GORGIAS&lt;/a&gt; était un philosophe présocratique et l'une des figures les plus importantes de la &lt;a href=&quot;https://www.youtube.com/watch?v=kXdG-BS3SDI&amp;t=184s&quot; title=&quot; Les sophistes par Bibiclo&quot;&gt;sophistique&lt;/a&gt;.  Contrairement aux philosophes comme Platon ou Aristote, qui cherchaient à découvrir des vérités universelles en mettant l'accent sur l'importance de l'opinion et de la persuasion dans les affaires humaines.  Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;  - &quot;Sur le Non-Être ou sur la Nature&quot; : Il développe une argumentation radicale qui remet en question la possibilité même de la connaissance et de la communication.&lt;/p&gt; &lt;p&gt; -  Il soutient trois thèses principales : - Rien n'existe.  - Si quelque chose existait, nous ne pourrions pas le connaître. - Si nous pouvions le connaître, nous ne pourrions pas le communiquer aux autres. &lt;/p&gt; &lt;p&gt; Ces thèses sont souvent interprétées comme une critique de l'ontologie éléatique, notamment des idées de Parménide, qui affirmait que l'être est un et immuable. &lt;/p&gt;  &lt;p&gt; - &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89loge_d%27H%C3%A9l%C3%A8ne &quot;  title=&quot; Gorgias Eloge d’Helene  parWikipedia&quot;&gt;&quot;Éloge d'Hélène&quot;&lt;/a&gt;  : Dans ce discours, Il défend Hélène de Troie, souvent considérée comme responsable de la guerre de Troie. Il utilise des arguments rhétoriques pour montrer qu'elle ne peut être tenue pour responsable, car elle a été soit victime de la volonté des dieux, soit de la séduction de Pâris, soit de la force.  &lt;/p&gt; &lt;p&gt; -  &quot;Défense de Palamède&quot; : Dans ce discours, il défend Palamède, un héros grec accusé de trahison par Ulysse. Il utilise des arguments logiques et rhétoriques pour démontrer son l'innocence, montrant ainsi la puissance de la parole pour influencer les jugements. &lt;p&gt; Il  est souvent considéré comme un relativiste et un sceptique. Il met en doute la possibilité de connaître la vérité absolue et souligne l'importance de la persuasion dans les affaires humaines. Sa philosophie a eu une influence significative sur la pensée grecque, notamment sur Platon, qui le critique sévèrement dans son dialogue &quot;Gorgias&quot;. Platon y oppose la recherche de la vérité à l'art de la persuasion, qu'il associe à la sophistique. &lt;/p&gt; &#10;&#10;"/>
     <hyperlink ref="E22" r:id="rId3" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/D%C3%A9mocrite&quot; title=&quot; Wikipedia&quot;&gt; DÉMOCRITE&lt;/a&gt; était un philosophe Grec connu pour être l'un des fondateurs avec LEUCIPPE de la philosophie  &lt;a href=&quot;https://www.youtube.com/watch?v=AGvcey2B3Vc&amp;t=3s&amp;ab_channel=Coursitout&quot;   title=&quot;l'Atomisme des philosophes Grecs par Coursitout&quot;&gt; atomiste&lt;/a&gt;, une théorie selon laquelle tout dans l'univers est composé de particules indivisibles appelées atomes. Selon lui, ils sont en mouvement perpétuel et se combinent pour former toutes les substances et objets que nous voyons autour de nous.  Il était réputé pour sa grande curiosité intellectuelle et aurait beaucoup voyagé, notamment en Égypte et en Orient, afin d’enrichir ses connaissances. Surnommé parfois « le philosophe rieur », il adoptait une attitude détachée face aux préoccupations humaines, considérant que la sérénité naît de la compréhension du monde et de la maîtrise de soi.  &lt;/p&gt; &lt;p&gt;Il avait une approche &lt;a href=&quot;https://www.youtube.com/watch?v=_uXOu9ZRD4I&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;le matérialisme par Alain Bajomée&quot;&gt; matérialiste&lt;/a&gt; de la réalité et croyait que tout ce qui existe était composé de matière et de vide, et que la perception humaine était basée sur l'interaction entre les atomes et les sens. Il était également connu pour ses idées sur l'éthique et la morale et croyait que le bonheur et la vertu pouvaient être atteints grâce à une vie simple et équilibrée, et que les désirs excessifs et les passions pouvaient entraîner la souffrance. &lt;/p&gt; &lt;p&gt; Sa pensée ne se limite pas à la physique : il développe aussi une réflexion approfondie sur la connaissance en distinguant les qualités « réelles » (comme la forme et le mouvement des atomes) des qualités « sensibles » (comme les couleurs ou les saveurs), qui dépendent de nos perceptions. Cette distinction annonce des débats majeurs de la philosophie moderne. Son influence se retrouvera plus tard chez des penseurs comme Épicure, qui reprendra l’atomisme en y intégrant une dimension éthique centrée sur la recherche du plaisir mesuré et de l’absence de trouble.   &lt;/p&gt; &lt;p&gt; Peu de ses écrits ont survécu jusqu'à nos jours, et la plupart de ce que nous connaissons provient de commentaires ultérieurs et de citations dans les œuvres d'autres philosophes grecs. Cependant, ses contributions à la théorie atomique ont été fondamentales pour la compréhension moderne de la physique et de la chimie. &lt;/p&gt; &lt;audio controls title=&quot;Démocrite contre Platon par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2015/06/s27/net-fi-be35a965-485b-4f98-9b10-0e2051e903ec.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
     <hyperlink ref="E23" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thrasymaque&quot;title=&quot; Wikipedia&quot;&gt;THRASYMAQUE&lt;/a&gt; était un philosophe sophiste grec connue pour son rôle dans &lt;a href=&quot;https://www.youtube.com/watch?v=qSrvZvjPG_w&quot; style=&quot;color:#88A1E9&quot; title=&quot; PLATON-Cest quoi la république par Kosmos &quot;&gt;&quot;La République&quot;&lt;/a&gt; de Platon. Il est l'un des interlocuteurs de Socrate dans ce dialogue, où il défend une vision provocante et cynique de la justice. &lt;/p&gt;&lt;p&gt; Il  affirme que &quot;&lt;a href=&quot;https://www.youtube.com/watch?v=VlLLr8kVya0&quot;  title=&quot;  Qu'est-ce que la Justice en Philosophie ?   par Coursitout &quot;&gt;la justice&lt;/a&gt; n'est rien d'autre que l'intérêt du plus fort&quot;. Selon lui, les lois et les normes sociales sont établies par ceux qui détiennent le pouvoir (les gouvernants, les tyrans, les aristocrates) pour servir leurs propres intérêts. Ainsi, la justice n'est pas une valeur universelle ou objective, mais un outil de domination. Il  va plus loin en affirmant que l'injustice est une vertu. Selon lui, les individus injustes sont plus heureux et plus prospères que les justes, car ils savent exploiter les autres à leur avantage. La justice, au contraire, est une faiblesse qui empêche les individus de réaliser leur plein potentiel. &lt;/p&gt;&lt;p&gt; Il  est souvent vu comme un précurseur du relativisme moral, qui nie l'existence de valeurs universelles. Sa pensée peut être rapprochée du réalisme politique, qui considère que la politique est avant tout une lutte pour le pouvoir et que les notions de justice et de moralité sont secondaires. &lt;/p&gt; &lt;p&gt; Il  incarne une vision cynique et réaliste de la justice, qui &lt;a href=&quot;https://www.persee.fr/doc/antiq_0770-2817_2018_num_87_1_3962&quot; style=&quot;color:#88A1E9&quot; title=&quot;Les difficultés du débat sur la justice entre Socrate et Thrasymaque dans la République par Persée &quot;&gt;contraste fortement&lt;/a&gt; avec l'idéalisme de Socrate. Bien que ses arguments soient finalement réfutés dans le dialogue, ils restent une contribution importante à la philosophie politique, car ils soulèvent des questions fondamentales sur la nature du pouvoir, de la moralité et de la justice. &lt;/p&gt;"/>
     <hyperlink ref="E33" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eudoxe_de_Cnide&quot;  title=&quot; Wikipedia&quot;&gt;EUDOXE de Cnide&lt;/a&gt; était un mathématicien, astronome et philosophe grec de l'Antiquité, originaire de la ville de Cnide, en Asie Mineure (actuelle Turquie). Il est surtout connu pour   &lt;a href=&quot;https://www.youtube.com/watch?v=YiWuTuTPOEw&quot;  style=&quot;color:#88A1E9&quot; title=&quot; The Fascinating History of Mathematics : Eudoxus of Cnidus par Cambia Math Tutors&quot;&gt;ses travaux &lt;/a&gt;  en géométrie et en théorie des proportions. Ses contributions ont jeté les bases de nombreuses décounidevertes ultérieures, notamment celles d'Euclide. Il a développé une théorie générale des proportions qui permettait de comparer des grandeurs incommensurables. Cette théorie a permis de surmonter les limitations des mathématiques pythagoriciennes, qui étaient basées sur les nombres entiers. Il a étudié les sections coniques et les solides géométriques, contribuant à la compréhension des formes tridimensionnelles. &lt;/p&gt; &lt;p&gt; Il a proposé un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%A9ocentrisme&quot;  title=&quot; geocentrisme par wikipedia&quot;&gt;modèle géocentrique &lt;/a&gt; complexe pour expliquer les mouvements apparents des planètes, du Soleil et de la Lune. Selon ce modèle, chaque corps céleste est attaché à une série de sphères imbriquées, tournant à des vitesses et des angles différents. Ce système permettait de reproduire les mouvements rétrogrades des planètes (lorsqu'elles semblent reculer dans le ciel). Bien que ce modèle ait été remplacé plus tard par celui de Ptolémée, il a marqué une étape importante dans l'histoire de l'astronomie. &lt;/p&gt; &lt;p&gt; Il a soutenu que le plaisir est le bien suprême, une idée qui contraste avec les vues de Platon et d'Aristote. Pour Eudoxe, le plaisir est une fin en soi et non simplement un moyen et a critiqué la théorie des Idées de Platon, arguant que les Idées ne peuvent pas exister séparément des objets concrets. &lt;/p&gt; "/>
     <hyperlink ref="H40" r:id="rId6" display="https://www.laphilo.fr/pho/aristippel-mini.webp"/>
-    <hyperlink ref="E47" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89picure&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9donisme&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'hédonisme par Wikipédia&quot;&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href=&quot;https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href=&quot;https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href=&quot;https://www.youtube.com/watch?v=cb1YHXSuxlM&quot;   title=&quot;La philosophie du bonheur par Parole de philosophe&quot;&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt;  &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées &quot;atomes&quot;.&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt;  &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title=&quot;Est il bien raisonnable d'avoir peur de la mort par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E57" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame&quot; title=&quot;Wikipedia&quot;&gt;Hégésinous de PERGAME&lt;/a&gt; était un philosophe grec, représentant de la &lt;em&gt;Moyenne Académie&lt;/em&gt; platonicienne. Il succéda à Évandre et Télécès à la direction de l'Académie d'Athènes et fut le maître direct de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt;, qui allait révolutionner la pensée académicienne avec sa Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Comme ses prédécesseurs, Hégésinous s'inscrivait dans la tradition sceptique d'Arcésilas, défendant la suspension du jugement face à l'incertitude radicale de la connaissance humaine. Son enseignement, dont nous ne conservons aucun écrit, fut néanmoins suffisamment stimulant pour former l'un des plus grands dialecticiens de l'Antiquité en la personne de Carnéade.&lt;/p&gt; &lt;p&gt;Hégésinous appartient à cette lignée de scholarques discrets qui assurèrent la survie institutionnelle de l'Académie durant les IIIe et IIe siècles av. J.-C. Son rôle de maillon entre la Moyenne et la Nouvelle Académie est fondamental, même si son nom reste peu connu en dehors des spécialistes de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie hellénistique sur Wikipedia&quot;&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;"/>
-    <hyperlink ref="E58" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Wikipedia&quot;&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Dialectique&quot; title=&quot;Dialectique par Wikipedia&quot;&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272&quot; title=&quot;Opinion et certitude par Persee&quot;&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href=&quot;https://fr.wikipedia.org/wiki/Cic%C3%A9ron&quot; style=&quot;color:#6A142A&quot; title=&quot;Cicéron sur Wikipedia&quot;&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il.&lt;/p&gt;"/>
-    <hyperlink ref="E60" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s&quot; title=&quot;Wikipedia&quot;&gt;TÉLÉCLÈS&lt;/a&gt; était un philosophe grec représentant de la Moyenne Académie platonicienne. Disciple de Lacydès de Cyrène, il dirigea conjointement l'Académie d'Athènes avec Évandre, après que Lacydès leur eut confié la responsabilité de l'École de son vivant.&lt;/p&gt; &lt;p&gt;Très peu de détails biographiques nous sont parvenus sur sa vie et sa pensée. Il s'inscrivait dans la tradition sceptique inaugurée par Arcésilas, défendant l'idée que la raison humaine ne peut accéder à une certitude absolue, et que la sagesse réside dans la suspension du jugement et l'adhésion au vraisemblable. Ses étudiants comprenaient de futurs représentants de la Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Téléclès appartient à ces figures de transition dont le rôle, discret mais essentiel, fut d'assurer la pérennité de l'Académie entre deux grandes figures : Lacydès avant lui et &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; style=&quot;color:#6A142A&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt; après lui. Son passage à la direction de l'École illustre la collégialité qui caractérisait l'organisation de la pensée académicienne.&lt;/p&gt;"/>
-    <hyperlink ref="E61" r:id="rId11" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes&quot;  title=&quot; Wikipedia&quot;&gt;PANÉTIUS DE RHODES&lt;/a&gt;  était un philosophe grec considéré comme le fondateur de l'école Stoïcienne de Rhodes. Il a étudié avec Diogène de Babylone et est devenu plus tard l'un des penseurs de Cicéron, le célèbre orateur et homme politique romain. &lt;/p&gt; &lt;p&gt;  Il a contribué à façonner la  &lt;a href=&quot;https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie&quot;  title=&quot;Le Stoïcisme par apprendre la philo&quot;&gt;pensée stoïcienne&lt;/a&gt; en l'adaptant aux besoins de son temps en la conciliant  avec d'autres courants philosophiques comme l'épicurisme et le scepticisme. Il rompt avec les dogmes stoïciens. « Il nie la conflagration universelle et croit à l'éternité d'un monde que la Providence rend parfait ». &lt;/p&gt; &lt;p&gt; Il se défie de la mantique (la divination) et nie l'immortalité de l'âme. Il reconnaît en nous, à côté des impulsions de l'instinct premier, des tendances fondamentales où s'associent nature et raison. &lt;/p&gt; &lt;p&gt; Il aboutit à un humanisme, il tend à une sérénité morale faite de calme, de mesure, d'harmonie. Il a également développé la notion de justice naturelle, qui est une forme de justice qui découle de la nature même de l'homme et de la société, et qui est différente de la justice conventionnelle établie par les lois et les coutumes.&lt;/p&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E62" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Posidonios&quot;  title=&quot; Wikipedia&quot;&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href=&quot;https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770&quot;  title=&quot;Posidonius d'Apamée théoricien de la géométrie par Persée&quot;&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href=&quot;https://www.youtube.com/watch?v=EqU-kD8dW4Y&quot; title=&quot;Grèce antique - 33 La civilisation hellénistique par Yannick Rub&quot;&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289&quot;  title=&quot;La philosophiede Posidonius par Persee&quot;&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; "/>
-    <hyperlink ref="E68" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que&quot; title=&quot; Wikipedia&quot;&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href=&quot;https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Le Stoïcisme par le Précepteur&quot;&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=J3wZoqElCgs&quot; title=&quot;Who is Seneca par Daily Stoic &quot;&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href=&quot;https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin&quot; title=&quot;La vie Heureuse par Karl Baudoin&quot;&gt; &quot;une vie heureuse&quot;.&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : - De la brièveté de la vie (consideration sur l’usage du temps). - De la colère (sur la maîtrise de cette passion destructive). - De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt;  est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href=&quot;https://www.youtube.com/watch?v=d_cge9OwVAs&quot; title=&quot;La vie philosophique de Sénèque par Kosmos&quot;&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title=&quot;Les lettres à Lucilius – Senèque  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="E69" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;AMMONIOS d'Athènes&lt;/a&gt; était un philosophe platonicien originaire d'Égypte, qui enseigna à Athènes et fut l'un des maîtres de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Plutarque&quot; style=&quot;color:#6A142A&quot; title=&quot;Plutarque sur Wikipedia&quot;&gt;Plutarque&lt;/a&gt;. Représentant du médio-platonisme, il cherchait à concilier la philosophie de Platon avec d'autres courants de pensée de l'Antiquité tardive.&lt;/p&gt; &lt;p&gt;Son enseignement oral laissa une empreinte durable sur ses disciples, bien qu'il n'ait laissé aucun écrit. Il défendait une lecture spirituelle et morale du platonisme, insistant sur la contemplation du Bien et la purification de l'âme. Plutarque, son élève le plus illustre, rapporte ses enseignements dans ses &lt;em&gt;Moralia&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Ammonios d'Athènes appartient à ce courant de platoniciens qui, entre Platon et Plotin, ont préparé le terrain au &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;, en développant une exégèse du &lt;em&gt;Timée&lt;/em&gt; et de la &lt;em&gt;République&lt;/em&gt;. Sa discrétion littéraire contraste avec l'influence considérable qu'il exerça sur le cercle intellectuel d'Athènes de son époque.&lt;/p&gt;"/>
-    <hyperlink ref="H79" r:id="rId15" display="https://www.laphilo.fr/pho/jamblique-mini.webp"/>
-    <hyperlink ref="H86" r:id="rId16" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="H87" r:id="rId17" display="https://www.laphilo.fr/pho/scyrene-mini.webp"/>
-    <hyperlink ref="E88" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot;   title=&quot;Proclus par Wikipédia&quot;&gt; PROCLUS&lt;/a&gt; était un philosophe &lt;a href=&quot;https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D&quot;   title=&quot;Le Néoplatonisme par Anne Baudart&quot;&gt; Néoplatonicien grec&lt;/a&gt; et il est considéré comme l'un des derniers grands philosophes de l'Antiquité classique.&lt;/p&gt;&#10;&lt;p&gt; Sa philosophie est basée sur les enseignements de Platon et d'Aristote. Il a développé une théorie complexe de l'univers qui est basée sur l'idée d'une hiérarchie de réalités. Au sommet de cette hiérarchie se trouve l'Un, qui est la réalité ultime et incompréhensible. Voici les principaux concepts de la philosophie de Proclus :&lt;/p&gt;&#10;&lt;dd&gt;L'Un : Réalité ultime et incompréhensible, qui est la source de toutes choses.&lt;/dd&gt;&#10;&lt;dd&gt;Le Démiurge : Force créatrice qui a donné forme à l'univers.&lt;/dd&gt;&#10;&lt;dd&gt;Les dieux : Intermédiaires entre l'Un et le monde sensible.&lt;/dd&gt;&#10;&lt;dd&gt;Les âmes : Principes vitaux qui animent les êtres vivants.&lt;/dd&gt;&#10;&lt;dd&gt;La matière : Réalité la plus basse de la hiérarchie, source du changement et de la corruption.&lt;/dd&gt;&#10;&lt;p&gt; Il a écrit un grand nombre &lt;a href=&quot;https://remacle.org/bloodwolf/philosophes/proclus/table.htm&quot;   title=&quot;Proclus par Philippe Remacle&quot;&gt; d'ouvrages sur la philosophie&lt;/a&gt;, dont les plus importants sont &lt;a href=&quot;https://www.youtube.com/watch?v=SJK1kbyXXno&quot;   title=&quot;Les éléments de Théologie de Proclus par LabEx HaStec&quot;&gt; les Commentaires sur le Timée de Platon&lt;/a&gt;, les Éléments de théologie et les Hypotyposes platonicae. Ces ouvrages ont été d'une grande influence sur la philosophie occidentale, et ils continuent à être étudiés aujourd'hui. &lt;/p&gt;   &lt;audio controls title=&quot; Proclus, un philosophe étoilé par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;"/>
-    <hyperlink ref="E89" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;HERMIAS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien, élève du grand &lt;a href=&quot;https://fr.wikipedia.org/wiki/Syrianos&quot; title=&quot;Syrianus sur Wikipedia&quot;&gt;Syrianus&lt;/a&gt; à Athènes. De retour à Alexandrie, il y fonda une école philosophique et épousa Aidésia, dont il eut pour fils le célèbre Ammonios d'Alexandrie.&lt;/p&gt; &lt;p&gt;Son œuvre principale est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes prises lors des cours de Syrianus. Cet ouvrage, qui nous est parvenu, offre une interprétation allégorique et métaphysique du dialogue platonicien sur l'amour, l'âme et la beauté, dans la tradition néoplatonicienne.&lt;/p&gt; &lt;p&gt;Hermias s'inscrit dans la lignée des maîtres qui firent d'Alexandrie un foyer majeur de la pensée antique tardive. Son rôle de transmetteur entre l'école d'Athènes et celle d'Alexandrie fut déterminant pour la pérennité du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;. Sa mort prématurée laissa Aidésia seule pour assurer l'avenir philosophique de leurs fils.&lt;/p&gt;"/>
-    <hyperlink ref="H91" r:id="rId20" display="https://www.laphilo.fr/pho/damascios-mini.webp"/>
-    <hyperlink ref="E92" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;AMMONIOS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien de la fin de l'Antiquité, fils d'Hermias et d'Aidésia, tous deux philosophes. Il succéda à Proclos comme tête de l'école néoplatonicienne d'Athènes et dirigea l'école alexandrine, formant une génération de commentateurs d'Aristote comme Olympiodore, Jean Philopon ou Simplicius, dans un contexte de tensions entre païens et chrétiens. Il enseigna l'Aristote aux païens et le Platon aux chrétiens pour favoriser une harmonie entre doctrines. &lt;/p&gt; &lt;p&gt; Spécialiste des commentaires d'Aristote, il défendit une interprétation néoplatonicienne unifiant Aristote et Platon : Aristote prépare à Platon, l'âme s'élève de la matière à l'Intellect divin. Ses écrits, perdus sauf fragments, insistent sur la théurgie et l'exégèse allégorique.&lt;/p&gt; &lt;p&gt; Son école alexandrine préserva le corpus aristotélicien pour l'Islam et l'Occident médiéval. &lt;/p&gt; Aucun texte complet ne survit directement, mais ses leçons sont préservées via les commentaires de ses élèves, comme ceux de Philopon sur l'Isagogè. Il chercha à harmoniser les deux grands penseurs antiques pour préserver la tradition païenne face au christianisme dominant.https://www.ljallamion.fr/spip.php?article6169 &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E93" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isidore_de_Gaza&quot; title=&quot;Wikipedia&quot;&gt;ISIDORE de Gaza&lt;/a&gt; était un philosophe néoplatonicien, né à Gaza en Palestine. Maître de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Damascios&quot; title=&quot;Damascios sur Wikipedia&quot;&gt;Damascios&lt;/a&gt;, le dernier scholarque de l'Académie d'Athènes, il fut l'un des derniers grands représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot;  title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique.&lt;/p&gt; &lt;p&gt;Damascios lui consacra une biographie dans sa &lt;em&gt;Vie d'Isidore&lt;/em&gt; (aussi connue sous le nom de &lt;em&gt;Vie des philosophes&lt;/em&gt;), où il le dépeint comme un personnage d'une grande intégrité morale, attaché aux traditions philosophiques grecques et à la piété envers les dieux, dans un contexte où le christianisme triomphait. Isidore représentait une philosophie vécue comme exercice spirituel, alliant rigueur intellectuelle et pratique ascétique.&lt;/p&gt; &lt;p&gt;Sa pensée s'inscrit dans la grande tradition de l'école néoplatonicienne d'Athènes, héritière de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot; title=&quot;Proclus sur Wikipedia&quot;&gt;Proclus&lt;/a&gt;. Il incarne ces penseurs de la fin du paganisme grec qui, face à la montée de la chrétienté, s'accrochaient à la philosophie comme à une forme de spiritualité rationnelle et contemplative, gardienne de l'héritage intellectuel de la Grèce.&lt;/p&gt;"/>
-    <hyperlink ref="H93" r:id="rId23" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="H96" r:id="rId24" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="E97" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Simplicius_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698&quot; style=&quot;color:#88A1E9&quot; title=&quot;A propos de la biographie de Simplicius par Persée&quot;&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le &quot;Manuel d’Épictète&quot; et, selon la tradition, sur &quot;De l’âme&quot;. Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href=&quot;https://www.youtube.com/watch?v=C17VYcyLkiY&quot; style=&quot;color:#88A1E9&quot; title=&quot;SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions&quot;&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.  &lt;a href=&quot;https://www.youtube.com/watch?v=6a4uQpmGsUg&quot; style=&quot;color:#88A1E9&quot; title=&quot;Simplicius – The Last Guardian of Ancient Philosophy par A time in history&quot;&gt; Transmis et traduits&lt;/a&gt; dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; "/>
-    <hyperlink ref="E100" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Priscien_de_Lydie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316&quot; title=&quot;la géographie et les originesnéoplatonisme sur Persee&quot;&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité :  - « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. - « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;"/>
-    <hyperlink ref="E102" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;EULAMIOS de Phrygie&lt;/a&gt; était un philosophe néoplatonicien du VIe siècle, originaire de Phrygie en Asie Mineure (actuelle Turquie). Il appartient au cercle des derniers représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique, dont il perpétua la tradition après la fermeture de l'Académie d'Athènes par Justinien en 529.&lt;/p&gt; &lt;p&gt;Figure peu documentée de cette période de transition, il s'inscrit dans le mouvement de philosophes néoplatoniciens qui, après l'exil perse et la dispersion de l'école athénienne, continuèrent à enseigner et transmettre la philosophie grecque en dehors des institutions officielles. Ses liens avec les cercles de Damascios et Simplicius laissent penser qu'il participa à la préservation du corpus philosophique antique.&lt;/p&gt; &lt;p&gt;Eulamios représente la philosophie de survie du néoplatonisme face à la christianisation de l'Empire. Comme ses contemporains, il incarne la volonté de maintenir vivante une tradition intellectuelle millénaire, préservant ainsi les conditions de la redécouverte médiévale et renaissante de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_antique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie antique sur Wikipedia&quot;&gt;philosophie antique&lt;/a&gt;.&lt;/p&gt;"/>
-    <hyperlink ref="H102" r:id="rId28" display="https://www.laphilo.fr/photo/logo.webp"/>
-    <hyperlink ref="E103" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie&quot; title=&quot;Wikipedia&quot;&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.https://fr.wikipedia.org/wiki/Diogène_de_Phénicie    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;"/>
+    <hyperlink ref="E48" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89picure&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9donisme&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'hédonisme par Wikipédia&quot;&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href=&quot;https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href=&quot;https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur&quot; style=&quot;color:#88A1E9&quot;   title=&quot;L'épicurisme par le Précepteur&quot;&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href=&quot;https://www.youtube.com/watch?v=cb1YHXSuxlM&quot;   title=&quot;La philosophie du bonheur par Parole de philosophe&quot;&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt;  &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées &quot;atomes&quot;.&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt;  &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title=&quot;Est il bien raisonnable d'avoir peur de la mort par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E58" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame&quot; title=&quot;Wikipedia&quot;&gt;Hégésinous de PERGAME&lt;/a&gt; était un philosophe grec, représentant de la &lt;em&gt;Moyenne Académie&lt;/em&gt; platonicienne. Il succéda à Évandre et Télécès à la direction de l'Académie d'Athènes et fut le maître direct de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt;, qui allait révolutionner la pensée académicienne avec sa Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Comme ses prédécesseurs, Hégésinous s'inscrivait dans la tradition sceptique d'Arcésilas, défendant la suspension du jugement face à l'incertitude radicale de la connaissance humaine. Son enseignement, dont nous ne conservons aucun écrit, fut néanmoins suffisamment stimulant pour former l'un des plus grands dialecticiens de l'Antiquité en la personne de Carnéade.&lt;/p&gt; &lt;p&gt;Hégésinous appartient à cette lignée de scholarques discrets qui assurèrent la survie institutionnelle de l'Académie durant les IIIe et IIe siècles av. J.-C. Son rôle de maillon entre la Moyenne et la Nouvelle Académie est fondamental, même si son nom reste peu connu en dehors des spécialistes de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie hellénistique sur Wikipedia&quot;&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;"/>
+    <hyperlink ref="E59" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; title=&quot;Wikipedia&quot;&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Dialectique&quot; title=&quot;Dialectique par Wikipedia&quot;&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272&quot; title=&quot;Opinion et certitude par Persee&quot;&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href=&quot;https://fr.wikipedia.org/wiki/Cic%C3%A9ron&quot; style=&quot;color:#6A142A&quot; title=&quot;Cicéron sur Wikipedia&quot;&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il.&lt;/p&gt;"/>
+    <hyperlink ref="E62" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s&quot; title=&quot;Wikipedia&quot;&gt;TÉLÉCLÈS&lt;/a&gt; était un philosophe grec représentant de la Moyenne Académie platonicienne. Disciple de Lacydès de Cyrène, il dirigea conjointement l'Académie d'Athènes avec Évandre, après que Lacydès leur eut confié la responsabilité de l'École de son vivant.&lt;/p&gt; &lt;p&gt;Très peu de détails biographiques nous sont parvenus sur sa vie et sa pensée. Il s'inscrivait dans la tradition sceptique inaugurée par Arcésilas, défendant l'idée que la raison humaine ne peut accéder à une certitude absolue, et que la sagesse réside dans la suspension du jugement et l'adhésion au vraisemblable. Ses étudiants comprenaient de futurs représentants de la Nouvelle Académie.&lt;/p&gt; &lt;p&gt;Téléclès appartient à ces figures de transition dont le rôle, discret mais essentiel, fut d'assurer la pérennité de l'Académie entre deux grandes figures : Lacydès avant lui et &lt;a href=&quot;https://fr.wikipedia.org/wiki/Carn%C3%A9ade&quot; style=&quot;color:#6A142A&quot; title=&quot;Carnéade sur Wikipedia&quot;&gt;Carnéade&lt;/a&gt; après lui. Son passage à la direction de l'École illustre la collégialité qui caractérisait l'organisation de la pensée académicienne.&lt;/p&gt;"/>
+    <hyperlink ref="E63" r:id="rId11" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes&quot;  title=&quot; Wikipedia&quot;&gt;PANÉTIUS DE RHODES&lt;/a&gt;  était un philosophe grec considéré comme le fondateur de l'école Stoïcienne de Rhodes. Il a étudié avec Diogène de Babylone et est devenu plus tard l'un des penseurs de Cicéron, le célèbre orateur et homme politique romain. &lt;/p&gt; &lt;p&gt;  Il a contribué à façonner la  &lt;a href=&quot;https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie&quot;  title=&quot;Le Stoïcisme par apprendre la philo&quot;&gt;pensée stoïcienne&lt;/a&gt; en l'adaptant aux besoins de son temps en la conciliant  avec d'autres courants philosophiques comme l'épicurisme et le scepticisme. Il rompt avec les dogmes stoïciens. « Il nie la conflagration universelle et croit à l'éternité d'un monde que la Providence rend parfait ». &lt;/p&gt; &lt;p&gt; Il se défie de la mantique (la divination) et nie l'immortalité de l'âme. Il reconnaît en nous, à côté des impulsions de l'instinct premier, des tendances fondamentales où s'associent nature et raison. &lt;/p&gt; &lt;p&gt; Il aboutit à un humanisme, il tend à une sérénité morale faite de calme, de mesure, d'harmonie. Il a également développé la notion de justice naturelle, qui est une forme de justice qui découle de la nature même de l'homme et de la société, et qui est différente de la justice conventionnelle établie par les lois et les coutumes.&lt;/p&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E64" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Posidonios&quot;  title=&quot; Wikipedia&quot;&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href=&quot;https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770&quot;  title=&quot;Posidonius d'Apamée théoricien de la géométrie par Persée&quot;&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href=&quot;https://www.youtube.com/watch?v=EqU-kD8dW4Y&quot; title=&quot;Grèce antique - 33 La civilisation hellénistique par Yannick Rub&quot;&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289&quot;  title=&quot;La philosophiede Posidonius par Persee&quot;&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; "/>
+    <hyperlink ref="E69" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que&quot; title=&quot; Wikipedia&quot;&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href=&quot;https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Le Stoïcisme par le Précepteur&quot;&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=J3wZoqElCgs&quot; title=&quot;Who is Seneca par Daily Stoic &quot;&gt; Sa philosophie &lt;/a&gt; est ancrée dans le stoïcisme : il prône la maîtrise des passions, la domination de la peur et des désirs, ainsi que la recherche de la tranquillité de l’âme (« tranquillitas animi »). Il insiste beaucoup sur la brièveté de la vie et sur l’idée qu’il faut apprendre à bien vivre plutôt qu’à accumuler les biens, ce qui a inspiré de nombreux penseurs ultérieurs, de Montaigne aux moralistes modernes. Sa pensée met l'accent sur l'importance de la raison et de l'autodiscipline pour atteindre un état d'équilibre émotionnel et mental, que les émotions négatives telles que la colère, la peur et la tristesse sont des perturbations de la raison qui peuvent être surmontées par une pratique constante de la vertu et de la sagesse afin d'avoir  &lt;a href=&quot;https://www.youtube.com/watch?v=B7FVZUWL6II&amp;ab_channel=KarlBaudoin&quot; title=&quot;La vie Heureuse par Karl Baudoin&quot;&gt; &quot;une vie heureuse&quot;.&lt;/a&gt; &lt;/p&gt; &lt;p&gt;Parmi ses traités les plus célèbres, on retient notamment : - De la brièveté de la vie (consideration sur l’usage du temps). - De la colère (sur la maîtrise de cette passion destructive). - De la tranquillité de l’âme et De la vie heureuse (sur la condition du sage et du bonheur intérieur). On lui doit aussi les Lettres à Lucilius, une vaste correspondance philosophique qui mêle conseils pratiques et réflexions sur la morale, très lue au XVIIᵉ siècle et dans la culture moderne. &lt;/p&gt; &lt;p&gt;  est aussi un dramaturge important : il a composé des tragédies comme Médée, Phèdre, Thyeste ou Les Troyennes, qui, très inspirées de tragédies grecques, ont profondément influencé le théâtre classique français (Corneille, Racine, etc.). Son style est souvent plus théâtral et sombre que celui des auteurs grecs, avec de longs monologues et une forte charge psychologique, ce qui en fait un pont entre la tragédie antique et le théâtre moderne. &lt;/p&gt; &lt;p&gt; Il a &lt;a href=&quot;https://www.youtube.com/watch?v=d_cge9OwVAs&quot; title=&quot;La vie philosophique de Sénèque par Kosmos&quot;&gt; enseigné que la vie &lt;/a&gt; humaine était un processus continu d'apprentissage et de développement et que la poursuite de la sagesse était une quête permanente. &lt;/p&gt;     &lt;audio controls title=&quot;Les lettres à Lucilius – Senèque  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-06.01.2014-ITEMA_20570995-2014C12410S0006-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="E70" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_d%27Ath%C3%A8nes&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;AMMONIOS d'Athènes&lt;/a&gt; était un philosophe platonicien originaire d'Égypte, qui enseigna à Athènes et fut l'un des maîtres de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Plutarque&quot; style=&quot;color:#6A142A&quot; title=&quot;Plutarque sur Wikipedia&quot;&gt;Plutarque&lt;/a&gt;. Représentant du médio-platonisme, il cherchait à concilier la philosophie de Platon avec d'autres courants de pensée de l'Antiquité tardive.&lt;/p&gt; &lt;p&gt;Son enseignement oral laissa une empreinte durable sur ses disciples, bien qu'il n'ait laissé aucun écrit. Il défendait une lecture spirituelle et morale du platonisme, insistant sur la contemplation du Bien et la purification de l'âme. Plutarque, son élève le plus illustre, rapporte ses enseignements dans ses &lt;em&gt;Moralia&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Ammonios d'Athènes appartient à ce courant de platoniciens qui, entre Platon et Plotin, ont préparé le terrain au &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;, en développant une exégèse du &lt;em&gt;Timée&lt;/em&gt; et de la &lt;em&gt;République&lt;/em&gt;. Sa discrétion littéraire contraste avec l'influence considérable qu'il exerça sur le cercle intellectuel d'Athènes de son époque.&lt;/p&gt;"/>
+    <hyperlink ref="H80" r:id="rId15" display="https://www.laphilo.fr/pho/jamblique-mini.webp"/>
+    <hyperlink ref="H87" r:id="rId16" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="H88" r:id="rId17" display="https://www.laphilo.fr/pho/scyrene-mini.webp"/>
+    <hyperlink ref="E89" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot;   title=&quot;Proclus par Wikipédia&quot;&gt; PROCLUS&lt;/a&gt; était un philosophe &lt;a href=&quot;https://www.youtube.com/watch?v=E70txcPRDmk&amp;t=330s&amp;ab_channel=R%C3%A9sonance%5Bs%5D&quot;   title=&quot;Le Néoplatonisme par Anne Baudart&quot;&gt; Néoplatonicien grec&lt;/a&gt; et il est considéré comme l'un des derniers grands philosophes de l'Antiquité classique.&lt;/p&gt;&#10;&lt;p&gt; Sa philosophie est basée sur les enseignements de Platon et d'Aristote. Il a développé une théorie complexe de l'univers qui est basée sur l'idée d'une hiérarchie de réalités. Au sommet de cette hiérarchie se trouve l'Un, qui est la réalité ultime et incompréhensible. Voici les principaux concepts de la philosophie de Proclus :&lt;/p&gt;&#10;&lt;dd&gt;L'Un : Réalité ultime et incompréhensible, qui est la source de toutes choses.&lt;/dd&gt;&#10;&lt;dd&gt;Le Démiurge : Force créatrice qui a donné forme à l'univers.&lt;/dd&gt;&#10;&lt;dd&gt;Les dieux : Intermédiaires entre l'Un et le monde sensible.&lt;/dd&gt;&#10;&lt;dd&gt;Les âmes : Principes vitaux qui animent les êtres vivants.&lt;/dd&gt;&#10;&lt;dd&gt;La matière : Réalité la plus basse de la hiérarchie, source du changement et de la corruption.&lt;/dd&gt;&#10;&lt;p&gt; Il a écrit un grand nombre &lt;a href=&quot;https://remacle.org/bloodwolf/philosophes/proclus/table.htm&quot;   title=&quot;Proclus par Philippe Remacle&quot;&gt; d'ouvrages sur la philosophie&lt;/a&gt;, dont les plus importants sont &lt;a href=&quot;https://www.youtube.com/watch?v=SJK1kbyXXno&quot;   title=&quot;Les éléments de Théologie de Proclus par LabEx HaStec&quot;&gt; les Commentaires sur le Timée de Platon&lt;/a&gt;, les Éléments de théologie et les Hypotyposes platonicae. Ces ouvrages ont été d'une grande influence sur la philosophie occidentale, et ils continuent à être étudiés aujourd'hui. &lt;/p&gt;   &lt;audio controls title=&quot; Proclus, un philosophe étoilé par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/24469-21.02.2025-ITEMA_24036318-2025C51809S0052-NET_MFC_F489C5B4-00F4-4AC5-897E-962A7323BFBA-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;"/>
+    <hyperlink ref="E90" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hermias_d%27Alexandrie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;HERMIAS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien, élève du grand &lt;a href=&quot;https://fr.wikipedia.org/wiki/Syrianos&quot; title=&quot;Syrianus sur Wikipedia&quot;&gt;Syrianus&lt;/a&gt; à Athènes. De retour à Alexandrie, il y fonda une école philosophique et épousa Aidésia, dont il eut pour fils le célèbre Ammonios d'Alexandrie.&lt;/p&gt; &lt;p&gt;Son œuvre principale est un commentaire du &lt;em&gt;Phèdre&lt;/em&gt; de Platon, rédigé à partir des notes prises lors des cours de Syrianus. Cet ouvrage, qui nous est parvenu, offre une interprétation allégorique et métaphysique du dialogue platonicien sur l'amour, l'âme et la beauté, dans la tradition néoplatonicienne.&lt;/p&gt; &lt;p&gt;Hermias s'inscrit dans la lignée des maîtres qui firent d'Alexandrie un foyer majeur de la pensée antique tardive. Son rôle de transmetteur entre l'école d'Athènes et celle d'Alexandrie fut déterminant pour la pérennité du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt;. Sa mort prématurée laissa Aidésia seule pour assurer l'avenir philosophique de leurs fils.&lt;/p&gt;"/>
+    <hyperlink ref="H92" r:id="rId20" display="https://www.laphilo.fr/pho/damascios-mini.webp"/>
+    <hyperlink ref="E93" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;AMMONIOS d'Alexandrie&lt;/a&gt; était un philosophe néoplatonicien de la fin de l'Antiquité, fils d'Hermias et d'Aidésia, tous deux philosophes. Il succéda à Proclos comme tête de l'école néoplatonicienne d'Athènes et dirigea l'école alexandrine, formant une génération de commentateurs d'Aristote comme Olympiodore, Jean Philopon ou Simplicius, dans un contexte de tensions entre païens et chrétiens. Il enseigna l'Aristote aux païens et le Platon aux chrétiens pour favoriser une harmonie entre doctrines. &lt;/p&gt; &lt;p&gt; Spécialiste des commentaires d'Aristote, il défendit une interprétation néoplatonicienne unifiant Aristote et Platon : Aristote prépare à Platon, l'âme s'élève de la matière à l'Intellect divin. Ses écrits, perdus sauf fragments, insistent sur la théurgie et l'exégèse allégorique.&lt;/p&gt; &lt;p&gt; Son école alexandrine préserva le corpus aristotélicien pour l'Islam et l'Occident médiéval. &lt;/p&gt; Aucun texte complet ne survit directement, mais ses leçons sont préservées via les commentaires de ses élèves, comme ceux de Philopon sur l'Isagogè. Il chercha à harmoniser les deux grands penseurs antiques pour préserver la tradition païenne face au christianisme dominant.https://www.ljallamion.fr/spip.php?article6169 &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E94" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isidore_de_Gaza&quot; title=&quot;Wikipedia&quot;&gt;ISIDORE de Gaza&lt;/a&gt; était un philosophe néoplatonicien, né à Gaza en Palestine. Maître de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Damascios&quot; title=&quot;Damascios sur Wikipedia&quot;&gt;Damascios&lt;/a&gt;, le dernier scholarque de l'Académie d'Athènes, il fut l'un des derniers grands représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot;  title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique.&lt;/p&gt; &lt;p&gt;Damascios lui consacra une biographie dans sa &lt;em&gt;Vie d'Isidore&lt;/em&gt; (aussi connue sous le nom de &lt;em&gt;Vie des philosophes&lt;/em&gt;), où il le dépeint comme un personnage d'une grande intégrité morale, attaché aux traditions philosophiques grecques et à la piété envers les dieux, dans un contexte où le christianisme triomphait. Isidore représentait une philosophie vécue comme exercice spirituel, alliant rigueur intellectuelle et pratique ascétique.&lt;/p&gt; &lt;p&gt;Sa pensée s'inscrit dans la grande tradition de l'école néoplatonicienne d'Athènes, héritière de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Proclus&quot; title=&quot;Proclus sur Wikipedia&quot;&gt;Proclus&lt;/a&gt;. Il incarne ces penseurs de la fin du paganisme grec qui, face à la montée de la chrétienté, s'accrochaient à la philosophie comme à une forme de spiritualité rationnelle et contemplative, gardienne de l'héritage intellectuel de la Grèce.&lt;/p&gt;"/>
+    <hyperlink ref="H94" r:id="rId23" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="H97" r:id="rId24" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="E98" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Simplicius_(philosophe)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;SIMPLICIUS de Cilicie&lt;/a&gt; était un philosophe néoplatonicien grec de l’Antiquité tardive ou  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1991_num_89_83_6698&quot; style=&quot;color:#88A1E9&quot; title=&quot;A propos de la biographie de Simplicius par Persée&quot;&gt;sa pensée&lt;/a&gt; joue un rôle clé dans la transmission de la philosophie grecque classique vers le monde byzantin, arabe et latin. &lt;/p&gt; &lt;p&gt; Connu pour ses commentaires sur plusieurs œuvres d’Aristote : Catégories, Physique et Du ciel, auxquels s’ajoute un commentaire sur le &quot;Manuel d’Épictète&quot; et, selon la tradition, sur &quot;De l’âme&quot;. Ces commentaires sont volumineux et cherchent moins à proposer un &lt;a href=&quot;https://www.youtube.com/watch?v=C17VYcyLkiY&quot; style=&quot;color:#88A1E9&quot; title=&quot;SIMPLICIUS | Developing Critical Thinking Skills | The Last Great Philosopher of the Ancient World par Timeless Questions&quot;&gt;“système personnel”&lt;/a&gt; qu’à expliquer, harmoniser et défendre Aristote dans une perspective néoplatonicienne. Ils contiennent aussi de nombreux extraits et rapports d’auteurs plus anciens (présocratiques, stoïciens, péripatéticiens), ce qui en fait une source précieuse pour l’histoire de la philosophie. &lt;/p&gt; &lt;p&gt; Néoplatonicien, il cherche à montrer la concorde profonde entre Platon et Aristote, qu’il considère comme deux expressions complémentaires d’une même vérité. Dans ses commentaires à la Physique, il défend par exemple la thèse de l’éternité du monde contre Jean Philopon, en s’appuyant à la fois sur Aristote et une lecture platonicienne non créationniste du Timée. Il intègre aussi des thèmes théologiques néoplatoniciens (hiérarchie des principes, intellect en acte, providence) pour interpréter la “métaphysique” aristotélicienne comme une véritable théologie première.&lt;/p&gt; &lt;p&gt; Ses œuvres seront très appréciées dans les traditions aristotéliciennes postérieures, notamment parce qu’elles offrent une synthèse de la philosophie tardo-antique et sauvent de l’oubli des doctrines anciennes.  &lt;a href=&quot;https://www.youtube.com/watch?v=6a4uQpmGsUg&quot; style=&quot;color:#88A1E9&quot; title=&quot;Simplicius – The Last Guardian of Ancient Philosophy par A time in history&quot;&gt; Transmis et traduits&lt;/a&gt; dans le monde arabo-musulman, puis redécouverts en Occident latin, ses commentaires contribuent à façonner la manière dont Aristote, Platon et le néoplatonisme seront compris au Moyen Âge. Aujourd’hui encore, ses textes servent de source majeure pour reconstituer la pensée de nombreux philosophes dont les œuvres originales sont perdues. &lt;/p&gt; "/>
+    <hyperlink ref="E101" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Priscien_de_Lydie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;PRISCIEN de Lydie&lt;/a&gt; était un philosophe néoplatonicien, disciple de Damascios et membre du cercle des derniers philosophes de l'Académie d'Athènes. Après la fermeture de celle-ci par l'édit de Justinien en 529, il s'exila en Perse avec Damascios et Simplicius, à la cour du roi sassanide Khosrô Ier.&lt;/p&gt; &lt;p&gt;Priscien est surtout connu pour ses &lt;em&gt;Solutions aux questions de Khosrô&lt;/em&gt; (&lt;em&gt;Solutiones ad Chosroem&lt;/em&gt;), un texte philosophique rédigé à la demande du roi de Perse, qui témoigne des échanges intellectuels entre la philosophie grecque et la cour perse. Il rédigea également un commentaire sur le &lt;em&gt;De Anima&lt;/em&gt; d'Aristote, s'inscrivant dans la &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_2014_num_2_1_6316&quot; title=&quot;la géographie et les originesnéoplatonisme sur Persee&quot;&gt;tradition néoplatonicienne &lt;/a&gt; d'harmonisation entre Aristote et Platon.&lt;/p&gt; &lt;p&gt;    Deux traités de Priscien ont traversé l’Antiquité :  - « Une Métaphrase de Théophraste » sur la perception des sens (ou Metaphrasis in Theophrastum), qui reprend et reformule la théorie aristotélicienne et théophrastique de la perception sensorielle en la reliant à la tradition platonicienne. - « Les Réponses à Chosroès » (Solutiones ad Chosroem), un recueil de questions philosophiques posées par le roi perse et de réponses données par Priscien, conservé seulement dans une traduction latine tardive et corrompue.     &lt;/p&gt; &lt;p&gt;Son œuvre illustre la mobilité des philosophes néoplatoniciens tardifs et la façon dont la pensée grecque se transmit à l'Orient. Priscien fait partie de ces passeurs discrets dont le rôle fut essentiel pour la survie du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et sa transmission ultérieure à l'Islam et à l'Occident médiéval.&lt;/p&gt; &lt;p&gt; Dans sa Métaphrase de Théophraste, Priscien s’inscrit dans une tendance néoplatonicienne qui cherche à articuler la psychologie aristotélicienne avec des thèmes platoniciens (notamment sur l’âme, les facultés et le processus cognitif). Les Réponses à Chosroès le montrent comme un philosophe assez sophistiqué, capable de répondre à des questions métaphysiques et cosmologiques dans un cadre à la fois philosophique et politique. &lt;/p&gt;"/>
+    <hyperlink ref="E103" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eulamios_de_Phrygie&quot; style=&quot;color:#6A142A&quot; title=&quot;Wikipedia&quot;&gt;EULAMIOS de Phrygie&lt;/a&gt; était un philosophe néoplatonicien du VIe siècle, originaire de Phrygie en Asie Mineure (actuelle Turquie). Il appartient au cercle des derniers représentants du &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; style=&quot;color:#6A142A&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; antique, dont il perpétua la tradition après la fermeture de l'Académie d'Athènes par Justinien en 529.&lt;/p&gt; &lt;p&gt;Figure peu documentée de cette période de transition, il s'inscrit dans le mouvement de philosophes néoplatoniciens qui, après l'exil perse et la dispersion de l'école athénienne, continuèrent à enseigner et transmettre la philosophie grecque en dehors des institutions officielles. Ses liens avec les cercles de Damascios et Simplicius laissent penser qu'il participa à la préservation du corpus philosophique antique.&lt;/p&gt; &lt;p&gt;Eulamios représente la philosophie de survie du néoplatonisme face à la christianisation de l'Empire. Comme ses contemporains, il incarne la volonté de maintenir vivante une tradition intellectuelle millénaire, préservant ainsi les conditions de la redécouverte médiévale et renaissante de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_antique&quot; style=&quot;color:#6A142A&quot; title=&quot;Philosophie antique sur Wikipedia&quot;&gt;philosophie antique&lt;/a&gt;.&lt;/p&gt;"/>
+    <hyperlink ref="H103" r:id="rId28" display="https://www.laphilo.fr/photo/logo.webp"/>
+    <hyperlink ref="E104" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Ph%C3%A9nicie&quot; title=&quot;Wikipedia&quot;&gt;DIOGÈNE de Phénicie&lt;/a&gt; était un philosophe néoplatonicien, distinct de son homonyme Hermias d'Alexandrie. Originaire de Phénicie, il s'inscrit dans la tradition de l'école néoplatonicienne tardive qui cherchait à préserver et transmettre l'héritage philosophique grec face à la montée du christianisme.&lt;/p&gt; &lt;p&gt;  Comme Damascios, Simplicios de Cilicie, Eulamios de Phrygie, Priscien de Lydie, Hermias de Phénicie et Isidore de Gaza, Diogène de Phénicie fait partie des sept philosophes qui choisissent de s’exiler à la cour du roi sassanide Khosro Iᵉʳ (Chosroès) en Perse. En 532, ils s’installent à Harrân, en Mésopotamie, où ils continuent une activité philosophique dans un cadre plus tolérant que celui de l’Empire romain d’Orient chrétien. &lt;/p&gt; &lt;p&gt;  On ne connaît pas directement d’œuvres écrites de lui, et il est surtout connu par le récit de l’historien Agathias, qui décrit ce groupe de philosophes comme « la fleur la plus noble de la philosophie de leur temps ». Son importance est donc surtout historique : il incarne la dernière génération de la philosophie païenne néoplatonicienne, dont l’exil en Perse constitue un maillon dans la transmission de la pensée grecque vers le monde iranien et, plus tard, islamique.https://fr.wikipedia.org/wiki/Diogène_de_Phénicie    &lt;/p&gt;&lt;p&gt;Il s'inscrit dans un courant qui s'efforçait de concilier &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme&quot; title=&quot;Néoplatonisme sur Wikipedia&quot;&gt;néoplatonisme&lt;/a&gt; et traditions religieuses orientales, explorant les rapports entre philosophie grecque, théurgie et spiritualité. Comme nombre de ses contemporains, il fut confronté au basculement culturel majeur que représenta la fermeture de l'Académie par Justinien en 529.&lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -7683,7 +7683,7 @@
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)"  style="color:#6A142A"  title=" Wikipedia"&gt;AMMONIOS d’Alexandrie&lt;/a&gt; (vers 440-vers 520) est un philosophe néoplatonicien, le grand maître de l’école d’Alexandrie à la fin de l’Antiquité. Fils des philosophes Hermias et Aidésia, il est emmené jeune à Athènes par sa mère pour y suivre l’enseignement de Proclus, qui dirige l’école platonicienne. Revenu dans sa ville natale, il y enseigne pendant plusieurs décennies, à la tête de l’école d’Alexandrie, tandis que celle d’Athènes est dirigée par les successeurs de Proclus.&lt;/p&gt; &lt;p&gt;Ammonios est avant tout un commentateur d’Aristote. Il considère que la philosophie d’Aristote et celle de Platon s’accordent sur l’essentiel : l’étude d’Aristote, à commencer par sa logique, prépare à celle de Platon, qui conduit jusqu’à la connaissance du divin. Son commentaire du traité &lt;em&gt;De l’interprétation&lt;/em&gt;, qui examine les propositions, la vérité et le temps, nous est parvenu en entier ; on y trouve une discussion célèbre sur les futurs contingents : peut-on dire dès aujourd’hui qu’une bataille navale aura lieu demain, sans supprimer la liberté ? Ses autres leçons nous sont connues par les notes de ses élèves. Il forme en effet toute une génération de commentateurs : Jean Philopon, chrétien, Simplicius, Asclépius et Olympiodore. Dans une ville où les chrétiens sont désormais majoritaires et où les païens sont parfois persécutés, il aurait conclu un accord avec les autorités chrétiennes pour pouvoir continuer à enseigner, ce que lui reprocha Damascius.&lt;/p&gt; &lt;p&gt;L’école d’Alexandrie, en partie chrétienne après lui, a transmis le corpus d’Aristote et ses commentaires aux savants syriaques et arabes, puis à l’Occident médiéval.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ammonios_(fils_d%27Hermias)" style="color:#6A142A" title=" Wikipedia"&gt;AMMONIOS d’Alexandrie&lt;/a&gt; (vers 440-vers 520) est un philosophe néoplatonicien, le grand maître de l’école d’Alexandrie à la fin de l’Antiquité. Fils des philosophes Hermias et Aidésia, il est emmené jeune à Athènes par sa mère pour y suivre l’enseignement de Proclus, qui dirige l’école platonicienne. Revenu dans sa ville natale, il y enseigne pendant plusieurs décennies, à la tête de l’école d’Alexandrie, tandis que celle d’Athènes est dirigée par les successeurs de Proclus.&lt;/p&gt; &lt;p&gt;Il est avant tout un commentateur d’Aristote. Il considère que la philosophie d’Aristote et celle de Platon s’accordent sur l’essentiel : l’étude d’Aristote, à commencer par sa logique, prépare à celle de Platon, qui conduit jusqu’à la connaissance du divin. Son commentaire du &lt;a href="https://www.thomas-d-aquin.com/documents/files/Interpretation.pdf" title="Traité de l'Interpretation par thomas "&gt;traité &lt;em&gt;De l’interprétation&lt;/em&gt;&lt;/a&gt;, qui examine les propositions, la vérité et le temps, nous est parvenu en entier ; on y trouve une discussion célèbre sur les futurs contingents : peut-on dire dès aujourd’hui qu’une bataille navale aura lieu demain, sans supprimer la liberté ? Ses autres leçons nous sont connues par les notes de ses élèves. Il forme en effet toute une génération de commentateurs : Jean Philopon, chrétien, Simplicius, Asclépius et Olympiodore. Dans une ville où les chrétiens sont désormais majoritaires et où les païens sont parfois persécutés, il aurait conclu un accord avec les autorités chrétiennes pour pouvoir continuer à enseigner, ce que lui reprocha Damascius.&lt;/p&gt; &lt;p&gt;L’école d’Alexandrie, en partie chrétienne après lui, a transmis le corpus d’Aristote et ses commentaires aux savants syriaques et arabes, puis à l’Occident médiéval.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F93" s="7" t="s">

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3227,7 +3227,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:P114"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="6.39"/>
@@ -8230,6 +8230,570 @@
       <c r="P104">
         <v>2</v>
       </c>
+    </row>
+    <row r="105" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="7">
+        <v>160</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 160 – vers 220</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERTULLIEN</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tertullien" title=" Wikipedia"&gt;TERTULLIEN&lt;/a&gt; est un écrivain et théologien chrétien de langue latine. Né à &lt;a href="https://fr.wikipedia.org/wiki/Carthage" title=" Wikipedia"&gt;Carthage&lt;/a&gt; vers 160, dans une famille païenne, il reçoit une solide formation de rhéteur et connaît bien le droit. Il se convertit au christianisme vers 195 et met dès lors son talent de polémiste au service de sa nouvelle foi. Il est le premier grand auteur chrétien d’Occident à écrire en latin, et son style brillant, nerveux et souvent ironique, a marqué toute la littérature chrétienne.&lt;/p&gt; &lt;p&gt;Dans l’&lt;em&gt;Apologétique&lt;/em&gt; (197), il défend les chrétiens persécutés devant les magistrats romains : ils sont de loyaux sujets, et les persécutions ne font que les multiplier, car « le sang des chrétiens est une semence ». Il combat aussi les hérétiques, notamment les gnostiques et Marcion. Contre ceux qui mêlent la foi et la philosophie grecque, il lance sa célèbre question : « Qu’y a-t-il de commun entre Athènes et Jérusalem ? » La foi n’a pas besoin des philosophes. On lui prête à tort la formule « Je crois parce que c’est absurde », mais il écrit bien, de la résurrection du Christ : « c’est certain, parce que c’est impossible ».&lt;/p&gt; &lt;p&gt;Il forge une grande partie du vocabulaire théologique latin. Le premier, il emploie le mot « Trinité » et la formule « une seule substance, trois personnes », qui sera reprise par l’Église. Vers 207, attiré par la rigueur morale des montanistes, qui attendent une nouvelle révélation de l’Esprit, il rompt avec l’Église. Il meurt vers 220. Il a profondément influencé saint Cyprien et saint Augustin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tertullien-mini.webp</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Romaine</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain chrétien de Carthage, premier grand théologien de langue latine, pour qui la foi n’a rien à attendre d’Athènes.</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="7">
+        <v>185</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 185 – vers 253</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORIGÈNE</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Orig%C3%A8ne" title=" Wikipedia"&gt;ORIGÈNE&lt;/a&gt; est un théologien et philosophe chrétien, le plus grand penseur de l’Église grecque avant le IVe siècle. Né vers 185 à &lt;a href="https://fr.wikipedia.org/wiki/Alexandrie" title=" Wikipedia"&gt;Alexandrie&lt;/a&gt;, il voit son père mourir martyr en 202. Très jeune, il dirige l’école chrétienne de la ville, mène une vie d’ascète et suit probablement les leçons d’Ammonios Saccas, qui fut aussi le maître de Plotin. En conflit avec son évêque, il s’installe vers 231 à Césarée, en Palestine, où il fonde une école réputée.&lt;/p&gt; &lt;p&gt;Il consacre sa vie à la Bible. Dans les &lt;em&gt;Hexaples&lt;/em&gt;, il dispose en six colonnes le texte hébreu et plusieurs traductions grecques de l’Ancien Testament : c’est la première grande entreprise de critique textuelle. Il distingue dans l’Écriture, comme dans l’homme, trois niveaux, le corps, l’âme et l’esprit : sous le sens littéral se cachent un sens moral et un sens spirituel, que l’on atteint par l’interprétation allégorique. Dans le &lt;em&gt;Contre Celse&lt;/em&gt;, il répond au premier grand adversaire païen du christianisme.&lt;/p&gt; &lt;p&gt;Dans le &lt;em&gt;Traité des principes&lt;/em&gt;, il construit la première grande synthèse de la foi chrétienne, nourrie de &lt;a href="https://fr.wikipedia.org/wiki/Platonisme" title=" Wikipedia"&gt;platonisme&lt;/a&gt;. Toutes les âmes existaient avant leur naissance, et c’est en se détournant de Dieu qu’elles sont tombées dans les corps. Les peines ne sont pas éternelles : à la fin des temps, toutes les créatures pourraient être sauvées et revenir à Dieu, c’est l’« apocatastase ». Torturé pendant la persécution de Dèce, il meurt vers 253. Certaines de ses thèses sont condamnées par l’Église en 553.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/origene-mini.webp</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Égyptienne</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique ; Platonisme</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">théologien chrétien d’Alexandrie, maître de la lecture spirituelle des Écritures et penseur du salut universel.</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="7">
+        <v>120</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 120 – après 180</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCIEN de Samosate</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lucien_de_Samosate" title=" Wikipedia"&gt;LUCIEN de Samosate&lt;/a&gt; est un écrivain satirique de langue grecque. Né vers 120 à Samosate, en Commagène, sur les bords de l’Euphrate, il est d’origine syrienne. Placé en apprentissage chez un oncle sculpteur, il s’enfuit pour étudier la rhétorique, puis parcourt l’Asie Mineure, la Grèce, l’Italie et la Gaule comme conférencier. Vers quarante ans, il se tourne vers la philosophie et s’installe à Athènes. À la fin de sa vie, il occupe une charge administrative en Égypte. Il meurt après 180.&lt;/p&gt; &lt;p&gt;Il laisse quelque quatre-vingts œuvres, souvent sous forme de dialogues comiques. Il se moque des dieux de l’Olympe, de la superstition et des philosophes qui ne vivent pas selon leurs principes. Dans &lt;em&gt;Les Vies des philosophes à l’encan&lt;/em&gt;, Zeus vend aux enchères Pythagore, Diogène ou Socrate comme des esclaves. Dans l’&lt;em&gt;Hermotime&lt;/em&gt;, il montre qu’une vie entière ne suffirait pas à examiner toutes les écoles avant d’en choisir une. Dans les &lt;em&gt;Dialogues des morts&lt;/em&gt;, le cynique Ménippe rit des riches et des puissants devenus de simples squelettes.&lt;/p&gt; &lt;p&gt;Il dénonce aussi les charlatans : dans &lt;em&gt;Alexandre ou le faux prophète&lt;/em&gt;, il démasque un escroc qui fonde un culte autour d’un serpent. Son &lt;em&gt;Histoire véritable&lt;/em&gt;, récit parodique d’un voyage jusqu’à la Lune, est parfois vue comme le premier roman de science-fiction. Proche du &lt;a href="https://fr.wikipedia.org/wiki/Scepticisme_%28philosophie%29" title=" Wikipedia"&gt;scepticisme&lt;/a&gt; et des cyniques, il admire Épicure. Traduit par Érasme et Thomas More, il a inspiré Rabelais, Swift et Voltaire.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/lucien-mini.webp</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Syrienne</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scepticisme ; Cynisme</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain satirique de langue grecque, moqueur des philosophes, des dieux et des charlatans.</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P107"/>
+    </row>
+    <row r="108" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="7">
+        <v>125</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 125 – après 170</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APULÉE</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apul%C3%A9e" title=" Wikipedia"&gt;APULÉE&lt;/a&gt; est un écrivain et philosophe de langue latine. Né vers 125 à Madaure, en Numidie, dans l’actuelle Algérie, fils d’un notable, il étudie à Carthage, puis à Athènes, où il découvre la philosophie de Platon, et à Rome. Grand voyageur, curieux de tout, il se fait initier à plusieurs cultes à mystères, notamment celui d’Isis. Il se présente lui-même comme un « philosophe platonicien », et sa célébrité de conférencier est immense en Afrique romaine. On perd sa trace après 170.&lt;/p&gt; &lt;p&gt;Vers 158, il épouse à Oea, l’actuelle Tripoli, une riche veuve, Pudentilla. La famille de celle-ci l’accuse d’avoir usé de magie pour la séduire. Il se défend lui-même devant le proconsul, et son &lt;em&gt;Apologie&lt;/em&gt;, brillante et ironique, est la seule plaidoirie de l’Antiquité romaine impériale qui nous soit parvenue. Son chef-d’œuvre, &lt;em&gt;Les Métamorphoses&lt;/em&gt;, appelé aussi &lt;em&gt;L’Âne d’or&lt;/em&gt;, est le seul roman latin conservé en entier : le jeune Lucius, changé en âne par curiosité pour la magie, traverse mille aventures avant d’être sauvé par la déesse Isis. On y lit le célèbre conte d’Amour et Psyché.&lt;/p&gt; &lt;p&gt;Dans ses œuvres philosophiques, il expose la doctrine de Platon et développe une théorie des démons : dans &lt;em&gt;Le Dieu de Socrate&lt;/em&gt;, ces êtres intermédiaires relient les hommes aux dieux, trop lointains pour intervenir eux-mêmes ; le « démon » de Socrate, cette voix intérieure qui le détournait de mal agir, en serait un. Saint Augustin, son compatriote, critiquera cette doctrine dans &lt;em&gt;La Cité de Dieu&lt;/em&gt;. Apulée a aussi transmis au Moyen Âge une part de la pensée de Platon.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/apulee-mini.webp</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Romaine</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platonisme</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain et philosophe platonicien de Numidie, auteur de L’Âne d’or et d’une théorie des démons.</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P108"/>
+    </row>
+    <row r="109" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="7">
+        <v>-470</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-385</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 470 A JC - vers 385 A JC</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PHILOLAOS de Crotone</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philolaos_de_Crotone" title=" Wikipedia"&gt;PHILOLAOS de Crotone&lt;/a&gt; est un philosophe grec de l’école de &lt;a href="https://fr.wikipedia.org/wiki/Pythagore" title=" Wikipedia"&gt;Pythagore&lt;/a&gt;, contemporain de Socrate. Né vers 470 avant notre ère à Crotone, en Italie du Sud, il doit fuir les persécutions dont sont victimes les pythagoriciens et s’installe un temps à Thèbes, où il a pour élèves Simmias et Cébès, les deux interlocuteurs de Socrate dans le &lt;em&gt;Phédon&lt;/em&gt; de Platon. Il est le premier pythagoricien à mettre par écrit les doctrines de l’école, jusque-là tenues secrètes. Selon une tradition, Platon aurait acheté son livre très cher. Il meurt vers 385.&lt;/p&gt; &lt;p&gt;Il ne reste de son livre &lt;em&gt;Sur la nature&lt;/em&gt; que quelques fragments. Le monde y est composé de deux sortes de choses : les « illimitées », comme les matières, et les « limitantes », comme les formes. Elles ne peuvent former un tout ordonné que si une « harmonie » les accorde, selon les rapports numériques que l’on trouve dans les intervalles de la musique. « Tout ce qui est connu a un nombre, car sans lui il n’est pas possible de rien penser ni de rien connaître. » Le nombre est ce qui rend le monde intelligible.&lt;/p&gt; &lt;p&gt;Il propose aussi un système du monde audacieux : la Terre n’est pas au centre de l’univers. Au centre se trouve un « feu central », autour duquel tournent une « anti-Terre » invisible, la Terre, la Lune, le Soleil, les planètes et les étoiles. Copernic citera cette doctrine comme un précédent à la sienne. On lui attribue aussi l’idée que l’âme est enfermée dans le corps comme dans une prison, en punition d’une faute.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/philolaos-mini.webp</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pythagorisme ; Présocratique</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe pythagoricien grec, pour qui tout ce qui est connu a un nombre, et qui ôta la Terre du centre du monde.</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P109"/>
+    </row>
+    <row r="110" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="7">
+        <v>-435</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-350</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 435 A JC - vers 350 A JC</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHYTAS de Tarente</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Archytas_de_Tarente" title=" Wikipedia"&gt;ARCHYTAS de Tarente&lt;/a&gt; est un philosophe, mathématicien et homme d’État grec de l’école de Pythagore. Né vers 435 avant notre ère à Tarente, une riche cité grecque d’Italie du Sud, il en est élu stratège, le premier magistrat, sept années de suite, et ne connaît jamais la défaite à la tête de ses armées. Ami de Platon, il le fait sauver en 361 de la cour de Denys de Syracuse, qui le retenait prisonnier, en envoyant un navire le chercher. Selon une tradition rapportée par le poète Horace, il meurt dans un naufrage, vers 350.&lt;/p&gt; &lt;p&gt;Mathématicien de génie, il résout le problème de la duplication du cube, qui consiste à construire un cube de volume double d’un cube donné, par une construction dans l’espace d’une grande ingéniosité. Il développe la théorie musicale des pythagoriciens et nomme la « moyenne harmonique ». On le dit aussi fondateur de la mécanique, et la légende lui attribue une colombe de bois capable de voler. Pour lui, les sciences sont sœurs : l’arithmétique, la géométrie, l’astronomie et la musique étudient les mêmes nombres.&lt;/p&gt; &lt;p&gt;Il pense que le calcul juste fonde la paix civile : quand on sait compter, on peut partager équitablement, et les riches comme les pauvres s’accordent. Il est connu pour un argument sur l’infini : si je me tiens à la limite de l’univers, puis-je tendre la main ou un bâton au-delà ? Si oui, il y a encore quelque chose au-delà ; sinon, quelque chose m’arrête. L’univers est donc sans limite.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/archytas-mini.webp</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; politique</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pythagorisme</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe pythagoricien, mathématicien et homme d’État grec, ami de Platon.</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P110"/>
+    </row>
+    <row r="111" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="7">
+        <v>-465</v>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-395</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 465 A JC - vers 395 A JC</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRODICOS de Céos</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Prodicos_de_C%C3%A9os" title=" Wikipedia"&gt;PRODICOS de Céos&lt;/a&gt; est un sophiste grec, contemporain de Socrate. Né vers 465 avant notre ère dans l’île de Céos, il vient souvent à Athènes comme ambassadeur de sa cité et y donne des leçons très recherchées, et très chères. Socrate, chez Platon, se dit parfois son élève, en plaisantant : il aurait suivi sa leçon à une drachme, faute de pouvoir payer celle à cinquante. Platon le dépeint malade, emmitouflé dans des couvertures, la voix si grave qu’elle résonne dans la pièce. Il meurt après 399.&lt;/p&gt; &lt;p&gt;Il est célèbre pour son art de distinguer les synonymes, c’est-à-dire les mots de sens voisin, comme « discuter » et « se disputer », ou « se réjouir » et « prendre plaisir ». Il pense que bien employer les mots est la condition pour bien penser. Cette attention au langage annonce celle de Socrate, qui cherche à définir exactement les notions. Xénophon a conservé l’une de ses leçons, le « choix d’Héraclès » : à la croisée des chemins, le jeune Héraclès rencontre deux femmes, la Vertu et le Vice. Le Vice lui promet une vie facile et pleine de plaisirs, la Vertu une vie de travail et de gloire. Héraclès choisit la Vertu.&lt;/p&gt; &lt;p&gt;Il propose aussi une explication de l’origine des dieux : les premiers hommes ont divinisé ce qui leur était utile, le soleil, les rivières, le pain sous le nom de Déméter, le vin sous celui de Dionysos. Cette idée lui a valu d’être compté parmi les athées de l’Antiquité. Il est une figure importante du &lt;a href="https://fr.wikipedia.org/wiki/Sophiste" title=" Wikipedia"&gt;mouvement sophiste&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/prodicos-mini.webp</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langage ; ethique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sophisme</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sophiste grec, maître de la distinction des mots et auteur du « choix d’Héraclès » entre le vice et la vertu.</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P111"/>
+    </row>
+    <row r="112" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="7">
+        <v>-443</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-399</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 443 A JC - vers 399 A JC</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIPPIAS d'Élis</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hippias_d%27%C3%89lis" title=" Wikipedia"&gt;HIPPIAS d'Élis&lt;/a&gt; est un sophiste grec, contemporain de Socrate. Né vers 443 avant notre ère à Élis, la cité qui organisait les jeux Olympiques, il est souvent chargé d’ambassades par sa patrie. Il parcourt la Grèce en donnant des leçons et des conférences sur tous les sujets, et fait fortune. Platon lui consacre deux dialogues, l’&lt;em&gt;Hippias majeur&lt;/em&gt;, où Socrate lui demande ce qu’est le beau et n’obtient d’abord que des exemples, comme « une belle jeune fille », et l’&lt;em&gt;Hippias mineur&lt;/em&gt;, qui se demande si le menteur volontaire vaut mieux que l’involontaire.&lt;/p&gt; &lt;p&gt;Il est le modèle du savant universel. Il enseigne l’astronomie, la géométrie, la musique, la grammaire, la poésie, l’histoire et les arts de la mémoire. Il établit la liste des vainqueurs des jeux Olympiques, qui servira à dater les événements de l’histoire grecque. On lui attribue l’invention d’une courbe, la quadratrice, qui permet de diviser un angle en trois parties égales. À Olympie, il se vante de porter des vêtements, des chaussures et un anneau qu’il a tous faits lui-même : le sage doit se suffire à lui-même.&lt;/p&gt; &lt;p&gt;Chez Platon, il oppose la nature et la loi : « La loi, tyran des hommes, fait violence à la nature sur bien des points. » Les lois varient d’une cité à l’autre, mais par nature, tous les hommes sages sont parents, concitoyens et amis. Il annonce ainsi l’idée d’un droit naturel commun à tous. Il est l’un des grands représentants du &lt;a href="https://fr.wikipedia.org/wiki/Sophiste" title=" Wikipedia"&gt;mouvement sophiste&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hippias-mini.webp</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sophisme</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sophiste grec au savoir universel, qui opposa la nature à la loi, « tyran des hommes ».</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P112"/>
+    </row>
+    <row r="113" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="7">
+        <v>-335</v>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-269</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 335 A JC - vers 269 A JC</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STRATON de Lampsaque</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Straton_de_Lampsaque" title=" Wikipedia"&gt;STRATON de Lampsaque&lt;/a&gt; est un philosophe grec de l’école d’&lt;a href="https://fr.wikipedia.org/wiki/Aristote" title=" Wikipedia"&gt;Aristote&lt;/a&gt;, le Lycée. Né vers 335 avant notre ère à Lampsaque, sur les Dardanelles, il est l’élève de Théophraste. Il séjourne à Alexandrie, où il est le précepteur du futur roi Ptolémée II. Vers 287, il succède à Théophraste à la tête du Lycée, qu’il dirige pendant dix-huit ans. Il meurt vers 269. Il ne reste de ses nombreux ouvrages que des fragments et des témoignages.&lt;/p&gt; &lt;p&gt;On l’appelle « le Physicien », car il consacre l’essentiel de ses recherches à la nature. Il se sépare d’Aristote sur un point capital : il n’y a pas besoin d’un dieu, premier moteur, pour expliquer l’univers, ni de causes finales. La nature agit d’elle-même, par le chaud et le froid, par la pesanteur et le mouvement, sans intention ni but. Cicéron le résume ainsi : tout ce qui existe ou se produit est l’œuvre de la nature. Il est l’un des premiers penseurs du &lt;a href="https://fr.wikipedia.org/wiki/Naturalisme_%28philosophie%29" title=" Wikipedia"&gt;naturalisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Esprit expérimental, il admet que le vide existe dans les corps sous forme de petits interstices, ce qui explique que la lumière traverse l’eau ou que l’air se comprime. Il observe que les corps qui tombent accélèrent : un filet d’eau se divise en gouttes en tombant, et une pierre frappe plus fort si elle tombe de haut. Il place l’âme dans la tête et montre que la sensation suppose toujours la pensée. Ses idées inspireront les ingénieurs d’Alexandrie, comme Héron, qui étudieront les machines à air et à vapeur.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/straton-mini.webp</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aristotélisme ; Naturalisme</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe péripatéticien grec, surnommé « le Physicien », qui expliqua le monde par la seule nature.</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P113"/>
+    </row>
+    <row r="114" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="7">
+        <v>150</v>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IIe – IIIe siècle</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALEXANDRE d'Aphrodise</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexandre_d%27Aphrodise" title=" Wikipedia"&gt;ALEXANDRE d'Aphrodise&lt;/a&gt; est un philosophe grec qui vécut vers la fin du IIe et au début du IIIe siècle de notre ère. Né à Aphrodisias, en Carie, dans l’actuelle Turquie, il est nommé à Athènes, entre 198 et 209, à la chaire de philosophie aristotélicienne fondée par l’empereur Marc Aurèle. Il dédie aux empereurs Septime Sévère et Caracalla son traité &lt;em&gt;Du destin&lt;/em&gt;. On sait très peu de choses de sa vie, mais une partie importante de son œuvre nous est parvenue.&lt;/p&gt; &lt;p&gt;Il est le plus grand commentateur antique d’&lt;a href="https://fr.wikipedia.org/wiki/Aristote" title=" Wikipedia"&gt;Aristote&lt;/a&gt;, si bien qu’on l’a surnommé « l’Exégète ». Ses commentaires de la &lt;em&gt;Métaphysique&lt;/em&gt;, des &lt;em&gt;Premiers Analytiques&lt;/em&gt;, des &lt;em&gt;Topiques&lt;/em&gt; ou des &lt;em&gt;Météorologiques&lt;/em&gt; font autorité pendant des siècles. Dans son traité &lt;em&gt;De l’âme&lt;/em&gt;, il soutient que l’intellect humain n’est d’abord qu’une simple disposition du corps, qui naît et meurt avec lui. Il ne pense en acte que grâce à un « intellect agent » qui vient du dehors et n’est autre que Dieu, la cause première.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Du destin&lt;/em&gt;, il défend contre les stoïciens la liberté humaine et la contingence : tout n’est pas déterminé à l’avance, et certaines choses dépendent de nous. Il critique aussi leur théorie du mélange des corps. Sa doctrine de l’intellect a eu une immense influence sur les philosophes arabes, d’al-Kindi à Averroès, puis à la Renaissance, où les « alexandristes », comme Pomponazzi, soutiennent que l’âme est mortelle. Ses commentaires, traduits en arabe puis en latin, ont façonné pour longtemps la manière de lire Aristote.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/alexandreaphrodise-mini.webp</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aristotélisme</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe grec, le plus grand commentateur antique d’Aristote, surnommé « l’Exégète ».</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P114"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3227,7 +3227,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P114"/>
+  <dimension ref="A1:P119"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="6.39"/>
@@ -8794,6 +8794,290 @@
         </is>
       </c>
       <c r="P114"/>
+    </row>
+    <row r="115" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="7">
+        <v>329</v>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">379</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 329 – 379</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BASILE de Césarée</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Basile_de_C%C3%A9sar%C3%A9e" title=" Wikipedia"&gt;BASILE de Césarée&lt;/a&gt; est un évêque et théologien chrétien de langue grecque, l’un des trois « Pères cappadociens » avec son frère Grégoire de Nysse et son ami Grégoire de Nazianze. Né vers 329 à Césarée de Cappadoce, dans l’actuelle Turquie, dans une famille riche et très chrétienne, il étudie à Constantinople et à Athènes. Il renonce ensuite à une carrière brillante de rhéteur pour mener une vie d’ascète, après avoir visité les moines d’Égypte et de Syrie. Évêque de Césarée en 370, il meurt en 379.&lt;/p&gt; &lt;p&gt;Il rédige des &lt;em&gt;Règles&lt;/em&gt; pour les communautés de moines, qui deviennent la base du monachisme oriental : il préfère la vie en commun, faite de prière, de travail et de service, à la solitude de l’ermite. Évêque, il fonde aux portes de sa ville un vaste ensemble d’hospices, d’hôpitaux et d’ateliers pour les pauvres, les malades et les voyageurs. Dans ses sermons, il dénonce durement l’égoïsme des riches : « Le pain que tu gardes appartient à celui qui a faim. »&lt;/p&gt; &lt;p&gt;Théologien, il combat l’arianisme, soutenu par l’empereur Valens, qui nie la divinité du Christ. Dans son traité &lt;em&gt;Sur le Saint-Esprit&lt;/em&gt;, il défend la divinité de l’Esprit, et précise la formule qui s’imposera : en Dieu, une seule essence, trois « hypostases », ou personnes. Dans ses homélies sur les six jours de la création, il commente la Genèse à l’aide de la science de son temps. Il conseille aux jeunes chrétiens de lire les auteurs païens, comme les abeilles qui butinent ce qui est bon. Il est une figure de la &lt;a href="https://fr.wikipedia.org/wiki/Patristique" title=" Wikipedia"&gt;patristique&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/basile-mini.webp</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique ; ethique</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Père de l’Église grec, évêque de Césarée, législateur du monachisme oriental et théologien de la Trinité.</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="7">
+        <v>329</v>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">390</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 329 – 390</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRÉGOIRE de Nazianze</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_de_Nazianze" title=" Wikipedia"&gt;GRÉGOIRE de Nazianze&lt;/a&gt; est un évêque, théologien et poète chrétien de langue grecque, l’un des trois « Pères cappadociens ». Né vers 329 près de Nazianze, en Cappadoce, fils de l’évêque de la ville, il étudie à Césarée de Palestine, à Alexandrie, puis pendant dix ans à Athènes, où il se lie d’une profonde amitié avec Basile de Césarée. Homme de méditation et d’étude, il aspire à la vie retirée, mais on lui impose à plusieurs reprises des charges qu’il ne voulait pas. Il meurt vers 390.&lt;/p&gt; &lt;p&gt;En 379, il est appelé à Constantinople pour y diriger la petite communauté fidèle au concile de Nicée, alors que la capitale est dominée par les ariens. Dans une modeste chapelle, il prononce ses cinq &lt;em&gt;Discours théologiques&lt;/em&gt; (380), chefs-d’œuvre d’éloquence, où il défend l’égale divinité du Père, du Fils et du Saint-Esprit. Ils lui valent le surnom de « Théologien ». Il y souligne aussi les limites de notre raison : nous pouvons savoir que Dieu est, mais non ce qu’il est.&lt;/p&gt; &lt;p&gt;Contre ceux qui niaient que le Christ ait eu une âme humaine, il formule un principe célèbre : « Ce qui n’a pas été assumé n’a pas été guéri. » Si le Christ n’a pas pris toute l’humanité, il ne l’a pas sauvée tout entière. Il préside quelque temps le concile de Constantinople en 381, puis démissionne, lassé des intrigues, et se retire dans sa Cappadoce natale. Il y écrit de nombreux poèmes, dont une longue autobiographie en vers. Il est un grand nom de la &lt;a href="https://fr.wikipedia.org/wiki/Patristique" title=" Wikipedia"&gt;patristique&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/nazianze-mini.webp</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Père de l’Église grec, surnommé « le Théologien », orateur et poète, défenseur de la Trinité à Constantinople.</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P116"/>
+    </row>
+    <row r="117" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="7">
+        <v>130</v>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 130 – vers 202</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IRÉNÉE de Lyon</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ir%C3%A9n%C3%A9e_de_Lyon" title=" Wikipedia"&gt;IRÉNÉE de Lyon&lt;/a&gt; est un évêque et théologien chrétien de langue grecque, le premier grand théologien de l’Église. Né vers 130 à Smyrne, en Asie Mineure, il y écoute dans sa jeunesse l’évêque Polycarpe, qui avait connu l’apôtre Jean. Il s’installe ensuite en Gaule et devient prêtre à Lyon. En 177, pendant la persécution qui coûte la vie à l’évêque Pothin et à Blandine, il est en mission à Rome. À son retour, il devient évêque de Lyon. Il meurt vers 202. Le pape François l’a proclamé docteur de l’Église en 2022.&lt;/p&gt; &lt;p&gt;Son grand ouvrage, &lt;em&gt;Contre les hérésies&lt;/em&gt;, réfute les gnostiques, en particulier les disciples de Valentin. Ceux-ci enseignaient que le monde matériel est l’œuvre d’un dieu inférieur et mauvais, et que le salut est réservé à quelques initiés qui possèdent une connaissance secrète. Contre eux, Irénée affirme qu’il n’y a qu’un seul Dieu, créateur du monde et de la matière, qui est bonne. La vraie doctrine n’est pas secrète : elle est transmise publiquement par les évêques, successeurs des apôtres, et par les quatre Évangiles, dont il est le premier à fixer la liste.&lt;/p&gt; &lt;p&gt;Il présente l’histoire du salut comme une éducation progressive de l’humanité par Dieu. Le Christ « récapitule » en lui toute l’histoire humaine depuis Adam : il reprend tout pour tout sauver. L’homme est appelé à grandir jusqu’à ressembler à Dieu. Sa formule est restée célèbre : « La gloire de Dieu, c’est l’homme vivant, et la vie de l’homme, c’est la vision de Dieu. » Il est une figure majeure de la &lt;a href="https://fr.wikipedia.org/wiki/Patristique" title=" Wikipedia"&gt;patristique&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/irenee-mini.webp</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">évêque de Lyon et premier grand théologien chrétien, adversaire des gnostiques.</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="7">
+        <v>150</v>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 150 – vers 215</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLÉMENT d'Alexandrie</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9ment_d%27Alexandrie" title=" Wikipedia"&gt;CLÉMENT d'Alexandrie&lt;/a&gt; est un théologien chrétien de langue grecque. Né vers 150, probablement à Athènes, dans une famille païenne, il reçoit une vaste culture et se convertit au christianisme. Après avoir voyagé à la recherche de maîtres, il s’installe à Alexandrie auprès de Pantène, qui y dirigeait une école chrétienne, et lui succède. Il quitte la ville vers 202, pendant la persécution de Septime Sévère, et meurt vers 215, sans doute en Cappadoce. Origène fut peut-être son élève.&lt;/p&gt; &lt;p&gt;Son œuvre forme une trilogie. Le &lt;em&gt;Protreptique&lt;/em&gt; exhorte les païens à abandonner leurs dieux et leurs mystères pour le Christ, le vrai Logos. Le &lt;em&gt;Pédagogue&lt;/em&gt; montre comment le Christ éduque le croyant dans tous les détails de la vie quotidienne : nourriture, vêtements, loisirs. Les &lt;em&gt;Stromates&lt;/em&gt;, ou « Tapisseries », mêlent librement réflexions philosophiques et religieuses, et citent des centaines d’auteurs grecs dont beaucoup ne sont connus que par lui.&lt;/p&gt; &lt;p&gt;Contrairement à Tertullien, il voit dans la philosophie grecque une alliée de la foi. Dieu l’a donnée aux Grecs comme la Loi aux Juifs, pour les conduire au Christ, comme un pédagogue conduit l’enfant à son maître. Le chrétien accompli est pour lui le « vrai gnostique », celui qui unit la foi à la connaissance, sans mépriser le monde, contrairement aux sectes gnostiques. Il ouvre ainsi la voie à une grande synthèse entre le &lt;a href="https://fr.wikipedia.org/wiki/Platonisme" title=" Wikipedia"&gt;platonisme&lt;/a&gt; et le christianisme, que reprendra Origène.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/clementalexandrie-mini.webp</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique ; Platonisme</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">théologien chrétien d’Alexandrie, qui voyait dans la philosophie grecque une préparation au Christ.</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P118"/>
+    </row>
+    <row r="119" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="7">
+        <v>100</v>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 100 – vers 165</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUSTIN de Naplouse</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Justin_de_Naplouse" title=" Wikipedia"&gt;JUSTIN de Naplouse&lt;/a&gt; est un philosophe chrétien de langue grecque, appelé aussi Justin le Martyr. Né vers 100 à Flavia Neapolis, l’actuelle Naplouse, en Samarie, dans une famille païenne, il part à la recherche de la vérité. Il raconte avoir frappé à la porte de plusieurs écoles : un stoïcien qui ne parlait pas de Dieu, un péripatéticien pressé de se faire payer, un pythagoricien qui exigeait d’abord la musique et la géométrie, puis un platonicien qui l’enthousiasma. Un vieillard rencontré au bord de la mer lui fait enfin découvrir les prophètes de la Bible et le Christ.&lt;/p&gt; &lt;p&gt;Converti vers 130, il garde le manteau des philosophes et ouvre une école à Rome. Dans ses deux &lt;em&gt;Apologies&lt;/em&gt;, adressées à l’empereur Antonin le Pieux, il défend les chrétiens contre les accusations dont ils sont victimes et décrit leur culte, en particulier la célébration de l’eucharistie. Dans le &lt;em&gt;Dialogue avec Tryphon&lt;/em&gt;, il discute avec un juif de l’interprétation des Écritures. Il est le premier à présenter le christianisme comme une philosophie, « la seule sûre et utile ».&lt;/p&gt; &lt;p&gt;Sa théorie des « semences du Logos » est restée célèbre. Le Logos, la Raison divine qui s’est incarnée dans le Christ, a semé en tout homme une part de vérité. Ainsi, ceux qui ont vécu selon la raison, comme Socrate ou Héraclite, étaient d’une certaine manière déjà chrétiens. Dénoncé, il est décapité à Rome vers 165, avec plusieurs de ses disciples. Il est l’un des premiers grands noms de la &lt;a href="https://fr.wikipedia.org/wiki/Patristique" title=" Wikipedia"&gt;patristique&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/justin-mini.webp</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique ; Platonisme</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe chrétien et martyr du IIe siècle, pour qui des « semences du Logos » se trouvent chez tous les hommes.</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P119"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -3227,7 +3227,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P119"/>
+  <dimension ref="A1:P123"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="6.39"/>
@@ -9078,6 +9078,239 @@
         </is>
       </c>
       <c r="P119"/>
+    </row>
+    <row r="120" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="7">
+        <v>298</v>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">373</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 298 – 373</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATHANASE d'Alexandrie</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Athanase_d%27Alexandrie" title=" Wikipedia"&gt;ATHANASE d'Alexandrie&lt;/a&gt; est un évêque et théologien chrétien de langue grecque. Né vers 298 à Alexandrie, en Égypte, il est encore jeune diacre quand il accompagne son évêque au concile de Nicée, en 325. Le concile condamne alors Arius, un prêtre alexandrin qui enseignait que le Fils de Dieu n’est pas éternel, mais créé par le Père. Devenu évêque d’Alexandrie en 328, Athanase consacre toute sa vie à défendre la foi de Nicée : le Fils est « de même substance » que le Père, pleinement Dieu comme lui.&lt;/p&gt; &lt;p&gt;Ce combat lui vaut l’hostilité de plusieurs empereurs, favorables aux ariens. Il est exilé cinq fois, notamment à Trèves, en Gaule, et passe au total dix-sept ans loin de son siège, parfois caché chez les moines du désert. On a dit de lui qu’il était seul contre le monde. Dans &lt;em&gt;Sur l’incarnation du Verbe&lt;/em&gt;, il explique pourquoi le Christ doit être vraiment Dieu : seul Dieu peut sauver l’homme de la mort et le transformer. Sa formule est restée célèbre : « Dieu s’est fait homme pour que l’homme devienne Dieu. »&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Vie d’Antoine&lt;/em&gt;, consacrée au père des moines d’Égypte, fait connaître le monachisme dans tout le monde chrétien et devient le modèle des vies de saints. Augustin raconte, dans ses &lt;em&gt;Confessions&lt;/em&gt;, l’effet que sa lecture produisit sur lui et ses amis. En 367, une de ses lettres donne pour la première fois la liste exacte des vingt-sept livres du Nouveau Testament. Il meurt à Alexandrie en 373. Il est une grande figure de la &lt;a href="https://fr.wikipedia.org/wiki/Patristique" title=" Wikipedia"&gt;patristique&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/athanase-mini.webp</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Égyptienne</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">évêque d’Alexandrie, défenseur infatigable de la divinité du Christ contre Arius, auteur de la Vie d’Antoine.</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="7">
+        <v>349</v>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">407</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 349 – 407</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEAN CHRYSOSTOME</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Chrysostome" title=" Wikipedia"&gt;JEAN CHRYSOSTOME&lt;/a&gt; est un prêtre, archevêque et théologien chrétien de langue grecque, le plus célèbre prédicateur de l’Église ancienne. Né vers 349 à Antioche, en Syrie, il étudie la rhétorique auprès du grand orateur païen Libanios, puis mène plusieurs années une vie d’ermite si rude qu’elle ruine sa santé. Ordonné prêtre à Antioche, il y prêche pendant douze ans devant des foules immenses. Son éloquence lui vaudra, après sa mort, le surnom de « Chrysostome », c’est-à-dire « Bouche d’or ».&lt;/p&gt; &lt;p&gt;Ses centaines d’homélies commentent la Bible verset par verset, surtout l’Évangile de Matthieu et les lettres de saint Paul, en tirant des leçons pour la vie quotidienne. Il y insiste sur la justice sociale : les biens de la terre appartiennent à tous, et le riche n’en est que l’intendant ; refuser de partager, c’est voler les pauvres. Il demande aux chrétiens de reconnaître le Christ dans le mendiant. Ses sermons contiennent aussi des attaques violentes contre les juifs, qui ont pesé lourd dans l’histoire de l’antijudaïsme chrétien.&lt;/p&gt; &lt;p&gt;En 398, il devient archevêque de Constantinople. Il réforme le clergé, réduit le train de vie de l’Église et critique le luxe de la cour, ce qui l’oppose à l’impératrice Eudoxie. Déposé par un synode, il est exilé en Arménie et meurt en 407, épuisé par une marche forcée. La liturgie la plus célébrée dans les Églises orthodoxes porte son nom. Il est l’un des grands noms de la &lt;a href="https://fr.wikipedia.org/wiki/Patristique" title=" Wikipedia"&gt;patristique&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/chrysostome-mini.webp</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Syrienne</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Père de l’Église grec, prédicateur surnommé « Bouche d’or », archevêque de Constantinople mort en exil.</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="7">
+        <v>170</v>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 170 – vers 235</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIPPOLYTE de Rome</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hippolyte_de_Rome" title=" Wikipedia"&gt;HIPPOLYTE de Rome&lt;/a&gt; est un prêtre et théologien chrétien de langue grecque, qui vécut à Rome. Né vers 170, peut-être en Orient, il devient l’une des grandes figures de l’Église de Rome au début du IIIe siècle. Exigeant et rigoureux, il s’oppose aux papes Zéphyrin et Calliste, qu’il juge trop indulgents envers les pécheurs et trop vagues sur la distinction entre le Père et le Fils. Il se sépare d’eux et prend la tête d’une communauté dissidente : on le considère parfois comme le premier antipape.&lt;/p&gt; &lt;p&gt;Son œuvre principale, la &lt;em&gt;Réfutation de toutes les hérésies&lt;/em&gt;, a été redécouverte au XIXe siècle dans un monastère du mont Athos. Pour lui, les hérésies chrétiennes ne viennent pas de l’Écriture, mais de la philosophie grecque, des mystères païens et de l’astrologie. Pour le montrer, il consacre son premier livre à un résumé des doctrines des philosophes grecs, de Thalès à Épicure. Ce tableau et les citations qu’il contient, notamment de nombreux fragments d’Héraclite, sont une source précieuse pour connaître la pensée des premiers philosophes.&lt;/p&gt; &lt;p&gt;On lui a longtemps attribué la &lt;em&gt;Tradition apostolique&lt;/em&gt;, qui décrit l’organisation et la liturgie de l’Église ancienne, mais cette attribution est aujourd’hui discutée. En 235, il est déporté dans les mines de Sardaigne avec le pape Pontien, se réconcilie avec lui et y meurt. Il est honoré comme saint et martyr. Il appartient à la &lt;a href="https://fr.wikipedia.org/wiki/Patristique" title=" Wikipedia"&gt;patristique&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hippolyte-mini.webp</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Romaine</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prêtre et théologien de Rome, auteur de la Réfutation de toutes les hérésies, précieuse source sur les philosophes grecs.</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P122"/>
+    </row>
+    <row r="123" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="7">
+        <v>-470</v>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-400</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ve siècle A JC</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASPASIE de Milet</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aspasie" title=" Wikipedia"&gt;ASPASIE de Milet&lt;/a&gt; est une femme de l’Athènes classique, célèbre pour son intelligence et son art de la parole. Née vers 470 avant notre ère à Milet, une cité grecque d’Asie Mineure, elle s’installe à Athènes, où elle devient la compagne de Périclès, le grand homme d’État de la cité. Étrangère, elle ne peut l’épouser légalement, mais elle lui donne un fils. Sa liberté, sa culture et son influence choquent : les poètes comiques la présentent comme une courtisane qui mènerait Périclès, et on l’accuse même d’impiété. On ignore la date de sa mort.&lt;/p&gt; &lt;p&gt;Les témoignages sur sa pensée viennent surtout des disciples de Socrate, ce qui montre l’estime dont elle jouissait dans ce cercle. Dans le &lt;em&gt;Ménexène&lt;/em&gt; de Platon, Socrate prétend réciter un discours funèbre en l’honneur des Athéniens morts à la guerre, qu’Aspasie lui aurait appris ; il affirme même qu’elle aurait écrit celui, si célèbre, de Périclès. Chez Xénophon, Socrate la recommande comme la meilleure conseillère sur le mariage et la vie du couple.&lt;/p&gt; &lt;p&gt;Un dialogue perdu d’Eschine, un autre disciple de Socrate, la montrait interrogeant un couple : chacun préférerait-il les biens les plus beaux, l’or, les vêtements, puis l’époux le meilleur ? Ce raisonnement, qui part d’exemples pour arriver à une conclusion générale, est cité par Cicéron comme un modèle d’induction. Il est difficile de distinguer la femme réelle de la légende, mais elle reste une figure de la femme philosophe dans l’Antiquité, proche du &lt;a href="https://fr.wikipedia.org/wiki/Socrate" title=" Wikipedia"&gt;cercle de Socrate&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/aspasie-mini.webp</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; langage</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; Sophisme</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme cultivée de l’Athènes de Périclès, que Socrate disait son maître en éloquence.</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P123"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-greco-romains.xlsx
+++ b/data/frise-philosophes-greco-romains.xlsx
@@ -4216,293 +4216,430 @@
         </is>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="193.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
+    <row r="22" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7">
+        <v>-470</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-385</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 470 A JC - vers 385 A JC</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PHILOLAOS de Crotone</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philolaos_de_Crotone" title=" Wikipedia"&gt;PHILOLAOS de Crotone&lt;/a&gt; est un philosophe grec de l’école de &lt;a href="https://fr.wikipedia.org/wiki/Pythagore" title=" Wikipedia"&gt;Pythagore&lt;/a&gt;, contemporain de Socrate. Né à Crotone, en Italie du Sud, il doit fuir les persécutions dont sont victimes les pythagoriciens et s’installe un temps à Thèbes, où il a pour élèves Simmias et Cébès, les deux interlocuteurs de Socrate dans le &lt;em&gt;Phédon&lt;/em&gt; de Platon. Il est le premier pythagoricien à mettre par écrit les doctrines de l’école, jusque-là tenues secrètes. Selon une tradition, Platon aurait acheté son livre très cher.&lt;/p&gt; &lt;p&gt;Il ne reste de son livre &lt;em&gt;Sur la nature&lt;/em&gt; que &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1998_num_111_2_4347_t2_0780_0000_2" title="Philolaos of Croton, Pythagorean and Presocratic par persée"&gt;quelques fragments.&lt;/a&gt; Le monde y est composé de deux sortes de choses : les « illimitées », comme les matières, et les « limitantes », comme les formes. Elles ne peuvent former un tout ordonné que si une « harmonie » les accorde, selon les rapports numériques que l’on trouve dans les intervalles de la musique. « Tout ce qui est connu a un nombre, car sans lui il n’est pas possible de rien penser ni de rien connaître. » Le nombre est ce qui rend le monde intelligible.&lt;/p&gt; &lt;p&gt;Il propose aussi un système du monde audacieux : la Terre n’est pas au centre de l’univers. Au centre se trouve un « feu central », autour duquel tournent une « anti-Terre » invisible, la Terre, la Lune, le Soleil, les planètes et les étoiles. Copernic citera cette doctrine comme un précédent à la sienne. On lui attribue aussi l’idée que l’âme est enfermée dans le corps comme dans une prison, en punition d’une faute.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E7S4aZrmTqw</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Philolaus  Harmony in Cosmos and Human Life" par Fundamental Reflections</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/philolaos-mini.webp</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pythagorisme ; Présocratique</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe pythagoricien grec, pour qui tout ce qui est connu a un nombre, et qui ôta la Terre du centre du monde.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P22"/>
+    </row>
+    <row r="23" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7">
+        <v>-470</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-400</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470 A JC - 400 A JC</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASPASIE de Milet</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aspasie" title=" Wikipedia"&gt;ASPASIE de Milet&lt;/a&gt; est une femme de l’Athènes classique, célèbre pour&lt;a href="https://www.worldhistory.org/trans/fr/1-491/aspasie-de-milet/" title="Aspasie de Milet par World History Encyclopedia"&gt; son intelligence&lt;/a&gt; et son art de la parole. Née à Milet, une cité grecque d’Asie Mineure, elle s’installe à Athènes, où elle devient la compagne de Périclès, le grand homme d’État de la cité. Étrangère, elle ne peut l’épouser légalement, mais elle lui donne un fils. Sa liberté, sa culture et son influence choquent : les poètes comiques la présentent comme une courtisane qui mènerait Périclès, et on l’accuse même d’impiété. On ignore la date de sa mort.&lt;/p&gt; &lt;p&gt;Les témoignages sur sa pensée viennent surtout des disciples de Socrate, ce qui montre l’estime dont elle jouissait dans ce cercle. Dans le &lt;em&gt;Ménexène&lt;/em&gt; de Platon, Socrate prétend réciter un discours funèbre en l’honneur des Athéniens morts à la guerre, qu’Aspasie lui aurait appris ; il affirme même &lt;a href="https://www.youtube.com/watch?v=ugjbiSjuDgY" title="Aspasie de Milet en 10 œuvres - Culture Prime par France tv culture"&gt;qu’elle aurait écrit&lt;/a&gt; celui, si célèbre, de Périclès. Chez Xénophon, Socrate la recommande comme la meilleure conseillère sur le mariage et la vie du couple.&lt;/p&gt; &lt;p&gt;Un dialogue perdu d’Eschine, un autre disciple de Socrate, &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2007_num_109_1_6738_t1_0385_0000_2" title="Jouanna (D.), Aspasie de Milet, égérie de Périclès. par persée"&gt;la montrait interrogeant&lt;/a&gt; un couple : chacun préférerait-il les biens les plus beaux, l’or, les vêtements, puis l’époux le meilleur ? Ce raisonnement, qui part d’exemples pour arriver à une conclusion générale, est cité par Cicéron comme un modèle d’induction. Il est difficile de distinguer la femme réelle de la légende, mais elle reste une figure de la femme philosophe dans l’Antiquité, proche du &lt;a href="https://fr.wikipedia.org/wiki/Socrate" title=" Wikipedia"&gt;cercle de Socrate&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IKX28arhifY</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Aspasie : l'étrangère qui fascinait Athènes" par Cyrus North</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/aspasie-mini.webp</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; langage</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; Sophisme</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme cultivée de l’Athènes de Périclès, que Socrate disait son maître en éloquence.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P23"/>
+    </row>
+    <row r="24" customFormat="false" ht="193.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
         <v>-460</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B24" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E24" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G24" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H24" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
-        <v>-459</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
-        <v>-450</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Euclide_de_M%C3%A9gare"   title=" Wikipedia"&gt;EUCLIDE de Mégare&lt;/a&gt; (vers 435-365 av. J.-C.) est un philosophe grec, disciple de Socrate et fondateur de &lt;a href="https://www.youtube.com/watch?v=RGVwwTCSsqg" style="color:#88A1E9" title="Euclides and the Megarian School par Foolish Musings "&gt;l’école mégarique&lt;/a&gt; ; il ne faut pas le confondre avec &lt;a href="https://www.youtube.com/watch?v=enZpq8jvFEs" style="color:#88A1E9" title="L'AXIOMATIQUE - Les Éléments d'Euclide par Monsieur Phi "&gt;Euclide le mathématicien&lt;/a&gt;, auteur des &lt;em&gt;Éléments&lt;/em&gt;, qui vécut un siècle plus tard. On raconte que, lorsque les Mégariens furent interdits de séjour à Athènes, il venait la nuit, déguisé en femme, pour écouter Socrate. Il assiste à la mort de son maître, en 399 av. J.-C., et accueille ensuite à Mégare Platon et d’autres disciples qui fuient Athènes.&lt;/p&gt; &lt;p&gt;Ses écrits, des dialogues, sont perdus. Il réunit l’éthique de Socrate et la métaphysique de &lt;a href="https://fr.wikipedia.org/wiki/Parm%C3%A9nide" title=" Wikipedia"&gt;Parménide&lt;/a&gt; : le Bien est un, toujours semblable à lui-même, même s’il reçoit plusieurs noms, sagesse, Dieu, intellect. Ce qui s’oppose au Bien n’existe pas. Comme les Éléates, Euclide se méfie du changement et du multiple, et privilégie l’être immuable. Il est surtout un redoutable dialecticien : il attaque les conclusions de ses adversaires plutôt que leurs prémisses, et rejette le raisonnement par analogie. Ses successeurs font de l’école mégarique un foyer de la logique grecque. Eubulide invente des paradoxes restés célèbres : celui du menteur, « je mens » ; celui du tas, à partir de combien de grains a-t-on un tas ? ; ou celui du chauve. Diodore Cronos réfléchit sur le possible et le nécessaire avec son « argument dominateur », et Philon définit l’implication logique d’une manière très proche de la logique moderne.&lt;/p&gt; &lt;p&gt;Le mégarique Stilpon eut pour élève Zénon de Kition, le fondateur du stoïcisme, qui hérita de ce goût pour la logique.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
+        <v>-459</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="I25" s="9"/>
+      <c r="J25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="n">
+        <v>-450</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Euclide_de_M%C3%A9gare"   title=" Wikipedia"&gt;EUCLIDE de Mégare&lt;/a&gt; (vers 435-365 av. J.-C.) est un philosophe grec, disciple de Socrate et fondateur de &lt;a href="https://www.youtube.com/watch?v=RGVwwTCSsqg" style="color:#88A1E9" title="Euclides and the Megarian School par Foolish Musings "&gt;l’école mégarique&lt;/a&gt; ; il ne faut pas le confondre avec &lt;a href="https://www.youtube.com/watch?v=enZpq8jvFEs" style="color:#88A1E9" title="L'AXIOMATIQUE - Les Éléments d'Euclide par Monsieur Phi "&gt;Euclide le mathématicien&lt;/a&gt;, auteur des &lt;em&gt;Éléments&lt;/em&gt;, qui vécut un siècle plus tard. On raconte que, lorsque les Mégariens furent interdits de séjour à Athènes, il venait la nuit, déguisé en femme, pour écouter Socrate. Il assiste à la mort de son maître, en 399 av. J.-C., et accueille ensuite à Mégare Platon et d’autres disciples qui fuient Athènes.&lt;/p&gt; &lt;p&gt;Ses écrits, des dialogues, sont perdus. Il réunit l’éthique de Socrate et la métaphysique de &lt;a href="https://fr.wikipedia.org/wiki/Parm%C3%A9nide" title=" Wikipedia"&gt;Parménide&lt;/a&gt; : le Bien est un, toujours semblable à lui-même, même s’il reçoit plusieurs noms, sagesse, Dieu, intellect. Ce qui s’oppose au Bien n’existe pas. Comme les Éléates, Euclide se méfie du changement et du multiple, et privilégie l’être immuable. Il est surtout un redoutable dialecticien : il attaque les conclusions de ses adversaires plutôt que leurs prémisses, et rejette le raisonnement par analogie. Ses successeurs font de l’école mégarique un foyer de la logique grecque. Eubulide invente des paradoxes restés célèbres : celui du menteur, « je mens » ; celui du tas, à partir de combien de grains a-t-on un tas ? ; ou celui du chauve. Diodore Cronos réfléchit sur le possible et le nécessaire avec son « argument dominateur », et Philon définit l’implication logique d’une manière très proche de la logique moderne.&lt;/p&gt; &lt;p&gt;Le mégarique Stilpon eut pour élève Zénon de Kition, le fondateur du stoïcisme, qui hérita de ce goût pour la logique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I26" s="9"/>
+      <c r="J26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Socratisme ; École mégarique</t>
         </is>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P24">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P26">
         <v>2</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7">
         <v>-450</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B27" s="7">
         <v>-400</v>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ve siècle A JC</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">DIOTIME de Mantinée</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diotime" title=" Wikipedia"&gt;DIOTIME de Mantinée&lt;/a&gt; est une prêtresse et une sage du Ve siècle avant J.-C., connue uniquement par le &lt;em&gt;Banquet&lt;/em&gt; de Platon. Socrate y raconte que, dans sa jeunesse, c'est elle qui lui a enseigné tout ce qu'il sait sur l'amour. Aucune autre source&lt;a href="https://www.youtube.com/watch?v=6fOSzE0LLaM" title="Diotima de Mantinée et Platon: L'amour, l'idéal et l'ascension vers le Bien (discussion IA) par L'altruisme"&gt; antique ne la mentionne&lt;/a&gt;, et son nom, « honorée par Zeus », ainsi que son origine, Mantinée, qui évoque le mot grec pour « devin », laissent penser qu'elle pourrait être une invention de Platon.&lt;/p&gt; &lt;p&gt;Son discours est pourtant le sommet du dialogue. Diotime explique qu'Éros n'est pas un dieu mais un « grand démon », un intermédiaire entre les mortels et les immortels, fils de Pauvreté et d'Expédient : il manque de ce qu'il désire et cherche sans cesse à l'obtenir. Aimer, c'est désirer posséder le bien pour toujours, et donc vouloir engendrer dans la beauté, par les enfants ou par les œuvres de l'esprit.&lt;/p&gt; &lt;p&gt;Le choix de Platon de faire parler une femme n'est pas anodin : dans un banquet où ne siègent que des hommes, c'est une étrangère, prêtresse et savante, qui détient la vérité la plus haute. Socrate, qui d'ordinaire interroge les autres, se présente ici comme un élève qu'elle corrige et fait progresser. La méthode de Diotime ressemble d'ailleurs à celle de Socrate lui-même : elle pose des questions, relève les contradictions et conduit pas à pas son interlocuteur vers la vérité.&lt;/p&gt; &lt;p&gt;Elle décrit ensuite la célèbre « échelle de l'amour » : de l'amour d'un beau corps, on s'élève à celui de tous les beaux corps, puis des belles âmes, des belles lois, des belles connaissances, jusqu'à la contemplation de la Beauté en soi, éternelle et parfaite. Réelle ou imaginée, &lt;a href="https://www.persee.fr/doc/bude_1247-6862_1954_num_13_4_5049" title="Socrate et Diotime par persée"&gt;Diotime reste la femme &lt;/a&gt;qui, chez Platon, enseigne au plus grand des philosophes l'une des idées les plus influentes de l'histoire de la pensée.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t xml:space="preserve">xQ_rep6SFzM</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">"Philosophie - Diotime ou la philosophe ayant inspiré l'amour platonicien" par Coursitout</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/diotimedemantinee-mini.webp</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Grecque</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">metaphysique ; esthetique</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Platonisme</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prêtresse et sage qui, dans le Banquet de Platon, enseigne à Socrate la nature de l'amour.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7">
         <v>-450</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">-400</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">vers 450 A JC – 400 A JC</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">CRATYLE</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cratyle" title=" Wikipedia"&gt;CRATYLE&lt;/a&gt; est un philosophe grec d’Athènes, de la fin du Ve siècle av. J.-C., partisan radical de la pensée d’&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclite" title=" Wikipedia"&gt;Héraclite&lt;/a&gt;. Selon Aristote, Platon l’aurait fréquenté dans sa jeunesse, avant de rencontrer Socrate, et en aurait retenu l’idée que les choses sensibles sont dans un flux perpétuel, et qu’il ne peut donc y avoir de science à leur sujet.&lt;/p&gt; &lt;p&gt;Il pousse le &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9raclit%C3%A9isme" title=" Wikipedia"&gt;mobilisme&lt;/a&gt; jusqu’à ses conséquences extrêmes. Héraclite disait qu’on ne peut entrer deux fois dans le même fleuve ; Cratyle lui reproche d’avoir été trop timide : on ne peut pas même y entrer une seule fois. Puisque tout change sans cesse, même pendant qu’on parle, aucune parole ne peut dire vrai. Selon Aristote, il finit par ne plus rien dire du tout et se contentait de remuer le doigt. Pour Aristote, ce geste muet montre où mène le refus de toute affirmation stable : à l’impossibilité même de parler.&lt;/p&gt; &lt;p&gt;Platon a donné son nom à l’un de ses dialogues, &lt;a href="https://www.artyuiop.fr/artyuiop/Platon_-_Cratyle_files/artyuiop95-Platon-Cratyle-trad._Victor_Cousin.pdf" title="Cratyle par artyuiop"&gt;le &lt;em&gt;Cratyle&lt;/em&gt;,&lt;/a&gt; consacré à la justesse des noms. Il y soutient que chaque chose a un nom juste par nature, qui exprime son essence, contre Hermogène, pour qui les noms ne sont que des conventions. Socrate examine les deux thèses avec ironie, se livre à de savoureuses étymologies, et conclut qu’il vaut mieux connaître les choses par elles-mêmes que par leurs noms. Le débat entre la nature et la convention des signes traverse ensuite toute l’histoire de la philosophie du langage, jusqu’à Saussure. Pour Platon, la leçon est claire : si tout s’écoulait, il n’y aurait rien à connaître, d’où la nécessité des Idées, réalités immuables.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t xml:space="preserve">txurJe1ifBg</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">"CRATYLE (1) de PLATON : Première Philosophie du LANGAGE, de la Nature et de l'Origine des Mots" par Frère Ismaël</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/cratyle-mini.webp</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Grecque</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">langage ; metaphysique</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mobilisme</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">philosophe grec, héraclitéen radical, qui a donné son nom au dialogue de Platon sur le langage.</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P26"/>
-    </row>
-    <row r="27" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P28"/>
+    </row>
+    <row r="29" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
         <v>-445</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B29" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C29" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D29" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antisth%C3%A8ne" style="color:#6A142A"   title="Antisthène par Wikipédia"&gt; ANTISTHÈNE &lt;/a&gt; était un philosophe disciple de Socrate et il a eu une influence significative sur le développement de la philosophie morale et éthique en cherchant à préserver et à développer les idées de son maître, en mettant l'accent sur la vertu personnelle et l'authenticité. Né à Athènes d’une mère thrace, il suit d’abord le sophiste Gorgias, avant de devenir l’un des plus fidèles disciples de Socrate. &lt;/p&gt;
 &lt;p&gt; Il est considéré comme le fondateur de &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=133s&amp;ab_channel=AlainBajom%C3%A9e" style="color:#88A1E9"   title="Comprendre les Cyniques par Alain Bajomée"&gt; l'école de pensée cynique.&lt;/a&gt; Après la mort de Socrate, il a développé ses propres idées en reprenant certains des thèmes centraux de l’enseignement de Socrate. Le nom de « cynique » viendrait du gymnase du Cynosarge, où il enseignait, ou du grec &lt;em&gt;kunikos&lt;/em&gt;, « semblable au chien » ; il fait référence à l'accent mis sur la vie simple et naturelle détachée des désirs matériels et des plaisirs superficiels, ainsi qu'à la critique des conventions sociales. Il croyait que le bonheur réside dans la maîtrise de soi et dans le rejet des biens matériels. Il vivait lui-même une vie ascétique et rejetait les besoins et les désirs superflus. &lt;/p&gt;
@@ -4510,108 +4647,14 @@
 </t>
         </is>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F29" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G29" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H29" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="n">
-        <v>-436</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isocrate"  style="color:#6A142A"  title=" Wikipedia"&gt;ISOCRATE&lt;/a&gt; était un orateur et philosophe grec souvent éclipsé par des figures comme Platon ou Aristote, mais son impact sur l'éducation, la rhétorique et la pensée politique est considérable. Il  se distingue par  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2007_num_109_2_6552"  style="color:#88A1E9" title="La πλεονεξία chez Isocrate  par Persée"&gt;son approche&lt;/a&gt; pragmatique de la philosophie contrairement à Platon, qui cherche la vérité absolue, lui se concentre sur l'utilité pratique de la connaissance.  En 390 av. J.-C., il fonde une école à Athènes, rivale de l'Académie de Platon, qui attire des étudiants de toute la Grèce, dont certains deviendront des figures importantes, comme les orateurs Hypéride et Lycurgue.&lt;/p&gt; &lt;p&gt; Pour lui, la rhétorique n'est pas seulement un art de persuader, mais un moyen de former des citoyens éclairés et de promouvoir la justice. Il croit que la parole bien maîtrisée peut améliorer la société en encourageant le débat raisonné et en renforçant les institutions. Il rejette l'individualisme excessif et prône un équilibre entre les intérêts personnels et ceux de la communauté.  Il a laissé une vingtaine de discours et &lt;a href="https://www.persee.fr/doc/ktema_0221-5896_2016_num_41_1_1487"  style="color:#88A1E9" title=" Isocrate et Sparte par Persée"&gt;plusieurs lettres&lt;/a&gt;, dont les plus célèbres sont : &lt;/p&gt; &lt;p&gt;Le Panégyrique d'Athènes : Un plaidoyer pour l'unité grecque sous l'hégémonie athénienne. &lt;/p&gt; &lt;p&gt;Sur la paix : Un appel à la modération et à la coopération entre les cités grecques.&lt;/p&gt; &lt;p&gt;L'Éloge d'Hélène : Une défense rhétorique de la figure d'Hélène de Troie. &lt;/p&gt; &lt;p&gt;Le Philippe : Une lettre adressée à Philippe II de Macédoine, l'exhortant à unifier la Grèce. &lt;/p&gt; &lt;p&gt; Il aura marqué l'histoire de la pensée occidentale à plusieurs titres, son modèle éducatif, centré sur la rhétorique et la culture générale, a influencé l'éducation libérale en Occident et en politique, ses idées sur l'unité grecque et la coopération internationale résonnent encore aujourd'hui.&lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P28"/>
-    </row>
-    <row r="29" customFormat="false" ht="154.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
-        <v>-435</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristippe_de_Cyr%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTIPPE de Cyrène&lt;/a&gt; était un philosophe grec antique, fondateur de  &lt;a href="https://www.youtube.com/watch?v=Rp7sm07EJBY&amp;t=270s" style="color:#88A1E9" title=" Les CYRÉNAÏQUES en 8 minutes par Alain Bajoumée"&gt;l'école cyrénaïque&lt;/a&gt;, une école de pensée qui met l'accent sur la recherche du plaisir comme but principal de la vie, une forme &lt;a href="https://www.youtube.com/watch?v=HOE8sDMhGUE" style="color:#88A1E9" title=" L'hédonisme sans mesure: la philosophie du plaisir par philosophie"&gt;d'hédonisme&lt;/a&gt;. Cependant, contrairement à l'hédonisme moderne souvent associé à la recherche effrénée du plaisir, la philosophie d'Aristippe est plus subtile et contextuelle : &lt;/p&gt;
-&lt;p&gt;Poursuite du plaisir : Pour lui, le plaisir est le bien suprême. Il croyait que le but de la vie était de maximiser le plaisir et de minimiser la douleur. Cependant, il distinguait entre les plaisirs physiques et les plaisirs intellectuels, et il valorisait particulièrement les plaisirs immédiats et concrets. &lt;/p&gt; &lt;p&gt;Adaptabilité et flexibilité : Il enseignait l'importance de s'adapter aux circonstances. Il croyait que la sagesse consistait à savoir profiter des plaisirs disponibles tout en évitant les douleurs inutiles. Cette idée est souvent résumée par sa maxime : "Posséder sans être possédé." &lt;/p&gt; &lt;p&gt;Indépendance émotionnelle : Il prônait une forme de détachement émotionnel. Il croyait que l'on devait être capable de jouir des plaisirs sans devenir esclave de ses désirs. Cette idée est proche de la notion de "ataraxie" (tranquillité de l'âme) que l'on retrouve plus tard dans l'épicurisme. &lt;/p&gt; &lt;p&gt;Critique des conventions sociales : Il était connu pour son mépris des conventions sociales et des normes traditionnelles et croyait que les individus devaient vivre selon leurs propres termes, sans se soucier excessivement de l'opinion des autres. &lt;/p&gt; &lt;p&gt; L'école cyrénaïque a eu une influence limitée par rapport à d'autres écoles philosophiques de l'Antiquité, mais elle a néanmoins contribué à façonner la pensée hédoniste et à influencer des philosophes ultérieurs comme Épicure.  &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>217</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="2" t="s">
@@ -4621,10 +4664,10 @@
         <v>200</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4632,115 +4675,209 @@
         </is>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
-        <v>-430</v>
+        <v>-436</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>223</v>
+        <v>205</v>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isocrate"  style="color:#6A142A"  title=" Wikipedia"&gt;ISOCRATE&lt;/a&gt; était un orateur et philosophe grec souvent éclipsé par des figures comme Platon ou Aristote, mais son impact sur l'éducation, la rhétorique et la pensée politique est considérable. Il  se distingue par  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_2007_num_109_2_6552"  style="color:#88A1E9" title="La πλεονεξία chez Isocrate  par Persée"&gt;son approche&lt;/a&gt; pragmatique de la philosophie contrairement à Platon, qui cherche la vérité absolue, lui se concentre sur l'utilité pratique de la connaissance.  En 390 av. J.-C., il fonde une école à Athènes, rivale de l'Académie de Platon, qui attire des étudiants de toute la Grèce, dont certains deviendront des figures importantes, comme les orateurs Hypéride et Lycurgue.&lt;/p&gt; &lt;p&gt; Pour lui, la rhétorique n'est pas seulement un art de persuader, mais un moyen de former des citoyens éclairés et de promouvoir la justice. Il croit que la parole bien maîtrisée peut améliorer la société en encourageant le débat raisonné et en renforçant les institutions. Il rejette l'individualisme excessif et prône un équilibre entre les intérêts personnels et ceux de la communauté.  Il a laissé une vingtaine de discours et &lt;a href="https://www.persee.fr/doc/ktema_0221-5896_2016_num_41_1_1487"  style="color:#88A1E9" title=" Isocrate et Sparte par Persée"&gt;plusieurs lettres&lt;/a&gt;, dont les plus célèbres sont : &lt;/p&gt; &lt;p&gt;Le Panégyrique d'Athènes : Un plaidoyer pour l'unité grecque sous l'hégémonie athénienne. &lt;/p&gt; &lt;p&gt;Sur la paix : Un appel à la modération et à la coopération entre les cités grecques.&lt;/p&gt; &lt;p&gt;L'Éloge d'Hélène : Une défense rhétorique de la figure d'Hélène de Troie. &lt;/p&gt; &lt;p&gt;Le Philippe : Une lettre adressée à Philippe II de Macédoine, l'exhortant à unifier la Grèce. &lt;/p&gt; &lt;p&gt; Il aura marqué l'histoire de la pensée occidentale à plusieurs titres, son modèle éducatif, centré sur la rhétorique et la culture générale, a influencé l'éducation libérale en Occident et en politique, ses idées sur l'unité grecque et la coopération internationale résonnent encore aujourd'hui.&lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F30" s="7" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="232.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P30"/>
+    </row>
+    <row r="31" customFormat="false" ht="154.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
-        <v>-428</v>
+        <v>-435</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Platon"  style="color:#6A142A"  title=" Wikipedia"&gt;PLATON&lt;/a&gt; fut  un des plus grands penseurs de l'Antiquité.  Il était l'élève de Socrate, dont la méthode dialectique et la quête de la vérité le marquent profondément. La condamnation à mort de Socrate en 399 av. J.-C. influence sa méfiance envers la démocratie athénienne. &lt;/p&gt; &lt;p&gt; Il fonda  &lt;a href="https://www.youtube.com/watch?v=q0M8zV-XHbQ"  style="color:#88A1E9" title="L'académie de Platon Platon par Luc Ferry"&gt;l'Académie&lt;/a&gt; à Athènes, qui est considérée comme la première institution d'enseignement supérieur de l'histoire où  il y enseigne la philosophie, les mathématiques et les sciences. L'Académie fonctionnera pendant près de 900 ans.&lt;/p&gt; Il développe une philosophie complexe et systématique, centrée sur des concepts clés comme les Idées, &lt;a href="https://www.persee.fr/doc/phlou_0776-5541_1905_num_12_46_1881"  style="color:#88A1E9" title="Dieu, d'après Platon par Persée"&gt;l'âme&lt;/a&gt;, la justice et la connaissance. Ses idées sont principalement exposées sous forme de dialogues, où Socrate est souvent le personnage principal. Il distingue &lt;a href="https://www.youtube.com/watch?v=o5TbXYe64A8&amp;t=18s&amp;ab_channel=AlainBajom%C3%A9e"  style="color:#88A1E9" title="La théorie des idées par Alain Bajomée"&gt;deux mondes&lt;/a&gt; : le monde sensible (celui que nous percevons par les sens) et le monde intelligible (celui des Idées, éternel et immuable). Pour lui, les Idées sont des réalités parfaites et immuables qui existent indépendamment du monde matériel. Par exemple, il existe une Idée de la Beauté, de la Justice ou du Bien, dont les objets sensibles ne sont que des copies imparfaites. &lt;/p&gt; &lt;p&gt;Il a écrit une trentaine de dialogues, dont les plus célèbres sont : La République (justice, politique, éducation). Phédon (immortalité de l'âme). &lt;a href="https://www.youtube.com/watch?v=Mbtxr1hsP7A"  title="  Ce que Le Banquet de Platon révèle sur l'amour  par Resumon ça"&gt;Le Banquet &lt;/a&gt;(amour et beauté). Phèdre (rhétorique et amour). Ménon (vertu et réminiscence). Timée (cosmologie et physique). Critias (mythe de l'Atlantide). Apologie de Socrate (défense de Socrate lors de son procès). Phédon (immortalité de l'âme). &lt;/p&gt; &lt;p&gt;  Dans son ouvrage  le plus célèbre  &lt;a href="https://www.youtube.com/watch?v=qSrvZvjPG_w&amp;t=811s&amp;ab_channel=Kosmos"  style="color:#88A1E9" title="La République, c'est quoi par Kosmos"&gt;La République&lt;/a&gt;, il décrit sa vision d'une société idéale où les dirigeants sont des philosophes-rois et où la justice et la vertu sont les principes fondamentaux. Il y présente une métaphore de la condition humaine, l'allégorie de la &lt;a href="https://www.youtube.com/watch?v=N519gbEXbbw&amp;t=13s&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9" title="L'allégorie de la Caverne par le Précepteur "&gt;La Caverne&lt;/a&gt;, lieu où des gens vivent et où ils ne voient que des ombres projetées sur les murs en croyant que c'est la réalité.&lt;/p&gt; &lt;p&gt; Il reste une figure centrale de la philosophie, dont les idées continuent d'inspirer et de provoquer la réflexion. Sa quête de la vérité, sa vision idéaliste et sa méthode dialectique en font un penseur intemporel. &lt;/p&gt;   &lt;audio controls title="Platon et la politique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.11.2025-ITEMA_24317262-2025C48904S0324-NET_MFC_E07CEF22-5D42-4358-8035-01B7B6D438EF-21-f49f7fca67cbafd4d44c5b4c00fead78.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        <v>213</v>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristippe_de_Cyr%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTIPPE de Cyrène&lt;/a&gt; était un philosophe grec antique, fondateur de  &lt;a href="https://www.youtube.com/watch?v=Rp7sm07EJBY&amp;t=270s" style="color:#88A1E9" title=" Les CYRÉNAÏQUES en 8 minutes par Alain Bajoumée"&gt;l'école cyrénaïque&lt;/a&gt;, une école de pensée qui met l'accent sur la recherche du plaisir comme but principal de la vie, une forme &lt;a href="https://www.youtube.com/watch?v=HOE8sDMhGUE" style="color:#88A1E9" title=" L'hédonisme sans mesure: la philosophie du plaisir par philosophie"&gt;d'hédonisme&lt;/a&gt;. Cependant, contrairement à l'hédonisme moderne souvent associé à la recherche effrénée du plaisir, la philosophie d'Aristippe est plus subtile et contextuelle : &lt;/p&gt;
+&lt;p&gt;Poursuite du plaisir : Pour lui, le plaisir est le bien suprême. Il croyait que le but de la vie était de maximiser le plaisir et de minimiser la douleur. Cependant, il distinguait entre les plaisirs physiques et les plaisirs intellectuels, et il valorisait particulièrement les plaisirs immédiats et concrets. &lt;/p&gt; &lt;p&gt;Adaptabilité et flexibilité : Il enseignait l'importance de s'adapter aux circonstances. Il croyait que la sagesse consistait à savoir profiter des plaisirs disponibles tout en évitant les douleurs inutiles. Cette idée est souvent résumée par sa maxime : "Posséder sans être possédé." &lt;/p&gt; &lt;p&gt;Indépendance émotionnelle : Il prônait une forme de détachement émotionnel. Il croyait que l'on devait être capable de jouir des plaisirs sans devenir esclave de ses désirs. Cette idée est proche de la notion de "ataraxie" (tranquillité de l'âme) que l'on retrouve plus tard dans l'épicurisme. &lt;/p&gt; &lt;p&gt;Critique des conventions sociales : Il était connu pour son mépris des conventions sociales et des normes traditionnelles et croyait que les individus devaient vivre selon leurs propres termes, sans se soucier excessivement de l'opinion des autres. &lt;/p&gt; &lt;p&gt; L'école cyrénaïque a eu une influence limitée par rapport à d'autres écoles philosophiques de l'Antiquité, mais elle a néanmoins contribué à façonner la pensée hédoniste et à influencer des philosophes ultérieurs comme Épicure.  &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F31" s="7" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="n">
+        <v>-430</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="I32" s="9"/>
+      <c r="J32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="232.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="n">
+        <v>-428</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Platon"  style="color:#6A142A"  title=" Wikipedia"&gt;PLATON&lt;/a&gt; fut  un des plus grands penseurs de l'Antiquité.  Il était l'élève de Socrate, dont la méthode dialectique et la quête de la vérité le marquent profondément. La condamnation à mort de Socrate en 399 av. J.-C. influence sa méfiance envers la démocratie athénienne. &lt;/p&gt; &lt;p&gt; Il fonda  &lt;a href="https://www.youtube.com/watch?v=q0M8zV-XHbQ"  style="color:#88A1E9" title="L'académie de Platon Platon par Luc Ferry"&gt;l'Académie&lt;/a&gt; à Athènes, qui est considérée comme la première institution d'enseignement supérieur de l'histoire où  il y enseigne la philosophie, les mathématiques et les sciences. L'Académie fonctionnera pendant près de 900 ans.&lt;/p&gt; Il développe une philosophie complexe et systématique, centrée sur des concepts clés comme les Idées, &lt;a href="https://www.persee.fr/doc/phlou_0776-5541_1905_num_12_46_1881"  style="color:#88A1E9" title="Dieu, d'après Platon par Persée"&gt;l'âme&lt;/a&gt;, la justice et la connaissance. Ses idées sont principalement exposées sous forme de dialogues, où Socrate est souvent le personnage principal. Il distingue &lt;a href="https://www.youtube.com/watch?v=o5TbXYe64A8&amp;t=18s&amp;ab_channel=AlainBajom%C3%A9e"  style="color:#88A1E9" title="La théorie des idées par Alain Bajomée"&gt;deux mondes&lt;/a&gt; : le monde sensible (celui que nous percevons par les sens) et le monde intelligible (celui des Idées, éternel et immuable). Pour lui, les Idées sont des réalités parfaites et immuables qui existent indépendamment du monde matériel. Par exemple, il existe une Idée de la Beauté, de la Justice ou du Bien, dont les objets sensibles ne sont que des copies imparfaites. &lt;/p&gt; &lt;p&gt;Il a écrit une trentaine de dialogues, dont les plus célèbres sont : La République (justice, politique, éducation). Phédon (immortalité de l'âme). &lt;a href="https://www.youtube.com/watch?v=Mbtxr1hsP7A"  title="  Ce que Le Banquet de Platon révèle sur l'amour  par Resumon ça"&gt;Le Banquet &lt;/a&gt;(amour et beauté). Phèdre (rhétorique et amour). Ménon (vertu et réminiscence). Timée (cosmologie et physique). Critias (mythe de l'Atlantide). Apologie de Socrate (défense de Socrate lors de son procès). Phédon (immortalité de l'âme). &lt;/p&gt; &lt;p&gt;  Dans son ouvrage  le plus célèbre  &lt;a href="https://www.youtube.com/watch?v=qSrvZvjPG_w&amp;t=811s&amp;ab_channel=Kosmos"  style="color:#88A1E9" title="La République, c'est quoi par Kosmos"&gt;La République&lt;/a&gt;, il décrit sa vision d'une société idéale où les dirigeants sont des philosophes-rois et où la justice et la vertu sont les principes fondamentaux. Il y présente une métaphore de la condition humaine, l'allégorie de la &lt;a href="https://www.youtube.com/watch?v=N519gbEXbbw&amp;t=13s&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9" title="L'allégorie de la Caverne par le Précepteur "&gt;La Caverne&lt;/a&gt;, lieu où des gens vivent et où ils ne voient que des ombres projetées sur les murs en croyant que c'est la réalité.&lt;/p&gt; &lt;p&gt; Il reste une figure centrale de la philosophie, dont les idées continuent d'inspirer et de provoquer la réflexion. Sa quête de la vérité, sa vision idéaliste et sa méthode dialectique en font un penseur intemporel. &lt;/p&gt;   &lt;audio controls title="Platon et la politique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-20.11.2025-ITEMA_24317262-2025C48904S0324-NET_MFC_E07CEF22-5D42-4358-8035-01B7B6D438EF-21-f49f7fca67cbafd4d44c5b4c00fead78.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="I33" s="9"/>
+      <c r="J33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Platonisme ; Dualisme</t>
         </is>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P31">
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P33">
         <v>3</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="n">
+    <row r="34" customFormat="false" ht="206.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
         <v>-412</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B34" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D34" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diog%C3%A8ne_de_Sinope"   title="Diogène de Sinope par Wikipédia"&gt; DIOGÈNE DE SINOPE &lt;/a&gt; était un philosophe grec antique connu pour son mode de vie ascétique et ses provocations intellectuelles. Il est souvent surnommé "Diogène le Cynique" en raison de son affiliation à l'école de pensée cynique, qui prônait le rejet des conventions sociales, le détachement des désirs matériels et une vie en accord avec la nature. Il vivait une vie extrêmement simple et minimaliste et rejetait les besoins conventionnels et matérialistes, préférant se contenter de peu. Il est célèbre pour avoir vécu dans un tonneau (ou grand récipient) à Athènes. &lt;/p&gt;
 &lt;p&gt;Diogène était connu pour &lt;a href="https://www.philo5.com/Les%20philosophes%20Textes/Diogene_OntDitSur.htm#_ftn4"  title="Diogène de Sinope d'après Diogène Laërce par philo5"&gt; défier les normes&lt;/a&gt; sociales et philosophiques de son époque en utilisant souvent des actions et des paroles provocantes pour critiquer la société, remettre en question les valeurs établies et provoquer des réflexions profondes. Par exemple, il se promenait en plein jour avec une lanterne allumée à la recherche d'un "homme honnête", soulignant ainsi l'absence de personnes vertueuses.  &lt;a href="https://www.youtube.com/watch?v=aNUDOhr9yLs"  title=" La philosophie Diogène de Sinope par parole de philosophes "&gt; Il croyait &lt;/a&gt; que la société et ses institutions étaient corrompues et prônait la simplicité et la nature, rejetant les normes artificielles et les désirs superficiels qui causaient souvent des souffrances et des conflits.&lt;/p&gt;
@@ -4748,170 +4885,76 @@
 &lt;p&gt;Ses enseignements exacts  ne sont pas bien documentés, car peu de ses écrits ont survécu. Cependant, &lt;a href="https://www.youtube.com/watch?v=epW-8gZwQEk&amp;ab_channel=R%C3%A9sonance%5Bs%5D"  title="Diogène de Sinope, le chien royal par Résonance"&gt;son mode de vie&lt;/a&gt; et ses actions ont eu un impact durable sur la philosophie occidentale en remettant en question les valeurs conventionnelles et en mettant l'accent sur la simplicité et l'authenticité. &lt;/p&gt;   &lt;audio controls title="Osons le cynisme ! retour à Diogène par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2014/02/s09/LES_NOUVEAUX_CHEMINS_DE_LA_CONNAISSANCE.NET_FC_4EBE3123-A5B5-49FF-96B5-DB4346498425.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F34" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G34" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/sinope-mini.webp</t>
         </is>
-      </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="n">
-        <v>-408</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="n">
-        <v>-407</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Speusippe"  style="color:#6A142A"  title=" Wikipedia"&gt;SPEUSIPPE&lt;/a&gt; était un philosophe grec connu pour être le neveu de Platon et pour avoir succédé à ce dernier à la tête de l'Académie, l'école philosophique qu'il avait fondé. Il est souvent considéré comme un philosophe qui a cherché à développer et à modifier les idées de Platon plutôt que de les suivre strictement. &lt;/p&gt; &lt;p&gt; Il a rejeté la théorie des Formes de Platon, qui postulait l'existence d'entités immuables et éternelles (les Formes) comme fondement de la réalité. À la place, il a proposé une vision plus naturaliste et mathématique de la réalité, mettant l'accent sur les nombres et les  &lt;a href="https://remacle.org/bloodwolf/philosophes/speusippe/fragments.htm"  style="color:#88A1E9" title=" Speusippe fragment par remacle"&gt;principes mathématiques&lt;/a&gt; comme fondements de l'univers.  Il a également développé une théorie des principes premiers, où il distinguait entre l'Un (qui représente l'unité et la simplicité) et la Multiplicité (qui représente la diversité et la complexité). Ces principes étaient considérés comme les fondements de toute existence. &lt;/p&gt; Il a soutenu que le bonheur ne réside pas dans la possession de biens matériels ou de plaisirs, mais dans la réalisation d'une &lt;a href="https://remacle.org/bloodwolf/philosophes/laerce/4speusippe.htm"  style="color:#88A1E9" title=" Speusippe livre IV par Remacle"&gt;harmonie intérieure&lt;/a&gt; et d'une vie vertueuse. Il a mis l'accent sur l'importance de la modération et de l'équilibre dans la vie humaine. Il s'est intéressé à la classification des êtres vivants et a tenté de développer un système pour organiser et comprendre la diversité du monde naturel. Bien que ses travaux dans ce domaine soient peu connus, ils montrent un intérêt pour l'observation et la systématisation de la nature. &lt;/p&gt; &lt;p&gt; Il a dirigé l'Académie pendant environ huit ans, mais son influence a été éclipsée par celle de son successeur, Xénocrate, et par la postérité de Platon. Ses écrits ont été perdus, et nous ne connaissons sa pensée qu'à travers les témoignages d'autres philosophes, tels qu'Aristote, qui a critiqué certaines de ses idées.&lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>260</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="152.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
-        <v>-405</v>
+        <v>-408</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eubulide"  style="color:#6A142A"  title=" Wikipedia"&gt;EUBULIDE de Milet&lt;/a&gt;  était un philosophe grec antique appartenant à l'école mégarique, une école de philosophie fondée par Euclide de Mégare, un disciple de Socrate. L'école mégarique est connue pour son intérêt pour la logique et les arguments dialectiques. &lt;/p&gt; &lt;p&gt; Eubulide est surtout connu pour ses paradoxes, qui ont été conçus pour mettre en lumière les difficultés et les ambiguïtés dans le langage et la pensée. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=CIgkTJYt1b0"  style="color:#88A1E9" title="Le paradoxe du menteur par Logique Contradictoire"&gt;Le paradoxe du menteur&lt;/a&gt; : Ce paradoxe met en scène une personne qui déclare "Je mens". Si la personne dit la vérité, alors elle ment, ce qui est une contradiction. Si elle ment, alors elle dit la vérité, ce qui est également une contradiction. Ce paradoxe a des implications profondes pour la logique et la sémantique. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=2tn152iCDpk"  title="Le paradoxe du Sorite par Philosophie Analytique"&gt;Le paradoxe du sorite&lt;/a&gt; (ou paradoxe du tas) : Ce paradoxe questionne à quel moment un tas de grains cesse d'être un tas lorsqu'on enlève un grain à la fois. Il soulève des questions sur les limites floues et les définitions vagues. &lt;/p&gt; &lt;p&gt;Le paradoxe de l'électre : Ce paradoxe explore les problèmes de connaissance et de reconnaissance. Si Electre sait que son frère Oreste est dans la pièce, mais ne reconnaît pas Oreste lorsqu'elle le voit, peut-on dire qu'elle sait vraiment qu'il est là ? &lt;/p&gt; &lt;p&gt;Le paradoxe du voilé : Ce paradoxe pose la question de savoir si on peut reconnaître quelqu'un qui est voilé. Si on ne peut pas le reconnaître, comment peut-on savoir que c'est la même personne ? &lt;/p&gt; &lt;p&gt;  Les paradoxes d'Eubulide ont eu une influence durable sur la philosophie, en particulier dans les domaines de la logique, de la sémantique et de l'épistémologie. Ils ont été étudiés et discutés par de nombreux philosophes ultérieurs, y compris les stoïciens et les sceptiques, et continuent d'être un sujet de débat dans la philosophie contemporaine. &lt;/p&gt; </t>
-        </is>
+        <v>247</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>248</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>267</v>
+        <v>249</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>250</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Socratisme ; École mégarique</t>
-        </is>
+        <v>252</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4919,50 +4962,45 @@
         </is>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
-        <v>-400</v>
+        <v>-407</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ar%C3%A9t%C3%A9_de_Cyr%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;ARÉTÉ de Cyrène&lt;/a&gt; (IVe siècle av. J.-C.) est l’une des premières &lt;a href="https://www.youtube.com/watch?v=9vy8w9K-YgQ" style="color:#88A1E9" title="Arete Of Cyrene 1st Woman Philosopher Before BC par Celebrities World"&gt;femmes philosophes&lt;/a&gt; connues de la Grèce antique. Fille d’Aristippe de Cyrène, disciple de Socrate et fondateur de l’école cyrénaïque, elle reçoit de son père une formation philosophique et prend une place centrale dans la transmission de sa doctrine.&lt;/p&gt; &lt;p&gt;Nous la connaissons surtout par l’historien Diogène Laërce et par d’autres sources tardives, et aucun de ses écrits ne nous est parvenu. Son rôle principal est d’avoir formé son propre fils, Aristippe le Jeune, surnommé « l’instruit par sa mère » (&lt;em&gt;Mêtrodidaktos&lt;/em&gt;), qui donnera à l’école sa forme systématique. &lt;a href="https://www.youtube.com/watch?v=Rp7sm07EJBY&amp;t=324s" style="color:#88A1E9" title="Les Cyrénaîsme par Alain Bajoumée"&gt;Les cyrénaïques&lt;/a&gt; font du plaisir le seul bien et de la douleur le seul mal. Ils fondent cette morale sur une théorie de la connaissance : nous ne connaissons que nos propres sensations, non les choses qui les causent. Le plaisir est un « mouvement doux », la douleur un « mouvement rude » ; le plaisir présent, corporel et vif, est le seul dont nous soyons sûrs, car le passé n’est plus et l’avenir est incertain. Mais le sage cyrénaïque n’est pas un débauché : il cherche à maîtriser le plaisir sans s’en rendre esclave, et à rester libre en toutes circonstances. Une lettre attribuée à Aristippe, sans doute apocryphe, conseille à Arété de gérer ses biens avec mesure et de veiller à l’éducation de son fils.&lt;/p&gt; &lt;p&gt;Des auteurs plus tardifs lui ont prêté une longue carrière d’enseignante et de nombreux livres, sans preuve. Elle reste cependant le symbole de la place des femmes dans la philosophie antique, aux côtés d’Hipparchia ou de Théano.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Speusippe"  style="color:#6A142A"  title=" Wikipedia"&gt;SPEUSIPPE&lt;/a&gt; était un philosophe grec connu pour être le neveu de Platon et pour avoir succédé à ce dernier à la tête de l'Académie, l'école philosophique qu'il avait fondé. Il est souvent considéré comme un philosophe qui a cherché à développer et à modifier les idées de Platon plutôt que de les suivre strictement. &lt;/p&gt; &lt;p&gt; Il a rejeté la théorie des Formes de Platon, qui postulait l'existence d'entités immuables et éternelles (les Formes) comme fondement de la réalité. À la place, il a proposé une vision plus naturaliste et mathématique de la réalité, mettant l'accent sur les nombres et les  &lt;a href="https://remacle.org/bloodwolf/philosophes/speusippe/fragments.htm"  style="color:#88A1E9" title=" Speusippe fragment par remacle"&gt;principes mathématiques&lt;/a&gt; comme fondements de l'univers.  Il a également développé une théorie des principes premiers, où il distinguait entre l'Un (qui représente l'unité et la simplicité) et la Multiplicité (qui représente la diversité et la complexité). Ces principes étaient considérés comme les fondements de toute existence. &lt;/p&gt; Il a soutenu que le bonheur ne réside pas dans la possession de biens matériels ou de plaisirs, mais dans la réalisation d'une &lt;a href="https://remacle.org/bloodwolf/philosophes/laerce/4speusippe.htm"  style="color:#88A1E9" title=" Speusippe livre IV par Remacle"&gt;harmonie intérieure&lt;/a&gt; et d'une vie vertueuse. Il a mis l'accent sur l'importance de la modération et de l'équilibre dans la vie humaine. Il s'est intéressé à la classification des êtres vivants et a tenté de développer un système pour organiser et comprendre la diversité du monde naturel. Bien que ses travaux dans ce domaine soient peu connus, ils montrent un intérêt pour l'observation et la systématisation de la nature. &lt;/p&gt; &lt;p&gt; Il a dirigé l'Académie pendant environ huit ans, mais son influence a été éclipsée par celle de son successeur, Xénocrate, et par la postérité de Platon. Ses écrits ont été perdus, et nous ne connaissons sa pensée qu'à travers les témoignages d'autres philosophes, tels qu'Aristote, qui a critiqué certaines de ses idées.&lt;/p&gt; </t>
         </is>
       </c>
       <c r="F36" s="7" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
+        <v>261</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4970,45 +5008,47 @@
         </is>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="152.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
-        <v>-396</v>
+        <v>-405</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/X%C3%A9nocrate"  style="color:#6A142A"  title=" Wikipedia"&gt;XÉNOCRATE&lt;/a&gt; était un philosophe grec, disciple de Platon et un membre éminent de l'Académie platonicienne, qu'il dirigea après Speusippe. Né à Chalcédoine, il dirige l’école de 339 av. J.-C. à sa mort, en 314. Il est considéré comme un représentant de la "vieille Académie", c'est-à-dire de la période où l'Académie platonicienne restait proche des enseignements originaux de Platon. Sa philosophie s'inscrit dans cette tradition, mais il a  développé des  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1948_num_50_3_3399" style="color:#88A1E9" title="Xénocrate et les Orphiques  par persée"&gt;idées originales&lt;/a&gt;, notamment en métaphysique, en éthique et en cosmologie. &lt;/p&gt; &lt;p&gt; Il a interprété les Idées comme des nombres, une approche qui influencera plus tard le néoplatonisme. Il a divisé la réalité en trois niveaux : le monde intelligible (celui des Idées), le monde sensible (celui des phénomènes) et le monde intermédiaire (celui de l'âme et des mathématiques). Il a également développé une cosmologie inspirée de Platon, en particulier du  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1953_num_66_309_3305" style="color:#88A1E9" title=" Les dimensions de l'univers platonicien d'après Timée en 5 mn par persée"&gt;Timée&lt;/a&gt;, et a soutenu que l'univers était organisé de manière harmonieuse par une intelligence divine. Il définit l’âme comme « un nombre qui se meut lui-même », et serait le premier à avoir divisé la philosophie en trois parties : la physique, l’éthique et la logique. &lt;/p&gt; &lt;p&gt; Il  a développé une conception hiérarchisée des dieux, distinguant les dieux suprêmes (comme le Démiurge du Timée de Platon) des dieux inférieurs et des démons. Il  a joué un rôle important dans la transmission et l'interprétation de la philosophie platonicienne. Bien que sa pensée ait été éclipsée par celle d'Aristote et des néoplatoniciens, il a influencé des philosophes ultérieurs comme Plotin et Proclus. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eubulide"  style="color:#6A142A"  title=" Wikipedia"&gt;EUBULIDE de Milet&lt;/a&gt;  était un philosophe grec antique appartenant à l'école mégarique, une école de philosophie fondée par Euclide de Mégare, un disciple de Socrate. L'école mégarique est connue pour son intérêt pour la logique et les arguments dialectiques. &lt;/p&gt; &lt;p&gt; Eubulide est surtout connu pour ses paradoxes, qui ont été conçus pour mettre en lumière les difficultés et les ambiguïtés dans le langage et la pensée. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=CIgkTJYt1b0"  style="color:#88A1E9" title="Le paradoxe du menteur par Logique Contradictoire"&gt;Le paradoxe du menteur&lt;/a&gt; : Ce paradoxe met en scène une personne qui déclare "Je mens". Si la personne dit la vérité, alors elle ment, ce qui est une contradiction. Si elle ment, alors elle dit la vérité, ce qui est également une contradiction. Ce paradoxe a des implications profondes pour la logique et la sémantique. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=2tn152iCDpk"  title="Le paradoxe du Sorite par Philosophie Analytique"&gt;Le paradoxe du sorite&lt;/a&gt; (ou paradoxe du tas) : Ce paradoxe questionne à quel moment un tas de grains cesse d'être un tas lorsqu'on enlève un grain à la fois. Il soulève des questions sur les limites floues et les définitions vagues. &lt;/p&gt; &lt;p&gt;Le paradoxe de l'électre : Ce paradoxe explore les problèmes de connaissance et de reconnaissance. Si Electre sait que son frère Oreste est dans la pièce, mais ne reconnaît pas Oreste lorsqu'elle le voit, peut-on dire qu'elle sait vraiment qu'il est là ? &lt;/p&gt; &lt;p&gt;Le paradoxe du voilé : Ce paradoxe pose la question de savoir si on peut reconnaître quelqu'un qui est voilé. Si on ne peut pas le reconnaître, comment peut-on savoir que c'est la même personne ? &lt;/p&gt; &lt;p&gt;  Les paradoxes d'Eubulide ont eu une influence durable sur la philosophie, en particulier dans les domaines de la logique, de la sémantique et de l'épistémologie. Ils ont été étudiés et discutés par de nombreux philosophes ultérieurs, y compris les stoïciens et les sceptiques, et continuent d'être un sujet de débat dans la philosophie contemporaine. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F37" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>285</v>
+        <v>266</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>267</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>236</v>
+        <v>269</v>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; École mégarique</t>
+        </is>
       </c>
       <c r="M37" s="2" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -5016,293 +5056,296 @@
         </is>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
-        <v>-385</v>
+        <v>-400</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>291</v>
+        <v>273</v>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ar%C3%A9t%C3%A9_de_Cyr%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;ARÉTÉ de Cyrène&lt;/a&gt; (IVe siècle av. J.-C.) est l’une des premières &lt;a href="https://www.youtube.com/watch?v=9vy8w9K-YgQ" style="color:#88A1E9" title="Arete Of Cyrene 1st Woman Philosopher Before BC par Celebrities World"&gt;femmes philosophes&lt;/a&gt; connues de la Grèce antique. Fille d’Aristippe de Cyrène, disciple de Socrate et fondateur de l’école cyrénaïque, elle reçoit de son père une formation philosophique et prend une place centrale dans la transmission de sa doctrine.&lt;/p&gt; &lt;p&gt;Nous la connaissons surtout par l’historien Diogène Laërce et par d’autres sources tardives, et aucun de ses écrits ne nous est parvenu. Son rôle principal est d’avoir formé son propre fils, Aristippe le Jeune, surnommé « l’instruit par sa mère » (&lt;em&gt;Mêtrodidaktos&lt;/em&gt;), qui donnera à l’école sa forme systématique. &lt;a href="https://www.youtube.com/watch?v=Rp7sm07EJBY&amp;t=324s" style="color:#88A1E9" title="Les Cyrénaîsme par Alain Bajoumée"&gt;Les cyrénaïques&lt;/a&gt; font du plaisir le seul bien et de la douleur le seul mal. Ils fondent cette morale sur une théorie de la connaissance : nous ne connaissons que nos propres sensations, non les choses qui les causent. Le plaisir est un « mouvement doux », la douleur un « mouvement rude » ; le plaisir présent, corporel et vif, est le seul dont nous soyons sûrs, car le passé n’est plus et l’avenir est incertain. Mais le sage cyrénaïque n’est pas un débauché : il cherche à maîtriser le plaisir sans s’en rendre esclave, et à rester libre en toutes circonstances. Une lettre attribuée à Aristippe, sans doute apocryphe, conseille à Arété de gérer ses biens avec mesure et de veiller à l’éducation de son fils.&lt;/p&gt; &lt;p&gt;Des auteurs plus tardifs lui ont prêté une longue carrière d’enseignante et de nombreux livres, sans preuve. Elle reste cependant le symbole de la place des femmes dans la philosophie antique, aux côtés d’Hipparchia ou de Théano.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F38" s="7" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>295</v>
+        <v>279</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="39" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
-        <v>-384</v>
+        <v>-396</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristote"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTOTE&lt;/a&gt; est l'un des philosophes les plus influents de l'histoire occidentale. Disciple de Platon et précepteur d'Alexandre le Grand, il a contribué à de nombreux domaines de la connaissance, notamment la philosophie, la science, la logique,  &lt;a href="https://www.youtube.com/watch?v=Zo1J19uk-Cc" style="color:#88A1E9"   title=" L'éthique de la vertu d'Aristote par Coursitout"&gt; l'éthique&lt;/a&gt;, la politique, la métaphysique, la biologie et la physique. Il a fondé sa propre école, &lt;a href="https://fr.wikipedia.org/wiki/Lyc%C3%A9e_(%C3%A9cole_philosophique)" style="color:#88A1E9"   title="Le Lycée par wikipedia"&gt;le Lycée&lt;/a&gt;. &lt;/p&gt;&lt;p&gt; Ses travaux sont organisés en plusieurs catégories : &lt;/p&gt;&lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=4fhmo_C1VIA" style="color:#88A1E9"   title="ARISTOTE - Les principes de la logique par le Précepteur"&gt; La Logique&lt;/a&gt; : Il est considéré comme le père de la logique formelle.  Il établit une classification des concepts en dix catégories (substance, quantité, qualité, relation, etc.). &lt;/p&gt; &lt;p&gt;La Métaphysique : Il  explore la nature de l'être et de la réalité dans son ouvrage Métaphysique. Il introduit les concepts de &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1946_num_44_3_4064" style="color:#88A1E9"   title="        La première doctrine de la substance : la substance selon Aristotee par  Persée"&gt;"substance"&lt;/a&gt;  (ce qui existe par soi-même) et d'"accident" (ce qui modifie la substance). Il propose une théorie des quatre causes (matérielle, formelle, efficiente et finale) pour expliquer pourquoi les choses existent et changent. &lt;/p&gt; &lt;p&gt;La Politique :  Dans "Politique", il analyse les différentes formes de gouvernement (monarchie, aristocratie, démocratie) et leurs dérives (tyrannie, oligarchie, démagogie). Il défend l'idée que l'homme est un "animal politique" destiné à vivre en société. &lt;/p&gt; La Science et la Biologie : Contrairement à Platon, qui privilégie les idées abstraites, il s'appuie sur l'observation et l'expérience pour étudier la nature.  Il est l'un des premiers à classer les animaux selon leurs caractéristiques communes. &lt;/p&gt; &lt;p&gt;Rhétorique :   Il étudie l'art de persuader, distinguant trois types de preuves : l'ethos (caractère de l'orateur), le pathos (émotions du public) et le logos (argumentation logique). &lt;/p&gt; &lt;p&gt; Il  privilégie &lt;a href="https://www.youtube.com/watch?v=CdOxw_GRKWk&amp;t=173s&amp;ab_channel=CULTUREG" style="color:#88A1E9"   title="L'Empirisme par Culture G"&gt;l' Empirisme&lt;/a&gt;  par l'observation et l'expérience pour comprendre le monde, contrairement à l'idéalisme de Platon. Il  croit que tout dans la nature a une fin ou un but (telos), ce qui influence sa vision du monde. &lt;/p&gt; &lt;p&gt;  Dans son oeuvre "l'Organon", il développe des concepts de logique comme le syllogisme, un raisonnement déductif composé de deux prémisses et d'une conclusion. &lt;/p&gt; &lt;p&gt; Il a également étudié les phénomènes physiques tels que la chute des corps et le mouvement des astres et a développé une logique formelle, qui est encore utilisée aujourd'hui.&lt;/p&gt; &lt;p&gt; Il a soutenu que le but de la vie humaine est l'accomplissement de la "vertu", qui est un état de caractère qui permet de vivre de manière équilibrée et heureuse ainsi qu'une théorie de la politique où il dit que &lt;a href="https://www.youtube.com/watch?v=djOrZrEDMto&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'homme est un animal politique par le Précepteur"&gt; L'homme est un animal politique&lt;/a&gt; et qu'il existe différents types de régimes  (démocratie, oligarchie, monarchie) et que le meilleur est celui qui est gouverné par des personnes vertueuses.   &lt;/p&gt;         &lt;/p&gt; &lt;p&gt;                       &lt;audio controls title="Raison et réalité: l'être avec Aristote par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-07.05.2022-ITEMA_23018730-2020C3372E0467-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;                                            
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/X%C3%A9nocrate"  style="color:#6A142A"  title=" Wikipedia"&gt;XÉNOCRATE&lt;/a&gt; était un philosophe grec, disciple de Platon et un membre éminent de l'Académie platonicienne, qu'il dirigea après Speusippe. Né à Chalcédoine, il dirige l’école de 339 av. J.-C. à sa mort, en 314. Il est considéré comme un représentant de la "vieille Académie", c'est-à-dire de la période où l'Académie platonicienne restait proche des enseignements originaux de Platon. Sa philosophie s'inscrit dans cette tradition, mais il a  développé des  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1948_num_50_3_3399" style="color:#88A1E9" title="Xénocrate et les Orphiques  par persée"&gt;idées originales&lt;/a&gt;, notamment en métaphysique, en éthique et en cosmologie. &lt;/p&gt; &lt;p&gt; Il a interprété les Idées comme des nombres, une approche qui influencera plus tard le néoplatonisme. Il a divisé la réalité en trois niveaux : le monde intelligible (celui des Idées), le monde sensible (celui des phénomènes) et le monde intermédiaire (celui de l'âme et des mathématiques). Il a également développé une cosmologie inspirée de Platon, en particulier du  &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1953_num_66_309_3305" style="color:#88A1E9" title=" Les dimensions de l'univers platonicien d'après Timée en 5 mn par persée"&gt;Timée&lt;/a&gt;, et a soutenu que l'univers était organisé de manière harmonieuse par une intelligence divine. Il définit l’âme comme « un nombre qui se meut lui-même », et serait le premier à avoir divisé la philosophie en trois parties : la physique, l’éthique et la logique. &lt;/p&gt; &lt;p&gt; Il  a développé une conception hiérarchisée des dieux, distinguant les dieux suprêmes (comme le Démiurge du Timée de Platon) des dieux inférieurs et des démons. Il  a joué un rôle important dans la transmission et l'interprétation de la philosophie platonicienne. Bien que sa pensée ait été éclipsée par celle d'Aristote et des néoplatoniciens, il a influencé des philosophes ultérieurs comme Plotin et Proclus. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F39" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"La philosophie d'Aristote" par Voyages Endormis</t>
-        </is>
+        <v>284</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aristotélisme ; Essentialisme</t>
-        </is>
+        <v>174</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="40" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
-        <v>-380</v>
+        <v>-385</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristippe_le_Jeune"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTIPPE le Jeune&lt;/a&gt; était un philosophe grec moins connue que son grand-père, Aristippe de Cyrène, fondateur de l'école &lt;a href="https://www.youtube.com/watch?v=I5PEbJhoUEs" style="color:#88A1E9" title="Aristippe le Cyrénaïque vu sous l'angle d'Ibiza par Chroniques philosophique "&gt;philosophique cyrénaïque&lt;/a&gt;. Les informations sur lui sont relativement limitées et souvent entremêlées avec celles de son grand-père, ce qui rend difficile une distinction claire entre leurs contributions respectives. &lt;/p&gt; &lt;p&gt;  Il  est souvent crédité d'avoir systématisé et formalisé les enseignements de son grand-père, contribuant ainsi à l'évolution de la pensée cyrénaïque. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=QNRG_j24a5U" style="color:#88A1E9" title="L'Hédonisme par la Philosophie du Bonheur "&gt;Hédonisme&lt;/a&gt; : Comme son grand-père, il soutenait que le plaisir est le but ultime de la vie. Cependant, il a peut-être développé une approche plus nuancée, en distinguant entre différents types de plaisirs et en mettant l'accent sur la modération. &lt;/p&gt;
-&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pr%C3%A9sentisme" style="color:#88A1E9" title="Le Présentisme par Wikipedia "&gt;Présentisme&lt;/a&gt; : Il croyait en l'importance de vivre dans le moment présent. Il considérait que le passé est irréversible et le futur incertain, donc le présent est le seul moment où l'on peut véritablement expérimenter le plaisir. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.axiologie.org/nihilisme-definition/valeur-subjective/proposition-9.html" style="color:#88A1E9" title="Le subjectivisme par Axiologie "&gt;Subjectivisme&lt;/a&gt; : Il a également contribué à la théorie de la connaissance des cyrénaïques, qui soutient que la seule certitude que nous avons est celle de nos propres sensations et expériences subjectives. Cette idée a des implications profondes pour l'épistémologie et la philosophie de l'esprit. &lt;/p&gt; &lt;p&gt; Il est une figure importante dans l'histoire de la philosophie grecque, principalement pour son rôle dans la systématisation et la promotion des idées hédonistes de l'école cyrénaïque. &lt;/p&gt; </t>
-        </is>
+        <v>290</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>291</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>310</v>
+        <v>293</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>294</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="n">
+        <v>-384</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristote"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTOTE&lt;/a&gt; est l'un des philosophes les plus influents de l'histoire occidentale. Disciple de Platon et précepteur d'Alexandre le Grand, il a contribué à de nombreux domaines de la connaissance, notamment la philosophie, la science, la logique,  &lt;a href="https://www.youtube.com/watch?v=Zo1J19uk-Cc" style="color:#88A1E9"   title=" L'éthique de la vertu d'Aristote par Coursitout"&gt; l'éthique&lt;/a&gt;, la politique, la métaphysique, la biologie et la physique. Il a fondé sa propre école, &lt;a href="https://fr.wikipedia.org/wiki/Lyc%C3%A9e_(%C3%A9cole_philosophique)" style="color:#88A1E9"   title="Le Lycée par wikipedia"&gt;le Lycée&lt;/a&gt;. &lt;/p&gt;&lt;p&gt; Ses travaux sont organisés en plusieurs catégories : &lt;/p&gt;&lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=4fhmo_C1VIA" style="color:#88A1E9"   title="ARISTOTE - Les principes de la logique par le Précepteur"&gt; La Logique&lt;/a&gt; : Il est considéré comme le père de la logique formelle.  Il établit une classification des concepts en dix catégories (substance, quantité, qualité, relation, etc.). &lt;/p&gt; &lt;p&gt;La Métaphysique : Il  explore la nature de l'être et de la réalité dans son ouvrage Métaphysique. Il introduit les concepts de &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1946_num_44_3_4064" style="color:#88A1E9"   title="        La première doctrine de la substance : la substance selon Aristotee par  Persée"&gt;"substance"&lt;/a&gt;  (ce qui existe par soi-même) et d'"accident" (ce qui modifie la substance). Il propose une théorie des quatre causes (matérielle, formelle, efficiente et finale) pour expliquer pourquoi les choses existent et changent. &lt;/p&gt; &lt;p&gt;La Politique :  Dans "Politique", il analyse les différentes formes de gouvernement (monarchie, aristocratie, démocratie) et leurs dérives (tyrannie, oligarchie, démagogie). Il défend l'idée que l'homme est un "animal politique" destiné à vivre en société. &lt;/p&gt; La Science et la Biologie : Contrairement à Platon, qui privilégie les idées abstraites, il s'appuie sur l'observation et l'expérience pour étudier la nature.  Il est l'un des premiers à classer les animaux selon leurs caractéristiques communes. &lt;/p&gt; &lt;p&gt;Rhétorique :   Il étudie l'art de persuader, distinguant trois types de preuves : l'ethos (caractère de l'orateur), le pathos (émotions du public) et le logos (argumentation logique). &lt;/p&gt; &lt;p&gt; Il  privilégie &lt;a href="https://www.youtube.com/watch?v=CdOxw_GRKWk&amp;t=173s&amp;ab_channel=CULTUREG" style="color:#88A1E9"   title="L'Empirisme par Culture G"&gt;l' Empirisme&lt;/a&gt;  par l'observation et l'expérience pour comprendre le monde, contrairement à l'idéalisme de Platon. Il  croit que tout dans la nature a une fin ou un but (telos), ce qui influence sa vision du monde. &lt;/p&gt; &lt;p&gt;  Dans son oeuvre "l'Organon", il développe des concepts de logique comme le syllogisme, un raisonnement déductif composé de deux prémisses et d'une conclusion. &lt;/p&gt; &lt;p&gt; Il a également étudié les phénomènes physiques tels que la chute des corps et le mouvement des astres et a développé une logique formelle, qui est encore utilisée aujourd'hui.&lt;/p&gt; &lt;p&gt; Il a soutenu que le but de la vie humaine est l'accomplissement de la "vertu", qui est un état de caractère qui permet de vivre de manière équilibrée et heureuse ainsi qu'une théorie de la politique où il dit que &lt;a href="https://www.youtube.com/watch?v=djOrZrEDMto&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'homme est un animal politique par le Précepteur"&gt; L'homme est un animal politique&lt;/a&gt; et qu'il existe différents types de régimes  (démocratie, oligarchie, monarchie) et que le meilleur est celui qui est gouverné par des personnes vertueuses.   &lt;/p&gt;         &lt;/p&gt; &lt;p&gt;                       &lt;audio controls title="Raison et réalité: l'être avec Aristote par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-07.05.2022-ITEMA_23018730-2020C3372E0467-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;                                            
+</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La philosophie d'Aristote" par Voyages Endormis</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="I41" s="9"/>
+      <c r="J41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aristotélisme ; Essentialisme</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="n">
+        <v>-380</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aristippe_le_Jeune"  style="color:#6A142A"  title=" Wikipedia"&gt;ARISTIPPE le Jeune&lt;/a&gt; était un philosophe grec moins connue que son grand-père, Aristippe de Cyrène, fondateur de l'école &lt;a href="https://www.youtube.com/watch?v=I5PEbJhoUEs" style="color:#88A1E9" title="Aristippe le Cyrénaïque vu sous l'angle d'Ibiza par Chroniques philosophique "&gt;philosophique cyrénaïque&lt;/a&gt;. Les informations sur lui sont relativement limitées et souvent entremêlées avec celles de son grand-père, ce qui rend difficile une distinction claire entre leurs contributions respectives. &lt;/p&gt; &lt;p&gt;  Il  est souvent crédité d'avoir systématisé et formalisé les enseignements de son grand-père, contribuant ainsi à l'évolution de la pensée cyrénaïque. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=QNRG_j24a5U" style="color:#88A1E9" title="L'Hédonisme par la Philosophie du Bonheur "&gt;Hédonisme&lt;/a&gt; : Comme son grand-père, il soutenait que le plaisir est le but ultime de la vie. Cependant, il a peut-être développé une approche plus nuancée, en distinguant entre différents types de plaisirs et en mettant l'accent sur la modération. &lt;/p&gt;
+&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pr%C3%A9sentisme" style="color:#88A1E9" title="Le Présentisme par Wikipedia "&gt;Présentisme&lt;/a&gt; : Il croyait en l'importance de vivre dans le moment présent. Il considérait que le passé est irréversible et le futur incertain, donc le présent est le seul moment où l'on peut véritablement expérimenter le plaisir. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.axiologie.org/nihilisme-definition/valeur-subjective/proposition-9.html" style="color:#88A1E9" title="Le subjectivisme par Axiologie "&gt;Subjectivisme&lt;/a&gt; : Il a également contribué à la théorie de la connaissance des cyrénaïques, qui soutient que la seule certitude que nous avons est celle de nos propres sensations et expériences subjectives. Cette idée a des implications profondes pour l'épistémologie et la philosophie de l'esprit. &lt;/p&gt; &lt;p&gt; Il est une figure importante dans l'histoire de la philosophie grecque, principalement pour son rôle dans la systématisation et la promotion des idées hédonistes de l'école cyrénaïque. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="I42" s="9"/>
+      <c r="J42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K42" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="L40" s="2" t="s">
+      <c r="L42" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="M42" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7">
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7">
         <v>-372</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">-288</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">vers 372 A JC - 288 A JC</t>
         </is>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D43" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ophraste"  style="color:#6A142A"  title=" Wikipedia"&gt;THÉOPHRASTE&lt;/a&gt; était un philosophe et naturaliste grec de l'Antiquité, souvent considéré comme le père de la botanique. Il fut un disciple d'Aristote et lui succéda à la tête du Lycée.  Il a écrit sur de nombreux sujets, notamment la logique, la métaphysique, l'éthique et la physique. Il a remis en question certaines des catégories aristotéliciennes et a exploré des questions liées à la causalité et à la nature de l'âme. &lt;/p&gt; &lt;p&gt; Il est célèbre pour ses  &lt;a href="https://www.youtube.com/watch?v=_8w0rzsq7io" style="color:#88A1E9" title="  Approches philosophique et botanique de la croissance végétale chez Théophraste par UMR 8546"&gt;travaux en botanique&lt;/a&gt;, qui constituent une avancée majeure dans l'étude scientifique des plantes. Ses deux principaux ouvrages sur le sujet sont : &lt;/p&gt;
 &lt;p&gt;"Histoire des plantes" : Une encyclopédie en neuf livres qui décrit les caractéristiques, les classifications et les utilisations des plantes. Il y aborde des sujets comme la morphologie, la reproduction et la croissance des végétaux. &lt;/p&gt; &lt;p&gt;"Causes des plantes" : Un traité en six livres qui explore les causes naturelles des phénomènes végétaux, comme la germination, la floraison et la fructification. &lt;/p&gt; &lt;p&gt; 
 Il a classé les plantes en fonction de leurs caractéristiques morphologiques et de leurs usages, jetant les bases de la &lt;a href="https://www.youtube.com/watch?v=E7uRf4fU_pk" style="color:#88A1E9" title="  Histoire de la botanique en 5 mn par Terre D'Avalonne"&gt;taxonomie végétale&lt;/a&gt;. Il a également étudié les relations entre les plantes et leur environnement, anticipant certaines idées de l'écologie moderne. &lt;/p&gt; &lt;p&gt; Outre la botanique, il a écrit sur des sujets variés tels que la minéralogie, la météorologie et la zoologie. Son ouvrage "Sur les pierres" est le premier traité sur les minéraux et leurs propriétés. &lt;/p&gt; &lt;p&gt;  Il  était connu pour son approche empirique et systématique, héritée d'Aristote. Il observait attentivement les phénomènes naturels et cherchait à les expliquer de manière rationnelle. Son style d'écriture était clair et méthodique, ce qui a contribué à la diffusion de ses idées. &lt;/p&gt;  </t>
         </is>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F43" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G43" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H43" s="9" t="s">
         <v>318</v>
-      </c>
-      <c r="I41" s="9"/>
-      <c r="J41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="n">
-        <v>-365</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Crat%C3%A8s_de_Th%C3%A8bes"  style="color:#6A142A"  title=" Wikipedia"&gt;CRATÈS de Thèbes&lt;/a&gt; était un philosophe  grec, disciple de Diogène de Sinope et contemporain d'Alexandre le Grand. Il est connu pour avoir radicalement transformé sa vie en renonçant à sa richesse et en adoptant un mode de vie simple et ascétique, conformément aux principes du &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=134s" style="color:#88A1E9" title=" Les Cynique en 5 mn par Alain Bajomée"&gt;Cynisme&lt;/a&gt;, une école philosophique qui prône la simplicité, l'autosuffisance et le mépris des conventions sociales. &lt;/p&gt; &lt;p&gt;Rejet des biens matériels : Il croyait que la richesse et les possessions matérielles étaient des sources de troubles et d'esclavage. En vivant dans la pauvreté volontaire, il cherchait à atteindre une liberté intérieure et une indépendance vis-à-vis des désirs superflus. &lt;/p&gt; &lt;p&gt;Vie en harmonie avec la nature : Comme les autres cyniques, il prônait un retour à une vie simple, en accord avec la nature. Il rejetait les artifices de la société et vivait de manière frugale, souvent dans la rue ou dans des lieux publics. &lt;/p&gt; &lt;p&gt;Critique des conventions sociales : Il remettait en question les normes sociales, y compris les institutions comme le mariage, la propriété et les hiérarchies sociales. Son mariage avec Hipparchia était une manifestation de cette critique, car il défiait les attentes traditionnelles. &lt;/p&gt; &lt;p&gt;Bienveillance et humour : Contrairement à Diogène, qui était souvent perçu comme provocateur et abrupt, il était connu pour sa gentillesse et son humour. Il était surnommé "l'ouvreur de portes" parce qu'il entrait chez les gens pour leur donner des conseils philosophiques, toujours avec bienveillance. &lt;/p&gt; &lt;p&gt; Ses œuvres étaient souvent satiriques et utilisaient l'humour pour transmettre des messages philosophiques. Par exemple, il a écrit un poème décrivant une cité idéale appelée "Péra", symbolisant une communauté où les biens matériels n'ont aucune importance. &lt;/p&gt; &lt;p&gt; Il est resté une figure respectée dans la tradition philosophique, notamment pour son engagement envers la vertu et sa capacité à vivre selon ses principes. Bien que le cynisme en tant qu'école philosophique ait décliné après l'Antiquité, les idées ont influencé d'autres courants, comme le stoïcisme, et continuent d'inspirer ceux qui cherchent à vivre une vie simple et authentique. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="I42" s="9"/>
-      <c r="J42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n">
-        <v>-365</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diodore_Cronos"  style="color:#6A142A"  title=" Wikipedia"&gt;Diodore CRONOS&lt;/a&gt; (mort vers 284 av. J.-C.) est un philosophe grec de l’école mégarique, l’un des plus grands logiciens de l’Antiquité. Né à Iasos, en Carie, il enseigne à Athènes et à Alexandrie. Il eut pour élève Zénon de Kition, le fondateur du stoïcisme, ainsi que ses cinq filles, toutes réputées pour leur talent en dialectique. Son surnom de « Cronos », du nom du vieux dieu, se moquait peut-être de lui comme d’un esprit démodé.&lt;/p&gt; &lt;p&gt;Il est surtout célèbre pour l’« argument dominateur », &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1961_num_74_349_3654_t1_0317_0000_2"  style="color:#88A1E9" title=" Le dominateur et les possibles par Persée"&gt;le Dominateur&lt;/a&gt;, que les Anciens jugeaient le plus redoutable des raisonnements. Il part de trois affirmations qui ne peuvent être vraies ensemble : tout ce qui est passé et vrai est nécessaire, car le passé ne peut plus changer ; l’impossible ne peut pas découler du possible ; et il existe un possible qui n’est pas et ne sera jamais vrai. Diodore rejette la troisième. Il en conclut que le possible est ce qui est ou qui sera, et que ce qui n’arrivera jamais n’était pas possible. Cette thèse semble mener au fatalisme, et les stoïciens, comme Chrysippe, ont cherché à y échapper. Diodore propose aussi une définition de l’implication : « si A, alors B » est vrai lorsqu’il n’a jamais été et ne sera jamais le cas que A soit vrai et B faux. Il défend enfin des arguments contre le mouvement : on ne peut jamais dire d’une chose « elle se meut », seulement « elle s’est mue ». La légende raconte qu’il mourut de dépit pour n’avoir pas su résoudre sur-le-champ une énigme posée par Stilpon devant le roi Ptolémée.&lt;/p&gt; &lt;p&gt;Au XXe siècle, le logicien Arthur Prior s’est inspiré de Diodore pour créer la logique du temps.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Socratisme ; École mégarique</t>
-        </is>
+        <v>319</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5310,43 +5353,45 @@
         </is>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="221.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
-        <v>-362</v>
+        <v>-365</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>338</v>
+        <v>323</v>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Crat%C3%A8s_de_Th%C3%A8bes"  style="color:#6A142A"  title=" Wikipedia"&gt;CRATÈS de Thèbes&lt;/a&gt; était un philosophe  grec, disciple de Diogène de Sinope et contemporain d'Alexandre le Grand. Il est connu pour avoir radicalement transformé sa vie en renonçant à sa richesse et en adoptant un mode de vie simple et ascétique, conformément aux principes du &lt;a href="https://www.youtube.com/watch?v=WFqZ8X9ziHI&amp;t=134s" style="color:#88A1E9" title=" Les Cynique en 5 mn par Alain Bajomée"&gt;Cynisme&lt;/a&gt;, une école philosophique qui prône la simplicité, l'autosuffisance et le mépris des conventions sociales. &lt;/p&gt; &lt;p&gt;Rejet des biens matériels : Il croyait que la richesse et les possessions matérielles étaient des sources de troubles et d'esclavage. En vivant dans la pauvreté volontaire, il cherchait à atteindre une liberté intérieure et une indépendance vis-à-vis des désirs superflus. &lt;/p&gt; &lt;p&gt;Vie en harmonie avec la nature : Comme les autres cyniques, il prônait un retour à une vie simple, en accord avec la nature. Il rejetait les artifices de la société et vivait de manière frugale, souvent dans la rue ou dans des lieux publics. &lt;/p&gt; &lt;p&gt;Critique des conventions sociales : Il remettait en question les normes sociales, y compris les institutions comme le mariage, la propriété et les hiérarchies sociales. Son mariage avec Hipparchia était une manifestation de cette critique, car il défiait les attentes traditionnelles. &lt;/p&gt; &lt;p&gt;Bienveillance et humour : Contrairement à Diogène, qui était souvent perçu comme provocateur et abrupt, il était connu pour sa gentillesse et son humour. Il était surnommé "l'ouvreur de portes" parce qu'il entrait chez les gens pour leur donner des conseils philosophiques, toujours avec bienveillance. &lt;/p&gt; &lt;p&gt; Ses œuvres étaient souvent satiriques et utilisaient l'humour pour transmettre des messages philosophiques. Par exemple, il a écrit un poème décrivant une cité idéale appelée "Péra", symbolisant une communauté où les biens matériels n'ont aucune importance. &lt;/p&gt; &lt;p&gt; Il est resté une figure respectée dans la tradition philosophique, notamment pour son engagement envers la vertu et sa capacité à vivre selon ses principes. Bien que le cynisme en tant qu'école philosophique ait décliné après l'Antiquité, les idées ont influencé d'autres courants, comme le stoïcisme, et continuent d'inspirer ceux qui cherchent à vivre une vie simple et authentique. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F44" s="7" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>342</v>
+        <v>201</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5354,43 +5399,47 @@
         </is>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
-        <v>-360</v>
+        <v>-365</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>355</v>
+        <v>329</v>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Diodore_Cronos"  style="color:#6A142A"  title=" Wikipedia"&gt;Diodore CRONOS&lt;/a&gt; (mort vers 284 av. J.-C.) est un philosophe grec de l’école mégarique, l’un des plus grands logiciens de l’Antiquité. Né à Iasos, en Carie, il enseigne à Athènes et à Alexandrie. Il eut pour élève Zénon de Kition, le fondateur du stoïcisme, ainsi que ses cinq filles, toutes réputées pour leur talent en dialectique. Son surnom de « Cronos », du nom du vieux dieu, se moquait peut-être de lui comme d’un esprit démodé.&lt;/p&gt; &lt;p&gt;Il est surtout célèbre pour l’« argument dominateur », &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1961_num_74_349_3654_t1_0317_0000_2"  style="color:#88A1E9" title=" Le dominateur et les possibles par Persée"&gt;le Dominateur&lt;/a&gt;, que les Anciens jugeaient le plus redoutable des raisonnements. Il part de trois affirmations qui ne peuvent être vraies ensemble : tout ce qui est passé et vrai est nécessaire, car le passé ne peut plus changer ; l’impossible ne peut pas découler du possible ; et il existe un possible qui n’est pas et ne sera jamais vrai. Diodore rejette la troisième. Il en conclut que le possible est ce qui est ou qui sera, et que ce qui n’arrivera jamais n’était pas possible. Cette thèse semble mener au fatalisme, et les stoïciens, comme Chrysippe, ont cherché à y échapper. Diodore propose aussi une définition de l’implication : « si A, alors B » est vrai lorsqu’il n’a jamais été et ne sera jamais le cas que A soit vrai et B faux. Il défend enfin des arguments contre le mouvement : on ne peut jamais dire d’une chose « elle se meut », seulement « elle s’est mue ». La légende raconte qu’il mourut de dépit pour n’avoir pas su résoudre sur-le-champ une énigme posée par Stilpon devant le roi Ptolémée.&lt;/p&gt; &lt;p&gt;Au XXe siècle, le logicien Arthur Prior s’est inspiré de Diodore pour créer la logique du temps.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F45" s="7" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>302</v>
+        <v>269</v>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; École mégarique</t>
+        </is>
       </c>
       <c r="M45" s="2" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -5398,47 +5447,43 @@
         </is>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="221.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
-        <v>-360</v>
+        <v>-362</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stilpon_de_M%C3%A9gare" style="color:#6A142A" title=" Wikipedia"&gt;STILPON de Mégare&lt;/a&gt; était est un philosophe, spécialisée dans la &lt;a href="https://fr.wikisource.org/wiki/L%E2%80%99Art_d%E2%80%99avoir_toujours_raison/La_dialectique_%C3%A9ristique" title="L’Art d’avoir toujours raison/La dialectique éristique par wikisource"&gt;dialectique de type éristique&lt;/a&gt;. Il est associé à l'école mégarique, fondée par Euclide de Mégare et était connu pour son éloquence et sa capacité à débattre, ce qui lui a valu une grande renommée dans le monde grec. &lt;/p&gt; &lt;p&gt; Les Mégariques étaient connus pour leur intérêt pour les paradoxes et les arguments sophistiqués. &lt;/p&gt; &lt;p&gt;Critique des universaux : Il est surtout connu pour sa critique des idées platoniciennes, en particulier la théorie des Formes. Il soutenait que les concepts généraux (comme "l'homme" ou "le bien") ne peuvent pas exister indépendamment des choses particulières. Pour lui, seules les choses individuelles sont réelles, et les universaux ne sont que des noms ou des constructions mentales. &lt;/p&gt; &lt;p&gt;Réfutation des catégories : Il a également critiqué la théorie des catégories d'Aristote, arguant que les distinctions entre les catégories (comme la substance, la qualité, la quantité) étaient artificielles et ne reflétaient pas la réalité. &lt;/p&gt; &lt;p&gt;Éthique et autosuffisance : Comme d'autres philosophes de son époque, il s'intéressait à l'éthique. Il prônait l'autosuffisance (autarkeia) et la tranquillité de l'âme (ataraxia). Il croyait que le bonheur pouvait être atteint en se libérant des désirs inutiles et en se concentrant sur ce qui est véritablement important. &lt;/p&gt; &lt;p&gt;Dialectique et logique : Il était un maître de la dialectique et utilisait souvent des arguments logiques pour déconstruire les positions de ses adversaires. Il était connu pour sa capacité à réduire les arguments de ses interlocuteurs à l'absurde, ce qui en faisait un redoutable débatteur. &lt;/p&gt; &lt;p&gt; Il était un philosophe dialecticien et éthique, dont les idées ont influencé plusieurs courants philosophiques ultérieurs. Bien que son œuvre ne nous soit pas parvenue directement, sa réputation de penseur rigoureux et son impact sur la philosophie antique sont indéniables. &lt;/p&gt;</t>
-        </is>
+        <v>337</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>338</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Socratisme ; École mégarique</t>
-        </is>
+        <v>252</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>342</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -5446,196 +5491,195 @@
         </is>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7">
-        <v>-350</v>
-      </c>
-      <c r="B47" s="7">
-        <v>-280</v>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">350 A JC - 280 A JC</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIPPARCHIA de Maronée</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hipparchia" title=" Wikipedia"&gt;HIPPARCHIA de Maronée&lt;/a&gt; était une philosophe cynique grecque, originaire de Maronée en Thrace. Issue d'une famille aisée, elle tomba amoureuse du philosophe Cratès de Thèbes, disciple de Diogène, qui avait renoncé à toute sa fortune. Ses parents s'opposèrent au mariage ; elle menaça de se tuer. Cratès lui-même tenta de la dissuader en lui montrant sa pauvreté, mais elle choisit de partager sa vie et ses idées.&lt;/p&gt; &lt;p&gt;Le cynisme prônait une vie simple, conforme à la nature, libérée des richesses, des honneurs et des conventions sociales jugées artificielles. Hipparchia vécut ainsi avec Cratès, en public et sans honte, portant le même manteau grossier que lui, et participa comme un homme aux banquets et aux discussions philosophiques, ce qui fit scandale à Athènes.&lt;/p&gt; &lt;p&gt;Selon Diogène Laërce, elle aurait &lt;a href="https://www.philomag.com/articles/hipparchie-la-vie-forte-des-cyniques" title="Hipparchie, “la vie forte des cyniques” par philosophie magazine"&gt;écrit des traités philosophiques&lt;/a&gt;, des lettres et des réponses à des questions posées au philosophe Théodore, aujourd'hui perdus. Elle eut avec Cratès au moins deux enfants et continua de mener une vie de philosophe. Pour les anciens, elle était la preuve qu'une femme pouvait choisir librement la vie philosophique la plus exigeante, et plusieurs auteurs, jusqu'à l'époque chrétienne, citèrent son exemple.&lt;/p&gt; &lt;p&gt;Diogène Laërce rapporte une anecdote célèbre : lors d'un banquet, le philosophe Théodore l'Athée voulut l'humilier en lui demandant qui avait donc laissé sa navette sur le métier à tisser. Elle répondit qu'elle avait consacré à l'étude le temps qu'on aurait voulu lui faire perdre au rouet. Hipparchia est ainsi devenue le symbole de la femme qui revendique le droit de penser et de vivre en philosophe.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBK-mTkHjtg</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"L’Athénienne qui préférait le cynisme à la cuisine | ARTE" par Invitation au voyage</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hipparchiademaronee-mini.webp</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grecque</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cynisme</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe cynique grecque, épouse de Cratès, qui vécut selon ses idées contre les conventions de son temps.</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
+    <row r="47" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>-360</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="I47" s="9"/>
+      <c r="J47" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="48" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
-        <v>-341</v>
+        <v>-360</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9donisme" style="color:#88A1E9"   title="L'hédonisme par Wikipédia"&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href="https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur"   title="L'épicurisme par le Précepteur"&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href="https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'épicurisme par le Précepteur"&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href="https://www.youtube.com/watch?v=cb1YHXSuxlM"   title="La philosophie du bonheur par Parole de philosophe"&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées "atomes".&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt; &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title="Est il bien raisonnable d'avoir peur de la mort par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        <v>346</v>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stilpon_de_M%C3%A9gare" style="color:#6A142A" title=" Wikipedia"&gt;STILPON de Mégare&lt;/a&gt; était est un philosophe, spécialisée dans la &lt;a href="https://fr.wikisource.org/wiki/L%E2%80%99Art_d%E2%80%99avoir_toujours_raison/La_dialectique_%C3%A9ristique" title="L’Art d’avoir toujours raison/La dialectique éristique par wikisource"&gt;dialectique de type éristique&lt;/a&gt;. Il est associé à l'école mégarique, fondée par Euclide de Mégare et était connu pour son éloquence et sa capacité à débattre, ce qui lui a valu une grande renommée dans le monde grec. &lt;/p&gt; &lt;p&gt; Les Mégariques étaient connus pour leur intérêt pour les paradoxes et les arguments sophistiqués. &lt;/p&gt; &lt;p&gt;Critique des universaux : Il est surtout connu pour sa critique des idées platoniciennes, en particulier la théorie des Formes. Il soutenait que les concepts généraux (comme "l'homme" ou "le bien") ne peuvent pas exister indépendamment des choses particulières. Pour lui, seules les choses individuelles sont réelles, et les universaux ne sont que des noms ou des constructions mentales. &lt;/p&gt; &lt;p&gt;Réfutation des catégories : Il a également critiqué la théorie des catégories d'Aristote, arguant que les distinctions entre les catégories (comme la substance, la qualité, la quantité) étaient artificielles et ne reflétaient pas la réalité. &lt;/p&gt; &lt;p&gt;Éthique et autosuffisance : Comme d'autres philosophes de son époque, il s'intéressait à l'éthique. Il prônait l'autosuffisance (autarkeia) et la tranquillité de l'âme (ataraxia). Il croyait que le bonheur pouvait être atteint en se libérant des désirs inutiles et en se concentrant sur ce qui est véritablement important. &lt;/p&gt; &lt;p&gt;Dialectique et logique : Il était un maître de la dialectique et utilisait souvent des arguments logiques pour déconstruire les positions de ses adversaires. Il était connu pour sa capacité à réduire les arguments de ses interlocuteurs à l'absurde, ce qui en faisait un redoutable débatteur. &lt;/p&gt; &lt;p&gt; Il était un philosophe dialecticien et éthique, dont les idées ont influencé plusieurs courants philosophiques ultérieurs. Bien que son œuvre ne nous soit pas parvenue directement, sa réputation de penseur rigoureux et son impact sur la philosophie antique sont indéniables. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F48" s="7" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>369</v>
+        <v>351</v>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socratisme ; École mégarique</t>
+        </is>
       </c>
       <c r="M48" s="2" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P48">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
-        <v>-340</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="I49" s="9"/>
-      <c r="J49" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>378</v>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7">
+        <v>-350</v>
+      </c>
+      <c r="B49" s="7">
+        <v>-280</v>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">350 A JC - 280 A JC</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIPPARCHIA de Maronée</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hipparchia" title=" Wikipedia"&gt;HIPPARCHIA de Maronée&lt;/a&gt; était une philosophe cynique grecque, originaire de Maronée en Thrace. Issue d'une famille aisée, elle tomba amoureuse du philosophe Cratès de Thèbes, disciple de Diogène, qui avait renoncé à toute sa fortune. Ses parents s'opposèrent au mariage ; elle menaça de se tuer. Cratès lui-même tenta de la dissuader en lui montrant sa pauvreté, mais elle choisit de partager sa vie et ses idées.&lt;/p&gt; &lt;p&gt;Le cynisme prônait une vie simple, conforme à la nature, libérée des richesses, des honneurs et des conventions sociales jugées artificielles. Hipparchia vécut ainsi avec Cratès, en public et sans honte, portant le même manteau grossier que lui, et participa comme un homme aux banquets et aux discussions philosophiques, ce qui fit scandale à Athènes.&lt;/p&gt; &lt;p&gt;Selon Diogène Laërce, elle aurait &lt;a href="https://www.philomag.com/articles/hipparchie-la-vie-forte-des-cyniques" title="Hipparchie, “la vie forte des cyniques” par philosophie magazine"&gt;écrit des traités philosophiques&lt;/a&gt;, des lettres et des réponses à des questions posées au philosophe Théodore, aujourd'hui perdus. Elle eut avec Cratès au moins deux enfants et continua de mener une vie de philosophe. Pour les anciens, elle était la preuve qu'une femme pouvait choisir librement la vie philosophique la plus exigeante, et plusieurs auteurs, jusqu'à l'époque chrétienne, citèrent son exemple.&lt;/p&gt; &lt;p&gt;Diogène Laërce rapporte une anecdote célèbre : lors d'un banquet, le philosophe Théodore l'Athée voulut l'humilier en lui demandant qui avait donc laissé sa navette sur le métier à tisser. Elle répondit qu'elle avait consacré à l'étude le temps qu'on aurait voulu lui faire perdre au rouet. Hipparchia est ainsi devenue le symbole de la femme qui revendique le droit de penser et de vivre en philosophe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBK-mTkHjtg</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L’Athénienne qui préférait le cynisme à la cuisine | ARTE" par Invitation au voyage</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hipparchiademaronee-mini.webp</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cynisme</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe cynique grecque, épouse de Cratès, qui vécut selon ses idées contre les conventions de son temps.</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
-        <v>-334</v>
+        <v>-341</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Z%C3%A9non_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;ZENON de Kition&lt;/a&gt; (vers 334-262 av. J.-C.) est le fondateur de l’école &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcienne&lt;/a&gt;. Né à Kition, dans l’île de Chypre, il arrive à Athènes vers 312 av. J.-C. après un naufrage. Selon la légende, il lit chez un libraire les souvenirs de Xénophon sur Socrate et demande où trouver de tels hommes : le libraire lui montre le cynique Cratès qui passait. Zénon suit ses leçons, puis celles du mégarique Stilpon et des platoniciens.&lt;/p&gt; &lt;p&gt;Vers 300 av. J.-C., il enseigne sous le Portique peint d’Athènes, la &lt;em&gt;Stoa poikilè&lt;/em&gt;, d’où le nom de stoïcisme. Ses livres sont perdus. Il divise la philosophie en trois parties, que les stoïciens comparent à un jardin : la logique en est la clôture, la physique les arbres, l’éthique les fruits. Le monde est un tout vivant, ordonné par une raison divine, le &lt;em&gt;logos&lt;/em&gt;, présente en toute chose comme un feu artiste. Le but de la vie est de « vivre en accord avec la nature », c’est-à-dire avec la raison. La vertu est le seul bien, le vice le seul mal ; la santé, la richesse ou la réputation sont « indifférentes ». Les passions, comme la peur, le chagrin ou la colère, sont des jugements erronés et des élans excessifs : le sage s’en libère et atteint la tranquillité. Pour expliquer la connaissance, Zénon montre sa main ouverte, puis la ferme peu à peu jusqu’à serrer le poing : la sensation, l’assentiment, la compréhension, la science.&lt;/p&gt; &lt;p&gt;Les Athéniens honorent sa vertu d’une couronne d’or. Ses successeurs, Cléanthe et Chrysippe, développent sa doctrine, qui marquera Sénèque, Épictète et Marc Aurèle.&lt;/p&gt;</t>
+        <v>363</v>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure"  style="color:#6A142A"  title=" Wikipedia"&gt;EPICURE&lt;/a&gt; était un philosophe grec &lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9donisme" style="color:#88A1E9"   title="L'hédonisme par Wikipédia"&gt; Hédoniste&lt;/a&gt; qui a fondé l'école &lt;a href="https://www.youtube.com/watch?v=bAKGBamfaIo&amp;ab_channel=LePr%C3%A9cepteur"   title="L'épicurisme par le Précepteur"&gt; Epicurienne&lt;/a&gt; où il enseignait que le bonheur est le but de la vie et qu'il peut être atteint en cherchant à éliminer la douleur physique et mentale et que la peur de la mort est infondée, car &lt;a href="https://www.youtube.com/watch?v=DXpUGmRYOqo&amp;ab_channel=LePr%C3%A9cepteur" style="color:#88A1E9"   title="L'épicurisme par le Précepteur"&gt; la Mort n'est rien&lt;/a&gt;, c'est la fin de la conscience et donc de la souffrance.&lt;/p&gt;&lt;p&gt;  Il fonda à Athènes une école appelée « le Jardin », ouverte aussi bien aux hommes qu’aux femmes et même aux esclaves, ce qui était remarquable pour l’époque. Il y enseignait dans une atmosphère d’amitié et de simplicité, valorisant les liens humains comme une source essentielle de bonheur. Sa philosophie visait avant tout à libérer les hommes de leurs peurs — notamment celle des dieux et de la mort — afin de leur permettre d’atteindre l’ataraxie, c’est-à-dire une &lt;a href="https://www.youtube.com/watch?v=cb1YHXSuxlM"   title="La philosophie du bonheur par Parole de philosophe"&gt; paix intérieure durable. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt;Il prônait une vie simple et modérée, éloignée des plaisirs excessifs et des soucis inutiles et développa une théorie matérialiste de l'univers, selon laquelle tout ce qui existe est formé de particules élémentaires indestructibles appelées "atomes".&lt;/p&gt;&lt;p&gt; Il croyait que les dieux existent, mais qu'ils sont indifférents à l'humanité et ne sont pas impliqués dans les événements de la vie humaine.&lt;/p&gt; &lt;p&gt; Il a soutenu que les sens sont fiables et que la raison peut être utilisée pour comprendre les phénomènes naturels. Cette école de pensée a été très populaire à l'époque antique et a continué à avoir une influence sur la philosophie occidentale jusqu'à nos jours.&lt;/p&gt; &lt;p&gt; Il distingue différents types de désirs : les désirs naturels et nécessaires (comme manger ou se protéger), les désirs naturels mais non nécessaires (comme le luxe), et les désirs vains (comme la richesse ou la gloire). Selon lui, seuls les premiers doivent être satisfaits pour atteindre le bonheur. Sa pensée aura une influence durable, notamment à travers le poète latin Lucrèce, qui en diffusera les principes dans son œuvre De rerum natura, contribuant à la transmission de l’épicurisme jusqu’à l’époque moderne. &lt;/p&gt; &lt;audio controls title="Est il bien raisonnable d'avoir peur de la mort par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-25.02.2020-ITEMA_22291597-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F50" s="7" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="2" t="s">
@@ -5645,10 +5689,10 @@
         <v>368</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -5656,35 +5700,33 @@
         </is>
       </c>
       <c r="P50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
-        <v>-330</v>
+        <v>-340</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9anthe"  style="color:#6A142A"  title=" Wikipedia"&gt;CLÉANTHE&lt;/a&gt; (vers 330-232 av. J.-C.) est un philosophe stoïcien grec, successeur de Zénon de Kition à la tête de l’école du Portique. Né à Assos, en Asie Mineure, ancien pugiliste, il arrive à Athènes presque sans ressources ; pour payer ses études, il tire de l’eau la nuit dans les jardins, ce qui lui vaut le surnom de « puiseur d’eau ». Il suit l’enseignement de Zénon pendant dix-neuf ans. Ses camarades le surnomment « l’âne », parce qu’il apprend lentement, mais il répond qu’il est le seul à pouvoir porter le fardeau de Zénon.&lt;/p&gt; &lt;p&gt;Il dirige l’école de 262 à sa mort. Moins brillant dialecticien que son successeur Chrysippe, il apporte pourtant des idées propres, surtout en physique et en théologie. Pour lui, l’univers est un être vivant animé par un souffle de feu, dont la tension maintient l’unité de toutes choses ; le soleil en est la partie directrice. Il défend une morale exigeante : la vertu est le seul bien, et le plaisir n’est pas conforme à la nature. Son œuvre la plus célèbre est l’&lt;a href="https://www.persee.fr/doc/rea_0035-2004_1998_num_100_1_4719" style="color:#88A1E9" title="L'universel &amp; le singulier. L'hymne à Zeus de Cléanthe. par Persée"&gt;&lt;em&gt;Hymne à Zeus&lt;/em&gt;&lt;/a&gt;, poème où Zeus est identifié à la raison universelle qui gouverne le monde : seuls les méchants s’en écartent, par ignorance. Une autre prière, citée par Épictète et traduite par Sénèque, résume l’attitude stoïcienne : « Conduis-moi, Zeus, et toi, Destinée, là où vous m’avez fixé ma place. » Sénèque en tire la formule : « Le destin conduit celui qui consent, il traîne celui qui résiste. »&lt;/p&gt; &lt;p&gt;Il meurt très âgé, en jeûnant. Hume a donné son nom au défenseur de &lt;a href="https://www.youtube.com/watch?v=HBbaB-X6xCI" style="color:#88A1E9" title=" L'argument a posteriori 1/2 : le raisonnement par analogie de Cléanthe par Gresza"&gt;l’argument par analogie&lt;/a&gt; dans ses &lt;em&gt;Dialogues sur la religion naturelle&lt;/em&gt;.&lt;/p&gt;</t>
-        </is>
+        <v>373</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>374</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="2" t="s">
@@ -5694,10 +5736,10 @@
         <v>368</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>386</v>
+        <v>278</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -5705,91 +5747,94 @@
         </is>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
-        <v>-325</v>
+        <v>-334</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bion_de_Borysth%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;BION de Borysthène&lt;/a&gt; était un écrivain et un philosophe cynique grec connu pour ses idées critiques envers les conventions sociales et pour son style de vie ascétique, caractéristique des philosophes cyniques. Il était d'origine modeste, selon certaines sources et cette condition sociale a probablement influencé sa critique acerbe des hiérarchies et des conventions sociales. &lt;/p&gt; &lt;p&gt; Après avoir été vendu comme esclave, il fut libéré et reçut une éducation philosophique auprès de divers maîtres, et peut-être aussi auprès de représentants d'autres écoles philosophiques, comme les académiciens ou les péripatéticiens. Cette diversité d'influences se reflète dans sa   &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme" title="eclectisme par wikipedia"&gt;pensée éclectique&lt;/a&gt;. Il suit en effet tour à tour l’Académie, le cynique Cratès, le cyrénaïque Théodore l’Athée et le péripatéticien Théophraste.  Il adopta le mode de vie cynique, caractérisé par un rejet des richesses, des plaisirs matériels et des conventions sociales. &lt;/p&gt; &lt;p&gt; Il était également un écrivain talentueux, connu pour ses &lt;em&gt;Diatribes&lt;/em&gt;, des discours philosophiques souvent satiriques et moralisateurs.  &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1978_num_1_1_3417_t1_0102_0000_2" style="color:#88A1E9" title="Jan Fredrik Kindstrand, Bion of Borysthenes. A collection of the Fragments with introduction and commentary  par Persée"&gt;Ses textes&lt;/a&gt; ont influencé des auteurs ultérieurs, comme Horace et Sénèque, qui ont repris certains de ses thèmes et de ses techniques littéraires. Ératosthène disait de lui qu’il fut le premier à habiller la philosophie de vêtements fleuris. Il vécut un temps à la cour du roi de Macédoine Antigone Gonatas. &lt;/p&gt; &lt;p&gt; Il incarne l'esprit cynique par excellence : libre, provocateur et profondément critique envers les conventions sociales. Sa vie et son œuvre témoignent d'une quête de vérité et d'authenticité, qui continue de résonner aujourd'hui. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Z%C3%A9non_de_Kition"  style="color:#6A142A"  title=" Wikipedia"&gt;ZENON de Kition&lt;/a&gt; (vers 334-262 av. J.-C.) est le fondateur de l’école &lt;a href="https://www.youtube.com/watch?v=2qecLXMw1nU&amp;ab_channel=LePr%C3%A9cepteur"   title="Le Stoïcisme en 10 citations par le Précepteur"&gt;stoïcienne&lt;/a&gt;. Né à Kition, dans l’île de Chypre, il arrive à Athènes vers 312 av. J.-C. après un naufrage. Selon la légende, il lit chez un libraire les souvenirs de Xénophon sur Socrate et demande où trouver de tels hommes : le libraire lui montre le cynique Cratès qui passait. Zénon suit ses leçons, puis celles du mégarique Stilpon et des platoniciens.&lt;/p&gt; &lt;p&gt;Vers 300 av. J.-C., il enseigne sous le Portique peint d’Athènes, la &lt;em&gt;Stoa poikilè&lt;/em&gt;, d’où le nom de stoïcisme. Ses livres sont perdus. Il divise la philosophie en trois parties, que les stoïciens comparent à un jardin : la logique en est la clôture, la physique les arbres, l’éthique les fruits. Le monde est un tout vivant, ordonné par une raison divine, le &lt;em&gt;logos&lt;/em&gt;, présente en toute chose comme un feu artiste. Le but de la vie est de « vivre en accord avec la nature », c’est-à-dire avec la raison. La vertu est le seul bien, le vice le seul mal ; la santé, la richesse ou la réputation sont « indifférentes ». Les passions, comme la peur, le chagrin ou la colère, sont des jugements erronés et des élans excessifs : le sage s’en libère et atteint la tranquillité. Pour expliquer la connaissance, Zénon montre sa main ouverte, puis la ferme peu à peu jusqu’à serrer le poing : la sensation, l’assentiment, la compréhension, la science.&lt;/p&gt; &lt;p&gt;Les Athéniens honorent sa vertu d’une couronne d’or. Ses successeurs, Cléanthe et Chrysippe, développent sa doctrine, qui marquera Sénèque, Épictète et Marc Aurèle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F52" s="7" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>200</v>
+        <v>368</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>201</v>
+        <v>386</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
-        <v>-315</v>
+        <v>-330</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Wikipedia"&gt;ARCÉSILAS de Pitane&lt;/a&gt; fut l'un des philosophes les plus originaux de l'Antiquité, fondateur de la Moyenne Académie. En prenant la direction de l'Académie platonicienne vers 268 av. J.-C., il en transforma radicalement l'esprit en introduisant le scepticisme comme méthode philosophique fondamentale.&lt;/p&gt; &lt;p&gt;S'inspirant de &lt;a href="https://fr.wikipedia.org/wiki/Pyrrhon_d%27%C3%89lis" style="color:#6A142A" title="Pyrrhon sur Wikipedia"&gt;Pyrrhon d'Élis&lt;/a&gt; et de la pratique dialectique de Socrate, Arcésilas défendit la thèse que la suspension du jugement (&lt;em&gt;épochè&lt;/em&gt;) est la seule attitude raisonnable face à l'incertitude de la connaissance. Il combattit vigoureusement le dogmatisme stoïcien de Zénon de Kition, notamment la notion de « représentation compréhensive » (&lt;em&gt;phantasia kataleptike&lt;/em&gt;) censée fonder la certitude.&lt;/p&gt; &lt;p&gt;Fidèle à l'esprit socratique, Arcésilas n'écrivit rien. Il enseignait oralement, par le dialogue et la réfutation. Sa pensée est connue par les rapports de Cicéron, Sextus Empiricus et Diogène Laërce. Sa maxime : &lt;em&gt;« Suspendre son jugement est ce qu'il y a de plus sage »&lt;/em&gt;. Il incarne la résistance intellectuelle au dogmatisme et reste une référence majeure pour toute philosophie du doute. Né à Pitane, en Éolide, il étudie d’abord auprès de Théophraste, au Lycée, avant de rejoindre l’Académie de Polémon et de Crantor. Sa méthode consiste à argumenter pour et contre chaque thèse, jusqu’à montrer qu’elles se valent. Pour agir sans rien affirmer, il suffit, selon lui, de suivre ce qui paraît raisonnable. Un stoïcien se moquait de lui en le comparant à une chimère : « Platon par-devant, Pyrrhon par-derrière, Diodore au milieu ».&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cl%C3%A9anthe"  style="color:#6A142A"  title=" Wikipedia"&gt;CLÉANTHE&lt;/a&gt; (vers 330-232 av. J.-C.) est un philosophe stoïcien grec, successeur de Zénon de Kition à la tête de l’école du Portique. Né à Assos, en Asie Mineure, ancien pugiliste, il arrive à Athènes presque sans ressources ; pour payer ses études, il tire de l’eau la nuit dans les jardins, ce qui lui vaut le surnom de « puiseur d’eau ». Il suit l’enseignement de Zénon pendant dix-neuf ans. Ses camarades le surnomment « l’âne », parce qu’il apprend lentement, mais il répond qu’il est le seul à pouvoir porter le fardeau de Zénon.&lt;/p&gt; &lt;p&gt;Il dirige l’école de 262 à sa mort. Moins brillant dialecticien que son successeur Chrysippe, il apporte pourtant des idées propres, surtout en physique et en théologie. Pour lui, l’univers est un être vivant animé par un souffle de feu, dont la tension maintient l’unité de toutes choses ; le soleil en est la partie directrice. Il défend une morale exigeante : la vertu est le seul bien, et le plaisir n’est pas conforme à la nature. Son œuvre la plus célèbre est l’&lt;a href="https://www.persee.fr/doc/rea_0035-2004_1998_num_100_1_4719" style="color:#88A1E9" title="L'universel &amp; le singulier. L'hymne à Zeus de Cléanthe. par Persée"&gt;&lt;em&gt;Hymne à Zeus&lt;/em&gt;&lt;/a&gt;, poème où Zeus est identifié à la raison universelle qui gouverne le monde : seuls les méchants s’en écartent, par ignorance. Une autre prière, citée par Épictète et traduite par Sénèque, résume l’attitude stoïcienne : « Conduis-moi, Zeus, et toi, Destinée, là où vous m’avez fixé ma place. » Sénèque en tire la formule : « Le destin conduit celui qui consent, il traîne celui qui résiste. »&lt;/p&gt; &lt;p&gt;Il meurt très âgé, en jeûnant. Hume a donné son nom au défenseur de &lt;a href="https://www.youtube.com/watch?v=HBbaB-X6xCI" style="color:#88A1E9" title=" L'argument a posteriori 1/2 : le raisonnement par analogie de Cléanthe par Gresza"&gt;l’argument par analogie&lt;/a&gt; dans ses &lt;em&gt;Dialogues sur la religion naturelle&lt;/em&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F53" s="7" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>252</v>
+        <v>368</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -5797,45 +5842,45 @@
         </is>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
-        <v>-306</v>
+        <v>-325</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Persaios_de_Kition" style="color:#6A142A" title=" Wikipedia"&gt;PERSAIOS de Kition&lt;/a&gt;  était un disciple direct de Zénon de Cition, le fondateur du&lt;a href="https://www.youtube.com/watch?v=Dm5sPn_HmNE" title="Stoïcisme : Les Bases En Trois Minutes par Gianni Bergandi"&gt; stoïcisme&lt;/a&gt;, et a joué un rôle important dans la diffusion des idées stoïciennes, bien que sa vie et son œuvre restent mal documentées en raison du peu de sources qui nous sont parvenues. Il aurait été l'esclave ou le pupille de Zénon avant de devenir son disciple et ami. Cette relation étroite avec le fondateur du stoïcisme lui a permis de jouer un rôle important dans les premiers développements de l'école. &lt;/p&gt; &lt;p&gt;  En tant que conseiller du roi Antigone II Gonatas, il a cherché à mettre en œuvre les idéaux stoïciens de vertu et de raison dans la gouvernance. Cela reflète une tendance du stoïcisme à s'engager dans le monde réel plutôt qu'à rester confiné à des spéculations abstraites. Il a écrit un ouvrage intitulé "Sur la royauté", dans lequel il explorait les qualités nécessaires pour être un bon roi selon les principes stoïciens. Pour lui, un dirigeant idéal devait être vertueux, rationnel et guidé par l'intérêt général plutôt que par des désirs égoïstes. &lt;/p&gt; &lt;p&gt; Contrairement à certains philosophes qui se concentraient sur des débats théoriques, il insistait sur l'importance de vivre selon les principes stoïciens dans la vie quotidienne. Il a critiqué la poursuite des plaisirs, une idée qui rejoint l'enseignement stoïcien selon lequel les plaisirs corporels et matériels sont des distractions par rapport à la vertu et à la raison. Il a soutenu que le bonheur véritable ne peut être trouvé que dans la sagesse et la maîtrise de soi. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bion_de_Borysth%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;BION de Borysthène&lt;/a&gt; était un écrivain et un philosophe cynique grec connu pour ses idées critiques envers les conventions sociales et pour son style de vie ascétique, caractéristique des philosophes cyniques. Il était d'origine modeste, selon certaines sources et cette condition sociale a probablement influencé sa critique acerbe des hiérarchies et des conventions sociales. &lt;/p&gt; &lt;p&gt; Après avoir été vendu comme esclave, il fut libéré et reçut une éducation philosophique auprès de divers maîtres, et peut-être aussi auprès de représentants d'autres écoles philosophiques, comme les académiciens ou les péripatéticiens. Cette diversité d'influences se reflète dans sa   &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme" title="eclectisme par wikipedia"&gt;pensée éclectique&lt;/a&gt;. Il suit en effet tour à tour l’Académie, le cynique Cratès, le cyrénaïque Théodore l’Athée et le péripatéticien Théophraste.  Il adopta le mode de vie cynique, caractérisé par un rejet des richesses, des plaisirs matériels et des conventions sociales. &lt;/p&gt; &lt;p&gt; Il était également un écrivain talentueux, connu pour ses &lt;em&gt;Diatribes&lt;/em&gt;, des discours philosophiques souvent satiriques et moralisateurs.  &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1978_num_1_1_3417_t1_0102_0000_2" style="color:#88A1E9" title="Jan Fredrik Kindstrand, Bion of Borysthenes. A collection of the Fragments with introduction and commentary  par Persée"&gt;Ses textes&lt;/a&gt; ont influencé des auteurs ultérieurs, comme Horace et Sénèque, qui ont repris certains de ses thèmes et de ses techniques littéraires. Ératosthène disait de lui qu’il fut le premier à habiller la philosophie de vêtements fleuris. Il vécut un temps à la cour du roi de Macédoine Antigone Gonatas. &lt;/p&gt; &lt;p&gt; Il incarne l'esprit cynique par excellence : libre, provocateur et profondément critique envers les conventions sociales. Sa vie et son œuvre témoignent d'une quête de vérité et d'authenticité, qui continue de résonner aujourd'hui. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F54" s="7" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>386</v>
+        <v>201</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5843,43 +5888,45 @@
         </is>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="209.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
-        <v>-281</v>
+        <v>-315</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>423</v>
+        <v>406</v>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Wikipedia"&gt;ARCÉSILAS de Pitane&lt;/a&gt; fut l'un des philosophes les plus originaux de l'Antiquité, fondateur de la Moyenne Académie. En prenant la direction de l'Académie platonicienne vers 268 av. J.-C., il en transforma radicalement l'esprit en introduisant le scepticisme comme méthode philosophique fondamentale.&lt;/p&gt; &lt;p&gt;S'inspirant de &lt;a href="https://fr.wikipedia.org/wiki/Pyrrhon_d%27%C3%89lis" style="color:#6A142A" title="Pyrrhon sur Wikipedia"&gt;Pyrrhon d'Élis&lt;/a&gt; et de la pratique dialectique de Socrate, Arcésilas défendit la thèse que la suspension du jugement (&lt;em&gt;épochè&lt;/em&gt;) est la seule attitude raisonnable face à l'incertitude de la connaissance. Il combattit vigoureusement le dogmatisme stoïcien de Zénon de Kition, notamment la notion de « représentation compréhensive » (&lt;em&gt;phantasia kataleptike&lt;/em&gt;) censée fonder la certitude.&lt;/p&gt; &lt;p&gt;Fidèle à l'esprit socratique, Arcésilas n'écrivit rien. Il enseignait oralement, par le dialogue et la réfutation. Sa pensée est connue par les rapports de Cicéron, Sextus Empiricus et Diogène Laërce. Sa maxime : &lt;em&gt;« Suspendre son jugement est ce qu'il y a de plus sage »&lt;/em&gt;. Il incarne la résistance intellectuelle au dogmatisme et reste une référence majeure pour toute philosophie du doute. Né à Pitane, en Éolide, il étudie d’abord auprès de Théophraste, au Lycée, avant de rejoindre l’Académie de Polémon et de Crantor. Sa méthode consiste à argumenter pour et contre chaque thèse, jusqu’à montrer qu’elles se valent. Pour agir sans rien affirmer, il suffit, selon lui, de suivre ce qui paraît raisonnable. Un stoïcien se moquait de lui en le comparant à une chimère : « Platon par-devant, Pyrrhon par-derrière, Diodore au milieu ».&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F55" s="7" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>427</v>
+        <v>252</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>428</v>
+        <v>342</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5887,45 +5934,45 @@
         </is>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
-        <v>-280</v>
+        <v>-306</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s" style="color:#6A142A" title="Wikipedia"&gt;LACYDÈS de Cyrène&lt;/a&gt; (mort vers 205 av. J.-C.) est un philosophe grec, successeur d’&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Arcésilas sur Wikipedia"&gt;Arcésilas de Pitane&lt;/a&gt; à la tête de l’Académie, l’école fondée à Athènes par Platon. Originaire de Cyrène, en Libye actuelle, il vient étudier à Athènes et devient le disciple d’Arcésilas, auquel il succède vers 241 av. J.-C.&lt;/p&gt; &lt;p&gt;Il enseigne dans un jardin de l’Académie aménagé pour lui par le roi Attale Ier de Pergame, admirateur de la philosophie, et qu’on appelle le &lt;em&gt;Lacydion&lt;/em&gt;. Invité à la cour de ce roi, il refuse de s’y rendre, en disant que les portraits des rois se regardent de loin. Lacydès reste fidèle au &lt;a href="https://www.youtube.com/watch?v=kG3klWpBf2Y"  title="Le sceptisisme de la nouvelle-académie"&gt;scepticisme académique&lt;/a&gt; de son maître. Contre les stoïciens, qui croient à des perceptions si claires qu’elles garantissent la vérité, les académiciens soutiennent que rien ne peut être connu avec certitude : toute impression vraie pourrait être imitée par une impression fausse. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et se contenter de ce qui paraît raisonnable. Une anecdote rapportée par les Anciens illustre, avec humour, les difficultés de cette position : ses esclaves volaient ses provisions puis remettaient les scellés intacts ; pris sur le fait, ils lui auraient opposé sa propre doctrine : comment pouvait-il être sûr de ce qu’il voyait ?&lt;/p&gt; &lt;p&gt;Atteint de paralysie dans sa vieillesse, il confie de son vivant la direction de l’école à ses disciples Téléclès et Évandre, cas rare dans l’histoire de l’Académie. Selon Diogène Laërce, il aurait écrit des traités sur la philosophie et sur la nature, aujourd’hui perdus.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Persaios_de_Kition" style="color:#6A142A" title=" Wikipedia"&gt;PERSAIOS de Kition&lt;/a&gt;  était un disciple direct de Zénon de Cition, le fondateur du&lt;a href="https://www.youtube.com/watch?v=Dm5sPn_HmNE" title="Stoïcisme : Les Bases En Trois Minutes par Gianni Bergandi"&gt; stoïcisme&lt;/a&gt;, et a joué un rôle important dans la diffusion des idées stoïciennes, bien que sa vie et son œuvre restent mal documentées en raison du peu de sources qui nous sont parvenues. Il aurait été l'esclave ou le pupille de Zénon avant de devenir son disciple et ami. Cette relation étroite avec le fondateur du stoïcisme lui a permis de jouer un rôle important dans les premiers développements de l'école. &lt;/p&gt; &lt;p&gt;  En tant que conseiller du roi Antigone II Gonatas, il a cherché à mettre en œuvre les idéaux stoïciens de vertu et de raison dans la gouvernance. Cela reflète une tendance du stoïcisme à s'engager dans le monde réel plutôt qu'à rester confiné à des spéculations abstraites. Il a écrit un ouvrage intitulé "Sur la royauté", dans lequel il explorait les qualités nécessaires pour être un bon roi selon les principes stoïciens. Pour lui, un dirigeant idéal devait être vertueux, rationnel et guidé par l'intérêt général plutôt que par des désirs égoïstes. &lt;/p&gt; &lt;p&gt; Contrairement à certains philosophes qui se concentraient sur des débats théoriques, il insistait sur l'importance de vivre selon les principes stoïciens dans la vie quotidienne. Il a critiqué la poursuite des plaisirs, une idée qui rejoint l'enseignement stoïcien selon lequel les plaisirs corporels et matériels sont des distractions par rapport à la vertu et à la raison. Il a soutenu que le bonheur véritable ne peut être trouvé que dans la sagesse et la maîtrise de soi. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F56" s="7" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>252</v>
+        <v>24</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5933,47 +5980,43 @@
         </is>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="209.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
-        <v>-240</v>
+        <v>-281</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89vandre_(philosophe)" title="Wikipedia"&gt;ÉVANDRE&lt;/a&gt; (IIIe siècle av. J.-C.) est un philosophe grec originaire de Phocée, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de &lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s_de_Cyr%C3%A8ne" title=" Wikipedia"&gt;Lacydès de Cyrène&lt;/a&gt;, il reçoit de lui, avec Téléclès, la direction de l’école du vivant même de leur maître : Lacydès, malade, la leur confie vers 224 av. J.-C. Évandre et Téléclès la dirigent ensemble, cas rare dans l’histoire de l’institution.&lt;/p&gt; &lt;p&gt;Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par &lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" title=" Wikipedia"&gt;Arcésilas&lt;/a&gt;. Celui-ci avait donné à l’école platonicienne une orientation sceptique, en s’appuyant sur le Socrate qui affirmait ne rien savoir. Contre les stoïciens, qui pensaient que certaines représentations sont si évidentes qu’elles garantissent la vérité, les académiciens soutiennent qu’aucune perception ne permet de distinguer avec certitude le vrai du faux : un rêve, une illusion ou un jumeau peuvent produire la même impression qu’une perception exacte. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et ne rien affirmer. Pour agir, il suffit de suivre ce qui paraît raisonnable. Les académiciens enseignaient en argumentant pour et contre chaque thèse, afin de montrer que les deux positions se valent et d’exercer l’esprit critique de leurs élèves. Évandre transmet cet héritage à une génération d’étudiants.&lt;/p&gt; &lt;p&gt;Aucun de ses écrits ne nous est parvenu. Il a pour successeur Hégésinous de Pergame, qui forme à son tour &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant penseur de la Nouvelle Académie.&lt;/p&gt;</t>
-        </is>
+        <v>422</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>423</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="I57" s="12" t="s">
-        <v>445</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="I57" s="9"/>
       <c r="J57" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>252</v>
+        <v>427</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>342</v>
+        <v>428</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5981,32 +6024,32 @@
         </is>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
-        <v>-230</v>
+        <v>-280</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame" title="Wikipedia"&gt;Hégésinous de PERGAME&lt;/a&gt; (IIe siècle av. J.-C.) est un philosophe grec, chef de l’Académie, l’école fondée à Athènes par Platon. Originaire de Pergame, en Asie Mineure, il succède à Évandre et Téléclès, qui avaient dirigé ensemble l’école, et il a pour élève et successeur &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant dialecticien de l’Antiquité.&lt;/p&gt; &lt;p&gt;Nous ne connaissons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu : son nom nous est connu par les listes des chefs successifs de l’Académie et par Cicéron, qui indique que Carnéade l’eut pour maître. Il appartient à la période sceptique de l’Académie, inaugurée par Arcésilas. Les académiciens de ce temps refusent d’affirmer quoi que ce soit avec certitude. Contre les stoïciens, qui croient que certaines perceptions portent en elles la marque de leur vérité, ils montrent qu’une perception vraie pourrait toujours être imitée par une perception fausse, comme dans le rêve ou l’illusion. Il faut donc suspendre son jugement. Mais cela n’empêche pas de vivre : pour agir, on peut suivre ce qui paraît raisonnable. L’enseignement de l’Académie se fait par la discussion contradictoire, en argumentant pour et contre chaque thèse. C’est cette méthode que Carnéade portera à son sommet : envoyé à Rome en ambassade en 155 av. J.-C., il fit scandale en défendant un jour la justice, puis en la réfutant le lendemain.&lt;/p&gt; &lt;p&gt;Hégésinous est ainsi un maillon de la transmission entre la Moyenne et la Nouvelle Académie, durant la période de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique" style="color:#6A142A" title="Philosophie hellénistique sur Wikipedia"&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;</t>
+        <v>432</v>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s" style="color:#6A142A" title="Wikipedia"&gt;LACYDÈS de Cyrène&lt;/a&gt; (mort vers 205 av. J.-C.) est un philosophe grec, successeur d’&lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" style="color:#6A142A" title="Arcésilas sur Wikipedia"&gt;Arcésilas de Pitane&lt;/a&gt; à la tête de l’Académie, l’école fondée à Athènes par Platon. Originaire de Cyrène, en Libye actuelle, il vient étudier à Athènes et devient le disciple d’Arcésilas, auquel il succède vers 241 av. J.-C.&lt;/p&gt; &lt;p&gt;Il enseigne dans un jardin de l’Académie aménagé pour lui par le roi Attale Ier de Pergame, admirateur de la philosophie, et qu’on appelle le &lt;em&gt;Lacydion&lt;/em&gt;. Invité à la cour de ce roi, il refuse de s’y rendre, en disant que les portraits des rois se regardent de loin. Lacydès reste fidèle au &lt;a href="https://www.youtube.com/watch?v=kG3klWpBf2Y"  title="Le sceptisisme de la nouvelle-académie"&gt;scepticisme académique&lt;/a&gt; de son maître. Contre les stoïciens, qui croient à des perceptions si claires qu’elles garantissent la vérité, les académiciens soutiennent que rien ne peut être connu avec certitude : toute impression vraie pourrait être imitée par une impression fausse. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et se contenter de ce qui paraît raisonnable. Une anecdote rapportée par les Anciens illustre, avec humour, les difficultés de cette position : ses esclaves volaient ses provisions puis remettaient les scellés intacts ; pris sur le fait, ils lui auraient opposé sa propre doctrine : comment pouvait-il être sûr de ce qu’il voyait ?&lt;/p&gt; &lt;p&gt;Atteint de paralysie dans sa vieillesse, il confie de son vivant la direction de l’école à ses disciples Téléclès et Évandre, cas rare dans l’histoire de l’Académie. Selon Diogène Laërce, il aurait écrit des traités sur la philosophie et sur la nature, aujourd’hui perdus.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F58" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="G58" s="15" t="s">
-        <v>452</v>
+        <v>434</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>435</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="2" t="s">
@@ -6019,7 +6062,7 @@
         <v>342</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -6027,34 +6070,36 @@
         </is>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
-        <v>-213</v>
+        <v>-240</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Wikipedia"&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href="https://fr.wikipedia.org/wiki/Dialectique" title="Dialectique par Wikipedia"&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272" title="Opinion et certitude par Persee"&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron" style="color:#6A142A" title="Cicéron sur Wikipedia"&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il. Formé à la dialectique par le stoïcien Diogène de Babylone, il étudie de près l’œuvre de Chrysippe pour mieux la réfuter, au point de dire : « Sans Chrysippe, je ne serais pas. » Il distingue trois degrés de vraisemblance : la représentation simplement probable, celle qui n’est contredite par aucune autre, et celle qui a été examinée sous tous ses aspects. Il critique aussi la divination, le destin et la providence des stoïciens. Son disciple Clitomaque a mis par écrit son enseignement.&lt;/p&gt;</t>
+        <v>440</v>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89vandre_(philosophe)" title="Wikipedia"&gt;ÉVANDRE&lt;/a&gt; (IIIe siècle av. J.-C.) est un philosophe grec originaire de Phocée, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de &lt;a href="https://fr.wikipedia.org/wiki/Lacyd%C3%A8s_de_Cyr%C3%A8ne" title=" Wikipedia"&gt;Lacydès de Cyrène&lt;/a&gt;, il reçoit de lui, avec Téléclès, la direction de l’école du vivant même de leur maître : Lacydès, malade, la leur confie vers 224 av. J.-C. Évandre et Téléclès la dirigent ensemble, cas rare dans l’histoire de l’institution.&lt;/p&gt; &lt;p&gt;Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par &lt;a href="https://fr.wikipedia.org/wiki/Arc%C3%A9silas_de_Pitane" title=" Wikipedia"&gt;Arcésilas&lt;/a&gt;. Celui-ci avait donné à l’école platonicienne une orientation sceptique, en s’appuyant sur le Socrate qui affirmait ne rien savoir. Contre les stoïciens, qui pensaient que certaines représentations sont si évidentes qu’elles garantissent la vérité, les académiciens soutiennent qu’aucune perception ne permet de distinguer avec certitude le vrai du faux : un rêve, une illusion ou un jumeau peuvent produire la même impression qu’une perception exacte. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;) et ne rien affirmer. Pour agir, il suffit de suivre ce qui paraît raisonnable. Les académiciens enseignaient en argumentant pour et contre chaque thèse, afin de montrer que les deux positions se valent et d’exercer l’esprit critique de leurs élèves. Évandre transmet cet héritage à une génération d’étudiants.&lt;/p&gt; &lt;p&gt;Aucun de ses écrits ne nous est parvenu. Il a pour successeur Hégésinous de Pergame, qui forme à son tour &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant penseur de la Nouvelle Académie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F59" s="7" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="I59" s="9"/>
+        <v>444</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>445</v>
+      </c>
       <c r="J59" s="2" t="s">
         <v>23</v>
       </c>
@@ -6065,28 +6110,120 @@
         <v>342</v>
       </c>
       <c r="M59" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="n">
+        <v>-230</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9g%C3%A9sinous_de_Pergame" title="Wikipedia"&gt;Hégésinous de PERGAME&lt;/a&gt; (IIe siècle av. J.-C.) est un philosophe grec, chef de l’Académie, l’école fondée à Athènes par Platon. Originaire de Pergame, en Asie Mineure, il succède à Évandre et Téléclès, qui avaient dirigé ensemble l’école, et il a pour élève et successeur &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, le plus brillant dialecticien de l’Antiquité.&lt;/p&gt; &lt;p&gt;Nous ne connaissons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu : son nom nous est connu par les listes des chefs successifs de l’Académie et par Cicéron, qui indique que Carnéade l’eut pour maître. Il appartient à la période sceptique de l’Académie, inaugurée par Arcésilas. Les académiciens de ce temps refusent d’affirmer quoi que ce soit avec certitude. Contre les stoïciens, qui croient que certaines perceptions portent en elles la marque de leur vérité, ils montrent qu’une perception vraie pourrait toujours être imitée par une perception fausse, comme dans le rêve ou l’illusion. Il faut donc suspendre son jugement. Mais cela n’empêche pas de vivre : pour agir, on peut suivre ce qui paraît raisonnable. L’enseignement de l’Académie se fait par la discussion contradictoire, en argumentant pour et contre chaque thèse. C’est cette méthode que Carnéade portera à son sommet : envoyé à Rome en ambassade en 155 av. J.-C., il fit scandale en défendant un jour la justice, puis en la réfutant le lendemain.&lt;/p&gt; &lt;p&gt;Hégésinous est ainsi un maillon de la transmission entre la Moyenne et la Nouvelle Académie, durant la période de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_hell%C3%A9nistique" style="color:#6A142A" title="Philosophie hellénistique sur Wikipedia"&gt;philosophie hellénistique&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="G60" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="I60" s="9"/>
+      <c r="J60" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7" t="n">
+        <v>-213</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" title="Wikipedia"&gt;CARNÉADE de Cyrène&lt;/a&gt; fut le plus grand philosophe de la &lt;em&gt;Nouvelle Académie&lt;/em&gt; et l'un des maîtres absolus de la &lt;a href="https://fr.wikipedia.org/wiki/Dialectique" title="Dialectique par Wikipedia"&gt;dialectique &lt;/a&gt; dans l'Antiquité. Scholarque de l'Académie à partir de 167 av. J.-C., il porta le scepticisme académique à son plus haut niveau de sophistication.&lt;/p&gt; &lt;p&gt;Sa célébrité atteignit son apogée lors de son ambassade à Rome en 155 av. J.-C., où il prononça deux discours consécutifs sur la justice : le premier pour l'exalter, le second pour la réfuter avec les mêmes arguments — scandalisant Caton l'Ancien mais éblouissant les Romains par sa virtuosité intellectuelle. Il ne laissa aucun écrit, préférant l'enseignement oral et la réfutation vivante.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1980_num_58_1_3272" title="Opinion et certitude par Persee"&gt;Sa contribution majeure &lt;/a&gt; fut la théorie du &lt;em&gt;pithanon&lt;/em&gt; (le vraisemblable ou probable) : face à l'impossibilité de la certitude, le sage peut néanmoins agir en se guidant sur les représentations qui s'imposent avec le plus de force et de cohérence. Cette solution pratique au scepticisme radical influença profondément &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron" style="color:#6A142A" title="Cicéron sur Wikipedia"&gt;Cicéron&lt;/a&gt; et, à travers lui, toute la tradition probabiliste occidentale. &lt;em&gt;« Aucune représentation n'est infaillible »&lt;/em&gt;, enseignait-il. Formé à la dialectique par le stoïcien Diogène de Babylone, il étudie de près l’œuvre de Chrysippe pour mieux la réfuter, au point de dire : « Sans Chrysippe, je ne serais pas. » Il distingue trois degrés de vraisemblance : la représentation simplement probable, celle qui n’est contredite par aucune autre, et celle qui a été examinée sous tous ses aspects. Il critique aussi la divination, le destin et la providence des stoïciens. Son disciple Clitomaque a mis par écrit son enseignement.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="I61" s="9"/>
+      <c r="J61" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="M61" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="n">
+      <c r="O61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7" t="n">
         <v>-80</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B62" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C62" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D62" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89n%C3%A9sid%C3%A8me" style="color:#6A142A" title=" Wikipedia"&gt;ÉNÉSIDÈME&lt;/a&gt; était un philosophe grec de la tradition sceptique.  Il vécu à une époque où le &lt;a href="https://www.youtube.com/watch?v=57h2CU3V2fs" title="Le scepticisme : définition, exemples... (expliqué en 2 minutes) par le Savoir Partagé"&gt;&lt;font color="#88a1e9"&gt;scepticisme&lt;/font&gt; &lt;/a&gt;philosophique était en plein essor, en réaction aux dogmatismes des écoles philosophiques comme le stoïcisme et l'épicurisme.  &lt;/p&gt; &lt;p&gt; Il a systématisé les  &lt;a href="https://www.persee.fr/doc/rea_0035-2004_1918_num_20_2_2006" style="color:#88A1E9" title="Pour l'histoire du scepticisme antique : les tropes d'Énésidème contre la logique inductive par Persée"&gt;arguments sceptiques&lt;/a&gt; dans ce qu'on appelle les &lt;a href="https://guykarl.canalblog.com/archives/2012/08/31/25001663.html" style="color:#88A1E9" title="PYRRHONISME : les dix tropes d' ENESIDEME par Le jardin Philosophe"&gt;"Dix Modes"&lt;/a&gt;, qui visent à montrer que nos perceptions et nos jugements sont influencés par divers facteurs, rendant impossible l'accès à une connaissance certaine : &lt;/p&gt;
 &lt;p&gt;La diversité des animaux : Les espèces perçoivent le monde de manière différente, ce qui suggère que nos perceptions ne reflètent pas nécessairement la réalité objective. &lt;/p&gt;
@@ -6096,114 +6233,14 @@
 &lt;p&gt;Les quantités et constitutions : La quantité et la composition d'un objet peuvent affecter la manière dont nous le percevons. &lt;/p&gt; &lt;p&gt;La relation : Tout est perçu en relation avec autre chose, ce qui rend difficile de connaître la nature intrinsèque d'un objet.&lt;/p&gt; &lt;p&gt;La fréquence ou la rareté : La fréquence avec laquelle nous rencontrons quelque chose peut influencer notre perception de sa valeur ou de sa nature. &lt;/p&gt; &lt;p&gt;Les coutumes et les croyances : Les habitudes culturelles et les croyances peuvent profondément influencer nos perceptions et nos jugements. &lt;/p&gt; &lt;p&gt; Ses arguments mettent en lumière les limites de notre capacité à connaître le monde de manière certaine et nous invitent à adopter une attitude plus humble et critique face à nos propres perceptions et jugements. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F62" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G62" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="H60" s="9" t="s">
+      <c r="H62" s="9" t="s">
         <v>528</v>
-      </c>
-      <c r="I60" s="9"/>
-      <c r="J60" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7">
-        <v>160</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vers 160 – vers 210</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sextus_Empiricus"  title=" Wikipedia"&gt;Sextus EMPIRICUS&lt;/a&gt;  était un philosophe et médecin grec et  une figure importante du scepticisme, souvent appelé "pyrrhonisme" en référence à Pyrrhon d'Élis. Contrairement à d'autres formes de scepticisme, qui peuvent aboutir à une négation de la possibilité de connaître la vérité, le &lt;a href="https://www.youtube.com/watch?v=Xvgfo_ADlPM"  title=" Sextus Empiricus, Esquisses pyrrhoniennes, Ne rien affirmer et l'enseignement inexistant par Koalemos"&gt;pyrrhonisme&lt;/a&gt; propose de suspendre tout jugement sur la nature ultime des choses, car il considère que les arguments pour et contre toute proposition sont également convaincants. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2002_num_100_4_7456_t1_0797_0000_2" title="Sextus Empiricus, Esquisses pyrrhoniennes. Introduction, traduction et commentaires par Pierre Pellegrin par Persée"&gt;"Les Esquisses pyrrhoniennes"&lt;/a&gt;, il présente une introduction systématique au scepticisme pyrrhonien. L'ouvrage est divisé en trois livres : &lt;/p&gt; &lt;p&gt;Livre I : Il expose les principes fondamentaux du scepticisme, y compris la distinction entre le scepticisme pyrrhonien et d'autres formes de scepticisme, comme celui de l'Académie. Il explique également les concepts clés tels que l'épochè (suspension du jugement), les tropes (modes d'argumentation sceptique), et l'ataraxie. &lt;/p&gt; &lt;p&gt;Livre II : Il traite de la critique sceptique des dogmatismes philosophiques, en particulier dans les domaines de la logique, de la physique et de l'éthique. Il montre comment les arguments des dogmatiques peuvent être contredits, ce qui justifie la suspension du jugement. &lt;/p&gt; &lt;p&gt;Livre III : Il approfondit la critique des dogmatismes, en se concentrant sur des questions spécifiques comme la causalité, la divinité, et la nature du bien et du mal. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/spira_0994-3722_2007_num_39_1_1264_t14_0182_0000_2" style="color:#88A1E9" title=" Sur le Contre les professeurs de Sextus Empiricus par Persée"&gt;"Contre les professeurs"&lt;/a&gt;, il s'attaque à diverses disciplines intellectuelles de son époque, notamment la grammaire, la rhétorique, la géométrie, l'arithmétique, l'astronomie et la musique. Il soutient qu'elles ne peuvent pas prétendre à une connaissance certaine ou absolue. Son but est de montrer que les prétentions à la vérité dans ces domaines sont infondées. &lt;/p&gt; &lt;p&gt; Il  est également connu pour avoir systématisé &lt;a href="https://hal.science/hal-03091658v1/document" style="color:#88A1E9" title=" Sextus Empiricus et les tropes par Hall science"&gt;les "tropes"&lt;/a&gt;, des arguments ou modes de raisonnement qui justifient la suspension du jugement. Ce sont des outils dialectiques qui montrent comment les perceptions et les jugements varient selon les circonstances, les individus, les cultures, etc. &lt;/p&gt; &lt;p&gt;Ses écrits ont été redécouverts à la Renaissance et ont joué un rôle clé dans le développement de la pensée sceptique moderne, influençant des philosophes comme Montaigne, Descartes et Hume. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="I61" s="9"/>
-      <c r="J61" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7">
-        <v>-240</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-167</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vers 240 A JC - 167 A JC</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s" title="Wikipedia"&gt;TÉLÉCLÈS&lt;/a&gt; (mort vers 167 av. J.-C.) est un philosophe grec, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de Lacydès de Cyrène, il reçoit de lui, avec son condisciple Évandre, la direction de l’école du vivant même de leur maître, que la maladie empêchait d’enseigner. Les deux philosophes la dirigent ensemble, une organisation collégiale rare dans l’histoire de l’Académie.&lt;/p&gt; &lt;p&gt;Nous ne savons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu. Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par Arcésilas, qui avait donné à l’école de Platon une orientation sceptique en s’inspirant du Socrate qui affirmait ne rien savoir. Les académiciens de cette époque s’opposent avant tout aux stoïciens. Ceux-ci soutiennent qu’il existe des représentations « compréhensives », si claires et si distinctes qu’elles garantissent leur propre vérité et fondent la science. Les académiciens répondent qu’aucune perception ne peut être distinguée avec certitude d’une perception trompeuse : un rêve, une illusion d’optique ou deux jumeaux suffisent à le montrer. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;), mais il peut agir en suivant ce qui lui paraît raisonnable ou vraisemblable. L’enseignement se fait par la discussion : on argumente pour et contre chaque thèse, afin d’exercer l’esprit critique.&lt;/p&gt; &lt;p&gt;Après Téléclès et Évandre, la direction passe à Hégésinous de Pergame, puis à &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" style="color:#6A142A" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, qui donnera à l’Académie un éclat nouveau et portera le scepticisme jusqu’à Rome.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>477</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="2" t="s">
@@ -6215,8 +6252,8 @@
       <c r="L62" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="M62" s="11" t="s">
-        <v>478</v>
+      <c r="M62" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -6224,45 +6261,49 @@
         </is>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n">
-        <v>-185</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>480</v>
+    <row r="63" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7">
+        <v>160</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 160 – vers 210</t>
+        </is>
       </c>
       <c r="D63" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes"  title=" Wikipedia"&gt;PANÉTIUS DE RHODES&lt;/a&gt; (vers 185-109 av. J.-C.) est un philosophe stoïcien grec, qui a adapté le stoïcisme au monde romain. Issu d’une grande famille de Rhodes, il étudie à Athènes auprès de Diogène de Babylone, puis s’installe à Rome, où il devient l’ami et le conseiller de Scipion Émilien, le vainqueur de Carthage. Il prend ensuite la tête de l’école stoïcienne d’Athènes, de 129 à sa mort.&lt;/p&gt; &lt;p&gt;Panétius assouplit la &lt;a href="https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie"  title="Le Stoïcisme par apprendre la philo"&gt;pensée stoïcienne&lt;/a&gt; et la rapproche de Platon et d’Aristote, qu’il admire. Il abandonne plusieurs thèses de ses prédécesseurs : il doute de la divination, nie la conflagration universelle qui devait périodiquement détruire le monde, qu’il juge éternel, et refuse l’immortalité de l’âme. Surtout, il s’intéresse moins au sage idéal, presque introuvable, qu’à l’homme ordinaire qui progresse vers la sagesse. Sa morale part de la nature humaine : chacun porte en lui des tendances fondamentales où s’unissent la nature et la raison, la recherche de la vérité, le goût de l’ordre, le désir de grandeur d’âme et le sens de la communauté. Chacun doit aussi tenir compte de sa propre nature, de ses talents et de sa situation, comme un acteur choisit le rôle qui lui convient. Il en tire une éthique des « devoirs », les actions convenables de la vie quotidienne et de la vie publique, fondée sur la justice, la bienveillance et le sens de la mesure.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Du devoir&lt;/em&gt; est perdu, mais Cicéron l’a largement repris dans son &lt;em&gt;De officiis&lt;/em&gt;, l’un des livres de morale les plus lus en Europe jusqu’au XIXe siècle. Panétius a ainsi donné au stoïcisme le visage humaniste qu’adopteront les élites romaines.&lt;/p&gt;</t>
+        <v>465</v>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sextus_Empiricus"  title=" Wikipedia"&gt;Sextus EMPIRICUS&lt;/a&gt;  était un philosophe et médecin grec et  une figure importante du scepticisme, souvent appelé "pyrrhonisme" en référence à Pyrrhon d'Élis. Contrairement à d'autres formes de scepticisme, qui peuvent aboutir à une négation de la possibilité de connaître la vérité, le &lt;a href="https://www.youtube.com/watch?v=Xvgfo_ADlPM"  title=" Sextus Empiricus, Esquisses pyrrhoniennes, Ne rien affirmer et l'enseignement inexistant par Koalemos"&gt;pyrrhonisme&lt;/a&gt; propose de suspendre tout jugement sur la nature ultime des choses, car il considère que les arguments pour et contre toute proposition sont également convaincants. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2002_num_100_4_7456_t1_0797_0000_2" title="Sextus Empiricus, Esquisses pyrrhoniennes. Introduction, traduction et commentaires par Pierre Pellegrin par Persée"&gt;"Les Esquisses pyrrhoniennes"&lt;/a&gt;, il présente une introduction systématique au scepticisme pyrrhonien. L'ouvrage est divisé en trois livres : &lt;/p&gt; &lt;p&gt;Livre I : Il expose les principes fondamentaux du scepticisme, y compris la distinction entre le scepticisme pyrrhonien et d'autres formes de scepticisme, comme celui de l'Académie. Il explique également les concepts clés tels que l'épochè (suspension du jugement), les tropes (modes d'argumentation sceptique), et l'ataraxie. &lt;/p&gt; &lt;p&gt;Livre II : Il traite de la critique sceptique des dogmatismes philosophiques, en particulier dans les domaines de la logique, de la physique et de l'éthique. Il montre comment les arguments des dogmatiques peuvent être contredits, ce qui justifie la suspension du jugement. &lt;/p&gt; &lt;p&gt;Livre III : Il approfondit la critique des dogmatismes, en se concentrant sur des questions spécifiques comme la causalité, la divinité, et la nature du bien et du mal. &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://www.persee.fr/doc/spira_0994-3722_2007_num_39_1_1264_t14_0182_0000_2" style="color:#88A1E9" title=" Sur le Contre les professeurs de Sextus Empiricus par Persée"&gt;"Contre les professeurs"&lt;/a&gt;, il s'attaque à diverses disciplines intellectuelles de son époque, notamment la grammaire, la rhétorique, la géométrie, l'arithmétique, l'astronomie et la musique. Il soutient qu'elles ne peuvent pas prétendre à une connaissance certaine ou absolue. Son but est de montrer que les prétentions à la vérité dans ces domaines sont infondées. &lt;/p&gt; &lt;p&gt; Il  est également connu pour avoir systématisé &lt;a href="https://hal.science/hal-03091658v1/document" style="color:#88A1E9" title=" Sextus Empiricus et les tropes par Hall science"&gt;les "tropes"&lt;/a&gt;, des arguments ou modes de raisonnement qui justifient la suspension du jugement. Ce sont des outils dialectiques qui montrent comment les perceptions et les jugements varient selon les circonstances, les individus, les cultures, etc. &lt;/p&gt; &lt;p&gt;Ses écrits ont été redécouverts à la Renaissance et ont joué un rôle clé dans le développement de la pensée sceptique moderne, influençant des philosophes comme Montaigne, Descartes et Hume. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F63" s="7" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>252</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6270,45 +6311,49 @@
         </is>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="n">
-        <v>-135</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>488</v>
+    <row r="64" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7">
+        <v>-240</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-167</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 240 A JC - 167 A JC</t>
+        </is>
       </c>
       <c r="D64" s="8" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Posidonios"  title=" Wikipedia"&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770"  title="Posidonius d'Apamée théoricien de la géométrie par Persée"&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href="https://www.youtube.com/watch?v=EqU-kD8dW4Y" title="Grèce antique - 33 La civilisation hellénistique par Yannick Rub"&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289"  title="La philosophiede Posidonius par Persee"&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/T%C3%A9l%C3%A9cl%C3%A8s" title="Wikipedia"&gt;TÉLÉCLÈS&lt;/a&gt; (mort vers 167 av. J.-C.) est un philosophe grec, l’un des chefs de l’Académie, l’école fondée à Athènes par Platon. Disciple de Lacydès de Cyrène, il reçoit de lui, avec son condisciple Évandre, la direction de l’école du vivant même de leur maître, que la maladie empêchait d’enseigner. Les deux philosophes la dirigent ensemble, une organisation collégiale rare dans l’histoire de l’Académie.&lt;/p&gt; &lt;p&gt;Nous ne savons presque rien de sa vie, et aucun de ses écrits ne nous est parvenu. Il appartient à la période qu’on appelle la « Moyenne Académie », ouverte par Arcésilas, qui avait donné à l’école de Platon une orientation sceptique en s’inspirant du Socrate qui affirmait ne rien savoir. Les académiciens de cette époque s’opposent avant tout aux stoïciens. Ceux-ci soutiennent qu’il existe des représentations « compréhensives », si claires et si distinctes qu’elles garantissent leur propre vérité et fondent la science. Les académiciens répondent qu’aucune perception ne peut être distinguée avec certitude d’une perception trompeuse : un rêve, une illusion d’optique ou deux jumeaux suffisent à le montrer. Le sage doit donc suspendre son jugement (&lt;em&gt;épochè&lt;/em&gt;), mais il peut agir en suivant ce qui lui paraît raisonnable ou vraisemblable. L’enseignement se fait par la discussion : on argumente pour et contre chaque thèse, afin d’exercer l’esprit critique.&lt;/p&gt; &lt;p&gt;Après Téléclès et Évandre, la direction passe à Hégésinous de Pergame, puis à &lt;a href="https://fr.wikipedia.org/wiki/Carn%C3%A9ade" style="color:#6A142A" title="Carnéade sur Wikipedia"&gt;Carnéade&lt;/a&gt;, qui donnera à l’Académie un éclat nouveau et portera le scepticisme jusqu’à Rome.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F64" s="7" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>494</v>
+        <v>342</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>478</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -6316,49 +6361,45 @@
         </is>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
-        <v>-110</v>
+        <v>-185</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philod%C3%A8me_de_Gadara" title="Wikipedia"&gt;PHILODÈME de Gadara&lt;/a&gt; était un philosophe et poète épicurien, originaire de Gadara en Syrie (l'actuelle Jordanie). Élève de Zénon de Sidon à Athènes, il s'installa en Campanie sous la protection du mécène romain Lucius Calpurnius Pison, proche de César, et anima un cercle intellectuel brillant qui accueillit le jeune Virgile et ses amis poètes.&lt;/p&gt; &lt;p&gt;Il défendit et enrichit la philosophie d'&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure" title="Épicure sur Wikipedia"&gt;Épicure&lt;/a&gt; en l'appliquant à des domaines nouveaux : la rhétorique, la musique, l'esthétique et la critique littéraire. Ses traités, longtemps perdus, ont été miraculeusement retrouvés dans la &lt;em&gt;Villa des Papyrus&lt;/em&gt; d'Herculanum, ensevelie par l'éruption du Vésuve en 79 apr. J.-C. Ces rouleaux carbonisés, partiellement déchiffrés grâce aux techniques modernes, constituent une source irremplaçable sur l'épicurisme tardif.&lt;/p&gt; &lt;p&gt;Philodème concilia la rigueur philosophique épicurienne — recherche de l'&lt;em&gt;ataraxie&lt;/em&gt; et du plaisir vertueux — avec une sensibilité poétique et artistique raffinée. Il représente l'épicurisme dans sa version la plus ouverte au monde des arts et de la culture romaine. Ses traités abordent aussi la morale : la colère, la mort, qu’il ne faut pas craindre, ou la « franchise » avec laquelle le maître corrige ses disciples. Poète, il a laissé une trentaine d’épigrammes, souvent amoureuses, conservées dans l’&lt;em&gt;Anthologie grecque&lt;/em&gt;. Les quelque 1 800 rouleaux de la villa, découverts à partir de 1752, sont aujourd’hui déchiffrés grâce à l’imagerie scientifique et à l’intelligence artificielle, sans qu’on ait besoin de les dérouler.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ca2cJql73D4</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Vie et oeuvre de Philodème" par Michel Onfray</t>
-        </is>
+        <v>481</v>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pan%C3%A9tios_de_Rhodes"  title=" Wikipedia"&gt;PANÉTIUS DE RHODES&lt;/a&gt; (vers 185-109 av. J.-C.) est un philosophe stoïcien grec, qui a adapté le stoïcisme au monde romain. Issu d’une grande famille de Rhodes, il étudie à Athènes auprès de Diogène de Babylone, puis s’installe à Rome, où il devient l’ami et le conseiller de Scipion Émilien, le vainqueur de Carthage. Il prend ensuite la tête de l’école stoïcienne d’Athènes, de 129 à sa mort.&lt;/p&gt; &lt;p&gt;Panétius assouplit la &lt;a href="https://www.youtube.com/watch?v=2sbLLblvEZw&amp;ab_channel=Apprendrelaphilosophie"  title="Le Stoïcisme par apprendre la philo"&gt;pensée stoïcienne&lt;/a&gt; et la rapproche de Platon et d’Aristote, qu’il admire. Il abandonne plusieurs thèses de ses prédécesseurs : il doute de la divination, nie la conflagration universelle qui devait périodiquement détruire le monde, qu’il juge éternel, et refuse l’immortalité de l’âme. Surtout, il s’intéresse moins au sage idéal, presque introuvable, qu’à l’homme ordinaire qui progresse vers la sagesse. Sa morale part de la nature humaine : chacun porte en lui des tendances fondamentales où s’unissent la nature et la raison, la recherche de la vérité, le goût de l’ordre, le désir de grandeur d’âme et le sens de la communauté. Chacun doit aussi tenir compte de sa propre nature, de ses talents et de sa situation, comme un acteur choisit le rôle qui lui convient. Il en tire une éthique des « devoirs », les actions convenables de la vie quotidienne et de la vie publique, fondée sur la justice, la bienveillance et le sens de la mesure.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Du devoir&lt;/em&gt; est perdu, mais Cicéron l’a largement repris dans son &lt;em&gt;De officiis&lt;/em&gt;, l’un des livres de morale les plus lus en Europe jusqu’au XIXe siècle. Panétius a ainsi donné au stoïcisme le visage humaniste qu’adopteront les élites romaines.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>484</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>502</v>
+        <v>24</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>503</v>
+        <v>386</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -6368,18 +6409,114 @@
     </row>
     <row r="66" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
+        <v>-135</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Posidonios"  title=" Wikipedia"&gt;POSIDONIOD d'Apamée&lt;/a&gt; était un philosophe stoïcien, &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1914_num_27_121_6770"  title="Posidonius d'Apamée théoricien de la géométrie par Persée"&gt;astronome&lt;/a&gt;, géographe, historien et polymathe. Son œuvre, bien que largement perdue, a eu une influence considérable sur la pensée antique et a servi de pont entre la culture grecque et romaine.&lt;/p&gt; &lt;p&gt;  Il  a vécu à une époque où le monde méditerranéen était dominé par les  &lt;a href="https://www.youtube.com/watch?v=EqU-kD8dW4Y" title="Grèce antique - 33 La civilisation hellénistique par Yannick Rub"&gt;royaumes hellénistiques&lt;/a&gt; issus de la dissolution de l'empire d'Alexandre le Grand. Il a étudié à Athènes sous la direction de Panaitios de Rhodes, un philosophe stoïcien renommé, qui a profondément influencé sa pensée. &lt;/p&gt; &lt;p&gt; Il croyait en un univers ordonné et rationnel, gouverné par le Logos (la raison divine). Cependant, il a apporté des nuances importantes à la doctrine stoïcienne traditionnelle. Par exemple, il a réintroduit des éléments de la pensée d'Aristote et de Platon, en particulier en ce qui concerne la psychologie et l'éthique. Il a soutenu que l'âme humaine avait des aspects irrationnels et émotionnels, ce qui contrastait avec la vision plus austère des premiers stoïciens. Il s'intéressait particulièrement aux coutumes et aux croyances des peuples non-grecs, et ses descriptions des Celtes et des Germains sont parmi les plus anciennes que nous possédions. &lt;/p&gt; &lt;p&gt;Ses idées ont été reprises et développées par des penseurs romains comme Cicéron et Sénèque. En géographie, ses travaux ont servi de référence jusqu'à la fin de l'Antiquité. &lt;a href="https://www.persee.fr/doc/jds_0021-8103_1922_num_20_4_5289"  title="La philosophiede Posidonius par Persee"&gt;Sa synthèse&lt;/a&gt; du stoïcisme avec des éléments platoniciens et aristotéliciens a ouvert la voie à des développements ultérieurs dans la pensée néoplatonicienne et chrétienne. &lt;/p&gt;  </t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="I66" s="9"/>
+      <c r="J66" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7" t="n">
+        <v>-110</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philod%C3%A8me_de_Gadara" title="Wikipedia"&gt;PHILODÈME de Gadara&lt;/a&gt; était un philosophe et poète épicurien, originaire de Gadara en Syrie (l'actuelle Jordanie). Élève de Zénon de Sidon à Athènes, il s'installa en Campanie sous la protection du mécène romain Lucius Calpurnius Pison, proche de César, et anima un cercle intellectuel brillant qui accueillit le jeune Virgile et ses amis poètes.&lt;/p&gt; &lt;p&gt;Il défendit et enrichit la philosophie d'&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picure" title="Épicure sur Wikipedia"&gt;Épicure&lt;/a&gt; en l'appliquant à des domaines nouveaux : la rhétorique, la musique, l'esthétique et la critique littéraire. Ses traités, longtemps perdus, ont été miraculeusement retrouvés dans la &lt;em&gt;Villa des Papyrus&lt;/em&gt; d'Herculanum, ensevelie par l'éruption du Vésuve en 79 apr. J.-C. Ces rouleaux carbonisés, partiellement déchiffrés grâce aux techniques modernes, constituent une source irremplaçable sur l'épicurisme tardif.&lt;/p&gt; &lt;p&gt;Philodème concilia la rigueur philosophique épicurienne — recherche de l'&lt;em&gt;ataraxie&lt;/em&gt; et du plaisir vertueux — avec une sensibilité poétique et artistique raffinée. Il représente l'épicurisme dans sa version la plus ouverte au monde des arts et de la culture romaine. Ses traités abordent aussi la morale : la colère, la mort, qu’il ne faut pas craindre, ou la « franchise » avec laquelle le maître corrige ses disciples. Poète, il a laissé une trentaine d’épigrammes, souvent amoureuses, conservées dans l’&lt;em&gt;Anthologie grecque&lt;/em&gt;. Les quelque 1 800 rouleaux de la villa, découverts à partir de 1752, sont aujourd’hui déchiffrés grâce à l’imagerie scientifique et à l’intelligence artificielle, sans qu’on ait besoin de les dérouler.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ca2cJql73D4</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Vie et oeuvre de Philodème" par Michel Onfray</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="I67" s="9"/>
+      <c r="J67" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7" t="n">
         <v>-106</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B68" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C68" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D68" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Cic%C3%A9ron"  style="color:#6A142A"  title=" Wikipedia"&gt; Marcus CICERON&lt;/a&gt; était un philosophe &lt;a href="https://fr.wiktionary.org/wiki/%C3%A9clectique"  style="color:#88A1E9"  title="L'éclectisme par Wiktionnaire"&gt;Électique&lt;/a&gt; Romain et le premier a rédiger en latin des ouvrages à une époque où le grec domine dans le monde intellectuel. Il est l'héritier d'une triple tradition : sceptique, stoïcienne et platonicienne. &lt;/p&gt; &lt;p&gt; 
 On connait sa théorie de la "nature humaine" qui selon lui est orientée vers la recherche du bien car les êtres humains sont naturellement doués d'une raison qui leur permet de discerner le bien du mal. Il a écrit de nombreux traités philosophiques, dont &lt;a href="https://fr.wikipedia.org/wiki/De_finibus_bonorum_et_malorum"  title="bien et maux par wikipedia"&gt;De Finibus Bonorum et Malorum&lt;/a&gt; (Sur les fins ultimes du bien et du mal) ainsi que "De Oratore", qui décrit l'art de la persuasion et la façon dont il peut être utilisé pour influencer les autres. &lt;/p&gt; &lt;p&gt;  
@@ -6388,317 +6525,224 @@
 </t>
         </is>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F68" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="G66" s="9" t="s">
+      <c r="G68" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="H66" s="9" t="s">
+      <c r="H68" s="9" t="s">
         <v>511</v>
-      </c>
-      <c r="I66" s="9"/>
-      <c r="J66" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="n">
-        <v>-94</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lucr%C3%A8ce"  style="color:#6A142A"  title=" Wikipedia"&gt;LUCRÈCE&lt;/a&gt; (vers 98-55 av. J.-C.) est un poète et philosophe romain, disciple d’Épicure, auteur d’un seul livre, l’un des chefs-d’œuvre de la littérature latine : &lt;em&gt;De la nature des choses&lt;/em&gt; (&lt;em&gt;De rerum natura&lt;/em&gt;). Nous ne savons presque rien de sa vie. La légende, rapportée par saint Jérôme, selon laquelle il serait devenu fou après avoir bu un philtre d’amour et se serait suicidé, a sans doute été inventée par ses adversaires.&lt;/p&gt; &lt;p&gt;Son poème, en six livres et près de 7 400 vers, expose la doctrine de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89picurisme"  style="color:#88A1E9"  title="Epicurisme par Wikipedia"&gt;épicurisme&lt;/a&gt; pour délivrer les hommes de la peur. Rien ne naît de rien, rien ne retourne au néant : tout ce qui existe est fait d’atomes, invisibles et éternels, qui se meuvent dans le vide. En tombant, ils s’écartent parfois légèrement de leur trajectoire : ce &lt;a href="https://www.youtube.com/watch?v=7iQzfXtB4wc&amp;ab_channel=Coursitout"  style="color:#88A1E9"  title="Le clinamen par Coursitout"&gt;&lt;em&gt;clinamen&lt;/em&gt;&lt;/a&gt; explique la rencontre des atomes, la formation des mondes et la liberté humaine. L’âme elle-même est faite d’atomes très fins &lt;a href="https://www.youtube.com/watch?v=VKJsOwjD5P4&amp;ab_channel=librairiemollat"  style="color:#88A1E9"  title="Bernard Combeaud - Lucrèce, la naissance des choses"&gt;et se disperse&lt;/a&gt; à la mort. Il n’y a donc rien à craindre après la mort : « la mort n’est rien pour nous ». Les dieux existent, mais ne s’occupent pas des hommes. Lucrèce dénonce avec force la superstition, qui pousse au crime, comme le sacrifice d’Iphigénie par son propre père : « Tant la religion a pu inspirer de maux ! » Il décrit aussi la naissance de la vie et des sociétés humaines, du langage et des arts, et finit son poème par la terrible peste d’Athènes. Le bonheur est la paix de l’âme, que procurent des plaisirs simples et l’amitié.&lt;/p&gt; &lt;p&gt;Retrouvé en 1417 par l’humaniste Pogge, le poème a marqué Montaigne, Gassendi, les libertins et les Lumières.&lt;/p&gt;  &lt;audio controls title="Comment maîtriser ses passions ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-12.09.2016-ITEMA_21073425-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="I67" s="9"/>
-      <c r="J67" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="n">
-        <v>-20</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philon_d%27Alexandrie"  style="color:#6A142A"  title=" Wikipedia"&gt;PHILON d'Alexandrie&lt;/a&gt;  était un philosophe juif hellénisé qui d'harmonisa la philosophie grecque, en particulier le platonisme et le stoïcisme, avec les enseignements de la Bible hébraïque. &lt;/p&gt; &lt;p&gt; Il a écrit de nombreux traités et des commentaires allégoriques sur les livres de la Torah et a interprété les textes bibliques à travers le prisme de la philosophie grecque, cherchant à dégager des significations philosophiques et morales profondes. Dans son œuvre &lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1962_num_161_1_7742" style="color:#88A1E9" title="Philon d'Alexandrie, De opificio mundi par Persée"&gt;"De Opificio Mundi"&lt;/a&gt;, il explore la Genèse en utilisant des concepts platoniciens. &lt;/p&gt; &lt;p&gt; Il tente de montrer que les enseignements de la Torah sont en harmonie avec les idées des grands philosophes grecs. Certaines de ses œuvres défendent la religion juive contre les critiques des païens et des autres philosophes. Par exemple, dans  &lt;a href="https://www.persee.fr/doc/rjuiv_0484-8616_1968_num_127_1_1588 " style="color:#88A1E9" title="        Schadenfreude chez Philon d'Alexandrie ? Note sur In Flaccum  par Persée"&gt;"Contre Flaccus"&lt;/a&gt; et "L'Ambassade à Gaius", il décrit les persécutions subies par les Juifs d'Alexandrie et plaide pour leurs droits. &lt;/p&gt; &lt;p&gt; Il est souvent considéré comme un précurseur de la philosophie religieuse et de la théologie mystique. &lt;/p&gt; &lt;p&gt;Dieu et le Logos : Il décrit Dieu comme transcendant et inconnaissable, mais il introduit également le concept du Logos comme un intermédiaire entre Dieu et le monde. Le Logos est à la fois la raison divine qui ordonne l'univers et le moyen par lequel Dieu interagit avec le monde. &lt;/p&gt;
-&lt;p&gt;Allégorie : Il utilise largement l'interprétation allégorique pour expliquer les textes bibliques. Il croit que les récits bibliques ont un sens littéral, mais aussi un sens spirituel plus profond qui peut être découvert par l'interprétation philosophique. &lt;/p&gt; &lt;p&gt;Éthique et Vertu : Il insiste sur l'importance de la vertu et de la vie morale. Il croit que l'étude de la philosophie et la pratique des vertus permettent à l'âme de se rapprocher de Dieu. &lt;/p&gt; &lt;p&gt; Bien qu'il soit resté fidèle au judaïsme, sa pensée a eu une influence significative sur les premiers penseurs chrétiens, tels que Clément d'Alexandrie et Origène. Son concept du Logos a notamment influencé la christologie chrétienne. &lt;/p&gt; &lt;p&gt; </t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>536</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="2" t="s">
-        <v>537</v>
+        <v>512</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>538</v>
+        <v>386</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="N68" s="0" t="s">
-        <v>540</v>
-      </c>
-      <c r="O68" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>513</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
-        <v>-4</v>
+        <v>-94</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>542</v>
+        <v>515</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="E69" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9n%C3%A8que" title=" Wikipedia"&gt;SENEQUE&lt;/a&gt; était un philosophe, écrivain et homme d'état romain et il est l'un des principaux représentants de l'école de pensée  &lt;a href="https://www.youtube.com/watch?v=kiDRr1Ud22I&amp;t=1561s&amp;ab_channel=LePr%C3%A9cepteur"  title="Le Stoïcisme par le Précepteur"&gt; Stoicienne.&lt;/a&gt; Il appartenait à une famille aisée et reçut une éducation riche en rhétorique et en philosophie grecque. Il devint un conseiller influent à la cour impériale, notamment précepteur puis conseiller de l’empereur Néron, dont il aurait rédigé plusieurs discours et joué un rôle dans la politique des premières années de son règne. Après la mort du préfet du prétoire Burrus en 62, il perdit progressivement du pouvoir et, accusé de complot contre l’empereur, il fut contraint de se suicider en ouvrant ses veines en 65, selon une scène souvent décrite comme très stoïque.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=J3wZoqElCgs" title="Who is Seneca par Daily Stoic "&gt; Sa philosophie &lt;/a&gt; est ancrée dans le st